--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.gemini\antigravity\scratch\Idle-RPG\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18754898-69F7-4DB5-B6AF-E16CF6D25A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5999100B-BB67-47C4-BAF6-BC2EC0C31CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18585,43 +18585,43 @@
       </c>
       <c r="G207" s="2">
         <f>計算表!G207</f>
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="H207" s="2">
         <f>計算表!H207</f>
-        <v>10000</v>
+        <v>100000</v>
       </c>
       <c r="I207" s="2">
         <f>計算表!I207</f>
-        <v>20000</v>
+        <v>500000</v>
       </c>
       <c r="J207" s="2">
         <f>計算表!J207</f>
-        <v>40000</v>
+        <v>2000000</v>
       </c>
       <c r="K207" s="2">
         <f>計算表!K207</f>
-        <v>80000</v>
+        <v>10000000</v>
       </c>
       <c r="L207" s="2">
         <f>計算表!L207</f>
-        <v>800000</v>
+        <v>50000000</v>
       </c>
       <c r="M207" s="2">
         <f>計算表!M207</f>
-        <v>8000000</v>
+        <v>200000000</v>
       </c>
       <c r="N207" s="2">
         <f>計算表!N207</f>
-        <v>80000000</v>
+        <v>1000000000</v>
       </c>
       <c r="O207" s="2">
         <f>計算表!O207</f>
-        <v>800000000</v>
+        <v>10000000000</v>
       </c>
       <c r="P207" s="2">
         <f>計算表!P207</f>
-        <v>8000000000</v>
+        <v>1000000000000</v>
       </c>
       <c r="Q207" s="2">
         <f>計算表!Q207</f>
@@ -36262,6 +36262,9 @@
     <col min="7" max="7" width="15.42578125" customWidth="1"/>
     <col min="8" max="8" width="15.140625" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -41589,35 +41592,35 @@
       <c r="F207" t="s">
         <v>551</v>
       </c>
-      <c r="G207">
-        <v>5000</v>
-      </c>
-      <c r="H207">
+      <c r="G207" s="1">
         <v>10000</v>
       </c>
-      <c r="I207">
-        <v>20000</v>
-      </c>
-      <c r="J207">
-        <v>40000</v>
-      </c>
-      <c r="K207">
-        <v>80000</v>
-      </c>
-      <c r="L207">
-        <v>800000</v>
-      </c>
-      <c r="M207">
-        <v>8000000</v>
-      </c>
-      <c r="N207">
-        <v>80000000</v>
-      </c>
-      <c r="O207">
-        <v>800000000</v>
-      </c>
-      <c r="P207">
-        <v>8000000000</v>
+      <c r="H207" s="1">
+        <v>100000</v>
+      </c>
+      <c r="I207" s="1">
+        <v>500000</v>
+      </c>
+      <c r="J207" s="1">
+        <v>2000000</v>
+      </c>
+      <c r="K207" s="1">
+        <v>10000000</v>
+      </c>
+      <c r="L207" s="1">
+        <v>50000000</v>
+      </c>
+      <c r="M207" s="1">
+        <v>200000000</v>
+      </c>
+      <c r="N207" s="1">
+        <v>1000000000</v>
+      </c>
+      <c r="O207" s="1">
+        <v>10000000000</v>
+      </c>
+      <c r="P207" s="1">
+        <v>1000000000000</v>
       </c>
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.25">

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.gemini\antigravity\scratch\Idle-RPG\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D6B7BA-528F-4FF5-AF7E-91A0C7C4DE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD59C419-050D-4347-8AB2-74A5E5D801C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2332" uniqueCount="993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2333" uniqueCount="994">
   <si>
     <t>編號</t>
   </si>
@@ -2898,9 +2898,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>a=全局減傷上限（%）。於最終傷害階段對所有傷害生效，上限 85%。　※此列與「2-屬性派生/全局減傷」重複，實際上限由該列控制，本列不生效。</t>
-  </si>
-  <si>
     <t>a=太古倍率（=原上限的 135%）。　※實際由「5-太古詞條/太古詞條數值倍率」控制，本列不生效。</t>
   </si>
   <si>
@@ -3056,6 +3053,14 @@
   </si>
   <si>
     <t>魔法防禦</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刪除</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>a=全局減傷上限（%）已經不設上限。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3067,7 +3072,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3104,6 +3109,13 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -3128,7 +3140,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3138,6 +3150,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -7708,9 +7721,9 @@
         <f>計算表!A59</f>
         <v>58</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="2" t="str">
         <f>計算表!B59</f>
-        <v>0</v>
+        <v>刪除</v>
       </c>
       <c r="C59" t="str">
         <f>計算表!C59</f>
@@ -7726,7 +7739,7 @@
       </c>
       <c r="F59" t="str">
         <f>計算表!F59</f>
-        <v>a=全局減傷上限（%）。於最終傷害階段對所有傷害生效，上限 85%。　※此列與「2-屬性派生/全局減傷」重複，實際上限由該列控制，本列不生效。</v>
+        <v>a=全局減傷上限（%）已經不設上限。</v>
       </c>
       <c r="G59">
         <f>計算表!G59</f>
@@ -36999,7 +37012,7 @@
         <v>37</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="G9" s="3">
         <v>1</v>
@@ -37554,10 +37567,10 @@
         <v>69</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>89</v>
@@ -37605,13 +37618,13 @@
         <v>69</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E28" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>988</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>989</v>
       </c>
       <c r="G28" s="3">
         <v>0.875</v>
@@ -37680,10 +37693,10 @@
         <v>99</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>983</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>984</v>
       </c>
       <c r="G31" s="3">
         <v>1E-4</v>
@@ -37701,10 +37714,10 @@
         <v>100</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="G32" s="3">
         <v>1E-4</v>
@@ -38264,6 +38277,9 @@
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
+      <c r="B59" s="3" t="s">
+        <v>992</v>
+      </c>
       <c r="C59" s="3" t="s">
         <v>110</v>
       </c>
@@ -38273,8 +38289,8 @@
       <c r="E59" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>945</v>
+      <c r="F59" s="5" t="s">
+        <v>993</v>
       </c>
       <c r="G59" s="3">
         <v>85</v>
@@ -38292,7 +38308,7 @@
         <v>137</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>138</v>
@@ -38448,7 +38464,7 @@
         <v>149</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="G67" s="3">
         <v>10000</v>
@@ -38628,7 +38644,7 @@
         <v>169</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="G75" s="3">
         <v>100</v>
@@ -38802,10 +38818,10 @@
         <v>99</v>
       </c>
       <c r="E82" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="F82" s="3" t="s">
         <v>973</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>974</v>
       </c>
       <c r="G82" s="3">
         <v>100</v>
@@ -38823,13 +38839,13 @@
         <v>178</v>
       </c>
       <c r="D83" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>978</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="F83" s="3" t="s">
         <v>979</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>980</v>
       </c>
       <c r="G83" s="3">
         <v>10</v>
@@ -39141,10 +39157,10 @@
         <v>99</v>
       </c>
       <c r="E95" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="F95" s="3" t="s">
         <v>975</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>976</v>
       </c>
       <c r="G95" s="3">
         <v>200</v>
@@ -39279,13 +39295,13 @@
         <v>207</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E101" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="F101" s="3" t="s">
         <v>981</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>982</v>
       </c>
       <c r="G101" s="3">
         <v>20</v>
@@ -39528,7 +39544,7 @@
         <v>252</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -40914,7 +40930,7 @@
         <v>383</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.25">
@@ -40932,7 +40948,7 @@
         <v>385</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="G158" s="3">
         <v>1.35</v>
@@ -40974,7 +40990,7 @@
         <v>390</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G160" s="3">
         <v>2</v>
@@ -40995,7 +41011,7 @@
         <v>392</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.25">
@@ -41583,7 +41599,7 @@
         <v>453</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="184" spans="1:15" x14ac:dyDescent="0.25">
@@ -41649,7 +41665,7 @@
         <v>459</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>460</v>
@@ -41667,13 +41683,13 @@
         <v>454</v>
       </c>
       <c r="D187" s="3" t="s">
+        <v>984</v>
+      </c>
+      <c r="E187" s="3" t="s">
         <v>985</v>
       </c>
-      <c r="E187" s="3" t="s">
+      <c r="F187" s="3" t="s">
         <v>986</v>
-      </c>
-      <c r="F187" s="3" t="s">
-        <v>987</v>
       </c>
       <c r="G187" s="3">
         <v>1</v>
@@ -41739,7 +41755,7 @@
         <v>466</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="190" spans="1:15" x14ac:dyDescent="0.25">
@@ -41757,7 +41773,7 @@
         <v>468</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="191" spans="1:15" x14ac:dyDescent="0.25">
@@ -41775,7 +41791,7 @@
         <v>470</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="192" spans="1:15" x14ac:dyDescent="0.25">
@@ -41793,7 +41809,7 @@
         <v>473</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="G192" s="3">
         <v>2</v>
@@ -41982,7 +41998,7 @@
         <v>500</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="G201" s="3">
         <v>3</v>
@@ -42099,7 +42115,7 @@
         <v>514</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="G206" s="3">
         <v>0.7</v>
@@ -42147,7 +42163,7 @@
         <v>519</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.25">
@@ -43686,7 +43702,7 @@
         <v>676</v>
       </c>
       <c r="F255" s="3" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.25">
@@ -43704,7 +43720,7 @@
         <v>678</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -43809,7 +43825,7 @@
         <v>690</v>
       </c>
       <c r="F261" s="3" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
@@ -43923,7 +43939,7 @@
         <v>704</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.25">
@@ -43941,7 +43957,7 @@
         <v>706</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="G267" s="3">
         <v>0.1</v>
@@ -43983,7 +43999,7 @@
         <v>712</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.25">
@@ -44001,7 +44017,7 @@
         <v>714</v>
       </c>
       <c r="F270" s="3" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.25">
@@ -44019,7 +44035,7 @@
         <v>716</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="G271" s="3">
         <v>0.8</v>
@@ -44064,7 +44080,7 @@
         <v>721</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="G273" s="3">
         <v>30</v>
@@ -47556,7 +47572,7 @@
         <v>888</v>
       </c>
       <c r="F392" s="3" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G392" s="3">
         <v>2</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.gemini\antigravity\scratch\Idle-RPG\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3785F69D-961E-418D-B5A4-DD945B61D6C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED81ECA-E855-495D-AD0C-27F2B3B7D5BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -23184,7 +23184,7 @@
       </c>
       <c r="G269">
         <f>計算表!G269</f>
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H269">
         <f>計算表!H269</f>
@@ -37242,7 +37242,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <f t="shared" ref="A4:A256" si="0">A3+1</f>
+        <f t="shared" ref="A4:A106" si="0">A3+1</f>
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -44392,7 +44392,7 @@
         <v>778</v>
       </c>
       <c r="G269" s="3">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.25">

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.gemini\antigravity\scratch\Idle-RPG\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED81ECA-E855-495D-AD0C-27F2B3B7D5BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB653FB6-5548-4482-972E-6DDC521B688E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5354,11 +5354,11 @@
       </c>
       <c r="H28">
         <f>計算表!H28</f>
-        <v>1.387E-2</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="I28">
         <f>計算表!I28</f>
-        <v>8.6099999999999996E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J28">
         <f>計算表!J28</f>
@@ -37996,10 +37996,10 @@
         <v>0.875</v>
       </c>
       <c r="H28" s="3">
-        <v>1.387E-2</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="I28" s="3">
-        <v>8.6099999999999996E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -26436,7 +26436,7 @@
       </c>
       <c r="F313" t="str">
         <f>計算表!F313</f>
-        <v>a=一級基準 b=每級成長係數 c=出現權重 d=最低稀有度 e=百分比。放出量同「物理防禦」詞條；僅對非菁英且非 BOSS 的普通敵人生效。</v>
+        <v>a=一級基準 b=每級成長係數 c=出現權重 d=最低稀有度 e=百分比。基礎值恢復 10 倍；成長係數維持原值；僅對非菁英且非 BOSS 的普通敵人生效。</v>
       </c>
       <c r="G313">
         <f>計算表!G313</f>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="H313">
         <f>計算表!H313</f>
-        <v>0.35</v>
+        <v>0.035</v>
       </c>
       <c r="I313">
         <f>計算表!I313</f>
@@ -45838,7 +45838,7 @@
         <v>3</v>
       </c>
       <c r="H313" s="3">
-        <v>0.35</v>
+        <v>0.035</v>
       </c>
       <c r="I313" s="3">
         <v>9</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.gemini\antigravity\scratch\Idle-RPG\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A00D1A7-8497-43D6-AE22-B059B8A77FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACB37FB-0A08-431A-9F11-96B3A676C90C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
     <sheet name="計算表" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -5364,11 +5363,11 @@
       </c>
       <c r="H28">
         <f>計算表!H28</f>
-        <v>8.0000000000000002E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="I28">
         <f>計算表!I28</f>
-        <v>2.5000000000000001E-2</v>
+        <v>0.05</v>
       </c>
       <c r="J28">
         <f>計算表!J28</f>
@@ -38080,10 +38079,10 @@
         <v>0.875</v>
       </c>
       <c r="H28" s="3">
-        <v>8.0000000000000002E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="I28" s="3">
-        <v>2.5000000000000001E-2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -3341,9 +3341,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R469"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" ns3:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.140625" style="1"/>
     <col min="3" max="3" width="18.28515625" customWidth="1"/>
@@ -3352,7 +3352,7 @@
     <col min="6" max="6" width="91.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ns3:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3408,7 +3408,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ns3:dyDescent="0.25">
       <c r="A2">
         <f>計算表!A2</f>
         <v>1</v>
@@ -3482,7 +3482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ns3:dyDescent="0.25">
       <c r="A3">
         <f>計算表!A3</f>
         <v>2</v>
@@ -3556,7 +3556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ns3:dyDescent="0.25">
       <c r="A4">
         <f>計算表!A4</f>
         <v>3</v>
@@ -3630,7 +3630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ns3:dyDescent="0.25">
       <c r="A5">
         <f>計算表!A5</f>
         <v>4</v>
@@ -3704,7 +3704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ns3:dyDescent="0.25">
       <c r="A6">
         <f>計算表!A6</f>
         <v>5</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ns3:dyDescent="0.25">
       <c r="A7">
         <f>計算表!A7</f>
         <v>6</v>
@@ -3852,7 +3852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ns3:dyDescent="0.25">
       <c r="A8">
         <f>計算表!A8</f>
         <v>7</v>
@@ -3926,7 +3926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ns3:dyDescent="0.25">
       <c r="A9">
         <f>計算表!A9</f>
         <v>8</v>
@@ -4000,7 +4000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ns3:dyDescent="0.25">
       <c r="A10">
         <f>計算表!A10</f>
         <v>9</v>
@@ -4074,7 +4074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ns3:dyDescent="0.25">
       <c r="A11">
         <f>計算表!A11</f>
         <v>10</v>
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ns3:dyDescent="0.25">
       <c r="A12">
         <f>計算表!A12</f>
         <v>11</v>
@@ -4222,7 +4222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ns3:dyDescent="0.25">
       <c r="A13">
         <f>計算表!A13</f>
         <v>12</v>
@@ -4296,7 +4296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ns3:dyDescent="0.25">
       <c r="A14">
         <f>計算表!A14</f>
         <v>13</v>
@@ -4370,7 +4370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ns3:dyDescent="0.25">
       <c r="A15">
         <f>計算表!A15</f>
         <v>14</v>
@@ -4444,7 +4444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ns3:dyDescent="0.25">
       <c r="A16">
         <f>計算表!A16</f>
         <v>15</v>
@@ -4518,7 +4518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ns3:dyDescent="0.25">
       <c r="A17">
         <f>計算表!A17</f>
         <v>16</v>
@@ -4592,7 +4592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ns3:dyDescent="0.25">
       <c r="A18">
         <f>計算表!A18</f>
         <v>17</v>
@@ -4666,7 +4666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ns3:dyDescent="0.25">
       <c r="A19">
         <f>計算表!A19</f>
         <v>18</v>
@@ -4740,7 +4740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ns3:dyDescent="0.25">
       <c r="A20">
         <f>計算表!A20</f>
         <v>19</v>
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ns3:dyDescent="0.25">
       <c r="A21">
         <f>計算表!A21</f>
         <v>20</v>
@@ -4888,7 +4888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ns3:dyDescent="0.25">
       <c r="A22">
         <f>計算表!A22</f>
         <v>21</v>
@@ -4962,7 +4962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ns3:dyDescent="0.25">
       <c r="A23">
         <f>計算表!A23</f>
         <v>22</v>
@@ -5036,7 +5036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ns3:dyDescent="0.25">
       <c r="A24">
         <f>計算表!A24</f>
         <v>23</v>
@@ -5110,7 +5110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ns3:dyDescent="0.25">
       <c r="A25">
         <f>計算表!A25</f>
         <v>24</v>
@@ -5184,7 +5184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ns3:dyDescent="0.25">
       <c r="A26">
         <f>計算表!A26</f>
         <v>25</v>
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ns3:dyDescent="0.25">
       <c r="A27">
         <f>計算表!A27</f>
         <v>26</v>
@@ -5332,7 +5332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ns3:dyDescent="0.25">
       <c r="A28">
         <f>計算表!A28</f>
         <v>27</v>
@@ -5406,7 +5406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ns3:dyDescent="0.25">
       <c r="A29">
         <f>計算表!A29</f>
         <v>28</v>
@@ -5480,7 +5480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ns3:dyDescent="0.25">
       <c r="A30">
         <f>計算表!A30</f>
         <v>29</v>
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ns3:dyDescent="0.25">
       <c r="A31">
         <f>計算表!A31</f>
         <v>30</v>
@@ -5628,7 +5628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ns3:dyDescent="0.25">
       <c r="A32">
         <f>計算表!A32</f>
         <v>31</v>
@@ -5702,7 +5702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ns3:dyDescent="0.25">
       <c r="A33">
         <f>計算表!A33</f>
         <v>32</v>
@@ -5776,7 +5776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ns3:dyDescent="0.25">
       <c r="A34">
         <f>計算表!A34</f>
         <v>33</v>
@@ -5850,7 +5850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ns3:dyDescent="0.25">
       <c r="A35">
         <f>計算表!A35</f>
         <v>34</v>
@@ -5924,7 +5924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ns3:dyDescent="0.25">
       <c r="A36">
         <f>計算表!A36</f>
         <v>35</v>
@@ -5998,7 +5998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" ns3:dyDescent="0.25">
       <c r="A37">
         <f>計算表!A37</f>
         <v>36</v>
@@ -6072,7 +6072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ns3:dyDescent="0.25">
       <c r="A38">
         <f>計算表!A38</f>
         <v>37</v>
@@ -6146,7 +6146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" ns3:dyDescent="0.25">
       <c r="A39">
         <f>計算表!A39</f>
         <v>38</v>
@@ -6220,7 +6220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ns3:dyDescent="0.25">
       <c r="A40">
         <f>計算表!A40</f>
         <v>39</v>
@@ -6294,7 +6294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" ns3:dyDescent="0.25">
       <c r="A41">
         <f>計算表!A41</f>
         <v>40</v>
@@ -6368,7 +6368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" ns3:dyDescent="0.25">
       <c r="A42">
         <f>計算表!A42</f>
         <v>41</v>
@@ -6442,7 +6442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" ns3:dyDescent="0.25">
       <c r="A43">
         <f>計算表!A43</f>
         <v>42</v>
@@ -6516,7 +6516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ns3:dyDescent="0.25">
       <c r="A44">
         <f>計算表!A44</f>
         <v>43</v>
@@ -6590,7 +6590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" ns3:dyDescent="0.25">
       <c r="A45">
         <f>計算表!A45</f>
         <v>44</v>
@@ -6664,7 +6664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ns3:dyDescent="0.25">
       <c r="A46">
         <f>計算表!A46</f>
         <v>45</v>
@@ -6738,229 +6738,199 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ns3:dyDescent="0.25">
       <c r="A47">
-        <f>計算表!A47</f>
         <v>46</v>
       </c>
       <c r="B47" s="2">
-        <f>計算表!B47</f>
-        <v>0</v>
-      </c>
-      <c r="C47" t="str">
-        <f>計算表!C47</f>
-        <v>2-屬性上限</v>
-      </c>
-      <c r="D47" t="str">
-        <f>計算表!D47</f>
-        <v>物理抗性 上限</v>
-      </c>
-      <c r="E47" t="str">
-        <f>計算表!E47</f>
-        <v>上限 = a</v>
-      </c>
-      <c r="F47" t="str">
-        <f>計算表!F47</f>
-        <v>a=物理抗性上限（%）。結算防禦後再按比例直接減免物理傷害。</v>
+        <v>0</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>3-戰鬥核心</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>物理抗性減傷</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>抗性總合^a/(抗性總合^a+b+c×敵人等級)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>a=抗性次方 b=分母常數 c=敵人等級係數。抗性≤0 時不減傷。</t>
+        </is>
       </c>
       <c r="G47">
-        <f>計算表!G47</f>
-        <v>95</v>
+        <v>1.8</v>
       </c>
       <c r="H47">
-        <f>計算表!H47</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I47">
-        <f>計算表!I47</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J47">
-        <f>計算表!J47</f>
         <v>0</v>
       </c>
       <c r="K47">
-        <f>計算表!K47</f>
         <v>0</v>
       </c>
       <c r="L47">
-        <f>計算表!L47</f>
         <v>0</v>
       </c>
       <c r="M47">
-        <f>計算表!M47</f>
         <v>0</v>
       </c>
       <c r="N47">
-        <f>計算表!N47</f>
         <v>0</v>
       </c>
       <c r="O47">
-        <f>計算表!O47</f>
         <v>0</v>
       </c>
       <c r="P47">
-        <f>計算表!P47</f>
         <v>0</v>
       </c>
       <c r="Q47">
-        <f>計算表!Q47</f>
         <v>0</v>
       </c>
       <c r="R47">
-        <f>計算表!R47</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ns3:dyDescent="0.25">
       <c r="A48">
-        <f>計算表!A48</f>
         <v>47</v>
       </c>
       <c r="B48" s="2">
-        <f>計算表!B48</f>
-        <v>0</v>
-      </c>
-      <c r="C48" t="str">
-        <f>計算表!C48</f>
-        <v>2-屬性上限</v>
-      </c>
-      <c r="D48" t="str">
-        <f>計算表!D48</f>
-        <v>魔法抗性 上限</v>
-      </c>
-      <c r="E48" t="str">
-        <f>計算表!E48</f>
-        <v>上限 = a</v>
-      </c>
-      <c r="F48" t="str">
-        <f>計算表!F48</f>
-        <v>a=魔法抗性上限（%）。結算防禦後再按比例直接減免魔法傷害。</v>
+        <v>0</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>3-戰鬥核心</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>魔法抗性減傷</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>抗性總合^a/(抗性總合^a+b+c×敵人等級)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>a=抗性次方 b=分母常數 c=敵人等級係數。抗性≤0 時不減傷。</t>
+        </is>
       </c>
       <c r="G48">
-        <f>計算表!G48</f>
-        <v>95</v>
+        <v>1.8</v>
       </c>
       <c r="H48">
-        <f>計算表!H48</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I48">
-        <f>計算表!I48</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J48">
-        <f>計算表!J48</f>
         <v>0</v>
       </c>
       <c r="K48">
-        <f>計算表!K48</f>
         <v>0</v>
       </c>
       <c r="L48">
-        <f>計算表!L48</f>
         <v>0</v>
       </c>
       <c r="M48">
-        <f>計算表!M48</f>
         <v>0</v>
       </c>
       <c r="N48">
-        <f>計算表!N48</f>
         <v>0</v>
       </c>
       <c r="O48">
-        <f>計算表!O48</f>
         <v>0</v>
       </c>
       <c r="P48">
-        <f>計算表!P48</f>
         <v>0</v>
       </c>
       <c r="Q48">
-        <f>計算表!Q48</f>
         <v>0</v>
       </c>
       <c r="R48">
-        <f>計算表!R48</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ns3:dyDescent="0.25">
       <c r="A49">
-        <f>計算表!A49</f>
         <v>48</v>
       </c>
       <c r="B49" s="2">
-        <f>計算表!B49</f>
-        <v>0</v>
-      </c>
-      <c r="C49" t="str">
-        <f>計算表!C49</f>
-        <v>2-屬性上限</v>
-      </c>
-      <c r="D49" t="str">
-        <f>計算表!D49</f>
-        <v>六系元素抗性 上限</v>
-      </c>
-      <c r="E49" t="str">
-        <f>計算表!E49</f>
-        <v>上限 = a</v>
-      </c>
-      <c r="F49" t="str">
-        <f>計算表!F49</f>
-        <v>a=六系元素（火/冰/雷/毒/光/暗）抗性各自的上限（%）。按比例降低該屬性傷害。</v>
+        <v>0</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>3-戰鬥核心</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>六系元素抗性減傷</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>抗性總合^a/(抗性總合^a+b+c×敵人等級)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>a=抗性次方 b=分母常數 c=敵人等級係數。六系元素共用此曲線；抗性≤0 時不減傷。</t>
+        </is>
       </c>
       <c r="G49">
-        <f>計算表!G49</f>
-        <v>95</v>
+        <v>1.8</v>
       </c>
       <c r="H49">
-        <f>計算表!H49</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I49">
-        <f>計算表!I49</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J49">
-        <f>計算表!J49</f>
         <v>0</v>
       </c>
       <c r="K49">
-        <f>計算表!K49</f>
         <v>0</v>
       </c>
       <c r="L49">
-        <f>計算表!L49</f>
         <v>0</v>
       </c>
       <c r="M49">
-        <f>計算表!M49</f>
         <v>0</v>
       </c>
       <c r="N49">
-        <f>計算表!N49</f>
         <v>0</v>
       </c>
       <c r="O49">
-        <f>計算表!O49</f>
         <v>0</v>
       </c>
       <c r="P49">
-        <f>計算表!P49</f>
         <v>0</v>
       </c>
       <c r="Q49">
-        <f>計算表!Q49</f>
         <v>0</v>
       </c>
       <c r="R49">
-        <f>計算表!R49</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ns3:dyDescent="0.25">
       <c r="A50">
         <f>計算表!A50</f>
         <v>49</v>
@@ -7034,7 +7004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ns3:dyDescent="0.25">
       <c r="A51">
         <f>計算表!A51</f>
         <v>50</v>
@@ -7108,7 +7078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ns3:dyDescent="0.25">
       <c r="A52">
         <f>計算表!A52</f>
         <v>51</v>
@@ -7182,7 +7152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ns3:dyDescent="0.25">
       <c r="A53">
         <f>計算表!A53</f>
         <v>52</v>
@@ -7256,7 +7226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ns3:dyDescent="0.25">
       <c r="A54">
         <f>計算表!A54</f>
         <v>53</v>
@@ -7330,7 +7300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ns3:dyDescent="0.25">
       <c r="A55">
         <f>計算表!A55</f>
         <v>54</v>
@@ -7404,7 +7374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ns3:dyDescent="0.25">
       <c r="A56">
         <f>計算表!A56</f>
         <v>55</v>
@@ -7478,7 +7448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ns3:dyDescent="0.25">
       <c r="A57">
         <f>計算表!A57</f>
         <v>56</v>
@@ -7552,7 +7522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ns3:dyDescent="0.25">
       <c r="A58">
         <f>計算表!A58</f>
         <v>57</v>
@@ -7626,7 +7596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ns3:dyDescent="0.25">
       <c r="A59">
         <f>計算表!A59</f>
         <v>58</v>
@@ -7700,7 +7670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" ns3:dyDescent="0.25">
       <c r="A60">
         <f>計算表!A60</f>
         <v>59</v>
@@ -7774,7 +7744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ns3:dyDescent="0.25">
       <c r="A61">
         <f>計算表!A61</f>
         <v>60</v>
@@ -7848,7 +7818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ns3:dyDescent="0.25">
       <c r="A62">
         <f>計算表!A62</f>
         <v>61</v>
@@ -7922,7 +7892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" ns3:dyDescent="0.25">
       <c r="A63">
         <f>計算表!A63</f>
         <v>62</v>
@@ -7996,7 +7966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" ns3:dyDescent="0.25">
       <c r="A64">
         <f>計算表!A64</f>
         <v>63</v>
@@ -8070,7 +8040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" ns3:dyDescent="0.25">
       <c r="A65">
         <f>計算表!A65</f>
         <v>64</v>
@@ -8144,7 +8114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" ns3:dyDescent="0.25">
       <c r="A66">
         <f>計算表!A66</f>
         <v>65</v>
@@ -8218,7 +8188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" ns3:dyDescent="0.25">
       <c r="A67">
         <f>計算表!A67</f>
         <v>66</v>
@@ -8292,7 +8262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" ns3:dyDescent="0.25">
       <c r="A68">
         <f>計算表!A68</f>
         <v>67</v>
@@ -8366,7 +8336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" ns3:dyDescent="0.25">
       <c r="A69">
         <f>計算表!A69</f>
         <v>68</v>
@@ -8440,7 +8410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" ns3:dyDescent="0.25">
       <c r="A70">
         <f>計算表!A70</f>
         <v>69</v>
@@ -8514,7 +8484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" ns3:dyDescent="0.25">
       <c r="A71">
         <f>計算表!A71</f>
         <v>70</v>
@@ -8588,7 +8558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" ns3:dyDescent="0.25">
       <c r="A72">
         <f>計算表!A72</f>
         <v>71</v>
@@ -8662,7 +8632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" ns3:dyDescent="0.25">
       <c r="A73">
         <f>計算表!A73</f>
         <v>72</v>
@@ -8736,7 +8706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" ns3:dyDescent="0.25">
       <c r="A74">
         <f>計算表!A74</f>
         <v>73</v>
@@ -8810,7 +8780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" ns3:dyDescent="0.25">
       <c r="A75">
         <f>計算表!A75</f>
         <v>74</v>
@@ -8884,7 +8854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" ns3:dyDescent="0.25">
       <c r="A76">
         <f>計算表!A76</f>
         <v>75</v>
@@ -8958,7 +8928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" ns3:dyDescent="0.25">
       <c r="A77">
         <f>計算表!A77</f>
         <v>76</v>
@@ -9032,7 +9002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" ns3:dyDescent="0.25">
       <c r="A78">
         <f>計算表!A78</f>
         <v>77</v>
@@ -9106,7 +9076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" ns3:dyDescent="0.25">
       <c r="A79">
         <f>計算表!A79</f>
         <v>78</v>
@@ -9180,7 +9150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" ns3:dyDescent="0.25">
       <c r="A80">
         <f>計算表!A80</f>
         <v>79</v>
@@ -9254,7 +9224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ns3:dyDescent="0.25">
       <c r="A81">
         <f>計算表!A81</f>
         <v>80</v>
@@ -9328,7 +9298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ns3:dyDescent="0.25">
       <c r="A82">
         <f>計算表!A82</f>
         <v>81</v>
@@ -9402,7 +9372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ns3:dyDescent="0.25">
       <c r="A83">
         <f>計算表!A83</f>
         <v>82</v>
@@ -9476,7 +9446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" ns3:dyDescent="0.25">
       <c r="A84">
         <f>計算表!A84</f>
         <v>83</v>
@@ -9550,7 +9520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" ns3:dyDescent="0.25">
       <c r="A85">
         <f>計算表!A85</f>
         <v>84</v>
@@ -9624,7 +9594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" ns3:dyDescent="0.25">
       <c r="A86">
         <f>計算表!A86</f>
         <v>85</v>
@@ -9698,7 +9668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" ns3:dyDescent="0.25">
       <c r="A87">
         <f>計算表!A87</f>
         <v>86</v>
@@ -9772,7 +9742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ns3:dyDescent="0.25">
       <c r="A88">
         <f>計算表!A88</f>
         <v>87</v>
@@ -9846,7 +9816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" ns3:dyDescent="0.25">
       <c r="A89">
         <f>計算表!A89</f>
         <v>88</v>
@@ -9920,7 +9890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" ns3:dyDescent="0.25">
       <c r="A90">
         <f>計算表!A90</f>
         <v>89</v>
@@ -9994,7 +9964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" ns3:dyDescent="0.25">
       <c r="A91">
         <f>計算表!A91</f>
         <v>90</v>
@@ -10068,7 +10038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" ns3:dyDescent="0.25">
       <c r="A92">
         <f>計算表!A92</f>
         <v>91</v>
@@ -10142,7 +10112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" ns3:dyDescent="0.25">
       <c r="A93">
         <f>計算表!A93</f>
         <v>92</v>
@@ -10216,7 +10186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" ns3:dyDescent="0.25">
       <c r="A94">
         <f>計算表!A94</f>
         <v>93</v>
@@ -10290,7 +10260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" ns3:dyDescent="0.25">
       <c r="A95">
         <f>計算表!A95</f>
         <v>94</v>
@@ -10364,7 +10334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" ns3:dyDescent="0.25">
       <c r="A96">
         <f>計算表!A96</f>
         <v>95</v>
@@ -10438,7 +10408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" ns3:dyDescent="0.25">
       <c r="A97">
         <f>計算表!A97</f>
         <v>96</v>
@@ -10512,7 +10482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" ns3:dyDescent="0.25">
       <c r="A98">
         <f>計算表!A98</f>
         <v>97</v>
@@ -10586,7 +10556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" ns3:dyDescent="0.25">
       <c r="A99">
         <f>計算表!A99</f>
         <v>98</v>
@@ -10660,7 +10630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" ns3:dyDescent="0.25">
       <c r="A100">
         <f>計算表!A100</f>
         <v>99</v>
@@ -10734,7 +10704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" ns3:dyDescent="0.25">
       <c r="A101">
         <f>計算表!A101</f>
         <v>100</v>
@@ -10808,7 +10778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" ns3:dyDescent="0.25">
       <c r="A102">
         <f>計算表!A102</f>
         <v>101</v>
@@ -10882,7 +10852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" ns3:dyDescent="0.25">
       <c r="A103">
         <f>計算表!A103</f>
         <v>102</v>
@@ -10956,7 +10926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" ns3:dyDescent="0.25">
       <c r="A104">
         <f>計算表!A104</f>
         <v>103</v>
@@ -11030,7 +11000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" ns3:dyDescent="0.25">
       <c r="A105">
         <f>計算表!A105</f>
         <v>104</v>
@@ -11104,7 +11074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" ns3:dyDescent="0.25">
       <c r="A106">
         <f>計算表!A106</f>
         <v>105</v>
@@ -11178,7 +11148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" ns3:dyDescent="0.25">
       <c r="A107">
         <f>計算表!A107</f>
         <v>106</v>
@@ -11252,7 +11222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" ns3:dyDescent="0.25">
       <c r="A108">
         <f>計算表!A108</f>
         <v>107</v>
@@ -11326,7 +11296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" ns3:dyDescent="0.25">
       <c r="A109">
         <f>計算表!A109</f>
         <v>108</v>
@@ -11400,7 +11370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" ns3:dyDescent="0.25">
       <c r="A110">
         <f>計算表!A110</f>
         <v>109</v>
@@ -11474,7 +11444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" ns3:dyDescent="0.25">
       <c r="A111">
         <f>計算表!A111</f>
         <v>110</v>
@@ -11548,7 +11518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" ns3:dyDescent="0.25">
       <c r="A112">
         <f>計算表!A112</f>
         <v>111</v>
@@ -11622,7 +11592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" ns3:dyDescent="0.25">
       <c r="A113">
         <f>計算表!A113</f>
         <v>112</v>
@@ -11696,7 +11666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" ns3:dyDescent="0.25">
       <c r="A114">
         <f>計算表!A114</f>
         <v>113</v>
@@ -11770,7 +11740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" ns3:dyDescent="0.25">
       <c r="A115">
         <f>計算表!A115</f>
         <v>114</v>
@@ -11844,7 +11814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" ns3:dyDescent="0.25">
       <c r="A116">
         <f>計算表!A116</f>
         <v>115</v>
@@ -11918,7 +11888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" ns3:dyDescent="0.25">
       <c r="A117">
         <f>計算表!A117</f>
         <v>116</v>
@@ -11992,7 +11962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" ns3:dyDescent="0.25">
       <c r="A118">
         <f>計算表!A118</f>
         <v>117</v>
@@ -12066,7 +12036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" ns3:dyDescent="0.25">
       <c r="A119">
         <f>計算表!A119</f>
         <v>118</v>
@@ -12140,7 +12110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" ns3:dyDescent="0.25">
       <c r="A120">
         <f>計算表!A120</f>
         <v>119</v>
@@ -12214,7 +12184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" ns3:dyDescent="0.25">
       <c r="A121">
         <f>計算表!A121</f>
         <v>120</v>
@@ -12288,7 +12258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" ns3:dyDescent="0.25">
       <c r="A122">
         <f>計算表!A122</f>
         <v>121</v>
@@ -12362,7 +12332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" ns3:dyDescent="0.25">
       <c r="A123">
         <f>計算表!A123</f>
         <v>122</v>
@@ -12436,7 +12406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" ns3:dyDescent="0.25">
       <c r="A124">
         <f>計算表!A124</f>
         <v>123</v>
@@ -12510,7 +12480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" ns3:dyDescent="0.25">
       <c r="A125">
         <f>計算表!A125</f>
         <v>124</v>
@@ -12584,7 +12554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" ns3:dyDescent="0.25">
       <c r="A126">
         <f>計算表!A126</f>
         <v>125</v>
@@ -12658,7 +12628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" ns3:dyDescent="0.25">
       <c r="A127">
         <f>計算表!A127</f>
         <v>126</v>
@@ -12732,7 +12702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" ns3:dyDescent="0.25">
       <c r="A128">
         <f>計算表!A128</f>
         <v>127</v>
@@ -12806,7 +12776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" ns3:dyDescent="0.25">
       <c r="A129">
         <f>計算表!A129</f>
         <v>128</v>
@@ -12880,7 +12850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" ns3:dyDescent="0.25">
       <c r="A130">
         <f>計算表!A130</f>
         <v>129</v>
@@ -12954,7 +12924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" ns3:dyDescent="0.25">
       <c r="A131">
         <f>計算表!A131</f>
         <v>130</v>
@@ -13028,7 +12998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" ns3:dyDescent="0.25">
       <c r="A132">
         <f>計算表!A132</f>
         <v>131</v>
@@ -13102,7 +13072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" ns3:dyDescent="0.25">
       <c r="A133">
         <f>計算表!A133</f>
         <v>132</v>
@@ -13176,7 +13146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" ns3:dyDescent="0.25">
       <c r="A134">
         <f>計算表!A134</f>
         <v>133</v>
@@ -13250,7 +13220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" ns3:dyDescent="0.25">
       <c r="A135">
         <f>計算表!A135</f>
         <v>134</v>
@@ -13324,7 +13294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" ns3:dyDescent="0.25">
       <c r="A136">
         <f>計算表!A136</f>
         <v>135</v>
@@ -13398,7 +13368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" ns3:dyDescent="0.25">
       <c r="A137">
         <f>計算表!A137</f>
         <v>136</v>
@@ -13472,7 +13442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" ns3:dyDescent="0.25">
       <c r="A138">
         <f>計算表!A138</f>
         <v>137</v>
@@ -13546,7 +13516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" ns3:dyDescent="0.25">
       <c r="A139">
         <f>計算表!A139</f>
         <v>138</v>
@@ -13620,7 +13590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" ns3:dyDescent="0.25">
       <c r="A140">
         <f>計算表!A140</f>
         <v>139</v>
@@ -13694,7 +13664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" ns3:dyDescent="0.25">
       <c r="A141">
         <f>計算表!A141</f>
         <v>140</v>
@@ -13768,7 +13738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" ns3:dyDescent="0.25">
       <c r="A142">
         <f>計算表!A142</f>
         <v>141</v>
@@ -13842,7 +13812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" ns3:dyDescent="0.25">
       <c r="A143">
         <f>計算表!A143</f>
         <v>142</v>
@@ -13916,7 +13886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" ns3:dyDescent="0.25">
       <c r="A144">
         <f>計算表!A144</f>
         <v>143</v>
@@ -13990,7 +13960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" ns3:dyDescent="0.25">
       <c r="A145">
         <f>計算表!A145</f>
         <v>144</v>
@@ -14064,7 +14034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" ns3:dyDescent="0.25">
       <c r="A146">
         <f>計算表!A146</f>
         <v>145</v>
@@ -14138,7 +14108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" ns3:dyDescent="0.25">
       <c r="A147">
         <f>計算表!A147</f>
         <v>146</v>
@@ -14212,7 +14182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" ns3:dyDescent="0.25">
       <c r="A148">
         <f>計算表!A148</f>
         <v>147</v>
@@ -14286,7 +14256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" ns3:dyDescent="0.25">
       <c r="A149">
         <f>計算表!A149</f>
         <v>148</v>
@@ -14360,7 +14330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" ns3:dyDescent="0.25">
       <c r="A150">
         <f>計算表!A150</f>
         <v>149</v>
@@ -14434,7 +14404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" ns3:dyDescent="0.25">
       <c r="A151">
         <f>計算表!A151</f>
         <v>150</v>
@@ -14508,7 +14478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" ns3:dyDescent="0.25">
       <c r="A152">
         <f>計算表!A152</f>
         <v>151</v>
@@ -14582,7 +14552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" ns3:dyDescent="0.25">
       <c r="A153">
         <f>計算表!A153</f>
         <v>152</v>
@@ -14656,7 +14626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" ns3:dyDescent="0.25">
       <c r="A154">
         <f>計算表!A154</f>
         <v>153</v>
@@ -14730,7 +14700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" ns3:dyDescent="0.25">
       <c r="A155">
         <f>計算表!A155</f>
         <v>154</v>
@@ -14804,7 +14774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" ns3:dyDescent="0.25">
       <c r="A156">
         <f>計算表!A156</f>
         <v>155</v>
@@ -14878,7 +14848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" ns3:dyDescent="0.25">
       <c r="A157">
         <f>計算表!A157</f>
         <v>156</v>
@@ -14952,7 +14922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" ns3:dyDescent="0.25">
       <c r="A158">
         <f>計算表!A158</f>
         <v>157</v>
@@ -15026,7 +14996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" ns3:dyDescent="0.25">
       <c r="A159">
         <f>計算表!A159</f>
         <v>158</v>
@@ -15100,7 +15070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" ns3:dyDescent="0.25">
       <c r="A160">
         <f>計算表!A160</f>
         <v>159</v>
@@ -15174,7 +15144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" ns3:dyDescent="0.25">
       <c r="A161">
         <f>計算表!A161</f>
         <v>160</v>
@@ -15248,7 +15218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" ns3:dyDescent="0.25">
       <c r="A162">
         <f>計算表!A162</f>
         <v>161</v>
@@ -15322,7 +15292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" ns3:dyDescent="0.25">
       <c r="A163">
         <f>計算表!A163</f>
         <v>162</v>
@@ -15396,7 +15366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" ns3:dyDescent="0.25">
       <c r="A164">
         <f>計算表!A164</f>
         <v>163</v>
@@ -15470,7 +15440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" ns3:dyDescent="0.25">
       <c r="A165">
         <f>計算表!A165</f>
         <v>164</v>
@@ -15544,7 +15514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" ns3:dyDescent="0.25">
       <c r="A166">
         <f>計算表!A166</f>
         <v>165</v>
@@ -15618,7 +15588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" ns3:dyDescent="0.25">
       <c r="A167">
         <f>計算表!A167</f>
         <v>166</v>
@@ -15692,7 +15662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" ns3:dyDescent="0.25">
       <c r="A168">
         <f>計算表!A168</f>
         <v>167</v>
@@ -15766,7 +15736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" ns3:dyDescent="0.25">
       <c r="A169">
         <f>計算表!A169</f>
         <v>168</v>
@@ -15840,7 +15810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" ns3:dyDescent="0.25">
       <c r="A170">
         <f>計算表!A170</f>
         <v>169</v>
@@ -15914,7 +15884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" ns3:dyDescent="0.25">
       <c r="A171">
         <f>計算表!A171</f>
         <v>170</v>
@@ -15988,7 +15958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" ns3:dyDescent="0.25">
       <c r="A172">
         <f>計算表!A172</f>
         <v>171</v>
@@ -16062,7 +16032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" ns3:dyDescent="0.25">
       <c r="A173">
         <f>計算表!A173</f>
         <v>172</v>
@@ -16136,7 +16106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" ns3:dyDescent="0.25">
       <c r="A174">
         <f>計算表!A174</f>
         <v>173</v>
@@ -16210,7 +16180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" ns3:dyDescent="0.25">
       <c r="A175">
         <f>計算表!A175</f>
         <v>174</v>
@@ -16284,7 +16254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" ns3:dyDescent="0.25">
       <c r="A176">
         <f>計算表!A176</f>
         <v>175</v>
@@ -16358,7 +16328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" ns3:dyDescent="0.25">
       <c r="A177">
         <f>計算表!A177</f>
         <v>176</v>
@@ -16432,7 +16402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" ns3:dyDescent="0.25">
       <c r="A178">
         <f>計算表!A178</f>
         <v>177</v>
@@ -16506,7 +16476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" ns3:dyDescent="0.25">
       <c r="A179">
         <f>計算表!A179</f>
         <v>178</v>
@@ -16580,7 +16550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" ns3:dyDescent="0.25">
       <c r="A180">
         <f>計算表!A180</f>
         <v>179</v>
@@ -16654,7 +16624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" ns3:dyDescent="0.25">
       <c r="A181">
         <f>計算表!A181</f>
         <v>180</v>
@@ -16728,7 +16698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" ns3:dyDescent="0.25">
       <c r="A182">
         <f>計算表!A182</f>
         <v>181</v>
@@ -16802,7 +16772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" ns3:dyDescent="0.25">
       <c r="A183">
         <f>計算表!A183</f>
         <v>182</v>
@@ -16876,7 +16846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" ns3:dyDescent="0.25">
       <c r="A184">
         <f>計算表!A184</f>
         <v>183</v>
@@ -16950,7 +16920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" ns3:dyDescent="0.25">
       <c r="A185">
         <f>計算表!A185</f>
         <v>184</v>
@@ -17024,7 +16994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" ns3:dyDescent="0.25">
       <c r="A186">
         <f>計算表!A186</f>
         <v>185</v>
@@ -17098,7 +17068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" ns3:dyDescent="0.25">
       <c r="A187">
         <f>計算表!A187</f>
         <v>186</v>
@@ -17172,7 +17142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" ns3:dyDescent="0.25">
       <c r="A188">
         <f>計算表!A188</f>
         <v>187</v>
@@ -17246,7 +17216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" ns3:dyDescent="0.25">
       <c r="A189">
         <f>計算表!A189</f>
         <v>188</v>
@@ -17320,7 +17290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" ns3:dyDescent="0.25">
       <c r="A190">
         <f>計算表!A190</f>
         <v>189</v>
@@ -17394,7 +17364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" ns3:dyDescent="0.25">
       <c r="A191">
         <f>計算表!A191</f>
         <v>190</v>
@@ -17468,7 +17438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" ns3:dyDescent="0.25">
       <c r="A192">
         <f>計算表!A192</f>
         <v>191</v>
@@ -17542,7 +17512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" ns3:dyDescent="0.25">
       <c r="A193">
         <f>計算表!A193</f>
         <v>192</v>
@@ -17616,7 +17586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" ns3:dyDescent="0.25">
       <c r="A194">
         <f>計算表!A194</f>
         <v>193</v>
@@ -17690,7 +17660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" ns3:dyDescent="0.25">
       <c r="A195">
         <f>計算表!A195</f>
         <v>194</v>
@@ -17764,7 +17734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18" ns3:dyDescent="0.25">
       <c r="A196">
         <f>計算表!A196</f>
         <v>195</v>
@@ -17838,7 +17808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18" ns3:dyDescent="0.25">
       <c r="A197">
         <f>計算表!A197</f>
         <v>196</v>
@@ -17912,7 +17882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18" ns3:dyDescent="0.25">
       <c r="A198">
         <f>計算表!A198</f>
         <v>197</v>
@@ -17986,7 +17956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18" ns3:dyDescent="0.25">
       <c r="A199">
         <f>計算表!A199</f>
         <v>198</v>
@@ -18060,7 +18030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18" ns3:dyDescent="0.25">
       <c r="A200">
         <f>計算表!A200</f>
         <v>199</v>
@@ -18134,7 +18104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18" ns3:dyDescent="0.25">
       <c r="A201">
         <f>計算表!A201</f>
         <v>200</v>
@@ -18208,7 +18178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18" ns3:dyDescent="0.25">
       <c r="A202">
         <f>計算表!A202</f>
         <v>201</v>
@@ -18282,7 +18252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18" ns3:dyDescent="0.25">
       <c r="A203">
         <f>計算表!A203</f>
         <v>202</v>
@@ -18356,7 +18326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18" ns3:dyDescent="0.25">
       <c r="A204">
         <f>計算表!A204</f>
         <v>203</v>
@@ -18430,7 +18400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18" ns3:dyDescent="0.25">
       <c r="A205">
         <f>計算表!A205</f>
         <v>204</v>
@@ -18504,7 +18474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18" ns3:dyDescent="0.25">
       <c r="A206">
         <f>計算表!A206</f>
         <v>205</v>
@@ -18578,7 +18548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18" ns3:dyDescent="0.25">
       <c r="A207">
         <f>計算表!A207</f>
         <v>206</v>
@@ -18652,7 +18622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18" ns3:dyDescent="0.25">
       <c r="A208">
         <f>計算表!A208</f>
         <v>207</v>
@@ -18726,7 +18696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:18" ns3:dyDescent="0.25">
       <c r="A209">
         <f>計算表!A209</f>
         <v>208</v>
@@ -18800,7 +18770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:18" ns3:dyDescent="0.25">
       <c r="A210">
         <f>計算表!A210</f>
         <v>209</v>
@@ -18874,7 +18844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:18" ns3:dyDescent="0.25">
       <c r="A211">
         <f>計算表!A211</f>
         <v>210</v>
@@ -18948,7 +18918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:18" ns3:dyDescent="0.25">
       <c r="A212">
         <f>計算表!A212</f>
         <v>211</v>
@@ -19022,7 +18992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:18" ns3:dyDescent="0.25">
       <c r="A213">
         <f>計算表!A213</f>
         <v>212</v>
@@ -19096,7 +19066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:18" ns3:dyDescent="0.25">
       <c r="A214">
         <f>計算表!A214</f>
         <v>213</v>
@@ -19170,7 +19140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:18" ns3:dyDescent="0.25">
       <c r="A215">
         <f>計算表!A215</f>
         <v>214</v>
@@ -19244,7 +19214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:18" ns3:dyDescent="0.25">
       <c r="A216">
         <f>計算表!A216</f>
         <v>215</v>
@@ -19318,7 +19288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:18" ns3:dyDescent="0.25">
       <c r="A217">
         <f>計算表!A217</f>
         <v>216</v>
@@ -19392,7 +19362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:18" ns3:dyDescent="0.25">
       <c r="A218">
         <f>計算表!A218</f>
         <v>217</v>
@@ -19466,7 +19436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:18" ns3:dyDescent="0.25">
       <c r="A219">
         <f>計算表!A219</f>
         <v>218</v>
@@ -19540,7 +19510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:18" ns3:dyDescent="0.25">
       <c r="A220">
         <f>計算表!A220</f>
         <v>219</v>
@@ -19614,7 +19584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:18" ns3:dyDescent="0.25">
       <c r="A221">
         <f>計算表!A221</f>
         <v>220</v>
@@ -19688,7 +19658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:18" ns3:dyDescent="0.25">
       <c r="A222">
         <f>計算表!A222</f>
         <v>221</v>
@@ -19762,7 +19732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:18" ns3:dyDescent="0.25">
       <c r="A223">
         <f>計算表!A223</f>
         <v>222</v>
@@ -19836,7 +19806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:18" ns3:dyDescent="0.25">
       <c r="A224">
         <f>計算表!A224</f>
         <v>223</v>
@@ -19910,7 +19880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:18" ns3:dyDescent="0.25">
       <c r="A225">
         <f>計算表!A225</f>
         <v>224</v>
@@ -19984,7 +19954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:18" ns3:dyDescent="0.25">
       <c r="A226">
         <f>計算表!A226</f>
         <v>225</v>
@@ -20058,7 +20028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:18" ns3:dyDescent="0.25">
       <c r="A227">
         <f>計算表!A227</f>
         <v>226</v>
@@ -20132,7 +20102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:18" ns3:dyDescent="0.25">
       <c r="A228">
         <f>計算表!A228</f>
         <v>227</v>
@@ -20206,7 +20176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:18" ns3:dyDescent="0.25">
       <c r="A229">
         <f>計算表!A229</f>
         <v>228</v>
@@ -20280,7 +20250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:18" ns3:dyDescent="0.25">
       <c r="A230">
         <f>計算表!A230</f>
         <v>229</v>
@@ -20354,7 +20324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:18" ns3:dyDescent="0.25">
       <c r="A231">
         <f>計算表!A231</f>
         <v>230</v>
@@ -20428,7 +20398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:18" ns3:dyDescent="0.25">
       <c r="A232">
         <f>計算表!A232</f>
         <v>231</v>
@@ -20502,7 +20472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:18" ns3:dyDescent="0.25">
       <c r="A233">
         <f>計算表!A233</f>
         <v>232</v>
@@ -20576,7 +20546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:18" ns3:dyDescent="0.25">
       <c r="A234">
         <f>計算表!A234</f>
         <v>233</v>
@@ -20650,7 +20620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:18" ns3:dyDescent="0.25">
       <c r="A235">
         <f>計算表!A235</f>
         <v>234</v>
@@ -20724,7 +20694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:18" ns3:dyDescent="0.25">
       <c r="A236">
         <f>計算表!A236</f>
         <v>235</v>
@@ -20798,7 +20768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:18" ns3:dyDescent="0.25">
       <c r="A237">
         <f>計算表!A237</f>
         <v>236</v>
@@ -20872,7 +20842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:18" ns3:dyDescent="0.25">
       <c r="A238">
         <f>計算表!A238</f>
         <v>237</v>
@@ -20946,7 +20916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:18" ns3:dyDescent="0.25">
       <c r="A239">
         <f>計算表!A239</f>
         <v>238</v>
@@ -21020,7 +20990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:18" ns3:dyDescent="0.25">
       <c r="A240">
         <f>計算表!A240</f>
         <v>239</v>
@@ -21094,7 +21064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" ns3:dyDescent="0.25">
       <c r="A241">
         <f>計算表!A241</f>
         <v>240</v>
@@ -21168,7 +21138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:18" ns3:dyDescent="0.25">
       <c r="A242">
         <f>計算表!A242</f>
         <v>241</v>
@@ -21242,7 +21212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:18" ns3:dyDescent="0.25">
       <c r="A243">
         <f>計算表!A243</f>
         <v>242</v>
@@ -21316,7 +21286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:18" ns3:dyDescent="0.25">
       <c r="A244">
         <f>計算表!A244</f>
         <v>243</v>
@@ -21390,7 +21360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:18" ns3:dyDescent="0.25">
       <c r="A245">
         <f>計算表!A245</f>
         <v>244</v>
@@ -21464,7 +21434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:18" ns3:dyDescent="0.25">
       <c r="A246">
         <f>計算表!A246</f>
         <v>245</v>
@@ -21538,7 +21508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:18" ns3:dyDescent="0.25">
       <c r="A247">
         <f>計算表!A247</f>
         <v>246</v>
@@ -21612,7 +21582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:18" ns3:dyDescent="0.25">
       <c r="A248">
         <f>計算表!A248</f>
         <v>247</v>
@@ -21686,7 +21656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:18" ns3:dyDescent="0.25">
       <c r="A249">
         <f>計算表!A249</f>
         <v>248</v>
@@ -21760,7 +21730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:18" ns3:dyDescent="0.25">
       <c r="A250">
         <f>計算表!A250</f>
         <v>249</v>
@@ -21834,7 +21804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:18" ns3:dyDescent="0.25">
       <c r="A251">
         <f>計算表!A251</f>
         <v>250</v>
@@ -21908,7 +21878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:18" ns3:dyDescent="0.25">
       <c r="A252">
         <f>計算表!A252</f>
         <v>251</v>
@@ -21982,7 +21952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:18" ns3:dyDescent="0.25">
       <c r="A253">
         <f>計算表!A253</f>
         <v>252</v>
@@ -22056,7 +22026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:18" ns3:dyDescent="0.25">
       <c r="A254">
         <f>計算表!A254</f>
         <v>253</v>
@@ -22130,7 +22100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:18" ns3:dyDescent="0.25">
       <c r="A255">
         <f>計算表!A255</f>
         <v>254</v>
@@ -22204,7 +22174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:18" ns3:dyDescent="0.25">
       <c r="A256">
         <f>計算表!A256</f>
         <v>255</v>
@@ -22278,7 +22248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:18" ns3:dyDescent="0.25">
       <c r="A257">
         <f>計算表!A257</f>
         <v>256</v>
@@ -22352,7 +22322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:18" ns3:dyDescent="0.25">
       <c r="A258">
         <f>計算表!A258</f>
         <v>257</v>
@@ -22426,7 +22396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:18" ns3:dyDescent="0.25">
       <c r="A259">
         <f>計算表!A259</f>
         <v>258</v>
@@ -22500,7 +22470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:18" ns3:dyDescent="0.25">
       <c r="A260">
         <f>計算表!A260</f>
         <v>259</v>
@@ -22574,7 +22544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:18" ns3:dyDescent="0.25">
       <c r="A261">
         <f>計算表!A261</f>
         <v>260</v>
@@ -22648,7 +22618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:18" ns3:dyDescent="0.25">
       <c r="A262">
         <f>計算表!A262</f>
         <v>261</v>
@@ -22722,7 +22692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:18" ns3:dyDescent="0.25">
       <c r="A263">
         <f>計算表!A263</f>
         <v>262</v>
@@ -22796,7 +22766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:18" ns3:dyDescent="0.25">
       <c r="A264">
         <f>計算表!A264</f>
         <v>263</v>
@@ -22870,7 +22840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:18" ns3:dyDescent="0.25">
       <c r="A265">
         <f>計算表!A265</f>
         <v>264</v>
@@ -22944,7 +22914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:18" ns3:dyDescent="0.25">
       <c r="A266">
         <f>計算表!A266</f>
         <v>265</v>
@@ -23018,7 +22988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:18" ns3:dyDescent="0.25">
       <c r="A267">
         <f>計算表!A267</f>
         <v>266</v>
@@ -23092,7 +23062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:18" ns3:dyDescent="0.25">
       <c r="A268">
         <f>計算表!A268</f>
         <v>267</v>
@@ -23166,7 +23136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:18" ns3:dyDescent="0.25">
       <c r="A269">
         <f>計算表!A269</f>
         <v>268</v>
@@ -23240,7 +23210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:18" ns3:dyDescent="0.25">
       <c r="A270">
         <f>計算表!A270</f>
         <v>269</v>
@@ -23314,7 +23284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:18" ns3:dyDescent="0.25">
       <c r="A271">
         <f>計算表!A271</f>
         <v>270</v>
@@ -23388,7 +23358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:18" ns3:dyDescent="0.25">
       <c r="A272">
         <f>計算表!A272</f>
         <v>271</v>
@@ -23462,7 +23432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:18" ns3:dyDescent="0.25">
       <c r="A273">
         <f>計算表!A273</f>
         <v>272</v>
@@ -23536,7 +23506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:18" ns3:dyDescent="0.25">
       <c r="A274">
         <f>計算表!A274</f>
         <v>273</v>
@@ -23610,7 +23580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:18" ns3:dyDescent="0.25">
       <c r="A275">
         <f>計算表!A275</f>
         <v>274</v>
@@ -23684,7 +23654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:18" ns3:dyDescent="0.25">
       <c r="A276">
         <f>計算表!A276</f>
         <v>275</v>
@@ -23758,7 +23728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:18" ns3:dyDescent="0.25">
       <c r="A277">
         <f>計算表!A277</f>
         <v>276</v>
@@ -23832,7 +23802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:18" ns3:dyDescent="0.25">
       <c r="A278">
         <f>計算表!A278</f>
         <v>277</v>
@@ -23906,7 +23876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:18" ns3:dyDescent="0.25">
       <c r="A279">
         <f>計算表!A279</f>
         <v>278</v>
@@ -23980,7 +23950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:18" ns3:dyDescent="0.25">
       <c r="A280">
         <f>計算表!A280</f>
         <v>279</v>
@@ -24054,7 +24024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:18" ns3:dyDescent="0.25">
       <c r="A281">
         <f>計算表!A281</f>
         <v>280</v>
@@ -24128,7 +24098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:18" ns3:dyDescent="0.25">
       <c r="A282">
         <f>計算表!A282</f>
         <v>281</v>
@@ -24202,7 +24172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:18" ns3:dyDescent="0.25">
       <c r="A283">
         <f>計算表!A283</f>
         <v>282</v>
@@ -24276,7 +24246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:18" ns3:dyDescent="0.25">
       <c r="A284">
         <f>計算表!A284</f>
         <v>283</v>
@@ -24350,7 +24320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:18" ns3:dyDescent="0.25">
       <c r="A285">
         <f>計算表!A285</f>
         <v>284</v>
@@ -24424,7 +24394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:18" ns3:dyDescent="0.25">
       <c r="A286">
         <f>計算表!A286</f>
         <v>285</v>
@@ -24498,7 +24468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:18" ns3:dyDescent="0.25">
       <c r="A287">
         <f>計算表!A287</f>
         <v>286</v>
@@ -24572,7 +24542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:18" ns3:dyDescent="0.25">
       <c r="A288">
         <f>計算表!A288</f>
         <v>287</v>
@@ -24646,7 +24616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:18" ns3:dyDescent="0.25">
       <c r="A289">
         <f>計算表!A289</f>
         <v>288</v>
@@ -24720,7 +24690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:18" ns3:dyDescent="0.25">
       <c r="A290">
         <f>計算表!A290</f>
         <v>289</v>
@@ -24794,7 +24764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:18" ns3:dyDescent="0.25">
       <c r="A291">
         <f>計算表!A291</f>
         <v>290</v>
@@ -24868,7 +24838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:18" ns3:dyDescent="0.25">
       <c r="A292">
         <f>計算表!A292</f>
         <v>291</v>
@@ -24942,7 +24912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:18" ns3:dyDescent="0.25">
       <c r="A293">
         <f>計算表!A293</f>
         <v>292</v>
@@ -25016,7 +24986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:18" ns3:dyDescent="0.25">
       <c r="A294">
         <f>計算表!A294</f>
         <v>293</v>
@@ -25090,7 +25060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:18" ns3:dyDescent="0.25">
       <c r="A295">
         <f>計算表!A295</f>
         <v>294</v>
@@ -25164,7 +25134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:18" ns3:dyDescent="0.25">
       <c r="A296">
         <f>計算表!A296</f>
         <v>295</v>
@@ -25238,7 +25208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:18" ns3:dyDescent="0.25">
       <c r="A297">
         <f>計算表!A297</f>
         <v>296</v>
@@ -25312,7 +25282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:18" ns3:dyDescent="0.25">
       <c r="A298">
         <f>計算表!A298</f>
         <v>297</v>
@@ -25386,7 +25356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:18" ns3:dyDescent="0.25">
       <c r="A299">
         <f>計算表!A299</f>
         <v>298</v>
@@ -25460,7 +25430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:18" ns3:dyDescent="0.25">
       <c r="A300">
         <f>計算表!A300</f>
         <v>299</v>
@@ -25534,7 +25504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:18" ns3:dyDescent="0.25">
       <c r="A301">
         <f>計算表!A301</f>
         <v>300</v>
@@ -25608,7 +25578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:18" ns3:dyDescent="0.25">
       <c r="A302">
         <f>計算表!A302</f>
         <v>301</v>
@@ -25682,7 +25652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:18" ns3:dyDescent="0.25">
       <c r="A303">
         <f>計算表!A303</f>
         <v>302</v>
@@ -25756,7 +25726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:18" ns3:dyDescent="0.25">
       <c r="A304">
         <f>計算表!A304</f>
         <v>303</v>
@@ -25830,7 +25800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:18" ns3:dyDescent="0.25">
       <c r="A305">
         <f>計算表!A305</f>
         <v>304</v>
@@ -25904,7 +25874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:18" ns3:dyDescent="0.25">
       <c r="A306">
         <f>計算表!A306</f>
         <v>305</v>
@@ -25978,7 +25948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:18" ns3:dyDescent="0.25">
       <c r="A307">
         <f>計算表!A307</f>
         <v>306</v>
@@ -26052,7 +26022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:18" ns3:dyDescent="0.25">
       <c r="A308">
         <f>計算表!A308</f>
         <v>307</v>
@@ -26126,7 +26096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:18" ns3:dyDescent="0.25">
       <c r="A309">
         <f>計算表!A309</f>
         <v>308</v>
@@ -26200,7 +26170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:18" ns3:dyDescent="0.25">
       <c r="A310">
         <f>計算表!A310</f>
         <v>309</v>
@@ -26274,7 +26244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:18" ns3:dyDescent="0.25">
       <c r="A311">
         <f>計算表!A311</f>
         <v>310</v>
@@ -26348,7 +26318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:18" ns3:dyDescent="0.25">
       <c r="A312">
         <f>計算表!A312</f>
         <v>311</v>
@@ -26422,7 +26392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:18" ns3:dyDescent="0.25">
       <c r="A313">
         <f>計算表!A313</f>
         <v>312</v>
@@ -26496,7 +26466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:18" ns3:dyDescent="0.25">
       <c r="A314">
         <f>計算表!A314</f>
         <v>313</v>
@@ -26570,7 +26540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:18" ns3:dyDescent="0.25">
       <c r="A315">
         <f>計算表!A315</f>
         <v>314</v>
@@ -26644,7 +26614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:18" ns3:dyDescent="0.25">
       <c r="A316">
         <f>計算表!A316</f>
         <v>315</v>
@@ -26718,7 +26688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:18" ns3:dyDescent="0.25">
       <c r="A317">
         <f>計算表!A317</f>
         <v>316</v>
@@ -26792,7 +26762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:18" ns3:dyDescent="0.25">
       <c r="A318">
         <f>計算表!A318</f>
         <v>317</v>
@@ -26866,7 +26836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:18" ns3:dyDescent="0.25">
       <c r="A319">
         <f>計算表!A319</f>
         <v>318</v>
@@ -26940,7 +26910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:18" ns3:dyDescent="0.25">
       <c r="A320">
         <f>計算表!A320</f>
         <v>319</v>
@@ -27014,7 +26984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:18" ns3:dyDescent="0.25">
       <c r="A321">
         <f>計算表!A321</f>
         <v>320</v>
@@ -27088,7 +27058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:18" ns3:dyDescent="0.25">
       <c r="A322">
         <f>計算表!A322</f>
         <v>321</v>
@@ -27162,7 +27132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:18" ns3:dyDescent="0.25">
       <c r="A323">
         <f>計算表!A323</f>
         <v>322</v>
@@ -27236,7 +27206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:18" ns3:dyDescent="0.25">
       <c r="A324">
         <f>計算表!A324</f>
         <v>323</v>
@@ -27310,7 +27280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:18" ns3:dyDescent="0.25">
       <c r="A325">
         <f>計算表!A325</f>
         <v>324</v>
@@ -27384,7 +27354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:18" ns3:dyDescent="0.25">
       <c r="A326">
         <f>計算表!A326</f>
         <v>325</v>
@@ -27458,7 +27428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:18" ns3:dyDescent="0.25">
       <c r="A327">
         <f>計算表!A327</f>
         <v>326</v>
@@ -27532,7 +27502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:18" ns3:dyDescent="0.25">
       <c r="A328">
         <f>計算表!A328</f>
         <v>327</v>
@@ -27606,7 +27576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:18" ns3:dyDescent="0.25">
       <c r="A329">
         <f>計算表!A329</f>
         <v>328</v>
@@ -27680,7 +27650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:18" ns3:dyDescent="0.25">
       <c r="A330">
         <f>計算表!A330</f>
         <v>329</v>
@@ -27754,7 +27724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:18" ns3:dyDescent="0.25">
       <c r="A331">
         <f>計算表!A331</f>
         <v>330</v>
@@ -27828,7 +27798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:18" ns3:dyDescent="0.25">
       <c r="A332">
         <f>計算表!A332</f>
         <v>331</v>
@@ -27902,7 +27872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:18" ns3:dyDescent="0.25">
       <c r="A333">
         <f>計算表!A333</f>
         <v>332</v>
@@ -27976,7 +27946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:18" ns3:dyDescent="0.25">
       <c r="A334">
         <f>計算表!A334</f>
         <v>333</v>
@@ -28050,7 +28020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:18" ns3:dyDescent="0.25">
       <c r="A335">
         <f>計算表!A335</f>
         <v>334</v>
@@ -28124,7 +28094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:18" ns3:dyDescent="0.25">
       <c r="A336">
         <f>計算表!A336</f>
         <v>335</v>
@@ -28198,7 +28168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:18" ns3:dyDescent="0.25">
       <c r="A337">
         <f>計算表!A337</f>
         <v>336</v>
@@ -28272,7 +28242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:18" ns3:dyDescent="0.25">
       <c r="A338">
         <f>計算表!A338</f>
         <v>337</v>
@@ -28346,7 +28316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:18" ns3:dyDescent="0.25">
       <c r="A339">
         <f>計算表!A339</f>
         <v>338</v>
@@ -28420,7 +28390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:18" ns3:dyDescent="0.25">
       <c r="A340">
         <f>計算表!A340</f>
         <v>339</v>
@@ -28494,7 +28464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:18" ns3:dyDescent="0.25">
       <c r="A341">
         <f>計算表!A341</f>
         <v>340</v>
@@ -28568,7 +28538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:18" ns3:dyDescent="0.25">
       <c r="A342">
         <f>計算表!A342</f>
         <v>341</v>
@@ -28642,7 +28612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:18" ns3:dyDescent="0.25">
       <c r="A343">
         <f>計算表!A343</f>
         <v>342</v>
@@ -28716,7 +28686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:18" ns3:dyDescent="0.25">
       <c r="A344">
         <f>計算表!A344</f>
         <v>343</v>
@@ -28790,7 +28760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:18" ns3:dyDescent="0.25">
       <c r="A345">
         <f>計算表!A345</f>
         <v>344</v>
@@ -28864,7 +28834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:18" ns3:dyDescent="0.25">
       <c r="A346">
         <f>計算表!A346</f>
         <v>345</v>
@@ -28938,7 +28908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:18" ns3:dyDescent="0.25">
       <c r="A347">
         <f>計算表!A347</f>
         <v>346</v>
@@ -29012,7 +28982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:18" ns3:dyDescent="0.25">
       <c r="A348">
         <f>計算表!A348</f>
         <v>347</v>
@@ -29086,7 +29056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:18" ns3:dyDescent="0.25">
       <c r="A349">
         <f>計算表!A349</f>
         <v>348</v>
@@ -29160,7 +29130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:18" ns3:dyDescent="0.25">
       <c r="A350">
         <f>計算表!A350</f>
         <v>349</v>
@@ -29234,7 +29204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:18" ns3:dyDescent="0.25">
       <c r="A351">
         <f>計算表!A351</f>
         <v>350</v>
@@ -29308,7 +29278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:18" ns3:dyDescent="0.25">
       <c r="A352">
         <f>計算表!A352</f>
         <v>351</v>
@@ -29382,7 +29352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:18" ns3:dyDescent="0.25">
       <c r="A353">
         <f>計算表!A353</f>
         <v>352</v>
@@ -29456,7 +29426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:18" ns3:dyDescent="0.25">
       <c r="A354">
         <f>計算表!A354</f>
         <v>353</v>
@@ -29530,7 +29500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:18" ns3:dyDescent="0.25">
       <c r="A355">
         <f>計算表!A355</f>
         <v>354</v>
@@ -29604,7 +29574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:18" ns3:dyDescent="0.25">
       <c r="A356">
         <f>計算表!A356</f>
         <v>355</v>
@@ -29678,7 +29648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:18" ns3:dyDescent="0.25">
       <c r="A357">
         <f>計算表!A357</f>
         <v>356</v>
@@ -29752,7 +29722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:18" ns3:dyDescent="0.25">
       <c r="A358">
         <f>計算表!A358</f>
         <v>357</v>
@@ -29826,7 +29796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:18" ns3:dyDescent="0.25">
       <c r="A359">
         <f>計算表!A359</f>
         <v>358</v>
@@ -29900,7 +29870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:18" ns3:dyDescent="0.25">
       <c r="A360">
         <f>計算表!A360</f>
         <v>359</v>
@@ -29974,7 +29944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:18" ns3:dyDescent="0.25">
       <c r="A361">
         <f>計算表!A361</f>
         <v>360</v>
@@ -30048,7 +30018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:18" ns3:dyDescent="0.25">
       <c r="A362">
         <f>計算表!A362</f>
         <v>361</v>
@@ -30122,7 +30092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:18" ns3:dyDescent="0.25">
       <c r="A363">
         <f>計算表!A363</f>
         <v>362</v>
@@ -30196,7 +30166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:18" ns3:dyDescent="0.25">
       <c r="A364">
         <f>計算表!A364</f>
         <v>363</v>
@@ -30270,7 +30240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:18" ns3:dyDescent="0.25">
       <c r="A365">
         <f>計算表!A365</f>
         <v>364</v>
@@ -30344,7 +30314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:18" ns3:dyDescent="0.25">
       <c r="A366">
         <f>計算表!A366</f>
         <v>365</v>
@@ -30418,7 +30388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:18" ns3:dyDescent="0.25">
       <c r="A367">
         <f>計算表!A367</f>
         <v>366</v>
@@ -30492,7 +30462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:18" ns3:dyDescent="0.25">
       <c r="A368">
         <f>計算表!A368</f>
         <v>367</v>
@@ -30566,7 +30536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:18" ns3:dyDescent="0.25">
       <c r="A369">
         <f>計算表!A369</f>
         <v>368</v>
@@ -30640,7 +30610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:18" ns3:dyDescent="0.25">
       <c r="A370">
         <f>計算表!A370</f>
         <v>369</v>
@@ -30714,7 +30684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:18" ns3:dyDescent="0.25">
       <c r="A371">
         <f>計算表!A371</f>
         <v>370</v>
@@ -30788,7 +30758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:18" ns3:dyDescent="0.25">
       <c r="A372">
         <f>計算表!A372</f>
         <v>371</v>
@@ -30862,7 +30832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:18" ns3:dyDescent="0.25">
       <c r="A373">
         <f>計算表!A373</f>
         <v>372</v>
@@ -30936,7 +30906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:18" ns3:dyDescent="0.25">
       <c r="A374">
         <f>計算表!A374</f>
         <v>373</v>
@@ -31010,7 +30980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:18" ns3:dyDescent="0.25">
       <c r="A375">
         <f>計算表!A375</f>
         <v>374</v>
@@ -31084,7 +31054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:18" ns3:dyDescent="0.25">
       <c r="A376">
         <f>計算表!A376</f>
         <v>375</v>
@@ -31158,7 +31128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:18" ns3:dyDescent="0.25">
       <c r="A377">
         <f>計算表!A377</f>
         <v>376</v>
@@ -31232,7 +31202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:18" ns3:dyDescent="0.25">
       <c r="A378">
         <f>計算表!A378</f>
         <v>377</v>
@@ -31306,7 +31276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:18" ns3:dyDescent="0.25">
       <c r="A379">
         <f>計算表!A379</f>
         <v>378</v>
@@ -31380,7 +31350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:18" ns3:dyDescent="0.25">
       <c r="A380">
         <f>計算表!A380</f>
         <v>379</v>
@@ -31454,7 +31424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:18" ns3:dyDescent="0.25">
       <c r="A381">
         <f>計算表!A381</f>
         <v>380</v>
@@ -31528,7 +31498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:18" ns3:dyDescent="0.25">
       <c r="A382">
         <f>計算表!A382</f>
         <v>381</v>
@@ -31602,7 +31572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:18" ns3:dyDescent="0.25">
       <c r="A383">
         <f>計算表!A383</f>
         <v>382</v>
@@ -31676,7 +31646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:18" ns3:dyDescent="0.25">
       <c r="A384">
         <f>計算表!A384</f>
         <v>383</v>
@@ -31750,7 +31720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:18" ns3:dyDescent="0.25">
       <c r="A385">
         <f>計算表!A385</f>
         <v>384</v>
@@ -31824,7 +31794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:18" ns3:dyDescent="0.25">
       <c r="A386">
         <f>計算表!A386</f>
         <v>385</v>
@@ -31898,7 +31868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:18" ns3:dyDescent="0.25">
       <c r="A387">
         <f>計算表!A387</f>
         <v>386</v>
@@ -31972,7 +31942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:18" ns3:dyDescent="0.25">
       <c r="A388">
         <f>計算表!A388</f>
         <v>387</v>
@@ -32046,7 +32016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:18" ns3:dyDescent="0.25">
       <c r="A389">
         <f>計算表!A389</f>
         <v>388</v>
@@ -32120,7 +32090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:18" ns3:dyDescent="0.25">
       <c r="A390">
         <f>計算表!A390</f>
         <v>389</v>
@@ -32194,7 +32164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:18" ns3:dyDescent="0.25">
       <c r="A391">
         <f>計算表!A391</f>
         <v>390</v>
@@ -32268,7 +32238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:18" ns3:dyDescent="0.25">
       <c r="A392">
         <f>計算表!A392</f>
         <v>391</v>
@@ -32342,7 +32312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:18" ns3:dyDescent="0.25">
       <c r="A393">
         <f>計算表!A393</f>
         <v>392</v>
@@ -32416,7 +32386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:18" ns3:dyDescent="0.25">
       <c r="A394">
         <f>計算表!A394</f>
         <v>393</v>
@@ -32490,7 +32460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:18" ns3:dyDescent="0.25">
       <c r="A395">
         <f>計算表!A395</f>
         <v>394</v>
@@ -32564,7 +32534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:18" ns3:dyDescent="0.25">
       <c r="A396">
         <f>計算表!A396</f>
         <v>395</v>
@@ -32638,7 +32608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:18" ns3:dyDescent="0.25">
       <c r="A397">
         <f>計算表!A397</f>
         <v>396</v>
@@ -32712,7 +32682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:18" ns3:dyDescent="0.25">
       <c r="A398">
         <f>計算表!A398</f>
         <v>397</v>
@@ -32786,7 +32756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:18" ns3:dyDescent="0.25">
       <c r="A399">
         <f>計算表!A399</f>
         <v>398</v>
@@ -32860,7 +32830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:18" ns3:dyDescent="0.25">
       <c r="A400">
         <f>計算表!A400</f>
         <v>399</v>
@@ -32934,7 +32904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:18" ns3:dyDescent="0.25">
       <c r="A401">
         <f>計算表!A401</f>
         <v>400</v>
@@ -33008,7 +32978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:18" ns3:dyDescent="0.25">
       <c r="A402">
         <f>計算表!A402</f>
         <v>401</v>
@@ -33082,7 +33052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:18" ns3:dyDescent="0.25">
       <c r="A403">
         <f>計算表!A403</f>
         <v>402</v>
@@ -33156,7 +33126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:18" ns3:dyDescent="0.25">
       <c r="A404">
         <f>計算表!A404</f>
         <v>403</v>
@@ -33230,7 +33200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:18" ns3:dyDescent="0.25">
       <c r="A405">
         <f>計算表!A405</f>
         <v>404</v>
@@ -33304,7 +33274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:18" ns3:dyDescent="0.25">
       <c r="A406">
         <f>計算表!A406</f>
         <v>405</v>
@@ -33378,7 +33348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:18" ns3:dyDescent="0.25">
       <c r="A407">
         <f>計算表!A407</f>
         <v>406</v>
@@ -33452,7 +33422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:18" ns3:dyDescent="0.25">
       <c r="A408">
         <f>計算表!A408</f>
         <v>407</v>
@@ -33526,7 +33496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:18" ns3:dyDescent="0.25">
       <c r="A409">
         <f>計算表!A409</f>
         <v>408</v>
@@ -33600,7 +33570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:18" ns3:dyDescent="0.25">
       <c r="A410">
         <f>計算表!A410</f>
         <v>409</v>
@@ -33674,7 +33644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:18" ns3:dyDescent="0.25">
       <c r="A411">
         <f>計算表!A411</f>
         <v>410</v>
@@ -33748,7 +33718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:18" ns3:dyDescent="0.25">
       <c r="A412">
         <f>計算表!A412</f>
         <v>411</v>
@@ -33822,7 +33792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:18" ns3:dyDescent="0.25">
       <c r="A413">
         <f>計算表!A413</f>
         <v>412</v>
@@ -33896,7 +33866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:18" ns3:dyDescent="0.25">
       <c r="A414">
         <f>計算表!A414</f>
         <v>413</v>
@@ -33970,7 +33940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:18" ns3:dyDescent="0.25">
       <c r="A415">
         <f>計算表!A415</f>
         <v>414</v>
@@ -34044,7 +34014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:18" ns3:dyDescent="0.25">
       <c r="A416">
         <f>計算表!A416</f>
         <v>415</v>
@@ -34118,7 +34088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:18" ns3:dyDescent="0.25">
       <c r="A417">
         <f>計算表!A417</f>
         <v>416</v>
@@ -34192,7 +34162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:18" ns3:dyDescent="0.25">
       <c r="A418">
         <f>計算表!A418</f>
         <v>417</v>
@@ -34266,7 +34236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:18" ns3:dyDescent="0.25">
       <c r="A419">
         <f>計算表!A419</f>
         <v>418</v>
@@ -34340,7 +34310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:18" ns3:dyDescent="0.25">
       <c r="A420">
         <f>計算表!A420</f>
         <v>419</v>
@@ -34414,7 +34384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:18" ns3:dyDescent="0.25">
       <c r="A421">
         <f>計算表!A421</f>
         <v>420</v>
@@ -34488,7 +34458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:18" ns3:dyDescent="0.25">
       <c r="A422">
         <f>計算表!A422</f>
         <v>421</v>
@@ -34562,7 +34532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:18" ns3:dyDescent="0.25">
       <c r="A423">
         <f>計算表!A423</f>
         <v>422</v>
@@ -34636,7 +34606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:18" ns3:dyDescent="0.25">
       <c r="A424">
         <f>計算表!A424</f>
         <v>423</v>
@@ -34710,7 +34680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:18" ns3:dyDescent="0.25">
       <c r="A425">
         <f>計算表!A425</f>
         <v>424</v>
@@ -34784,7 +34754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:18" ns3:dyDescent="0.25">
       <c r="A426">
         <f>計算表!A426</f>
         <v>425</v>
@@ -34858,7 +34828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:18" ns3:dyDescent="0.25">
       <c r="A427">
         <f>計算表!A427</f>
         <v>426</v>
@@ -34932,7 +34902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:18" ns3:dyDescent="0.25">
       <c r="A428">
         <f>計算表!A428</f>
         <v>427</v>
@@ -35006,7 +34976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:18" ns3:dyDescent="0.25">
       <c r="A429">
         <f>計算表!A429</f>
         <v>428</v>
@@ -35080,7 +35050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:18" ns3:dyDescent="0.25">
       <c r="A430">
         <f>計算表!A430</f>
         <v>429</v>
@@ -35154,7 +35124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:18" ns3:dyDescent="0.25">
       <c r="A431">
         <f>計算表!A431</f>
         <v>430</v>
@@ -35228,7 +35198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:18" ns3:dyDescent="0.25">
       <c r="A432">
         <f>計算表!A432</f>
         <v>431</v>
@@ -35302,7 +35272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:18" ns3:dyDescent="0.25">
       <c r="A433">
         <f>計算表!A433</f>
         <v>432</v>
@@ -35376,7 +35346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:18" ns3:dyDescent="0.25">
       <c r="A434">
         <f>計算表!A434</f>
         <v>433</v>
@@ -35450,7 +35420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:18" ns3:dyDescent="0.25">
       <c r="A435">
         <f>計算表!A435</f>
         <v>434</v>
@@ -35524,7 +35494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:18" ns3:dyDescent="0.25">
       <c r="A436">
         <f>計算表!A436</f>
         <v>435</v>
@@ -35598,7 +35568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:18" ns3:dyDescent="0.25">
       <c r="A437">
         <f>計算表!A437</f>
         <v>436</v>
@@ -35672,7 +35642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:18" ns3:dyDescent="0.25">
       <c r="A438">
         <f>計算表!A438</f>
         <v>437</v>
@@ -35746,7 +35716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:18" ns3:dyDescent="0.25">
       <c r="A439">
         <f>計算表!A439</f>
         <v>438</v>
@@ -35820,7 +35790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:18" ns3:dyDescent="0.25">
       <c r="A440">
         <f>計算表!A440</f>
         <v>439</v>
@@ -35894,7 +35864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:18" ns3:dyDescent="0.25">
       <c r="A441">
         <f>計算表!A441</f>
         <v>440</v>
@@ -35968,7 +35938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:18" ns3:dyDescent="0.25">
       <c r="A442">
         <f>計算表!A442</f>
         <v>441</v>
@@ -36042,7 +36012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:18" ns3:dyDescent="0.25">
       <c r="A443">
         <f>計算表!A443</f>
         <v>442</v>
@@ -36116,7 +36086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:18" ns3:dyDescent="0.25">
       <c r="A444">
         <f>計算表!A444</f>
         <v>443</v>
@@ -36190,7 +36160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:18" ns3:dyDescent="0.25">
       <c r="A445">
         <f>計算表!A445</f>
         <v>444</v>
@@ -36264,7 +36234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:18" ns3:dyDescent="0.25">
       <c r="A446">
         <f>計算表!A446</f>
         <v>445</v>
@@ -36338,7 +36308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:18" ns3:dyDescent="0.25">
       <c r="A447">
         <f>計算表!A447</f>
         <v>446</v>
@@ -36412,7 +36382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:18" ns3:dyDescent="0.25">
       <c r="A448">
         <f>計算表!A448</f>
         <v>447</v>
@@ -36486,7 +36456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:18" ns3:dyDescent="0.25">
       <c r="A449">
         <f>計算表!A449</f>
         <v>448</v>
@@ -36560,7 +36530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:18" ns3:dyDescent="0.25">
       <c r="A450">
         <f>計算表!A450</f>
         <v>449</v>
@@ -36634,7 +36604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:18" ns3:dyDescent="0.25">
       <c r="A451">
         <f>計算表!A451</f>
         <v>450</v>
@@ -36708,7 +36678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:18" ns3:dyDescent="0.25">
       <c r="A452">
         <f>計算表!A452</f>
         <v>451</v>
@@ -36782,7 +36752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:18" ns3:dyDescent="0.25">
       <c r="A453">
         <f>計算表!A453</f>
         <v>452</v>
@@ -36856,7 +36826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:18" ns3:dyDescent="0.25">
       <c r="A454">
         <f>計算表!A454</f>
         <v>453</v>
@@ -36930,7 +36900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:18" ns3:dyDescent="0.25">
       <c r="A455">
         <f>計算表!A455</f>
         <v>454</v>
@@ -37004,7 +36974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:18" ns3:dyDescent="0.25">
       <c r="A456">
         <f>計算表!A456</f>
         <v>455</v>
@@ -37078,7 +37048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:18" ns3:dyDescent="0.25">
       <c r="A457">
         <f>計算表!A457</f>
         <v>456</v>
@@ -37152,40 +37122,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:18" ns3:dyDescent="0.25">
       <c r="B458" s="2"/>
     </row>
-    <row r="459" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:18" ns3:dyDescent="0.25">
       <c r="B459" s="2"/>
     </row>
-    <row r="460" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:18" ns3:dyDescent="0.25">
       <c r="B460" s="2"/>
     </row>
-    <row r="461" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:18" ns3:dyDescent="0.25">
       <c r="B461" s="2"/>
     </row>
-    <row r="462" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:18" ns3:dyDescent="0.25">
       <c r="B462" s="2"/>
     </row>
-    <row r="463" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:18" ns3:dyDescent="0.25">
       <c r="B463" s="2"/>
     </row>
-    <row r="464" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:18" ns3:dyDescent="0.25">
       <c r="B464" s="2"/>
     </row>
-    <row r="465" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="465" spans="2:2" ns3:dyDescent="0.25">
       <c r="B465" s="2"/>
     </row>
-    <row r="466" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="466" spans="2:2" ns3:dyDescent="0.25">
       <c r="B466" s="2"/>
     </row>
-    <row r="467" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="467" spans="2:2" ns3:dyDescent="0.25">
       <c r="B467" s="2"/>
     </row>
-    <row r="468" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="468" spans="2:2" ns3:dyDescent="0.25">
       <c r="B468" s="2"/>
     </row>
-    <row r="469" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="469" spans="2:2" ns3:dyDescent="0.25">
       <c r="B469" s="2"/>
     </row>
   </sheetData>
@@ -37195,9 +37165,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R457"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="3" customWidth="1"/>
     <col min="2" max="2" width="6" style="3" customWidth="1"/>
@@ -37214,7 +37184,7 @@
     <col min="17" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ns3:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -37270,7 +37240,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ns3:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -37299,7 +37269,7 @@
         <v>9999</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ns3:dyDescent="0.25">
       <c r="A3" s="3">
         <f>A2+1</f>
         <v>2</v>
@@ -37323,7 +37293,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ns3:dyDescent="0.25">
       <c r="A4" s="3">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -37350,7 +37320,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ns3:dyDescent="0.25">
       <c r="A5" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -37377,7 +37347,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ns3:dyDescent="0.25">
       <c r="A6" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -37401,7 +37371,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ns3:dyDescent="0.25">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -37422,7 +37392,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ns3:dyDescent="0.25">
       <c r="A8" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -37446,7 +37416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ns3:dyDescent="0.25">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -37482,7 +37452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ns3:dyDescent="0.25">
       <c r="A10" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -37518,7 +37488,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ns3:dyDescent="0.25">
       <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -37555,7 +37525,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ns3:dyDescent="0.25">
       <c r="A12" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -37592,7 +37562,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ns3:dyDescent="0.25">
       <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -37629,7 +37599,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ns3:dyDescent="0.25">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -37666,7 +37636,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ns3:dyDescent="0.25">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -37703,7 +37673,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ns3:dyDescent="0.25">
       <c r="A16" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -37740,7 +37710,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ns3:dyDescent="0.25">
       <c r="A17" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -37777,7 +37747,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ns3:dyDescent="0.25">
       <c r="A18" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -37814,7 +37784,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ns3:dyDescent="0.25">
       <c r="A19" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -37851,7 +37821,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ns3:dyDescent="0.25">
       <c r="A20" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -37878,7 +37848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ns3:dyDescent="0.25">
       <c r="A21" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -37902,7 +37872,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ns3:dyDescent="0.25">
       <c r="A22" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -37926,7 +37896,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ns3:dyDescent="0.25">
       <c r="A23" s="3">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -37953,7 +37923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ns3:dyDescent="0.25">
       <c r="A24" s="3">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -37980,7 +37950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ns3:dyDescent="0.25">
       <c r="A25" s="3">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -38007,7 +37977,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ns3:dyDescent="0.25">
       <c r="A26" s="3">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -38034,7 +38004,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ns3:dyDescent="0.25">
       <c r="A27" s="3">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -38058,7 +38028,7 @@
         <v>5.0000000000000002E-5</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ns3:dyDescent="0.25">
       <c r="A28" s="3">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -38085,7 +38055,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ns3:dyDescent="0.25">
       <c r="A29" s="3">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -38106,7 +38076,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ns3:dyDescent="0.25">
       <c r="A30" s="3">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -38130,7 +38100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ns3:dyDescent="0.25">
       <c r="A31" s="3">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -38151,7 +38121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ns3:dyDescent="0.25">
       <c r="A32" s="3">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -38172,7 +38142,7 @@
         <v>1E-4</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ns3:dyDescent="0.25">
       <c r="A33" s="3">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -38193,7 +38163,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ns3:dyDescent="0.25">
       <c r="A34" s="3">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -38214,7 +38184,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ns3:dyDescent="0.25">
       <c r="A35" s="3">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -38238,7 +38208,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ns3:dyDescent="0.25">
       <c r="A36" s="3">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -38259,7 +38229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ns3:dyDescent="0.25">
       <c r="A37" s="3">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -38280,7 +38250,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ns3:dyDescent="0.25">
       <c r="A38" s="3">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -38301,7 +38271,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ns3:dyDescent="0.25">
       <c r="A39" s="3">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -38322,7 +38292,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ns3:dyDescent="0.25">
       <c r="A40" s="3">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -38343,7 +38313,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ns3:dyDescent="0.25">
       <c r="A41" s="3">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -38364,7 +38334,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ns3:dyDescent="0.25">
       <c r="A42" s="3">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -38385,7 +38355,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ns3:dyDescent="0.25">
       <c r="A43" s="3">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -38406,7 +38376,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ns3:dyDescent="0.25">
       <c r="A44" s="3">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -38427,7 +38397,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ns3:dyDescent="0.25">
       <c r="A45" s="3">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -38448,7 +38418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ns3:dyDescent="0.25">
       <c r="A46" s="3">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -38469,70 +38439,199 @@
         <v>60</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ns3:dyDescent="0.25">
       <c r="A47" s="3">
-        <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>150</v>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>3-戰鬥核心</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>物理抗性減傷</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>抗性總合^a/(抗性總合^a+b+c×敵人等級)</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>a=抗性次方 b=分母常數 c=敵人等級係數。抗性≤0 時不減傷。</t>
+        </is>
       </c>
       <c r="G47" s="3">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1.8</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>10</v>
+      </c>
+      <c r="I47">
+        <v>0.1</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ns3:dyDescent="0.25">
       <c r="A48" s="3">
-        <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>152</v>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>3-戰鬥核心</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>魔法抗性減傷</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>抗性總合^a/(抗性總合^a+b+c×敵人等級)</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>a=抗性次方 b=分母常數 c=敵人等級係數。抗性≤0 時不減傷。</t>
+        </is>
       </c>
       <c r="G48" s="3">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1.8</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>10</v>
+      </c>
+      <c r="I48">
+        <v>0.1</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ns3:dyDescent="0.25">
       <c r="A49" s="3">
-        <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>154</v>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>3-戰鬥核心</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>六系元素抗性減傷</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>抗性總合^a/(抗性總合^a+b+c×敵人等級)</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>a=抗性次方 b=分母常數 c=敵人等級係數。六系元素共用此曲線；抗性≤0 時不減傷。</t>
+        </is>
       </c>
       <c r="G49" s="3">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1.8</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>10</v>
+      </c>
+      <c r="I49">
+        <v>0.1</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ns3:dyDescent="0.25">
       <c r="A50" s="3">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -38553,7 +38652,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ns3:dyDescent="0.25">
       <c r="A51" s="3">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -38574,7 +38673,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ns3:dyDescent="0.25">
       <c r="A52" s="3">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -38595,7 +38694,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ns3:dyDescent="0.25">
       <c r="A53" s="3">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -38616,7 +38715,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ns3:dyDescent="0.25">
       <c r="A54" s="3">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -38637,7 +38736,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ns3:dyDescent="0.25">
       <c r="A55" s="3">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -38658,7 +38757,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ns3:dyDescent="0.25">
       <c r="A56" s="3">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -38679,7 +38778,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ns3:dyDescent="0.25">
       <c r="A57" s="3">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -38700,7 +38799,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ns3:dyDescent="0.25">
       <c r="A58" s="3">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -38721,7 +38820,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ns3:dyDescent="0.25">
       <c r="A59" s="3">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -38745,7 +38844,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ns3:dyDescent="0.25">
       <c r="A60" s="3">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -38769,7 +38868,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ns3:dyDescent="0.25">
       <c r="A61" s="3">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -38793,7 +38892,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ns3:dyDescent="0.25">
       <c r="A62" s="3">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -38814,7 +38913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ns3:dyDescent="0.25">
       <c r="A63" s="3">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -38835,7 +38934,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ns3:dyDescent="0.25">
       <c r="A64" s="3">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -38859,7 +38958,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" ns3:dyDescent="0.25">
       <c r="A65" s="3">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -38880,7 +38979,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" ns3:dyDescent="0.25">
       <c r="A66" s="3">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -38901,7 +39000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" ns3:dyDescent="0.25">
       <c r="A67" s="3">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -38922,7 +39021,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" ns3:dyDescent="0.25">
       <c r="A68" s="3">
         <f t="shared" ref="A68:A131" si="2">A67+1</f>
         <v>67</v>
@@ -38943,7 +39042,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" ns3:dyDescent="0.25">
       <c r="A69" s="3">
         <f t="shared" si="2"/>
         <v>68</v>
@@ -38964,7 +39063,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" ns3:dyDescent="0.25">
       <c r="A70" s="3">
         <f t="shared" si="2"/>
         <v>69</v>
@@ -38988,7 +39087,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" ns3:dyDescent="0.25">
       <c r="A71" s="3">
         <f t="shared" si="2"/>
         <v>70</v>
@@ -39018,7 +39117,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" ns3:dyDescent="0.25">
       <c r="A72" s="3">
         <f t="shared" si="2"/>
         <v>71</v>
@@ -39039,7 +39138,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" ns3:dyDescent="0.25">
       <c r="A73" s="3">
         <f t="shared" si="2"/>
         <v>72</v>
@@ -39060,7 +39159,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" ns3:dyDescent="0.25">
       <c r="A74" s="3">
         <f t="shared" si="2"/>
         <v>73</v>
@@ -39081,7 +39180,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" ns3:dyDescent="0.25">
       <c r="A75" s="3">
         <f t="shared" si="2"/>
         <v>74</v>
@@ -39102,7 +39201,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" ns3:dyDescent="0.25">
       <c r="A76" s="3">
         <f t="shared" si="2"/>
         <v>75</v>
@@ -39123,7 +39222,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" ns3:dyDescent="0.25">
       <c r="A77" s="3">
         <f t="shared" si="2"/>
         <v>76</v>
@@ -39150,7 +39249,7 @@
         <v>1.095</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ns3:dyDescent="0.25">
       <c r="A78" s="3">
         <f t="shared" si="2"/>
         <v>77</v>
@@ -39177,7 +39276,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" ns3:dyDescent="0.25">
       <c r="A79" s="3">
         <f t="shared" si="2"/>
         <v>78</v>
@@ -39204,7 +39303,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" ns3:dyDescent="0.25">
       <c r="A80" s="3">
         <f t="shared" si="2"/>
         <v>79</v>
@@ -39231,7 +39330,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" ns3:dyDescent="0.25">
       <c r="A81" s="3">
         <f t="shared" si="2"/>
         <v>80</v>
@@ -39258,7 +39357,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" ns3:dyDescent="0.25">
       <c r="A82" s="3">
         <f t="shared" si="2"/>
         <v>81</v>
@@ -39279,7 +39378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" ns3:dyDescent="0.25">
       <c r="A83" s="3">
         <f t="shared" si="2"/>
         <v>82</v>
@@ -39303,7 +39402,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" ns3:dyDescent="0.25">
       <c r="A84" s="3">
         <f t="shared" si="2"/>
         <v>83</v>
@@ -39327,7 +39426,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" ns3:dyDescent="0.25">
       <c r="A85" s="3">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -39360,7 +39459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" ns3:dyDescent="0.25">
       <c r="A86" s="3">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -39381,7 +39480,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" ns3:dyDescent="0.25">
       <c r="A87" s="3">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -39402,7 +39501,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" ns3:dyDescent="0.25">
       <c r="A88" s="3">
         <f t="shared" si="2"/>
         <v>87</v>
@@ -39423,7 +39522,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" ns3:dyDescent="0.25">
       <c r="A89" s="3">
         <f t="shared" si="2"/>
         <v>88</v>
@@ -39444,7 +39543,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" ns3:dyDescent="0.25">
       <c r="A90" s="3">
         <f t="shared" si="2"/>
         <v>89</v>
@@ -39465,7 +39564,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" ns3:dyDescent="0.25">
       <c r="A91" s="3">
         <f t="shared" si="2"/>
         <v>90</v>
@@ -39501,7 +39600,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" ns3:dyDescent="0.25">
       <c r="A92" s="3">
         <f t="shared" si="2"/>
         <v>91</v>
@@ -39537,7 +39636,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ns3:dyDescent="0.25">
       <c r="A93" s="3">
         <f t="shared" si="2"/>
         <v>92</v>
@@ -39573,7 +39672,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" ns3:dyDescent="0.25">
       <c r="A94" s="3">
         <f t="shared" si="2"/>
         <v>93</v>
@@ -39597,7 +39696,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" ns3:dyDescent="0.25">
       <c r="A95" s="3">
         <f t="shared" si="2"/>
         <v>94</v>
@@ -39618,7 +39717,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" ns3:dyDescent="0.25">
       <c r="A96" s="3">
         <f t="shared" si="2"/>
         <v>95</v>
@@ -39642,7 +39741,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" ns3:dyDescent="0.25">
       <c r="A97" s="3">
         <f t="shared" si="2"/>
         <v>96</v>
@@ -39666,7 +39765,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" ht="15.75" ns3:dyDescent="0.25">
       <c r="A98" s="3">
         <f t="shared" si="2"/>
         <v>97</v>
@@ -39694,7 +39793,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" ht="15.75" ns3:dyDescent="0.25">
       <c r="A99" s="3">
         <f t="shared" si="2"/>
         <v>98</v>
@@ -39722,7 +39821,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" ns3:dyDescent="0.25">
       <c r="A100" s="3">
         <f t="shared" si="2"/>
         <v>99</v>
@@ -39743,7 +39842,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" ns3:dyDescent="0.25">
       <c r="A101" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
@@ -39767,7 +39866,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" ns3:dyDescent="0.25">
       <c r="A102" s="3">
         <f t="shared" si="2"/>
         <v>101</v>
@@ -39794,7 +39893,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" ns3:dyDescent="0.25">
       <c r="A103" s="3">
         <f t="shared" si="2"/>
         <v>102</v>
@@ -39818,7 +39917,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" ns3:dyDescent="0.25">
       <c r="A104" s="3">
         <f t="shared" si="2"/>
         <v>103</v>
@@ -39839,7 +39938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" ns3:dyDescent="0.25">
       <c r="A105" s="3">
         <f t="shared" si="2"/>
         <v>104</v>
@@ -39869,7 +39968,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" ns3:dyDescent="0.25">
       <c r="A106" s="3">
         <f t="shared" si="2"/>
         <v>105</v>
@@ -39893,7 +39992,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" ns3:dyDescent="0.25">
       <c r="A107" s="3">
         <f t="shared" si="2"/>
         <v>106</v>
@@ -39917,7 +40016,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" ns3:dyDescent="0.25">
       <c r="A108" s="3">
         <f t="shared" si="2"/>
         <v>107</v>
@@ -39941,7 +40040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" ns3:dyDescent="0.25">
       <c r="A109" s="3">
         <f t="shared" si="2"/>
         <v>108</v>
@@ -39968,7 +40067,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" ht="15.75" ns3:dyDescent="0.25">
       <c r="A110" s="3">
         <f t="shared" si="2"/>
         <v>109</v>
@@ -40005,7 +40104,7 @@
       <c r="Q110"/>
       <c r="R110"/>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" ns3:dyDescent="0.25">
       <c r="A111" s="3">
         <f t="shared" si="2"/>
         <v>110</v>
@@ -40026,7 +40125,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" ns3:dyDescent="0.25">
       <c r="A112" s="3">
         <f t="shared" si="2"/>
         <v>111</v>
@@ -40047,7 +40146,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" ns3:dyDescent="0.25">
       <c r="A113" s="3">
         <f t="shared" si="2"/>
         <v>112</v>
@@ -40065,7 +40164,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" ns3:dyDescent="0.25">
       <c r="A114" s="3">
         <f t="shared" si="2"/>
         <v>113</v>
@@ -40089,7 +40188,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" ns3:dyDescent="0.25">
       <c r="A115" s="3">
         <f t="shared" si="2"/>
         <v>114</v>
@@ -40119,7 +40218,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" ns3:dyDescent="0.25">
       <c r="A116" s="3">
         <f t="shared" si="2"/>
         <v>115</v>
@@ -40149,7 +40248,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" ns3:dyDescent="0.25">
       <c r="A117" s="3">
         <f t="shared" si="2"/>
         <v>116</v>
@@ -40179,7 +40278,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" ns3:dyDescent="0.25">
       <c r="A118" s="3">
         <f t="shared" si="2"/>
         <v>117</v>
@@ -40209,7 +40308,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" ns3:dyDescent="0.25">
       <c r="A119" s="3">
         <f t="shared" si="2"/>
         <v>118</v>
@@ -40239,7 +40338,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" ns3:dyDescent="0.25">
       <c r="A120" s="3">
         <f t="shared" si="2"/>
         <v>119</v>
@@ -40269,7 +40368,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" ns3:dyDescent="0.25">
       <c r="A121" s="3">
         <f t="shared" si="2"/>
         <v>120</v>
@@ -40299,7 +40398,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" ns3:dyDescent="0.25">
       <c r="A122" s="3">
         <f t="shared" si="2"/>
         <v>121</v>
@@ -40329,7 +40428,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" ns3:dyDescent="0.25">
       <c r="A123" s="3">
         <f t="shared" si="2"/>
         <v>122</v>
@@ -40359,7 +40458,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" ns3:dyDescent="0.25">
       <c r="A124" s="3">
         <f t="shared" si="2"/>
         <v>123</v>
@@ -40389,7 +40488,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" ns3:dyDescent="0.25">
       <c r="A125" s="3">
         <f t="shared" si="2"/>
         <v>124</v>
@@ -40419,7 +40518,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" ns3:dyDescent="0.25">
       <c r="A126" s="3">
         <f t="shared" si="2"/>
         <v>125</v>
@@ -40449,7 +40548,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" ns3:dyDescent="0.25">
       <c r="A127" s="3">
         <f t="shared" si="2"/>
         <v>126</v>
@@ -40479,7 +40578,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" ns3:dyDescent="0.25">
       <c r="A128" s="3">
         <f t="shared" si="2"/>
         <v>127</v>
@@ -40509,7 +40608,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" ns3:dyDescent="0.25">
       <c r="A129" s="3">
         <f t="shared" si="2"/>
         <v>128</v>
@@ -40539,7 +40638,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" ns3:dyDescent="0.25">
       <c r="A130" s="3">
         <f t="shared" si="2"/>
         <v>129</v>
@@ -40569,7 +40668,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" ns3:dyDescent="0.25">
       <c r="A131" s="3">
         <f t="shared" si="2"/>
         <v>130</v>
@@ -40602,7 +40701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" ns3:dyDescent="0.25">
       <c r="A132" s="3">
         <f t="shared" ref="A132:A195" si="3">A131+1</f>
         <v>131</v>
@@ -40635,7 +40734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" ns3:dyDescent="0.25">
       <c r="A133" s="3">
         <f t="shared" si="3"/>
         <v>132</v>
@@ -40668,7 +40767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" ns3:dyDescent="0.25">
       <c r="A134" s="3">
         <f t="shared" si="3"/>
         <v>133</v>
@@ -40701,7 +40800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" ns3:dyDescent="0.25">
       <c r="A135" s="3">
         <f t="shared" si="3"/>
         <v>134</v>
@@ -40734,7 +40833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" ns3:dyDescent="0.25">
       <c r="A136" s="3">
         <f t="shared" si="3"/>
         <v>135</v>
@@ -40767,7 +40866,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" ns3:dyDescent="0.25">
       <c r="A137" s="3">
         <f t="shared" si="3"/>
         <v>136</v>
@@ -40800,7 +40899,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" ns3:dyDescent="0.25">
       <c r="A138" s="3">
         <f t="shared" si="3"/>
         <v>137</v>
@@ -40821,7 +40920,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" ns3:dyDescent="0.25">
       <c r="A139" s="3">
         <f t="shared" si="3"/>
         <v>138</v>
@@ -40851,7 +40950,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" ns3:dyDescent="0.25">
       <c r="A140" s="3">
         <f t="shared" si="3"/>
         <v>139</v>
@@ -40881,7 +40980,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" ns3:dyDescent="0.25">
       <c r="A141" s="3">
         <f t="shared" si="3"/>
         <v>140</v>
@@ -40902,7 +41001,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" ns3:dyDescent="0.25">
       <c r="A142" s="3">
         <f t="shared" si="3"/>
         <v>141</v>
@@ -40932,7 +41031,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" ns3:dyDescent="0.25">
       <c r="A143" s="3">
         <f t="shared" si="3"/>
         <v>142</v>
@@ -40962,7 +41061,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" ns3:dyDescent="0.25">
       <c r="A144" s="3">
         <f t="shared" si="3"/>
         <v>143</v>
@@ -40992,7 +41091,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" ns3:dyDescent="0.25">
       <c r="A145" s="3">
         <f t="shared" si="3"/>
         <v>144</v>
@@ -41013,7 +41112,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" ns3:dyDescent="0.25">
       <c r="A146" s="3">
         <f t="shared" si="3"/>
         <v>145</v>
@@ -41034,7 +41133,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" ns3:dyDescent="0.25">
       <c r="A147" s="3">
         <f t="shared" si="3"/>
         <v>146</v>
@@ -41055,7 +41154,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" ns3:dyDescent="0.25">
       <c r="A148" s="3">
         <f t="shared" si="3"/>
         <v>147</v>
@@ -41076,7 +41175,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" ns3:dyDescent="0.25">
       <c r="A149" s="3">
         <f t="shared" si="3"/>
         <v>148</v>
@@ -41097,7 +41196,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" ns3:dyDescent="0.25">
       <c r="A150" s="3">
         <f t="shared" si="3"/>
         <v>149</v>
@@ -41121,7 +41220,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" ns3:dyDescent="0.25">
       <c r="A151" s="3">
         <f t="shared" si="3"/>
         <v>150</v>
@@ -41160,7 +41259,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" ns3:dyDescent="0.25">
       <c r="A152" s="3">
         <f t="shared" si="3"/>
         <v>151</v>
@@ -41199,7 +41298,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" ns3:dyDescent="0.25">
       <c r="A153" s="3">
         <f t="shared" si="3"/>
         <v>152</v>
@@ -41238,7 +41337,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" ns3:dyDescent="0.25">
       <c r="A154" s="3">
         <f t="shared" si="3"/>
         <v>153</v>
@@ -41277,7 +41376,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" ns3:dyDescent="0.25">
       <c r="A155" s="3">
         <f t="shared" si="3"/>
         <v>154</v>
@@ -41316,7 +41415,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" ns3:dyDescent="0.25">
       <c r="A156" s="3">
         <f t="shared" si="3"/>
         <v>155</v>
@@ -41355,7 +41454,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" ns3:dyDescent="0.25">
       <c r="A157" s="3">
         <f t="shared" si="3"/>
         <v>156</v>
@@ -41394,7 +41493,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" ns3:dyDescent="0.25">
       <c r="A158" s="3">
         <f t="shared" si="3"/>
         <v>157</v>
@@ -41433,7 +41532,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" ns3:dyDescent="0.25">
       <c r="A159" s="3">
         <f t="shared" si="3"/>
         <v>158</v>
@@ -41451,7 +41550,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" ns3:dyDescent="0.25">
       <c r="A160" s="3">
         <f t="shared" si="3"/>
         <v>159</v>
@@ -41472,7 +41571,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" ns3:dyDescent="0.25">
       <c r="A161" s="3">
         <f t="shared" si="3"/>
         <v>160</v>
@@ -41493,7 +41592,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" ns3:dyDescent="0.25">
       <c r="A162" s="3">
         <f t="shared" si="3"/>
         <v>161</v>
@@ -41514,7 +41613,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" ns3:dyDescent="0.25">
       <c r="A163" s="3">
         <f t="shared" si="3"/>
         <v>162</v>
@@ -41532,7 +41631,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15" ns3:dyDescent="0.25">
       <c r="A164" s="3">
         <f t="shared" si="3"/>
         <v>163</v>
@@ -41559,7 +41658,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15" ns3:dyDescent="0.25">
       <c r="A165" s="3">
         <f t="shared" si="3"/>
         <v>164</v>
@@ -41589,7 +41688,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15" ns3:dyDescent="0.25">
       <c r="A166" s="3">
         <f t="shared" si="3"/>
         <v>165</v>
@@ -41613,7 +41712,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15" ns3:dyDescent="0.25">
       <c r="A167" s="3">
         <f t="shared" si="3"/>
         <v>166</v>
@@ -41637,7 +41736,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:15" ns3:dyDescent="0.25">
       <c r="A168" s="3">
         <f t="shared" si="3"/>
         <v>167</v>
@@ -41661,7 +41760,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15" ns3:dyDescent="0.25">
       <c r="A169" s="3">
         <f t="shared" si="3"/>
         <v>168</v>
@@ -41685,7 +41784,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:15" ns3:dyDescent="0.25">
       <c r="A170" s="3">
         <f t="shared" si="3"/>
         <v>169</v>
@@ -41730,7 +41829,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15" ns3:dyDescent="0.25">
       <c r="A171" s="3">
         <f t="shared" si="3"/>
         <v>170</v>
@@ -41775,7 +41874,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15" ns3:dyDescent="0.25">
       <c r="A172" s="3">
         <f t="shared" si="3"/>
         <v>171</v>
@@ -41796,7 +41895,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15" ns3:dyDescent="0.25">
       <c r="A173" s="3">
         <f t="shared" si="3"/>
         <v>172</v>
@@ -41823,7 +41922,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:15" ns3:dyDescent="0.25">
       <c r="A174" s="3">
         <f t="shared" si="3"/>
         <v>173</v>
@@ -41850,7 +41949,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:15" ns3:dyDescent="0.25">
       <c r="A175" s="3">
         <f t="shared" si="3"/>
         <v>174</v>
@@ -41874,7 +41973,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:15" ns3:dyDescent="0.25">
       <c r="A176" s="3">
         <f t="shared" si="3"/>
         <v>175</v>
@@ -41895,7 +41994,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:15" ns3:dyDescent="0.25">
       <c r="A177" s="3">
         <f t="shared" si="3"/>
         <v>176</v>
@@ -41928,7 +42027,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:15" ns3:dyDescent="0.25">
       <c r="A178" s="3">
         <f t="shared" si="3"/>
         <v>177</v>
@@ -41952,7 +42051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15" ns3:dyDescent="0.25">
       <c r="A179" s="3">
         <f t="shared" si="3"/>
         <v>178</v>
@@ -41982,7 +42081,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:15" ns3:dyDescent="0.25">
       <c r="A180" s="3">
         <f t="shared" si="3"/>
         <v>179</v>
@@ -42006,7 +42105,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:15" ns3:dyDescent="0.25">
       <c r="A181" s="3">
         <f t="shared" si="3"/>
         <v>180</v>
@@ -42030,7 +42129,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:15" ns3:dyDescent="0.25">
       <c r="A182" s="3">
         <f t="shared" si="3"/>
         <v>181</v>
@@ -42054,7 +42153,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:15" ns3:dyDescent="0.25">
       <c r="A183" s="3">
         <f t="shared" si="3"/>
         <v>182</v>
@@ -42078,7 +42177,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:15" ns3:dyDescent="0.25">
       <c r="A184" s="3">
         <f t="shared" si="3"/>
         <v>183</v>
@@ -42102,7 +42201,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:15" ns3:dyDescent="0.25">
       <c r="A185" s="3">
         <f t="shared" si="3"/>
         <v>184</v>
@@ -42120,7 +42219,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:15" ns3:dyDescent="0.25">
       <c r="A186" s="3">
         <f t="shared" si="3"/>
         <v>185</v>
@@ -42144,7 +42243,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:15" ns3:dyDescent="0.25">
       <c r="A187" s="3">
         <f t="shared" si="3"/>
         <v>186</v>
@@ -42171,7 +42270,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:15" ns3:dyDescent="0.25">
       <c r="A188" s="3">
         <f t="shared" si="3"/>
         <v>187</v>
@@ -42192,7 +42291,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:15" ns3:dyDescent="0.25">
       <c r="A189" s="3">
         <f t="shared" si="3"/>
         <v>188</v>
@@ -42237,7 +42336,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:15" ns3:dyDescent="0.25">
       <c r="A190" s="3">
         <f t="shared" si="3"/>
         <v>189</v>
@@ -42258,7 +42357,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:15" ns3:dyDescent="0.25">
       <c r="A191" s="3">
         <f t="shared" si="3"/>
         <v>190</v>
@@ -42276,7 +42375,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15" ns3:dyDescent="0.25">
       <c r="A192" s="3">
         <f t="shared" si="3"/>
         <v>191</v>
@@ -42294,7 +42393,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:11" ns3:dyDescent="0.25">
       <c r="A193" s="3">
         <f t="shared" si="3"/>
         <v>192</v>
@@ -42312,7 +42411,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:11" ns3:dyDescent="0.25">
       <c r="A194" s="3">
         <f t="shared" si="3"/>
         <v>193</v>
@@ -42333,7 +42432,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:11" ns3:dyDescent="0.25">
       <c r="A195" s="3">
         <f t="shared" si="3"/>
         <v>194</v>
@@ -42357,7 +42456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:11" ns3:dyDescent="0.25">
       <c r="A196" s="3">
         <f t="shared" ref="A196:A259" si="4">A195+1</f>
         <v>195</v>
@@ -42378,7 +42477,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:11" ns3:dyDescent="0.25">
       <c r="A197" s="3">
         <f t="shared" si="4"/>
         <v>196</v>
@@ -42399,7 +42498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:11" ns3:dyDescent="0.25">
       <c r="A198" s="3">
         <f t="shared" si="4"/>
         <v>197</v>
@@ -42420,7 +42519,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:11" ns3:dyDescent="0.25">
       <c r="A199" s="3">
         <f t="shared" si="4"/>
         <v>198</v>
@@ -42441,7 +42540,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:11" ns3:dyDescent="0.25">
       <c r="A200" s="3">
         <f t="shared" si="4"/>
         <v>199</v>
@@ -42459,7 +42558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:11" ns3:dyDescent="0.25">
       <c r="A201" s="3">
         <f t="shared" si="4"/>
         <v>200</v>
@@ -42480,7 +42579,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:11" ns3:dyDescent="0.25">
       <c r="A202" s="3">
         <f t="shared" si="4"/>
         <v>201</v>
@@ -42501,7 +42600,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:11" ns3:dyDescent="0.25">
       <c r="A203" s="3">
         <f t="shared" si="4"/>
         <v>202</v>
@@ -42522,7 +42621,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:11" ns3:dyDescent="0.25">
       <c r="A204" s="3">
         <f t="shared" si="4"/>
         <v>203</v>
@@ -42540,7 +42639,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:11" ns3:dyDescent="0.25">
       <c r="A205" s="3">
         <f t="shared" si="4"/>
         <v>204</v>
@@ -42573,7 +42672,7 @@
         <v>8100</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:11" ns3:dyDescent="0.25">
       <c r="A206" s="3">
         <f t="shared" si="4"/>
         <v>205</v>
@@ -42597,7 +42696,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:11" ns3:dyDescent="0.25">
       <c r="A207" s="3">
         <f t="shared" si="4"/>
         <v>206</v>
@@ -42618,7 +42717,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:11" ns3:dyDescent="0.25">
       <c r="A208" s="3">
         <f t="shared" si="4"/>
         <v>207</v>
@@ -42639,7 +42738,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:16" ns3:dyDescent="0.25">
       <c r="A209" s="3">
         <f t="shared" si="4"/>
         <v>208</v>
@@ -42666,7 +42765,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:16" ns3:dyDescent="0.25">
       <c r="A210" s="3">
         <f t="shared" si="4"/>
         <v>209</v>
@@ -42684,7 +42783,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:16" ns3:dyDescent="0.25">
       <c r="A211" s="3">
         <f t="shared" si="4"/>
         <v>210</v>
@@ -42711,7 +42810,7 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:16" ns3:dyDescent="0.25">
       <c r="A212" s="3">
         <f t="shared" si="4"/>
         <v>211</v>
@@ -42735,7 +42834,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:16" ns3:dyDescent="0.25">
       <c r="A213" s="3">
         <f t="shared" si="4"/>
         <v>212</v>
@@ -42753,7 +42852,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:16" ns3:dyDescent="0.25">
       <c r="A214" s="3">
         <f t="shared" si="4"/>
         <v>213</v>
@@ -42801,7 +42900,7 @@
         <v>1000000000000</v>
       </c>
     </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:16" ns3:dyDescent="0.25">
       <c r="A215" s="3">
         <f t="shared" si="4"/>
         <v>214</v>
@@ -42825,7 +42924,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:16" ns3:dyDescent="0.25">
       <c r="A216" s="3">
         <f t="shared" si="4"/>
         <v>215</v>
@@ -42852,7 +42951,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:16" ns3:dyDescent="0.25">
       <c r="A217" s="3">
         <f t="shared" si="4"/>
         <v>216</v>
@@ -42882,7 +42981,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:16" ns3:dyDescent="0.25">
       <c r="A218" s="3">
         <f t="shared" si="4"/>
         <v>217</v>
@@ -42912,7 +43011,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:16" ns3:dyDescent="0.25">
       <c r="A219" s="3">
         <f t="shared" si="4"/>
         <v>218</v>
@@ -42942,7 +43041,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:16" ns3:dyDescent="0.25">
       <c r="A220" s="3">
         <f t="shared" si="4"/>
         <v>219</v>
@@ -42975,7 +43074,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:16" ns3:dyDescent="0.25">
       <c r="A221" s="3">
         <f t="shared" si="4"/>
         <v>220</v>
@@ -43008,7 +43107,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:16" ns3:dyDescent="0.25">
       <c r="A222" s="3">
         <f t="shared" si="4"/>
         <v>221</v>
@@ -43041,7 +43140,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:16" ns3:dyDescent="0.25">
       <c r="A223" s="3">
         <f t="shared" si="4"/>
         <v>222</v>
@@ -43074,7 +43173,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:16" ns3:dyDescent="0.25">
       <c r="A224" s="3">
         <f t="shared" si="4"/>
         <v>223</v>
@@ -43107,7 +43206,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" ns3:dyDescent="0.25">
       <c r="A225" s="3">
         <f t="shared" si="4"/>
         <v>224</v>
@@ -43140,7 +43239,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" ns3:dyDescent="0.25">
       <c r="A226" s="3">
         <f t="shared" si="4"/>
         <v>225</v>
@@ -43173,7 +43272,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" ns3:dyDescent="0.25">
       <c r="A227" s="3">
         <f t="shared" si="4"/>
         <v>226</v>
@@ -43206,7 +43305,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" ns3:dyDescent="0.25">
       <c r="A228" s="3">
         <f t="shared" si="4"/>
         <v>227</v>
@@ -43239,7 +43338,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" ns3:dyDescent="0.25">
       <c r="A229" s="3">
         <f t="shared" si="4"/>
         <v>228</v>
@@ -43272,7 +43371,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" ns3:dyDescent="0.25">
       <c r="A230" s="3">
         <f t="shared" si="4"/>
         <v>229</v>
@@ -43305,7 +43404,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" ns3:dyDescent="0.25">
       <c r="A231" s="3">
         <f t="shared" si="4"/>
         <v>230</v>
@@ -43338,7 +43437,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" ns3:dyDescent="0.25">
       <c r="A232" s="3">
         <f t="shared" si="4"/>
         <v>231</v>
@@ -43374,7 +43473,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" ns3:dyDescent="0.25">
       <c r="A233" s="3">
         <f t="shared" si="4"/>
         <v>232</v>
@@ -43410,7 +43509,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" ns3:dyDescent="0.25">
       <c r="A234" s="3">
         <f t="shared" si="4"/>
         <v>233</v>
@@ -43446,7 +43545,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" ns3:dyDescent="0.25">
       <c r="A235" s="3">
         <f t="shared" si="4"/>
         <v>234</v>
@@ -43476,7 +43575,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" ns3:dyDescent="0.25">
       <c r="A236" s="3">
         <f t="shared" si="4"/>
         <v>235</v>
@@ -43506,7 +43605,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" ns3:dyDescent="0.25">
       <c r="A237" s="3">
         <f t="shared" si="4"/>
         <v>236</v>
@@ -43536,7 +43635,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" ns3:dyDescent="0.25">
       <c r="A238" s="3">
         <f t="shared" si="4"/>
         <v>237</v>
@@ -43569,7 +43668,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" ns3:dyDescent="0.25">
       <c r="A239" s="3">
         <f t="shared" si="4"/>
         <v>238</v>
@@ -43602,7 +43701,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" ns3:dyDescent="0.25">
       <c r="A240" s="3">
         <f t="shared" si="4"/>
         <v>239</v>
@@ -43635,7 +43734,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:16" ns3:dyDescent="0.25">
       <c r="A241" s="3">
         <f t="shared" si="4"/>
         <v>240</v>
@@ -43668,7 +43767,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:16" ns3:dyDescent="0.25">
       <c r="A242" s="3">
         <f t="shared" si="4"/>
         <v>241</v>
@@ -43701,7 +43800,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:16" ns3:dyDescent="0.25">
       <c r="A243" s="3">
         <f t="shared" si="4"/>
         <v>242</v>
@@ -43734,7 +43833,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:16" ns3:dyDescent="0.25">
       <c r="A244" s="3">
         <f t="shared" si="4"/>
         <v>243</v>
@@ -43770,7 +43869,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:16" ns3:dyDescent="0.25">
       <c r="A245" s="3">
         <f t="shared" si="4"/>
         <v>244</v>
@@ -43806,7 +43905,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:16" ns3:dyDescent="0.25">
       <c r="A246" s="3">
         <f t="shared" si="4"/>
         <v>245</v>
@@ -43842,7 +43941,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:16" ns3:dyDescent="0.25">
       <c r="A247" s="3">
         <f t="shared" si="4"/>
         <v>246</v>
@@ -43878,7 +43977,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="248" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:16" ns3:dyDescent="0.25">
       <c r="A248" s="3">
         <f t="shared" si="4"/>
         <v>247</v>
@@ -43914,7 +44013,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:16" ns3:dyDescent="0.25">
       <c r="A249" s="3">
         <f t="shared" si="4"/>
         <v>248</v>
@@ -43953,7 +44052,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:16" ns3:dyDescent="0.25">
       <c r="A250" s="3">
         <f t="shared" si="4"/>
         <v>249</v>
@@ -43992,7 +44091,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:16" ns3:dyDescent="0.25">
       <c r="A251" s="3">
         <f t="shared" si="4"/>
         <v>250</v>
@@ -44031,7 +44130,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:16" ns3:dyDescent="0.25">
       <c r="A252" s="3">
         <f t="shared" si="4"/>
         <v>251</v>
@@ -44073,7 +44172,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:16" ns3:dyDescent="0.25">
       <c r="A253" s="3">
         <f t="shared" si="4"/>
         <v>252</v>
@@ -44118,7 +44217,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:16" ns3:dyDescent="0.25">
       <c r="A254" s="3">
         <f t="shared" si="4"/>
         <v>253</v>
@@ -44166,7 +44265,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:16" ns3:dyDescent="0.25">
       <c r="A255" s="3">
         <f t="shared" si="4"/>
         <v>254</v>
@@ -44184,7 +44283,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:16" ns3:dyDescent="0.25">
       <c r="A256" s="3">
         <f t="shared" si="4"/>
         <v>255</v>
@@ -44205,7 +44304,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:11" ns3:dyDescent="0.25">
       <c r="A257" s="3">
         <f t="shared" si="4"/>
         <v>256</v>
@@ -44223,7 +44322,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:11" ns3:dyDescent="0.25">
       <c r="A258" s="3">
         <f t="shared" si="4"/>
         <v>257</v>
@@ -44241,7 +44340,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:11" ns3:dyDescent="0.25">
       <c r="A259" s="3">
         <f t="shared" si="4"/>
         <v>258</v>
@@ -44262,7 +44361,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:11" ns3:dyDescent="0.25">
       <c r="A260" s="3">
         <f t="shared" ref="A260:A323" si="5">A259+1</f>
         <v>259</v>
@@ -44280,7 +44379,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:11" ns3:dyDescent="0.25">
       <c r="A261" s="3">
         <f t="shared" si="5"/>
         <v>260</v>
@@ -44307,7 +44406,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:11" ns3:dyDescent="0.25">
       <c r="A262" s="3">
         <f t="shared" si="5"/>
         <v>261</v>
@@ -44328,7 +44427,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:11" ns3:dyDescent="0.25">
       <c r="A263" s="3">
         <f t="shared" si="5"/>
         <v>262</v>
@@ -44346,7 +44445,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:11" ns3:dyDescent="0.25">
       <c r="A264" s="3">
         <f t="shared" si="5"/>
         <v>263</v>
@@ -44379,7 +44478,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:11" ns3:dyDescent="0.25">
       <c r="A265" s="3">
         <f t="shared" si="5"/>
         <v>264</v>
@@ -44400,7 +44499,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:11" ns3:dyDescent="0.25">
       <c r="A266" s="3">
         <f t="shared" si="5"/>
         <v>265</v>
@@ -44418,7 +44517,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:11" ns3:dyDescent="0.25">
       <c r="A267" s="3">
         <f t="shared" si="5"/>
         <v>266</v>
@@ -44442,7 +44541,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:11" ns3:dyDescent="0.25">
       <c r="A268" s="3">
         <f t="shared" si="5"/>
         <v>267</v>
@@ -44460,7 +44559,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:11" ns3:dyDescent="0.25">
       <c r="A269" s="3">
         <f t="shared" si="5"/>
         <v>268</v>
@@ -44481,7 +44580,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:11" ns3:dyDescent="0.25">
       <c r="A270" s="3">
         <f t="shared" si="5"/>
         <v>269</v>
@@ -44502,7 +44601,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:11" ns3:dyDescent="0.25">
       <c r="A271" s="3">
         <f t="shared" si="5"/>
         <v>270</v>
@@ -44523,7 +44622,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:11" ns3:dyDescent="0.25">
       <c r="A272" s="3">
         <f t="shared" si="5"/>
         <v>271</v>
@@ -44544,7 +44643,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" ns3:dyDescent="0.25">
       <c r="A273" s="3">
         <f t="shared" si="5"/>
         <v>272</v>
@@ -44580,7 +44679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" ns3:dyDescent="0.25">
       <c r="A274" s="3">
         <f t="shared" si="5"/>
         <v>273</v>
@@ -44616,7 +44715,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" ns3:dyDescent="0.25">
       <c r="A275" s="3">
         <f t="shared" si="5"/>
         <v>274</v>
@@ -44652,7 +44751,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" ns3:dyDescent="0.25">
       <c r="A276" s="3">
         <f t="shared" si="5"/>
         <v>275</v>
@@ -44688,7 +44787,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" ns3:dyDescent="0.25">
       <c r="A277" s="3">
         <f t="shared" si="5"/>
         <v>276</v>
@@ -44724,7 +44823,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" ns3:dyDescent="0.25">
       <c r="A278" s="3">
         <f t="shared" si="5"/>
         <v>277</v>
@@ -44760,7 +44859,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" ns3:dyDescent="0.25">
       <c r="A279" s="3">
         <f t="shared" si="5"/>
         <v>278</v>
@@ -44796,7 +44895,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" ns3:dyDescent="0.25">
       <c r="A280" s="3">
         <f t="shared" si="5"/>
         <v>279</v>
@@ -44832,7 +44931,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" ns3:dyDescent="0.25">
       <c r="A281" s="3">
         <f t="shared" si="5"/>
         <v>280</v>
@@ -44868,7 +44967,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" ns3:dyDescent="0.25">
       <c r="A282" s="3">
         <f t="shared" si="5"/>
         <v>281</v>
@@ -44901,7 +45000,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" ns3:dyDescent="0.25">
       <c r="A283" s="3">
         <f t="shared" si="5"/>
         <v>282</v>
@@ -44934,7 +45033,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" ns3:dyDescent="0.25">
       <c r="A284" s="3">
         <f t="shared" si="5"/>
         <v>283</v>
@@ -44967,7 +45066,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" ns3:dyDescent="0.25">
       <c r="A285" s="3">
         <f t="shared" si="5"/>
         <v>284</v>
@@ -45000,7 +45099,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" ns3:dyDescent="0.25">
       <c r="A286" s="3">
         <f t="shared" si="5"/>
         <v>285</v>
@@ -45033,7 +45132,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" ns3:dyDescent="0.25">
       <c r="A287" s="3">
         <f t="shared" si="5"/>
         <v>286</v>
@@ -45066,7 +45165,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" ns3:dyDescent="0.25">
       <c r="A288" s="3">
         <f t="shared" si="5"/>
         <v>287</v>
@@ -45099,7 +45198,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:11" ns3:dyDescent="0.25">
       <c r="A289" s="3">
         <f t="shared" si="5"/>
         <v>288</v>
@@ -45132,7 +45231,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:11" ns3:dyDescent="0.25">
       <c r="A290" s="3">
         <f t="shared" si="5"/>
         <v>289</v>
@@ -45165,7 +45264,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:11" ns3:dyDescent="0.25">
       <c r="A291" s="3">
         <f t="shared" si="5"/>
         <v>290</v>
@@ -45198,7 +45297,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:11" ns3:dyDescent="0.25">
       <c r="A292" s="3">
         <f t="shared" si="5"/>
         <v>291</v>
@@ -45231,7 +45330,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:11" ns3:dyDescent="0.25">
       <c r="A293" s="3">
         <f t="shared" si="5"/>
         <v>292</v>
@@ -45264,7 +45363,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:11" ns3:dyDescent="0.25">
       <c r="A294" s="3">
         <f t="shared" si="5"/>
         <v>293</v>
@@ -45297,7 +45396,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:11" ns3:dyDescent="0.25">
       <c r="A295" s="3">
         <f t="shared" si="5"/>
         <v>294</v>
@@ -45330,7 +45429,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:11" ns3:dyDescent="0.25">
       <c r="A296" s="3">
         <f t="shared" si="5"/>
         <v>295</v>
@@ -45363,7 +45462,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:11" ns3:dyDescent="0.25">
       <c r="A297" s="3">
         <f t="shared" si="5"/>
         <v>296</v>
@@ -45396,7 +45495,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:11" ns3:dyDescent="0.25">
       <c r="A298" s="3">
         <f t="shared" si="5"/>
         <v>297</v>
@@ -45429,7 +45528,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:11" ns3:dyDescent="0.25">
       <c r="A299" s="3">
         <f t="shared" si="5"/>
         <v>298</v>
@@ -45462,7 +45561,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:11" ns3:dyDescent="0.25">
       <c r="A300" s="3">
         <f t="shared" si="5"/>
         <v>299</v>
@@ -45495,7 +45594,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:11" ns3:dyDescent="0.25">
       <c r="A301" s="3">
         <f t="shared" si="5"/>
         <v>300</v>
@@ -45528,7 +45627,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:11" ns3:dyDescent="0.25">
       <c r="A302" s="3">
         <f t="shared" si="5"/>
         <v>301</v>
@@ -45561,7 +45660,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:11" ns3:dyDescent="0.25">
       <c r="A303" s="3">
         <f t="shared" si="5"/>
         <v>302</v>
@@ -45594,7 +45693,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:11" ns3:dyDescent="0.25">
       <c r="A304" s="3">
         <f t="shared" si="5"/>
         <v>303</v>
@@ -45627,7 +45726,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:11" ns3:dyDescent="0.25">
       <c r="A305" s="3">
         <f t="shared" si="5"/>
         <v>304</v>
@@ -45660,7 +45759,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:11" ns3:dyDescent="0.25">
       <c r="A306" s="3">
         <f t="shared" si="5"/>
         <v>305</v>
@@ -45693,7 +45792,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:11" ns3:dyDescent="0.25">
       <c r="A307" s="3">
         <f t="shared" si="5"/>
         <v>306</v>
@@ -45726,7 +45825,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:11" ns3:dyDescent="0.25">
       <c r="A308" s="3">
         <f t="shared" si="5"/>
         <v>307</v>
@@ -45759,7 +45858,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:11" ns3:dyDescent="0.25">
       <c r="A309" s="3">
         <f t="shared" si="5"/>
         <v>308</v>
@@ -45792,7 +45891,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:11" ns3:dyDescent="0.25">
       <c r="A310" s="3">
         <f t="shared" si="5"/>
         <v>309</v>
@@ -45825,7 +45924,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:11" ns3:dyDescent="0.25">
       <c r="A311" s="3">
         <f t="shared" si="5"/>
         <v>310</v>
@@ -45858,7 +45957,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:11" ns3:dyDescent="0.25">
       <c r="A312" s="3">
         <f t="shared" si="5"/>
         <v>311</v>
@@ -45891,7 +45990,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:11" ns3:dyDescent="0.25">
       <c r="A313" s="3">
         <f t="shared" si="5"/>
         <v>312</v>
@@ -45924,7 +46023,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:11" ns3:dyDescent="0.25">
       <c r="A314" s="3">
         <f t="shared" si="5"/>
         <v>313</v>
@@ -45957,7 +46056,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:11" ns3:dyDescent="0.25">
       <c r="A315" s="3">
         <f t="shared" si="5"/>
         <v>314</v>
@@ -45990,7 +46089,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:11" ns3:dyDescent="0.25">
       <c r="A316" s="3">
         <f t="shared" si="5"/>
         <v>315</v>
@@ -46023,7 +46122,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:11" ns3:dyDescent="0.25">
       <c r="A317" s="3">
         <f t="shared" si="5"/>
         <v>316</v>
@@ -46056,7 +46155,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:11" ns3:dyDescent="0.25">
       <c r="A318" s="3">
         <f t="shared" si="5"/>
         <v>317</v>
@@ -46089,7 +46188,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:11" ns3:dyDescent="0.25">
       <c r="A319" s="3">
         <f t="shared" si="5"/>
         <v>318</v>
@@ -46122,7 +46221,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:11" ns3:dyDescent="0.25">
       <c r="A320" s="3">
         <f t="shared" si="5"/>
         <v>319</v>
@@ -46155,7 +46254,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:11" ns3:dyDescent="0.25">
       <c r="A321" s="3">
         <f t="shared" si="5"/>
         <v>320</v>
@@ -46188,7 +46287,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:11" ns3:dyDescent="0.25">
       <c r="A322" s="3">
         <f t="shared" si="5"/>
         <v>321</v>
@@ -46221,7 +46320,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:11" ns3:dyDescent="0.25">
       <c r="A323" s="3">
         <f t="shared" si="5"/>
         <v>322</v>
@@ -46254,7 +46353,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:11" ns3:dyDescent="0.25">
       <c r="A324" s="3">
         <f t="shared" ref="A324:A387" si="6">A323+1</f>
         <v>323</v>
@@ -46287,7 +46386,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:11" ns3:dyDescent="0.25">
       <c r="A325" s="3">
         <f t="shared" si="6"/>
         <v>324</v>
@@ -46320,7 +46419,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:11" ns3:dyDescent="0.25">
       <c r="A326" s="3">
         <f t="shared" si="6"/>
         <v>325</v>
@@ -46353,7 +46452,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:11" ns3:dyDescent="0.25">
       <c r="A327" s="3">
         <f t="shared" si="6"/>
         <v>326</v>
@@ -46386,7 +46485,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:11" ns3:dyDescent="0.25">
       <c r="A328" s="3">
         <f t="shared" si="6"/>
         <v>327</v>
@@ -46419,7 +46518,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:11" ns3:dyDescent="0.25">
       <c r="A329" s="3">
         <f t="shared" si="6"/>
         <v>328</v>
@@ -46452,7 +46551,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:11" ns3:dyDescent="0.25">
       <c r="A330" s="3">
         <f t="shared" si="6"/>
         <v>329</v>
@@ -46485,7 +46584,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:11" ns3:dyDescent="0.25">
       <c r="A331" s="3">
         <f t="shared" si="6"/>
         <v>330</v>
@@ -46518,7 +46617,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:11" ns3:dyDescent="0.25">
       <c r="A332" s="3">
         <f t="shared" si="6"/>
         <v>331</v>
@@ -46551,7 +46650,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:11" ns3:dyDescent="0.25">
       <c r="A333" s="3">
         <f t="shared" si="6"/>
         <v>332</v>
@@ -46584,7 +46683,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:11" ns3:dyDescent="0.25">
       <c r="A334" s="3">
         <f t="shared" si="6"/>
         <v>333</v>
@@ -46617,7 +46716,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:11" ns3:dyDescent="0.25">
       <c r="A335" s="3">
         <f t="shared" si="6"/>
         <v>334</v>
@@ -46650,7 +46749,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:11" ns3:dyDescent="0.25">
       <c r="A336" s="3">
         <f t="shared" si="6"/>
         <v>335</v>
@@ -46683,7 +46782,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:11" ns3:dyDescent="0.25">
       <c r="A337" s="3">
         <f t="shared" si="6"/>
         <v>336</v>
@@ -46716,7 +46815,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:11" ns3:dyDescent="0.25">
       <c r="A338" s="3">
         <f t="shared" si="6"/>
         <v>337</v>
@@ -46749,7 +46848,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:11" ns3:dyDescent="0.25">
       <c r="A339" s="3">
         <f t="shared" si="6"/>
         <v>338</v>
@@ -46782,7 +46881,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:11" ns3:dyDescent="0.25">
       <c r="A340" s="3">
         <f t="shared" si="6"/>
         <v>339</v>
@@ -46815,7 +46914,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:11" ns3:dyDescent="0.25">
       <c r="A341" s="3">
         <f t="shared" si="6"/>
         <v>340</v>
@@ -46848,7 +46947,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:11" ns3:dyDescent="0.25">
       <c r="A342" s="3">
         <f t="shared" si="6"/>
         <v>341</v>
@@ -46875,7 +46974,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:11" ns3:dyDescent="0.25">
       <c r="A343" s="3">
         <f t="shared" si="6"/>
         <v>342</v>
@@ -46902,7 +47001,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:11" ns3:dyDescent="0.25">
       <c r="A344" s="3">
         <f t="shared" si="6"/>
         <v>343</v>
@@ -46929,7 +47028,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:11" ns3:dyDescent="0.25">
       <c r="A345" s="3">
         <f t="shared" si="6"/>
         <v>344</v>
@@ -46956,7 +47055,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:11" ns3:dyDescent="0.25">
       <c r="A346" s="3">
         <f t="shared" si="6"/>
         <v>345</v>
@@ -46983,7 +47082,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:11" ns3:dyDescent="0.25">
       <c r="A347" s="3">
         <f t="shared" si="6"/>
         <v>346</v>
@@ -47010,7 +47109,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:11" ns3:dyDescent="0.25">
       <c r="A348" s="3">
         <f t="shared" si="6"/>
         <v>347</v>
@@ -47037,7 +47136,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:11" ns3:dyDescent="0.25">
       <c r="A349" s="3">
         <f t="shared" si="6"/>
         <v>348</v>
@@ -47058,7 +47157,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:11" ns3:dyDescent="0.25">
       <c r="A350" s="3">
         <f t="shared" si="6"/>
         <v>349</v>
@@ -47079,7 +47178,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:11" ns3:dyDescent="0.25">
       <c r="A351" s="3">
         <f t="shared" si="6"/>
         <v>350</v>
@@ -47100,7 +47199,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:11" ns3:dyDescent="0.25">
       <c r="A352" s="3">
         <f t="shared" si="6"/>
         <v>351</v>
@@ -47121,7 +47220,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" ns3:dyDescent="0.25">
       <c r="A353" s="3">
         <f t="shared" si="6"/>
         <v>352</v>
@@ -47142,7 +47241,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" ns3:dyDescent="0.25">
       <c r="A354" s="3">
         <f t="shared" si="6"/>
         <v>353</v>
@@ -47163,7 +47262,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" ns3:dyDescent="0.25">
       <c r="A355" s="3">
         <f t="shared" si="6"/>
         <v>354</v>
@@ -47184,7 +47283,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" ns3:dyDescent="0.25">
       <c r="A356" s="3">
         <f t="shared" si="6"/>
         <v>355</v>
@@ -47205,7 +47304,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" ns3:dyDescent="0.25">
       <c r="A357" s="3">
         <f t="shared" si="6"/>
         <v>356</v>
@@ -47226,7 +47325,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" ns3:dyDescent="0.25">
       <c r="A358" s="3">
         <f t="shared" si="6"/>
         <v>357</v>
@@ -47247,7 +47346,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" ns3:dyDescent="0.25">
       <c r="A359" s="3">
         <f t="shared" si="6"/>
         <v>358</v>
@@ -47268,7 +47367,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" ns3:dyDescent="0.25">
       <c r="A360" s="3">
         <f t="shared" si="6"/>
         <v>359</v>
@@ -47289,7 +47388,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" ns3:dyDescent="0.25">
       <c r="A361" s="3">
         <f t="shared" si="6"/>
         <v>360</v>
@@ -47316,7 +47415,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" ns3:dyDescent="0.25">
       <c r="A362" s="3">
         <f t="shared" si="6"/>
         <v>361</v>
@@ -47343,7 +47442,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" ns3:dyDescent="0.25">
       <c r="A363" s="3">
         <f t="shared" si="6"/>
         <v>362</v>
@@ -47370,7 +47469,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" ns3:dyDescent="0.25">
       <c r="A364" s="3">
         <f t="shared" si="6"/>
         <v>363</v>
@@ -47397,7 +47496,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" ns3:dyDescent="0.25">
       <c r="A365" s="3">
         <f t="shared" si="6"/>
         <v>364</v>
@@ -47424,7 +47523,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" ns3:dyDescent="0.25">
       <c r="A366" s="3">
         <f t="shared" si="6"/>
         <v>365</v>
@@ -47451,7 +47550,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" ns3:dyDescent="0.25">
       <c r="A367" s="3">
         <f t="shared" si="6"/>
         <v>366</v>
@@ -47478,7 +47577,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" ns3:dyDescent="0.25">
       <c r="A368" s="3">
         <f t="shared" si="6"/>
         <v>367</v>
@@ -47505,7 +47604,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" ns3:dyDescent="0.25">
       <c r="A369" s="3">
         <f t="shared" si="6"/>
         <v>368</v>
@@ -47532,7 +47631,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" ns3:dyDescent="0.25">
       <c r="A370" s="3">
         <f t="shared" si="6"/>
         <v>369</v>
@@ -47559,7 +47658,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" ns3:dyDescent="0.25">
       <c r="A371" s="3">
         <f t="shared" si="6"/>
         <v>370</v>
@@ -47586,7 +47685,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" ns3:dyDescent="0.25">
       <c r="A372" s="3">
         <f t="shared" si="6"/>
         <v>371</v>
@@ -47613,7 +47712,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" ns3:dyDescent="0.25">
       <c r="A373" s="3">
         <f t="shared" si="6"/>
         <v>372</v>
@@ -47640,7 +47739,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" ns3:dyDescent="0.25">
       <c r="A374" s="3">
         <f t="shared" si="6"/>
         <v>373</v>
@@ -47667,7 +47766,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" ns3:dyDescent="0.25">
       <c r="A375" s="3">
         <f t="shared" si="6"/>
         <v>374</v>
@@ -47694,7 +47793,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" ns3:dyDescent="0.25">
       <c r="A376" s="3">
         <f t="shared" si="6"/>
         <v>375</v>
@@ -47721,7 +47820,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" ns3:dyDescent="0.25">
       <c r="A377" s="3">
         <f t="shared" si="6"/>
         <v>376</v>
@@ -47748,7 +47847,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" ns3:dyDescent="0.25">
       <c r="A378" s="3">
         <f t="shared" si="6"/>
         <v>377</v>
@@ -47775,7 +47874,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" ns3:dyDescent="0.25">
       <c r="A379" s="3">
         <f t="shared" si="6"/>
         <v>378</v>
@@ -47799,7 +47898,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" ns3:dyDescent="0.25">
       <c r="A380" s="3">
         <f t="shared" si="6"/>
         <v>379</v>
@@ -47823,7 +47922,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" ns3:dyDescent="0.25">
       <c r="A381" s="3">
         <f t="shared" si="6"/>
         <v>380</v>
@@ -47847,7 +47946,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" ns3:dyDescent="0.25">
       <c r="A382" s="3">
         <f t="shared" si="6"/>
         <v>381</v>
@@ -47871,7 +47970,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" ns3:dyDescent="0.25">
       <c r="A383" s="3">
         <f t="shared" si="6"/>
         <v>382</v>
@@ -47895,7 +47994,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" ns3:dyDescent="0.25">
       <c r="A384" s="3">
         <f t="shared" si="6"/>
         <v>383</v>
@@ -47919,7 +48018,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:8" ns3:dyDescent="0.25">
       <c r="A385" s="3">
         <f t="shared" si="6"/>
         <v>384</v>
@@ -47943,7 +48042,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:8" ns3:dyDescent="0.25">
       <c r="A386" s="3">
         <f t="shared" si="6"/>
         <v>385</v>
@@ -47967,7 +48066,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:8" ns3:dyDescent="0.25">
       <c r="A387" s="3">
         <f t="shared" si="6"/>
         <v>386</v>
@@ -47991,7 +48090,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:8" ns3:dyDescent="0.25">
       <c r="A388" s="3">
         <f t="shared" ref="A388:A451" si="7">A387+1</f>
         <v>387</v>
@@ -48015,7 +48114,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:8" ns3:dyDescent="0.25">
       <c r="A389" s="3">
         <f t="shared" si="7"/>
         <v>388</v>
@@ -48039,7 +48138,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:8" ns3:dyDescent="0.25">
       <c r="A390" s="3">
         <f t="shared" si="7"/>
         <v>389</v>
@@ -48063,7 +48162,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:8" ns3:dyDescent="0.25">
       <c r="A391" s="3">
         <f t="shared" si="7"/>
         <v>390</v>
@@ -48084,7 +48183,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:8" ns3:dyDescent="0.25">
       <c r="A392" s="3">
         <f t="shared" si="7"/>
         <v>391</v>
@@ -48105,7 +48204,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:8" ns3:dyDescent="0.25">
       <c r="A393" s="3">
         <f t="shared" si="7"/>
         <v>392</v>
@@ -48126,7 +48225,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:8" ns3:dyDescent="0.25">
       <c r="A394" s="3">
         <f t="shared" si="7"/>
         <v>393</v>
@@ -48147,7 +48246,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:8" ns3:dyDescent="0.25">
       <c r="A395" s="3">
         <f t="shared" si="7"/>
         <v>394</v>
@@ -48168,7 +48267,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:8" ns3:dyDescent="0.25">
       <c r="A396" s="3">
         <f t="shared" si="7"/>
         <v>395</v>
@@ -48192,7 +48291,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:8" ns3:dyDescent="0.25">
       <c r="A397" s="3">
         <f t="shared" si="7"/>
         <v>396</v>
@@ -48213,7 +48312,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:8" ns3:dyDescent="0.25">
       <c r="A398" s="3">
         <f t="shared" si="7"/>
         <v>397</v>
@@ -48234,7 +48333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:8" ns3:dyDescent="0.25">
       <c r="A399" s="3">
         <f t="shared" si="7"/>
         <v>398</v>
@@ -48255,7 +48354,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:8" ns3:dyDescent="0.25">
       <c r="A400" s="3">
         <f t="shared" si="7"/>
         <v>399</v>
@@ -48276,7 +48375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:7" ns3:dyDescent="0.25">
       <c r="A401" s="3">
         <f t="shared" si="7"/>
         <v>400</v>
@@ -48297,7 +48396,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:7" ns3:dyDescent="0.25">
       <c r="A402" s="3">
         <f t="shared" si="7"/>
         <v>401</v>
@@ -48318,7 +48417,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:7" ns3:dyDescent="0.25">
       <c r="A403" s="3">
         <f t="shared" si="7"/>
         <v>402</v>
@@ -48339,7 +48438,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:7" ns3:dyDescent="0.25">
       <c r="A404" s="3">
         <f t="shared" si="7"/>
         <v>403</v>
@@ -48360,7 +48459,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:7" ns3:dyDescent="0.25">
       <c r="A405" s="3">
         <f t="shared" si="7"/>
         <v>404</v>
@@ -48381,7 +48480,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:7" ns3:dyDescent="0.25">
       <c r="A406" s="3">
         <f t="shared" si="7"/>
         <v>405</v>
@@ -48402,7 +48501,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:7" ns3:dyDescent="0.25">
       <c r="A407" s="3">
         <f t="shared" si="7"/>
         <v>406</v>
@@ -48423,7 +48522,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:7" ns3:dyDescent="0.25">
       <c r="A408" s="3">
         <f t="shared" si="7"/>
         <v>407</v>
@@ -48444,7 +48543,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:7" ns3:dyDescent="0.25">
       <c r="A409" s="3">
         <f t="shared" si="7"/>
         <v>408</v>
@@ -48465,7 +48564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:7" ns3:dyDescent="0.25">
       <c r="A410" s="3">
         <f t="shared" si="7"/>
         <v>409</v>
@@ -48486,7 +48585,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:7" ns3:dyDescent="0.25">
       <c r="A411" s="3">
         <f t="shared" si="7"/>
         <v>410</v>
@@ -48507,7 +48606,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:7" ns3:dyDescent="0.25">
       <c r="A412" s="3">
         <f t="shared" si="7"/>
         <v>411</v>
@@ -48528,7 +48627,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:7" ns3:dyDescent="0.25">
       <c r="A413" s="3">
         <f t="shared" si="7"/>
         <v>412</v>
@@ -48549,7 +48648,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:7" ns3:dyDescent="0.25">
       <c r="A414" s="3">
         <f t="shared" si="7"/>
         <v>413</v>
@@ -48570,7 +48669,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:7" ns3:dyDescent="0.25">
       <c r="A415" s="3">
         <f t="shared" si="7"/>
         <v>414</v>
@@ -48591,7 +48690,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:7" ns3:dyDescent="0.25">
       <c r="A416" s="3">
         <f t="shared" si="7"/>
         <v>415</v>
@@ -48612,7 +48711,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:7" ns3:dyDescent="0.25">
       <c r="A417" s="3">
         <f t="shared" si="7"/>
         <v>416</v>
@@ -48633,7 +48732,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:7" ns3:dyDescent="0.25">
       <c r="A418" s="3">
         <f t="shared" si="7"/>
         <v>417</v>
@@ -48654,7 +48753,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:7" ns3:dyDescent="0.25">
       <c r="A419" s="3">
         <f t="shared" si="7"/>
         <v>418</v>
@@ -48675,7 +48774,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:7" ns3:dyDescent="0.25">
       <c r="A420" s="3">
         <f t="shared" si="7"/>
         <v>419</v>
@@ -48696,7 +48795,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:7" ns3:dyDescent="0.25">
       <c r="A421" s="3">
         <f t="shared" si="7"/>
         <v>420</v>
@@ -48717,7 +48816,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:7" ns3:dyDescent="0.25">
       <c r="A422" s="3">
         <f t="shared" si="7"/>
         <v>421</v>
@@ -48738,7 +48837,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:7" ns3:dyDescent="0.25">
       <c r="A423" s="3">
         <f t="shared" si="7"/>
         <v>422</v>
@@ -48759,7 +48858,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:7" ns3:dyDescent="0.25">
       <c r="A424" s="3">
         <f t="shared" si="7"/>
         <v>423</v>
@@ -48780,7 +48879,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:7" ns3:dyDescent="0.25">
       <c r="A425" s="3">
         <f t="shared" si="7"/>
         <v>424</v>
@@ -48801,7 +48900,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:7" ns3:dyDescent="0.25">
       <c r="A426" s="3">
         <f t="shared" si="7"/>
         <v>425</v>
@@ -48822,7 +48921,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:7" ns3:dyDescent="0.25">
       <c r="A427" s="3">
         <f t="shared" si="7"/>
         <v>426</v>
@@ -48843,7 +48942,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:7" ns3:dyDescent="0.25">
       <c r="A428" s="3">
         <f t="shared" si="7"/>
         <v>427</v>
@@ -48864,7 +48963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:7" ns3:dyDescent="0.25">
       <c r="A429" s="3">
         <f t="shared" si="7"/>
         <v>428</v>
@@ -48885,7 +48984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:7" ns3:dyDescent="0.25">
       <c r="A430" s="3">
         <f t="shared" si="7"/>
         <v>429</v>
@@ -48906,7 +49005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:7" ns3:dyDescent="0.25">
       <c r="A431" s="3">
         <f t="shared" si="7"/>
         <v>430</v>
@@ -48927,7 +49026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:7" ns3:dyDescent="0.25">
       <c r="A432" s="3">
         <f t="shared" si="7"/>
         <v>431</v>
@@ -48948,7 +49047,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:7" ns3:dyDescent="0.25">
       <c r="A433" s="3">
         <f t="shared" si="7"/>
         <v>432</v>
@@ -48969,7 +49068,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:7" ns3:dyDescent="0.25">
       <c r="A434" s="3">
         <f t="shared" si="7"/>
         <v>433</v>
@@ -48990,7 +49089,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:7" ns3:dyDescent="0.25">
       <c r="A435" s="3">
         <f t="shared" si="7"/>
         <v>434</v>
@@ -49011,7 +49110,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:7" ns3:dyDescent="0.25">
       <c r="A436" s="3">
         <f t="shared" si="7"/>
         <v>435</v>
@@ -49032,7 +49131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:7" ns3:dyDescent="0.25">
       <c r="A437" s="3">
         <f t="shared" si="7"/>
         <v>436</v>
@@ -49053,7 +49152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:7" ns3:dyDescent="0.25">
       <c r="A438" s="3">
         <f t="shared" si="7"/>
         <v>437</v>
@@ -49074,7 +49173,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:7" ns3:dyDescent="0.25">
       <c r="A439" s="3">
         <f t="shared" si="7"/>
         <v>438</v>
@@ -49095,7 +49194,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:7" ns3:dyDescent="0.25">
       <c r="A440" s="3">
         <f t="shared" si="7"/>
         <v>439</v>
@@ -49116,7 +49215,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:7" ns3:dyDescent="0.25">
       <c r="A441" s="3">
         <f t="shared" si="7"/>
         <v>440</v>
@@ -49137,7 +49236,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:7" ns3:dyDescent="0.25">
       <c r="A442" s="3">
         <f t="shared" si="7"/>
         <v>441</v>
@@ -49158,7 +49257,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:7" ns3:dyDescent="0.25">
       <c r="A443" s="3">
         <f t="shared" si="7"/>
         <v>442</v>
@@ -49179,7 +49278,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:7" ns3:dyDescent="0.25">
       <c r="A444" s="3">
         <f t="shared" si="7"/>
         <v>443</v>
@@ -49200,7 +49299,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:7" ns3:dyDescent="0.25">
       <c r="A445" s="3">
         <f t="shared" si="7"/>
         <v>444</v>
@@ -49221,7 +49320,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:7" ns3:dyDescent="0.25">
       <c r="A446" s="3">
         <f t="shared" si="7"/>
         <v>445</v>
@@ -49242,7 +49341,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:7" ns3:dyDescent="0.25">
       <c r="A447" s="3">
         <f t="shared" si="7"/>
         <v>446</v>
@@ -49263,7 +49362,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:7" ns3:dyDescent="0.25">
       <c r="A448" s="3">
         <f t="shared" si="7"/>
         <v>447</v>
@@ -49284,7 +49383,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:7" ns3:dyDescent="0.25">
       <c r="A449" s="3">
         <f t="shared" si="7"/>
         <v>448</v>
@@ -49305,7 +49404,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:7" ns3:dyDescent="0.25">
       <c r="A450" s="3">
         <f t="shared" si="7"/>
         <v>449</v>
@@ -49326,7 +49425,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:7" ns3:dyDescent="0.25">
       <c r="A451" s="3">
         <f t="shared" si="7"/>
         <v>450</v>
@@ -49347,7 +49446,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:7" ns3:dyDescent="0.25">
       <c r="A452" s="3">
         <f t="shared" ref="A452:A457" si="8">A451+1</f>
         <v>451</v>
@@ -49368,7 +49467,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:7" ns3:dyDescent="0.25">
       <c r="A453" s="3">
         <f t="shared" si="8"/>
         <v>452</v>
@@ -49389,7 +49488,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:7" ns3:dyDescent="0.25">
       <c r="A454" s="3">
         <f t="shared" si="8"/>
         <v>453</v>
@@ -49410,7 +49509,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:7" ns3:dyDescent="0.25">
       <c r="A455" s="3">
         <f t="shared" si="8"/>
         <v>454</v>
@@ -49431,7 +49530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:7" ns3:dyDescent="0.25">
       <c r="A456" s="3">
         <f t="shared" si="8"/>
         <v>455</v>
@@ -49452,7 +49551,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:7" ns3:dyDescent="0.25">
       <c r="A457" s="3">
         <f t="shared" si="8"/>
         <v>456</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.gemini\antigravity\scratch\Idle-RPG\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B229753-E3CA-4DAD-9E01-562B071AFC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2331E3-5B59-4A5E-84F5-BA993F86622C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2375" uniqueCount="1000">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2447" uniqueCount="1015">
   <si>
     <t>編號</t>
   </si>
@@ -3071,6 +3071,51 @@
   <si>
     <t>(a+魔防定值+b×魔防定值*c^轉生次數+智力×d+耐力*e)×(1+魔防%)</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>對火屬性傷害%</t>
+  </si>
+  <si>
+    <t>a=一級基準 b=每級成長係數 c=出現權重 d=最低稀有度 e=百分比。約為暴擊傷害%詞條的 1/10；對對應屬性敵人造成的傷害提高。</t>
+  </si>
+  <si>
+    <t>對冰屬性傷害%</t>
+  </si>
+  <si>
+    <t>對雷屬性傷害%</t>
+  </si>
+  <si>
+    <t>對毒屬性傷害%</t>
+  </si>
+  <si>
+    <t>對光屬性傷害%</t>
+  </si>
+  <si>
+    <t>對暗屬性傷害%</t>
+  </si>
+  <si>
+    <t>尖晶石</t>
+  </si>
+  <si>
+    <t>數值 = a × 等級（1~5階線性；6階起每階×2）</t>
+  </si>
+  <si>
+    <t>對應屬性=b。a=每級加成（線性，Lv5=a×5；6階起每階×2） c=百分比。</t>
+  </si>
+  <si>
+    <t>海藍寶石</t>
+  </si>
+  <si>
+    <t>天河石</t>
+  </si>
+  <si>
+    <t>橄欖石</t>
+  </si>
+  <si>
+    <t>黃水晶</t>
+  </si>
+  <si>
+    <t>黑碧璽</t>
   </si>
 </sst>
 </file>
@@ -10489,7 +10534,7 @@
       </c>
       <c r="H97">
         <f>計算表!H97</f>
-        <v>2.6</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="I97">
         <f>計算表!I97</f>
@@ -13597,11 +13642,11 @@
       </c>
       <c r="H139">
         <f>計算表!H139</f>
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I139">
         <f>計算表!I139</f>
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="J139">
         <f>計算表!J139</f>
@@ -13667,7 +13712,7 @@
       </c>
       <c r="G140">
         <f>計算表!G140</f>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H140">
         <f>計算表!H140</f>
@@ -13675,11 +13720,11 @@
       </c>
       <c r="I140">
         <f>計算表!I140</f>
-        <v>250</v>
+        <v>49</v>
       </c>
       <c r="J140">
         <f>計算表!J140</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="K140">
         <f>計算表!K140</f>
@@ -15973,7 +16018,7 @@
       </c>
       <c r="J171">
         <f>計算表!J171</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K171">
         <f>計算表!K171</f>
@@ -26605,7 +26650,7 @@
       </c>
       <c r="D315" t="str">
         <f>計算表!D315</f>
-        <v>範圍傷害%</v>
+        <v>對火屬性傷害%</v>
       </c>
       <c r="E315" t="str">
         <f>計算表!E315</f>
@@ -26613,23 +26658,23 @@
       </c>
       <c r="F315" t="str">
         <f>計算表!F315</f>
-        <v>a=一級基準 b=每級成長係數 c=出現權重 d=最低稀有度 e=百分比。</v>
+        <v>a=一級基準 b=每級成長係數 c=出現權重 d=最低稀有度 e=百分比。約為暴擊傷害%詞條的 1/10；對對應屬性敵人造成的傷害提高。</v>
       </c>
       <c r="G315">
         <f>計算表!G315</f>
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="H315">
         <f>計算表!H315</f>
-        <v>0.02</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I315">
         <f>計算表!I315</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J315" t="str">
         <f>計算表!J315</f>
-        <v>稀有</v>
+        <v>獨特</v>
       </c>
       <c r="K315" t="str">
         <f>計算表!K315</f>
@@ -26679,7 +26724,7 @@
       </c>
       <c r="D316" t="str">
         <f>計算表!D316</f>
-        <v>格擋率%</v>
+        <v>對冰屬性傷害%</v>
       </c>
       <c r="E316" t="str">
         <f>計算表!E316</f>
@@ -26687,23 +26732,23 @@
       </c>
       <c r="F316" t="str">
         <f>計算表!F316</f>
-        <v>a=一級基準 b=每級成長係數 c=出現權重 d=最低稀有度 e=百分比。</v>
+        <v>a=一級基準 b=每級成長係數 c=出現權重 d=最低稀有度 e=百分比。約為暴擊傷害%詞條的 1/10；對對應屬性敵人造成的傷害提高。</v>
       </c>
       <c r="G316">
         <f>計算表!G316</f>
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="H316">
         <f>計算表!H316</f>
-        <v>1.2E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I316">
         <f>計算表!I316</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J316" t="str">
         <f>計算表!J316</f>
-        <v>-</v>
+        <v>獨特</v>
       </c>
       <c r="K316" t="str">
         <f>計算表!K316</f>
@@ -26753,7 +26798,7 @@
       </c>
       <c r="D317" t="str">
         <f>計算表!D317</f>
-        <v>格擋減傷%</v>
+        <v>對雷屬性傷害%</v>
       </c>
       <c r="E317" t="str">
         <f>計算表!E317</f>
@@ -26761,15 +26806,15 @@
       </c>
       <c r="F317" t="str">
         <f>計算表!F317</f>
-        <v>a=一級基準 b=每級成長係數 c=出現權重 d=最低稀有度 e=百分比。</v>
+        <v>a=一級基準 b=每級成長係數 c=出現權重 d=最低稀有度 e=百分比。約為暴擊傷害%詞條的 1/10；對對應屬性敵人造成的傷害提高。</v>
       </c>
       <c r="G317">
         <f>計算表!G317</f>
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="H317">
         <f>計算表!H317</f>
-        <v>0.02</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I317">
         <f>計算表!I317</f>
@@ -26777,7 +26822,7 @@
       </c>
       <c r="J317" t="str">
         <f>計算表!J317</f>
-        <v>稀有</v>
+        <v>獨特</v>
       </c>
       <c r="K317" t="str">
         <f>計算表!K317</f>
@@ -26827,7 +26872,7 @@
       </c>
       <c r="D318" t="str">
         <f>計算表!D318</f>
-        <v>閃避率%</v>
+        <v>對毒屬性傷害%</v>
       </c>
       <c r="E318" t="str">
         <f>計算表!E318</f>
@@ -26835,23 +26880,23 @@
       </c>
       <c r="F318" t="str">
         <f>計算表!F318</f>
-        <v>a=一級基準 b=每級成長係數 c=出現權重 d=最低稀有度 e=百分比。</v>
+        <v>a=一級基準 b=每級成長係數 c=出現權重 d=最低稀有度 e=百分比。約為暴擊傷害%詞條的 1/10；對對應屬性敵人造成的傷害提高。</v>
       </c>
       <c r="G318">
         <f>計算表!G318</f>
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="H318">
         <f>計算表!H318</f>
-        <v>0.01</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I318">
         <f>計算表!I318</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J318" t="str">
         <f>計算表!J318</f>
-        <v>-</v>
+        <v>獨特</v>
       </c>
       <c r="K318" t="str">
         <f>計算表!K318</f>
@@ -26901,7 +26946,7 @@
       </c>
       <c r="D319" t="str">
         <f>計算表!D319</f>
-        <v>韌性%</v>
+        <v>對光屬性傷害%</v>
       </c>
       <c r="E319" t="str">
         <f>計算表!E319</f>
@@ -26909,15 +26954,15 @@
       </c>
       <c r="F319" t="str">
         <f>計算表!F319</f>
-        <v>a=一級基準 b=每級成長係數 c=出現權重 d=最低稀有度 e=百分比。</v>
+        <v>a=一級基準 b=每級成長係數 c=出現權重 d=最低稀有度 e=百分比。約為暴擊傷害%詞條的 1/10；對對應屬性敵人造成的傷害提高。</v>
       </c>
       <c r="G319">
         <f>計算表!G319</f>
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="H319">
         <f>計算表!H319</f>
-        <v>0.02</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I319">
         <f>計算表!I319</f>
@@ -26925,7 +26970,7 @@
       </c>
       <c r="J319" t="str">
         <f>計算表!J319</f>
-        <v>稀有</v>
+        <v>獨特</v>
       </c>
       <c r="K319" t="str">
         <f>計算表!K319</f>
@@ -26975,7 +27020,7 @@
       </c>
       <c r="D320" t="str">
         <f>計算表!D320</f>
-        <v>護盾效率%</v>
+        <v>對暗屬性傷害%</v>
       </c>
       <c r="E320" t="str">
         <f>計算表!E320</f>
@@ -26983,15 +27028,15 @@
       </c>
       <c r="F320" t="str">
         <f>計算表!F320</f>
-        <v>a=一級基準 b=每級成長係數 c=出現權重 d=最低稀有度 e=百分比。</v>
+        <v>a=一級基準 b=每級成長係數 c=出現權重 d=最低稀有度 e=百分比。約為暴擊傷害%詞條的 1/10；對對應屬性敵人造成的傷害提高。</v>
       </c>
       <c r="G320">
         <f>計算表!G320</f>
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="H320">
         <f>計算表!H320</f>
-        <v>2.5000000000000001E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I320">
         <f>計算表!I320</f>
@@ -27049,7 +27094,7 @@
       </c>
       <c r="D321" t="str">
         <f>計算表!D321</f>
-        <v>物理抗性%</v>
+        <v>範圍傷害%</v>
       </c>
       <c r="E321" t="str">
         <f>計算表!E321</f>
@@ -27061,19 +27106,19 @@
       </c>
       <c r="G321">
         <f>計算表!G321</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H321">
         <f>計算表!H321</f>
-        <v>8.0000000000000002E-3</v>
+        <v>0.02</v>
       </c>
       <c r="I321">
         <f>計算表!I321</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J321" t="str">
         <f>計算表!J321</f>
-        <v>獨特</v>
+        <v>稀有</v>
       </c>
       <c r="K321" t="str">
         <f>計算表!K321</f>
@@ -27123,7 +27168,7 @@
       </c>
       <c r="D322" t="str">
         <f>計算表!D322</f>
-        <v>魔法抗性%</v>
+        <v>格擋率%</v>
       </c>
       <c r="E322" t="str">
         <f>計算表!E322</f>
@@ -27135,19 +27180,19 @@
       </c>
       <c r="G322">
         <f>計算表!G322</f>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H322">
         <f>計算表!H322</f>
-        <v>8.0000000000000002E-3</v>
+        <v>1.2E-2</v>
       </c>
       <c r="I322">
         <f>計算表!I322</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J322" t="str">
         <f>計算表!J322</f>
-        <v>獨特</v>
+        <v>-</v>
       </c>
       <c r="K322" t="str">
         <f>計算表!K322</f>
@@ -27197,7 +27242,7 @@
       </c>
       <c r="D323" t="str">
         <f>計算表!D323</f>
-        <v>火焰抗性%</v>
+        <v>格擋減傷%</v>
       </c>
       <c r="E323" t="str">
         <f>計算表!E323</f>
@@ -27221,7 +27266,7 @@
       </c>
       <c r="J323" t="str">
         <f>計算表!J323</f>
-        <v>精良</v>
+        <v>稀有</v>
       </c>
       <c r="K323" t="str">
         <f>計算表!K323</f>
@@ -27271,7 +27316,7 @@
       </c>
       <c r="D324" t="str">
         <f>計算表!D324</f>
-        <v>冰霜抗性%</v>
+        <v>閃避率%</v>
       </c>
       <c r="E324" t="str">
         <f>計算表!E324</f>
@@ -27283,19 +27328,19 @@
       </c>
       <c r="G324">
         <f>計算表!G324</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H324">
         <f>計算表!H324</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I324">
         <f>計算表!I324</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J324" t="str">
         <f>計算表!J324</f>
-        <v>精良</v>
+        <v>-</v>
       </c>
       <c r="K324" t="str">
         <f>計算表!K324</f>
@@ -27345,7 +27390,7 @@
       </c>
       <c r="D325" t="str">
         <f>計算表!D325</f>
-        <v>雷電抗性%</v>
+        <v>韌性%</v>
       </c>
       <c r="E325" t="str">
         <f>計算表!E325</f>
@@ -27369,7 +27414,7 @@
       </c>
       <c r="J325" t="str">
         <f>計算表!J325</f>
-        <v>精良</v>
+        <v>稀有</v>
       </c>
       <c r="K325" t="str">
         <f>計算表!K325</f>
@@ -27419,7 +27464,7 @@
       </c>
       <c r="D326" t="str">
         <f>計算表!D326</f>
-        <v>劇毒抗性%</v>
+        <v>護盾效率%</v>
       </c>
       <c r="E326" t="str">
         <f>計算表!E326</f>
@@ -27431,11 +27476,11 @@
       </c>
       <c r="G326">
         <f>計算表!G326</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H326">
         <f>計算表!H326</f>
-        <v>0.02</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I326">
         <f>計算表!I326</f>
@@ -27443,7 +27488,7 @@
       </c>
       <c r="J326" t="str">
         <f>計算表!J326</f>
-        <v>精良</v>
+        <v>獨特</v>
       </c>
       <c r="K326" t="str">
         <f>計算表!K326</f>
@@ -27493,7 +27538,7 @@
       </c>
       <c r="D327" t="str">
         <f>計算表!D327</f>
-        <v>聖光抗性%</v>
+        <v>物理抗性%</v>
       </c>
       <c r="E327" t="str">
         <f>計算表!E327</f>
@@ -27505,11 +27550,11 @@
       </c>
       <c r="G327">
         <f>計算表!G327</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H327">
         <f>計算表!H327</f>
-        <v>0.02</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="I327">
         <f>計算表!I327</f>
@@ -27517,7 +27562,7 @@
       </c>
       <c r="J327" t="str">
         <f>計算表!J327</f>
-        <v>精良</v>
+        <v>獨特</v>
       </c>
       <c r="K327" t="str">
         <f>計算表!K327</f>
@@ -27567,7 +27612,7 @@
       </c>
       <c r="D328" t="str">
         <f>計算表!D328</f>
-        <v>暗影抗性%</v>
+        <v>魔法抗性%</v>
       </c>
       <c r="E328" t="str">
         <f>計算表!E328</f>
@@ -27579,11 +27624,11 @@
       </c>
       <c r="G328">
         <f>計算表!G328</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H328">
         <f>計算表!H328</f>
-        <v>0.02</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="I328">
         <f>計算表!I328</f>
@@ -27591,7 +27636,7 @@
       </c>
       <c r="J328" t="str">
         <f>計算表!J328</f>
-        <v>精良</v>
+        <v>獨特</v>
       </c>
       <c r="K328" t="str">
         <f>計算表!K328</f>
@@ -27641,7 +27686,7 @@
       </c>
       <c r="D329" t="str">
         <f>計算表!D329</f>
-        <v>控制時間縮減%</v>
+        <v>火焰抗性%</v>
       </c>
       <c r="E329" t="str">
         <f>計算表!E329</f>
@@ -27665,7 +27710,7 @@
       </c>
       <c r="J329" t="str">
         <f>計算表!J329</f>
-        <v>獨特</v>
+        <v>精良</v>
       </c>
       <c r="K329" t="str">
         <f>計算表!K329</f>
@@ -27715,7 +27760,7 @@
       </c>
       <c r="D330" t="str">
         <f>計算表!D330</f>
-        <v>移動速度%</v>
+        <v>冰霜抗性%</v>
       </c>
       <c r="E330" t="str">
         <f>計算表!E330</f>
@@ -27727,19 +27772,19 @@
       </c>
       <c r="G330">
         <f>計算表!G330</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H330">
         <f>計算表!H330</f>
-        <v>1.2E-2</v>
+        <v>0.02</v>
       </c>
       <c r="I330">
         <f>計算表!I330</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J330" t="str">
         <f>計算表!J330</f>
-        <v>-</v>
+        <v>精良</v>
       </c>
       <c r="K330" t="str">
         <f>計算表!K330</f>
@@ -27789,7 +27834,7 @@
       </c>
       <c r="D331" t="str">
         <f>計算表!D331</f>
-        <v>掉寶率%</v>
+        <v>雷電抗性%</v>
       </c>
       <c r="E331" t="str">
         <f>計算表!E331</f>
@@ -27801,19 +27846,19 @@
       </c>
       <c r="G331">
         <f>計算表!G331</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H331">
         <f>計算表!H331</f>
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="I331">
         <f>計算表!I331</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J331" t="str">
         <f>計算表!J331</f>
-        <v>獨特</v>
+        <v>精良</v>
       </c>
       <c r="K331" t="str">
         <f>計算表!K331</f>
@@ -27863,7 +27908,7 @@
       </c>
       <c r="D332" t="str">
         <f>計算表!D332</f>
-        <v>經驗加成%</v>
+        <v>劇毒抗性%</v>
       </c>
       <c r="E332" t="str">
         <f>計算表!E332</f>
@@ -27883,15 +27928,15 @@
       </c>
       <c r="I332">
         <f>計算表!I332</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J332" t="str">
         <f>計算表!J332</f>
-        <v>獨特</v>
+        <v>精良</v>
       </c>
       <c r="K332" t="str">
         <f>計算表!K332</f>
-        <v>是（限飾品）</v>
+        <v>是</v>
       </c>
       <c r="L332">
         <f>計算表!L332</f>
@@ -27937,7 +27982,7 @@
       </c>
       <c r="D333" t="str">
         <f>計算表!D333</f>
-        <v>金幣加成%</v>
+        <v>聖光抗性%</v>
       </c>
       <c r="E333" t="str">
         <f>計算表!E333</f>
@@ -27949,23 +27994,23 @@
       </c>
       <c r="G333">
         <f>計算表!G333</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H333">
         <f>計算表!H333</f>
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
       <c r="I333">
         <f>計算表!I333</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J333" t="str">
         <f>計算表!J333</f>
-        <v>獨特</v>
+        <v>精良</v>
       </c>
       <c r="K333" t="str">
         <f>計算表!K333</f>
-        <v>是（限飾品）</v>
+        <v>是</v>
       </c>
       <c r="L333">
         <f>計算表!L333</f>
@@ -28011,7 +28056,7 @@
       </c>
       <c r="D334" t="str">
         <f>計算表!D334</f>
-        <v>幸運值</v>
+        <v>暗影抗性%</v>
       </c>
       <c r="E334" t="str">
         <f>計算表!E334</f>
@@ -28023,11 +28068,11 @@
       </c>
       <c r="G334">
         <f>計算表!G334</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H334">
         <f>計算表!H334</f>
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="I334">
         <f>計算表!I334</f>
@@ -28035,11 +28080,11 @@
       </c>
       <c r="J334" t="str">
         <f>計算表!J334</f>
-        <v>獨特</v>
+        <v>精良</v>
       </c>
       <c r="K334" t="str">
         <f>計算表!K334</f>
-        <v>否（限飾品）</v>
+        <v>是</v>
       </c>
       <c r="L334">
         <f>計算表!L334</f>
@@ -28085,7 +28130,7 @@
       </c>
       <c r="D335" t="str">
         <f>計算表!D335</f>
-        <v>負重上限</v>
+        <v>控制時間縮減%</v>
       </c>
       <c r="E335" t="str">
         <f>計算表!E335</f>
@@ -28097,11 +28142,11 @@
       </c>
       <c r="G335">
         <f>計算表!G335</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H335">
         <f>計算表!H335</f>
-        <v>0.3</v>
+        <v>0.02</v>
       </c>
       <c r="I335">
         <f>計算表!I335</f>
@@ -28109,11 +28154,11 @@
       </c>
       <c r="J335" t="str">
         <f>計算表!J335</f>
-        <v>-</v>
+        <v>獨特</v>
       </c>
       <c r="K335" t="str">
         <f>計算表!K335</f>
-        <v>否（限飾品）</v>
+        <v>是</v>
       </c>
       <c r="L335">
         <f>計算表!L335</f>
@@ -28159,7 +28204,7 @@
       </c>
       <c r="D336" t="str">
         <f>計算表!D336</f>
-        <v>強化成功率%</v>
+        <v>移動速度%</v>
       </c>
       <c r="E336" t="str">
         <f>計算表!E336</f>
@@ -28175,15 +28220,15 @@
       </c>
       <c r="H336">
         <f>計算表!H336</f>
-        <v>1.4999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="I336">
         <f>計算表!I336</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J336" t="str">
         <f>計算表!J336</f>
-        <v>獨特</v>
+        <v>-</v>
       </c>
       <c r="K336" t="str">
         <f>計算表!K336</f>
@@ -28233,7 +28278,7 @@
       </c>
       <c r="D337" t="str">
         <f>計算表!D337</f>
-        <v>分解高產率%</v>
+        <v>掉寶率%</v>
       </c>
       <c r="E337" t="str">
         <f>計算表!E337</f>
@@ -28253,7 +28298,7 @@
       </c>
       <c r="I337">
         <f>計算表!I337</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J337" t="str">
         <f>計算表!J337</f>
@@ -28307,7 +28352,7 @@
       </c>
       <c r="D338" t="str">
         <f>計算表!D338</f>
-        <v>合成變異率%</v>
+        <v>經驗加成%</v>
       </c>
       <c r="E338" t="str">
         <f>計算表!E338</f>
@@ -28319,23 +28364,23 @@
       </c>
       <c r="G338">
         <f>計算表!G338</f>
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="H338">
         <f>計算表!H338</f>
-        <v>1.2E-2</v>
+        <v>0.02</v>
       </c>
       <c r="I338">
         <f>計算表!I338</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J338" t="str">
         <f>計算表!J338</f>
-        <v>史詩</v>
+        <v>獨特</v>
       </c>
       <c r="K338" t="str">
         <f>計算表!K338</f>
-        <v>是</v>
+        <v>是（限飾品）</v>
       </c>
       <c r="L338">
         <f>計算表!L338</f>
@@ -28381,7 +28426,7 @@
       </c>
       <c r="D339" t="str">
         <f>計算表!D339</f>
-        <v>狂暴閾值+</v>
+        <v>金幣加成%</v>
       </c>
       <c r="E339" t="str">
         <f>計算表!E339</f>
@@ -28393,23 +28438,23 @@
       </c>
       <c r="G339">
         <f>計算表!G339</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H339">
         <f>計算表!H339</f>
-        <v>0.08</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I339">
         <f>計算表!I339</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J339" t="str">
         <f>計算表!J339</f>
-        <v>史詩</v>
+        <v>獨特</v>
       </c>
       <c r="K339" t="str">
         <f>計算表!K339</f>
-        <v>否</v>
+        <v>是（限飾品）</v>
       </c>
       <c r="L339">
         <f>計算表!L339</f>
@@ -28455,7 +28500,7 @@
       </c>
       <c r="D340" t="str">
         <f>計算表!D340</f>
-        <v>詞條上限率%</v>
+        <v>幸運值</v>
       </c>
       <c r="E340" t="str">
         <f>計算表!E340</f>
@@ -28467,23 +28512,23 @@
       </c>
       <c r="G340">
         <f>計算表!G340</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H340">
         <f>計算表!H340</f>
-        <v>1.4999999999999999E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I340">
         <f>計算表!I340</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J340" t="str">
         <f>計算表!J340</f>
-        <v>史詩</v>
+        <v>獨特</v>
       </c>
       <c r="K340" t="str">
         <f>計算表!K340</f>
-        <v>是（限飾品）</v>
+        <v>否（限飾品）</v>
       </c>
       <c r="L340">
         <f>計算表!L340</f>
@@ -28529,7 +28574,7 @@
       </c>
       <c r="D341" t="str">
         <f>計算表!D341</f>
-        <v>寶石鑲嵌效率%</v>
+        <v>負重上限</v>
       </c>
       <c r="E341" t="str">
         <f>計算表!E341</f>
@@ -28541,23 +28586,23 @@
       </c>
       <c r="G341">
         <f>計算表!G341</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H341">
         <f>計算表!H341</f>
-        <v>2.5000000000000001E-2</v>
+        <v>0.3</v>
       </c>
       <c r="I341">
         <f>計算表!I341</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J341" t="str">
         <f>計算表!J341</f>
-        <v>史詩</v>
+        <v>-</v>
       </c>
       <c r="K341" t="str">
         <f>計算表!K341</f>
-        <v>是（限飾品）</v>
+        <v>否（限飾品）</v>
       </c>
       <c r="L341">
         <f>計算表!L341</f>
@@ -28599,39 +28644,39 @@
       </c>
       <c r="C342" t="str">
         <f>計算表!C342</f>
-        <v>表-特殊被動</v>
+        <v>表-詞條池</v>
       </c>
       <c r="D342" t="str">
         <f>計算表!D342</f>
-        <v>破甲</v>
+        <v>強化成功率%</v>
       </c>
       <c r="E342" t="str">
         <f>計算表!E342</f>
-        <v>數值 = a + b×(稀有度-2)</v>
+        <v>基準值 = (a + a×b×(裝備等級-1)) × 稀有度倍率</v>
       </c>
       <c r="F342" t="str">
         <f>計算表!F342</f>
-        <v>a=稀有級基準 b=每高一階 c=多件疊加後上限。稀有級以上才附帶。</v>
+        <v>a=一級基準 b=每級成長係數 c=出現權重 d=最低稀有度 e=百分比。</v>
       </c>
       <c r="G342">
         <f>計算表!G342</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H342">
         <f>計算表!H342</f>
-        <v>2</v>
-      </c>
-      <c r="I342" t="str">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I342">
         <f>計算表!I342</f>
-        <v>—</v>
-      </c>
-      <c r="J342">
+        <v>3</v>
+      </c>
+      <c r="J342" t="str">
         <f>計算表!J342</f>
-        <v>0</v>
-      </c>
-      <c r="K342">
+        <v>獨特</v>
+      </c>
+      <c r="K342" t="str">
         <f>計算表!K342</f>
-        <v>0</v>
+        <v>是</v>
       </c>
       <c r="L342">
         <f>計算表!L342</f>
@@ -28673,39 +28718,39 @@
       </c>
       <c r="C343" t="str">
         <f>計算表!C343</f>
-        <v>表-特殊被動</v>
+        <v>表-詞條池</v>
       </c>
       <c r="D343" t="str">
         <f>計算表!D343</f>
-        <v>反震</v>
+        <v>分解高產率%</v>
       </c>
       <c r="E343" t="str">
         <f>計算表!E343</f>
-        <v>數值 = a + b×(稀有度-2)</v>
+        <v>基準值 = (a + a×b×(裝備等級-1)) × 稀有度倍率</v>
       </c>
       <c r="F343" t="str">
         <f>計算表!F343</f>
-        <v>a=稀有級基準 b=每高一階 c=多件疊加後上限。稀有級以上才附帶。</v>
+        <v>a=一級基準 b=每級成長係數 c=出現權重 d=最低稀有度 e=百分比。</v>
       </c>
       <c r="G343">
         <f>計算表!G343</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H343">
         <f>計算表!H343</f>
-        <v>1</v>
-      </c>
-      <c r="I343" t="str">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I343">
         <f>計算表!I343</f>
-        <v>—</v>
-      </c>
-      <c r="J343">
+        <v>3</v>
+      </c>
+      <c r="J343" t="str">
         <f>計算表!J343</f>
-        <v>0</v>
-      </c>
-      <c r="K343">
+        <v>獨特</v>
+      </c>
+      <c r="K343" t="str">
         <f>計算表!K343</f>
-        <v>0</v>
+        <v>是</v>
       </c>
       <c r="L343">
         <f>計算表!L343</f>
@@ -28747,39 +28792,39 @@
       </c>
       <c r="C344" t="str">
         <f>計算表!C344</f>
-        <v>表-特殊被動</v>
+        <v>表-詞條池</v>
       </c>
       <c r="D344" t="str">
         <f>計算表!D344</f>
-        <v>連擊</v>
+        <v>合成變異率%</v>
       </c>
       <c r="E344" t="str">
         <f>計算表!E344</f>
-        <v>數值 = a + b×(稀有度-2)</v>
+        <v>基準值 = (a + a×b×(裝備等級-1)) × 稀有度倍率</v>
       </c>
       <c r="F344" t="str">
         <f>計算表!F344</f>
-        <v>a=稀有級基準 b=每高一階 c=多件疊加後上限。稀有級以上才附帶。</v>
+        <v>a=一級基準 b=每級成長係數 c=出現權重 d=最低稀有度 e=百分比。</v>
       </c>
       <c r="G344">
         <f>計算表!G344</f>
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="H344">
         <f>計算表!H344</f>
-        <v>2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="I344">
         <f>計算表!I344</f>
-        <v>45</v>
-      </c>
-      <c r="J344">
+        <v>2</v>
+      </c>
+      <c r="J344" t="str">
         <f>計算表!J344</f>
-        <v>0</v>
-      </c>
-      <c r="K344">
+        <v>史詩</v>
+      </c>
+      <c r="K344" t="str">
         <f>計算表!K344</f>
-        <v>0</v>
+        <v>是</v>
       </c>
       <c r="L344">
         <f>計算表!L344</f>
@@ -28821,39 +28866,39 @@
       </c>
       <c r="C345" t="str">
         <f>計算表!C345</f>
-        <v>表-特殊被動</v>
+        <v>表-詞條池</v>
       </c>
       <c r="D345" t="str">
         <f>計算表!D345</f>
-        <v>暈眩</v>
+        <v>狂暴閾值+</v>
       </c>
       <c r="E345" t="str">
         <f>計算表!E345</f>
-        <v>數值 = a + b×(稀有度-2)</v>
+        <v>基準值 = (a + a×b×(裝備等級-1)) × 稀有度倍率</v>
       </c>
       <c r="F345" t="str">
         <f>計算表!F345</f>
-        <v>a=稀有級基準 b=每高一階 c=多件疊加後上限。稀有級以上才附帶。</v>
+        <v>a=一級基準 b=每級成長係數 c=出現權重 d=最低稀有度 e=百分比。</v>
       </c>
       <c r="G345">
         <f>計算表!G345</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H345">
         <f>計算表!H345</f>
-        <v>1.5</v>
+        <v>0.08</v>
       </c>
       <c r="I345">
         <f>計算表!I345</f>
-        <v>30</v>
-      </c>
-      <c r="J345">
+        <v>2</v>
+      </c>
+      <c r="J345" t="str">
         <f>計算表!J345</f>
-        <v>0</v>
-      </c>
-      <c r="K345">
+        <v>史詩</v>
+      </c>
+      <c r="K345" t="str">
         <f>計算表!K345</f>
-        <v>0</v>
+        <v>否</v>
       </c>
       <c r="L345">
         <f>計算表!L345</f>
@@ -28895,39 +28940,39 @@
       </c>
       <c r="C346" t="str">
         <f>計算表!C346</f>
-        <v>表-特殊被動</v>
+        <v>表-詞條池</v>
       </c>
       <c r="D346" t="str">
         <f>計算表!D346</f>
-        <v>減速</v>
+        <v>詞條上限率%</v>
       </c>
       <c r="E346" t="str">
         <f>計算表!E346</f>
-        <v>數值 = a + b×(稀有度-2)</v>
+        <v>基準值 = (a + a×b×(裝備等級-1)) × 稀有度倍率</v>
       </c>
       <c r="F346" t="str">
         <f>計算表!F346</f>
-        <v>a=稀有級基準 b=每高一階 c=多件疊加後上限。稀有級以上才附帶。</v>
+        <v>a=一級基準 b=每級成長係數 c=出現權重 d=最低稀有度 e=百分比。</v>
       </c>
       <c r="G346">
         <f>計算表!G346</f>
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H346">
         <f>計算表!H346</f>
-        <v>3</v>
-      </c>
-      <c r="I346" t="str">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I346">
         <f>計算表!I346</f>
-        <v>—</v>
-      </c>
-      <c r="J346">
+        <v>2</v>
+      </c>
+      <c r="J346" t="str">
         <f>計算表!J346</f>
-        <v>0</v>
-      </c>
-      <c r="K346">
+        <v>史詩</v>
+      </c>
+      <c r="K346" t="str">
         <f>計算表!K346</f>
-        <v>0</v>
+        <v>是（限飾品）</v>
       </c>
       <c r="L346">
         <f>計算表!L346</f>
@@ -28969,39 +29014,39 @@
       </c>
       <c r="C347" t="str">
         <f>計算表!C347</f>
-        <v>表-特殊被動</v>
+        <v>表-詞條池</v>
       </c>
       <c r="D347" t="str">
         <f>計算表!D347</f>
-        <v>真傷</v>
+        <v>寶石鑲嵌效率%</v>
       </c>
       <c r="E347" t="str">
         <f>計算表!E347</f>
-        <v>數值 = a + b×(稀有度-2)</v>
+        <v>基準值 = (a + a×b×(裝備等級-1)) × 稀有度倍率</v>
       </c>
       <c r="F347" t="str">
         <f>計算表!F347</f>
-        <v>a=稀有級基準 b=每高一階 c=多件疊加後上限。稀有級以上才附帶。</v>
+        <v>a=一級基準 b=每級成長係數 c=出現權重 d=最低稀有度 e=百分比。</v>
       </c>
       <c r="G347">
         <f>計算表!G347</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H347">
         <f>計算表!H347</f>
-        <v>1.5</v>
-      </c>
-      <c r="I347" t="str">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I347">
         <f>計算表!I347</f>
-        <v>—</v>
-      </c>
-      <c r="J347">
+        <v>2</v>
+      </c>
+      <c r="J347" t="str">
         <f>計算表!J347</f>
-        <v>0</v>
-      </c>
-      <c r="K347">
+        <v>史詩</v>
+      </c>
+      <c r="K347" t="str">
         <f>計算表!K347</f>
-        <v>0</v>
+        <v>是（限飾品）</v>
       </c>
       <c r="L347">
         <f>計算表!L347</f>
@@ -29047,7 +29092,7 @@
       </c>
       <c r="D348" t="str">
         <f>計算表!D348</f>
-        <v>吸魂</v>
+        <v>破甲</v>
       </c>
       <c r="E348" t="str">
         <f>計算表!E348</f>
@@ -29059,11 +29104,11 @@
       </c>
       <c r="G348">
         <f>計算表!G348</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H348">
         <f>計算表!H348</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I348" t="str">
         <f>計算表!I348</f>
@@ -29117,31 +29162,31 @@
       </c>
       <c r="C349" t="str">
         <f>計算表!C349</f>
-        <v>表-神鑄特效</v>
+        <v>表-特殊被動</v>
       </c>
       <c r="D349" t="str">
         <f>計算表!D349</f>
-        <v>龍血</v>
+        <v>反震</v>
       </c>
       <c r="E349" t="str">
         <f>計算表!E349</f>
-        <v>數值 = a × rnd(0.8, 1.2)</v>
+        <v>數值 = a + b×(稀有度-2)</v>
       </c>
       <c r="F349" t="str">
         <f>計算表!F349</f>
-        <v>生命上限提高 v%（僅神鑄創世裝備，生成必帶 2 條）。</v>
+        <v>a=稀有級基準 b=每高一階 c=多件疊加後上限。稀有級以上才附帶。</v>
       </c>
       <c r="G349">
         <f>計算表!G349</f>
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H349">
         <f>計算表!H349</f>
-        <v>0</v>
-      </c>
-      <c r="I349">
+        <v>1</v>
+      </c>
+      <c r="I349" t="str">
         <f>計算表!I349</f>
-        <v>0</v>
+        <v>—</v>
       </c>
       <c r="J349">
         <f>計算表!J349</f>
@@ -29191,31 +29236,31 @@
       </c>
       <c r="C350" t="str">
         <f>計算表!C350</f>
-        <v>表-神鑄特效</v>
+        <v>表-特殊被動</v>
       </c>
       <c r="D350" t="str">
         <f>計算表!D350</f>
-        <v>神力</v>
+        <v>連擊</v>
       </c>
       <c r="E350" t="str">
         <f>計算表!E350</f>
-        <v>數值 = a × rnd(0.8, 1.2)</v>
+        <v>數值 = a + b×(稀有度-2)</v>
       </c>
       <c r="F350" t="str">
         <f>計算表!F350</f>
-        <v>物理與魔法攻擊額外提高 v%（額外乘區）（僅神鑄創世裝備，生成必帶 2 條）。</v>
+        <v>a=稀有級基準 b=每高一階 c=多件疊加後上限。稀有級以上才附帶。</v>
       </c>
       <c r="G350">
         <f>計算表!G350</f>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H350">
         <f>計算表!H350</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I350">
         <f>計算表!I350</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J350">
         <f>計算表!J350</f>
@@ -29265,31 +29310,31 @@
       </c>
       <c r="C351" t="str">
         <f>計算表!C351</f>
-        <v>表-神鑄特效</v>
+        <v>表-特殊被動</v>
       </c>
       <c r="D351" t="str">
         <f>計算表!D351</f>
-        <v>神速</v>
+        <v>暈眩</v>
       </c>
       <c r="E351" t="str">
         <f>計算表!E351</f>
-        <v>數值 = a × rnd(0.8, 1.2)</v>
+        <v>數值 = a + b×(稀有度-2)</v>
       </c>
       <c r="F351" t="str">
         <f>計算表!F351</f>
-        <v>攻擊速度提高 v%（僅神鑄創世裝備，生成必帶 2 條）。</v>
+        <v>a=稀有級基準 b=每高一階 c=多件疊加後上限。稀有級以上才附帶。</v>
       </c>
       <c r="G351">
         <f>計算表!G351</f>
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H351">
         <f>計算表!H351</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I351">
         <f>計算表!I351</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J351">
         <f>計算表!J351</f>
@@ -29339,31 +29384,31 @@
       </c>
       <c r="C352" t="str">
         <f>計算表!C352</f>
-        <v>表-神鑄特效</v>
+        <v>表-特殊被動</v>
       </c>
       <c r="D352" t="str">
         <f>計算表!D352</f>
-        <v>屠神</v>
+        <v>減速</v>
       </c>
       <c r="E352" t="str">
         <f>計算表!E352</f>
-        <v>數值 = a × rnd(0.8, 1.2)</v>
+        <v>數值 = a + b×(稀有度-2)</v>
       </c>
       <c r="F352" t="str">
         <f>計算表!F352</f>
-        <v>對菁英與 BOSS 傷害提高 v%（僅神鑄創世裝備，生成必帶 2 條）。</v>
+        <v>a=稀有級基準 b=每高一階 c=多件疊加後上限。稀有級以上才附帶。</v>
       </c>
       <c r="G352">
         <f>計算表!G352</f>
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H352">
         <f>計算表!H352</f>
-        <v>0</v>
-      </c>
-      <c r="I352">
+        <v>3</v>
+      </c>
+      <c r="I352" t="str">
         <f>計算表!I352</f>
-        <v>0</v>
+        <v>—</v>
       </c>
       <c r="J352">
         <f>計算表!J352</f>
@@ -29413,31 +29458,31 @@
       </c>
       <c r="C353" t="str">
         <f>計算表!C353</f>
-        <v>表-神鑄特效</v>
+        <v>表-特殊被動</v>
       </c>
       <c r="D353" t="str">
         <f>計算表!D353</f>
-        <v>貪婪</v>
+        <v>真傷</v>
       </c>
       <c r="E353" t="str">
         <f>計算表!E353</f>
-        <v>數值 = a × rnd(0.8, 1.2)</v>
+        <v>數值 = a + b×(稀有度-2)</v>
       </c>
       <c r="F353" t="str">
         <f>計算表!F353</f>
-        <v>金幣加成與掉寶率提高 v%（僅神鑄創世裝備，生成必帶 2 條）。</v>
+        <v>a=稀有級基準 b=每高一階 c=多件疊加後上限。稀有級以上才附帶。</v>
       </c>
       <c r="G353">
         <f>計算表!G353</f>
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="H353">
         <f>計算表!H353</f>
-        <v>0</v>
-      </c>
-      <c r="I353">
+        <v>1.5</v>
+      </c>
+      <c r="I353" t="str">
         <f>計算表!I353</f>
-        <v>0</v>
+        <v>—</v>
       </c>
       <c r="J353">
         <f>計算表!J353</f>
@@ -29487,31 +29532,31 @@
       </c>
       <c r="C354" t="str">
         <f>計算表!C354</f>
-        <v>表-神鑄特效</v>
+        <v>表-特殊被動</v>
       </c>
       <c r="D354" t="str">
         <f>計算表!D354</f>
-        <v>神壁</v>
+        <v>吸魂</v>
       </c>
       <c r="E354" t="str">
         <f>計算表!E354</f>
-        <v>數值 = a × rnd(0.8, 1.2)</v>
+        <v>數值 = a + b×(稀有度-2)</v>
       </c>
       <c r="F354" t="str">
         <f>計算表!F354</f>
-        <v>物理與魔法防禦提高 v%（僅神鑄創世裝備，生成必帶 2 條）。</v>
+        <v>a=稀有級基準 b=每高一階 c=多件疊加後上限。稀有級以上才附帶。</v>
       </c>
       <c r="G354">
         <f>計算表!G354</f>
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H354">
         <f>計算表!H354</f>
-        <v>0</v>
-      </c>
-      <c r="I354">
+        <v>1.5</v>
+      </c>
+      <c r="I354" t="str">
         <f>計算表!I354</f>
-        <v>0</v>
+        <v>—</v>
       </c>
       <c r="J354">
         <f>計算表!J354</f>
@@ -29565,7 +29610,7 @@
       </c>
       <c r="D355" t="str">
         <f>計算表!D355</f>
-        <v>天罰</v>
+        <v>龍血</v>
       </c>
       <c r="E355" t="str">
         <f>計算表!E355</f>
@@ -29573,11 +29618,11 @@
       </c>
       <c r="F355" t="str">
         <f>計算表!F355</f>
-        <v>攻擊時 v% 機率降下神雷（250% 物攻真實傷害）（僅神鑄創世裝備，生成必帶 2 條）。</v>
+        <v>生命上限提高 v%（僅神鑄創世裝備，生成必帶 2 條）。</v>
       </c>
       <c r="G355">
         <f>計算表!G355</f>
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H355">
         <f>計算表!H355</f>
@@ -29639,7 +29684,7 @@
       </c>
       <c r="D356" t="str">
         <f>計算表!D356</f>
-        <v>破滅</v>
+        <v>神力</v>
       </c>
       <c r="E356" t="str">
         <f>計算表!E356</f>
@@ -29647,11 +29692,11 @@
       </c>
       <c r="F356" t="str">
         <f>計算表!F356</f>
-        <v>暴擊時 v% 機率傷害翻倍（僅神鑄創世裝備，生成必帶 2 條）。</v>
+        <v>物理與魔法攻擊額外提高 v%（額外乘區）（僅神鑄創世裝備，生成必帶 2 條）。</v>
       </c>
       <c r="G356">
         <f>計算表!G356</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H356">
         <f>計算表!H356</f>
@@ -29713,7 +29758,7 @@
       </c>
       <c r="D357" t="str">
         <f>計算表!D357</f>
-        <v>聖佑</v>
+        <v>神速</v>
       </c>
       <c r="E357" t="str">
         <f>計算表!E357</f>
@@ -29721,11 +29766,11 @@
       </c>
       <c r="F357" t="str">
         <f>計算表!F357</f>
-        <v>受到的所有傷害降低 v%（上限 50%）（僅神鑄創世裝備，生成必帶 2 條）。</v>
+        <v>攻擊速度提高 v%（僅神鑄創世裝備，生成必帶 2 條）。</v>
       </c>
       <c r="G357">
         <f>計算表!G357</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H357">
         <f>計算表!H357</f>
@@ -29787,7 +29832,7 @@
       </c>
       <c r="D358" t="str">
         <f>計算表!D358</f>
-        <v>不朽</v>
+        <v>屠神</v>
       </c>
       <c r="E358" t="str">
         <f>計算表!E358</f>
@@ -29795,7 +29840,7 @@
       </c>
       <c r="F358" t="str">
         <f>計算表!F358</f>
-        <v>致命時 v% 機率保 1 血並回復 30%（60 秒限一次）（僅神鑄創世裝備，生成必帶 2 條）。</v>
+        <v>對菁英與 BOSS 傷害提高 v%（僅神鑄創世裝備，生成必帶 2 條）。</v>
       </c>
       <c r="G358">
         <f>計算表!G358</f>
@@ -29861,7 +29906,7 @@
       </c>
       <c r="D359" t="str">
         <f>計算表!D359</f>
-        <v>萬象汲取</v>
+        <v>貪婪</v>
       </c>
       <c r="E359" t="str">
         <f>計算表!E359</f>
@@ -29869,11 +29914,11 @@
       </c>
       <c r="F359" t="str">
         <f>計算表!F359</f>
-        <v>攻擊時額外回復造成傷害 v% 的生命與法力（僅神鑄創世裝備，生成必帶 2 條）。</v>
+        <v>金幣加成與掉寶率提高 v%（僅神鑄創世裝備，生成必帶 2 條）。</v>
       </c>
       <c r="G359">
         <f>計算表!G359</f>
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H359">
         <f>計算表!H359</f>
@@ -29935,7 +29980,7 @@
       </c>
       <c r="D360" t="str">
         <f>計算表!D360</f>
-        <v>神怒</v>
+        <v>神壁</v>
       </c>
       <c r="E360" t="str">
         <f>計算表!E360</f>
@@ -29943,11 +29988,11 @@
       </c>
       <c r="F360" t="str">
         <f>計算表!F360</f>
-        <v>生命低於 30% 時傷害提高 v%（僅神鑄創世裝備，生成必帶 2 條）。</v>
+        <v>物理與魔法防禦提高 v%（僅神鑄創世裝備，生成必帶 2 條）。</v>
       </c>
       <c r="G360">
         <f>計算表!G360</f>
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H360">
         <f>計算表!H360</f>
@@ -30005,31 +30050,31 @@
       </c>
       <c r="C361" t="str">
         <f>計算表!C361</f>
-        <v>表-寶石種類</v>
+        <v>表-神鑄特效</v>
       </c>
       <c r="D361" t="str">
         <f>計算表!D361</f>
-        <v>紅寶石</v>
+        <v>天罰</v>
       </c>
       <c r="E361" t="str">
         <f>計算表!E361</f>
-        <v>數值 = a × 等級 × (1+0.2×(等級-1))</v>
+        <v>數值 = a × rnd(0.8, 1.2)</v>
       </c>
       <c r="F361" t="str">
         <f>計算表!F361</f>
-        <v>對應屬性=b。a=一級基準 c=百分比。</v>
+        <v>攻擊時 v% 機率降下神雷（250% 物攻真實傷害）（僅神鑄創世裝備，生成必帶 2 條）。</v>
       </c>
       <c r="G361">
         <f>計算表!G361</f>
-        <v>6</v>
-      </c>
-      <c r="H361" t="str">
+        <v>12</v>
+      </c>
+      <c r="H361">
         <f>計算表!H361</f>
-        <v>物理攻擊</v>
-      </c>
-      <c r="I361" t="str">
+        <v>0</v>
+      </c>
+      <c r="I361">
         <f>計算表!I361</f>
-        <v>否</v>
+        <v>0</v>
       </c>
       <c r="J361">
         <f>計算表!J361</f>
@@ -30079,31 +30124,31 @@
       </c>
       <c r="C362" t="str">
         <f>計算表!C362</f>
-        <v>表-寶石種類</v>
+        <v>表-神鑄特效</v>
       </c>
       <c r="D362" t="str">
         <f>計算表!D362</f>
-        <v>藍寶石</v>
+        <v>破滅</v>
       </c>
       <c r="E362" t="str">
         <f>計算表!E362</f>
-        <v>數值 = a × 等級 × (1+0.2×(等級-1))</v>
+        <v>數值 = a × rnd(0.8, 1.2)</v>
       </c>
       <c r="F362" t="str">
         <f>計算表!F362</f>
-        <v>對應屬性=b。a=一級基準 c=百分比。</v>
+        <v>暴擊時 v% 機率傷害翻倍（僅神鑄創世裝備，生成必帶 2 條）。</v>
       </c>
       <c r="G362">
         <f>計算表!G362</f>
-        <v>6</v>
-      </c>
-      <c r="H362" t="str">
+        <v>15</v>
+      </c>
+      <c r="H362">
         <f>計算表!H362</f>
-        <v>魔法攻擊</v>
-      </c>
-      <c r="I362" t="str">
+        <v>0</v>
+      </c>
+      <c r="I362">
         <f>計算表!I362</f>
-        <v>否</v>
+        <v>0</v>
       </c>
       <c r="J362">
         <f>計算表!J362</f>
@@ -30153,31 +30198,31 @@
       </c>
       <c r="C363" t="str">
         <f>計算表!C363</f>
-        <v>表-寶石種類</v>
+        <v>表-神鑄特效</v>
       </c>
       <c r="D363" t="str">
         <f>計算表!D363</f>
-        <v>黃玉</v>
+        <v>聖佑</v>
       </c>
       <c r="E363" t="str">
         <f>計算表!E363</f>
-        <v>數值 = a × 等級 × (1+0.2×(等級-1))</v>
+        <v>數值 = a × rnd(0.8, 1.2)</v>
       </c>
       <c r="F363" t="str">
         <f>計算表!F363</f>
-        <v>對應屬性=b。a=一級基準 c=百分比。</v>
+        <v>受到的所有傷害降低 v%（上限 50%）（僅神鑄創世裝備，生成必帶 2 條）。</v>
       </c>
       <c r="G363">
         <f>計算表!G363</f>
-        <v>40</v>
-      </c>
-      <c r="H363" t="str">
+        <v>8</v>
+      </c>
+      <c r="H363">
         <f>計算表!H363</f>
-        <v>生命值</v>
-      </c>
-      <c r="I363" t="str">
+        <v>0</v>
+      </c>
+      <c r="I363">
         <f>計算表!I363</f>
-        <v>否</v>
+        <v>0</v>
       </c>
       <c r="J363">
         <f>計算表!J363</f>
@@ -30227,31 +30272,31 @@
       </c>
       <c r="C364" t="str">
         <f>計算表!C364</f>
-        <v>表-寶石種類</v>
+        <v>表-神鑄特效</v>
       </c>
       <c r="D364" t="str">
         <f>計算表!D364</f>
-        <v>綠寶石</v>
+        <v>不朽</v>
       </c>
       <c r="E364" t="str">
         <f>計算表!E364</f>
-        <v>數值 = a × 等級 × (1+0.2×(等級-1))</v>
+        <v>數值 = a × rnd(0.8, 1.2)</v>
       </c>
       <c r="F364" t="str">
         <f>計算表!F364</f>
-        <v>對應屬性=b。a=一級基準 c=百分比。</v>
+        <v>致命時 v% 機率保 1 血並回復 30%（60 秒限一次）（僅神鑄創世裝備，生成必帶 2 條）。</v>
       </c>
       <c r="G364">
         <f>計算表!G364</f>
-        <v>3</v>
-      </c>
-      <c r="H364" t="str">
+        <v>30</v>
+      </c>
+      <c r="H364">
         <f>計算表!H364</f>
-        <v>生命恢復/秒</v>
-      </c>
-      <c r="I364" t="str">
+        <v>0</v>
+      </c>
+      <c r="I364">
         <f>計算表!I364</f>
-        <v>否</v>
+        <v>0</v>
       </c>
       <c r="J364">
         <f>計算表!J364</f>
@@ -30301,31 +30346,31 @@
       </c>
       <c r="C365" t="str">
         <f>計算表!C365</f>
-        <v>表-寶石種類</v>
+        <v>表-神鑄特效</v>
       </c>
       <c r="D365" t="str">
         <f>計算表!D365</f>
-        <v>鑽石</v>
+        <v>萬象汲取</v>
       </c>
       <c r="E365" t="str">
         <f>計算表!E365</f>
-        <v>數值 = a × 等級 × (1+0.2×(等級-1))</v>
+        <v>數值 = a × rnd(0.8, 1.2)</v>
       </c>
       <c r="F365" t="str">
         <f>計算表!F365</f>
-        <v>對應屬性=b。a=一級基準 c=百分比。</v>
+        <v>攻擊時額外回復造成傷害 v% 的生命與法力（僅神鑄創世裝備，生成必帶 2 條）。</v>
       </c>
       <c r="G365">
         <f>計算表!G365</f>
         <v>5</v>
       </c>
-      <c r="H365" t="str">
+      <c r="H365">
         <f>計算表!H365</f>
-        <v>物理防禦</v>
-      </c>
-      <c r="I365" t="str">
+        <v>0</v>
+      </c>
+      <c r="I365">
         <f>計算表!I365</f>
-        <v>否</v>
+        <v>0</v>
       </c>
       <c r="J365">
         <f>計算表!J365</f>
@@ -30375,31 +30420,31 @@
       </c>
       <c r="C366" t="str">
         <f>計算表!C366</f>
-        <v>表-寶石種類</v>
+        <v>表-神鑄特效</v>
       </c>
       <c r="D366" t="str">
         <f>計算表!D366</f>
-        <v>青金石</v>
+        <v>神怒</v>
       </c>
       <c r="E366" t="str">
         <f>計算表!E366</f>
-        <v>數值 = a × 等級 × (1+0.2×(等級-1))</v>
+        <v>數值 = a × rnd(0.8, 1.2)</v>
       </c>
       <c r="F366" t="str">
         <f>計算表!F366</f>
-        <v>對應屬性=b。a=一級基準 c=百分比。</v>
+        <v>生命低於 30% 時傷害提高 v%（僅神鑄創世裝備，生成必帶 2 條）。</v>
       </c>
       <c r="G366">
         <f>計算表!G366</f>
-        <v>5</v>
-      </c>
-      <c r="H366" t="str">
+        <v>35</v>
+      </c>
+      <c r="H366">
         <f>計算表!H366</f>
-        <v>魔法防禦</v>
-      </c>
-      <c r="I366" t="str">
+        <v>0</v>
+      </c>
+      <c r="I366">
         <f>計算表!I366</f>
-        <v>否</v>
+        <v>0</v>
       </c>
       <c r="J366">
         <f>計算表!J366</f>
@@ -30453,7 +30498,7 @@
       </c>
       <c r="D367" t="str">
         <f>計算表!D367</f>
-        <v>紫水晶</v>
+        <v>紅寶石</v>
       </c>
       <c r="E367" t="str">
         <f>計算表!E367</f>
@@ -30465,15 +30510,15 @@
       </c>
       <c r="G367">
         <f>計算表!G367</f>
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="H367" t="str">
         <f>計算表!H367</f>
-        <v>暴擊率%</v>
+        <v>物理攻擊</v>
       </c>
       <c r="I367" t="str">
         <f>計算表!I367</f>
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J367">
         <f>計算表!J367</f>
@@ -30527,7 +30572,7 @@
       </c>
       <c r="D368" t="str">
         <f>計算表!D368</f>
-        <v>石榴石</v>
+        <v>藍寶石</v>
       </c>
       <c r="E368" t="str">
         <f>計算表!E368</f>
@@ -30539,15 +30584,15 @@
       </c>
       <c r="G368">
         <f>計算表!G368</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H368" t="str">
         <f>計算表!H368</f>
-        <v>暴擊傷害%</v>
+        <v>魔法攻擊</v>
       </c>
       <c r="I368" t="str">
         <f>計算表!I368</f>
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J368">
         <f>計算表!J368</f>
@@ -30601,7 +30646,7 @@
       </c>
       <c r="D369" t="str">
         <f>計算表!D369</f>
-        <v>蛋白石</v>
+        <v>黃玉</v>
       </c>
       <c r="E369" t="str">
         <f>計算表!E369</f>
@@ -30613,15 +30658,15 @@
       </c>
       <c r="G369">
         <f>計算表!G369</f>
-        <v>1.5</v>
+        <v>40</v>
       </c>
       <c r="H369" t="str">
         <f>計算表!H369</f>
-        <v>攻擊速度%</v>
+        <v>生命值</v>
       </c>
       <c r="I369" t="str">
         <f>計算表!I369</f>
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J369">
         <f>計算表!J369</f>
@@ -30675,7 +30720,7 @@
       </c>
       <c r="D370" t="str">
         <f>計算表!D370</f>
-        <v>黑曜石</v>
+        <v>綠寶石</v>
       </c>
       <c r="E370" t="str">
         <f>計算表!E370</f>
@@ -30687,15 +30732,15 @@
       </c>
       <c r="G370">
         <f>計算表!G370</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H370" t="str">
         <f>計算表!H370</f>
-        <v>吸血%</v>
+        <v>生命恢復/秒</v>
       </c>
       <c r="I370" t="str">
         <f>計算表!I370</f>
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J370">
         <f>計算表!J370</f>
@@ -30749,7 +30794,7 @@
       </c>
       <c r="D371" t="str">
         <f>計算表!D371</f>
-        <v>月光石</v>
+        <v>鑽石</v>
       </c>
       <c r="E371" t="str">
         <f>計算表!E371</f>
@@ -30761,15 +30806,15 @@
       </c>
       <c r="G371">
         <f>計算表!G371</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H371" t="str">
         <f>計算表!H371</f>
-        <v>閃避率%</v>
+        <v>物理防禦</v>
       </c>
       <c r="I371" t="str">
         <f>計算表!I371</f>
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J371">
         <f>計算表!J371</f>
@@ -30823,7 +30868,7 @@
       </c>
       <c r="D372" t="str">
         <f>計算表!D372</f>
-        <v>太陽石</v>
+        <v>青金石</v>
       </c>
       <c r="E372" t="str">
         <f>計算表!E372</f>
@@ -30835,11 +30880,11 @@
       </c>
       <c r="G372">
         <f>計算表!G372</f>
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="H372" t="str">
         <f>計算表!H372</f>
-        <v>幸運值</v>
+        <v>魔法防禦</v>
       </c>
       <c r="I372" t="str">
         <f>計算表!I372</f>
@@ -30897,7 +30942,7 @@
       </c>
       <c r="D373" t="str">
         <f>計算表!D373</f>
-        <v>翡翠</v>
+        <v>紫水晶</v>
       </c>
       <c r="E373" t="str">
         <f>計算表!E373</f>
@@ -30913,7 +30958,7 @@
       </c>
       <c r="H373" t="str">
         <f>計算表!H373</f>
-        <v>韌性%</v>
+        <v>暴擊率%</v>
       </c>
       <c r="I373" t="str">
         <f>計算表!I373</f>
@@ -30971,7 +31016,7 @@
       </c>
       <c r="D374" t="str">
         <f>計算表!D374</f>
-        <v>綠松石</v>
+        <v>石榴石</v>
       </c>
       <c r="E374" t="str">
         <f>計算表!E374</f>
@@ -30983,11 +31028,11 @@
       </c>
       <c r="G374">
         <f>計算表!G374</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H374" t="str">
         <f>計算表!H374</f>
-        <v>格擋率%</v>
+        <v>暴擊傷害%</v>
       </c>
       <c r="I374" t="str">
         <f>計算表!I374</f>
@@ -31045,7 +31090,7 @@
       </c>
       <c r="D375" t="str">
         <f>計算表!D375</f>
-        <v>瑪瑙</v>
+        <v>蛋白石</v>
       </c>
       <c r="E375" t="str">
         <f>計算表!E375</f>
@@ -31061,7 +31106,7 @@
       </c>
       <c r="H375" t="str">
         <f>計算表!H375</f>
-        <v>格擋減傷%</v>
+        <v>攻擊速度%</v>
       </c>
       <c r="I375" t="str">
         <f>計算表!I375</f>
@@ -31119,7 +31164,7 @@
       </c>
       <c r="D376" t="str">
         <f>計算表!D376</f>
-        <v>珍珠</v>
+        <v>黑曜石</v>
       </c>
       <c r="E376" t="str">
         <f>計算表!E376</f>
@@ -31131,11 +31176,11 @@
       </c>
       <c r="G376">
         <f>計算表!G376</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H376" t="str">
         <f>計算表!H376</f>
-        <v>護盾效率%</v>
+        <v>吸血%</v>
       </c>
       <c r="I376" t="str">
         <f>計算表!I376</f>
@@ -31193,7 +31238,7 @@
       </c>
       <c r="D377" t="str">
         <f>計算表!D377</f>
-        <v>孔雀石</v>
+        <v>月光石</v>
       </c>
       <c r="E377" t="str">
         <f>計算表!E377</f>
@@ -31205,11 +31250,11 @@
       </c>
       <c r="G377">
         <f>計算表!G377</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H377" t="str">
         <f>計算表!H377</f>
-        <v>物理抗性%</v>
+        <v>閃避率%</v>
       </c>
       <c r="I377" t="str">
         <f>計算表!I377</f>
@@ -31267,7 +31312,7 @@
       </c>
       <c r="D378" t="str">
         <f>計算表!D378</f>
-        <v>螢石</v>
+        <v>太陽石</v>
       </c>
       <c r="E378" t="str">
         <f>計算表!E378</f>
@@ -31279,15 +31324,15 @@
       </c>
       <c r="G378">
         <f>計算表!G378</f>
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="H378" t="str">
         <f>計算表!H378</f>
-        <v>魔法抗性%</v>
+        <v>幸運值</v>
       </c>
       <c r="I378" t="str">
         <f>計算表!I378</f>
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="J378">
         <f>計算表!J378</f>
@@ -31337,31 +31382,31 @@
       </c>
       <c r="C379" t="str">
         <f>計算表!C379</f>
-        <v>表-自動機組零件</v>
+        <v>表-寶石種類</v>
       </c>
       <c r="D379" t="str">
         <f>計算表!D379</f>
-        <v>加速齒輪</v>
+        <v>翡翠</v>
       </c>
       <c r="E379" t="str">
         <f>計算表!E379</f>
-        <v>效果值 = a × 階級(T1~T7)</v>
+        <v>數值 = a × 等級 × (1+0.2×(等級-1))</v>
       </c>
       <c r="F379" t="str">
         <f>計算表!F379</f>
-        <v>節點=b。分解速度 +v%/階（另固定+50 個百分點）（掉寶類零件效果實際×0.5）。</v>
+        <v>對應屬性=b。a=一級基準 c=百分比。</v>
       </c>
       <c r="G379">
         <f>計算表!G379</f>
-        <v>25</v>
+        <v>1.5</v>
       </c>
       <c r="H379" t="str">
         <f>計算表!H379</f>
-        <v>salvage</v>
-      </c>
-      <c r="I379">
+        <v>韌性%</v>
+      </c>
+      <c r="I379" t="str">
         <f>計算表!I379</f>
-        <v>0</v>
+        <v>是</v>
       </c>
       <c r="J379">
         <f>計算表!J379</f>
@@ -31411,31 +31456,31 @@
       </c>
       <c r="C380" t="str">
         <f>計算表!C380</f>
-        <v>表-自動機組零件</v>
+        <v>表-寶石種類</v>
       </c>
       <c r="D380" t="str">
         <f>計算表!D380</f>
-        <v>碎片熔煉爐</v>
+        <v>綠松石</v>
       </c>
       <c r="E380" t="str">
         <f>計算表!E380</f>
-        <v>效果值 = a × 階級(T1~T7)</v>
+        <v>數值 = a × 等級 × (1+0.2×(等級-1))</v>
       </c>
       <c r="F380" t="str">
         <f>計算表!F380</f>
-        <v>節點=b。分解碎片產量 +v%/階（掉寶類零件效果實際×0.5）。</v>
+        <v>對應屬性=b。a=一級基準 c=百分比。</v>
       </c>
       <c r="G380">
         <f>計算表!G380</f>
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H380" t="str">
         <f>計算表!H380</f>
-        <v>salvage</v>
-      </c>
-      <c r="I380">
+        <v>格擋率%</v>
+      </c>
+      <c r="I380" t="str">
         <f>計算表!I380</f>
-        <v>0</v>
+        <v>是</v>
       </c>
       <c r="J380">
         <f>計算表!J380</f>
@@ -31485,31 +31530,31 @@
       </c>
       <c r="C381" t="str">
         <f>計算表!C381</f>
-        <v>表-自動機組零件</v>
+        <v>表-寶石種類</v>
       </c>
       <c r="D381" t="str">
         <f>計算表!D381</f>
-        <v>淘金濾網</v>
+        <v>瑪瑙</v>
       </c>
       <c r="E381" t="str">
         <f>計算表!E381</f>
-        <v>效果值 = a × 階級(T1~T7)</v>
+        <v>數值 = a × 等級 × (1+0.2×(等級-1))</v>
       </c>
       <c r="F381" t="str">
         <f>計算表!F381</f>
-        <v>節點=b。分解金幣產量 +v%/階（掉寶類零件效果實際×0.5）。</v>
+        <v>對應屬性=b。a=一級基準 c=百分比。</v>
       </c>
       <c r="G381">
         <f>計算表!G381</f>
-        <v>25</v>
+        <v>1.5</v>
       </c>
       <c r="H381" t="str">
         <f>計算表!H381</f>
-        <v>salvage</v>
-      </c>
-      <c r="I381">
+        <v>格擋減傷%</v>
+      </c>
+      <c r="I381" t="str">
         <f>計算表!I381</f>
-        <v>0</v>
+        <v>是</v>
       </c>
       <c r="J381">
         <f>計算表!J381</f>
@@ -31559,31 +31604,31 @@
       </c>
       <c r="C382" t="str">
         <f>計算表!C382</f>
-        <v>表-自動機組零件</v>
+        <v>表-寶石種類</v>
       </c>
       <c r="D382" t="str">
         <f>計算表!D382</f>
-        <v>精粹透鏡</v>
+        <v>珍珠</v>
       </c>
       <c r="E382" t="str">
         <f>計算表!E382</f>
-        <v>效果值 = a × 階級(T1~T7)</v>
+        <v>數值 = a × 等級 × (1+0.2×(等級-1))</v>
       </c>
       <c r="F382" t="str">
         <f>計算表!F382</f>
-        <v>節點=b。附魔精華拆解產出率 +v%/階（掉寶類零件效果實際×0.5）。</v>
+        <v>對應屬性=b。a=一級基準 c=百分比。</v>
       </c>
       <c r="G382">
         <f>計算表!G382</f>
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H382" t="str">
         <f>計算表!H382</f>
-        <v>salvage</v>
-      </c>
-      <c r="I382">
+        <v>護盾效率%</v>
+      </c>
+      <c r="I382" t="str">
         <f>計算表!I382</f>
-        <v>0</v>
+        <v>是</v>
       </c>
       <c r="J382">
         <f>計算表!J382</f>
@@ -31633,31 +31678,31 @@
       </c>
       <c r="C383" t="str">
         <f>計算表!C383</f>
-        <v>表-自動機組零件</v>
+        <v>表-寶石種類</v>
       </c>
       <c r="D383" t="str">
         <f>計算表!D383</f>
-        <v>拓本回收臂</v>
+        <v>孔雀石</v>
       </c>
       <c r="E383" t="str">
         <f>計算表!E383</f>
-        <v>效果值 = a × 階級(T1~T7)</v>
+        <v>數值 = a × 等級 × (1+0.2×(等級-1))</v>
       </c>
       <c r="F383" t="str">
         <f>計算表!F383</f>
-        <v>節點=b。分解 v%/階 機率回收 1 本附魔書（掉寶類零件效果實際×0.5）。</v>
+        <v>對應屬性=b。a=一級基準 c=百分比。</v>
       </c>
       <c r="G383">
         <f>計算表!G383</f>
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="H383" t="str">
         <f>計算表!H383</f>
-        <v>salvage</v>
-      </c>
-      <c r="I383">
+        <v>物理抗性%</v>
+      </c>
+      <c r="I383" t="str">
         <f>計算表!I383</f>
-        <v>0</v>
+        <v>是</v>
       </c>
       <c r="J383">
         <f>計算表!J383</f>
@@ -31707,31 +31752,31 @@
       </c>
       <c r="C384" t="str">
         <f>計算表!C384</f>
-        <v>表-自動機組零件</v>
+        <v>表-寶石種類</v>
       </c>
       <c r="D384" t="str">
         <f>計算表!D384</f>
-        <v>複製處理艙</v>
+        <v>螢石</v>
       </c>
       <c r="E384" t="str">
         <f>計算表!E384</f>
-        <v>效果值 = a × 階級(T1~T7)</v>
+        <v>數值 = a × 等級 × (1+0.2×(等級-1))</v>
       </c>
       <c r="F384" t="str">
         <f>計算表!F384</f>
-        <v>節點=b。分解 v%/階 機率碎片+金幣翻倍（掉寶類零件效果實際×0.5）。</v>
+        <v>對應屬性=b。a=一級基準 c=百分比。</v>
       </c>
       <c r="G384">
         <f>計算表!G384</f>
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="H384" t="str">
         <f>計算表!H384</f>
-        <v>salvage</v>
-      </c>
-      <c r="I384">
+        <v>魔法抗性%</v>
+      </c>
+      <c r="I384" t="str">
         <f>計算表!I384</f>
-        <v>0</v>
+        <v>是</v>
       </c>
       <c r="J384">
         <f>計算表!J384</f>
@@ -31781,31 +31826,31 @@
       </c>
       <c r="C385" t="str">
         <f>計算表!C385</f>
-        <v>表-自動機組零件</v>
+        <v>表-寶石種類</v>
       </c>
       <c r="D385" t="str">
         <f>計算表!D385</f>
-        <v>知識回收器</v>
+        <v>尖晶石</v>
       </c>
       <c r="E385" t="str">
         <f>計算表!E385</f>
-        <v>效果值 = a × 階級(T1~T7)</v>
+        <v>數值 = a × 等級（1~5階線性；6階起每階×2）</v>
       </c>
       <c r="F385" t="str">
         <f>計算表!F385</f>
-        <v>節點=b。分解 v%/階 機率獲得經驗(裝備等級×25)（掉寶類零件效果實際×0.5）。</v>
+        <v>對應屬性=b。a=每級加成（線性，Lv5=a×5；6階起每階×2） c=百分比。</v>
       </c>
       <c r="G385">
         <f>計算表!G385</f>
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="H385" t="str">
         <f>計算表!H385</f>
-        <v>salvage</v>
-      </c>
-      <c r="I385">
+        <v>對火屬性傷害%</v>
+      </c>
+      <c r="I385" t="str">
         <f>計算表!I385</f>
-        <v>0</v>
+        <v>是</v>
       </c>
       <c r="J385">
         <f>計算表!J385</f>
@@ -31855,31 +31900,31 @@
       </c>
       <c r="C386" t="str">
         <f>計算表!C386</f>
-        <v>表-自動機組零件</v>
+        <v>表-寶石種類</v>
       </c>
       <c r="D386" t="str">
         <f>計算表!D386</f>
-        <v>探礦核心</v>
+        <v>海藍寶石</v>
       </c>
       <c r="E386" t="str">
         <f>計算表!E386</f>
-        <v>效果值 = a × 階級(T1~T7)</v>
+        <v>數值 = a × 等級（1~5階線性；6階起每階×2）</v>
       </c>
       <c r="F386" t="str">
         <f>計算表!F386</f>
-        <v>節點=b。分解 v%/階 機率額外掉一個零件（掉寶類零件效果實際×0.5）。</v>
+        <v>對應屬性=b。a=每級加成（線性，Lv5=a×5；6階起每階×2） c=百分比。</v>
       </c>
       <c r="G386">
         <f>計算表!G386</f>
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="H386" t="str">
         <f>計算表!H386</f>
-        <v>salvage</v>
-      </c>
-      <c r="I386">
+        <v>對冰屬性傷害%</v>
+      </c>
+      <c r="I386" t="str">
         <f>計算表!I386</f>
-        <v>0</v>
+        <v>是</v>
       </c>
       <c r="J386">
         <f>計算表!J386</f>
@@ -31929,19 +31974,19 @@
       </c>
       <c r="C387" t="str">
         <f>計算表!C387</f>
-        <v>表-自動機組零件</v>
+        <v>表-寶石種類</v>
       </c>
       <c r="D387" t="str">
         <f>計算表!D387</f>
-        <v>幸運晶片</v>
+        <v>天河石</v>
       </c>
       <c r="E387" t="str">
         <f>計算表!E387</f>
-        <v>效果值 = a × 階級(T1~T7)</v>
+        <v>數值 = a × 等級（1~5階線性；6階起每階×2）</v>
       </c>
       <c r="F387" t="str">
         <f>計算表!F387</f>
-        <v>節點=b。分解 v%/階 機率大豐收(碎片/金幣/精華×3)（掉寶類零件效果實際×0.5）。</v>
+        <v>對應屬性=b。a=每級加成（線性，Lv5=a×5；6階起每階×2） c=百分比。</v>
       </c>
       <c r="G387">
         <f>計算表!G387</f>
@@ -31949,11 +31994,11 @@
       </c>
       <c r="H387" t="str">
         <f>計算表!H387</f>
-        <v>salvage</v>
-      </c>
-      <c r="I387">
+        <v>對雷屬性傷害%</v>
+      </c>
+      <c r="I387" t="str">
         <f>計算表!I387</f>
-        <v>0</v>
+        <v>是</v>
       </c>
       <c r="J387">
         <f>計算表!J387</f>
@@ -32003,31 +32048,31 @@
       </c>
       <c r="C388" t="str">
         <f>計算表!C388</f>
-        <v>表-自動機組零件</v>
+        <v>表-寶石種類</v>
       </c>
       <c r="D388" t="str">
         <f>計算表!D388</f>
-        <v>太古精華萃取器</v>
+        <v>橄欖石</v>
       </c>
       <c r="E388" t="str">
         <f>計算表!E388</f>
-        <v>效果值 = a × 階級(T1~T7)</v>
+        <v>數值 = a × 等級（1~5階線性；6階起每階×2）</v>
       </c>
       <c r="F388" t="str">
         <f>計算表!F388</f>
-        <v>節點=b。分解太古精華掉落率 +v%/階（掉寶類零件效果實際×0.5）。</v>
+        <v>對應屬性=b。a=每級加成（線性，Lv5=a×5；6階起每階×2） c=百分比。</v>
       </c>
       <c r="G388">
         <f>計算表!G388</f>
-        <v>25</v>
+        <v>0.5</v>
       </c>
       <c r="H388" t="str">
         <f>計算表!H388</f>
-        <v>salvage</v>
-      </c>
-      <c r="I388">
+        <v>對毒屬性傷害%</v>
+      </c>
+      <c r="I388" t="str">
         <f>計算表!I388</f>
-        <v>0</v>
+        <v>是</v>
       </c>
       <c r="J388">
         <f>計算表!J388</f>
@@ -32077,31 +32122,31 @@
       </c>
       <c r="C389" t="str">
         <f>計算表!C389</f>
-        <v>表-自動機組零件</v>
+        <v>表-寶石種類</v>
       </c>
       <c r="D389" t="str">
         <f>計算表!D389</f>
-        <v>幸運核心</v>
+        <v>黃水晶</v>
       </c>
       <c r="E389" t="str">
         <f>計算表!E389</f>
-        <v>效果值 = a × 階級(T1~T7)</v>
+        <v>數值 = a × 等級（1~5階線性；6階起每階×2）</v>
       </c>
       <c r="F389" t="str">
         <f>計算表!F389</f>
-        <v>節點=b。合成大成功率 +v%/階（掉寶類零件效果實際×0.5）。</v>
+        <v>對應屬性=b。a=每級加成（線性，Lv5=a×5；6階起每階×2） c=百分比。</v>
       </c>
       <c r="G389">
         <f>計算表!G389</f>
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="H389" t="str">
         <f>計算表!H389</f>
-        <v>synth</v>
-      </c>
-      <c r="I389">
+        <v>對光屬性傷害%</v>
+      </c>
+      <c r="I389" t="str">
         <f>計算表!I389</f>
-        <v>0</v>
+        <v>是</v>
       </c>
       <c r="J389">
         <f>計算表!J389</f>
@@ -32151,31 +32196,31 @@
       </c>
       <c r="C390" t="str">
         <f>計算表!C390</f>
-        <v>表-自動機組零件</v>
+        <v>表-寶石種類</v>
       </c>
       <c r="D390" t="str">
         <f>計算表!D390</f>
-        <v>重骰模組</v>
+        <v>黑碧璽</v>
       </c>
       <c r="E390" t="str">
         <f>計算表!E390</f>
-        <v>效果值 = a × 階級(T1~T7)</v>
+        <v>數值 = a × 等級（1~5階線性；6階起每階×2）</v>
       </c>
       <c r="F390" t="str">
         <f>計算表!F390</f>
-        <v>節點=b。合成詞條重骰機率 +v%/階（掉寶類零件效果實際×0.5）。</v>
+        <v>對應屬性=b。a=每級加成（線性，Lv5=a×5；6階起每階×2） c=百分比。</v>
       </c>
       <c r="G390">
         <f>計算表!G390</f>
-        <v>15</v>
+        <v>0.5</v>
       </c>
       <c r="H390" t="str">
         <f>計算表!H390</f>
-        <v>synth</v>
-      </c>
-      <c r="I390">
+        <v>對暗屬性傷害%</v>
+      </c>
+      <c r="I390" t="str">
         <f>計算表!I390</f>
-        <v>0</v>
+        <v>是</v>
       </c>
       <c r="J390">
         <f>計算表!J390</f>
@@ -32225,27 +32270,27 @@
       </c>
       <c r="C391" t="str">
         <f>計算表!C391</f>
-        <v>表-固定參數</v>
+        <v>表-自動機組零件</v>
       </c>
       <c r="D391" t="str">
         <f>計算表!D391</f>
-        <v>出怪間隔</v>
+        <v>加速齒輪</v>
       </c>
       <c r="E391" t="str">
         <f>計算表!E391</f>
-        <v>a 秒 × (1-移動速度%)</v>
+        <v>效果值 = a × 階級(T1~T7)</v>
       </c>
       <c r="F391" t="str">
         <f>計算表!F391</f>
-        <v>RESPAWN_DELAY。</v>
+        <v>節點=b。分解速度 +v%/階（另固定+50 個百分點）（掉寶類零件效果實際×0.5）。</v>
       </c>
       <c r="G391">
         <f>計算表!G391</f>
-        <v>0.8</v>
-      </c>
-      <c r="H391">
+        <v>25</v>
+      </c>
+      <c r="H391" t="str">
         <f>計算表!H391</f>
-        <v>0</v>
+        <v>salvage</v>
       </c>
       <c r="I391">
         <f>計算表!I391</f>
@@ -32299,27 +32344,27 @@
       </c>
       <c r="C392" t="str">
         <f>計算表!C392</f>
-        <v>表-固定參數</v>
+        <v>表-自動機組零件</v>
       </c>
       <c r="D392" t="str">
         <f>計算表!D392</f>
-        <v>死亡復活時間</v>
+        <v>碎片熔煉爐</v>
       </c>
       <c r="E392" t="str">
         <f>計算表!E392</f>
-        <v>a 秒</v>
+        <v>效果值 = a × 階級(T1~T7)</v>
       </c>
       <c r="F392" t="str">
         <f>計算表!F392</f>
-        <v>REVIVE_DELAY。</v>
+        <v>節點=b。分解碎片產量 +v%/階（掉寶類零件效果實際×0.5）。</v>
       </c>
       <c r="G392">
         <f>計算表!G392</f>
-        <v>3</v>
-      </c>
-      <c r="H392">
+        <v>20</v>
+      </c>
+      <c r="H392" t="str">
         <f>計算表!H392</f>
-        <v>0</v>
+        <v>salvage</v>
       </c>
       <c r="I392">
         <f>計算表!I392</f>
@@ -32373,27 +32418,27 @@
       </c>
       <c r="C393" t="str">
         <f>計算表!C393</f>
-        <v>表-固定參數</v>
+        <v>表-自動機組零件</v>
       </c>
       <c r="D393" t="str">
         <f>計算表!D393</f>
-        <v>零件階級上限</v>
+        <v>淘金濾網</v>
       </c>
       <c r="E393" t="str">
         <f>計算表!E393</f>
-        <v>T a</v>
+        <v>效果值 = a × 階級(T1~T7)</v>
       </c>
       <c r="F393" t="str">
         <f>計算表!F393</f>
-        <v>PART_MAX_TIER。</v>
+        <v>節點=b。分解金幣產量 +v%/階（掉寶類零件效果實際×0.5）。</v>
       </c>
       <c r="G393">
         <f>計算表!G393</f>
-        <v>7</v>
-      </c>
-      <c r="H393">
+        <v>25</v>
+      </c>
+      <c r="H393" t="str">
         <f>計算表!H393</f>
-        <v>0</v>
+        <v>salvage</v>
       </c>
       <c r="I393">
         <f>計算表!I393</f>
@@ -32447,27 +32492,27 @@
       </c>
       <c r="C394" t="str">
         <f>計算表!C394</f>
-        <v>表-固定參數</v>
+        <v>表-自動機組零件</v>
       </c>
       <c r="D394" t="str">
         <f>計算表!D394</f>
-        <v>零件庫存保留</v>
+        <v>精粹透鏡</v>
       </c>
       <c r="E394" t="str">
         <f>計算表!E394</f>
-        <v>每種未安裝最多保留 a 顆</v>
+        <v>效果值 = a × 階級(T1~T7)</v>
       </c>
       <c r="F394" t="str">
         <f>計算表!F394</f>
-        <v>PART_KEEP_PER_KEY，多餘自動分解。</v>
+        <v>節點=b。附魔精華拆解產出率 +v%/階（掉寶類零件效果實際×0.5）。</v>
       </c>
       <c r="G394">
         <f>計算表!G394</f>
-        <v>10</v>
-      </c>
-      <c r="H394">
+        <v>20</v>
+      </c>
+      <c r="H394" t="str">
         <f>計算表!H394</f>
-        <v>0</v>
+        <v>salvage</v>
       </c>
       <c r="I394">
         <f>計算表!I394</f>
@@ -32521,27 +32566,27 @@
       </c>
       <c r="C395" t="str">
         <f>計算表!C395</f>
-        <v>表-固定參數</v>
+        <v>表-自動機組零件</v>
       </c>
       <c r="D395" t="str">
         <f>計算表!D395</f>
-        <v>合成節點槽位</v>
+        <v>拓本回收臂</v>
       </c>
       <c r="E395" t="str">
         <f>計算表!E395</f>
-        <v>a 格</v>
+        <v>效果值 = a × 階級(T1~T7)</v>
       </c>
       <c r="F395" t="str">
         <f>計算表!F395</f>
-        <v>分解槽為金幣解鎖 10~20 格。　※合成功能已停用，本列未生效。</v>
+        <v>節點=b。分解 v%/階 機率回收 1 本附魔書（掉寶類零件效果實際×0.5）。</v>
       </c>
       <c r="G395">
         <f>計算表!G395</f>
-        <v>2</v>
-      </c>
-      <c r="H395">
+        <v>0.4</v>
+      </c>
+      <c r="H395" t="str">
         <f>計算表!H395</f>
-        <v>0</v>
+        <v>salvage</v>
       </c>
       <c r="I395">
         <f>計算表!I395</f>
@@ -32595,27 +32640,27 @@
       </c>
       <c r="C396" t="str">
         <f>計算表!C396</f>
-        <v>表-固定參數</v>
+        <v>表-自動機組零件</v>
       </c>
       <c r="D396" t="str">
         <f>計算表!D396</f>
-        <v>寶石一般上限 / 神鑄上限</v>
+        <v>複製處理艙</v>
       </c>
       <c r="E396" t="str">
         <f>計算表!E396</f>
-        <v>一般 a 階；神鑄可到 b 階</v>
+        <v>效果值 = a × 階級(T1~T7)</v>
       </c>
       <c r="F396" t="str">
         <f>計算表!F396</f>
-        <v>GEM_MAX_LEVEL / GEM_FORGE_MAX_LEVEL。</v>
+        <v>節點=b。分解 v%/階 機率碎片+金幣翻倍（掉寶類零件效果實際×0.5）。</v>
       </c>
       <c r="G396">
         <f>計算表!G396</f>
-        <v>5</v>
-      </c>
-      <c r="H396">
+        <v>3</v>
+      </c>
+      <c r="H396" t="str">
         <f>計算表!H396</f>
-        <v>10</v>
+        <v>salvage</v>
       </c>
       <c r="I396">
         <f>計算表!I396</f>
@@ -32669,27 +32714,27 @@
       </c>
       <c r="C397" t="str">
         <f>計算表!C397</f>
-        <v>表-固定參數</v>
+        <v>表-自動機組零件</v>
       </c>
       <c r="D397" t="str">
         <f>計算表!D397</f>
-        <v>詞條數硬上限</v>
+        <v>知識回收器</v>
       </c>
       <c r="E397" t="str">
         <f>計算表!E397</f>
-        <v>a 條</v>
+        <v>效果值 = a × 階級(T1~T7)</v>
       </c>
       <c r="F397" t="str">
         <f>計算表!F397</f>
-        <v>MAX_AFFIXES = 創世 7 條 + 詞條上限率突破 1 條。單件裝備可堆疊的最大詞條數。</v>
+        <v>節點=b。分解 v%/階 機率獲得經驗(裝備等級×25)（掉寶類零件效果實際×0.5）。</v>
       </c>
       <c r="G397">
         <f>計算表!G397</f>
-        <v>8</v>
-      </c>
-      <c r="H397">
+        <v>1.5</v>
+      </c>
+      <c r="H397" t="str">
         <f>計算表!H397</f>
-        <v>0</v>
+        <v>salvage</v>
       </c>
       <c r="I397">
         <f>計算表!I397</f>
@@ -32743,27 +32788,27 @@
       </c>
       <c r="C398" t="str">
         <f>計算表!C398</f>
-        <v>表-戰力權重</v>
+        <v>表-自動機組零件</v>
       </c>
       <c r="D398" t="str">
         <f>計算表!D398</f>
-        <v>物理攻擊</v>
+        <v>探礦核心</v>
       </c>
       <c r="E398" t="str">
         <f>計算表!E398</f>
-        <v>評分權重 = a</v>
+        <v>效果值 = a × 階級(T1~T7)</v>
       </c>
       <c r="F398" t="str">
         <f>計算表!F398</f>
-        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+        <v>節點=b。分解 v%/階 機率額外掉一個零件（掉寶類零件效果實際×0.5）。</v>
       </c>
       <c r="G398">
         <f>計算表!G398</f>
-        <v>1</v>
-      </c>
-      <c r="H398">
+        <v>0.15</v>
+      </c>
+      <c r="H398" t="str">
         <f>計算表!H398</f>
-        <v>0</v>
+        <v>salvage</v>
       </c>
       <c r="I398">
         <f>計算表!I398</f>
@@ -32817,27 +32862,27 @@
       </c>
       <c r="C399" t="str">
         <f>計算表!C399</f>
-        <v>表-戰力權重</v>
+        <v>表-自動機組零件</v>
       </c>
       <c r="D399" t="str">
         <f>計算表!D399</f>
-        <v>物理攻擊%</v>
+        <v>幸運晶片</v>
       </c>
       <c r="E399" t="str">
         <f>計算表!E399</f>
-        <v>評分權重 = a</v>
+        <v>效果值 = a × 階級(T1~T7)</v>
       </c>
       <c r="F399" t="str">
         <f>計算表!F399</f>
-        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+        <v>節點=b。分解 v%/階 機率大豐收(碎片/金幣/精華×3)（掉寶類零件效果實際×0.5）。</v>
       </c>
       <c r="G399">
         <f>計算表!G399</f>
-        <v>2.6</v>
-      </c>
-      <c r="H399">
+        <v>0.5</v>
+      </c>
+      <c r="H399" t="str">
         <f>計算表!H399</f>
-        <v>0</v>
+        <v>salvage</v>
       </c>
       <c r="I399">
         <f>計算表!I399</f>
@@ -32891,27 +32936,27 @@
       </c>
       <c r="C400" t="str">
         <f>計算表!C400</f>
-        <v>表-戰力權重</v>
+        <v>表-自動機組零件</v>
       </c>
       <c r="D400" t="str">
         <f>計算表!D400</f>
-        <v>魔法攻擊</v>
+        <v>太古精華萃取器</v>
       </c>
       <c r="E400" t="str">
         <f>計算表!E400</f>
-        <v>評分權重 = a</v>
+        <v>效果值 = a × 階級(T1~T7)</v>
       </c>
       <c r="F400" t="str">
         <f>計算表!F400</f>
-        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+        <v>節點=b。分解太古精華掉落率 +v%/階（掉寶類零件效果實際×0.5）。</v>
       </c>
       <c r="G400">
         <f>計算表!G400</f>
-        <v>1</v>
-      </c>
-      <c r="H400">
+        <v>25</v>
+      </c>
+      <c r="H400" t="str">
         <f>計算表!H400</f>
-        <v>0</v>
+        <v>salvage</v>
       </c>
       <c r="I400">
         <f>計算表!I400</f>
@@ -32965,27 +33010,27 @@
       </c>
       <c r="C401" t="str">
         <f>計算表!C401</f>
-        <v>表-戰力權重</v>
+        <v>表-自動機組零件</v>
       </c>
       <c r="D401" t="str">
         <f>計算表!D401</f>
-        <v>魔法攻擊%</v>
+        <v>幸運核心</v>
       </c>
       <c r="E401" t="str">
         <f>計算表!E401</f>
-        <v>評分權重 = a</v>
+        <v>效果值 = a × 階級(T1~T7)</v>
       </c>
       <c r="F401" t="str">
         <f>計算表!F401</f>
-        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+        <v>節點=b。合成大成功率 +v%/階（掉寶類零件效果實際×0.5）。</v>
       </c>
       <c r="G401">
         <f>計算表!G401</f>
-        <v>2.6</v>
-      </c>
-      <c r="H401">
+        <v>8</v>
+      </c>
+      <c r="H401" t="str">
         <f>計算表!H401</f>
-        <v>0</v>
+        <v>synth</v>
       </c>
       <c r="I401">
         <f>計算表!I401</f>
@@ -33039,27 +33084,27 @@
       </c>
       <c r="C402" t="str">
         <f>計算表!C402</f>
-        <v>表-戰力權重</v>
+        <v>表-自動機組零件</v>
       </c>
       <c r="D402" t="str">
         <f>計算表!D402</f>
-        <v>生命值</v>
+        <v>重骰模組</v>
       </c>
       <c r="E402" t="str">
         <f>計算表!E402</f>
-        <v>評分權重 = a</v>
+        <v>效果值 = a × 階級(T1~T7)</v>
       </c>
       <c r="F402" t="str">
         <f>計算表!F402</f>
-        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+        <v>節點=b。合成詞條重骰機率 +v%/階（掉寶類零件效果實際×0.5）。</v>
       </c>
       <c r="G402">
         <f>計算表!G402</f>
-        <v>0.16</v>
-      </c>
-      <c r="H402">
+        <v>15</v>
+      </c>
+      <c r="H402" t="str">
         <f>計算表!H402</f>
-        <v>0</v>
+        <v>synth</v>
       </c>
       <c r="I402">
         <f>計算表!I402</f>
@@ -33113,23 +33158,23 @@
       </c>
       <c r="C403" t="str">
         <f>計算表!C403</f>
-        <v>表-戰力權重</v>
+        <v>表-固定參數</v>
       </c>
       <c r="D403" t="str">
         <f>計算表!D403</f>
-        <v>生命值%</v>
+        <v>出怪間隔</v>
       </c>
       <c r="E403" t="str">
         <f>計算表!E403</f>
-        <v>評分權重 = a</v>
+        <v>a 秒 × (1-移動速度%)</v>
       </c>
       <c r="F403" t="str">
         <f>計算表!F403</f>
-        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+        <v>RESPAWN_DELAY。</v>
       </c>
       <c r="G403">
         <f>計算表!G403</f>
-        <v>2.2000000000000002</v>
+        <v>0.8</v>
       </c>
       <c r="H403">
         <f>計算表!H403</f>
@@ -33187,23 +33232,23 @@
       </c>
       <c r="C404" t="str">
         <f>計算表!C404</f>
-        <v>表-戰力權重</v>
+        <v>表-固定參數</v>
       </c>
       <c r="D404" t="str">
         <f>計算表!D404</f>
-        <v>生命恢復/秒</v>
+        <v>死亡復活時間</v>
       </c>
       <c r="E404" t="str">
         <f>計算表!E404</f>
-        <v>評分權重 = a</v>
+        <v>a 秒</v>
       </c>
       <c r="F404" t="str">
         <f>計算表!F404</f>
-        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+        <v>REVIVE_DELAY。</v>
       </c>
       <c r="G404">
         <f>計算表!G404</f>
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="H404">
         <f>計算表!H404</f>
@@ -33261,23 +33306,23 @@
       </c>
       <c r="C405" t="str">
         <f>計算表!C405</f>
-        <v>表-戰力權重</v>
+        <v>表-固定參數</v>
       </c>
       <c r="D405" t="str">
         <f>計算表!D405</f>
-        <v>物理防禦</v>
+        <v>零件階級上限</v>
       </c>
       <c r="E405" t="str">
         <f>計算表!E405</f>
-        <v>評分權重 = a</v>
+        <v>T a</v>
       </c>
       <c r="F405" t="str">
         <f>計算表!F405</f>
-        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+        <v>PART_MAX_TIER。</v>
       </c>
       <c r="G405">
         <f>計算表!G405</f>
-        <v>0.9</v>
+        <v>7</v>
       </c>
       <c r="H405">
         <f>計算表!H405</f>
@@ -33335,23 +33380,23 @@
       </c>
       <c r="C406" t="str">
         <f>計算表!C406</f>
-        <v>表-戰力權重</v>
+        <v>表-固定參數</v>
       </c>
       <c r="D406" t="str">
         <f>計算表!D406</f>
-        <v>物理防禦%</v>
+        <v>零件庫存保留</v>
       </c>
       <c r="E406" t="str">
         <f>計算表!E406</f>
-        <v>評分權重 = a</v>
+        <v>每種未安裝最多保留 a 顆</v>
       </c>
       <c r="F406" t="str">
         <f>計算表!F406</f>
-        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+        <v>PART_KEEP_PER_KEY，多餘自動分解。</v>
       </c>
       <c r="G406">
         <f>計算表!G406</f>
-        <v>1.8</v>
+        <v>10</v>
       </c>
       <c r="H406">
         <f>計算表!H406</f>
@@ -33409,23 +33454,23 @@
       </c>
       <c r="C407" t="str">
         <f>計算表!C407</f>
-        <v>表-戰力權重</v>
+        <v>表-固定參數</v>
       </c>
       <c r="D407" t="str">
         <f>計算表!D407</f>
-        <v>魔法防禦</v>
+        <v>合成節點槽位</v>
       </c>
       <c r="E407" t="str">
         <f>計算表!E407</f>
-        <v>評分權重 = a</v>
+        <v>a 格</v>
       </c>
       <c r="F407" t="str">
         <f>計算表!F407</f>
-        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+        <v>分解槽為金幣解鎖 10~20 格。　※合成功能已停用，本列未生效。</v>
       </c>
       <c r="G407">
         <f>計算表!G407</f>
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="H407">
         <f>計算表!H407</f>
@@ -33483,27 +33528,27 @@
       </c>
       <c r="C408" t="str">
         <f>計算表!C408</f>
-        <v>表-戰力權重</v>
+        <v>表-固定參數</v>
       </c>
       <c r="D408" t="str">
         <f>計算表!D408</f>
-        <v>法力值</v>
+        <v>寶石一般上限 / 神鑄上限</v>
       </c>
       <c r="E408" t="str">
         <f>計算表!E408</f>
-        <v>評分權重 = a</v>
+        <v>一般 a 階；神鑄可到 b 階</v>
       </c>
       <c r="F408" t="str">
         <f>計算表!F408</f>
-        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+        <v>GEM_MAX_LEVEL / GEM_FORGE_MAX_LEVEL。</v>
       </c>
       <c r="G408">
         <f>計算表!G408</f>
-        <v>0.25</v>
+        <v>5</v>
       </c>
       <c r="H408">
         <f>計算表!H408</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I408">
         <f>計算表!I408</f>
@@ -33557,23 +33602,23 @@
       </c>
       <c r="C409" t="str">
         <f>計算表!C409</f>
-        <v>表-戰力權重</v>
+        <v>表-固定參數</v>
       </c>
       <c r="D409" t="str">
         <f>計算表!D409</f>
-        <v>法力恢復/秒</v>
+        <v>詞條數硬上限</v>
       </c>
       <c r="E409" t="str">
         <f>計算表!E409</f>
-        <v>評分權重 = a</v>
+        <v>a 條</v>
       </c>
       <c r="F409" t="str">
         <f>計算表!F409</f>
-        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+        <v>MAX_AFFIXES = 創世 7 條 + 詞條上限率突破 1 條。單件裝備可堆疊的最大詞條數。</v>
       </c>
       <c r="G409">
         <f>計算表!G409</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H409">
         <f>計算表!H409</f>
@@ -33635,7 +33680,7 @@
       </c>
       <c r="D410" t="str">
         <f>計算表!D410</f>
-        <v>力量</v>
+        <v>物理攻擊</v>
       </c>
       <c r="E410" t="str">
         <f>計算表!E410</f>
@@ -33647,7 +33692,7 @@
       </c>
       <c r="G410">
         <f>計算表!G410</f>
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="H410">
         <f>計算表!H410</f>
@@ -33709,7 +33754,7 @@
       </c>
       <c r="D411" t="str">
         <f>計算表!D411</f>
-        <v>敏捷</v>
+        <v>物理攻擊%</v>
       </c>
       <c r="E411" t="str">
         <f>計算表!E411</f>
@@ -33721,7 +33766,7 @@
       </c>
       <c r="G411">
         <f>計算表!G411</f>
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="H411">
         <f>計算表!H411</f>
@@ -33783,7 +33828,7 @@
       </c>
       <c r="D412" t="str">
         <f>計算表!D412</f>
-        <v>智力</v>
+        <v>魔法攻擊</v>
       </c>
       <c r="E412" t="str">
         <f>計算表!E412</f>
@@ -33795,7 +33840,7 @@
       </c>
       <c r="G412">
         <f>計算表!G412</f>
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="H412">
         <f>計算表!H412</f>
@@ -33857,7 +33902,7 @@
       </c>
       <c r="D413" t="str">
         <f>計算表!D413</f>
-        <v>耐力</v>
+        <v>魔法攻擊%</v>
       </c>
       <c r="E413" t="str">
         <f>計算表!E413</f>
@@ -33869,7 +33914,7 @@
       </c>
       <c r="G413">
         <f>計算表!G413</f>
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="H413">
         <f>計算表!H413</f>
@@ -33931,7 +33976,7 @@
       </c>
       <c r="D414" t="str">
         <f>計算表!D414</f>
-        <v>攻擊速度%</v>
+        <v>生命值</v>
       </c>
       <c r="E414" t="str">
         <f>計算表!E414</f>
@@ -33943,7 +33988,7 @@
       </c>
       <c r="G414">
         <f>計算表!G414</f>
-        <v>2.8</v>
+        <v>0.16</v>
       </c>
       <c r="H414">
         <f>計算表!H414</f>
@@ -34005,7 +34050,7 @@
       </c>
       <c r="D415" t="str">
         <f>計算表!D415</f>
-        <v>暴擊率%</v>
+        <v>生命值%</v>
       </c>
       <c r="E415" t="str">
         <f>計算表!E415</f>
@@ -34017,7 +34062,7 @@
       </c>
       <c r="G415">
         <f>計算表!G415</f>
-        <v>2.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H415">
         <f>計算表!H415</f>
@@ -34079,7 +34124,7 @@
       </c>
       <c r="D416" t="str">
         <f>計算表!D416</f>
-        <v>暴擊傷害%</v>
+        <v>生命恢復/秒</v>
       </c>
       <c r="E416" t="str">
         <f>計算表!E416</f>
@@ -34091,7 +34136,7 @@
       </c>
       <c r="G416">
         <f>計算表!G416</f>
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="H416">
         <f>計算表!H416</f>
@@ -34153,7 +34198,7 @@
       </c>
       <c r="D417" t="str">
         <f>計算表!D417</f>
-        <v>物理穿透%</v>
+        <v>物理防禦</v>
       </c>
       <c r="E417" t="str">
         <f>計算表!E417</f>
@@ -34165,7 +34210,7 @@
       </c>
       <c r="G417">
         <f>計算表!G417</f>
-        <v>2.2000000000000002</v>
+        <v>0.9</v>
       </c>
       <c r="H417">
         <f>計算表!H417</f>
@@ -34227,7 +34272,7 @@
       </c>
       <c r="D418" t="str">
         <f>計算表!D418</f>
-        <v>魔法穿透%</v>
+        <v>物理防禦%</v>
       </c>
       <c r="E418" t="str">
         <f>計算表!E418</f>
@@ -34239,7 +34284,7 @@
       </c>
       <c r="G418">
         <f>計算表!G418</f>
-        <v>2.2000000000000002</v>
+        <v>1.8</v>
       </c>
       <c r="H418">
         <f>計算表!H418</f>
@@ -34301,7 +34346,7 @@
       </c>
       <c r="D419" t="str">
         <f>計算表!D419</f>
-        <v>命中率%</v>
+        <v>魔法防禦</v>
       </c>
       <c r="E419" t="str">
         <f>計算表!E419</f>
@@ -34313,7 +34358,7 @@
       </c>
       <c r="G419">
         <f>計算表!G419</f>
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="H419">
         <f>計算表!H419</f>
@@ -34375,7 +34420,7 @@
       </c>
       <c r="D420" t="str">
         <f>計算表!D420</f>
-        <v>冷卻縮減%</v>
+        <v>法力值</v>
       </c>
       <c r="E420" t="str">
         <f>計算表!E420</f>
@@ -34387,7 +34432,7 @@
       </c>
       <c r="G420">
         <f>計算表!G420</f>
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="H420">
         <f>計算表!H420</f>
@@ -34449,7 +34494,7 @@
       </c>
       <c r="D421" t="str">
         <f>計算表!D421</f>
-        <v>施法速度%</v>
+        <v>法力恢復/秒</v>
       </c>
       <c r="E421" t="str">
         <f>計算表!E421</f>
@@ -34461,7 +34506,7 @@
       </c>
       <c r="G421">
         <f>計算表!G421</f>
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="H421">
         <f>計算表!H421</f>
@@ -34523,7 +34568,7 @@
       </c>
       <c r="D422" t="str">
         <f>計算表!D422</f>
-        <v>吸血%</v>
+        <v>力量</v>
       </c>
       <c r="E422" t="str">
         <f>計算表!E422</f>
@@ -34535,7 +34580,7 @@
       </c>
       <c r="G422">
         <f>計算表!G422</f>
-        <v>2.2000000000000002</v>
+        <v>1.8</v>
       </c>
       <c r="H422">
         <f>計算表!H422</f>
@@ -34597,7 +34642,7 @@
       </c>
       <c r="D423" t="str">
         <f>計算表!D423</f>
-        <v>吸魔%</v>
+        <v>敏捷</v>
       </c>
       <c r="E423" t="str">
         <f>計算表!E423</f>
@@ -34609,7 +34654,7 @@
       </c>
       <c r="G423">
         <f>計算表!G423</f>
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="H423">
         <f>計算表!H423</f>
@@ -34671,7 +34716,7 @@
       </c>
       <c r="D424" t="str">
         <f>計算表!D424</f>
-        <v>對菁英傷害%</v>
+        <v>智力</v>
       </c>
       <c r="E424" t="str">
         <f>計算表!E424</f>
@@ -34683,7 +34728,7 @@
       </c>
       <c r="G424">
         <f>計算表!G424</f>
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="H424">
         <f>計算表!H424</f>
@@ -34745,7 +34790,7 @@
       </c>
       <c r="D425" t="str">
         <f>計算表!D425</f>
-        <v>對BOSS傷害%</v>
+        <v>耐力</v>
       </c>
       <c r="E425" t="str">
         <f>計算表!E425</f>
@@ -34757,7 +34802,7 @@
       </c>
       <c r="G425">
         <f>計算表!G425</f>
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="H425">
         <f>計算表!H425</f>
@@ -34819,7 +34864,7 @@
       </c>
       <c r="D426" t="str">
         <f>計算表!D426</f>
-        <v>對普通敵人傷害%</v>
+        <v>攻擊速度%</v>
       </c>
       <c r="E426" t="str">
         <f>計算表!E426</f>
@@ -34831,7 +34876,7 @@
       </c>
       <c r="G426">
         <f>計算表!G426</f>
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="H426">
         <f>計算表!H426</f>
@@ -34893,7 +34938,7 @@
       </c>
       <c r="D427" t="str">
         <f>計算表!D427</f>
-        <v>範圍傷害%</v>
+        <v>暴擊率%</v>
       </c>
       <c r="E427" t="str">
         <f>計算表!E427</f>
@@ -34905,7 +34950,7 @@
       </c>
       <c r="G427">
         <f>計算表!G427</f>
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="H427">
         <f>計算表!H427</f>
@@ -34967,7 +35012,7 @@
       </c>
       <c r="D428" t="str">
         <f>計算表!D428</f>
-        <v>全局減傷</v>
+        <v>暴擊傷害%</v>
       </c>
       <c r="E428" t="str">
         <f>計算表!E428</f>
@@ -34979,7 +35024,7 @@
       </c>
       <c r="G428">
         <f>計算表!G428</f>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H428">
         <f>計算表!H428</f>
@@ -35041,7 +35086,7 @@
       </c>
       <c r="D429" t="str">
         <f>計算表!D429</f>
-        <v>普通敵人傷害抗性</v>
+        <v>物理穿透%</v>
       </c>
       <c r="E429" t="str">
         <f>計算表!E429</f>
@@ -35053,7 +35098,7 @@
       </c>
       <c r="G429">
         <f>計算表!G429</f>
-        <v>1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H429">
         <f>計算表!H429</f>
@@ -35115,7 +35160,7 @@
       </c>
       <c r="D430" t="str">
         <f>計算表!D430</f>
-        <v>菁英傷害抗性</v>
+        <v>魔法穿透%</v>
       </c>
       <c r="E430" t="str">
         <f>計算表!E430</f>
@@ -35127,7 +35172,7 @@
       </c>
       <c r="G430">
         <f>計算表!G430</f>
-        <v>1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H430">
         <f>計算表!H430</f>
@@ -35189,7 +35234,7 @@
       </c>
       <c r="D431" t="str">
         <f>計算表!D431</f>
-        <v>BOSS傷害抗性</v>
+        <v>命中率%</v>
       </c>
       <c r="E431" t="str">
         <f>計算表!E431</f>
@@ -35201,7 +35246,7 @@
       </c>
       <c r="G431">
         <f>計算表!G431</f>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H431">
         <f>計算表!H431</f>
@@ -35263,7 +35308,7 @@
       </c>
       <c r="D432" t="str">
         <f>計算表!D432</f>
-        <v>格擋率%</v>
+        <v>冷卻縮減%</v>
       </c>
       <c r="E432" t="str">
         <f>計算表!E432</f>
@@ -35337,7 +35382,7 @@
       </c>
       <c r="D433" t="str">
         <f>計算表!D433</f>
-        <v>格擋減傷%</v>
+        <v>施法速度%</v>
       </c>
       <c r="E433" t="str">
         <f>計算表!E433</f>
@@ -35349,7 +35394,7 @@
       </c>
       <c r="G433">
         <f>計算表!G433</f>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="H433">
         <f>計算表!H433</f>
@@ -35411,7 +35456,7 @@
       </c>
       <c r="D434" t="str">
         <f>計算表!D434</f>
-        <v>閃避率%</v>
+        <v>吸血%</v>
       </c>
       <c r="E434" t="str">
         <f>計算表!E434</f>
@@ -35485,7 +35530,7 @@
       </c>
       <c r="D435" t="str">
         <f>計算表!D435</f>
-        <v>韌性%</v>
+        <v>吸魔%</v>
       </c>
       <c r="E435" t="str">
         <f>計算表!E435</f>
@@ -35497,7 +35542,7 @@
       </c>
       <c r="G435">
         <f>計算表!G435</f>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="H435">
         <f>計算表!H435</f>
@@ -35559,7 +35604,7 @@
       </c>
       <c r="D436" t="str">
         <f>計算表!D436</f>
-        <v>護盾效率%</v>
+        <v>對菁英傷害%</v>
       </c>
       <c r="E436" t="str">
         <f>計算表!E436</f>
@@ -35571,7 +35616,7 @@
       </c>
       <c r="G436">
         <f>計算表!G436</f>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H436">
         <f>計算表!H436</f>
@@ -35633,7 +35678,7 @@
       </c>
       <c r="D437" t="str">
         <f>計算表!D437</f>
-        <v>物理抗性%</v>
+        <v>對BOSS傷害%</v>
       </c>
       <c r="E437" t="str">
         <f>計算表!E437</f>
@@ -35645,7 +35690,7 @@
       </c>
       <c r="G437">
         <f>計算表!G437</f>
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="H437">
         <f>計算表!H437</f>
@@ -35707,7 +35752,7 @@
       </c>
       <c r="D438" t="str">
         <f>計算表!D438</f>
-        <v>魔法抗性%</v>
+        <v>對普通敵人傷害%</v>
       </c>
       <c r="E438" t="str">
         <f>計算表!E438</f>
@@ -35719,7 +35764,7 @@
       </c>
       <c r="G438">
         <f>計算表!G438</f>
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="H438">
         <f>計算表!H438</f>
@@ -35781,7 +35826,7 @@
       </c>
       <c r="D439" t="str">
         <f>計算表!D439</f>
-        <v>火焰抗性%</v>
+        <v>範圍傷害%</v>
       </c>
       <c r="E439" t="str">
         <f>計算表!E439</f>
@@ -35793,7 +35838,7 @@
       </c>
       <c r="G439">
         <f>計算表!G439</f>
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="H439">
         <f>計算表!H439</f>
@@ -35855,7 +35900,7 @@
       </c>
       <c r="D440" t="str">
         <f>計算表!D440</f>
-        <v>冰霜抗性%</v>
+        <v>全局減傷</v>
       </c>
       <c r="E440" t="str">
         <f>計算表!E440</f>
@@ -35867,7 +35912,7 @@
       </c>
       <c r="G440">
         <f>計算表!G440</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H440">
         <f>計算表!H440</f>
@@ -35929,7 +35974,7 @@
       </c>
       <c r="D441" t="str">
         <f>計算表!D441</f>
-        <v>雷電抗性%</v>
+        <v>普通敵人傷害抗性</v>
       </c>
       <c r="E441" t="str">
         <f>計算表!E441</f>
@@ -35941,7 +35986,7 @@
       </c>
       <c r="G441">
         <f>計算表!G441</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H441">
         <f>計算表!H441</f>
@@ -36003,7 +36048,7 @@
       </c>
       <c r="D442" t="str">
         <f>計算表!D442</f>
-        <v>劇毒抗性%</v>
+        <v>菁英傷害抗性</v>
       </c>
       <c r="E442" t="str">
         <f>計算表!E442</f>
@@ -36015,7 +36060,7 @@
       </c>
       <c r="G442">
         <f>計算表!G442</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H442">
         <f>計算表!H442</f>
@@ -36077,7 +36122,7 @@
       </c>
       <c r="D443" t="str">
         <f>計算表!D443</f>
-        <v>聖光抗性%</v>
+        <v>BOSS傷害抗性</v>
       </c>
       <c r="E443" t="str">
         <f>計算表!E443</f>
@@ -36089,7 +36134,7 @@
       </c>
       <c r="G443">
         <f>計算表!G443</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H443">
         <f>計算表!H443</f>
@@ -36151,7 +36196,7 @@
       </c>
       <c r="D444" t="str">
         <f>計算表!D444</f>
-        <v>暗影抗性%</v>
+        <v>格擋率%</v>
       </c>
       <c r="E444" t="str">
         <f>計算表!E444</f>
@@ -36163,7 +36208,7 @@
       </c>
       <c r="G444">
         <f>計算表!G444</f>
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="H444">
         <f>計算表!H444</f>
@@ -36225,7 +36270,7 @@
       </c>
       <c r="D445" t="str">
         <f>計算表!D445</f>
-        <v>控制時間縮減%</v>
+        <v>格擋減傷%</v>
       </c>
       <c r="E445" t="str">
         <f>計算表!E445</f>
@@ -36299,7 +36344,7 @@
       </c>
       <c r="D446" t="str">
         <f>計算表!D446</f>
-        <v>移動速度%</v>
+        <v>閃避率%</v>
       </c>
       <c r="E446" t="str">
         <f>計算表!E446</f>
@@ -36311,7 +36356,7 @@
       </c>
       <c r="G446">
         <f>計算表!G446</f>
-        <v>1.5</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H446">
         <f>計算表!H446</f>
@@ -36373,7 +36418,7 @@
       </c>
       <c r="D447" t="str">
         <f>計算表!D447</f>
-        <v>掉寶率%</v>
+        <v>韌性%</v>
       </c>
       <c r="E447" t="str">
         <f>計算表!E447</f>
@@ -36385,7 +36430,7 @@
       </c>
       <c r="G447">
         <f>計算表!G447</f>
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="H447">
         <f>計算表!H447</f>
@@ -36447,7 +36492,7 @@
       </c>
       <c r="D448" t="str">
         <f>計算表!D448</f>
-        <v>經驗加成%</v>
+        <v>護盾效率%</v>
       </c>
       <c r="E448" t="str">
         <f>計算表!E448</f>
@@ -36459,7 +36504,7 @@
       </c>
       <c r="G448">
         <f>計算表!G448</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H448">
         <f>計算表!H448</f>
@@ -36521,7 +36566,7 @@
       </c>
       <c r="D449" t="str">
         <f>計算表!D449</f>
-        <v>金幣加成%</v>
+        <v>物理抗性%</v>
       </c>
       <c r="E449" t="str">
         <f>計算表!E449</f>
@@ -36533,7 +36578,7 @@
       </c>
       <c r="G449">
         <f>計算表!G449</f>
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="H449">
         <f>計算表!H449</f>
@@ -36595,7 +36640,7 @@
       </c>
       <c r="D450" t="str">
         <f>計算表!D450</f>
-        <v>幸運值</v>
+        <v>魔法抗性%</v>
       </c>
       <c r="E450" t="str">
         <f>計算表!E450</f>
@@ -36607,7 +36652,7 @@
       </c>
       <c r="G450">
         <f>計算表!G450</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H450">
         <f>計算表!H450</f>
@@ -36669,7 +36714,7 @@
       </c>
       <c r="D451" t="str">
         <f>計算表!D451</f>
-        <v>負重上限</v>
+        <v>火焰抗性%</v>
       </c>
       <c r="E451" t="str">
         <f>計算表!E451</f>
@@ -36743,7 +36788,7 @@
       </c>
       <c r="D452" t="str">
         <f>計算表!D452</f>
-        <v>強化成功率%</v>
+        <v>冰霜抗性%</v>
       </c>
       <c r="E452" t="str">
         <f>計算表!E452</f>
@@ -36817,7 +36862,7 @@
       </c>
       <c r="D453" t="str">
         <f>計算表!D453</f>
-        <v>分解高產率%</v>
+        <v>雷電抗性%</v>
       </c>
       <c r="E453" t="str">
         <f>計算表!E453</f>
@@ -36891,7 +36936,7 @@
       </c>
       <c r="D454" t="str">
         <f>計算表!D454</f>
-        <v>合成變異率%</v>
+        <v>劇毒抗性%</v>
       </c>
       <c r="E454" t="str">
         <f>計算表!E454</f>
@@ -36903,7 +36948,7 @@
       </c>
       <c r="G454">
         <f>計算表!G454</f>
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="H454">
         <f>計算表!H454</f>
@@ -36965,7 +37010,7 @@
       </c>
       <c r="D455" t="str">
         <f>計算表!D455</f>
-        <v>狂暴閾值+</v>
+        <v>聖光抗性%</v>
       </c>
       <c r="E455" t="str">
         <f>計算表!E455</f>
@@ -36977,7 +37022,7 @@
       </c>
       <c r="G455">
         <f>計算表!G455</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H455">
         <f>計算表!H455</f>
@@ -37039,7 +37084,7 @@
       </c>
       <c r="D456" t="str">
         <f>計算表!D456</f>
-        <v>詞條上限率%</v>
+        <v>暗影抗性%</v>
       </c>
       <c r="E456" t="str">
         <f>計算表!E456</f>
@@ -37051,7 +37096,7 @@
       </c>
       <c r="G456">
         <f>計算表!G456</f>
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="H456">
         <f>計算表!H456</f>
@@ -37113,7 +37158,7 @@
       </c>
       <c r="D457" t="str">
         <f>計算表!D457</f>
-        <v>寶石鑲嵌效率%</v>
+        <v>控制時間縮減%</v>
       </c>
       <c r="E457" t="str">
         <f>計算表!E457</f>
@@ -37125,7 +37170,7 @@
       </c>
       <c r="G457">
         <f>計算表!G457</f>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="H457">
         <f>計算表!H457</f>
@@ -37173,40 +37218,892 @@
       </c>
     </row>
     <row r="458" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B458" s="2"/>
+      <c r="A458">
+        <f>計算表!A458</f>
+        <v>457</v>
+      </c>
+      <c r="B458" s="2">
+        <f>計算表!B458</f>
+        <v>0</v>
+      </c>
+      <c r="C458" t="str">
+        <f>計算表!C458</f>
+        <v>表-戰力權重</v>
+      </c>
+      <c r="D458" t="str">
+        <f>計算表!D458</f>
+        <v>移動速度%</v>
+      </c>
+      <c r="E458" t="str">
+        <f>計算表!E458</f>
+        <v>評分權重 = a</v>
+      </c>
+      <c r="F458" t="str">
+        <f>計算表!F458</f>
+        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+      </c>
+      <c r="G458">
+        <f>計算表!G458</f>
+        <v>1.5</v>
+      </c>
+      <c r="H458">
+        <f>計算表!H458</f>
+        <v>0</v>
+      </c>
+      <c r="I458">
+        <f>計算表!I458</f>
+        <v>0</v>
+      </c>
+      <c r="J458">
+        <f>計算表!J458</f>
+        <v>0</v>
+      </c>
+      <c r="K458">
+        <f>計算表!K458</f>
+        <v>0</v>
+      </c>
+      <c r="L458">
+        <f>計算表!L458</f>
+        <v>0</v>
+      </c>
+      <c r="M458">
+        <f>計算表!M458</f>
+        <v>0</v>
+      </c>
+      <c r="N458">
+        <f>計算表!N458</f>
+        <v>0</v>
+      </c>
+      <c r="O458">
+        <f>計算表!O458</f>
+        <v>0</v>
+      </c>
+      <c r="P458">
+        <f>計算表!P458</f>
+        <v>0</v>
+      </c>
+      <c r="Q458">
+        <f>計算表!Q458</f>
+        <v>0</v>
+      </c>
+      <c r="R458">
+        <f>計算表!R458</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="459" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B459" s="2"/>
+      <c r="A459">
+        <f>計算表!A459</f>
+        <v>458</v>
+      </c>
+      <c r="B459" s="2">
+        <f>計算表!B459</f>
+        <v>0</v>
+      </c>
+      <c r="C459" t="str">
+        <f>計算表!C459</f>
+        <v>表-戰力權重</v>
+      </c>
+      <c r="D459" t="str">
+        <f>計算表!D459</f>
+        <v>掉寶率%</v>
+      </c>
+      <c r="E459" t="str">
+        <f>計算表!E459</f>
+        <v>評分權重 = a</v>
+      </c>
+      <c r="F459" t="str">
+        <f>計算表!F459</f>
+        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+      </c>
+      <c r="G459">
+        <f>計算表!G459</f>
+        <v>0.8</v>
+      </c>
+      <c r="H459">
+        <f>計算表!H459</f>
+        <v>0</v>
+      </c>
+      <c r="I459">
+        <f>計算表!I459</f>
+        <v>0</v>
+      </c>
+      <c r="J459">
+        <f>計算表!J459</f>
+        <v>0</v>
+      </c>
+      <c r="K459">
+        <f>計算表!K459</f>
+        <v>0</v>
+      </c>
+      <c r="L459">
+        <f>計算表!L459</f>
+        <v>0</v>
+      </c>
+      <c r="M459">
+        <f>計算表!M459</f>
+        <v>0</v>
+      </c>
+      <c r="N459">
+        <f>計算表!N459</f>
+        <v>0</v>
+      </c>
+      <c r="O459">
+        <f>計算表!O459</f>
+        <v>0</v>
+      </c>
+      <c r="P459">
+        <f>計算表!P459</f>
+        <v>0</v>
+      </c>
+      <c r="Q459">
+        <f>計算表!Q459</f>
+        <v>0</v>
+      </c>
+      <c r="R459">
+        <f>計算表!R459</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="460" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B460" s="2"/>
+      <c r="A460">
+        <f>計算表!A460</f>
+        <v>459</v>
+      </c>
+      <c r="B460" s="2">
+        <f>計算表!B460</f>
+        <v>0</v>
+      </c>
+      <c r="C460" t="str">
+        <f>計算表!C460</f>
+        <v>表-戰力權重</v>
+      </c>
+      <c r="D460" t="str">
+        <f>計算表!D460</f>
+        <v>經驗加成%</v>
+      </c>
+      <c r="E460" t="str">
+        <f>計算表!E460</f>
+        <v>評分權重 = a</v>
+      </c>
+      <c r="F460" t="str">
+        <f>計算表!F460</f>
+        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+      </c>
+      <c r="G460">
+        <f>計算表!G460</f>
+        <v>0.8</v>
+      </c>
+      <c r="H460">
+        <f>計算表!H460</f>
+        <v>0</v>
+      </c>
+      <c r="I460">
+        <f>計算表!I460</f>
+        <v>0</v>
+      </c>
+      <c r="J460">
+        <f>計算表!J460</f>
+        <v>0</v>
+      </c>
+      <c r="K460">
+        <f>計算表!K460</f>
+        <v>0</v>
+      </c>
+      <c r="L460">
+        <f>計算表!L460</f>
+        <v>0</v>
+      </c>
+      <c r="M460">
+        <f>計算表!M460</f>
+        <v>0</v>
+      </c>
+      <c r="N460">
+        <f>計算表!N460</f>
+        <v>0</v>
+      </c>
+      <c r="O460">
+        <f>計算表!O460</f>
+        <v>0</v>
+      </c>
+      <c r="P460">
+        <f>計算表!P460</f>
+        <v>0</v>
+      </c>
+      <c r="Q460">
+        <f>計算表!Q460</f>
+        <v>0</v>
+      </c>
+      <c r="R460">
+        <f>計算表!R460</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="461" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B461" s="2"/>
+      <c r="A461">
+        <f>計算表!A461</f>
+        <v>460</v>
+      </c>
+      <c r="B461" s="2">
+        <f>計算表!B461</f>
+        <v>0</v>
+      </c>
+      <c r="C461" t="str">
+        <f>計算表!C461</f>
+        <v>表-戰力權重</v>
+      </c>
+      <c r="D461" t="str">
+        <f>計算表!D461</f>
+        <v>金幣加成%</v>
+      </c>
+      <c r="E461" t="str">
+        <f>計算表!E461</f>
+        <v>評分權重 = a</v>
+      </c>
+      <c r="F461" t="str">
+        <f>計算表!F461</f>
+        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+      </c>
+      <c r="G461">
+        <f>計算表!G461</f>
+        <v>0.8</v>
+      </c>
+      <c r="H461">
+        <f>計算表!H461</f>
+        <v>0</v>
+      </c>
+      <c r="I461">
+        <f>計算表!I461</f>
+        <v>0</v>
+      </c>
+      <c r="J461">
+        <f>計算表!J461</f>
+        <v>0</v>
+      </c>
+      <c r="K461">
+        <f>計算表!K461</f>
+        <v>0</v>
+      </c>
+      <c r="L461">
+        <f>計算表!L461</f>
+        <v>0</v>
+      </c>
+      <c r="M461">
+        <f>計算表!M461</f>
+        <v>0</v>
+      </c>
+      <c r="N461">
+        <f>計算表!N461</f>
+        <v>0</v>
+      </c>
+      <c r="O461">
+        <f>計算表!O461</f>
+        <v>0</v>
+      </c>
+      <c r="P461">
+        <f>計算表!P461</f>
+        <v>0</v>
+      </c>
+      <c r="Q461">
+        <f>計算表!Q461</f>
+        <v>0</v>
+      </c>
+      <c r="R461">
+        <f>計算表!R461</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="462" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B462" s="2"/>
+      <c r="A462">
+        <f>計算表!A462</f>
+        <v>461</v>
+      </c>
+      <c r="B462" s="2">
+        <f>計算表!B462</f>
+        <v>0</v>
+      </c>
+      <c r="C462" t="str">
+        <f>計算表!C462</f>
+        <v>表-戰力權重</v>
+      </c>
+      <c r="D462" t="str">
+        <f>計算表!D462</f>
+        <v>幸運值</v>
+      </c>
+      <c r="E462" t="str">
+        <f>計算表!E462</f>
+        <v>評分權重 = a</v>
+      </c>
+      <c r="F462" t="str">
+        <f>計算表!F462</f>
+        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+      </c>
+      <c r="G462">
+        <f>計算表!G462</f>
+        <v>1.5</v>
+      </c>
+      <c r="H462">
+        <f>計算表!H462</f>
+        <v>0</v>
+      </c>
+      <c r="I462">
+        <f>計算表!I462</f>
+        <v>0</v>
+      </c>
+      <c r="J462">
+        <f>計算表!J462</f>
+        <v>0</v>
+      </c>
+      <c r="K462">
+        <f>計算表!K462</f>
+        <v>0</v>
+      </c>
+      <c r="L462">
+        <f>計算表!L462</f>
+        <v>0</v>
+      </c>
+      <c r="M462">
+        <f>計算表!M462</f>
+        <v>0</v>
+      </c>
+      <c r="N462">
+        <f>計算表!N462</f>
+        <v>0</v>
+      </c>
+      <c r="O462">
+        <f>計算表!O462</f>
+        <v>0</v>
+      </c>
+      <c r="P462">
+        <f>計算表!P462</f>
+        <v>0</v>
+      </c>
+      <c r="Q462">
+        <f>計算表!Q462</f>
+        <v>0</v>
+      </c>
+      <c r="R462">
+        <f>計算表!R462</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="463" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B463" s="2"/>
+      <c r="A463">
+        <f>計算表!A463</f>
+        <v>462</v>
+      </c>
+      <c r="B463" s="2">
+        <f>計算表!B463</f>
+        <v>0</v>
+      </c>
+      <c r="C463" t="str">
+        <f>計算表!C463</f>
+        <v>表-戰力權重</v>
+      </c>
+      <c r="D463" t="str">
+        <f>計算表!D463</f>
+        <v>負重上限</v>
+      </c>
+      <c r="E463" t="str">
+        <f>計算表!E463</f>
+        <v>評分權重 = a</v>
+      </c>
+      <c r="F463" t="str">
+        <f>計算表!F463</f>
+        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+      </c>
+      <c r="G463">
+        <f>計算表!G463</f>
+        <v>0.8</v>
+      </c>
+      <c r="H463">
+        <f>計算表!H463</f>
+        <v>0</v>
+      </c>
+      <c r="I463">
+        <f>計算表!I463</f>
+        <v>0</v>
+      </c>
+      <c r="J463">
+        <f>計算表!J463</f>
+        <v>0</v>
+      </c>
+      <c r="K463">
+        <f>計算表!K463</f>
+        <v>0</v>
+      </c>
+      <c r="L463">
+        <f>計算表!L463</f>
+        <v>0</v>
+      </c>
+      <c r="M463">
+        <f>計算表!M463</f>
+        <v>0</v>
+      </c>
+      <c r="N463">
+        <f>計算表!N463</f>
+        <v>0</v>
+      </c>
+      <c r="O463">
+        <f>計算表!O463</f>
+        <v>0</v>
+      </c>
+      <c r="P463">
+        <f>計算表!P463</f>
+        <v>0</v>
+      </c>
+      <c r="Q463">
+        <f>計算表!Q463</f>
+        <v>0</v>
+      </c>
+      <c r="R463">
+        <f>計算表!R463</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="464" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B464" s="2"/>
-    </row>
-    <row r="465" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B465" s="2"/>
-    </row>
-    <row r="466" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B466" s="2"/>
-    </row>
-    <row r="467" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B467" s="2"/>
-    </row>
-    <row r="468" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B468" s="2"/>
-    </row>
-    <row r="469" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B469" s="2"/>
+      <c r="A464">
+        <f>計算表!A464</f>
+        <v>463</v>
+      </c>
+      <c r="B464" s="2">
+        <f>計算表!B464</f>
+        <v>0</v>
+      </c>
+      <c r="C464" t="str">
+        <f>計算表!C464</f>
+        <v>表-戰力權重</v>
+      </c>
+      <c r="D464" t="str">
+        <f>計算表!D464</f>
+        <v>強化成功率%</v>
+      </c>
+      <c r="E464" t="str">
+        <f>計算表!E464</f>
+        <v>評分權重 = a</v>
+      </c>
+      <c r="F464" t="str">
+        <f>計算表!F464</f>
+        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+      </c>
+      <c r="G464">
+        <f>計算表!G464</f>
+        <v>0.8</v>
+      </c>
+      <c r="H464">
+        <f>計算表!H464</f>
+        <v>0</v>
+      </c>
+      <c r="I464">
+        <f>計算表!I464</f>
+        <v>0</v>
+      </c>
+      <c r="J464">
+        <f>計算表!J464</f>
+        <v>0</v>
+      </c>
+      <c r="K464">
+        <f>計算表!K464</f>
+        <v>0</v>
+      </c>
+      <c r="L464">
+        <f>計算表!L464</f>
+        <v>0</v>
+      </c>
+      <c r="M464">
+        <f>計算表!M464</f>
+        <v>0</v>
+      </c>
+      <c r="N464">
+        <f>計算表!N464</f>
+        <v>0</v>
+      </c>
+      <c r="O464">
+        <f>計算表!O464</f>
+        <v>0</v>
+      </c>
+      <c r="P464">
+        <f>計算表!P464</f>
+        <v>0</v>
+      </c>
+      <c r="Q464">
+        <f>計算表!Q464</f>
+        <v>0</v>
+      </c>
+      <c r="R464">
+        <f>計算表!R464</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A465">
+        <f>計算表!A465</f>
+        <v>464</v>
+      </c>
+      <c r="B465" s="2">
+        <f>計算表!B465</f>
+        <v>0</v>
+      </c>
+      <c r="C465" t="str">
+        <f>計算表!C465</f>
+        <v>表-戰力權重</v>
+      </c>
+      <c r="D465" t="str">
+        <f>計算表!D465</f>
+        <v>分解高產率%</v>
+      </c>
+      <c r="E465" t="str">
+        <f>計算表!E465</f>
+        <v>評分權重 = a</v>
+      </c>
+      <c r="F465" t="str">
+        <f>計算表!F465</f>
+        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+      </c>
+      <c r="G465">
+        <f>計算表!G465</f>
+        <v>0.8</v>
+      </c>
+      <c r="H465">
+        <f>計算表!H465</f>
+        <v>0</v>
+      </c>
+      <c r="I465">
+        <f>計算表!I465</f>
+        <v>0</v>
+      </c>
+      <c r="J465">
+        <f>計算表!J465</f>
+        <v>0</v>
+      </c>
+      <c r="K465">
+        <f>計算表!K465</f>
+        <v>0</v>
+      </c>
+      <c r="L465">
+        <f>計算表!L465</f>
+        <v>0</v>
+      </c>
+      <c r="M465">
+        <f>計算表!M465</f>
+        <v>0</v>
+      </c>
+      <c r="N465">
+        <f>計算表!N465</f>
+        <v>0</v>
+      </c>
+      <c r="O465">
+        <f>計算表!O465</f>
+        <v>0</v>
+      </c>
+      <c r="P465">
+        <f>計算表!P465</f>
+        <v>0</v>
+      </c>
+      <c r="Q465">
+        <f>計算表!Q465</f>
+        <v>0</v>
+      </c>
+      <c r="R465">
+        <f>計算表!R465</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A466">
+        <f>計算表!A466</f>
+        <v>465</v>
+      </c>
+      <c r="B466" s="2">
+        <f>計算表!B466</f>
+        <v>0</v>
+      </c>
+      <c r="C466" t="str">
+        <f>計算表!C466</f>
+        <v>表-戰力權重</v>
+      </c>
+      <c r="D466" t="str">
+        <f>計算表!D466</f>
+        <v>合成變異率%</v>
+      </c>
+      <c r="E466" t="str">
+        <f>計算表!E466</f>
+        <v>評分權重 = a</v>
+      </c>
+      <c r="F466" t="str">
+        <f>計算表!F466</f>
+        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+      </c>
+      <c r="G466">
+        <f>計算表!G466</f>
+        <v>1.2</v>
+      </c>
+      <c r="H466">
+        <f>計算表!H466</f>
+        <v>0</v>
+      </c>
+      <c r="I466">
+        <f>計算表!I466</f>
+        <v>0</v>
+      </c>
+      <c r="J466">
+        <f>計算表!J466</f>
+        <v>0</v>
+      </c>
+      <c r="K466">
+        <f>計算表!K466</f>
+        <v>0</v>
+      </c>
+      <c r="L466">
+        <f>計算表!L466</f>
+        <v>0</v>
+      </c>
+      <c r="M466">
+        <f>計算表!M466</f>
+        <v>0</v>
+      </c>
+      <c r="N466">
+        <f>計算表!N466</f>
+        <v>0</v>
+      </c>
+      <c r="O466">
+        <f>計算表!O466</f>
+        <v>0</v>
+      </c>
+      <c r="P466">
+        <f>計算表!P466</f>
+        <v>0</v>
+      </c>
+      <c r="Q466">
+        <f>計算表!Q466</f>
+        <v>0</v>
+      </c>
+      <c r="R466">
+        <f>計算表!R466</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A467">
+        <f>計算表!A467</f>
+        <v>466</v>
+      </c>
+      <c r="B467" s="2">
+        <f>計算表!B467</f>
+        <v>0</v>
+      </c>
+      <c r="C467" t="str">
+        <f>計算表!C467</f>
+        <v>表-戰力權重</v>
+      </c>
+      <c r="D467" t="str">
+        <f>計算表!D467</f>
+        <v>狂暴閾值+</v>
+      </c>
+      <c r="E467" t="str">
+        <f>計算表!E467</f>
+        <v>評分權重 = a</v>
+      </c>
+      <c r="F467" t="str">
+        <f>計算表!F467</f>
+        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+      </c>
+      <c r="G467">
+        <f>計算表!G467</f>
+        <v>1</v>
+      </c>
+      <c r="H467">
+        <f>計算表!H467</f>
+        <v>0</v>
+      </c>
+      <c r="I467">
+        <f>計算表!I467</f>
+        <v>0</v>
+      </c>
+      <c r="J467">
+        <f>計算表!J467</f>
+        <v>0</v>
+      </c>
+      <c r="K467">
+        <f>計算表!K467</f>
+        <v>0</v>
+      </c>
+      <c r="L467">
+        <f>計算表!L467</f>
+        <v>0</v>
+      </c>
+      <c r="M467">
+        <f>計算表!M467</f>
+        <v>0</v>
+      </c>
+      <c r="N467">
+        <f>計算表!N467</f>
+        <v>0</v>
+      </c>
+      <c r="O467">
+        <f>計算表!O467</f>
+        <v>0</v>
+      </c>
+      <c r="P467">
+        <f>計算表!P467</f>
+        <v>0</v>
+      </c>
+      <c r="Q467">
+        <f>計算表!Q467</f>
+        <v>0</v>
+      </c>
+      <c r="R467">
+        <f>計算表!R467</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A468">
+        <f>計算表!A468</f>
+        <v>467</v>
+      </c>
+      <c r="B468" s="2">
+        <f>計算表!B468</f>
+        <v>0</v>
+      </c>
+      <c r="C468" t="str">
+        <f>計算表!C468</f>
+        <v>表-戰力權重</v>
+      </c>
+      <c r="D468" t="str">
+        <f>計算表!D468</f>
+        <v>詞條上限率%</v>
+      </c>
+      <c r="E468" t="str">
+        <f>計算表!E468</f>
+        <v>評分權重 = a</v>
+      </c>
+      <c r="F468" t="str">
+        <f>計算表!F468</f>
+        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+      </c>
+      <c r="G468">
+        <f>計算表!G468</f>
+        <v>1.2</v>
+      </c>
+      <c r="H468">
+        <f>計算表!H468</f>
+        <v>0</v>
+      </c>
+      <c r="I468">
+        <f>計算表!I468</f>
+        <v>0</v>
+      </c>
+      <c r="J468">
+        <f>計算表!J468</f>
+        <v>0</v>
+      </c>
+      <c r="K468">
+        <f>計算表!K468</f>
+        <v>0</v>
+      </c>
+      <c r="L468">
+        <f>計算表!L468</f>
+        <v>0</v>
+      </c>
+      <c r="M468">
+        <f>計算表!M468</f>
+        <v>0</v>
+      </c>
+      <c r="N468">
+        <f>計算表!N468</f>
+        <v>0</v>
+      </c>
+      <c r="O468">
+        <f>計算表!O468</f>
+        <v>0</v>
+      </c>
+      <c r="P468">
+        <f>計算表!P468</f>
+        <v>0</v>
+      </c>
+      <c r="Q468">
+        <f>計算表!Q468</f>
+        <v>0</v>
+      </c>
+      <c r="R468">
+        <f>計算表!R468</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A469">
+        <f>計算表!A469</f>
+        <v>468</v>
+      </c>
+      <c r="B469" s="2">
+        <f>計算表!B469</f>
+        <v>0</v>
+      </c>
+      <c r="C469" t="str">
+        <f>計算表!C469</f>
+        <v>表-戰力權重</v>
+      </c>
+      <c r="D469" t="str">
+        <f>計算表!D469</f>
+        <v>寶石鑲嵌效率%</v>
+      </c>
+      <c r="E469" t="str">
+        <f>計算表!E469</f>
+        <v>評分權重 = a</v>
+      </c>
+      <c r="F469" t="str">
+        <f>計算表!F469</f>
+        <v>「戰力評分」中該詞條/對應寶石屬性的權重；未列出者以 1 計。</v>
+      </c>
+      <c r="G469">
+        <f>計算表!G469</f>
+        <v>1</v>
+      </c>
+      <c r="H469">
+        <f>計算表!H469</f>
+        <v>0</v>
+      </c>
+      <c r="I469">
+        <f>計算表!I469</f>
+        <v>0</v>
+      </c>
+      <c r="J469">
+        <f>計算表!J469</f>
+        <v>0</v>
+      </c>
+      <c r="K469">
+        <f>計算表!K469</f>
+        <v>0</v>
+      </c>
+      <c r="L469">
+        <f>計算表!L469</f>
+        <v>0</v>
+      </c>
+      <c r="M469">
+        <f>計算表!M469</f>
+        <v>0</v>
+      </c>
+      <c r="N469">
+        <f>計算表!N469</f>
+        <v>0</v>
+      </c>
+      <c r="O469">
+        <f>計算表!O469</f>
+        <v>0</v>
+      </c>
+      <c r="P469">
+        <f>計算表!P469</f>
+        <v>0</v>
+      </c>
+      <c r="Q469">
+        <f>計算表!Q469</f>
+        <v>0</v>
+      </c>
+      <c r="R469">
+        <f>計算表!R469</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -37216,7 +38113,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R457"/>
+  <dimension ref="A1:R469"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="3" customWidth="1"/>
@@ -39731,7 +40628,7 @@
         <v>100000</v>
       </c>
       <c r="H97" s="3">
-        <v>2.6</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="98" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -40910,10 +41807,10 @@
         <v>5</v>
       </c>
       <c r="H139" s="3">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I139" s="3">
-        <v>150</v>
+        <v>49</v>
       </c>
       <c r="J139" s="3">
         <v>0.1</v>
@@ -40937,16 +41834,16 @@
         <v>345</v>
       </c>
       <c r="G140" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H140" s="3">
         <v>2</v>
       </c>
       <c r="I140" s="3">
-        <v>250</v>
+        <v>49</v>
       </c>
       <c r="J140" s="3">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
@@ -41825,7 +42722,7 @@
         <v>0</v>
       </c>
       <c r="J171" s="3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="K171" s="3">
         <v>0.5</v>
@@ -44332,7 +45229,7 @@
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260" s="3">
-        <f t="shared" ref="A260:A323" si="5">A259+1</f>
+        <f t="shared" ref="A260:A314" si="5">A259+1</f>
         <v>259</v>
       </c>
       <c r="C260" s="3" t="s">
@@ -46027,32 +46924,32 @@
     </row>
     <row r="315" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A315" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="A315:A346" si="6">A314+1</f>
         <v>314</v>
       </c>
       <c r="C315" s="3" t="s">
         <v>776</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>810</v>
+        <v>1000</v>
       </c>
       <c r="E315" s="3" t="s">
         <v>777</v>
       </c>
       <c r="F315" s="3" t="s">
-        <v>778</v>
+        <v>1001</v>
       </c>
       <c r="G315" s="3">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="H315" s="3">
-        <v>0.02</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I315" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J315" s="3" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="K315" s="3" t="s">
         <v>781</v>
@@ -46060,32 +46957,32 @@
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A316" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>315</v>
       </c>
       <c r="C316" s="3" t="s">
         <v>776</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>811</v>
+        <v>1002</v>
       </c>
       <c r="E316" s="3" t="s">
         <v>777</v>
       </c>
       <c r="F316" s="3" t="s">
-        <v>778</v>
+        <v>1001</v>
       </c>
       <c r="G316" s="3">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="H316" s="3">
-        <v>1.2E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I316" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J316" s="3" t="s">
-        <v>298</v>
+        <v>770</v>
       </c>
       <c r="K316" s="3" t="s">
         <v>781</v>
@@ -46093,32 +46990,32 @@
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A317" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>316</v>
       </c>
       <c r="C317" s="3" t="s">
         <v>776</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>812</v>
+        <v>1003</v>
       </c>
       <c r="E317" s="3" t="s">
         <v>777</v>
       </c>
       <c r="F317" s="3" t="s">
-        <v>778</v>
+        <v>1001</v>
       </c>
       <c r="G317" s="3">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="H317" s="3">
-        <v>0.02</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I317" s="3">
         <v>3</v>
       </c>
       <c r="J317" s="3" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="K317" s="3" t="s">
         <v>781</v>
@@ -46126,32 +47023,32 @@
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A318" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>317</v>
       </c>
       <c r="C318" s="3" t="s">
         <v>776</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>813</v>
+        <v>1004</v>
       </c>
       <c r="E318" s="3" t="s">
         <v>777</v>
       </c>
       <c r="F318" s="3" t="s">
-        <v>778</v>
+        <v>1001</v>
       </c>
       <c r="G318" s="3">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="H318" s="3">
-        <v>0.01</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I318" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J318" s="3" t="s">
-        <v>298</v>
+        <v>770</v>
       </c>
       <c r="K318" s="3" t="s">
         <v>781</v>
@@ -46159,32 +47056,32 @@
     </row>
     <row r="319" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A319" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>318</v>
       </c>
       <c r="C319" s="3" t="s">
         <v>776</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>814</v>
+        <v>1005</v>
       </c>
       <c r="E319" s="3" t="s">
         <v>777</v>
       </c>
       <c r="F319" s="3" t="s">
-        <v>778</v>
+        <v>1001</v>
       </c>
       <c r="G319" s="3">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="H319" s="3">
-        <v>0.02</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I319" s="3">
         <v>3</v>
       </c>
       <c r="J319" s="3" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="K319" s="3" t="s">
         <v>781</v>
@@ -46192,26 +47089,26 @@
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A320" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>319</v>
       </c>
       <c r="C320" s="3" t="s">
         <v>776</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>815</v>
+        <v>1006</v>
       </c>
       <c r="E320" s="3" t="s">
         <v>777</v>
       </c>
       <c r="F320" s="3" t="s">
-        <v>778</v>
+        <v>1001</v>
       </c>
       <c r="G320" s="3">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="H320" s="3">
-        <v>2.5000000000000001E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="I320" s="3">
         <v>3</v>
@@ -46225,14 +47122,14 @@
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A321" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>320</v>
       </c>
       <c r="C321" s="3" t="s">
         <v>776</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="E321" s="3" t="s">
         <v>777</v>
@@ -46241,16 +47138,16 @@
         <v>778</v>
       </c>
       <c r="G321" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H321" s="3">
-        <v>8.0000000000000002E-3</v>
+        <v>0.02</v>
       </c>
       <c r="I321" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J321" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="K321" s="3" t="s">
         <v>781</v>
@@ -46258,14 +47155,14 @@
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A322" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>321</v>
       </c>
       <c r="C322" s="3" t="s">
         <v>776</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="E322" s="3" t="s">
         <v>777</v>
@@ -46274,16 +47171,16 @@
         <v>778</v>
       </c>
       <c r="G322" s="3">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H322" s="3">
-        <v>8.0000000000000002E-3</v>
+        <v>1.2E-2</v>
       </c>
       <c r="I322" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J322" s="3" t="s">
-        <v>770</v>
+        <v>298</v>
       </c>
       <c r="K322" s="3" t="s">
         <v>781</v>
@@ -46291,14 +47188,14 @@
     </row>
     <row r="323" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A323" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>322</v>
       </c>
       <c r="C323" s="3" t="s">
         <v>776</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="E323" s="3" t="s">
         <v>777</v>
@@ -46316,7 +47213,7 @@
         <v>3</v>
       </c>
       <c r="J323" s="3" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="K323" s="3" t="s">
         <v>781</v>
@@ -46324,14 +47221,14 @@
     </row>
     <row r="324" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A324" s="3">
-        <f t="shared" ref="A324:A387" si="6">A323+1</f>
+        <f t="shared" si="6"/>
         <v>323</v>
       </c>
       <c r="C324" s="3" t="s">
         <v>776</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="E324" s="3" t="s">
         <v>777</v>
@@ -46340,16 +47237,16 @@
         <v>778</v>
       </c>
       <c r="G324" s="3">
+        <v>2</v>
+      </c>
+      <c r="H324" s="3">
+        <v>0.01</v>
+      </c>
+      <c r="I324" s="3">
         <v>4</v>
       </c>
-      <c r="H324" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="I324" s="3">
-        <v>3</v>
-      </c>
       <c r="J324" s="3" t="s">
-        <v>768</v>
+        <v>298</v>
       </c>
       <c r="K324" s="3" t="s">
         <v>781</v>
@@ -46364,7 +47261,7 @@
         <v>776</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="E325" s="3" t="s">
         <v>777</v>
@@ -46382,7 +47279,7 @@
         <v>3</v>
       </c>
       <c r="J325" s="3" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="K325" s="3" t="s">
         <v>781</v>
@@ -46397,7 +47294,7 @@
         <v>776</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="E326" s="3" t="s">
         <v>777</v>
@@ -46406,16 +47303,16 @@
         <v>778</v>
       </c>
       <c r="G326" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H326" s="3">
-        <v>0.02</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I326" s="3">
         <v>3</v>
       </c>
       <c r="J326" s="3" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="K326" s="3" t="s">
         <v>781</v>
@@ -46430,7 +47327,7 @@
         <v>776</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="E327" s="3" t="s">
         <v>777</v>
@@ -46439,16 +47336,16 @@
         <v>778</v>
       </c>
       <c r="G327" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H327" s="3">
-        <v>0.02</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="I327" s="3">
         <v>3</v>
       </c>
       <c r="J327" s="3" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="K327" s="3" t="s">
         <v>781</v>
@@ -46463,7 +47360,7 @@
         <v>776</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="E328" s="3" t="s">
         <v>777</v>
@@ -46472,16 +47369,16 @@
         <v>778</v>
       </c>
       <c r="G328" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H328" s="3">
-        <v>0.02</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="I328" s="3">
         <v>3</v>
       </c>
       <c r="J328" s="3" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="K328" s="3" t="s">
         <v>781</v>
@@ -46496,7 +47393,7 @@
         <v>776</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="E329" s="3" t="s">
         <v>777</v>
@@ -46514,7 +47411,7 @@
         <v>3</v>
       </c>
       <c r="J329" s="3" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="K329" s="3" t="s">
         <v>781</v>
@@ -46529,7 +47426,7 @@
         <v>776</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="E330" s="3" t="s">
         <v>777</v>
@@ -46538,16 +47435,16 @@
         <v>778</v>
       </c>
       <c r="G330" s="3">
+        <v>4</v>
+      </c>
+      <c r="H330" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="I330" s="3">
         <v>3</v>
       </c>
-      <c r="H330" s="3">
-        <v>1.2E-2</v>
-      </c>
-      <c r="I330" s="3">
-        <v>4</v>
-      </c>
       <c r="J330" s="3" t="s">
-        <v>298</v>
+        <v>768</v>
       </c>
       <c r="K330" s="3" t="s">
         <v>781</v>
@@ -46562,7 +47459,7 @@
         <v>776</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="E331" s="3" t="s">
         <v>777</v>
@@ -46571,16 +47468,16 @@
         <v>778</v>
       </c>
       <c r="G331" s="3">
+        <v>4</v>
+      </c>
+      <c r="H331" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="I331" s="3">
         <v>3</v>
       </c>
-      <c r="H331" s="3">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="I331" s="3">
-        <v>4</v>
-      </c>
       <c r="J331" s="3" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="K331" s="3" t="s">
         <v>781</v>
@@ -46595,7 +47492,7 @@
         <v>776</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="E332" s="3" t="s">
         <v>777</v>
@@ -46610,13 +47507,13 @@
         <v>0.02</v>
       </c>
       <c r="I332" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J332" s="3" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="K332" s="3" t="s">
-        <v>828</v>
+        <v>781</v>
       </c>
     </row>
     <row r="333" spans="1:11" x14ac:dyDescent="0.25">
@@ -46628,7 +47525,7 @@
         <v>776</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
       <c r="E333" s="3" t="s">
         <v>777</v>
@@ -46637,19 +47534,19 @@
         <v>778</v>
       </c>
       <c r="G333" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H333" s="3">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
       <c r="I333" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J333" s="3" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="K333" s="3" t="s">
-        <v>828</v>
+        <v>781</v>
       </c>
     </row>
     <row r="334" spans="1:11" x14ac:dyDescent="0.25">
@@ -46661,7 +47558,7 @@
         <v>776</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
       <c r="E334" s="3" t="s">
         <v>777</v>
@@ -46670,19 +47567,19 @@
         <v>778</v>
       </c>
       <c r="G334" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H334" s="3">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="I334" s="3">
         <v>3</v>
       </c>
       <c r="J334" s="3" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="K334" s="3" t="s">
-        <v>831</v>
+        <v>781</v>
       </c>
     </row>
     <row r="335" spans="1:11" x14ac:dyDescent="0.25">
@@ -46694,7 +47591,7 @@
         <v>776</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>108</v>
+        <v>824</v>
       </c>
       <c r="E335" s="3" t="s">
         <v>777</v>
@@ -46703,19 +47600,19 @@
         <v>778</v>
       </c>
       <c r="G335" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H335" s="3">
-        <v>0.3</v>
+        <v>0.02</v>
       </c>
       <c r="I335" s="3">
         <v>3</v>
       </c>
       <c r="J335" s="3" t="s">
-        <v>298</v>
+        <v>770</v>
       </c>
       <c r="K335" s="3" t="s">
-        <v>831</v>
+        <v>781</v>
       </c>
     </row>
     <row r="336" spans="1:11" x14ac:dyDescent="0.25">
@@ -46727,7 +47624,7 @@
         <v>776</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="E336" s="3" t="s">
         <v>777</v>
@@ -46739,13 +47636,13 @@
         <v>3</v>
       </c>
       <c r="H336" s="3">
-        <v>1.4999999999999999E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="I336" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J336" s="3" t="s">
-        <v>770</v>
+        <v>298</v>
       </c>
       <c r="K336" s="3" t="s">
         <v>781</v>
@@ -46760,7 +47657,7 @@
         <v>776</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E337" s="3" t="s">
         <v>777</v>
@@ -46775,7 +47672,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="I337" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J337" s="3" t="s">
         <v>770</v>
@@ -46793,7 +47690,7 @@
         <v>776</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="E338" s="3" t="s">
         <v>777</v>
@@ -46802,19 +47699,19 @@
         <v>778</v>
       </c>
       <c r="G338" s="3">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="H338" s="3">
-        <v>1.2E-2</v>
+        <v>0.02</v>
       </c>
       <c r="I338" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J338" s="3" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="K338" s="3" t="s">
-        <v>781</v>
+        <v>828</v>
       </c>
     </row>
     <row r="339" spans="1:11" x14ac:dyDescent="0.25">
@@ -46826,7 +47723,7 @@
         <v>776</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="E339" s="3" t="s">
         <v>777</v>
@@ -46835,19 +47732,19 @@
         <v>778</v>
       </c>
       <c r="G339" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H339" s="3">
-        <v>0.08</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="I339" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J339" s="3" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="K339" s="3" t="s">
-        <v>779</v>
+        <v>828</v>
       </c>
     </row>
     <row r="340" spans="1:11" x14ac:dyDescent="0.25">
@@ -46859,7 +47756,7 @@
         <v>776</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="E340" s="3" t="s">
         <v>777</v>
@@ -46868,19 +47765,19 @@
         <v>778</v>
       </c>
       <c r="G340" s="3">
+        <v>2</v>
+      </c>
+      <c r="H340" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="I340" s="3">
         <v>3</v>
       </c>
-      <c r="H340" s="3">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="I340" s="3">
-        <v>2</v>
-      </c>
       <c r="J340" s="3" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="K340" s="3" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.25">
@@ -46892,7 +47789,7 @@
         <v>776</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>837</v>
+        <v>108</v>
       </c>
       <c r="E341" s="3" t="s">
         <v>777</v>
@@ -46901,19 +47798,19 @@
         <v>778</v>
       </c>
       <c r="G341" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H341" s="3">
-        <v>2.5000000000000001E-2</v>
+        <v>0.3</v>
       </c>
       <c r="I341" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J341" s="3" t="s">
-        <v>771</v>
+        <v>298</v>
       </c>
       <c r="K341" s="3" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.25">
@@ -46922,25 +47819,31 @@
         <v>341</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>838</v>
+        <v>776</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="E342" s="3" t="s">
-        <v>840</v>
+        <v>777</v>
       </c>
       <c r="F342" s="3" t="s">
-        <v>841</v>
+        <v>778</v>
       </c>
       <c r="G342" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H342" s="3">
-        <v>2</v>
-      </c>
-      <c r="I342" s="3" t="s">
-        <v>236</v>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I342" s="3">
+        <v>3</v>
+      </c>
+      <c r="J342" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="K342" s="3" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="343" spans="1:11" x14ac:dyDescent="0.25">
@@ -46949,25 +47852,31 @@
         <v>342</v>
       </c>
       <c r="C343" s="3" t="s">
-        <v>838</v>
+        <v>776</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>842</v>
+        <v>833</v>
       </c>
       <c r="E343" s="3" t="s">
-        <v>840</v>
+        <v>777</v>
       </c>
       <c r="F343" s="3" t="s">
-        <v>841</v>
+        <v>778</v>
       </c>
       <c r="G343" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H343" s="3">
-        <v>1</v>
-      </c>
-      <c r="I343" s="3" t="s">
-        <v>236</v>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I343" s="3">
+        <v>3</v>
+      </c>
+      <c r="J343" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="K343" s="3" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="344" spans="1:11" x14ac:dyDescent="0.25">
@@ -46976,25 +47885,31 @@
         <v>343</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>838</v>
+        <v>776</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
       <c r="E344" s="3" t="s">
-        <v>840</v>
+        <v>777</v>
       </c>
       <c r="F344" s="3" t="s">
-        <v>841</v>
+        <v>778</v>
       </c>
       <c r="G344" s="3">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="H344" s="3">
+        <v>1.2E-2</v>
+      </c>
+      <c r="I344" s="3">
         <v>2</v>
       </c>
-      <c r="I344" s="3">
-        <v>45</v>
+      <c r="J344" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="K344" s="3" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="345" spans="1:11" x14ac:dyDescent="0.25">
@@ -47003,25 +47918,31 @@
         <v>344</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>838</v>
+        <v>776</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>844</v>
+        <v>835</v>
       </c>
       <c r="E345" s="3" t="s">
-        <v>840</v>
+        <v>777</v>
       </c>
       <c r="F345" s="3" t="s">
-        <v>841</v>
+        <v>778</v>
       </c>
       <c r="G345" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H345" s="3">
-        <v>1.5</v>
+        <v>0.08</v>
       </c>
       <c r="I345" s="3">
-        <v>30</v>
+        <v>2</v>
+      </c>
+      <c r="J345" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="K345" s="3" t="s">
+        <v>779</v>
       </c>
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.25">
@@ -47030,64 +47951,76 @@
         <v>345</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>838</v>
+        <v>776</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>845</v>
+        <v>836</v>
       </c>
       <c r="E346" s="3" t="s">
-        <v>840</v>
+        <v>777</v>
       </c>
       <c r="F346" s="3" t="s">
-        <v>841</v>
+        <v>778</v>
       </c>
       <c r="G346" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H346" s="3">
-        <v>3</v>
-      </c>
-      <c r="I346" s="3" t="s">
-        <v>236</v>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I346" s="3">
+        <v>2</v>
+      </c>
+      <c r="J346" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="K346" s="3" t="s">
+        <v>828</v>
       </c>
     </row>
     <row r="347" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A347" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="A347:A378" si="7">A346+1</f>
         <v>346</v>
       </c>
       <c r="C347" s="3" t="s">
-        <v>838</v>
+        <v>776</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>846</v>
+        <v>837</v>
       </c>
       <c r="E347" s="3" t="s">
-        <v>840</v>
+        <v>777</v>
       </c>
       <c r="F347" s="3" t="s">
-        <v>841</v>
+        <v>778</v>
       </c>
       <c r="G347" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H347" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="I347" s="3" t="s">
-        <v>236</v>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="I347" s="3">
+        <v>2</v>
+      </c>
+      <c r="J347" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="K347" s="3" t="s">
+        <v>828</v>
       </c>
     </row>
     <row r="348" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A348" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>347</v>
       </c>
       <c r="C348" s="3" t="s">
         <v>838</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="E348" s="3" t="s">
         <v>840</v>
@@ -47096,10 +48029,10 @@
         <v>841</v>
       </c>
       <c r="G348" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H348" s="3">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I348" s="3" t="s">
         <v>236</v>
@@ -47107,209 +48040,245 @@
     </row>
     <row r="349" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A349" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>348</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>848</v>
+        <v>838</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>849</v>
+        <v>842</v>
       </c>
       <c r="E349" s="3" t="s">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="F349" s="3" t="s">
-        <v>851</v>
+        <v>841</v>
       </c>
       <c r="G349" s="3">
-        <v>25</v>
+        <v>5</v>
+      </c>
+      <c r="H349" s="3">
+        <v>1</v>
+      </c>
+      <c r="I349" s="3" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A350" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>349</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>848</v>
+        <v>838</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>852</v>
+        <v>843</v>
       </c>
       <c r="E350" s="3" t="s">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="F350" s="3" t="s">
-        <v>853</v>
+        <v>841</v>
       </c>
       <c r="G350" s="3">
-        <v>18</v>
+        <v>10</v>
+      </c>
+      <c r="H350" s="3">
+        <v>2</v>
+      </c>
+      <c r="I350" s="3">
+        <v>45</v>
       </c>
     </row>
     <row r="351" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A351" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>350</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>848</v>
+        <v>838</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>854</v>
+        <v>844</v>
       </c>
       <c r="E351" s="3" t="s">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="F351" s="3" t="s">
-        <v>855</v>
+        <v>841</v>
       </c>
       <c r="G351" s="3">
-        <v>15</v>
+        <v>6</v>
+      </c>
+      <c r="H351" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="I351" s="3">
+        <v>30</v>
       </c>
     </row>
     <row r="352" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A352" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>351</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>848</v>
+        <v>838</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>856</v>
+        <v>845</v>
       </c>
       <c r="E352" s="3" t="s">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="F352" s="3" t="s">
-        <v>857</v>
+        <v>841</v>
       </c>
       <c r="G352" s="3">
-        <v>30</v>
+        <v>12</v>
+      </c>
+      <c r="H352" s="3">
+        <v>3</v>
+      </c>
+      <c r="I352" s="3" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>352</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>848</v>
+        <v>838</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>858</v>
+        <v>846</v>
       </c>
       <c r="E353" s="3" t="s">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="F353" s="3" t="s">
-        <v>859</v>
+        <v>841</v>
       </c>
       <c r="G353" s="3">
-        <v>25</v>
+        <v>6</v>
+      </c>
+      <c r="H353" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="I353" s="3" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>353</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>848</v>
+        <v>838</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>860</v>
+        <v>847</v>
       </c>
       <c r="E354" s="3" t="s">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="F354" s="3" t="s">
-        <v>861</v>
+        <v>841</v>
       </c>
       <c r="G354" s="3">
-        <v>25</v>
+        <v>5</v>
+      </c>
+      <c r="H354" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="I354" s="3" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>354</v>
       </c>
       <c r="C355" s="3" t="s">
         <v>848</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
       <c r="E355" s="3" t="s">
         <v>850</v>
       </c>
       <c r="F355" s="3" t="s">
-        <v>863</v>
+        <v>851</v>
       </c>
       <c r="G355" s="3">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>355</v>
       </c>
       <c r="C356" s="3" t="s">
         <v>848</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>864</v>
+        <v>852</v>
       </c>
       <c r="E356" s="3" t="s">
         <v>850</v>
       </c>
       <c r="F356" s="3" t="s">
-        <v>865</v>
+        <v>853</v>
       </c>
       <c r="G356" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>356</v>
       </c>
       <c r="C357" s="3" t="s">
         <v>848</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>866</v>
+        <v>854</v>
       </c>
       <c r="E357" s="3" t="s">
         <v>850</v>
       </c>
       <c r="F357" s="3" t="s">
-        <v>867</v>
+        <v>855</v>
       </c>
       <c r="G357" s="3">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>357</v>
       </c>
       <c r="C358" s="3" t="s">
         <v>848</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>868</v>
+        <v>856</v>
       </c>
       <c r="E358" s="3" t="s">
         <v>850</v>
       </c>
       <c r="F358" s="3" t="s">
-        <v>869</v>
+        <v>857</v>
       </c>
       <c r="G358" s="3">
         <v>30</v>
@@ -47317,218 +48286,182 @@
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>358</v>
       </c>
       <c r="C359" s="3" t="s">
         <v>848</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>870</v>
+        <v>858</v>
       </c>
       <c r="E359" s="3" t="s">
         <v>850</v>
       </c>
       <c r="F359" s="3" t="s">
-        <v>871</v>
+        <v>859</v>
       </c>
       <c r="G359" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>359</v>
       </c>
       <c r="C360" s="3" t="s">
         <v>848</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>872</v>
+        <v>860</v>
       </c>
       <c r="E360" s="3" t="s">
         <v>850</v>
       </c>
       <c r="F360" s="3" t="s">
-        <v>873</v>
+        <v>861</v>
       </c>
       <c r="G360" s="3">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>360</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>874</v>
+        <v>848</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>875</v>
+        <v>862</v>
       </c>
       <c r="E361" s="3" t="s">
-        <v>876</v>
+        <v>850</v>
       </c>
       <c r="F361" s="3" t="s">
-        <v>877</v>
+        <v>863</v>
       </c>
       <c r="G361" s="3">
-        <v>6</v>
-      </c>
-      <c r="H361" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I361" s="3" t="s">
-        <v>779</v>
+        <v>12</v>
       </c>
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>361</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>874</v>
+        <v>848</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>878</v>
+        <v>864</v>
       </c>
       <c r="E362" s="3" t="s">
-        <v>876</v>
+        <v>850</v>
       </c>
       <c r="F362" s="3" t="s">
-        <v>877</v>
+        <v>865</v>
       </c>
       <c r="G362" s="3">
-        <v>6</v>
-      </c>
-      <c r="H362" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="I362" s="3" t="s">
-        <v>779</v>
+        <v>15</v>
       </c>
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>362</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>874</v>
+        <v>848</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>879</v>
+        <v>866</v>
       </c>
       <c r="E363" s="3" t="s">
-        <v>876</v>
+        <v>850</v>
       </c>
       <c r="F363" s="3" t="s">
-        <v>877</v>
+        <v>867</v>
       </c>
       <c r="G363" s="3">
-        <v>40</v>
-      </c>
-      <c r="H363" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="I363" s="3" t="s">
-        <v>779</v>
+        <v>8</v>
       </c>
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>363</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>874</v>
+        <v>848</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>880</v>
+        <v>868</v>
       </c>
       <c r="E364" s="3" t="s">
-        <v>876</v>
+        <v>850</v>
       </c>
       <c r="F364" s="3" t="s">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="G364" s="3">
-        <v>3</v>
-      </c>
-      <c r="H364" s="3" t="s">
-        <v>785</v>
-      </c>
-      <c r="I364" s="3" t="s">
-        <v>779</v>
+        <v>30</v>
       </c>
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>364</v>
       </c>
       <c r="C365" s="3" t="s">
-        <v>874</v>
+        <v>848</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>881</v>
+        <v>870</v>
       </c>
       <c r="E365" s="3" t="s">
-        <v>876</v>
+        <v>850</v>
       </c>
       <c r="F365" s="3" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="G365" s="3">
         <v>5</v>
       </c>
-      <c r="H365" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="I365" s="3" t="s">
-        <v>779</v>
-      </c>
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>365</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>874</v>
+        <v>848</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>882</v>
+        <v>872</v>
       </c>
       <c r="E366" s="3" t="s">
-        <v>876</v>
+        <v>850</v>
       </c>
       <c r="F366" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G366" s="3">
-        <v>5</v>
-      </c>
-      <c r="H366" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I366" s="3" t="s">
-        <v>779</v>
+        <v>35</v>
       </c>
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>366</v>
       </c>
       <c r="C367" s="3" t="s">
         <v>874</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>883</v>
+        <v>875</v>
       </c>
       <c r="E367" s="3" t="s">
         <v>876</v>
@@ -47537,25 +48470,25 @@
         <v>877</v>
       </c>
       <c r="G367" s="3">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="H367" s="3" t="s">
-        <v>797</v>
+        <v>87</v>
       </c>
       <c r="I367" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>367</v>
       </c>
       <c r="C368" s="3" t="s">
         <v>874</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="E368" s="3" t="s">
         <v>876</v>
@@ -47564,25 +48497,25 @@
         <v>877</v>
       </c>
       <c r="G368" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H368" s="3" t="s">
-        <v>798</v>
+        <v>88</v>
       </c>
       <c r="I368" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>368</v>
       </c>
       <c r="C369" s="3" t="s">
         <v>874</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="E369" s="3" t="s">
         <v>876</v>
@@ -47591,25 +48524,25 @@
         <v>877</v>
       </c>
       <c r="G369" s="3">
-        <v>1.5</v>
+        <v>40</v>
       </c>
       <c r="H369" s="3" t="s">
-        <v>796</v>
+        <v>783</v>
       </c>
       <c r="I369" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>369</v>
       </c>
       <c r="C370" s="3" t="s">
         <v>874</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="E370" s="3" t="s">
         <v>876</v>
@@ -47618,25 +48551,25 @@
         <v>877</v>
       </c>
       <c r="G370" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H370" s="3" t="s">
-        <v>804</v>
+        <v>785</v>
       </c>
       <c r="I370" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>370</v>
       </c>
       <c r="C371" s="3" t="s">
         <v>874</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="E371" s="3" t="s">
         <v>876</v>
@@ -47645,25 +48578,25 @@
         <v>877</v>
       </c>
       <c r="G371" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H371" s="3" t="s">
-        <v>813</v>
+        <v>89</v>
       </c>
       <c r="I371" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>371</v>
       </c>
       <c r="C372" s="3" t="s">
         <v>874</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="E372" s="3" t="s">
         <v>876</v>
@@ -47672,10 +48605,10 @@
         <v>877</v>
       </c>
       <c r="G372" s="3">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="H372" s="3" t="s">
-        <v>830</v>
+        <v>90</v>
       </c>
       <c r="I372" s="3" t="s">
         <v>779</v>
@@ -47683,14 +48616,14 @@
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>372</v>
       </c>
       <c r="C373" s="3" t="s">
         <v>874</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="E373" s="3" t="s">
         <v>876</v>
@@ -47702,7 +48635,7 @@
         <v>1.5</v>
       </c>
       <c r="H373" s="3" t="s">
-        <v>814</v>
+        <v>797</v>
       </c>
       <c r="I373" s="3" t="s">
         <v>781</v>
@@ -47710,14 +48643,14 @@
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>373</v>
       </c>
       <c r="C374" s="3" t="s">
         <v>874</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="E374" s="3" t="s">
         <v>876</v>
@@ -47726,10 +48659,10 @@
         <v>877</v>
       </c>
       <c r="G374" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H374" s="3" t="s">
-        <v>811</v>
+        <v>798</v>
       </c>
       <c r="I374" s="3" t="s">
         <v>781</v>
@@ -47737,14 +48670,14 @@
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>374</v>
       </c>
       <c r="C375" s="3" t="s">
         <v>874</v>
       </c>
       <c r="D375" s="3" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
       <c r="E375" s="3" t="s">
         <v>876</v>
@@ -47756,7 +48689,7 @@
         <v>1.5</v>
       </c>
       <c r="H375" s="3" t="s">
-        <v>812</v>
+        <v>796</v>
       </c>
       <c r="I375" s="3" t="s">
         <v>781</v>
@@ -47764,14 +48697,14 @@
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>375</v>
       </c>
       <c r="C376" s="3" t="s">
         <v>874</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="E376" s="3" t="s">
         <v>876</v>
@@ -47780,10 +48713,10 @@
         <v>877</v>
       </c>
       <c r="G376" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H376" s="3" t="s">
-        <v>815</v>
+        <v>804</v>
       </c>
       <c r="I376" s="3" t="s">
         <v>781</v>
@@ -47791,14 +48724,14 @@
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>376</v>
       </c>
       <c r="C377" s="3" t="s">
         <v>874</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="E377" s="3" t="s">
         <v>876</v>
@@ -47807,10 +48740,10 @@
         <v>877</v>
       </c>
       <c r="G377" s="3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H377" s="3" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="I377" s="3" t="s">
         <v>781</v>
@@ -47818,14 +48751,14 @@
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>377</v>
       </c>
       <c r="C378" s="3" t="s">
         <v>874</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="E378" s="3" t="s">
         <v>876</v>
@@ -47834,715 +48767,787 @@
         <v>877</v>
       </c>
       <c r="G378" s="3">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="H378" s="3" t="s">
-        <v>817</v>
+        <v>830</v>
       </c>
       <c r="I378" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="A379:A410" si="8">A378+1</f>
         <v>378</v>
       </c>
       <c r="C379" s="3" t="s">
-        <v>895</v>
+        <v>874</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>896</v>
+        <v>889</v>
       </c>
       <c r="E379" s="3" t="s">
-        <v>897</v>
+        <v>876</v>
       </c>
       <c r="F379" s="3" t="s">
-        <v>898</v>
+        <v>877</v>
       </c>
       <c r="G379" s="3">
-        <v>25</v>
+        <v>1.5</v>
       </c>
       <c r="H379" s="3" t="s">
-        <v>899</v>
+        <v>814</v>
+      </c>
+      <c r="I379" s="3" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>379</v>
       </c>
       <c r="C380" s="3" t="s">
-        <v>895</v>
+        <v>874</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>900</v>
+        <v>890</v>
       </c>
       <c r="E380" s="3" t="s">
-        <v>897</v>
+        <v>876</v>
       </c>
       <c r="F380" s="3" t="s">
-        <v>901</v>
+        <v>877</v>
       </c>
       <c r="G380" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H380" s="3" t="s">
-        <v>899</v>
+        <v>811</v>
+      </c>
+      <c r="I380" s="3" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>380</v>
       </c>
       <c r="C381" s="3" t="s">
-        <v>895</v>
+        <v>874</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>902</v>
+        <v>891</v>
       </c>
       <c r="E381" s="3" t="s">
-        <v>897</v>
+        <v>876</v>
       </c>
       <c r="F381" s="3" t="s">
-        <v>903</v>
+        <v>877</v>
       </c>
       <c r="G381" s="3">
-        <v>25</v>
+        <v>1.5</v>
       </c>
       <c r="H381" s="3" t="s">
-        <v>899</v>
+        <v>812</v>
+      </c>
+      <c r="I381" s="3" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>381</v>
       </c>
       <c r="C382" s="3" t="s">
-        <v>895</v>
+        <v>874</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>904</v>
+        <v>892</v>
       </c>
       <c r="E382" s="3" t="s">
-        <v>897</v>
+        <v>876</v>
       </c>
       <c r="F382" s="3" t="s">
-        <v>905</v>
+        <v>877</v>
       </c>
       <c r="G382" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H382" s="3" t="s">
-        <v>899</v>
+        <v>815</v>
+      </c>
+      <c r="I382" s="3" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>382</v>
       </c>
       <c r="C383" s="3" t="s">
-        <v>895</v>
+        <v>874</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>906</v>
+        <v>893</v>
       </c>
       <c r="E383" s="3" t="s">
-        <v>897</v>
+        <v>876</v>
       </c>
       <c r="F383" s="3" t="s">
-        <v>907</v>
+        <v>877</v>
       </c>
       <c r="G383" s="3">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="H383" s="3" t="s">
-        <v>899</v>
+        <v>816</v>
+      </c>
+      <c r="I383" s="3" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>383</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>895</v>
+        <v>874</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>908</v>
+        <v>894</v>
       </c>
       <c r="E384" s="3" t="s">
-        <v>897</v>
+        <v>876</v>
       </c>
       <c r="F384" s="3" t="s">
-        <v>909</v>
+        <v>877</v>
       </c>
       <c r="G384" s="3">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="H384" s="3" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
+        <v>817</v>
+      </c>
+      <c r="I384" s="3" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>384</v>
       </c>
       <c r="C385" s="3" t="s">
-        <v>895</v>
+        <v>874</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>910</v>
+        <v>1007</v>
       </c>
       <c r="E385" s="3" t="s">
-        <v>897</v>
+        <v>1008</v>
       </c>
       <c r="F385" s="3" t="s">
-        <v>911</v>
+        <v>1009</v>
       </c>
       <c r="G385" s="3">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="H385" s="3" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1000</v>
+      </c>
+      <c r="I385" s="3" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>385</v>
       </c>
       <c r="C386" s="3" t="s">
-        <v>895</v>
+        <v>874</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>912</v>
+        <v>1010</v>
       </c>
       <c r="E386" s="3" t="s">
-        <v>897</v>
+        <v>1008</v>
       </c>
       <c r="F386" s="3" t="s">
-        <v>913</v>
+        <v>1009</v>
       </c>
       <c r="G386" s="3">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="H386" s="3" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
+        <v>1002</v>
+      </c>
+      <c r="I386" s="3" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" s="3">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>386</v>
       </c>
       <c r="C387" s="3" t="s">
-        <v>895</v>
+        <v>874</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>914</v>
+        <v>1011</v>
       </c>
       <c r="E387" s="3" t="s">
-        <v>897</v>
+        <v>1008</v>
       </c>
       <c r="F387" s="3" t="s">
-        <v>915</v>
+        <v>1009</v>
       </c>
       <c r="G387" s="3">
         <v>0.5</v>
       </c>
       <c r="H387" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I387" s="3" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A388" s="3">
+        <f t="shared" si="8"/>
+        <v>387</v>
+      </c>
+      <c r="C388" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="D388" s="3" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E388" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F388" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G388" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="H388" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I388" s="3" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A389" s="3">
+        <f t="shared" si="8"/>
+        <v>388</v>
+      </c>
+      <c r="C389" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="D389" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E389" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F389" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G389" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="H389" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I389" s="3" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A390" s="3">
+        <f t="shared" si="8"/>
+        <v>389</v>
+      </c>
+      <c r="C390" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="D390" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E390" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F390" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G390" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="H390" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I390" s="3" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A391" s="3">
+        <f t="shared" si="8"/>
+        <v>390</v>
+      </c>
+      <c r="C391" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="D391" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="E391" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="F391" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="G391" s="3">
+        <v>25</v>
+      </c>
+      <c r="H391" s="3" t="s">
         <v>899</v>
       </c>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A388" s="3">
-        <f t="shared" ref="A388:A451" si="7">A387+1</f>
-        <v>387</v>
-      </c>
-      <c r="C388" s="3" t="s">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A392" s="3">
+        <f t="shared" si="8"/>
+        <v>391</v>
+      </c>
+      <c r="C392" s="3" t="s">
         <v>895</v>
       </c>
-      <c r="D388" s="3" t="s">
+      <c r="D392" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="E392" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="F392" s="3" t="s">
+        <v>901</v>
+      </c>
+      <c r="G392" s="3">
+        <v>20</v>
+      </c>
+      <c r="H392" s="3" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A393" s="3">
+        <f t="shared" si="8"/>
+        <v>392</v>
+      </c>
+      <c r="C393" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="D393" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="E393" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="F393" s="3" t="s">
+        <v>903</v>
+      </c>
+      <c r="G393" s="3">
+        <v>25</v>
+      </c>
+      <c r="H393" s="3" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A394" s="3">
+        <f t="shared" si="8"/>
+        <v>393</v>
+      </c>
+      <c r="C394" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="D394" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="E394" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="F394" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="G394" s="3">
+        <v>20</v>
+      </c>
+      <c r="H394" s="3" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A395" s="3">
+        <f t="shared" si="8"/>
+        <v>394</v>
+      </c>
+      <c r="C395" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="D395" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="E395" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="F395" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="G395" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="H395" s="3" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A396" s="3">
+        <f t="shared" si="8"/>
+        <v>395</v>
+      </c>
+      <c r="C396" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="D396" s="3" t="s">
+        <v>908</v>
+      </c>
+      <c r="E396" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="F396" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="G396" s="3">
+        <v>3</v>
+      </c>
+      <c r="H396" s="3" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A397" s="3">
+        <f t="shared" si="8"/>
+        <v>396</v>
+      </c>
+      <c r="C397" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="D397" s="3" t="s">
+        <v>910</v>
+      </c>
+      <c r="E397" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="F397" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="G397" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="H397" s="3" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A398" s="3">
+        <f t="shared" si="8"/>
+        <v>397</v>
+      </c>
+      <c r="C398" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="D398" s="3" t="s">
+        <v>912</v>
+      </c>
+      <c r="E398" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="F398" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="G398" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="H398" s="3" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A399" s="3">
+        <f t="shared" si="8"/>
+        <v>398</v>
+      </c>
+      <c r="C399" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="D399" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="E399" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="F399" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="G399" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="H399" s="3" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A400" s="3">
+        <f t="shared" si="8"/>
+        <v>399</v>
+      </c>
+      <c r="C400" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="D400" s="3" t="s">
         <v>916</v>
       </c>
-      <c r="E388" s="3" t="s">
+      <c r="E400" s="3" t="s">
         <v>897</v>
       </c>
-      <c r="F388" s="3" t="s">
+      <c r="F400" s="3" t="s">
         <v>917</v>
       </c>
-      <c r="G388" s="3">
+      <c r="G400" s="3">
         <v>25</v>
       </c>
-      <c r="H388" s="3" t="s">
+      <c r="H400" s="3" t="s">
         <v>899</v>
       </c>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A389" s="3">
-        <f t="shared" si="7"/>
-        <v>388</v>
-      </c>
-      <c r="C389" s="3" t="s">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A401" s="3">
+        <f t="shared" si="8"/>
+        <v>400</v>
+      </c>
+      <c r="C401" s="3" t="s">
         <v>895</v>
       </c>
-      <c r="D389" s="3" t="s">
+      <c r="D401" s="3" t="s">
         <v>918</v>
       </c>
-      <c r="E389" s="3" t="s">
+      <c r="E401" s="3" t="s">
         <v>897</v>
       </c>
-      <c r="F389" s="3" t="s">
+      <c r="F401" s="3" t="s">
         <v>919</v>
       </c>
-      <c r="G389" s="3">
+      <c r="G401" s="3">
         <v>8</v>
       </c>
-      <c r="H389" s="3" t="s">
+      <c r="H401" s="3" t="s">
         <v>920</v>
       </c>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A390" s="3">
-        <f t="shared" si="7"/>
-        <v>389</v>
-      </c>
-      <c r="C390" s="3" t="s">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A402" s="3">
+        <f t="shared" si="8"/>
+        <v>401</v>
+      </c>
+      <c r="C402" s="3" t="s">
         <v>895</v>
       </c>
-      <c r="D390" s="3" t="s">
+      <c r="D402" s="3" t="s">
         <v>921</v>
       </c>
-      <c r="E390" s="3" t="s">
+      <c r="E402" s="3" t="s">
         <v>897</v>
       </c>
-      <c r="F390" s="3" t="s">
+      <c r="F402" s="3" t="s">
         <v>922</v>
       </c>
-      <c r="G390" s="3">
+      <c r="G402" s="3">
         <v>15</v>
       </c>
-      <c r="H390" s="3" t="s">
+      <c r="H402" s="3" t="s">
         <v>920</v>
       </c>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A391" s="3">
-        <f t="shared" si="7"/>
-        <v>390</v>
-      </c>
-      <c r="C391" s="3" t="s">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A403" s="3">
+        <f t="shared" si="8"/>
+        <v>402</v>
+      </c>
+      <c r="C403" s="3" t="s">
         <v>923</v>
       </c>
-      <c r="D391" s="3" t="s">
+      <c r="D403" s="3" t="s">
         <v>924</v>
       </c>
-      <c r="E391" s="3" t="s">
+      <c r="E403" s="3" t="s">
         <v>925</v>
       </c>
-      <c r="F391" s="3" t="s">
+      <c r="F403" s="3" t="s">
         <v>926</v>
       </c>
-      <c r="G391" s="3">
+      <c r="G403" s="3">
         <v>0.8</v>
       </c>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A392" s="3">
-        <f t="shared" si="7"/>
-        <v>391</v>
-      </c>
-      <c r="C392" s="3" t="s">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A404" s="3">
+        <f t="shared" si="8"/>
+        <v>403</v>
+      </c>
+      <c r="C404" s="3" t="s">
         <v>923</v>
       </c>
-      <c r="D392" s="3" t="s">
+      <c r="D404" s="3" t="s">
         <v>927</v>
       </c>
-      <c r="E392" s="3" t="s">
+      <c r="E404" s="3" t="s">
         <v>928</v>
       </c>
-      <c r="F392" s="3" t="s">
+      <c r="F404" s="3" t="s">
         <v>929</v>
       </c>
-      <c r="G392" s="3">
+      <c r="G404" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A393" s="3">
-        <f t="shared" si="7"/>
-        <v>392</v>
-      </c>
-      <c r="C393" s="3" t="s">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A405" s="3">
+        <f t="shared" si="8"/>
+        <v>404</v>
+      </c>
+      <c r="C405" s="3" t="s">
         <v>923</v>
       </c>
-      <c r="D393" s="3" t="s">
+      <c r="D405" s="3" t="s">
         <v>930</v>
       </c>
-      <c r="E393" s="3" t="s">
+      <c r="E405" s="3" t="s">
         <v>931</v>
       </c>
-      <c r="F393" s="3" t="s">
+      <c r="F405" s="3" t="s">
         <v>932</v>
       </c>
-      <c r="G393" s="3">
+      <c r="G405" s="3">
         <v>7</v>
       </c>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A394" s="3">
-        <f t="shared" si="7"/>
-        <v>393</v>
-      </c>
-      <c r="C394" s="3" t="s">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A406" s="3">
+        <f t="shared" si="8"/>
+        <v>405</v>
+      </c>
+      <c r="C406" s="3" t="s">
         <v>923</v>
       </c>
-      <c r="D394" s="3" t="s">
+      <c r="D406" s="3" t="s">
         <v>933</v>
       </c>
-      <c r="E394" s="3" t="s">
+      <c r="E406" s="3" t="s">
         <v>934</v>
       </c>
-      <c r="F394" s="3" t="s">
+      <c r="F406" s="3" t="s">
         <v>935</v>
       </c>
-      <c r="G394" s="3">
+      <c r="G406" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A395" s="3">
-        <f t="shared" si="7"/>
-        <v>394</v>
-      </c>
-      <c r="C395" s="3" t="s">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A407" s="3">
+        <f t="shared" si="8"/>
+        <v>406</v>
+      </c>
+      <c r="C407" s="3" t="s">
         <v>923</v>
       </c>
-      <c r="D395" s="3" t="s">
+      <c r="D407" s="3" t="s">
         <v>936</v>
       </c>
-      <c r="E395" s="3" t="s">
+      <c r="E407" s="3" t="s">
         <v>937</v>
       </c>
-      <c r="F395" s="3" t="s">
+      <c r="F407" s="3" t="s">
         <v>938</v>
       </c>
-      <c r="G395" s="3">
+      <c r="G407" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A396" s="3">
-        <f t="shared" si="7"/>
-        <v>395</v>
-      </c>
-      <c r="C396" s="3" t="s">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A408" s="3">
+        <f t="shared" si="8"/>
+        <v>407</v>
+      </c>
+      <c r="C408" s="3" t="s">
         <v>923</v>
       </c>
-      <c r="D396" s="3" t="s">
+      <c r="D408" s="3" t="s">
         <v>939</v>
       </c>
-      <c r="E396" s="3" t="s">
+      <c r="E408" s="3" t="s">
         <v>940</v>
       </c>
-      <c r="F396" s="3" t="s">
+      <c r="F408" s="3" t="s">
         <v>941</v>
       </c>
-      <c r="G396" s="3">
+      <c r="G408" s="3">
         <v>5</v>
       </c>
-      <c r="H396" s="3">
+      <c r="H408" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A397" s="3">
-        <f t="shared" si="7"/>
-        <v>396</v>
-      </c>
-      <c r="C397" s="3" t="s">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A409" s="3">
+        <f t="shared" si="8"/>
+        <v>408</v>
+      </c>
+      <c r="C409" s="3" t="s">
         <v>923</v>
       </c>
-      <c r="D397" s="3" t="s">
+      <c r="D409" s="3" t="s">
         <v>942</v>
       </c>
-      <c r="E397" s="3" t="s">
+      <c r="E409" s="3" t="s">
         <v>943</v>
       </c>
-      <c r="F397" s="3" t="s">
+      <c r="F409" s="3" t="s">
         <v>944</v>
       </c>
-      <c r="G397" s="3">
+      <c r="G409" s="3">
         <v>8</v>
       </c>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A398" s="3">
-        <f t="shared" si="7"/>
-        <v>397</v>
-      </c>
-      <c r="C398" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="D398" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E398" s="3" t="s">
-        <v>946</v>
-      </c>
-      <c r="F398" s="3" t="s">
-        <v>947</v>
-      </c>
-      <c r="G398" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A399" s="3">
-        <f t="shared" si="7"/>
-        <v>398</v>
-      </c>
-      <c r="C399" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="D399" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="E399" s="3" t="s">
-        <v>946</v>
-      </c>
-      <c r="F399" s="3" t="s">
-        <v>947</v>
-      </c>
-      <c r="G399" s="3">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A400" s="3">
-        <f t="shared" si="7"/>
-        <v>399</v>
-      </c>
-      <c r="C400" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="D400" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E400" s="3" t="s">
-        <v>946</v>
-      </c>
-      <c r="F400" s="3" t="s">
-        <v>947</v>
-      </c>
-      <c r="G400" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A401" s="3">
-        <f t="shared" si="7"/>
-        <v>400</v>
-      </c>
-      <c r="C401" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="D401" s="3" t="s">
-        <v>782</v>
-      </c>
-      <c r="E401" s="3" t="s">
-        <v>946</v>
-      </c>
-      <c r="F401" s="3" t="s">
-        <v>947</v>
-      </c>
-      <c r="G401" s="3">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A402" s="3">
-        <f t="shared" si="7"/>
-        <v>401</v>
-      </c>
-      <c r="C402" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="D402" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="E402" s="3" t="s">
-        <v>946</v>
-      </c>
-      <c r="F402" s="3" t="s">
-        <v>947</v>
-      </c>
-      <c r="G402" s="3">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A403" s="3">
-        <f t="shared" si="7"/>
-        <v>402</v>
-      </c>
-      <c r="C403" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="D403" s="3" t="s">
-        <v>784</v>
-      </c>
-      <c r="E403" s="3" t="s">
-        <v>946</v>
-      </c>
-      <c r="F403" s="3" t="s">
-        <v>947</v>
-      </c>
-      <c r="G403" s="3">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A404" s="3">
-        <f t="shared" si="7"/>
-        <v>403</v>
-      </c>
-      <c r="C404" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="D404" s="3" t="s">
-        <v>785</v>
-      </c>
-      <c r="E404" s="3" t="s">
-        <v>946</v>
-      </c>
-      <c r="F404" s="3" t="s">
-        <v>947</v>
-      </c>
-      <c r="G404" s="3">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A405" s="3">
-        <f t="shared" si="7"/>
-        <v>404</v>
-      </c>
-      <c r="C405" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="D405" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E405" s="3" t="s">
-        <v>946</v>
-      </c>
-      <c r="F405" s="3" t="s">
-        <v>947</v>
-      </c>
-      <c r="G405" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A406" s="3">
-        <f t="shared" si="7"/>
-        <v>405</v>
-      </c>
-      <c r="C406" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="D406" s="3" t="s">
-        <v>791</v>
-      </c>
-      <c r="E406" s="3" t="s">
-        <v>946</v>
-      </c>
-      <c r="F406" s="3" t="s">
-        <v>947</v>
-      </c>
-      <c r="G406" s="3">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A407" s="3">
-        <f t="shared" si="7"/>
-        <v>406</v>
-      </c>
-      <c r="C407" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="D407" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E407" s="3" t="s">
-        <v>946</v>
-      </c>
-      <c r="F407" s="3" t="s">
-        <v>947</v>
-      </c>
-      <c r="G407" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A408" s="3">
-        <f t="shared" si="7"/>
-        <v>407</v>
-      </c>
-      <c r="C408" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="D408" s="3" t="s">
-        <v>786</v>
-      </c>
-      <c r="E408" s="3" t="s">
-        <v>946</v>
-      </c>
-      <c r="F408" s="3" t="s">
-        <v>947</v>
-      </c>
-      <c r="G408" s="3">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A409" s="3">
-        <f t="shared" si="7"/>
-        <v>408</v>
-      </c>
-      <c r="C409" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="D409" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E409" s="3" t="s">
-        <v>946</v>
-      </c>
-      <c r="F409" s="3" t="s">
-        <v>947</v>
-      </c>
-      <c r="G409" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A410" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>409</v>
       </c>
       <c r="C410" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>787</v>
+        <v>87</v>
       </c>
       <c r="E410" s="3" t="s">
         <v>946</v>
@@ -48551,19 +49556,19 @@
         <v>947</v>
       </c>
       <c r="G410" s="3">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A411" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="A411:A442" si="9">A410+1</f>
         <v>410</v>
       </c>
       <c r="C411" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
       <c r="E411" s="3" t="s">
         <v>946</v>
@@ -48572,19 +49577,19 @@
         <v>947</v>
       </c>
       <c r="G411" s="3">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A412" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>411</v>
       </c>
       <c r="C412" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>789</v>
+        <v>88</v>
       </c>
       <c r="E412" s="3" t="s">
         <v>946</v>
@@ -48593,19 +49598,19 @@
         <v>947</v>
       </c>
       <c r="G412" s="3">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A413" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>412</v>
       </c>
       <c r="C413" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D413" s="3" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="E413" s="3" t="s">
         <v>946</v>
@@ -48614,19 +49619,19 @@
         <v>947</v>
       </c>
       <c r="G413" s="3">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A414" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>413</v>
       </c>
       <c r="C414" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D414" s="3" t="s">
-        <v>796</v>
+        <v>783</v>
       </c>
       <c r="E414" s="3" t="s">
         <v>946</v>
@@ -48635,19 +49640,19 @@
         <v>947</v>
       </c>
       <c r="G414" s="3">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A415" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>414</v>
       </c>
       <c r="C415" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D415" s="3" t="s">
-        <v>797</v>
+        <v>784</v>
       </c>
       <c r="E415" s="3" t="s">
         <v>946</v>
@@ -48656,19 +49661,19 @@
         <v>947</v>
       </c>
       <c r="G415" s="3">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A416" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>415</v>
       </c>
       <c r="C416" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D416" s="3" t="s">
-        <v>798</v>
+        <v>785</v>
       </c>
       <c r="E416" s="3" t="s">
         <v>946</v>
@@ -48677,19 +49682,19 @@
         <v>947</v>
       </c>
       <c r="G416" s="3">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="417" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A417" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>416</v>
       </c>
       <c r="C417" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>799</v>
+        <v>89</v>
       </c>
       <c r="E417" s="3" t="s">
         <v>946</v>
@@ -48698,19 +49703,19 @@
         <v>947</v>
       </c>
       <c r="G417" s="3">
-        <v>2.2000000000000002</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="418" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A418" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>417</v>
       </c>
       <c r="C418" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D418" s="3" t="s">
-        <v>800</v>
+        <v>791</v>
       </c>
       <c r="E418" s="3" t="s">
         <v>946</v>
@@ -48719,19 +49724,19 @@
         <v>947</v>
       </c>
       <c r="G418" s="3">
-        <v>2.2000000000000002</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="419" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A419" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>418</v>
       </c>
       <c r="C419" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>801</v>
+        <v>90</v>
       </c>
       <c r="E419" s="3" t="s">
         <v>946</v>
@@ -48740,19 +49745,19 @@
         <v>947</v>
       </c>
       <c r="G419" s="3">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="420" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A420" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>419</v>
       </c>
       <c r="C420" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>802</v>
+        <v>786</v>
       </c>
       <c r="E420" s="3" t="s">
         <v>946</v>
@@ -48761,19 +49766,19 @@
         <v>947</v>
       </c>
       <c r="G420" s="3">
-        <v>2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="421" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A421" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>420</v>
       </c>
       <c r="C421" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>803</v>
+        <v>84</v>
       </c>
       <c r="E421" s="3" t="s">
         <v>946</v>
@@ -48782,19 +49787,19 @@
         <v>947</v>
       </c>
       <c r="G421" s="3">
-        <v>1.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="422" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A422" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>421</v>
       </c>
       <c r="C422" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D422" s="3" t="s">
-        <v>804</v>
+        <v>787</v>
       </c>
       <c r="E422" s="3" t="s">
         <v>946</v>
@@ -48803,19 +49808,19 @@
         <v>947</v>
       </c>
       <c r="G422" s="3">
-        <v>2.2000000000000002</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="423" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A423" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>422</v>
       </c>
       <c r="C423" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D423" s="3" t="s">
-        <v>805</v>
+        <v>788</v>
       </c>
       <c r="E423" s="3" t="s">
         <v>946</v>
@@ -48824,19 +49829,19 @@
         <v>947</v>
       </c>
       <c r="G423" s="3">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="424" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A424" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>423</v>
       </c>
       <c r="C424" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D424" s="3" t="s">
-        <v>806</v>
+        <v>789</v>
       </c>
       <c r="E424" s="3" t="s">
         <v>946</v>
@@ -48845,19 +49850,19 @@
         <v>947</v>
       </c>
       <c r="G424" s="3">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="425" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A425" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>424</v>
       </c>
       <c r="C425" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>807</v>
+        <v>790</v>
       </c>
       <c r="E425" s="3" t="s">
         <v>946</v>
@@ -48866,19 +49871,19 @@
         <v>947</v>
       </c>
       <c r="G425" s="3">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="426" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A426" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>425</v>
       </c>
       <c r="C426" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>808</v>
+        <v>796</v>
       </c>
       <c r="E426" s="3" t="s">
         <v>946</v>
@@ -48887,19 +49892,19 @@
         <v>947</v>
       </c>
       <c r="G426" s="3">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="427" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A427" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>426</v>
       </c>
       <c r="C427" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D427" s="3" t="s">
-        <v>810</v>
+        <v>797</v>
       </c>
       <c r="E427" s="3" t="s">
         <v>946</v>
@@ -48908,19 +49913,19 @@
         <v>947</v>
       </c>
       <c r="G427" s="3">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="428" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A428" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>427</v>
       </c>
       <c r="C428" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D428" s="3" t="s">
-        <v>114</v>
+        <v>798</v>
       </c>
       <c r="E428" s="3" t="s">
         <v>946</v>
@@ -48929,19 +49934,19 @@
         <v>947</v>
       </c>
       <c r="G428" s="3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="429" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A429" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>428</v>
       </c>
       <c r="C429" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D429" s="3" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="E429" s="3" t="s">
         <v>946</v>
@@ -48950,19 +49955,19 @@
         <v>947</v>
       </c>
       <c r="G429" s="3">
-        <v>1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="430" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A430" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>429</v>
       </c>
       <c r="C430" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D430" s="3" t="s">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="E430" s="3" t="s">
         <v>946</v>
@@ -48971,19 +49976,19 @@
         <v>947</v>
       </c>
       <c r="G430" s="3">
-        <v>1</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="431" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A431" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>430</v>
       </c>
       <c r="C431" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>795</v>
+        <v>801</v>
       </c>
       <c r="E431" s="3" t="s">
         <v>946</v>
@@ -48992,19 +49997,19 @@
         <v>947</v>
       </c>
       <c r="G431" s="3">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="432" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A432" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>431</v>
       </c>
       <c r="C432" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>811</v>
+        <v>802</v>
       </c>
       <c r="E432" s="3" t="s">
         <v>946</v>
@@ -49018,14 +50023,14 @@
     </row>
     <row r="433" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A433" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>432</v>
       </c>
       <c r="C433" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>812</v>
+        <v>803</v>
       </c>
       <c r="E433" s="3" t="s">
         <v>946</v>
@@ -49034,19 +50039,19 @@
         <v>947</v>
       </c>
       <c r="G433" s="3">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="434" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A434" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>433</v>
       </c>
       <c r="C434" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D434" s="3" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="E434" s="3" t="s">
         <v>946</v>
@@ -49060,14 +50065,14 @@
     </row>
     <row r="435" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A435" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>434</v>
       </c>
       <c r="C435" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D435" s="3" t="s">
-        <v>814</v>
+        <v>805</v>
       </c>
       <c r="E435" s="3" t="s">
         <v>946</v>
@@ -49076,19 +50081,19 @@
         <v>947</v>
       </c>
       <c r="G435" s="3">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="436" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A436" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>435</v>
       </c>
       <c r="C436" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D436" s="3" t="s">
-        <v>815</v>
+        <v>806</v>
       </c>
       <c r="E436" s="3" t="s">
         <v>946</v>
@@ -49097,19 +50102,19 @@
         <v>947</v>
       </c>
       <c r="G436" s="3">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="437" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A437" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>436</v>
       </c>
       <c r="C437" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
       <c r="E437" s="3" t="s">
         <v>946</v>
@@ -49118,19 +50123,19 @@
         <v>947</v>
       </c>
       <c r="G437" s="3">
-        <v>2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="438" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A438" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>437</v>
       </c>
       <c r="C438" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D438" s="3" t="s">
-        <v>817</v>
+        <v>808</v>
       </c>
       <c r="E438" s="3" t="s">
         <v>946</v>
@@ -49139,19 +50144,19 @@
         <v>947</v>
       </c>
       <c r="G438" s="3">
-        <v>2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="439" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A439" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>438</v>
       </c>
       <c r="C439" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D439" s="3" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="E439" s="3" t="s">
         <v>946</v>
@@ -49160,19 +50165,19 @@
         <v>947</v>
       </c>
       <c r="G439" s="3">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="440" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A440" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>439</v>
       </c>
       <c r="C440" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D440" s="3" t="s">
-        <v>819</v>
+        <v>114</v>
       </c>
       <c r="E440" s="3" t="s">
         <v>946</v>
@@ -49181,19 +50186,19 @@
         <v>947</v>
       </c>
       <c r="G440" s="3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="441" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A441" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>440</v>
       </c>
       <c r="C441" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D441" s="3" t="s">
-        <v>820</v>
+        <v>792</v>
       </c>
       <c r="E441" s="3" t="s">
         <v>946</v>
@@ -49202,19 +50207,19 @@
         <v>947</v>
       </c>
       <c r="G441" s="3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="442" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A442" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>441</v>
       </c>
       <c r="C442" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D442" s="3" t="s">
-        <v>821</v>
+        <v>794</v>
       </c>
       <c r="E442" s="3" t="s">
         <v>946</v>
@@ -49223,19 +50228,19 @@
         <v>947</v>
       </c>
       <c r="G442" s="3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="443" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A443" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="A443:A469" si="10">A442+1</f>
         <v>442</v>
       </c>
       <c r="C443" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D443" s="3" t="s">
-        <v>822</v>
+        <v>795</v>
       </c>
       <c r="E443" s="3" t="s">
         <v>946</v>
@@ -49244,19 +50249,19 @@
         <v>947</v>
       </c>
       <c r="G443" s="3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="444" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A444" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>443</v>
       </c>
       <c r="C444" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D444" s="3" t="s">
-        <v>823</v>
+        <v>811</v>
       </c>
       <c r="E444" s="3" t="s">
         <v>946</v>
@@ -49265,19 +50270,19 @@
         <v>947</v>
       </c>
       <c r="G444" s="3">
-        <v>0.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="445" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A445" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>444</v>
       </c>
       <c r="C445" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D445" s="3" t="s">
-        <v>824</v>
+        <v>812</v>
       </c>
       <c r="E445" s="3" t="s">
         <v>946</v>
@@ -49291,14 +50296,14 @@
     </row>
     <row r="446" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A446" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>445</v>
       </c>
       <c r="C446" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D446" s="3" t="s">
-        <v>825</v>
+        <v>813</v>
       </c>
       <c r="E446" s="3" t="s">
         <v>946</v>
@@ -49307,19 +50312,19 @@
         <v>947</v>
       </c>
       <c r="G446" s="3">
-        <v>1.5</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="447" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A447" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>446</v>
       </c>
       <c r="C447" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D447" s="3" t="s">
-        <v>826</v>
+        <v>814</v>
       </c>
       <c r="E447" s="3" t="s">
         <v>946</v>
@@ -49328,19 +50333,19 @@
         <v>947</v>
       </c>
       <c r="G447" s="3">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="448" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A448" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>447</v>
       </c>
       <c r="C448" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D448" s="3" t="s">
-        <v>827</v>
+        <v>815</v>
       </c>
       <c r="E448" s="3" t="s">
         <v>946</v>
@@ -49349,19 +50354,19 @@
         <v>947</v>
       </c>
       <c r="G448" s="3">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="449" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A449" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>448</v>
       </c>
       <c r="C449" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D449" s="3" t="s">
-        <v>829</v>
+        <v>816</v>
       </c>
       <c r="E449" s="3" t="s">
         <v>946</v>
@@ -49370,19 +50375,19 @@
         <v>947</v>
       </c>
       <c r="G449" s="3">
-        <v>0.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="450" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A450" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>449</v>
       </c>
       <c r="C450" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D450" s="3" t="s">
-        <v>830</v>
+        <v>817</v>
       </c>
       <c r="E450" s="3" t="s">
         <v>946</v>
@@ -49391,19 +50396,19 @@
         <v>947</v>
       </c>
       <c r="G450" s="3">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="451" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A451" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>450</v>
       </c>
       <c r="C451" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D451" s="3" t="s">
-        <v>108</v>
+        <v>818</v>
       </c>
       <c r="E451" s="3" t="s">
         <v>946</v>
@@ -49417,14 +50422,14 @@
     </row>
     <row r="452" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A452" s="3">
-        <f t="shared" ref="A452:A457" si="8">A451+1</f>
+        <f t="shared" si="10"/>
         <v>451</v>
       </c>
       <c r="C452" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D452" s="3" t="s">
-        <v>832</v>
+        <v>819</v>
       </c>
       <c r="E452" s="3" t="s">
         <v>946</v>
@@ -49438,14 +50443,14 @@
     </row>
     <row r="453" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A453" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>452</v>
       </c>
       <c r="C453" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>833</v>
+        <v>820</v>
       </c>
       <c r="E453" s="3" t="s">
         <v>946</v>
@@ -49459,14 +50464,14 @@
     </row>
     <row r="454" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A454" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>453</v>
       </c>
       <c r="C454" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D454" s="3" t="s">
-        <v>834</v>
+        <v>821</v>
       </c>
       <c r="E454" s="3" t="s">
         <v>946</v>
@@ -49475,19 +50480,19 @@
         <v>947</v>
       </c>
       <c r="G454" s="3">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="455" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A455" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>454</v>
       </c>
       <c r="C455" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D455" s="3" t="s">
-        <v>835</v>
+        <v>822</v>
       </c>
       <c r="E455" s="3" t="s">
         <v>946</v>
@@ -49496,19 +50501,19 @@
         <v>947</v>
       </c>
       <c r="G455" s="3">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="456" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A456" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>455</v>
       </c>
       <c r="C456" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D456" s="3" t="s">
-        <v>836</v>
+        <v>823</v>
       </c>
       <c r="E456" s="3" t="s">
         <v>946</v>
@@ -49517,19 +50522,19 @@
         <v>947</v>
       </c>
       <c r="G456" s="3">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="457" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A457" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>456</v>
       </c>
       <c r="C457" s="3" t="s">
         <v>945</v>
       </c>
       <c r="D457" s="3" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
       <c r="E457" s="3" t="s">
         <v>946</v>
@@ -49538,6 +50543,258 @@
         <v>947</v>
       </c>
       <c r="G457" s="3">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A458" s="3">
+        <f t="shared" si="10"/>
+        <v>457</v>
+      </c>
+      <c r="C458" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="D458" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="E458" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="F458" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="G458" s="3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A459" s="3">
+        <f t="shared" si="10"/>
+        <v>458</v>
+      </c>
+      <c r="C459" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="D459" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="E459" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="F459" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="G459" s="3">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A460" s="3">
+        <f t="shared" si="10"/>
+        <v>459</v>
+      </c>
+      <c r="C460" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="D460" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="E460" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="F460" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="G460" s="3">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A461" s="3">
+        <f t="shared" si="10"/>
+        <v>460</v>
+      </c>
+      <c r="C461" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="D461" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="E461" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="F461" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="G461" s="3">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A462" s="3">
+        <f t="shared" si="10"/>
+        <v>461</v>
+      </c>
+      <c r="C462" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="D462" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="E462" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="F462" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="G462" s="3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A463" s="3">
+        <f t="shared" si="10"/>
+        <v>462</v>
+      </c>
+      <c r="C463" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="D463" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E463" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="F463" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="G463" s="3">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A464" s="3">
+        <f t="shared" si="10"/>
+        <v>463</v>
+      </c>
+      <c r="C464" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="D464" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="E464" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="F464" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="G464" s="3">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A465" s="3">
+        <f t="shared" si="10"/>
+        <v>464</v>
+      </c>
+      <c r="C465" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="D465" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="E465" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="F465" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="G465" s="3">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A466" s="3">
+        <f t="shared" si="10"/>
+        <v>465</v>
+      </c>
+      <c r="C466" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="D466" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="E466" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="F466" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="G466" s="3">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A467" s="3">
+        <f t="shared" si="10"/>
+        <v>466</v>
+      </c>
+      <c r="C467" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="D467" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="E467" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="F467" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="G467" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A468" s="3">
+        <f t="shared" si="10"/>
+        <v>467</v>
+      </c>
+      <c r="C468" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="D468" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="E468" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="F468" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="G468" s="3">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A469" s="3">
+        <f t="shared" si="10"/>
+        <v>468</v>
+      </c>
+      <c r="C469" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="D469" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="E469" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="F469" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="G469" s="3">
         <v>1</v>
       </c>
     </row>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.gemini\antigravity\scratch\Idle-RPG\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2331E3-5B59-4A5E-84F5-BA993F86622C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F3F1FF3-6BBF-4999-B183-6DE35DDC0D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2447" uniqueCount="1015">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2443" uniqueCount="1014">
   <si>
     <t>編號</t>
   </si>
@@ -3034,10 +3034,6 @@
   </si>
   <si>
     <t>魔法防禦</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>調整</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -5032,9 +5028,9 @@
         <f>計算表!A23</f>
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="str">
+      <c r="B23" s="2">
         <f>計算表!B23</f>
-        <v>調整</v>
+        <v>0</v>
       </c>
       <c r="C23" t="str">
         <f>計算表!C23</f>
@@ -5106,9 +5102,9 @@
         <f>計算表!A24</f>
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="str">
+      <c r="B24" s="2">
         <f>計算表!B24</f>
-        <v>調整</v>
+        <v>0</v>
       </c>
       <c r="C24" t="str">
         <f>計算表!C24</f>
@@ -5180,9 +5176,9 @@
         <f>計算表!A25</f>
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="str">
+      <c r="B25" s="2">
         <f>計算表!B25</f>
-        <v>調整</v>
+        <v>0</v>
       </c>
       <c r="C25" t="str">
         <f>計算表!C25</f>
@@ -5254,9 +5250,9 @@
         <f>計算表!A26</f>
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="str">
+      <c r="B26" s="2">
         <f>計算表!B26</f>
-        <v>調整</v>
+        <v>0</v>
       </c>
       <c r="C26" t="str">
         <f>計算表!C26</f>
@@ -38848,9 +38844,6 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>991</v>
-      </c>
       <c r="C23" s="3" t="s">
         <v>77</v>
       </c>
@@ -38858,10 +38851,10 @@
         <v>87</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="G23" s="3">
         <v>8</v>
@@ -38881,9 +38874,6 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>991</v>
-      </c>
       <c r="C24" s="3" t="s">
         <v>77</v>
       </c>
@@ -38891,10 +38881,10 @@
         <v>88</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="G24" s="3">
         <v>6</v>
@@ -38914,9 +38904,6 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>991</v>
-      </c>
       <c r="C25" s="3" t="s">
         <v>77</v>
       </c>
@@ -38924,10 +38911,10 @@
         <v>989</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="G25" s="3">
         <v>3</v>
@@ -38950,9 +38937,6 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>991</v>
-      </c>
       <c r="C26" s="3" t="s">
         <v>77</v>
       </c>
@@ -38960,10 +38944,10 @@
         <v>990</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="G26" s="3">
         <v>2</v>
@@ -46931,13 +46915,13 @@
         <v>776</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E315" s="3" t="s">
         <v>777</v>
       </c>
       <c r="F315" s="3" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="G315" s="3">
         <v>0.8</v>
@@ -46964,13 +46948,13 @@
         <v>776</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E316" s="3" t="s">
         <v>777</v>
       </c>
       <c r="F316" s="3" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="G316" s="3">
         <v>0.8</v>
@@ -46997,13 +46981,13 @@
         <v>776</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E317" s="3" t="s">
         <v>777</v>
       </c>
       <c r="F317" s="3" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="G317" s="3">
         <v>0.8</v>
@@ -47030,13 +47014,13 @@
         <v>776</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="E318" s="3" t="s">
         <v>777</v>
       </c>
       <c r="F318" s="3" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="G318" s="3">
         <v>0.8</v>
@@ -47063,13 +47047,13 @@
         <v>776</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E319" s="3" t="s">
         <v>777</v>
       </c>
       <c r="F319" s="3" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="G319" s="3">
         <v>0.8</v>
@@ -47096,13 +47080,13 @@
         <v>776</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="E320" s="3" t="s">
         <v>777</v>
       </c>
       <c r="F320" s="3" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="G320" s="3">
         <v>0.8</v>
@@ -48947,19 +48931,19 @@
         <v>874</v>
       </c>
       <c r="D385" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E385" s="3" t="s">
         <v>1007</v>
       </c>
-      <c r="E385" s="3" t="s">
+      <c r="F385" s="3" t="s">
         <v>1008</v>
-      </c>
-      <c r="F385" s="3" t="s">
-        <v>1009</v>
       </c>
       <c r="G385" s="3">
         <v>0.5</v>
       </c>
       <c r="H385" s="3" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="I385" s="3" t="s">
         <v>781</v>
@@ -48974,19 +48958,19 @@
         <v>874</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="E386" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F386" s="3" t="s">
         <v>1008</v>
-      </c>
-      <c r="F386" s="3" t="s">
-        <v>1009</v>
       </c>
       <c r="G386" s="3">
         <v>0.5</v>
       </c>
       <c r="H386" s="3" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="I386" s="3" t="s">
         <v>781</v>
@@ -49001,19 +48985,19 @@
         <v>874</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E387" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F387" s="3" t="s">
         <v>1008</v>
-      </c>
-      <c r="F387" s="3" t="s">
-        <v>1009</v>
       </c>
       <c r="G387" s="3">
         <v>0.5</v>
       </c>
       <c r="H387" s="3" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="I387" s="3" t="s">
         <v>781</v>
@@ -49028,19 +49012,19 @@
         <v>874</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="E388" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F388" s="3" t="s">
         <v>1008</v>
-      </c>
-      <c r="F388" s="3" t="s">
-        <v>1009</v>
       </c>
       <c r="G388" s="3">
         <v>0.5</v>
       </c>
       <c r="H388" s="3" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="I388" s="3" t="s">
         <v>781</v>
@@ -49055,19 +49039,19 @@
         <v>874</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="E389" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F389" s="3" t="s">
         <v>1008</v>
-      </c>
-      <c r="F389" s="3" t="s">
-        <v>1009</v>
       </c>
       <c r="G389" s="3">
         <v>0.5</v>
       </c>
       <c r="H389" s="3" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="I389" s="3" t="s">
         <v>781</v>
@@ -49082,19 +49066,19 @@
         <v>874</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="E390" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F390" s="3" t="s">
         <v>1008</v>
-      </c>
-      <c r="F390" s="3" t="s">
-        <v>1009</v>
       </c>
       <c r="G390" s="3">
         <v>0.5</v>
       </c>
       <c r="H390" s="3" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="I390" s="3" t="s">
         <v>781</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.gemini\antigravity\scratch\Idle-RPG\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D400BEAD-7E82-40B3-B6A4-506A6A072527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFCCFE68-265D-48C8-8291-831C2D95B927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="H83">
         <f>計算表!H83</f>
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="I83">
         <f>計算表!I83</f>
@@ -9575,11 +9575,11 @@
       </c>
       <c r="G84">
         <f>計算表!G84</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H84">
         <f>計算表!H84</f>
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="I84">
         <f>計算表!I84</f>
@@ -40290,7 +40290,7 @@
         <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -40311,10 +40311,10 @@
         <v>217</v>
       </c>
       <c r="G84" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H84" s="3">
-        <v>4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.gemini\antigravity\scratch\Idle-RPG\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFCCFE68-265D-48C8-8291-831C2D95B927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3FE9E6C-2F7E-4895-AF16-49F5A3C6FFCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -15939,19 +15939,19 @@
       </c>
       <c r="G170">
         <f>計算表!G170</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H170">
         <f>計算表!H170</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I170">
         <f>計算表!I170</f>
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J170">
         <f>計算表!J170</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K170">
         <f>計算表!K170</f>
@@ -42693,16 +42693,16 @@
         <v>450</v>
       </c>
       <c r="G170" s="3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H170" s="3">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I170" s="3">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J170" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K170" s="3">
         <v>8</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.gemini\antigravity\scratch\Idle-RPG\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5B517F-7C79-499A-9273-3D7E56896AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D00A72C-6010-4EE9-8BE5-18177CE5B5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2468" uniqueCount="1040">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2480" uniqueCount="1048">
   <si>
     <t>編號</t>
   </si>
@@ -3175,6 +3175,38 @@
   </si>
   <si>
     <t>{300+=0}</t>
+  </si>
+  <si>
+    <t>{1~49=0.5}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{50~99=0.75}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{100~149=1}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{150~199=1.5}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{200+=2}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{150~199=2}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{200~299=2.5}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{300+=3}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3907,9 +3939,9 @@
         <f>計算表!A7</f>
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="str">
+      <c r="B7" s="2">
         <f>計算表!B7</f>
-        <v>調整</v>
+        <v>0</v>
       </c>
       <c r="C7" t="str">
         <f>計算表!C7</f>
@@ -9531,9 +9563,9 @@
         <f>計算表!A83</f>
         <v>82</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83" s="2" t="str">
         <f>計算表!B83</f>
-        <v>0</v>
+        <v>調整</v>
       </c>
       <c r="C83" t="str">
         <f>計算表!C83</f>
@@ -9555,29 +9587,29 @@
         <f>計算表!G83</f>
         <v>100</v>
       </c>
-      <c r="H83">
+      <c r="H83" t="str">
         <f>計算表!H83</f>
-        <v>2.5</v>
-      </c>
-      <c r="I83">
+        <v>{1~49=0.5}</v>
+      </c>
+      <c r="I83" t="str">
         <f>計算表!I83</f>
-        <v>0</v>
-      </c>
-      <c r="J83">
+        <v>{50~99=0.75}</v>
+      </c>
+      <c r="J83" t="str">
         <f>計算表!J83</f>
-        <v>0</v>
-      </c>
-      <c r="K83">
+        <v>{100~149=1}</v>
+      </c>
+      <c r="K83" t="str">
         <f>計算表!K83</f>
-        <v>0</v>
-      </c>
-      <c r="L83">
+        <v>{150~199=2}</v>
+      </c>
+      <c r="L83" t="str">
         <f>計算表!L83</f>
-        <v>0</v>
-      </c>
-      <c r="M83">
+        <v>{200~299=2.5}</v>
+      </c>
+      <c r="M83" t="str">
         <f>計算表!M83</f>
-        <v>0</v>
+        <v>{300+=3}</v>
       </c>
       <c r="N83">
         <f>計算表!N83</f>
@@ -9605,9 +9637,9 @@
         <f>計算表!A84</f>
         <v>83</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B84" s="2" t="str">
         <f>計算表!B84</f>
-        <v>0</v>
+        <v>調整</v>
       </c>
       <c r="C84" t="str">
         <f>計算表!C84</f>
@@ -9629,25 +9661,25 @@
         <f>計算表!G84</f>
         <v>5</v>
       </c>
-      <c r="H84">
+      <c r="H84" t="str">
         <f>計算表!H84</f>
-        <v>2.5</v>
-      </c>
-      <c r="I84">
+        <v>{1~49=0.5}</v>
+      </c>
+      <c r="I84" t="str">
         <f>計算表!I84</f>
-        <v>0</v>
-      </c>
-      <c r="J84">
+        <v>{50~99=0.75}</v>
+      </c>
+      <c r="J84" t="str">
         <f>計算表!J84</f>
-        <v>0</v>
-      </c>
-      <c r="K84">
+        <v>{100~149=1}</v>
+      </c>
+      <c r="K84" t="str">
         <f>計算表!K84</f>
-        <v>0</v>
-      </c>
-      <c r="L84">
+        <v>{150~199=1.5}</v>
+      </c>
+      <c r="L84" t="str">
         <f>計算表!L84</f>
-        <v>0</v>
+        <v>{200+=2}</v>
       </c>
       <c r="M84">
         <f>計算表!M84</f>
@@ -38382,9 +38414,6 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>969</v>
-      </c>
       <c r="C7" s="3" t="s">
         <v>18</v>
       </c>
@@ -40273,7 +40302,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <f t="shared" si="2"/>
         <v>80</v>
@@ -40300,7 +40329,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <f t="shared" si="2"/>
         <v>81</v>
@@ -40321,11 +40350,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
+      <c r="B83" s="3" t="s">
+        <v>969</v>
+      </c>
       <c r="C83" s="3" t="s">
         <v>205</v>
       </c>
@@ -40341,15 +40373,33 @@
       <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H83" s="3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
+      <c r="B84" s="3" t="s">
+        <v>969</v>
+      </c>
       <c r="C84" s="3" t="s">
         <v>205</v>
       </c>
@@ -40365,11 +40415,23 @@
       <c r="G84" s="3">
         <v>5</v>
       </c>
-      <c r="H84" s="3">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H84" s="3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="L84" s="3" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -40402,7 +40464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -40423,7 +40485,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -40444,7 +40506,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <f t="shared" si="2"/>
         <v>87</v>
@@ -40465,7 +40527,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <f t="shared" si="2"/>
         <v>88</v>
@@ -40486,7 +40548,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <f t="shared" si="2"/>
         <v>89</v>
@@ -40507,7 +40569,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <f t="shared" si="2"/>
         <v>90</v>
@@ -40543,7 +40605,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <f t="shared" si="2"/>
         <v>91</v>
@@ -40579,7 +40641,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <f t="shared" si="2"/>
         <v>92</v>
@@ -40615,7 +40677,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <f t="shared" si="2"/>
         <v>93</v>
@@ -40639,7 +40701,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <f t="shared" si="2"/>
         <v>94</v>
@@ -40660,7 +40722,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <f t="shared" si="2"/>
         <v>95</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.gemini\antigravity\scratch\Idle-RPG\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEBD8014-3973-46F8-A314-79243465C65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9B9663-92E8-43C2-A9E1-4AB4697D1484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -9125,7 +9125,7 @@
       </c>
       <c r="G80">
         <f>計算表!G80</f>
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="H80">
         <f>計算表!H80</f>
@@ -9199,7 +9199,7 @@
       </c>
       <c r="G81">
         <f>計算表!G81</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H81">
         <f>計算表!H81</f>
@@ -32411,7 +32411,7 @@
         <v>208</v>
       </c>
       <c r="G80" s="3">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="H80" s="3">
         <v>1</v>
@@ -32438,7 +32438,7 @@
         <v>208</v>
       </c>
       <c r="G81" s="3">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H81" s="3">
         <v>1</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.gemini\antigravity\scratch\Idle-RPG\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9B9663-92E8-43C2-A9E1-4AB4697D1484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D169895-DBEC-43FE-9809-DE01009805D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="G165">
         <f>計算表!G165</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H165">
         <f>計算表!H165</f>
@@ -34892,7 +34892,7 @@
         <v>430</v>
       </c>
       <c r="G165" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H165" s="3">
         <v>1.2</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.gemini\antigravity\scratch\Idle-RPG\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D169895-DBEC-43FE-9809-DE01009805D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC998A61-73E8-49E1-8DEE-2261C2D945F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="G165">
         <f>計算表!G165</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H165">
         <f>計算表!H165</f>
@@ -15567,7 +15567,7 @@
       </c>
       <c r="H167">
         <f>計算表!H167</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I167">
         <f>計算表!I167</f>
@@ -22593,7 +22593,7 @@
       </c>
       <c r="G262">
         <f>計算表!G262</f>
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="H262">
         <f>計算表!H262</f>
@@ -34892,7 +34892,7 @@
         <v>430</v>
       </c>
       <c r="G165" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H165" s="3">
         <v>1.2</v>
@@ -34952,7 +34952,7 @@
         <v>1</v>
       </c>
       <c r="H167" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.25">
@@ -37640,7 +37640,7 @@
         <v>732</v>
       </c>
       <c r="G262" s="3">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="H262" s="3">
         <v>20</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.gemini\antigravity\scratch\Idle-RPG\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC998A61-73E8-49E1-8DEE-2261C2D945F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48249068-5DDD-45FE-8D6E-4D8078B46863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1861" uniqueCount="969">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="970">
   <si>
     <t>編號</t>
   </si>
@@ -1617,19 +1617,7 @@
     <t>背包容量</t>
   </si>
   <si>
-    <t>a + 背包擴充次數</t>
-  </si>
-  <si>
-    <t>上限 1000 格；滿了自動分解新進裝備。</t>
-  </si>
-  <si>
     <t>背包擴充費用</t>
-  </si>
-  <si>
-    <t>a × 購買次數²</t>
-  </si>
-  <si>
-    <t>購買次數=本次為第幾次擴充；達 1000 格後不可再擴充。</t>
   </si>
   <si>
     <t>生產線處理間隔</t>
@@ -2969,6 +2957,26 @@
   </si>
   <si>
     <t>煉獄之塔 101~150 層 BOSS 額外掉落魔種；每場獨立判定。</t>
+  </si>
+  <si>
+    <t>調整</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>a=初始格數 b為上限值；滿了自動分解新進裝備。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>a + b × c^購買次數</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>a + 背包擴充上限次數b</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>a=基值值 b=擴充倍數 c=指數底；達上限後不可再擴充。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -17909,9 +17917,9 @@
         <f>計算表!A199</f>
         <v>198</v>
       </c>
-      <c r="B199" s="2">
+      <c r="B199" s="2" t="str">
         <f>計算表!B199</f>
-        <v>0</v>
+        <v>調整</v>
       </c>
       <c r="C199" t="str">
         <f>計算表!C199</f>
@@ -17923,19 +17931,19 @@
       </c>
       <c r="E199" t="str">
         <f>計算表!E199</f>
-        <v>a + 背包擴充次數</v>
+        <v>a + 背包擴充上限次數b</v>
       </c>
       <c r="F199" t="str">
         <f>計算表!F199</f>
-        <v>上限 1000 格；滿了自動分解新進裝備。</v>
+        <v>a=初始格數 b為上限值；滿了自動分解新進裝備。</v>
       </c>
       <c r="G199">
         <f>計算表!G199</f>
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="H199">
         <f>計算表!H199</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I199">
         <f>計算表!I199</f>
@@ -17983,9 +17991,9 @@
         <f>計算表!A200</f>
         <v>199</v>
       </c>
-      <c r="B200" s="2">
+      <c r="B200" s="2" t="str">
         <f>計算表!B200</f>
-        <v>0</v>
+        <v>調整</v>
       </c>
       <c r="C200" t="str">
         <f>計算表!C200</f>
@@ -17997,11 +18005,11 @@
       </c>
       <c r="E200" t="str">
         <f>計算表!E200</f>
-        <v>a × 購買次數²</v>
+        <v>a + b × c^購買次數</v>
       </c>
       <c r="F200" t="str">
         <f>計算表!F200</f>
-        <v>購買次數=本次為第幾次擴充；達 1000 格後不可再擴充。</v>
+        <v>a=基值值 b=擴充倍數 c=指數底；達上限後不可再擴充。</v>
       </c>
       <c r="G200">
         <f>計算表!G200</f>
@@ -18009,11 +18017,11 @@
       </c>
       <c r="H200">
         <f>計算表!H200</f>
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I200">
         <f>計算表!I200</f>
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="J200">
         <f>計算表!J200</f>
@@ -30539,10 +30547,10 @@
         <v>34</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="G7" s="3">
         <v>10</v>
@@ -31091,10 +31099,10 @@
         <v>85</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="G23" s="3">
         <v>8</v>
@@ -31121,10 +31129,10 @@
         <v>86</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="G24" s="3">
         <v>6</v>
@@ -31148,13 +31156,13 @@
         <v>75</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="G25" s="3">
         <v>3</v>
@@ -31181,13 +31189,13 @@
         <v>75</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="G26" s="3">
         <v>2</v>
@@ -31886,13 +31894,13 @@
         <v>157</v>
       </c>
       <c r="D58" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>895</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>898</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>899</v>
       </c>
       <c r="G58" s="3">
         <v>1.8</v>
@@ -31913,13 +31921,13 @@
         <v>157</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="G59" s="3">
         <v>1.8</v>
@@ -31940,13 +31948,13 @@
         <v>157</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="G60" s="3">
         <v>1.8</v>
@@ -32033,13 +32041,13 @@
         <v>157</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="G64" s="3">
         <v>1</v>
@@ -32489,22 +32497,22 @@
         <v>100</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="I83" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="K83" s="3" t="s">
         <v>959</v>
       </c>
-      <c r="J83" s="3" t="s">
+      <c r="L83" s="3" t="s">
         <v>960</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>963</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>964</v>
-      </c>
       <c r="M83" s="3" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
@@ -32528,19 +32536,19 @@
         <v>5</v>
       </c>
       <c r="H84" s="3" t="s">
+        <v>954</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="L84" s="3" t="s">
         <v>958</v>
-      </c>
-      <c r="I84" s="3" t="s">
-        <v>959</v>
-      </c>
-      <c r="J84" s="3" t="s">
-        <v>960</v>
-      </c>
-      <c r="K84" s="3" t="s">
-        <v>961</v>
-      </c>
-      <c r="L84" s="3" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
@@ -32895,10 +32903,10 @@
         <v>206</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="G98" s="3">
         <v>20</v>
@@ -32923,10 +32931,10 @@
         <v>209</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="G99" s="3">
         <v>3</v>
@@ -33166,13 +33174,13 @@
         <v>239</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="G109" s="3">
         <v>100</v>
@@ -33248,22 +33256,22 @@
         <v>239</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="F111" t="s">
         <v>271</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="I111" s="5" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="J111"/>
       <c r="K111"/>
@@ -33620,22 +33628,22 @@
         <v>312</v>
       </c>
       <c r="H124" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>910</v>
+      </c>
+      <c r="J124" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="K124" s="3" t="s">
+        <v>912</v>
+      </c>
+      <c r="L124" s="3" t="s">
         <v>913</v>
       </c>
-      <c r="I124" s="3" t="s">
+      <c r="M124" s="3" t="s">
         <v>914</v>
-      </c>
-      <c r="J124" s="3" t="s">
-        <v>915</v>
-      </c>
-      <c r="K124" s="3" t="s">
-        <v>916</v>
-      </c>
-      <c r="L124" s="3" t="s">
-        <v>917</v>
-      </c>
-      <c r="M124" s="3" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
@@ -33659,22 +33667,22 @@
         <v>314</v>
       </c>
       <c r="H125" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>916</v>
+      </c>
+      <c r="J125" s="3" t="s">
+        <v>917</v>
+      </c>
+      <c r="K125" s="3" t="s">
+        <v>918</v>
+      </c>
+      <c r="L125" s="3" t="s">
         <v>919</v>
       </c>
-      <c r="I125" s="3" t="s">
+      <c r="M125" s="3" t="s">
         <v>920</v>
-      </c>
-      <c r="J125" s="3" t="s">
-        <v>921</v>
-      </c>
-      <c r="K125" s="3" t="s">
-        <v>922</v>
-      </c>
-      <c r="L125" s="3" t="s">
-        <v>923</v>
-      </c>
-      <c r="M125" s="3" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
@@ -33698,22 +33706,22 @@
         <v>316</v>
       </c>
       <c r="H126" s="3" t="s">
+        <v>921</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>922</v>
+      </c>
+      <c r="J126" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="K126" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="L126" s="3" t="s">
         <v>925</v>
       </c>
-      <c r="I126" s="3" t="s">
+      <c r="M126" s="3" t="s">
         <v>926</v>
-      </c>
-      <c r="J126" s="3" t="s">
-        <v>927</v>
-      </c>
-      <c r="K126" s="3" t="s">
-        <v>928</v>
-      </c>
-      <c r="L126" s="3" t="s">
-        <v>929</v>
-      </c>
-      <c r="M126" s="3" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
@@ -33737,22 +33745,22 @@
         <v>318</v>
       </c>
       <c r="H127" s="3" t="s">
+        <v>927</v>
+      </c>
+      <c r="I127" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="J127" s="3" t="s">
+        <v>929</v>
+      </c>
+      <c r="K127" s="3" t="s">
+        <v>930</v>
+      </c>
+      <c r="L127" s="3" t="s">
         <v>931</v>
       </c>
-      <c r="I127" s="3" t="s">
+      <c r="M127" s="3" t="s">
         <v>932</v>
-      </c>
-      <c r="J127" s="3" t="s">
-        <v>933</v>
-      </c>
-      <c r="K127" s="3" t="s">
-        <v>934</v>
-      </c>
-      <c r="L127" s="3" t="s">
-        <v>935</v>
-      </c>
-      <c r="M127" s="3" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
@@ -33776,22 +33784,22 @@
         <v>318</v>
       </c>
       <c r="H128" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="J128" s="3" t="s">
+        <v>935</v>
+      </c>
+      <c r="K128" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="L128" s="3" t="s">
         <v>937</v>
       </c>
-      <c r="I128" s="3" t="s">
+      <c r="M128" s="3" t="s">
         <v>938</v>
-      </c>
-      <c r="J128" s="3" t="s">
-        <v>939</v>
-      </c>
-      <c r="K128" s="3" t="s">
-        <v>940</v>
-      </c>
-      <c r="L128" s="3" t="s">
-        <v>941</v>
-      </c>
-      <c r="M128" s="3" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.25">
@@ -33815,22 +33823,22 @@
         <v>318</v>
       </c>
       <c r="H129" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="I129" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="J129" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="K129" s="3" t="s">
+        <v>942</v>
+      </c>
+      <c r="L129" s="3" t="s">
         <v>943</v>
       </c>
-      <c r="I129" s="3" t="s">
+      <c r="M129" s="3" t="s">
         <v>944</v>
-      </c>
-      <c r="J129" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="K129" s="3" t="s">
-        <v>946</v>
-      </c>
-      <c r="L129" s="3" t="s">
-        <v>947</v>
-      </c>
-      <c r="M129" s="3" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.25">
@@ -33854,22 +33862,22 @@
         <v>318</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="I130" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="J130" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="K130" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="L130" s="3" t="s">
+        <v>948</v>
+      </c>
+      <c r="M130" s="3" t="s">
         <v>949</v>
-      </c>
-      <c r="J130" s="3" t="s">
-        <v>950</v>
-      </c>
-      <c r="K130" s="3" t="s">
-        <v>951</v>
-      </c>
-      <c r="L130" s="3" t="s">
-        <v>952</v>
-      </c>
-      <c r="M130" s="3" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.25">
@@ -33893,22 +33901,22 @@
         <v>318</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="I131" s="3" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="K131" s="3" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="L131" s="3" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="M131" s="3" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.25">
@@ -35746,6 +35754,9 @@
         <f t="shared" si="4"/>
         <v>198</v>
       </c>
+      <c r="B199" s="3" t="s">
+        <v>965</v>
+      </c>
       <c r="C199" s="3" t="s">
         <v>520</v>
       </c>
@@ -35753,13 +35764,16 @@
         <v>526</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>527</v>
+        <v>968</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>528</v>
+        <v>966</v>
       </c>
       <c r="G199" s="3">
-        <v>60</v>
+        <v>100</v>
+      </c>
+      <c r="H199" s="3">
+        <v>1000</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
@@ -35767,20 +35781,29 @@
         <f t="shared" si="4"/>
         <v>199</v>
       </c>
+      <c r="B200" s="3" t="s">
+        <v>965</v>
+      </c>
       <c r="C200" s="3" t="s">
         <v>520</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>530</v>
+        <v>967</v>
       </c>
       <c r="F200" s="3" t="s">
-        <v>531</v>
+        <v>969</v>
       </c>
       <c r="G200" s="3">
         <v>10000</v>
+      </c>
+      <c r="H200" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I200" s="3">
+        <v>1.02</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
@@ -35792,10 +35815,10 @@
         <v>520</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="G201" s="3">
         <v>2</v>
@@ -35807,16 +35830,16 @@
         <v>201</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="F202" s="3" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="G202" s="3">
         <v>0.2</v>
@@ -35828,16 +35851,16 @@
         <v>202</v>
       </c>
       <c r="C203" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="D203" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="D203" s="3" t="s">
-        <v>538</v>
-      </c>
       <c r="E203" s="3" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F203" s="3" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="G203" s="3">
         <v>2</v>
@@ -35849,16 +35872,16 @@
         <v>203</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="F204" s="3" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="G204" s="3">
         <v>3</v>
@@ -35870,16 +35893,16 @@
         <v>204</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
@@ -35888,16 +35911,16 @@
         <v>205</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="F206" s="3" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="G206" s="3">
         <v>100</v>
@@ -35921,16 +35944,16 @@
         <v>206</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="F207" s="3" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="G207" s="3">
         <v>9</v>
@@ -35945,16 +35968,16 @@
         <v>207</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="F208" s="3" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="G208" s="3">
         <v>0.7</v>
@@ -35966,16 +35989,16 @@
         <v>208</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="F209" s="3" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="G209" s="3">
         <v>0.7</v>
@@ -35987,16 +36010,16 @@
         <v>209</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="F210" s="3" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="G210" s="3">
         <v>10</v>
@@ -36014,16 +36037,16 @@
         <v>210</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.25">
@@ -36032,16 +36055,16 @@
         <v>211</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="F212" s="3" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="G212" s="3">
         <v>10000</v>
@@ -36059,16 +36082,16 @@
         <v>212</v>
       </c>
       <c r="C213" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="D213" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="D213" s="3" t="s">
-        <v>569</v>
-      </c>
       <c r="E213" s="3" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="G213" s="3">
         <v>5000</v>
@@ -36083,13 +36106,13 @@
         <v>213</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E214" s="3" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="G214" s="3">
         <v>8</v>
@@ -36101,16 +36124,16 @@
         <v>214</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="F215" s="3" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="G215" s="4">
         <v>10000</v>
@@ -36149,22 +36172,22 @@
         <v>215</v>
       </c>
       <c r="C216" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="G216" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="D216" s="3" t="s">
+      <c r="H216" s="3" t="s">
         <v>578</v>
-      </c>
-      <c r="E216" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="F216" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="G216" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="H216" s="3" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.25">
@@ -36173,25 +36196,25 @@
         <v>216</v>
       </c>
       <c r="C217" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="G217" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="D217" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="E217" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="F217" s="3" t="s">
+      <c r="H217" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="G217" s="3" t="s">
+      <c r="I217" s="3" t="s">
         <v>581</v>
-      </c>
-      <c r="H217" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="I217" s="3" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.25">
@@ -36200,28 +36223,28 @@
         <v>217</v>
       </c>
       <c r="C218" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="G218" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="D218" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="E218" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="F218" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="G218" s="3" t="s">
+      <c r="H218" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="I218" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="H218" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="I218" s="3" t="s">
-        <v>585</v>
-      </c>
       <c r="J218" s="3" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.25">
@@ -36230,28 +36253,28 @@
         <v>218</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F219" s="3" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G219" s="3" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="H219" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="I219" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="I219" s="3" t="s">
-        <v>591</v>
-      </c>
       <c r="J219" s="3" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.25">
@@ -36260,28 +36283,28 @@
         <v>219</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="E220" s="3" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F220" s="3" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="H220" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="I220" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="I220" s="3" t="s">
-        <v>591</v>
-      </c>
       <c r="J220" s="3" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.25">
@@ -36290,31 +36313,31 @@
         <v>220</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F221" s="3" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="H221" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="I221" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="I221" s="3" t="s">
-        <v>591</v>
-      </c>
       <c r="J221" s="3" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="K221" s="3" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="222" spans="1:16" x14ac:dyDescent="0.25">
@@ -36323,31 +36346,31 @@
         <v>221</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D222" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="E222" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="H222" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="I222" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="J222" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="K222" s="3" t="s">
         <v>598</v>
-      </c>
-      <c r="E222" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="F222" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="G222" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="H222" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="I222" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="J222" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="K222" s="3" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="223" spans="1:16" x14ac:dyDescent="0.25">
@@ -36356,31 +36379,31 @@
         <v>222</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="E223" s="3" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F223" s="3" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="H223" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="I223" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="J223" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="K223" s="3" t="s">
         <v>600</v>
-      </c>
-      <c r="I223" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="J223" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="K223" s="3" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="224" spans="1:16" x14ac:dyDescent="0.25">
@@ -36389,31 +36412,31 @@
         <v>223</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="H224" s="3" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="I224" s="3" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="J224" s="3" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="K224" s="3" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.25">
@@ -36422,31 +36445,31 @@
         <v>224</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G225" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="H225" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="H225" s="3" t="s">
-        <v>610</v>
-      </c>
       <c r="I225" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="J225" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="J225" s="3" t="s">
-        <v>611</v>
-      </c>
       <c r="K225" s="3" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.25">
@@ -36455,31 +36478,31 @@
         <v>225</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G226" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="H226" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="H226" s="3" t="s">
-        <v>614</v>
-      </c>
       <c r="I226" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="J226" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="J226" s="3" t="s">
-        <v>615</v>
-      </c>
       <c r="K226" s="3" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.25">
@@ -36488,31 +36511,31 @@
         <v>226</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G227" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="H227" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="H227" s="3" t="s">
-        <v>618</v>
-      </c>
       <c r="I227" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="J227" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="J227" s="3" t="s">
-        <v>619</v>
-      </c>
       <c r="K227" s="3" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
@@ -36521,31 +36544,31 @@
         <v>227</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G228" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="H228" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="H228" s="3" t="s">
-        <v>622</v>
-      </c>
       <c r="I228" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="J228" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="J228" s="3" t="s">
-        <v>623</v>
-      </c>
       <c r="K228" s="3" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
@@ -36554,31 +36577,31 @@
         <v>228</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G229" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="H229" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="H229" s="3" t="s">
-        <v>626</v>
-      </c>
       <c r="I229" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="J229" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="J229" s="3" t="s">
-        <v>627</v>
-      </c>
       <c r="K229" s="3" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.25">
@@ -36587,31 +36610,31 @@
         <v>229</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G230" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="H230" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="H230" s="3" t="s">
-        <v>630</v>
-      </c>
       <c r="I230" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="J230" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="J230" s="3" t="s">
-        <v>631</v>
-      </c>
       <c r="K230" s="3" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
@@ -36620,31 +36643,31 @@
         <v>230</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G231" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="H231" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="H231" s="3" t="s">
-        <v>634</v>
-      </c>
       <c r="I231" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="J231" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="J231" s="3" t="s">
-        <v>635</v>
-      </c>
       <c r="K231" s="3" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.25">
@@ -36653,31 +36676,31 @@
         <v>231</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G232" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="H232" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="H232" s="3" t="s">
-        <v>638</v>
-      </c>
       <c r="I232" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="J232" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="J232" s="3" t="s">
-        <v>639</v>
-      </c>
       <c r="K232" s="3" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.25">
@@ -36686,34 +36709,34 @@
         <v>232</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D233" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="E233" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="H233" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="I233" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="J233" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="K233" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="L233" s="3" t="s">
         <v>641</v>
-      </c>
-      <c r="E233" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="F233" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="G233" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="H233" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="I233" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="J233" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="K233" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="L233" s="3" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.25">
@@ -36722,34 +36745,34 @@
         <v>233</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F234" s="3" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="H234" s="3" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I234" s="3" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="J234" s="3" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="K234" s="3" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="L234" s="3" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.25">
@@ -36758,34 +36781,34 @@
         <v>234</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F235" s="3" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="H235" s="3" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="I235" s="3" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="J235" s="3" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="K235" s="3" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="L235" s="3" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.25">
@@ -36794,28 +36817,28 @@
         <v>235</v>
       </c>
       <c r="C236" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="E236" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="H236" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D236" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="E236" s="3" t="s">
+      <c r="I236" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="F236" s="3" t="s">
+      <c r="J236" s="3" t="s">
         <v>650</v>
-      </c>
-      <c r="G236" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="H236" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="I236" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="J236" s="3" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.25">
@@ -36824,28 +36847,28 @@
         <v>236</v>
       </c>
       <c r="C237" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="E237" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="H237" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D237" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="E237" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="F237" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="G237" s="3" t="s">
-        <v>655</v>
-      </c>
-      <c r="H237" s="3" t="s">
+      <c r="I237" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="I237" s="3" t="s">
-        <v>656</v>
-      </c>
       <c r="J237" s="3" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.25">
@@ -36854,28 +36877,28 @@
         <v>237</v>
       </c>
       <c r="C238" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="E238" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="H238" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D238" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="E238" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="F238" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="G238" s="3" t="s">
-        <v>658</v>
-      </c>
-      <c r="H238" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="I238" s="3" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="J238" s="3" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.25">
@@ -36884,31 +36907,31 @@
         <v>238</v>
       </c>
       <c r="C239" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="E239" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G239" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="H239" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D239" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="E239" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="F239" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="G239" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="H239" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="I239" s="3" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="J239" s="3" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="K239" s="3" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.25">
@@ -36917,31 +36940,31 @@
         <v>239</v>
       </c>
       <c r="C240" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="E240" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="H240" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D240" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="E240" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="F240" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="G240" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="H240" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="I240" s="3" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="J240" s="3" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="K240" s="3" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.25">
@@ -36950,31 +36973,31 @@
         <v>240</v>
       </c>
       <c r="C241" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="E241" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="H241" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D241" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="E241" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="F241" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="G241" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="H241" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="I241" s="3" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="J241" s="3" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="K241" s="3" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.25">
@@ -36983,31 +37006,31 @@
         <v>241</v>
       </c>
       <c r="C242" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="E242" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F242" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G242" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="H242" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D242" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="E242" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="F242" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="G242" s="3" t="s">
-        <v>669</v>
-      </c>
-      <c r="H242" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="I242" s="3" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="J242" s="3" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="K242" s="3" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.25">
@@ -37016,31 +37039,31 @@
         <v>242</v>
       </c>
       <c r="C243" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="E243" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G243" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="H243" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D243" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="E243" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="F243" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="G243" s="3" t="s">
-        <v>673</v>
-      </c>
-      <c r="H243" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="I243" s="3" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="J243" s="3" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="K243" s="3" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.25">
@@ -37049,31 +37072,31 @@
         <v>243</v>
       </c>
       <c r="C244" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="E244" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G244" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="H244" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D244" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="E244" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="F244" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="G244" s="3" t="s">
-        <v>677</v>
-      </c>
-      <c r="H244" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="I244" s="3" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="J244" s="3" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="K244" s="3" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="245" spans="1:16" x14ac:dyDescent="0.25">
@@ -37082,34 +37105,34 @@
         <v>244</v>
       </c>
       <c r="C245" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="E245" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F245" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G245" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="H245" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D245" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="E245" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="F245" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="G245" s="3" t="s">
-        <v>681</v>
-      </c>
-      <c r="H245" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="I245" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="J245" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="K245" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="J245" s="3" t="s">
+      <c r="L245" s="3" t="s">
         <v>679</v>
-      </c>
-      <c r="K245" s="3" t="s">
-        <v>682</v>
-      </c>
-      <c r="L245" s="3" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="246" spans="1:16" x14ac:dyDescent="0.25">
@@ -37118,34 +37141,34 @@
         <v>245</v>
       </c>
       <c r="C246" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="E246" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G246" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="H246" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D246" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="E246" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="F246" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="G246" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="H246" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="I246" s="3" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="J246" s="3" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="K246" s="3" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="L246" s="3" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.25">
@@ -37154,34 +37177,34 @@
         <v>246</v>
       </c>
       <c r="C247" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="E247" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F247" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G247" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="H247" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D247" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="E247" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="F247" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="G247" s="3" t="s">
+      <c r="I247" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="J247" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="K247" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="L247" s="3" t="s">
         <v>687</v>
-      </c>
-      <c r="H247" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="I247" s="3" t="s">
-        <v>688</v>
-      </c>
-      <c r="J247" s="3" t="s">
-        <v>689</v>
-      </c>
-      <c r="K247" s="3" t="s">
-        <v>690</v>
-      </c>
-      <c r="L247" s="3" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.25">
@@ -37190,34 +37213,34 @@
         <v>247</v>
       </c>
       <c r="C248" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="E248" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F248" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G248" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="H248" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D248" s="3" t="s">
-        <v>621</v>
-      </c>
-      <c r="E248" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="F248" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="G248" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="H248" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="I248" s="3" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="J248" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="K248" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="L248" s="3" t="s">
         <v>689</v>
-      </c>
-      <c r="K248" s="3" t="s">
-        <v>690</v>
-      </c>
-      <c r="L248" s="3" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.25">
@@ -37226,34 +37249,34 @@
         <v>248</v>
       </c>
       <c r="C249" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="E249" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F249" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G249" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="H249" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D249" s="3" t="s">
-        <v>625</v>
-      </c>
-      <c r="E249" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="F249" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="G249" s="3" t="s">
-        <v>694</v>
-      </c>
-      <c r="H249" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="I249" s="3" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="J249" s="3" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="K249" s="3" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="L249" s="3" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.25">
@@ -37262,37 +37285,37 @@
         <v>249</v>
       </c>
       <c r="C250" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="E250" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F250" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G250" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="H250" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D250" s="3" t="s">
-        <v>629</v>
-      </c>
-      <c r="E250" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="F250" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="G250" s="3" t="s">
-        <v>696</v>
-      </c>
-      <c r="H250" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="I250" s="3" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="J250" s="3" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="K250" s="3" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="L250" s="3" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="M250" s="3" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.25">
@@ -37301,37 +37324,37 @@
         <v>250</v>
       </c>
       <c r="C251" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="E251" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F251" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G251" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="H251" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D251" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="E251" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="F251" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="G251" s="3" t="s">
-        <v>700</v>
-      </c>
-      <c r="H251" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="I251" s="3" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="J251" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="K251" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="L251" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="M251" s="3" t="s">
         <v>697</v>
-      </c>
-      <c r="K251" s="3" t="s">
-        <v>698</v>
-      </c>
-      <c r="L251" s="3" t="s">
-        <v>693</v>
-      </c>
-      <c r="M251" s="3" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.25">
@@ -37340,37 +37363,37 @@
         <v>251</v>
       </c>
       <c r="C252" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="E252" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F252" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G252" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="H252" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D252" s="3" t="s">
-        <v>637</v>
-      </c>
-      <c r="E252" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="F252" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="G252" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="H252" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="I252" s="3" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="J252" s="3" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="K252" s="3" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="L252" s="3" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="M252" s="3" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.25">
@@ -37379,40 +37402,40 @@
         <v>252</v>
       </c>
       <c r="C253" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="E253" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F253" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G253" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="H253" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D253" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="E253" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="F253" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="G253" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="H253" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="I253" s="3" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="J253" s="3" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="K253" s="3" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="L253" s="3" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="M253" s="3" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="N253" s="3" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
     </row>
     <row r="254" spans="1:16" x14ac:dyDescent="0.25">
@@ -37421,43 +37444,43 @@
         <v>253</v>
       </c>
       <c r="C254" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="E254" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G254" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="H254" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D254" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="E254" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="F254" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="G254" s="3" t="s">
-        <v>706</v>
-      </c>
-      <c r="H254" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="I254" s="3" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="J254" s="3" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="K254" s="3" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="L254" s="3" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="M254" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="N254" s="3" t="s">
         <v>703</v>
       </c>
-      <c r="N254" s="3" t="s">
-        <v>707</v>
-      </c>
       <c r="O254" s="3" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
     </row>
     <row r="255" spans="1:16" x14ac:dyDescent="0.25">
@@ -37466,46 +37489,46 @@
         <v>254</v>
       </c>
       <c r="C255" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="E255" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="G255" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="H255" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="D255" s="3" t="s">
-        <v>647</v>
-      </c>
-      <c r="E255" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="F255" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="G255" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="H255" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="I255" s="3" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="J255" s="3" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="K255" s="3" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="L255" s="3" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="M255" s="3" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="N255" s="3" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="O255" s="3" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="P255" s="3" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.25">
@@ -37514,16 +37537,16 @@
         <v>255</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="F256" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -37532,16 +37555,16 @@
         <v>256</v>
       </c>
       <c r="C257" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="D257" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="D257" s="3" t="s">
-        <v>717</v>
-      </c>
       <c r="E257" s="3" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="G257" s="3">
         <v>0.1</v>
@@ -37553,16 +37576,16 @@
         <v>257</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="F258" s="3" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
@@ -37571,16 +37594,16 @@
         <v>258</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
@@ -37589,16 +37612,16 @@
         <v>259</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="F260" s="3" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="G260" s="3">
         <v>0.5</v>
@@ -37610,13 +37633,13 @@
         <v>260</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="E261" s="3" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="G261" s="3">
         <v>0.4</v>
@@ -37628,16 +37651,16 @@
         <v>261</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="E262" s="3" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="F262" s="3" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="G262" s="3">
         <v>5000</v>
@@ -37655,16 +37678,16 @@
         <v>262</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="E263" s="3" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="F263" s="3" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="G263" s="3">
         <v>3</v>
@@ -37676,16 +37699,16 @@
         <v>263</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="E264" s="3" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.25">
@@ -37694,16 +37717,16 @@
         <v>264</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="E265" s="3" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="G265" s="3">
         <v>30</v>
@@ -37727,16 +37750,16 @@
         <v>265</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="G266" s="3">
         <v>0.75</v>
@@ -37748,13 +37771,13 @@
         <v>266</v>
       </c>
       <c r="C267" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="D267" s="3" t="s">
         <v>742</v>
       </c>
-      <c r="D267" s="3" t="s">
-        <v>746</v>
-      </c>
       <c r="E267" s="3" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="G267" s="3">
         <v>1.25</v>
@@ -37766,16 +37789,16 @@
         <v>267</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="G268" s="3">
         <v>45</v>
@@ -37790,16 +37813,16 @@
         <v>268</v>
       </c>
       <c r="C269" s="3" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.25">
@@ -37808,16 +37831,16 @@
         <v>269</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="F270" s="3" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="G270" s="3">
         <v>0.1</v>
@@ -37829,16 +37852,16 @@
         <v>270</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="G271" s="3">
         <v>24</v>
@@ -37850,16 +37873,16 @@
         <v>271</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="G272" s="3">
         <v>10</v>
@@ -37871,16 +37894,16 @@
         <v>272</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="G273" s="3">
         <v>20</v>
@@ -37892,16 +37915,16 @@
         <v>273</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="E274" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="G274" s="3">
         <v>1</v>
@@ -37928,16 +37951,16 @@
         <v>274</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="E275" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F275" s="3" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="G275" s="3">
         <v>1.35</v>
@@ -37964,16 +37987,16 @@
         <v>275</v>
       </c>
       <c r="C276" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="D276" s="3" t="s">
         <v>761</v>
-      </c>
-      <c r="D276" s="3" t="s">
-        <v>765</v>
       </c>
       <c r="E276" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="G276" s="3">
         <v>1.75</v>
@@ -38000,16 +38023,16 @@
         <v>276</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="E277" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="G277" s="3">
         <v>2.2999999999999998</v>
@@ -38036,16 +38059,16 @@
         <v>277</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="E278" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="G278" s="3">
         <v>3</v>
@@ -38072,16 +38095,16 @@
         <v>278</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="E279" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F279" s="3" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="G279" s="3">
         <v>4</v>
@@ -38108,16 +38131,16 @@
         <v>279</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="E280" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="G280" s="3">
         <v>5.2</v>
@@ -38144,16 +38167,16 @@
         <v>280</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="E281" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F281" s="3" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="G281" s="3">
         <v>6.8</v>
@@ -38180,16 +38203,16 @@
         <v>281</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="E282" s="3" t="s">
         <v>40</v>
       </c>
       <c r="F282" s="3" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="G282" s="3">
         <v>10.199999999999999</v>
@@ -38216,22 +38239,22 @@
         <v>282</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="F283" s="3" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="G283" s="3">
         <v>25</v>
       </c>
       <c r="H283" s="3" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.25">
@@ -38240,22 +38263,22 @@
         <v>283</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="E284" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="F284" s="3" t="s">
         <v>827</v>
-      </c>
-      <c r="F284" s="3" t="s">
-        <v>831</v>
       </c>
       <c r="G284" s="3">
         <v>20</v>
       </c>
       <c r="H284" s="3" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.25">
@@ -38264,22 +38287,22 @@
         <v>284</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="F285" s="3" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G285" s="3">
         <v>25</v>
       </c>
       <c r="H285" s="3" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.25">
@@ -38288,22 +38311,22 @@
         <v>285</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="F286" s="3" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="G286" s="3">
         <v>20</v>
       </c>
       <c r="H286" s="3" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.25">
@@ -38312,22 +38335,22 @@
         <v>286</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="F287" s="3" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="G287" s="3">
         <v>0.4</v>
       </c>
       <c r="H287" s="3" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.25">
@@ -38336,22 +38359,22 @@
         <v>287</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="F288" s="3" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="G288" s="3">
         <v>3</v>
       </c>
       <c r="H288" s="3" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
@@ -38360,22 +38383,22 @@
         <v>288</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="F289" s="3" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="G289" s="3">
         <v>1.5</v>
       </c>
       <c r="H289" s="3" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
@@ -38384,22 +38407,22 @@
         <v>289</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="F290" s="3" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="G290" s="3">
         <v>0.15</v>
       </c>
       <c r="H290" s="3" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
@@ -38408,22 +38431,22 @@
         <v>290</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="E291" s="3" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="F291" s="3" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="G291" s="3">
         <v>0.5</v>
       </c>
       <c r="H291" s="3" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
@@ -38432,22 +38455,22 @@
         <v>291</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="E292" s="3" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="F292" s="3" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="G292" s="3">
         <v>25</v>
       </c>
       <c r="H292" s="3" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
@@ -38456,22 +38479,22 @@
         <v>292</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="E293" s="3" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="F293" s="3" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="G293" s="3">
         <v>8</v>
       </c>
       <c r="H293" s="3" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
@@ -38480,22 +38503,22 @@
         <v>293</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="E294" s="3" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="F294" s="3" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="G294" s="3">
         <v>15</v>
       </c>
       <c r="H294" s="3" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
@@ -38504,16 +38527,16 @@
         <v>294</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="E295" s="3" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="F295" s="3" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="G295" s="3">
         <v>0.8</v>
@@ -38525,16 +38548,16 @@
         <v>295</v>
       </c>
       <c r="C296" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="D296" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="D296" s="3" t="s">
-        <v>857</v>
-      </c>
       <c r="E296" s="3" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="F296" s="3" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="G296" s="3">
         <v>3</v>
@@ -38546,16 +38569,16 @@
         <v>296</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="F297" s="3" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="G297" s="3">
         <v>7</v>
@@ -38567,16 +38590,16 @@
         <v>297</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="F298" s="3" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="G298" s="3">
         <v>10</v>
@@ -38588,16 +38611,16 @@
         <v>298</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="F299" s="3" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="G299" s="3">
         <v>2</v>
@@ -38609,16 +38632,16 @@
         <v>299</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="F300" s="3" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="G300" s="3">
         <v>5</v>
@@ -38633,16 +38656,16 @@
         <v>300</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="E301" s="3" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="F301" s="3" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="G301" s="3">
         <v>8</v>
@@ -38654,16 +38677,16 @@
         <v>301</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D302" s="3" t="s">
         <v>85</v>
       </c>
       <c r="E302" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F302" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G302" s="3">
         <v>1</v>
@@ -38675,16 +38698,16 @@
         <v>302</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F303" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G303" s="3">
         <v>2.6</v>
@@ -38696,16 +38719,16 @@
         <v>303</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D304" s="3" t="s">
         <v>86</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F304" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G304" s="3">
         <v>1</v>
@@ -38717,16 +38740,16 @@
         <v>304</v>
       </c>
       <c r="C305" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D305" s="3" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F305" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G305" s="3">
         <v>2.6</v>
@@ -38738,16 +38761,16 @@
         <v>305</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F306" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G306" s="3">
         <v>0.16</v>
@@ -38759,16 +38782,16 @@
         <v>306</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="E307" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F307" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G307" s="3">
         <v>2.2000000000000002</v>
@@ -38780,16 +38803,16 @@
         <v>307</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F308" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G308" s="3">
         <v>0.6</v>
@@ -38801,16 +38824,16 @@
         <v>308</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D309" s="3" t="s">
         <v>87</v>
       </c>
       <c r="E309" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F309" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G309" s="3">
         <v>0.9</v>
@@ -38822,16 +38845,16 @@
         <v>309</v>
       </c>
       <c r="C310" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="E310" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F310" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G310" s="3">
         <v>1.8</v>
@@ -38843,16 +38866,16 @@
         <v>310</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D311" s="3" t="s">
         <v>88</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F311" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G311" s="3">
         <v>0.9</v>
@@ -38864,16 +38887,16 @@
         <v>311</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="E312" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F312" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G312" s="3">
         <v>0.25</v>
@@ -38885,16 +38908,16 @@
         <v>312</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D313" s="3" t="s">
         <v>82</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F313" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G313" s="3">
         <v>2</v>
@@ -38906,16 +38929,16 @@
         <v>313</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="E314" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F314" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G314" s="3">
         <v>1.8</v>
@@ -38927,16 +38950,16 @@
         <v>314</v>
       </c>
       <c r="C315" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F315" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G315" s="3">
         <v>1.8</v>
@@ -38948,16 +38971,16 @@
         <v>315</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="E316" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F316" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G316" s="3">
         <v>1.8</v>
@@ -38969,16 +38992,16 @@
         <v>316</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="E317" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F317" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G317" s="3">
         <v>1.8</v>
@@ -38990,16 +39013,16 @@
         <v>317</v>
       </c>
       <c r="C318" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="E318" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F318" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G318" s="3">
         <v>2.8</v>
@@ -39011,16 +39034,16 @@
         <v>318</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="E319" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F319" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G319" s="3">
         <v>2.4</v>
@@ -39032,16 +39055,16 @@
         <v>319</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="E320" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F320" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G320" s="3">
         <v>0.9</v>
@@ -39053,16 +39076,16 @@
         <v>320</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="E321" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F321" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G321" s="3">
         <v>2.2000000000000002</v>
@@ -39074,16 +39097,16 @@
         <v>321</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="E322" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F322" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G322" s="3">
         <v>2.2000000000000002</v>
@@ -39095,16 +39118,16 @@
         <v>322</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="E323" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F323" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G323" s="3">
         <v>1.2</v>
@@ -39116,16 +39139,16 @@
         <v>323</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="E324" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F324" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G324" s="3">
         <v>2</v>
@@ -39137,16 +39160,16 @@
         <v>324</v>
       </c>
       <c r="C325" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="E325" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F325" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G325" s="3">
         <v>1.4</v>
@@ -39158,16 +39181,16 @@
         <v>325</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="E326" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F326" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G326" s="3">
         <v>2.2000000000000002</v>
@@ -39179,16 +39202,16 @@
         <v>326</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="E327" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F327" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G327" s="3">
         <v>1.4</v>
@@ -39200,16 +39223,16 @@
         <v>327</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="E328" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F328" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G328" s="3">
         <v>1.2</v>
@@ -39221,16 +39244,16 @@
         <v>328</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="E329" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F329" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G329" s="3">
         <v>1.2</v>
@@ -39242,16 +39265,16 @@
         <v>329</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="E330" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F330" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G330" s="3">
         <v>1.2</v>
@@ -39263,16 +39286,16 @@
         <v>330</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="E331" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F331" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G331" s="3">
         <v>1.4</v>
@@ -39284,16 +39307,16 @@
         <v>331</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D332" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E332" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F332" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G332" s="3">
         <v>1</v>
@@ -39305,16 +39328,16 @@
         <v>332</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="E333" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F333" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G333" s="3">
         <v>1</v>
@@ -39326,16 +39349,16 @@
         <v>333</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="E334" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F334" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G334" s="3">
         <v>1</v>
@@ -39347,16 +39370,16 @@
         <v>334</v>
       </c>
       <c r="C335" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="E335" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F335" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G335" s="3">
         <v>1</v>
@@ -39368,16 +39391,16 @@
         <v>335</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="E336" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F336" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G336" s="3">
         <v>2</v>
@@ -39389,16 +39412,16 @@
         <v>336</v>
       </c>
       <c r="C337" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="E337" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F337" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G337" s="3">
         <v>1.2</v>
@@ -39410,16 +39433,16 @@
         <v>337</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="E338" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F338" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G338" s="3">
         <v>2.2000000000000002</v>
@@ -39431,16 +39454,16 @@
         <v>338</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="E339" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F339" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G339" s="3">
         <v>1.2</v>
@@ -39452,16 +39475,16 @@
         <v>339</v>
       </c>
       <c r="C340" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="E340" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F340" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G340" s="3">
         <v>1</v>
@@ -39473,16 +39496,16 @@
         <v>340</v>
       </c>
       <c r="C341" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="E341" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F341" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G341" s="3">
         <v>2</v>
@@ -39494,16 +39517,16 @@
         <v>341</v>
       </c>
       <c r="C342" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="E342" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F342" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G342" s="3">
         <v>2</v>
@@ -39515,16 +39538,16 @@
         <v>342</v>
       </c>
       <c r="C343" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="E343" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F343" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G343" s="3">
         <v>0.8</v>
@@ -39536,16 +39559,16 @@
         <v>343</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="E344" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F344" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G344" s="3">
         <v>0.8</v>
@@ -39557,16 +39580,16 @@
         <v>344</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="E345" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F345" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G345" s="3">
         <v>0.8</v>
@@ -39578,16 +39601,16 @@
         <v>345</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="E346" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F346" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G346" s="3">
         <v>0.8</v>
@@ -39599,16 +39622,16 @@
         <v>346</v>
       </c>
       <c r="C347" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="E347" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F347" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G347" s="3">
         <v>0.8</v>
@@ -39620,16 +39643,16 @@
         <v>347</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="E348" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F348" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G348" s="3">
         <v>0.8</v>
@@ -39641,16 +39664,16 @@
         <v>348</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="E349" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F349" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G349" s="3">
         <v>1.2</v>
@@ -39662,16 +39685,16 @@
         <v>349</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="E350" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F350" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G350" s="3">
         <v>1.5</v>
@@ -39683,16 +39706,16 @@
         <v>350</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="E351" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F351" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G351" s="3">
         <v>0.8</v>
@@ -39704,16 +39727,16 @@
         <v>351</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="E352" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F352" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G352" s="3">
         <v>0.8</v>
@@ -39725,16 +39748,16 @@
         <v>352</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="E353" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F353" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G353" s="3">
         <v>0.8</v>
@@ -39746,16 +39769,16 @@
         <v>353</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="E354" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F354" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G354" s="3">
         <v>1.5</v>
@@ -39767,16 +39790,16 @@
         <v>354</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D355" s="3" t="s">
         <v>106</v>
       </c>
       <c r="E355" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F355" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G355" s="3">
         <v>0.8</v>
@@ -39788,16 +39811,16 @@
         <v>355</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="E356" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F356" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G356" s="3">
         <v>0.8</v>
@@ -39809,16 +39832,16 @@
         <v>356</v>
       </c>
       <c r="C357" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="E357" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F357" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G357" s="3">
         <v>0.8</v>
@@ -39830,16 +39853,16 @@
         <v>357</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="E358" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F358" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G358" s="3">
         <v>1.2</v>
@@ -39851,16 +39874,16 @@
         <v>358</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="E359" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F359" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G359" s="3">
         <v>1</v>
@@ -39872,16 +39895,16 @@
         <v>359</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E360" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F360" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G360" s="3">
         <v>1.2</v>
@@ -39893,16 +39916,16 @@
         <v>360</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="E361" s="3" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F361" s="3" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G361" s="3">
         <v>1</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.gemini\antigravity\scratch\Idle-RPG\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48249068-5DDD-45FE-8D6E-4D8078B46863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63A2138-A6E3-4ED4-974C-09909B5692BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="970">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="973">
   <si>
     <t>編號</t>
   </si>
@@ -2976,6 +2976,18 @@
   </si>
   <si>
     <t>a=基值值 b=擴充倍數 c=指數底；達上限後不可再擴充。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{1~50,a=10000,b=1.8}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{51~100,a=50000,b=2}</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{101~150,a=100000,b=2.2}</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -10369,9 +10381,9 @@
         <f>計算表!A97</f>
         <v>96</v>
       </c>
-      <c r="B97" s="2">
+      <c r="B97" s="2" t="str">
         <f>計算表!B97</f>
-        <v>0</v>
+        <v>調整</v>
       </c>
       <c r="C97" t="str">
         <f>計算表!C97</f>
@@ -10389,17 +10401,17 @@
         <f>計算表!F97</f>
         <v>開始挑戰前扣除，失敗或撤退不退回。</v>
       </c>
-      <c r="G97">
+      <c r="G97" t="str">
         <f>計算表!G97</f>
-        <v>100000</v>
-      </c>
-      <c r="H97">
+        <v>{1~50,a=10000,b=1.8}</v>
+      </c>
+      <c r="H97" t="str">
         <f>計算表!H97</f>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="I97">
+        <v>{51~100,a=50000,b=2}</v>
+      </c>
+      <c r="I97" t="str">
         <f>計算表!I97</f>
-        <v>0</v>
+        <v>{101~150,a=100000,b=2.2}</v>
       </c>
       <c r="J97">
         <f>計算表!J97</f>
@@ -17917,9 +17929,9 @@
         <f>計算表!A199</f>
         <v>198</v>
       </c>
-      <c r="B199" s="2" t="str">
+      <c r="B199" s="2">
         <f>計算表!B199</f>
-        <v>調整</v>
+        <v>0</v>
       </c>
       <c r="C199" t="str">
         <f>計算表!C199</f>
@@ -17991,9 +18003,9 @@
         <f>計算表!A200</f>
         <v>199</v>
       </c>
-      <c r="B200" s="2" t="str">
+      <c r="B200" s="2">
         <f>計算表!B200</f>
-        <v>調整</v>
+        <v>0</v>
       </c>
       <c r="C200" t="str">
         <f>計算表!C200</f>
@@ -30339,7 +30351,7 @@
     <col min="4" max="4" width="17.85546875" style="3" customWidth="1"/>
     <col min="5" max="5" width="52.140625" style="3" customWidth="1"/>
     <col min="6" max="6" width="110.42578125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="17.85546875" style="3" customWidth="1"/>
     <col min="8" max="8" width="15.140625" style="3" customWidth="1"/>
     <col min="9" max="9" width="15" style="3" customWidth="1"/>
     <col min="10" max="10" width="14.28515625" style="3" customWidth="1"/>
@@ -32871,6 +32883,9 @@
         <f t="shared" si="2"/>
         <v>96</v>
       </c>
+      <c r="B97" s="3" t="s">
+        <v>965</v>
+      </c>
       <c r="C97" s="3" t="s">
         <v>239</v>
       </c>
@@ -32883,11 +32898,14 @@
       <c r="F97" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="G97" s="3">
-        <v>100000</v>
-      </c>
-      <c r="H97" s="3">
-        <v>2.2000000000000002</v>
+      <c r="G97" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>972</v>
       </c>
     </row>
     <row r="98" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
@@ -35754,9 +35772,6 @@
         <f t="shared" si="4"/>
         <v>198</v>
       </c>
-      <c r="B199" s="3" t="s">
-        <v>965</v>
-      </c>
       <c r="C199" s="3" t="s">
         <v>520</v>
       </c>
@@ -35780,9 +35795,6 @@
       <c r="A200" s="3">
         <f t="shared" si="4"/>
         <v>199</v>
-      </c>
-      <c r="B200" s="3" t="s">
-        <v>965</v>
       </c>
       <c r="C200" s="3" t="s">
         <v>520</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="973">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="974">
   <si>
     <t>編號</t>
   </si>
@@ -2989,6 +2989,9 @@
   <si>
     <t>{101~150,a=100000,b=2.2}</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">總魔攻×a（地獄之塔再×b）</t>
   </si>
 </sst>
 </file>
@@ -10839,7 +10842,7 @@
       </c>
       <c r="E103" t="str">
         <f>計算表!E103</f>
-        <v>基準攻擊×a（地獄之塔再×b）</v>
+        <v>總魔攻×a（地獄之塔再×b）</v>
       </c>
       <c r="F103" t="str">
         <f>計算表!F103</f>
@@ -10851,7 +10854,7 @@
       </c>
       <c r="H103">
         <f>計算表!H103</f>
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I103">
         <f>計算表!I103</f>
@@ -33048,7 +33051,7 @@
         <v>260</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>251</v>
+        <v>973</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>261</v>
@@ -33057,7 +33060,7 @@
         <v>3</v>
       </c>
       <c r="H103" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:18" x14ac:dyDescent="0.25">

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.gemini\antigravity\scratch\Idle-RPG\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\develop\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5431D562-9D50-4909-B6D5-CFEA9D2E0B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08E94DB-E83D-49A9-BD15-FEB1FF3367A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -3326,9 +3326,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R323"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3384,7 +3384,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2">
         <f>計算表!A2</f>
         <v>1</v>
@@ -3441,7 +3441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>計算表!A3</f>
         <v>2</v>
@@ -3498,7 +3498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>計算表!A4</f>
         <v>3</v>
@@ -3555,7 +3555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>計算表!A5</f>
         <v>4</v>
@@ -3612,7 +3612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>計算表!A6</f>
         <v>5</v>
@@ -3669,7 +3669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>計算表!A7</f>
         <v>6</v>
@@ -3726,7 +3726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>計算表!A8</f>
         <v>7</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>計算表!A9</f>
         <v>8</v>
@@ -3840,7 +3840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>計算表!A10</f>
         <v>9</v>
@@ -3897,7 +3897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>計算表!A11</f>
         <v>10</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>計算表!A12</f>
         <v>11</v>
@@ -4011,7 +4011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>計算表!A13</f>
         <v>12</v>
@@ -4068,7 +4068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>計算表!A14</f>
         <v>13</v>
@@ -4125,7 +4125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>計算表!A15</f>
         <v>14</v>
@@ -4182,7 +4182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>計算表!A16</f>
         <v>15</v>
@@ -4239,7 +4239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>計算表!A17</f>
         <v>16</v>
@@ -4296,7 +4296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>計算表!A18</f>
         <v>17</v>
@@ -4353,7 +4353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>計算表!A19</f>
         <v>18</v>
@@ -4410,7 +4410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>計算表!A20</f>
         <v>19</v>
@@ -4467,7 +4467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>計算表!A21</f>
         <v>20</v>
@@ -4524,7 +4524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>計算表!A22</f>
         <v>21</v>
@@ -4581,7 +4581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>計算表!A23</f>
         <v>22</v>
@@ -4638,7 +4638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>計算表!A24</f>
         <v>23</v>
@@ -4695,7 +4695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>計算表!A25</f>
         <v>24</v>
@@ -4752,7 +4752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>計算表!A26</f>
         <v>25</v>
@@ -4809,7 +4809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>計算表!A27</f>
         <v>26</v>
@@ -4866,7 +4866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>計算表!A28</f>
         <v>27</v>
@@ -4923,7 +4923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>計算表!A29</f>
         <v>28</v>
@@ -4980,7 +4980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>計算表!A30</f>
         <v>29</v>
@@ -5037,7 +5037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>計算表!A31</f>
         <v>30</v>
@@ -5094,7 +5094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>計算表!A32</f>
         <v>31</v>
@@ -5151,7 +5151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>計算表!A33</f>
         <v>32</v>
@@ -5208,7 +5208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>計算表!A34</f>
         <v>33</v>
@@ -5265,7 +5265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35">
         <f>計算表!A35</f>
         <v>34</v>
@@ -5322,7 +5322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36">
         <f>計算表!A36</f>
         <v>35</v>
@@ -5379,7 +5379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37">
         <f>計算表!A37</f>
         <v>36</v>
@@ -5436,7 +5436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38">
         <f>計算表!A38</f>
         <v>37</v>
@@ -5493,7 +5493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39">
         <f>計算表!A39</f>
         <v>38</v>
@@ -5550,7 +5550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40">
         <f>計算表!A40</f>
         <v>39</v>
@@ -5607,7 +5607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41">
         <f>計算表!A41</f>
         <v>40</v>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42">
         <f>計算表!A42</f>
         <v>41</v>
@@ -5721,7 +5721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43">
         <f>計算表!A43</f>
         <v>42</v>
@@ -5778,7 +5778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44">
         <f>計算表!A44</f>
         <v>43</v>
@@ -5835,7 +5835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45">
         <f>計算表!A45</f>
         <v>44</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46">
         <f>計算表!A46</f>
         <v>45</v>
@@ -5949,7 +5949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47">
         <f>計算表!A47</f>
         <v>46</v>
@@ -6006,7 +6006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48">
         <f>計算表!A48</f>
         <v>47</v>
@@ -6063,7 +6063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49">
         <f>計算表!A49</f>
         <v>48</v>
@@ -6120,7 +6120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50">
         <f>計算表!A50</f>
         <v>49</v>
@@ -6177,7 +6177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51">
         <f>計算表!A51</f>
         <v>50</v>
@@ -6234,7 +6234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52">
         <f>計算表!A52</f>
         <v>51</v>
@@ -6291,7 +6291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53">
         <f>計算表!A53</f>
         <v>52</v>
@@ -6348,7 +6348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54">
         <f>計算表!A54</f>
         <v>53</v>
@@ -6405,7 +6405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55">
         <f>計算表!A55</f>
         <v>54</v>
@@ -6462,7 +6462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56">
         <f>計算表!A56</f>
         <v>55</v>
@@ -6519,7 +6519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57">
         <f>計算表!A57</f>
         <v>56</v>
@@ -6576,7 +6576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58">
         <f>計算表!A58</f>
         <v>57</v>
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59">
         <f>計算表!A59</f>
         <v>58</v>
@@ -6690,7 +6690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60">
         <f>計算表!A60</f>
         <v>59</v>
@@ -6747,7 +6747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61">
         <f>計算表!A61</f>
         <v>60</v>
@@ -6804,7 +6804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62">
         <f>計算表!A62</f>
         <v>61</v>
@@ -6861,7 +6861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63">
         <f>計算表!A63</f>
         <v>62</v>
@@ -6918,7 +6918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64">
         <f>計算表!A64</f>
         <v>63</v>
@@ -6975,7 +6975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65">
         <f>計算表!A65</f>
         <v>64</v>
@@ -7032,7 +7032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66">
         <f>計算表!A66</f>
         <v>65</v>
@@ -7089,7 +7089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67">
         <f>計算表!A67</f>
         <v>66</v>
@@ -7146,7 +7146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68">
         <f>計算表!A68</f>
         <v>67</v>
@@ -7203,7 +7203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69">
         <f>計算表!A69</f>
         <v>68</v>
@@ -7260,7 +7260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70">
         <f>計算表!A70</f>
         <v>69</v>
@@ -7317,7 +7317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71">
         <f>計算表!A71</f>
         <v>70</v>
@@ -7374,7 +7374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72">
         <f>計算表!A72</f>
         <v>71</v>
@@ -7431,7 +7431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73">
         <f>計算表!A73</f>
         <v>72</v>
@@ -7488,7 +7488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74">
         <f>計算表!A74</f>
         <v>73</v>
@@ -7545,7 +7545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75">
         <f>計算表!A75</f>
         <v>74</v>
@@ -7602,7 +7602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76">
         <f>計算表!A76</f>
         <v>75</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77">
         <f>計算表!A77</f>
         <v>76</v>
@@ -7716,7 +7716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78">
         <f>計算表!A78</f>
         <v>77</v>
@@ -7773,7 +7773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79">
         <f>計算表!A79</f>
         <v>78</v>
@@ -7830,7 +7830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80">
         <f>計算表!A80</f>
         <v>79</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81">
         <f>計算表!A81</f>
         <v>80</v>
@@ -7944,7 +7944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82">
         <f>計算表!A82</f>
         <v>81</v>
@@ -8001,7 +8001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83">
         <f>計算表!A83</f>
         <v>82</v>
@@ -8058,7 +8058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84">
         <f>計算表!A84</f>
         <v>83</v>
@@ -8115,7 +8115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85">
         <f>計算表!A85</f>
         <v>84</v>
@@ -8172,7 +8172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86">
         <f>計算表!A86</f>
         <v>85</v>
@@ -8229,7 +8229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87">
         <f>計算表!A87</f>
         <v>86</v>
@@ -8286,7 +8286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88">
         <f>計算表!A88</f>
         <v>87</v>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89">
         <f>計算表!A89</f>
         <v>88</v>
@@ -8400,7 +8400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90">
         <f>計算表!A90</f>
         <v>89</v>
@@ -8457,7 +8457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91">
         <f>計算表!A91</f>
         <v>90</v>
@@ -8514,7 +8514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92">
         <f>計算表!A92</f>
         <v>91</v>
@@ -8571,7 +8571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93">
         <f>計算表!A93</f>
         <v>92</v>
@@ -8628,7 +8628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94">
         <f>計算表!A94</f>
         <v>93</v>
@@ -8685,7 +8685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95">
         <f>計算表!A95</f>
         <v>94</v>
@@ -8742,7 +8742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96">
         <f>計算表!A96</f>
         <v>95</v>
@@ -8799,7 +8799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97">
         <f>計算表!A97</f>
         <v>96</v>
@@ -8856,7 +8856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98">
         <f>計算表!A98</f>
         <v>97</v>
@@ -8913,7 +8913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99">
         <f>計算表!A99</f>
         <v>98</v>
@@ -8970,7 +8970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100">
         <f>計算表!A100</f>
         <v>99</v>
@@ -9027,7 +9027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101">
         <f>計算表!A101</f>
         <v>100</v>
@@ -9084,7 +9084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102">
         <f>計算表!A102</f>
         <v>101</v>
@@ -9141,7 +9141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103">
         <f>計算表!A103</f>
         <v>102</v>
@@ -9198,7 +9198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104">
         <f>計算表!A104</f>
         <v>103</v>
@@ -9255,7 +9255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105">
         <f>計算表!A105</f>
         <v>104</v>
@@ -9312,7 +9312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106">
         <f>計算表!A106</f>
         <v>105</v>
@@ -9369,7 +9369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107">
         <f>計算表!A107</f>
         <v>106</v>
@@ -9426,7 +9426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108">
         <f>計算表!A108</f>
         <v>107</v>
@@ -9483,7 +9483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109">
         <f>計算表!A109</f>
         <v>108</v>
@@ -9540,7 +9540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110">
         <f>計算表!A110</f>
         <v>109</v>
@@ -9597,7 +9597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111">
         <f>計算表!A111</f>
         <v>110</v>
@@ -9654,7 +9654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112">
         <f>計算表!A112</f>
         <v>111</v>
@@ -9711,7 +9711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113">
         <f>計算表!A113</f>
         <v>112</v>
@@ -9768,7 +9768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114">
         <f>計算表!A114</f>
         <v>113</v>
@@ -9825,7 +9825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115">
         <f>計算表!A115</f>
         <v>114</v>
@@ -9882,7 +9882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116">
         <f>計算表!A116</f>
         <v>115</v>
@@ -9939,7 +9939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117">
         <f>計算表!A117</f>
         <v>116</v>
@@ -9996,7 +9996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118">
         <f>計算表!A118</f>
         <v>117</v>
@@ -10053,7 +10053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119">
         <f>計算表!A119</f>
         <v>118</v>
@@ -10110,7 +10110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120">
         <f>計算表!A120</f>
         <v>119</v>
@@ -10167,7 +10167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121">
         <f>計算表!A121</f>
         <v>120</v>
@@ -10224,7 +10224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122">
         <f>計算表!A122</f>
         <v>121</v>
@@ -10281,7 +10281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123">
         <f>計算表!A123</f>
         <v>122</v>
@@ -10338,7 +10338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124">
         <f>計算表!A124</f>
         <v>123</v>
@@ -10395,7 +10395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125">
         <f>計算表!A125</f>
         <v>124</v>
@@ -10452,7 +10452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126">
         <f>計算表!A126</f>
         <v>125</v>
@@ -10509,7 +10509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127">
         <f>計算表!A127</f>
         <v>126</v>
@@ -10566,7 +10566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128">
         <f>計算表!A128</f>
         <v>127</v>
@@ -10623,7 +10623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129">
         <f>計算表!A129</f>
         <v>128</v>
@@ -10680,7 +10680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130">
         <f>計算表!A130</f>
         <v>129</v>
@@ -10737,7 +10737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131">
         <f>計算表!A131</f>
         <v>130</v>
@@ -10794,7 +10794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132">
         <f>計算表!A132</f>
         <v>131</v>
@@ -10851,7 +10851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133">
         <f>計算表!A133</f>
         <v>132</v>
@@ -10908,7 +10908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134">
         <f>計算表!A134</f>
         <v>133</v>
@@ -10965,7 +10965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135">
         <f>計算表!A135</f>
         <v>134</v>
@@ -11022,7 +11022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136">
         <f>計算表!A136</f>
         <v>135</v>
@@ -11079,7 +11079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137">
         <f>計算表!A137</f>
         <v>136</v>
@@ -11136,7 +11136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138">
         <f>計算表!A138</f>
         <v>137</v>
@@ -11193,7 +11193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139">
         <f>計算表!A139</f>
         <v>138</v>
@@ -11250,7 +11250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140">
         <f>計算表!A140</f>
         <v>139</v>
@@ -11307,7 +11307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141">
         <f>計算表!A141</f>
         <v>140</v>
@@ -11364,7 +11364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142">
         <f>計算表!A142</f>
         <v>141</v>
@@ -11421,7 +11421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143">
         <f>計算表!A143</f>
         <v>142</v>
@@ -11478,7 +11478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144">
         <f>計算表!A144</f>
         <v>143</v>
@@ -11535,7 +11535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145">
         <f>計算表!A145</f>
         <v>144</v>
@@ -11592,7 +11592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146">
         <f>計算表!A146</f>
         <v>145</v>
@@ -11649,7 +11649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147">
         <f>計算表!A147</f>
         <v>146</v>
@@ -11706,7 +11706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148">
         <f>計算表!A148</f>
         <v>147</v>
@@ -11763,7 +11763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149">
         <f>計算表!A149</f>
         <v>148</v>
@@ -11820,7 +11820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150">
         <f>計算表!A150</f>
         <v>149</v>
@@ -11877,7 +11877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151">
         <f>計算表!A151</f>
         <v>150</v>
@@ -11934,7 +11934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152">
         <f>計算表!A152</f>
         <v>151</v>
@@ -11991,7 +11991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153">
         <f>計算表!A153</f>
         <v>152</v>
@@ -12048,7 +12048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154">
         <f>計算表!A154</f>
         <v>153</v>
@@ -12105,7 +12105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155">
         <f>計算表!A155</f>
         <v>154</v>
@@ -12162,7 +12162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156">
         <f>計算表!A156</f>
         <v>155</v>
@@ -12219,7 +12219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157">
         <f>計算表!A157</f>
         <v>156</v>
@@ -12276,7 +12276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158">
         <f>計算表!A158</f>
         <v>157</v>
@@ -12333,7 +12333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159">
         <f>計算表!A159</f>
         <v>158</v>
@@ -12390,7 +12390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160">
         <f>計算表!A160</f>
         <v>159</v>
@@ -12447,7 +12447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161">
         <f>計算表!A161</f>
         <v>160</v>
@@ -12504,7 +12504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162">
         <f>計算表!A162</f>
         <v>161</v>
@@ -12561,7 +12561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163">
         <f>計算表!A163</f>
         <v>162</v>
@@ -12618,7 +12618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164">
         <f>計算表!A164</f>
         <v>163</v>
@@ -12675,7 +12675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165">
         <f>計算表!A165</f>
         <v>164</v>
@@ -12732,7 +12732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166">
         <f>計算表!A166</f>
         <v>165</v>
@@ -12789,7 +12789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167">
         <f>計算表!A167</f>
         <v>166</v>
@@ -12846,7 +12846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168">
         <f>計算表!A168</f>
         <v>167</v>
@@ -12903,7 +12903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169">
         <f>計算表!A169</f>
         <v>168</v>
@@ -12960,7 +12960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170">
         <f>計算表!A170</f>
         <v>169</v>
@@ -13017,7 +13017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171">
         <f>計算表!A171</f>
         <v>170</v>
@@ -13074,7 +13074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172">
         <f>計算表!A172</f>
         <v>171</v>
@@ -13131,7 +13131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173">
         <f>計算表!A173</f>
         <v>172</v>
@@ -13188,7 +13188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174">
         <f>計算表!A174</f>
         <v>173</v>
@@ -13245,7 +13245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175">
         <f>計算表!A175</f>
         <v>174</v>
@@ -13302,7 +13302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176">
         <f>計算表!A176</f>
         <v>175</v>
@@ -13359,7 +13359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177">
         <f>計算表!A177</f>
         <v>176</v>
@@ -13416,7 +13416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178">
         <f>計算表!A178</f>
         <v>177</v>
@@ -13473,7 +13473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179">
         <f>計算表!A179</f>
         <v>178</v>
@@ -13530,7 +13530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180">
         <f>計算表!A180</f>
         <v>179</v>
@@ -13587,7 +13587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181">
         <f>計算表!A181</f>
         <v>180</v>
@@ -13644,7 +13644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182">
         <f>計算表!A182</f>
         <v>181</v>
@@ -13701,7 +13701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183">
         <f>計算表!A183</f>
         <v>182</v>
@@ -13758,7 +13758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184">
         <f>計算表!A184</f>
         <v>183</v>
@@ -13815,7 +13815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185">
         <f>計算表!A185</f>
         <v>184</v>
@@ -13872,7 +13872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186">
         <f>計算表!A186</f>
         <v>185</v>
@@ -13929,7 +13929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187">
         <f>計算表!A187</f>
         <v>186</v>
@@ -13986,7 +13986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188">
         <f>計算表!A188</f>
         <v>187</v>
@@ -14043,7 +14043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189">
         <f>計算表!A189</f>
         <v>188</v>
@@ -14100,7 +14100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190">
         <f>計算表!A190</f>
         <v>189</v>
@@ -14157,7 +14157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191">
         <f>計算表!A191</f>
         <v>190</v>
@@ -14214,7 +14214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192">
         <f>計算表!A192</f>
         <v>191</v>
@@ -14271,7 +14271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193">
         <f>計算表!A193</f>
         <v>192</v>
@@ -14328,7 +14328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194">
         <f>計算表!A194</f>
         <v>193</v>
@@ -14385,7 +14385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195">
         <f>計算表!A195</f>
         <v>194</v>
@@ -14442,7 +14442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A196">
         <f>計算表!A196</f>
         <v>195</v>
@@ -14499,7 +14499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A197">
         <f>計算表!A197</f>
         <v>196</v>
@@ -14556,7 +14556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A198">
         <f>計算表!A198</f>
         <v>197</v>
@@ -14613,7 +14613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A199">
         <f>計算表!A199</f>
         <v>198</v>
@@ -14670,7 +14670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A200">
         <f>計算表!A200</f>
         <v>199</v>
@@ -14727,7 +14727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A201">
         <f>計算表!A201</f>
         <v>200</v>
@@ -14784,7 +14784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A202">
         <f>計算表!A202</f>
         <v>201</v>
@@ -14841,7 +14841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A203">
         <f>計算表!A203</f>
         <v>202</v>
@@ -14898,7 +14898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A204">
         <f>計算表!A204</f>
         <v>203</v>
@@ -14955,7 +14955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A205">
         <f>計算表!A205</f>
         <v>204</v>
@@ -15012,7 +15012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A206">
         <f>計算表!A206</f>
         <v>205</v>
@@ -15069,7 +15069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A207">
         <f>計算表!A207</f>
         <v>206</v>
@@ -15126,7 +15126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208">
         <f>計算表!A208</f>
         <v>207</v>
@@ -15183,7 +15183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209">
         <f>計算表!A209</f>
         <v>208</v>
@@ -15240,7 +15240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210">
         <f>計算表!A210</f>
         <v>209</v>
@@ -15297,7 +15297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211">
         <f>計算表!A211</f>
         <v>210</v>
@@ -15354,7 +15354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A212">
         <f>計算表!A212</f>
         <v>211</v>
@@ -15411,7 +15411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A213">
         <f>計算表!A213</f>
         <v>212</v>
@@ -15468,7 +15468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A214">
         <f>計算表!A214</f>
         <v>213</v>
@@ -15525,7 +15525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A215">
         <f>計算表!A215</f>
         <v>214</v>
@@ -15582,7 +15582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A216">
         <f>計算表!A216</f>
         <v>215</v>
@@ -15639,7 +15639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217">
         <f>計算表!A217</f>
         <v>216</v>
@@ -15696,7 +15696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218">
         <f>計算表!A218</f>
         <v>217</v>
@@ -15753,7 +15753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219">
         <f>計算表!A219</f>
         <v>218</v>
@@ -15810,7 +15810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220">
         <f>計算表!A220</f>
         <v>219</v>
@@ -15867,7 +15867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221">
         <f>計算表!A221</f>
         <v>220</v>
@@ -15924,7 +15924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222">
         <f>計算表!A222</f>
         <v>221</v>
@@ -15981,7 +15981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A223">
         <f>計算表!A223</f>
         <v>222</v>
@@ -16038,7 +16038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224">
         <f>計算表!A224</f>
         <v>223</v>
@@ -16095,7 +16095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A225">
         <f>計算表!A225</f>
         <v>224</v>
@@ -16152,7 +16152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A226">
         <f>計算表!A226</f>
         <v>225</v>
@@ -16209,7 +16209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A227">
         <f>計算表!A227</f>
         <v>226</v>
@@ -16266,7 +16266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A228">
         <f>計算表!A228</f>
         <v>227</v>
@@ -16323,7 +16323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A229">
         <f>計算表!A229</f>
         <v>228</v>
@@ -16380,7 +16380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A230">
         <f>計算表!A230</f>
         <v>229</v>
@@ -16437,7 +16437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A231">
         <f>計算表!A231</f>
         <v>230</v>
@@ -16494,7 +16494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A232">
         <f>計算表!A232</f>
         <v>231</v>
@@ -16551,7 +16551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A233">
         <f>計算表!A233</f>
         <v>232</v>
@@ -16608,7 +16608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A234">
         <f>計算表!A234</f>
         <v>233</v>
@@ -16665,7 +16665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A235">
         <f>計算表!A235</f>
         <v>234</v>
@@ -16722,7 +16722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A236">
         <f>計算表!A236</f>
         <v>235</v>
@@ -16779,7 +16779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A237">
         <f>計算表!A237</f>
         <v>236</v>
@@ -16836,7 +16836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A238">
         <f>計算表!A238</f>
         <v>237</v>
@@ -16893,7 +16893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A239">
         <f>計算表!A239</f>
         <v>238</v>
@@ -16950,7 +16950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A240">
         <f>計算表!A240</f>
         <v>239</v>
@@ -17007,7 +17007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A241">
         <f>計算表!A241</f>
         <v>240</v>
@@ -17064,7 +17064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A242">
         <f>計算表!A242</f>
         <v>241</v>
@@ -17121,7 +17121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A243">
         <f>計算表!A243</f>
         <v>242</v>
@@ -17178,7 +17178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A244">
         <f>計算表!A244</f>
         <v>243</v>
@@ -17235,7 +17235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A245">
         <f>計算表!A245</f>
         <v>244</v>
@@ -17292,7 +17292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A246">
         <f>計算表!A246</f>
         <v>245</v>
@@ -17349,7 +17349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A247">
         <f>計算表!A247</f>
         <v>246</v>
@@ -17406,7 +17406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A248">
         <f>計算表!A248</f>
         <v>247</v>
@@ -17463,7 +17463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A249">
         <f>計算表!A249</f>
         <v>248</v>
@@ -17520,7 +17520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A250">
         <f>計算表!A250</f>
         <v>249</v>
@@ -17577,7 +17577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A251">
         <f>計算表!A251</f>
         <v>250</v>
@@ -17634,7 +17634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A252">
         <f>計算表!A252</f>
         <v>251</v>
@@ -17691,7 +17691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A253">
         <f>計算表!A253</f>
         <v>252</v>
@@ -17748,7 +17748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A254">
         <f>計算表!A254</f>
         <v>253</v>
@@ -17805,7 +17805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A255">
         <f>計算表!A255</f>
         <v>254</v>
@@ -17862,7 +17862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A256">
         <f>計算表!A256</f>
         <v>255</v>
@@ -17919,7 +17919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A257">
         <f>計算表!A257</f>
         <v>256</v>
@@ -17976,7 +17976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A258">
         <f>計算表!A258</f>
         <v>257</v>
@@ -18033,7 +18033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A259">
         <f>計算表!A259</f>
         <v>258</v>
@@ -18090,7 +18090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A260">
         <f>計算表!A260</f>
         <v>259</v>
@@ -18147,7 +18147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A261">
         <f>計算表!A261</f>
         <v>260</v>
@@ -18204,7 +18204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A262">
         <f>計算表!A262</f>
         <v>261</v>
@@ -18261,7 +18261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A263">
         <f>計算表!A263</f>
         <v>262</v>
@@ -18318,7 +18318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A264">
         <f>計算表!A264</f>
         <v>263</v>
@@ -18375,7 +18375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A265">
         <f>計算表!A265</f>
         <v>264</v>
@@ -18432,7 +18432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A266">
         <f>計算表!A266</f>
         <v>265</v>
@@ -18489,7 +18489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A267">
         <f>計算表!A267</f>
         <v>266</v>
@@ -18546,7 +18546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A268">
         <f>計算表!A268</f>
         <v>267</v>
@@ -18603,7 +18603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A269">
         <f>計算表!A269</f>
         <v>268</v>
@@ -18660,7 +18660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A270">
         <f>計算表!A270</f>
         <v>269</v>
@@ -18717,7 +18717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A271">
         <f>計算表!A271</f>
         <v>270</v>
@@ -18774,7 +18774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A272">
         <f>計算表!A272</f>
         <v>271</v>
@@ -18831,7 +18831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A273">
         <f>計算表!A273</f>
         <v>272</v>
@@ -18888,7 +18888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A274">
         <f>計算表!A274</f>
         <v>273</v>
@@ -18945,7 +18945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A275">
         <f>計算表!A275</f>
         <v>274</v>
@@ -19002,7 +19002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A276">
         <f>計算表!A276</f>
         <v>275</v>
@@ -19059,7 +19059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A277">
         <f>計算表!A277</f>
         <v>276</v>
@@ -19116,7 +19116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A278">
         <f>計算表!A278</f>
         <v>277</v>
@@ -19173,7 +19173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A279">
         <f>計算表!A279</f>
         <v>278</v>
@@ -19230,7 +19230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A280">
         <f>計算表!A280</f>
         <v>279</v>
@@ -19287,7 +19287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A281">
         <f>計算表!A281</f>
         <v>280</v>
@@ -19344,7 +19344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A282">
         <f>計算表!A282</f>
         <v>281</v>
@@ -19401,7 +19401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A283">
         <f>計算表!A283</f>
         <v>282</v>
@@ -19458,7 +19458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A284">
         <f>計算表!A284</f>
         <v>283</v>
@@ -19515,7 +19515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A285">
         <f>計算表!A285</f>
         <v>284</v>
@@ -19572,7 +19572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A286">
         <f>計算表!A286</f>
         <v>286</v>
@@ -19629,7 +19629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A287">
         <f>計算表!A287</f>
         <v>287</v>
@@ -19686,7 +19686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A288">
         <f>計算表!A288</f>
         <v>288</v>
@@ -19743,7 +19743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A289">
         <f>計算表!A289</f>
         <v>289</v>
@@ -19800,7 +19800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A290">
         <f>計算表!A290</f>
         <v>290</v>
@@ -19857,7 +19857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A291">
         <f>計算表!A291</f>
         <v>291</v>
@@ -19914,7 +19914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A292">
         <f>計算表!A292</f>
         <v>292</v>
@@ -19971,7 +19971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A293">
         <f>計算表!A293</f>
         <v>293</v>
@@ -20028,7 +20028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A294">
         <f>計算表!A294</f>
         <v>294</v>
@@ -20085,7 +20085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A295">
         <f>計算表!A295</f>
         <v>295</v>
@@ -20142,7 +20142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A296">
         <f>計算表!A296</f>
         <v>296</v>
@@ -20199,7 +20199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A297">
         <f>計算表!A297</f>
         <v>297</v>
@@ -20256,7 +20256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A298">
         <f>計算表!A298</f>
         <v>298</v>
@@ -20313,7 +20313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A299">
         <f>計算表!A299</f>
         <v>299</v>
@@ -20370,7 +20370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A300">
         <f>計算表!A300</f>
         <v>300</v>
@@ -20427,7 +20427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A301">
         <f>計算表!A301</f>
         <v>301</v>
@@ -20484,7 +20484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A302">
         <f>計算表!A302</f>
         <v>302</v>
@@ -20541,7 +20541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A303">
         <f>計算表!A303</f>
         <v>303</v>
@@ -20598,7 +20598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A304">
         <f>計算表!A304</f>
         <v>304</v>
@@ -20655,7 +20655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A305">
         <f>計算表!A305</f>
         <v>305</v>
@@ -20712,7 +20712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A306">
         <f>計算表!A306</f>
         <v>306</v>
@@ -20769,7 +20769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A307">
         <f>計算表!A307</f>
         <v>307</v>
@@ -20826,7 +20826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A308">
         <f>計算表!A308</f>
         <v>308</v>
@@ -20883,7 +20883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A309">
         <f>計算表!A309</f>
         <v>309</v>
@@ -20940,7 +20940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A310">
         <f>計算表!A310</f>
         <v>310</v>
@@ -20997,7 +20997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A311">
         <f>計算表!A311</f>
         <v>311</v>
@@ -21054,7 +21054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A312">
         <f>計算表!A312</f>
         <v>312</v>
@@ -21111,7 +21111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A313">
         <f>計算表!A313</f>
         <v>313</v>
@@ -21168,7 +21168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A314">
         <f>計算表!A314</f>
         <v>314</v>
@@ -21225,7 +21225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A315">
         <f>計算表!A315</f>
         <v>315</v>
@@ -21282,7 +21282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A316">
         <f>計算表!A316</f>
         <v>316</v>
@@ -21339,7 +21339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A317">
         <f>計算表!A317</f>
         <v>317</v>
@@ -21396,7 +21396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A318">
         <f>計算表!A318</f>
         <v>318</v>
@@ -21453,7 +21453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A319">
         <f>計算表!A319</f>
         <v>319</v>
@@ -21510,7 +21510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A320">
         <f>計算表!A320</f>
         <v>320</v>
@@ -21567,7 +21567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A321">
         <f>計算表!A321</f>
         <v>321</v>
@@ -21624,7 +21624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A322">
         <f>計算表!A322</f>
         <v>322</v>
@@ -21681,7 +21681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A323">
         <f>計算表!A323</f>
         <v>323</v>
@@ -21747,15 +21747,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R323"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.28515625" customWidth="1"/>
+    <col min="5" max="5" width="51" customWidth="1"/>
     <col min="6" max="6" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -21811,7 +21811,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -21840,7 +21840,7 @@
         <v>40</v>
       </c>
       <c r="J2">
-        <v>9999</v>
+        <v>1000</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -21867,7 +21867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -21923,7 +21923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -21979,7 +21979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -22035,7 +22035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -22091,7 +22091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -22147,7 +22147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -22203,7 +22203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -22259,7 +22259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -22315,7 +22315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -22371,7 +22371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -22427,7 +22427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -22483,7 +22483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -22539,7 +22539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -22595,7 +22595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -22651,7 +22651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -22707,7 +22707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -22763,7 +22763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -22819,7 +22819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -22875,7 +22875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -22931,7 +22931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -22987,7 +22987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -23043,7 +23043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -23099,7 +23099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -23155,7 +23155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -23211,7 +23211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -23267,7 +23267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -23323,7 +23323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -23379,7 +23379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -23435,7 +23435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -23491,7 +23491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -23547,7 +23547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -23603,7 +23603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -23659,7 +23659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -23715,7 +23715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -23771,7 +23771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -23827,7 +23827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -23883,7 +23883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -23939,7 +23939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -23995,7 +23995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -24051,7 +24051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -24107,7 +24107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -24163,7 +24163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -24219,7 +24219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -24275,7 +24275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -24331,7 +24331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -24387,7 +24387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -24443,7 +24443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -24499,7 +24499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -24555,7 +24555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -24611,7 +24611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -24667,7 +24667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -24723,7 +24723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -24779,7 +24779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -24835,7 +24835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -24891,7 +24891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -24947,7 +24947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -25003,7 +25003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -25059,7 +25059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -25115,7 +25115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -25171,7 +25171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -25227,7 +25227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -25283,7 +25283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -25339,7 +25339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -25395,7 +25395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -25451,7 +25451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -25507,7 +25507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -25563,7 +25563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -25619,7 +25619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -25675,7 +25675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -25731,7 +25731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -25787,7 +25787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -25843,7 +25843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -25899,7 +25899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -25955,7 +25955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -26011,7 +26011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -26067,7 +26067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -26123,7 +26123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -26179,7 +26179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>79</v>
       </c>
@@ -26235,7 +26235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>80</v>
       </c>
@@ -26291,7 +26291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>81</v>
       </c>
@@ -26347,7 +26347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>82</v>
       </c>
@@ -26403,7 +26403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>83</v>
       </c>
@@ -26459,7 +26459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>84</v>
       </c>
@@ -26515,7 +26515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>85</v>
       </c>
@@ -26571,7 +26571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>86</v>
       </c>
@@ -26627,7 +26627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>87</v>
       </c>
@@ -26683,7 +26683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>88</v>
       </c>
@@ -26739,7 +26739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>89</v>
       </c>
@@ -26795,7 +26795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>90</v>
       </c>
@@ -26851,7 +26851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>91</v>
       </c>
@@ -26907,7 +26907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>92</v>
       </c>
@@ -26963,7 +26963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>93</v>
       </c>
@@ -27019,7 +27019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>94</v>
       </c>
@@ -27075,7 +27075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>95</v>
       </c>
@@ -27131,7 +27131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>96</v>
       </c>
@@ -27187,7 +27187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>97</v>
       </c>
@@ -27243,7 +27243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>98</v>
       </c>
@@ -27299,7 +27299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>99</v>
       </c>
@@ -27355,7 +27355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>100</v>
       </c>
@@ -27411,7 +27411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>101</v>
       </c>
@@ -27467,7 +27467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>102</v>
       </c>
@@ -27523,7 +27523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>103</v>
       </c>
@@ -27579,7 +27579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>104</v>
       </c>
@@ -27635,7 +27635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>105</v>
       </c>
@@ -27691,7 +27691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>106</v>
       </c>
@@ -27747,7 +27747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>107</v>
       </c>
@@ -27803,7 +27803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>108</v>
       </c>
@@ -27859,7 +27859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>109</v>
       </c>
@@ -27915,7 +27915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>110</v>
       </c>
@@ -27971,7 +27971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>111</v>
       </c>
@@ -28027,7 +28027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>112</v>
       </c>
@@ -28083,7 +28083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>113</v>
       </c>
@@ -28139,7 +28139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>114</v>
       </c>
@@ -28195,7 +28195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>115</v>
       </c>
@@ -28251,7 +28251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>116</v>
       </c>
@@ -28307,7 +28307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>117</v>
       </c>
@@ -28363,7 +28363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>118</v>
       </c>
@@ -28419,7 +28419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>119</v>
       </c>
@@ -28475,7 +28475,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>120</v>
       </c>
@@ -28531,7 +28531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>121</v>
       </c>
@@ -28587,7 +28587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>122</v>
       </c>
@@ -28643,7 +28643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>123</v>
       </c>
@@ -28699,7 +28699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>124</v>
       </c>
@@ -28755,7 +28755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>125</v>
       </c>
@@ -28811,7 +28811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126</v>
       </c>
@@ -28867,7 +28867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>127</v>
       </c>
@@ -28923,7 +28923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>128</v>
       </c>
@@ -28979,7 +28979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>129</v>
       </c>
@@ -29035,7 +29035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>130</v>
       </c>
@@ -29091,7 +29091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>131</v>
       </c>
@@ -29147,7 +29147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>132</v>
       </c>
@@ -29203,7 +29203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>133</v>
       </c>
@@ -29259,7 +29259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>134</v>
       </c>
@@ -29315,7 +29315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>135</v>
       </c>
@@ -29371,7 +29371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>136</v>
       </c>
@@ -29427,7 +29427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>137</v>
       </c>
@@ -29483,7 +29483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>138</v>
       </c>
@@ -29539,7 +29539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>139</v>
       </c>
@@ -29595,7 +29595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>140</v>
       </c>
@@ -29651,7 +29651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>141</v>
       </c>
@@ -29707,7 +29707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>142</v>
       </c>
@@ -29763,7 +29763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>143</v>
       </c>
@@ -29819,7 +29819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>144</v>
       </c>
@@ -29875,7 +29875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>145</v>
       </c>
@@ -29931,7 +29931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>146</v>
       </c>
@@ -29987,7 +29987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>147</v>
       </c>
@@ -30043,7 +30043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>148</v>
       </c>
@@ -30099,7 +30099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>149</v>
       </c>
@@ -30155,7 +30155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>150</v>
       </c>
@@ -30211,7 +30211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>151</v>
       </c>
@@ -30267,7 +30267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>152</v>
       </c>
@@ -30323,7 +30323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>153</v>
       </c>
@@ -30379,7 +30379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>154</v>
       </c>
@@ -30435,7 +30435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>155</v>
       </c>
@@ -30491,7 +30491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>156</v>
       </c>
@@ -30547,7 +30547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>157</v>
       </c>
@@ -30603,7 +30603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>158</v>
       </c>
@@ -30659,7 +30659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>159</v>
       </c>
@@ -30715,7 +30715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>160</v>
       </c>
@@ -30771,7 +30771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>161</v>
       </c>
@@ -30827,7 +30827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>162</v>
       </c>
@@ -30883,7 +30883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>163</v>
       </c>
@@ -30939,7 +30939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>164</v>
       </c>
@@ -30995,7 +30995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>165</v>
       </c>
@@ -31051,7 +31051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>166</v>
       </c>
@@ -31107,7 +31107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>167</v>
       </c>
@@ -31163,7 +31163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>168</v>
       </c>
@@ -31219,7 +31219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>169</v>
       </c>
@@ -31275,7 +31275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>170</v>
       </c>
@@ -31331,7 +31331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>171</v>
       </c>
@@ -31387,7 +31387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>172</v>
       </c>
@@ -31443,7 +31443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>173</v>
       </c>
@@ -31499,7 +31499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>174</v>
       </c>
@@ -31555,7 +31555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>175</v>
       </c>
@@ -31611,7 +31611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>176</v>
       </c>
@@ -31667,7 +31667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>177</v>
       </c>
@@ -31723,7 +31723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>178</v>
       </c>
@@ -31779,7 +31779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>179</v>
       </c>
@@ -31835,7 +31835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>180</v>
       </c>
@@ -31891,7 +31891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>181</v>
       </c>
@@ -31947,7 +31947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>182</v>
       </c>
@@ -32003,7 +32003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>183</v>
       </c>
@@ -32059,7 +32059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>184</v>
       </c>
@@ -32115,7 +32115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>185</v>
       </c>
@@ -32171,7 +32171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>186</v>
       </c>
@@ -32227,7 +32227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>187</v>
       </c>
@@ -32283,7 +32283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>188</v>
       </c>
@@ -32339,7 +32339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>189</v>
       </c>
@@ -32395,7 +32395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>190</v>
       </c>
@@ -32451,7 +32451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>191</v>
       </c>
@@ -32507,7 +32507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>192</v>
       </c>
@@ -32563,7 +32563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>193</v>
       </c>
@@ -32619,7 +32619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>194</v>
       </c>
@@ -32675,7 +32675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>195</v>
       </c>
@@ -32731,7 +32731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>196</v>
       </c>
@@ -32787,7 +32787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>197</v>
       </c>
@@ -32843,7 +32843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>198</v>
       </c>
@@ -32899,7 +32899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>199</v>
       </c>
@@ -32955,7 +32955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>200</v>
       </c>
@@ -33011,7 +33011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>201</v>
       </c>
@@ -33067,7 +33067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>202</v>
       </c>
@@ -33123,7 +33123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>203</v>
       </c>
@@ -33179,7 +33179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>204</v>
       </c>
@@ -33235,7 +33235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>205</v>
       </c>
@@ -33291,7 +33291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>206</v>
       </c>
@@ -33347,7 +33347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>207</v>
       </c>
@@ -33403,7 +33403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>208</v>
       </c>
@@ -33459,7 +33459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>209</v>
       </c>
@@ -33515,7 +33515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>210</v>
       </c>
@@ -33571,7 +33571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>211</v>
       </c>
@@ -33627,7 +33627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>212</v>
       </c>
@@ -33683,7 +33683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>213</v>
       </c>
@@ -33739,7 +33739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>214</v>
       </c>
@@ -33795,7 +33795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>215</v>
       </c>
@@ -33851,7 +33851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>216</v>
       </c>
@@ -33907,7 +33907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>217</v>
       </c>
@@ -33963,7 +33963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>218</v>
       </c>
@@ -34019,7 +34019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>219</v>
       </c>
@@ -34075,7 +34075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>220</v>
       </c>
@@ -34131,7 +34131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>221</v>
       </c>
@@ -34187,7 +34187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>222</v>
       </c>
@@ -34243,7 +34243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>223</v>
       </c>
@@ -34299,7 +34299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>224</v>
       </c>
@@ -34355,7 +34355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>225</v>
       </c>
@@ -34411,7 +34411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>226</v>
       </c>
@@ -34467,7 +34467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>227</v>
       </c>
@@ -34523,7 +34523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>228</v>
       </c>
@@ -34579,7 +34579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>229</v>
       </c>
@@ -34635,7 +34635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>230</v>
       </c>
@@ -34691,7 +34691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>231</v>
       </c>
@@ -34747,7 +34747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>232</v>
       </c>
@@ -34803,7 +34803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>233</v>
       </c>
@@ -34859,7 +34859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>234</v>
       </c>
@@ -34915,7 +34915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>235</v>
       </c>
@@ -34971,7 +34971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>236</v>
       </c>
@@ -35027,7 +35027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>237</v>
       </c>
@@ -35083,7 +35083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>238</v>
       </c>
@@ -35139,7 +35139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>239</v>
       </c>
@@ -35195,7 +35195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>240</v>
       </c>
@@ -35251,7 +35251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>241</v>
       </c>
@@ -35307,7 +35307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>242</v>
       </c>
@@ -35363,7 +35363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>243</v>
       </c>
@@ -35419,7 +35419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>244</v>
       </c>
@@ -35475,7 +35475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>245</v>
       </c>
@@ -35531,7 +35531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>246</v>
       </c>
@@ -35587,7 +35587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>247</v>
       </c>
@@ -35643,7 +35643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>248</v>
       </c>
@@ -35699,7 +35699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>249</v>
       </c>
@@ -35755,7 +35755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>250</v>
       </c>
@@ -35811,7 +35811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>251</v>
       </c>
@@ -35867,7 +35867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>252</v>
       </c>
@@ -35923,7 +35923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>253</v>
       </c>
@@ -35979,7 +35979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>254</v>
       </c>
@@ -36035,7 +36035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>255</v>
       </c>
@@ -36091,7 +36091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>256</v>
       </c>
@@ -36147,7 +36147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>257</v>
       </c>
@@ -36203,7 +36203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>258</v>
       </c>
@@ -36259,7 +36259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>259</v>
       </c>
@@ -36315,7 +36315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>260</v>
       </c>
@@ -36371,7 +36371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>261</v>
       </c>
@@ -36427,7 +36427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>262</v>
       </c>
@@ -36483,7 +36483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>263</v>
       </c>
@@ -36539,7 +36539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>264</v>
       </c>
@@ -36595,7 +36595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>265</v>
       </c>
@@ -36651,7 +36651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>266</v>
       </c>
@@ -36707,7 +36707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>267</v>
       </c>
@@ -36763,7 +36763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>268</v>
       </c>
@@ -36819,7 +36819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>269</v>
       </c>
@@ -36875,7 +36875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>270</v>
       </c>
@@ -36931,7 +36931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>271</v>
       </c>
@@ -36987,7 +36987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>272</v>
       </c>
@@ -37043,7 +37043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>273</v>
       </c>
@@ -37099,7 +37099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>274</v>
       </c>
@@ -37155,7 +37155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>275</v>
       </c>
@@ -37211,7 +37211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>276</v>
       </c>
@@ -37267,7 +37267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>277</v>
       </c>
@@ -37323,7 +37323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>278</v>
       </c>
@@ -37379,7 +37379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>279</v>
       </c>
@@ -37435,7 +37435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>280</v>
       </c>
@@ -37491,7 +37491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>281</v>
       </c>
@@ -37547,7 +37547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>282</v>
       </c>
@@ -37603,7 +37603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>283</v>
       </c>
@@ -37659,7 +37659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>284</v>
       </c>
@@ -37715,7 +37715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>286</v>
       </c>
@@ -37771,7 +37771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>287</v>
       </c>
@@ -37827,7 +37827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>288</v>
       </c>
@@ -37883,7 +37883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>289</v>
       </c>
@@ -37939,7 +37939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>290</v>
       </c>
@@ -37995,7 +37995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>291</v>
       </c>
@@ -38051,7 +38051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>292</v>
       </c>
@@ -38107,7 +38107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>293</v>
       </c>
@@ -38163,7 +38163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>294</v>
       </c>
@@ -38219,7 +38219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>295</v>
       </c>
@@ -38275,7 +38275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>296</v>
       </c>
@@ -38331,7 +38331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>297</v>
       </c>
@@ -38387,7 +38387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>298</v>
       </c>
@@ -38443,7 +38443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>299</v>
       </c>
@@ -38499,7 +38499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>300</v>
       </c>
@@ -38555,7 +38555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>301</v>
       </c>
@@ -38611,7 +38611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>302</v>
       </c>
@@ -38667,7 +38667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>303</v>
       </c>
@@ -38723,7 +38723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>304</v>
       </c>
@@ -38779,7 +38779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>305</v>
       </c>
@@ -38835,7 +38835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>306</v>
       </c>
@@ -38891,7 +38891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>307</v>
       </c>
@@ -38947,7 +38947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>308</v>
       </c>
@@ -39003,7 +39003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>309</v>
       </c>
@@ -39059,7 +39059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>310</v>
       </c>
@@ -39115,7 +39115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>311</v>
       </c>
@@ -39171,7 +39171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>312</v>
       </c>
@@ -39227,7 +39227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>313</v>
       </c>
@@ -39283,7 +39283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>314</v>
       </c>
@@ -39339,7 +39339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>315</v>
       </c>
@@ -39395,7 +39395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>316</v>
       </c>
@@ -39451,7 +39451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>317</v>
       </c>
@@ -39507,7 +39507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>318</v>
       </c>
@@ -39563,7 +39563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>319</v>
       </c>
@@ -39619,7 +39619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>320</v>
       </c>
@@ -39675,7 +39675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>321</v>
       </c>
@@ -39731,7 +39731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>322</v>
       </c>
@@ -39787,7 +39787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>323</v>
       </c>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\develop\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE407D5-6F7B-4AA0-8F25-0F93EAB1E8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02954F51-4FC1-4A5A-A4C3-958CC6A35493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1899" uniqueCount="1088">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1889" uniqueCount="1084">
   <si>
     <t>編號</t>
   </si>
@@ -3329,6 +3329,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -3345,6 +3346,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>21~40</t>
     </r>
@@ -3361,6 +3363,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -3397,6 +3400,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -3413,6 +3417,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>41~60</t>
     </r>
@@ -3429,6 +3434,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -3465,6 +3471,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -3481,6 +3488,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>61~80</t>
     </r>
@@ -3497,6 +3505,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -3533,6 +3542,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>(</t>
     </r>
@@ -3549,6 +3559,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>81~100</t>
     </r>
@@ -3565,6 +3576,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)</t>
     </r>
@@ -3575,75 +3587,59 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{1~3,40}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{4,40}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{5,20}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{4,30}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{5,30}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{5,25}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>{6,5}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{6,10}</t>
+    <t>{4,20}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{7~9,5}</t>
+    <t>{5,2}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{1~3,20}</t>
+    <t>{1~3,90}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{5,35}</t>
+    <t>{1~3,100}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{7~9,10}</t>
+    <t>{4,5}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{1~3,10}</t>
+    <t>{1~3,95}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{12~13,3}</t>
+    <t>{4,8}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{1~3,7}</t>
+    <t>{6,1}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{4,15}</t>
+    <t>{5,3}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{7~9,15}</t>
+    <t>{1~3,88}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{6,25}</t>
+    <t>{7~9,1}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{5,10}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{1~3,64}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4062,9 +4058,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R353"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4120,7 +4116,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2">
         <f>計算表!A2</f>
         <v>1</v>
@@ -4194,7 +4190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>計算表!A3</f>
         <v>2</v>
@@ -4268,7 +4264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <f>計算表!A4</f>
         <v>3</v>
@@ -4342,7 +4338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>計算表!A5</f>
         <v>4</v>
@@ -4416,7 +4412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>計算表!A6</f>
         <v>5</v>
@@ -4490,7 +4486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>計算表!A7</f>
         <v>6</v>
@@ -4564,7 +4560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>計算表!A8</f>
         <v>7</v>
@@ -4638,7 +4634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>計算表!A9</f>
         <v>8</v>
@@ -4712,7 +4708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>計算表!A10</f>
         <v>9</v>
@@ -4786,7 +4782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>計算表!A11</f>
         <v>10</v>
@@ -4860,7 +4856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>計算表!A12</f>
         <v>11</v>
@@ -4934,7 +4930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>計算表!A13</f>
         <v>12</v>
@@ -5008,7 +5004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>計算表!A14</f>
         <v>13</v>
@@ -5082,7 +5078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>計算表!A15</f>
         <v>14</v>
@@ -5156,7 +5152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>計算表!A16</f>
         <v>15</v>
@@ -5230,7 +5226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>計算表!A17</f>
         <v>16</v>
@@ -5304,7 +5300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18">
         <f>計算表!A18</f>
         <v>17</v>
@@ -5378,7 +5374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19">
         <f>計算表!A19</f>
         <v>18</v>
@@ -5452,7 +5448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20">
         <f>計算表!A20</f>
         <v>19</v>
@@ -5526,7 +5522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21">
         <f>計算表!A21</f>
         <v>20</v>
@@ -5600,7 +5596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22">
         <f>計算表!A22</f>
         <v>21</v>
@@ -5674,7 +5670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23">
         <f>計算表!A23</f>
         <v>22</v>
@@ -5748,7 +5744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24">
         <f>計算表!A24</f>
         <v>23</v>
@@ -5822,7 +5818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25">
         <f>計算表!A25</f>
         <v>24</v>
@@ -5896,7 +5892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26">
         <f>計算表!A26</f>
         <v>25</v>
@@ -5970,7 +5966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27">
         <f>計算表!A27</f>
         <v>26</v>
@@ -6044,7 +6040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28">
         <f>計算表!A28</f>
         <v>27</v>
@@ -6118,7 +6114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29">
         <f>計算表!A29</f>
         <v>28</v>
@@ -6192,7 +6188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30">
         <f>計算表!A30</f>
         <v>29</v>
@@ -6266,7 +6262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31">
         <f>計算表!A31</f>
         <v>30</v>
@@ -6340,7 +6336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32">
         <f>計算表!A32</f>
         <v>31</v>
@@ -6414,7 +6410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33">
         <f>計算表!A33</f>
         <v>32</v>
@@ -6488,7 +6484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34">
         <f>計算表!A34</f>
         <v>33</v>
@@ -6562,7 +6558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35">
         <f>計算表!A35</f>
         <v>34</v>
@@ -6636,7 +6632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36">
         <f>計算表!A36</f>
         <v>35</v>
@@ -6710,7 +6706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37">
         <f>計算表!A37</f>
         <v>36</v>
@@ -6784,7 +6780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38">
         <f>計算表!A38</f>
         <v>37</v>
@@ -6858,7 +6854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39">
         <f>計算表!A39</f>
         <v>38</v>
@@ -6932,7 +6928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40">
         <f>計算表!A40</f>
         <v>39</v>
@@ -7006,7 +7002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41">
         <f>計算表!A41</f>
         <v>40</v>
@@ -7080,7 +7076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42">
         <f>計算表!A42</f>
         <v>41</v>
@@ -7154,7 +7150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43">
         <f>計算表!A43</f>
         <v>42</v>
@@ -7228,7 +7224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44">
         <f>計算表!A44</f>
         <v>43</v>
@@ -7302,7 +7298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45">
         <f>計算表!A45</f>
         <v>44</v>
@@ -7376,7 +7372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46">
         <f>計算表!A46</f>
         <v>45</v>
@@ -7450,7 +7446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47">
         <f>計算表!A47</f>
         <v>46</v>
@@ -7524,7 +7520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48">
         <f>計算表!A48</f>
         <v>47</v>
@@ -7598,7 +7594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49">
         <f>計算表!A49</f>
         <v>48</v>
@@ -7672,7 +7668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50">
         <f>計算表!A50</f>
         <v>49</v>
@@ -7746,7 +7742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51">
         <f>計算表!A51</f>
         <v>50</v>
@@ -7820,7 +7816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52">
         <f>計算表!A52</f>
         <v>51</v>
@@ -7894,7 +7890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53">
         <f>計算表!A53</f>
         <v>52</v>
@@ -7968,7 +7964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54">
         <f>計算表!A54</f>
         <v>53</v>
@@ -8042,7 +8038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55">
         <f>計算表!A55</f>
         <v>54</v>
@@ -8116,7 +8112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56">
         <f>計算表!A56</f>
         <v>55</v>
@@ -8190,7 +8186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57">
         <f>計算表!A57</f>
         <v>56</v>
@@ -8264,7 +8260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58">
         <f>計算表!A58</f>
         <v>57</v>
@@ -8338,7 +8334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59">
         <f>計算表!A59</f>
         <v>58</v>
@@ -8412,7 +8408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60">
         <f>計算表!A60</f>
         <v>59</v>
@@ -8486,7 +8482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61">
         <f>計算表!A61</f>
         <v>60</v>
@@ -8560,7 +8556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62">
         <f>計算表!A62</f>
         <v>61</v>
@@ -8634,7 +8630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63">
         <f>計算表!A63</f>
         <v>62</v>
@@ -8708,7 +8704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64">
         <f>計算表!A64</f>
         <v>63</v>
@@ -8782,7 +8778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65">
         <f>計算表!A65</f>
         <v>64</v>
@@ -8856,7 +8852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66">
         <f>計算表!A66</f>
         <v>65</v>
@@ -8930,7 +8926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67">
         <f>計算表!A67</f>
         <v>66</v>
@@ -9004,7 +9000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68">
         <f>計算表!A68</f>
         <v>67</v>
@@ -9078,7 +9074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69">
         <f>計算表!A69</f>
         <v>68</v>
@@ -9152,7 +9148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70">
         <f>計算表!A70</f>
         <v>69</v>
@@ -9226,7 +9222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71">
         <f>計算表!A71</f>
         <v>70</v>
@@ -9300,7 +9296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72">
         <f>計算表!A72</f>
         <v>71</v>
@@ -9374,7 +9370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73">
         <f>計算表!A73</f>
         <v>72</v>
@@ -9448,7 +9444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74">
         <f>計算表!A74</f>
         <v>73</v>
@@ -9522,7 +9518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75">
         <f>計算表!A75</f>
         <v>74</v>
@@ -9596,7 +9592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76">
         <f>計算表!A76</f>
         <v>75</v>
@@ -9670,7 +9666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77">
         <f>計算表!A77</f>
         <v>76</v>
@@ -9744,7 +9740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78">
         <f>計算表!A78</f>
         <v>77</v>
@@ -9818,7 +9814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79">
         <f>計算表!A79</f>
         <v>78</v>
@@ -9892,7 +9888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80">
         <f>計算表!A80</f>
         <v>79</v>
@@ -9966,7 +9962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81">
         <f>計算表!A81</f>
         <v>80</v>
@@ -10040,7 +10036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82">
         <f>計算表!A82</f>
         <v>81</v>
@@ -10114,7 +10110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83">
         <f>計算表!A83</f>
         <v>82</v>
@@ -10188,7 +10184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84">
         <f>計算表!A84</f>
         <v>83</v>
@@ -10262,7 +10258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85">
         <f>計算表!A85</f>
         <v>84</v>
@@ -10336,7 +10332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86">
         <f>計算表!A86</f>
         <v>85</v>
@@ -10410,7 +10406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87">
         <f>計算表!A87</f>
         <v>86</v>
@@ -10484,7 +10480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88">
         <f>計算表!A88</f>
         <v>87</v>
@@ -10558,7 +10554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89">
         <f>計算表!A89</f>
         <v>88</v>
@@ -10632,7 +10628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90">
         <f>計算表!A90</f>
         <v>89</v>
@@ -10706,7 +10702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91">
         <f>計算表!A91</f>
         <v>90</v>
@@ -10780,7 +10776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92">
         <f>計算表!A92</f>
         <v>91</v>
@@ -10854,7 +10850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93">
         <f>計算表!A93</f>
         <v>92</v>
@@ -10928,7 +10924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94">
         <f>計算表!A94</f>
         <v>93</v>
@@ -11002,7 +10998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95">
         <f>計算表!A95</f>
         <v>94</v>
@@ -11076,7 +11072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96">
         <f>計算表!A96</f>
         <v>95</v>
@@ -11150,7 +11146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97">
         <f>計算表!A97</f>
         <v>96</v>
@@ -11224,7 +11220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98">
         <f>計算表!A98</f>
         <v>97</v>
@@ -11298,7 +11294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99">
         <f>計算表!A99</f>
         <v>98</v>
@@ -11372,7 +11368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100">
         <f>計算表!A100</f>
         <v>99</v>
@@ -11446,7 +11442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101">
         <f>計算表!A101</f>
         <v>100</v>
@@ -11520,7 +11516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102">
         <f>計算表!A102</f>
         <v>101</v>
@@ -11594,7 +11590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103">
         <f>計算表!A103</f>
         <v>102</v>
@@ -11668,7 +11664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104">
         <f>計算表!A104</f>
         <v>103</v>
@@ -11695,15 +11691,15 @@
       </c>
       <c r="G104" t="str">
         <f>計算表!G104</f>
-        <v>{1~3,40}</v>
-      </c>
-      <c r="H104" t="str">
+        <v>{1~3,100}</v>
+      </c>
+      <c r="H104">
         <f>計算表!H104</f>
-        <v>{4,40}</v>
-      </c>
-      <c r="I104" t="str">
+        <v>0</v>
+      </c>
+      <c r="I104">
         <f>計算表!I104</f>
-        <v>{5,20}</v>
+        <v>0</v>
       </c>
       <c r="J104">
         <f>計算表!J104</f>
@@ -11742,7 +11738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105">
         <f>計算表!A105</f>
         <v>104</v>
@@ -11769,19 +11765,19 @@
       </c>
       <c r="G105" t="str">
         <f>計算表!G105</f>
-        <v>{1~3,40}</v>
+        <v>{1~3,95}</v>
       </c>
       <c r="H105" t="str">
         <f>計算表!H105</f>
-        <v>{4,30}</v>
-      </c>
-      <c r="I105" t="str">
+        <v>{4,5}</v>
+      </c>
+      <c r="I105">
         <f>計算表!I105</f>
-        <v>{5,25}</v>
-      </c>
-      <c r="J105" t="str">
+        <v>0</v>
+      </c>
+      <c r="J105">
         <f>計算表!J105</f>
-        <v>{6,5}</v>
+        <v>0</v>
       </c>
       <c r="K105">
         <f>計算表!K105</f>
@@ -11816,7 +11812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106">
         <f>計算表!A106</f>
         <v>105</v>
@@ -11843,23 +11839,23 @@
       </c>
       <c r="G106" t="str">
         <f>計算表!G106</f>
-        <v>{1~3,20}</v>
+        <v>{1~3,90}</v>
       </c>
       <c r="H106" t="str">
         <f>計算表!H106</f>
-        <v>{4,30}</v>
+        <v>{4,8}</v>
       </c>
       <c r="I106" t="str">
         <f>計算表!I106</f>
-        <v>{5,35}</v>
-      </c>
-      <c r="J106" t="str">
+        <v>{5,2}</v>
+      </c>
+      <c r="J106">
         <f>計算表!J106</f>
-        <v>{6,10}</v>
-      </c>
-      <c r="K106" t="str">
+        <v>0</v>
+      </c>
+      <c r="K106">
         <f>計算表!K106</f>
-        <v>{7~9,5}</v>
+        <v>0</v>
       </c>
       <c r="L106">
         <f>計算表!L106</f>
@@ -11890,7 +11886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107">
         <f>計算表!A107</f>
         <v>106</v>
@@ -11917,27 +11913,27 @@
       </c>
       <c r="G107" t="str">
         <f>計算表!G107</f>
-        <v>{1~3,10}</v>
+        <v>{1~3,88}</v>
       </c>
       <c r="H107" t="str">
         <f>計算表!H107</f>
-        <v>{4,30}</v>
+        <v>{4,8}</v>
       </c>
       <c r="I107" t="str">
         <f>計算表!I107</f>
-        <v>{5,35}</v>
+        <v>{5,3}</v>
       </c>
       <c r="J107" t="str">
         <f>計算表!J107</f>
-        <v>{6,10}</v>
-      </c>
-      <c r="K107" t="str">
+        <v>{6,1}</v>
+      </c>
+      <c r="K107">
         <f>計算表!K107</f>
-        <v>{7~9,10}</v>
-      </c>
-      <c r="L107" t="str">
+        <v>0</v>
+      </c>
+      <c r="L107">
         <f>計算表!L107</f>
-        <v>{10~11,5}</v>
+        <v>0</v>
       </c>
       <c r="M107">
         <f>計算表!M107</f>
@@ -11964,7 +11960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108">
         <f>計算表!A108</f>
         <v>107</v>
@@ -11991,31 +11987,31 @@
       </c>
       <c r="G108" t="str">
         <f>計算表!G108</f>
-        <v>{1~3,7}</v>
+        <v>{1~3,64}</v>
       </c>
       <c r="H108" t="str">
         <f>計算表!H108</f>
-        <v>{4,15}</v>
+        <v>{4,20}</v>
       </c>
       <c r="I108" t="str">
         <f>計算表!I108</f>
-        <v>{5,30}</v>
+        <v>{5,10}</v>
       </c>
       <c r="J108" t="str">
         <f>計算表!J108</f>
-        <v>{6,25}</v>
+        <v>{6,5}</v>
       </c>
       <c r="K108" t="str">
         <f>計算表!K108</f>
-        <v>{7~9,15}</v>
-      </c>
-      <c r="L108" t="str">
+        <v>{7~9,1}</v>
+      </c>
+      <c r="L108">
         <f>計算表!L108</f>
-        <v>{10~11,5}</v>
-      </c>
-      <c r="M108" t="str">
+        <v>0</v>
+      </c>
+      <c r="M108">
         <f>計算表!M108</f>
-        <v>{12~13,3}</v>
+        <v>0</v>
       </c>
       <c r="N108">
         <f>計算表!N108</f>
@@ -12038,7 +12034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109">
         <f>計算表!A109</f>
         <v>108</v>
@@ -12112,7 +12108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110">
         <f>計算表!A110</f>
         <v>109</v>
@@ -12186,7 +12182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111">
         <f>計算表!A111</f>
         <v>110</v>
@@ -12260,7 +12256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112">
         <f>計算表!A112</f>
         <v>111</v>
@@ -12334,7 +12330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113">
         <f>計算表!A113</f>
         <v>112</v>
@@ -12408,7 +12404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114">
         <f>計算表!A114</f>
         <v>113</v>
@@ -12482,7 +12478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115">
         <f>計算表!A115</f>
         <v>114</v>
@@ -12556,7 +12552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116">
         <f>計算表!A116</f>
         <v>115</v>
@@ -12630,7 +12626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117">
         <f>計算表!A117</f>
         <v>116</v>
@@ -12704,7 +12700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118">
         <f>計算表!A118</f>
         <v>117</v>
@@ -12778,7 +12774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119">
         <f>計算表!A119</f>
         <v>118</v>
@@ -12852,7 +12848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120">
         <f>計算表!A120</f>
         <v>119</v>
@@ -12926,7 +12922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121">
         <f>計算表!A121</f>
         <v>120</v>
@@ -13000,7 +12996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122">
         <f>計算表!A122</f>
         <v>121</v>
@@ -13074,7 +13070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123">
         <f>計算表!A123</f>
         <v>122</v>
@@ -13148,7 +13144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124">
         <f>計算表!A124</f>
         <v>123</v>
@@ -13222,7 +13218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125">
         <f>計算表!A125</f>
         <v>124</v>
@@ -13296,7 +13292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126">
         <f>計算表!A126</f>
         <v>125</v>
@@ -13370,7 +13366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127">
         <f>計算表!A127</f>
         <v>126</v>
@@ -13444,7 +13440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128">
         <f>計算表!A128</f>
         <v>127</v>
@@ -13518,7 +13514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129">
         <f>計算表!A129</f>
         <v>128</v>
@@ -13592,7 +13588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130">
         <f>計算表!A130</f>
         <v>129</v>
@@ -13666,7 +13662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131">
         <f>計算表!A131</f>
         <v>130</v>
@@ -13740,7 +13736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132">
         <f>計算表!A132</f>
         <v>131</v>
@@ -13814,7 +13810,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133">
         <f>計算表!A133</f>
         <v>132</v>
@@ -13888,7 +13884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134">
         <f>計算表!A134</f>
         <v>133</v>
@@ -13962,7 +13958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135">
         <f>計算表!A135</f>
         <v>134</v>
@@ -14036,7 +14032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136">
         <f>計算表!A136</f>
         <v>135</v>
@@ -14110,7 +14106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137">
         <f>計算表!A137</f>
         <v>136</v>
@@ -14184,7 +14180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138">
         <f>計算表!A138</f>
         <v>137</v>
@@ -14258,7 +14254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139">
         <f>計算表!A139</f>
         <v>138</v>
@@ -14332,7 +14328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140">
         <f>計算表!A140</f>
         <v>139</v>
@@ -14406,7 +14402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141">
         <f>計算表!A141</f>
         <v>140</v>
@@ -14480,7 +14476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142">
         <f>計算表!A142</f>
         <v>141</v>
@@ -14554,7 +14550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143">
         <f>計算表!A143</f>
         <v>142</v>
@@ -14628,7 +14624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144">
         <f>計算表!A144</f>
         <v>143</v>
@@ -14702,7 +14698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145">
         <f>計算表!A145</f>
         <v>144</v>
@@ -14776,7 +14772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146">
         <f>計算表!A146</f>
         <v>145</v>
@@ -14850,7 +14846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147">
         <f>計算表!A147</f>
         <v>146</v>
@@ -14924,7 +14920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148">
         <f>計算表!A148</f>
         <v>147</v>
@@ -14998,7 +14994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149">
         <f>計算表!A149</f>
         <v>148</v>
@@ -15072,7 +15068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150">
         <f>計算表!A150</f>
         <v>149</v>
@@ -15146,7 +15142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151">
         <f>計算表!A151</f>
         <v>150</v>
@@ -15220,7 +15216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152">
         <f>計算表!A152</f>
         <v>151</v>
@@ -15294,7 +15290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153">
         <f>計算表!A153</f>
         <v>152</v>
@@ -15368,7 +15364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154">
         <f>計算表!A154</f>
         <v>153</v>
@@ -15442,7 +15438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155">
         <f>計算表!A155</f>
         <v>154</v>
@@ -15516,7 +15512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156">
         <f>計算表!A156</f>
         <v>155</v>
@@ -15590,7 +15586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157">
         <f>計算表!A157</f>
         <v>156</v>
@@ -15664,7 +15660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158">
         <f>計算表!A158</f>
         <v>157</v>
@@ -15738,7 +15734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159">
         <f>計算表!A159</f>
         <v>158</v>
@@ -15812,7 +15808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160">
         <f>計算表!A160</f>
         <v>159</v>
@@ -15886,7 +15882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161">
         <f>計算表!A161</f>
         <v>160</v>
@@ -15960,7 +15956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162">
         <f>計算表!A162</f>
         <v>161</v>
@@ -16034,7 +16030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163">
         <f>計算表!A163</f>
         <v>162</v>
@@ -16108,7 +16104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164">
         <f>計算表!A164</f>
         <v>163</v>
@@ -16182,7 +16178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165">
         <f>計算表!A165</f>
         <v>164</v>
@@ -16256,7 +16252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166">
         <f>計算表!A166</f>
         <v>165</v>
@@ -16330,7 +16326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167">
         <f>計算表!A167</f>
         <v>166</v>
@@ -16404,7 +16400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168">
         <f>計算表!A168</f>
         <v>167</v>
@@ -16478,7 +16474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169">
         <f>計算表!A169</f>
         <v>168</v>
@@ -16552,7 +16548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170">
         <f>計算表!A170</f>
         <v>169</v>
@@ -16626,7 +16622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171">
         <f>計算表!A171</f>
         <v>170</v>
@@ -16700,7 +16696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172">
         <f>計算表!A172</f>
         <v>171</v>
@@ -16774,7 +16770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173">
         <f>計算表!A173</f>
         <v>172</v>
@@ -16848,7 +16844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174">
         <f>計算表!A174</f>
         <v>173</v>
@@ -16922,7 +16918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175">
         <f>計算表!A175</f>
         <v>174</v>
@@ -16996,7 +16992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176">
         <f>計算表!A176</f>
         <v>175</v>
@@ -17070,7 +17066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177">
         <f>計算表!A177</f>
         <v>176</v>
@@ -17144,7 +17140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178">
         <f>計算表!A178</f>
         <v>177</v>
@@ -17218,7 +17214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179">
         <f>計算表!A179</f>
         <v>178</v>
@@ -17292,7 +17288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180">
         <f>計算表!A180</f>
         <v>179</v>
@@ -17366,7 +17362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181">
         <f>計算表!A181</f>
         <v>180</v>
@@ -17440,7 +17436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182">
         <f>計算表!A182</f>
         <v>181</v>
@@ -17514,7 +17510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183">
         <f>計算表!A183</f>
         <v>182</v>
@@ -17588,7 +17584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184">
         <f>計算表!A184</f>
         <v>183</v>
@@ -17662,7 +17658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185">
         <f>計算表!A185</f>
         <v>184</v>
@@ -17736,7 +17732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186">
         <f>計算表!A186</f>
         <v>185</v>
@@ -17810,7 +17806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187">
         <f>計算表!A187</f>
         <v>186</v>
@@ -17884,7 +17880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188">
         <f>計算表!A188</f>
         <v>187</v>
@@ -17958,7 +17954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189">
         <f>計算表!A189</f>
         <v>188</v>
@@ -18032,7 +18028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190">
         <f>計算表!A190</f>
         <v>189</v>
@@ -18106,7 +18102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191">
         <f>計算表!A191</f>
         <v>190</v>
@@ -18180,7 +18176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192">
         <f>計算表!A192</f>
         <v>191</v>
@@ -18254,7 +18250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193">
         <f>計算表!A193</f>
         <v>192</v>
@@ -18328,7 +18324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194">
         <f>計算表!A194</f>
         <v>193</v>
@@ -18402,7 +18398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195">
         <f>計算表!A195</f>
         <v>194</v>
@@ -18476,7 +18472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A196">
         <f>計算表!A196</f>
         <v>195</v>
@@ -18550,7 +18546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A197">
         <f>計算表!A197</f>
         <v>196</v>
@@ -18624,7 +18620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A198">
         <f>計算表!A198</f>
         <v>197</v>
@@ -18698,7 +18694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A199">
         <f>計算表!A199</f>
         <v>198</v>
@@ -18772,7 +18768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A200">
         <f>計算表!A200</f>
         <v>199</v>
@@ -18846,7 +18842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A201">
         <f>計算表!A201</f>
         <v>200</v>
@@ -18920,7 +18916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A202">
         <f>計算表!A202</f>
         <v>201</v>
@@ -18994,7 +18990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A203">
         <f>計算表!A203</f>
         <v>202</v>
@@ -19068,7 +19064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A204">
         <f>計算表!A204</f>
         <v>203</v>
@@ -19142,7 +19138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A205">
         <f>計算表!A205</f>
         <v>204</v>
@@ -19216,7 +19212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A206">
         <f>計算表!A206</f>
         <v>205</v>
@@ -19290,7 +19286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A207">
         <f>計算表!A207</f>
         <v>206</v>
@@ -19364,7 +19360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208">
         <f>計算表!A208</f>
         <v>207</v>
@@ -19438,7 +19434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209">
         <f>計算表!A209</f>
         <v>208</v>
@@ -19512,7 +19508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210">
         <f>計算表!A210</f>
         <v>209</v>
@@ -19586,7 +19582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211">
         <f>計算表!A211</f>
         <v>210</v>
@@ -19660,7 +19656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A212">
         <f>計算表!A212</f>
         <v>211</v>
@@ -19734,7 +19730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A213">
         <f>計算表!A213</f>
         <v>212</v>
@@ -19808,7 +19804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A214">
         <f>計算表!A214</f>
         <v>213</v>
@@ -19882,7 +19878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A215">
         <f>計算表!A215</f>
         <v>214</v>
@@ -19956,7 +19952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A216">
         <f>計算表!A216</f>
         <v>215</v>
@@ -20030,7 +20026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217">
         <f>計算表!A217</f>
         <v>216</v>
@@ -20104,7 +20100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218">
         <f>計算表!A218</f>
         <v>217</v>
@@ -20178,7 +20174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219">
         <f>計算表!A219</f>
         <v>218</v>
@@ -20252,7 +20248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220">
         <f>計算表!A220</f>
         <v>219</v>
@@ -20326,7 +20322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221">
         <f>計算表!A221</f>
         <v>220</v>
@@ -20400,7 +20396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222">
         <f>計算表!A222</f>
         <v>221</v>
@@ -20474,7 +20470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A223">
         <f>計算表!A223</f>
         <v>222</v>
@@ -20548,7 +20544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224">
         <f>計算表!A224</f>
         <v>223</v>
@@ -20622,7 +20618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A225">
         <f>計算表!A225</f>
         <v>224</v>
@@ -20696,7 +20692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A226">
         <f>計算表!A226</f>
         <v>225</v>
@@ -20770,7 +20766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A227">
         <f>計算表!A227</f>
         <v>226</v>
@@ -20844,7 +20840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A228">
         <f>計算表!A228</f>
         <v>227</v>
@@ -20918,7 +20914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A229">
         <f>計算表!A229</f>
         <v>228</v>
@@ -20992,7 +20988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A230">
         <f>計算表!A230</f>
         <v>229</v>
@@ -21066,7 +21062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A231">
         <f>計算表!A231</f>
         <v>230</v>
@@ -21140,7 +21136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A232">
         <f>計算表!A232</f>
         <v>231</v>
@@ -21214,7 +21210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A233">
         <f>計算表!A233</f>
         <v>232</v>
@@ -21288,7 +21284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A234">
         <f>計算表!A234</f>
         <v>233</v>
@@ -21362,7 +21358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A235">
         <f>計算表!A235</f>
         <v>234</v>
@@ -21436,7 +21432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A236">
         <f>計算表!A236</f>
         <v>235</v>
@@ -21510,7 +21506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A237">
         <f>計算表!A237</f>
         <v>236</v>
@@ -21584,7 +21580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A238">
         <f>計算表!A238</f>
         <v>237</v>
@@ -21658,7 +21654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A239">
         <f>計算表!A239</f>
         <v>238</v>
@@ -21732,7 +21728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A240">
         <f>計算表!A240</f>
         <v>239</v>
@@ -21806,7 +21802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A241">
         <f>計算表!A241</f>
         <v>240</v>
@@ -21880,7 +21876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A242">
         <f>計算表!A242</f>
         <v>241</v>
@@ -21954,7 +21950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A243">
         <f>計算表!A243</f>
         <v>242</v>
@@ -22028,7 +22024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A244">
         <f>計算表!A244</f>
         <v>243</v>
@@ -22102,7 +22098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A245">
         <f>計算表!A245</f>
         <v>244</v>
@@ -22176,7 +22172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A246">
         <f>計算表!A246</f>
         <v>245</v>
@@ -22250,7 +22246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A247">
         <f>計算表!A247</f>
         <v>246</v>
@@ -22324,7 +22320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A248">
         <f>計算表!A248</f>
         <v>247</v>
@@ -22398,7 +22394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A249">
         <f>計算表!A249</f>
         <v>248</v>
@@ -22472,7 +22468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A250">
         <f>計算表!A250</f>
         <v>249</v>
@@ -22546,7 +22542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A251">
         <f>計算表!A251</f>
         <v>250</v>
@@ -22620,7 +22616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A252">
         <f>計算表!A252</f>
         <v>251</v>
@@ -22694,7 +22690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A253">
         <f>計算表!A253</f>
         <v>252</v>
@@ -22768,7 +22764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A254">
         <f>計算表!A254</f>
         <v>253</v>
@@ -22842,7 +22838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A255">
         <f>計算表!A255</f>
         <v>254</v>
@@ -22916,7 +22912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A256">
         <f>計算表!A256</f>
         <v>255</v>
@@ -22990,7 +22986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A257">
         <f>計算表!A257</f>
         <v>256</v>
@@ -23064,7 +23060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A258">
         <f>計算表!A258</f>
         <v>257</v>
@@ -23138,7 +23134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A259">
         <f>計算表!A259</f>
         <v>258</v>
@@ -23212,7 +23208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A260">
         <f>計算表!A260</f>
         <v>259</v>
@@ -23286,7 +23282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A261">
         <f>計算表!A261</f>
         <v>260</v>
@@ -23360,7 +23356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A262">
         <f>計算表!A262</f>
         <v>261</v>
@@ -23434,7 +23430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A263">
         <f>計算表!A263</f>
         <v>262</v>
@@ -23508,7 +23504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A264">
         <f>計算表!A264</f>
         <v>263</v>
@@ -23582,7 +23578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A265">
         <f>計算表!A265</f>
         <v>264</v>
@@ -23656,7 +23652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A266">
         <f>計算表!A266</f>
         <v>265</v>
@@ -23730,7 +23726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A267">
         <f>計算表!A267</f>
         <v>266</v>
@@ -23804,7 +23800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A268">
         <f>計算表!A268</f>
         <v>267</v>
@@ -23878,7 +23874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A269">
         <f>計算表!A269</f>
         <v>268</v>
@@ -23952,7 +23948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A270">
         <f>計算表!A270</f>
         <v>269</v>
@@ -24026,7 +24022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A271">
         <f>計算表!A271</f>
         <v>270</v>
@@ -24100,7 +24096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A272">
         <f>計算表!A272</f>
         <v>271</v>
@@ -24174,7 +24170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A273">
         <f>計算表!A273</f>
         <v>272</v>
@@ -24248,7 +24244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A274">
         <f>計算表!A274</f>
         <v>273</v>
@@ -24322,7 +24318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A275">
         <f>計算表!A275</f>
         <v>274</v>
@@ -24396,7 +24392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A276">
         <f>計算表!A276</f>
         <v>275</v>
@@ -24470,7 +24466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A277">
         <f>計算表!A277</f>
         <v>276</v>
@@ -24544,7 +24540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A278">
         <f>計算表!A278</f>
         <v>277</v>
@@ -24618,7 +24614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A279">
         <f>計算表!A279</f>
         <v>278</v>
@@ -24692,7 +24688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A280">
         <f>計算表!A280</f>
         <v>279</v>
@@ -24766,7 +24762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A281">
         <f>計算表!A281</f>
         <v>280</v>
@@ -24840,7 +24836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A282">
         <f>計算表!A282</f>
         <v>281</v>
@@ -24914,7 +24910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A283">
         <f>計算表!A283</f>
         <v>282</v>
@@ -24988,7 +24984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A284">
         <f>計算表!A284</f>
         <v>283</v>
@@ -25062,7 +25058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A285">
         <f>計算表!A285</f>
         <v>284</v>
@@ -25136,7 +25132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A286">
         <f>計算表!A286</f>
         <v>285</v>
@@ -25210,7 +25206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A287">
         <f>計算表!A287</f>
         <v>286</v>
@@ -25284,7 +25280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A288">
         <f>計算表!A288</f>
         <v>287</v>
@@ -25358,7 +25354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A289">
         <f>計算表!A289</f>
         <v>288</v>
@@ -25432,7 +25428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A290">
         <f>計算表!A290</f>
         <v>289</v>
@@ -25506,7 +25502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A291">
         <f>計算表!A291</f>
         <v>290</v>
@@ -25580,7 +25576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A292">
         <f>計算表!A292</f>
         <v>291</v>
@@ -25654,7 +25650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A293">
         <f>計算表!A293</f>
         <v>292</v>
@@ -25728,7 +25724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A294">
         <f>計算表!A294</f>
         <v>293</v>
@@ -25802,7 +25798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A295">
         <f>計算表!A295</f>
         <v>294</v>
@@ -25876,7 +25872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A296">
         <f>計算表!A296</f>
         <v>295</v>
@@ -25950,7 +25946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A297">
         <f>計算表!A297</f>
         <v>296</v>
@@ -26024,7 +26020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A298">
         <f>計算表!A298</f>
         <v>297</v>
@@ -26098,7 +26094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A299">
         <f>計算表!A299</f>
         <v>298</v>
@@ -26172,7 +26168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A300">
         <f>計算表!A300</f>
         <v>299</v>
@@ -26246,7 +26242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A301">
         <f>計算表!A301</f>
         <v>300</v>
@@ -26320,7 +26316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A302">
         <f>計算表!A302</f>
         <v>301</v>
@@ -26394,7 +26390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A303">
         <f>計算表!A303</f>
         <v>302</v>
@@ -26468,7 +26464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A304">
         <f>計算表!A304</f>
         <v>303</v>
@@ -26542,7 +26538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A305">
         <f>計算表!A305</f>
         <v>304</v>
@@ -26616,7 +26612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A306">
         <f>計算表!A306</f>
         <v>305</v>
@@ -26690,7 +26686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A307">
         <f>計算表!A307</f>
         <v>306</v>
@@ -26764,7 +26760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A308">
         <f>計算表!A308</f>
         <v>307</v>
@@ -26838,7 +26834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A309">
         <f>計算表!A309</f>
         <v>308</v>
@@ -26912,7 +26908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A310">
         <f>計算表!A310</f>
         <v>309</v>
@@ -26986,7 +26982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A311">
         <f>計算表!A311</f>
         <v>310</v>
@@ -27060,7 +27056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A312">
         <f>計算表!A312</f>
         <v>311</v>
@@ -27134,7 +27130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A313">
         <f>計算表!A313</f>
         <v>312</v>
@@ -27208,7 +27204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A314">
         <f>計算表!A314</f>
         <v>313</v>
@@ -27282,7 +27278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A315">
         <f>計算表!A315</f>
         <v>314</v>
@@ -27356,7 +27352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A316">
         <f>計算表!A316</f>
         <v>315</v>
@@ -27430,7 +27426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A317">
         <f>計算表!A317</f>
         <v>316</v>
@@ -27504,7 +27500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A318">
         <f>計算表!A318</f>
         <v>317</v>
@@ -27578,7 +27574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A319">
         <f>計算表!A319</f>
         <v>318</v>
@@ -27652,7 +27648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A320">
         <f>計算表!A320</f>
         <v>319</v>
@@ -27726,7 +27722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A321">
         <f>計算表!A321</f>
         <v>320</v>
@@ -27800,7 +27796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A322">
         <f>計算表!A322</f>
         <v>321</v>
@@ -27874,7 +27870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A323">
         <f>計算表!A323</f>
         <v>322</v>
@@ -27948,7 +27944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A324">
         <f>計算表!A324</f>
         <v>323</v>
@@ -28022,7 +28018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A325">
         <f>計算表!A325</f>
         <v>324</v>
@@ -28096,7 +28092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A326">
         <f>計算表!A326</f>
         <v>325</v>
@@ -28170,7 +28166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A327">
         <f>計算表!A327</f>
         <v>326</v>
@@ -28244,7 +28240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A328">
         <f>計算表!A328</f>
         <v>327</v>
@@ -28318,7 +28314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A329">
         <f>計算表!A329</f>
         <v>328</v>
@@ -28392,7 +28388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A330">
         <f>計算表!A330</f>
         <v>329</v>
@@ -28466,7 +28462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A331">
         <f>計算表!A331</f>
         <v>330</v>
@@ -28540,7 +28536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A332">
         <f>計算表!A332</f>
         <v>331</v>
@@ -28614,7 +28610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A333">
         <f>計算表!A333</f>
         <v>332</v>
@@ -28688,7 +28684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A334">
         <f>計算表!A334</f>
         <v>333</v>
@@ -28762,7 +28758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A335">
         <f>計算表!A335</f>
         <v>334</v>
@@ -28836,7 +28832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A336">
         <f>計算表!A336</f>
         <v>335</v>
@@ -28910,7 +28906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A337">
         <f>計算表!A337</f>
         <v>336</v>
@@ -28984,7 +28980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A338">
         <f>計算表!A338</f>
         <v>337</v>
@@ -29058,7 +29054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A339">
         <f>計算表!A339</f>
         <v>338</v>
@@ -29132,7 +29128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A340">
         <f>計算表!A340</f>
         <v>339</v>
@@ -29206,7 +29202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A341">
         <f>計算表!A341</f>
         <v>340</v>
@@ -29280,7 +29276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A342">
         <f>計算表!A342</f>
         <v>341</v>
@@ -29354,7 +29350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A343">
         <f>計算表!A343</f>
         <v>342</v>
@@ -29428,7 +29424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A344">
         <f>計算表!A344</f>
         <v>343</v>
@@ -29502,7 +29498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A345">
         <f>計算表!A345</f>
         <v>344</v>
@@ -29576,7 +29572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A346">
         <f>計算表!A346</f>
         <v>345</v>
@@ -29650,7 +29646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A347">
         <f>計算表!A347</f>
         <v>346</v>
@@ -29724,7 +29720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A348">
         <f>計算表!A348</f>
         <v>347</v>
@@ -30177,14 +30173,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R353"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="21.140625" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="6" width="21.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -30240,7 +30236,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -30296,7 +30292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -30353,7 +30349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
@@ -30410,7 +30406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -30467,7 +30463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -30524,7 +30520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -30581,7 +30577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -30638,7 +30634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -30695,7 +30691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -30752,7 +30748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -30809,7 +30805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -30866,7 +30862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -30923,7 +30919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -30980,7 +30976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -31037,7 +31033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -31094,7 +31090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -31151,7 +31147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -31208,7 +31204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -31265,7 +31261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -31322,7 +31318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -31379,7 +31375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -31436,7 +31432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -31493,7 +31489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -31550,7 +31546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -31607,7 +31603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -31664,7 +31660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -31721,7 +31717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -31778,7 +31774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -31835,7 +31831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -31892,7 +31888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -31949,7 +31945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -32006,7 +32002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -32063,7 +32059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -32120,7 +32116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -32177,7 +32173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -32234,7 +32230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -32291,7 +32287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -32348,7 +32344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -32405,7 +32401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -32462,7 +32458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -32519,7 +32515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -32576,7 +32572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -32633,7 +32629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -32690,7 +32686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -32747,7 +32743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -32804,7 +32800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -32861,7 +32857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -32918,7 +32914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -32975,7 +32971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -33032,7 +33028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -33089,7 +33085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -33146,7 +33142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -33203,7 +33199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -33260,7 +33256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -33317,7 +33313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -33374,7 +33370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -33431,7 +33427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -33488,7 +33484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -33545,7 +33541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -33602,7 +33598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -33659,7 +33655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -33716,7 +33712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -33773,7 +33769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -33830,7 +33826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -33887,7 +33883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -33944,7 +33940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -34001,7 +33997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68">
         <f t="shared" ref="A68:A131" si="1">A67+1</f>
         <v>67</v>
@@ -34058,7 +34054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69">
         <f t="shared" si="1"/>
         <v>68</v>
@@ -34115,7 +34111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -34172,7 +34168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>70</v>
@@ -34229,7 +34225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -34286,7 +34282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -34343,7 +34339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -34400,7 +34396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -34457,7 +34453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -34514,7 +34510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -34571,7 +34567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -34628,7 +34624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -34685,7 +34681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -34742,7 +34738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -34799,7 +34795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -34856,7 +34852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -34913,7 +34909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -34970,7 +34966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>84</v>
@@ -35027,7 +35023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>85</v>
@@ -35084,7 +35080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>86</v>
@@ -35141,7 +35137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -35198,7 +35194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>88</v>
@@ -35255,7 +35251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>89</v>
@@ -35312,7 +35308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>90</v>
@@ -35369,7 +35365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>91</v>
@@ -35426,7 +35422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -35483,7 +35479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>93</v>
@@ -35540,7 +35536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>94</v>
@@ -35597,7 +35593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -35654,7 +35650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>96</v>
@@ -35711,7 +35707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -35768,7 +35764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -35825,7 +35821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>99</v>
@@ -35882,7 +35878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -35939,7 +35935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>101</v>
@@ -35996,7 +35992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103">
         <f t="shared" si="1"/>
         <v>102</v>
@@ -36074,13 +36070,13 @@
         <v>298</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>1070</v>
-      </c>
-      <c r="H104" s="2" t="s">
-        <v>1071</v>
-      </c>
-      <c r="I104" s="2" t="s">
-        <v>1072</v>
+        <v>1074</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -36131,16 +36127,16 @@
         <v>298</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>1073</v>
-      </c>
-      <c r="I105" s="2" t="s">
         <v>1075</v>
       </c>
-      <c r="J105" s="2" t="s">
-        <v>1076</v>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
       </c>
       <c r="K105">
         <v>0</v>
@@ -36188,19 +36184,19 @@
         <v>298</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>1080</v>
-      </c>
-      <c r="J106" s="2" t="s">
-        <v>1077</v>
-      </c>
-      <c r="K106" s="2" t="s">
-        <v>1078</v>
+        <v>1072</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>0</v>
       </c>
       <c r="L106">
         <v>0</v>
@@ -36245,22 +36241,22 @@
         <v>298</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>1077</v>
-      </c>
-      <c r="K107" s="2" t="s">
-        <v>1081</v>
-      </c>
-      <c r="L107" t="s">
-        <v>304</v>
+        <v>1078</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
       </c>
       <c r="M107">
         <v>0</v>
@@ -36302,25 +36298,25 @@
         <v>298</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>1085</v>
+        <v>1071</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>1074</v>
+        <v>1082</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>1087</v>
+        <v>1070</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>1086</v>
-      </c>
-      <c r="L108" t="s">
-        <v>304</v>
-      </c>
-      <c r="M108" s="2" t="s">
-        <v>1083</v>
+        <v>1081</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
       </c>
       <c r="N108">
         <v>0</v>
@@ -36338,7 +36334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -36395,7 +36391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110">
         <f t="shared" si="1"/>
         <v>109</v>
@@ -36452,7 +36448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111">
         <f t="shared" si="1"/>
         <v>110</v>
@@ -36509,7 +36505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112">
         <f t="shared" si="1"/>
         <v>111</v>
@@ -36566,7 +36562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113">
         <f t="shared" si="1"/>
         <v>112</v>
@@ -36623,7 +36619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114">
         <f t="shared" si="1"/>
         <v>113</v>
@@ -36680,7 +36676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115">
         <f t="shared" si="1"/>
         <v>114</v>
@@ -36737,7 +36733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116">
         <f t="shared" si="1"/>
         <v>115</v>
@@ -36794,7 +36790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117">
         <f t="shared" si="1"/>
         <v>116</v>
@@ -36851,7 +36847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118">
         <f t="shared" si="1"/>
         <v>117</v>
@@ -36908,7 +36904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119">
         <f t="shared" si="1"/>
         <v>118</v>
@@ -36965,7 +36961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120">
         <f t="shared" si="1"/>
         <v>119</v>
@@ -37022,7 +37018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121">
         <f t="shared" si="1"/>
         <v>120</v>
@@ -37079,7 +37075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122">
         <f t="shared" si="1"/>
         <v>121</v>
@@ -37136,7 +37132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123">
         <f t="shared" si="1"/>
         <v>122</v>
@@ -37193,7 +37189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124">
         <f t="shared" si="1"/>
         <v>123</v>
@@ -37250,7 +37246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125">
         <f t="shared" si="1"/>
         <v>124</v>
@@ -37307,7 +37303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126">
         <f t="shared" si="1"/>
         <v>125</v>
@@ -37364,7 +37360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127">
         <f t="shared" si="1"/>
         <v>126</v>
@@ -37421,7 +37417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -37478,7 +37474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129">
         <f t="shared" si="1"/>
         <v>128</v>
@@ -37535,7 +37531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130">
         <f t="shared" si="1"/>
         <v>129</v>
@@ -37592,7 +37588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131">
         <f t="shared" si="1"/>
         <v>130</v>
@@ -37649,7 +37645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132">
         <f t="shared" ref="A132:A195" si="2">A131+1</f>
         <v>131</v>
@@ -37706,7 +37702,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133">
         <f t="shared" si="2"/>
         <v>132</v>
@@ -37763,7 +37759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134">
         <f t="shared" si="2"/>
         <v>133</v>
@@ -37820,7 +37816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135">
         <f t="shared" si="2"/>
         <v>134</v>
@@ -37877,7 +37873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136">
         <f t="shared" si="2"/>
         <v>135</v>
@@ -37934,7 +37930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137">
         <f t="shared" si="2"/>
         <v>136</v>
@@ -37991,7 +37987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138">
         <f t="shared" si="2"/>
         <v>137</v>
@@ -38048,7 +38044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139">
         <f t="shared" si="2"/>
         <v>138</v>
@@ -38105,7 +38101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140">
         <f t="shared" si="2"/>
         <v>139</v>
@@ -38162,7 +38158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141">
         <f t="shared" si="2"/>
         <v>140</v>
@@ -38219,7 +38215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142">
         <f t="shared" si="2"/>
         <v>141</v>
@@ -38276,7 +38272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143">
         <f t="shared" si="2"/>
         <v>142</v>
@@ -38333,7 +38329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144">
         <f t="shared" si="2"/>
         <v>143</v>
@@ -38390,7 +38386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145">
         <f t="shared" si="2"/>
         <v>144</v>
@@ -38447,7 +38443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146">
         <f t="shared" si="2"/>
         <v>145</v>
@@ -38504,7 +38500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147">
         <f t="shared" si="2"/>
         <v>146</v>
@@ -38561,7 +38557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148">
         <f t="shared" si="2"/>
         <v>147</v>
@@ -38618,7 +38614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149">
         <f t="shared" si="2"/>
         <v>148</v>
@@ -38675,7 +38671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150">
         <f t="shared" si="2"/>
         <v>149</v>
@@ -38732,7 +38728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151">
         <f t="shared" si="2"/>
         <v>150</v>
@@ -38789,7 +38785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152">
         <f t="shared" si="2"/>
         <v>151</v>
@@ -38846,7 +38842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153">
         <f t="shared" si="2"/>
         <v>152</v>
@@ -38903,7 +38899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154">
         <f t="shared" si="2"/>
         <v>153</v>
@@ -38960,7 +38956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155">
         <f t="shared" si="2"/>
         <v>154</v>
@@ -39017,7 +39013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156">
         <f t="shared" si="2"/>
         <v>155</v>
@@ -39074,7 +39070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157">
         <f t="shared" si="2"/>
         <v>156</v>
@@ -39131,7 +39127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158">
         <f t="shared" si="2"/>
         <v>157</v>
@@ -39188,7 +39184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159">
         <f t="shared" si="2"/>
         <v>158</v>
@@ -39245,7 +39241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160">
         <f t="shared" si="2"/>
         <v>159</v>
@@ -39302,7 +39298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161">
         <f t="shared" si="2"/>
         <v>160</v>
@@ -39359,7 +39355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162">
         <f t="shared" si="2"/>
         <v>161</v>
@@ -39416,7 +39412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163">
         <f t="shared" si="2"/>
         <v>162</v>
@@ -39473,7 +39469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164">
         <f t="shared" si="2"/>
         <v>163</v>
@@ -39530,7 +39526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165">
         <f t="shared" si="2"/>
         <v>164</v>
@@ -39587,7 +39583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166">
         <f t="shared" si="2"/>
         <v>165</v>
@@ -39644,7 +39640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167">
         <f t="shared" si="2"/>
         <v>166</v>
@@ -39701,7 +39697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168">
         <f t="shared" si="2"/>
         <v>167</v>
@@ -39758,7 +39754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169">
         <f t="shared" si="2"/>
         <v>168</v>
@@ -39815,7 +39811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170">
         <f t="shared" si="2"/>
         <v>169</v>
@@ -39872,7 +39868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171">
         <f t="shared" si="2"/>
         <v>170</v>
@@ -39929,7 +39925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172">
         <f t="shared" si="2"/>
         <v>171</v>
@@ -39986,7 +39982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173">
         <f t="shared" si="2"/>
         <v>172</v>
@@ -40043,7 +40039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174">
         <f t="shared" si="2"/>
         <v>173</v>
@@ -40100,7 +40096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175">
         <f t="shared" si="2"/>
         <v>174</v>
@@ -40157,7 +40153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176">
         <f t="shared" si="2"/>
         <v>175</v>
@@ -40214,7 +40210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177">
         <f t="shared" si="2"/>
         <v>176</v>
@@ -40271,7 +40267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178">
         <f t="shared" si="2"/>
         <v>177</v>
@@ -40328,7 +40324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179">
         <f t="shared" si="2"/>
         <v>178</v>
@@ -40385,7 +40381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180">
         <f t="shared" si="2"/>
         <v>179</v>
@@ -40442,7 +40438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181">
         <f t="shared" si="2"/>
         <v>180</v>
@@ -40499,7 +40495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182">
         <f t="shared" si="2"/>
         <v>181</v>
@@ -40556,7 +40552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183">
         <f t="shared" si="2"/>
         <v>182</v>
@@ -40613,7 +40609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184">
         <f t="shared" si="2"/>
         <v>183</v>
@@ -40670,7 +40666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185">
         <f t="shared" si="2"/>
         <v>184</v>
@@ -40727,7 +40723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186">
         <f t="shared" si="2"/>
         <v>185</v>
@@ -40784,7 +40780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187">
         <f t="shared" si="2"/>
         <v>186</v>
@@ -40841,7 +40837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188">
         <f t="shared" si="2"/>
         <v>187</v>
@@ -40898,7 +40894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189">
         <f t="shared" si="2"/>
         <v>188</v>
@@ -40955,7 +40951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -41012,7 +41008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191">
         <f t="shared" si="2"/>
         <v>190</v>
@@ -41069,7 +41065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192">
         <f t="shared" si="2"/>
         <v>191</v>
@@ -41126,7 +41122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193">
         <f t="shared" si="2"/>
         <v>192</v>
@@ -41183,7 +41179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194">
         <f t="shared" si="2"/>
         <v>193</v>
@@ -41240,7 +41236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195">
         <f t="shared" si="2"/>
         <v>194</v>
@@ -41297,7 +41293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A196">
         <f t="shared" ref="A196:A259" si="3">A195+1</f>
         <v>195</v>
@@ -41354,7 +41350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A197">
         <f t="shared" si="3"/>
         <v>196</v>
@@ -41411,7 +41407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A198">
         <f t="shared" si="3"/>
         <v>197</v>
@@ -41468,7 +41464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A199">
         <f t="shared" si="3"/>
         <v>198</v>
@@ -41525,7 +41521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A200">
         <f t="shared" si="3"/>
         <v>199</v>
@@ -41582,7 +41578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A201">
         <f t="shared" si="3"/>
         <v>200</v>
@@ -41639,7 +41635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A202">
         <f t="shared" si="3"/>
         <v>201</v>
@@ -41696,7 +41692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A203">
         <f t="shared" si="3"/>
         <v>202</v>
@@ -41753,7 +41749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A204">
         <f t="shared" si="3"/>
         <v>203</v>
@@ -41810,7 +41806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A205">
         <f t="shared" si="3"/>
         <v>204</v>
@@ -41867,7 +41863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A206">
         <f t="shared" si="3"/>
         <v>205</v>
@@ -41924,7 +41920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A207">
         <f t="shared" si="3"/>
         <v>206</v>
@@ -41981,7 +41977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208">
         <f t="shared" si="3"/>
         <v>207</v>
@@ -42038,7 +42034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209">
         <f t="shared" si="3"/>
         <v>208</v>
@@ -42095,7 +42091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210">
         <f t="shared" si="3"/>
         <v>209</v>
@@ -42152,7 +42148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211">
         <f t="shared" si="3"/>
         <v>210</v>
@@ -42209,7 +42205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A212">
         <f t="shared" si="3"/>
         <v>211</v>
@@ -42266,7 +42262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A213">
         <f t="shared" si="3"/>
         <v>212</v>
@@ -42323,7 +42319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A214">
         <f t="shared" si="3"/>
         <v>213</v>
@@ -42380,7 +42376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A215">
         <f t="shared" si="3"/>
         <v>214</v>
@@ -42437,7 +42433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A216">
         <f t="shared" si="3"/>
         <v>215</v>
@@ -42494,7 +42490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217">
         <f t="shared" si="3"/>
         <v>216</v>
@@ -42551,7 +42547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218">
         <f t="shared" si="3"/>
         <v>217</v>
@@ -42608,7 +42604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219">
         <f t="shared" si="3"/>
         <v>218</v>
@@ -42665,7 +42661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220">
         <f t="shared" si="3"/>
         <v>219</v>
@@ -42722,7 +42718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221">
         <f t="shared" si="3"/>
         <v>220</v>
@@ -42779,7 +42775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222">
         <f t="shared" si="3"/>
         <v>221</v>
@@ -42836,7 +42832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A223">
         <f t="shared" si="3"/>
         <v>222</v>
@@ -42893,7 +42889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224">
         <f t="shared" si="3"/>
         <v>223</v>
@@ -42950,7 +42946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A225">
         <f t="shared" si="3"/>
         <v>224</v>
@@ -43007,7 +43003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A226">
         <f t="shared" si="3"/>
         <v>225</v>
@@ -43064,7 +43060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A227">
         <f t="shared" si="3"/>
         <v>226</v>
@@ -43121,7 +43117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A228">
         <f t="shared" si="3"/>
         <v>227</v>
@@ -43178,7 +43174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A229">
         <f t="shared" si="3"/>
         <v>228</v>
@@ -43235,7 +43231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A230">
         <f t="shared" si="3"/>
         <v>229</v>
@@ -43292,7 +43288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A231">
         <f t="shared" si="3"/>
         <v>230</v>
@@ -43349,7 +43345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A232">
         <f t="shared" si="3"/>
         <v>231</v>
@@ -43406,7 +43402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A233">
         <f t="shared" si="3"/>
         <v>232</v>
@@ -43463,7 +43459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A234">
         <f t="shared" si="3"/>
         <v>233</v>
@@ -43520,7 +43516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A235">
         <f t="shared" si="3"/>
         <v>234</v>
@@ -43577,7 +43573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A236">
         <f t="shared" si="3"/>
         <v>235</v>
@@ -43634,7 +43630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A237">
         <f t="shared" si="3"/>
         <v>236</v>
@@ -43691,7 +43687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A238">
         <f t="shared" si="3"/>
         <v>237</v>
@@ -43748,7 +43744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A239">
         <f t="shared" si="3"/>
         <v>238</v>
@@ -43805,7 +43801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A240">
         <f t="shared" si="3"/>
         <v>239</v>
@@ -43862,7 +43858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A241">
         <f t="shared" si="3"/>
         <v>240</v>
@@ -43919,7 +43915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A242">
         <f t="shared" si="3"/>
         <v>241</v>
@@ -43976,7 +43972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A243">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -44033,7 +44029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A244">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -44090,7 +44086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A245">
         <f t="shared" si="3"/>
         <v>244</v>
@@ -44147,7 +44143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A246">
         <f t="shared" si="3"/>
         <v>245</v>
@@ -44204,7 +44200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A247">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -44261,7 +44257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A248">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -44318,7 +44314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A249">
         <f t="shared" si="3"/>
         <v>248</v>
@@ -44375,7 +44371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A250">
         <f t="shared" si="3"/>
         <v>249</v>
@@ -44432,7 +44428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A251">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -44489,7 +44485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A252">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -44546,7 +44542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A253">
         <f t="shared" si="3"/>
         <v>252</v>
@@ -44603,7 +44599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A254">
         <f t="shared" si="3"/>
         <v>253</v>
@@ -44660,7 +44656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A255">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -44717,7 +44713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A256">
         <f t="shared" si="3"/>
         <v>255</v>
@@ -44774,7 +44770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A257">
         <f t="shared" si="3"/>
         <v>256</v>
@@ -44831,7 +44827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A258">
         <f t="shared" si="3"/>
         <v>257</v>
@@ -44888,7 +44884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A259">
         <f t="shared" si="3"/>
         <v>258</v>
@@ -44945,7 +44941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A260">
         <f t="shared" ref="A260:A323" si="4">A259+1</f>
         <v>259</v>
@@ -45002,7 +44998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A261">
         <f t="shared" si="4"/>
         <v>260</v>
@@ -45059,7 +45055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A262">
         <f t="shared" si="4"/>
         <v>261</v>
@@ -45116,7 +45112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A263">
         <f t="shared" si="4"/>
         <v>262</v>
@@ -45173,7 +45169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A264">
         <f t="shared" si="4"/>
         <v>263</v>
@@ -45230,7 +45226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A265">
         <f t="shared" si="4"/>
         <v>264</v>
@@ -45287,7 +45283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A266">
         <f t="shared" si="4"/>
         <v>265</v>
@@ -45344,7 +45340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A267">
         <f t="shared" si="4"/>
         <v>266</v>
@@ -45401,7 +45397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A268">
         <f t="shared" si="4"/>
         <v>267</v>
@@ -45458,7 +45454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A269">
         <f t="shared" si="4"/>
         <v>268</v>
@@ -45515,7 +45511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A270">
         <f t="shared" si="4"/>
         <v>269</v>
@@ -45572,7 +45568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A271">
         <f t="shared" si="4"/>
         <v>270</v>
@@ -45629,7 +45625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A272">
         <f t="shared" si="4"/>
         <v>271</v>
@@ -45686,7 +45682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A273">
         <f t="shared" si="4"/>
         <v>272</v>
@@ -45743,7 +45739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A274">
         <f t="shared" si="4"/>
         <v>273</v>
@@ -45800,7 +45796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A275">
         <f t="shared" si="4"/>
         <v>274</v>
@@ -45857,7 +45853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A276">
         <f t="shared" si="4"/>
         <v>275</v>
@@ -45914,7 +45910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A277">
         <f t="shared" si="4"/>
         <v>276</v>
@@ -45971,7 +45967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A278">
         <f t="shared" si="4"/>
         <v>277</v>
@@ -46028,7 +46024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A279">
         <f t="shared" si="4"/>
         <v>278</v>
@@ -46085,7 +46081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A280">
         <f t="shared" si="4"/>
         <v>279</v>
@@ -46142,7 +46138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A281">
         <f t="shared" si="4"/>
         <v>280</v>
@@ -46199,7 +46195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A282">
         <f t="shared" si="4"/>
         <v>281</v>
@@ -46256,7 +46252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A283">
         <f t="shared" si="4"/>
         <v>282</v>
@@ -46313,7 +46309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A284">
         <f t="shared" si="4"/>
         <v>283</v>
@@ -46370,7 +46366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A285">
         <f t="shared" si="4"/>
         <v>284</v>
@@ -46427,7 +46423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A286">
         <f t="shared" si="4"/>
         <v>285</v>
@@ -46484,7 +46480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A287">
         <f t="shared" si="4"/>
         <v>286</v>
@@ -46541,7 +46537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A288">
         <f t="shared" si="4"/>
         <v>287</v>
@@ -46598,7 +46594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A289">
         <f t="shared" si="4"/>
         <v>288</v>
@@ -46655,7 +46651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A290">
         <f t="shared" si="4"/>
         <v>289</v>
@@ -46712,7 +46708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A291">
         <f t="shared" si="4"/>
         <v>290</v>
@@ -46769,7 +46765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A292">
         <f t="shared" si="4"/>
         <v>291</v>
@@ -46826,7 +46822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A293">
         <f t="shared" si="4"/>
         <v>292</v>
@@ -46883,7 +46879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A294">
         <f t="shared" si="4"/>
         <v>293</v>
@@ -46940,7 +46936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A295">
         <f t="shared" si="4"/>
         <v>294</v>
@@ -46997,7 +46993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A296">
         <f t="shared" si="4"/>
         <v>295</v>
@@ -47054,7 +47050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A297">
         <f t="shared" si="4"/>
         <v>296</v>
@@ -47111,7 +47107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A298">
         <f t="shared" si="4"/>
         <v>297</v>
@@ -47168,7 +47164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A299">
         <f t="shared" si="4"/>
         <v>298</v>
@@ -47225,7 +47221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A300">
         <f t="shared" si="4"/>
         <v>299</v>
@@ -47282,7 +47278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A301">
         <f t="shared" si="4"/>
         <v>300</v>
@@ -47339,7 +47335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A302">
         <f t="shared" si="4"/>
         <v>301</v>
@@ -47396,7 +47392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A303">
         <f t="shared" si="4"/>
         <v>302</v>
@@ -47453,7 +47449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A304">
         <f t="shared" si="4"/>
         <v>303</v>
@@ -47510,7 +47506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A305">
         <f t="shared" si="4"/>
         <v>304</v>
@@ -47567,7 +47563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A306">
         <f t="shared" si="4"/>
         <v>305</v>
@@ -47624,7 +47620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A307">
         <f t="shared" si="4"/>
         <v>306</v>
@@ -47681,7 +47677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A308">
         <f t="shared" si="4"/>
         <v>307</v>
@@ -47738,7 +47734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A309">
         <f t="shared" si="4"/>
         <v>308</v>
@@ -47795,7 +47791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A310">
         <f t="shared" si="4"/>
         <v>309</v>
@@ -47852,7 +47848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A311">
         <f t="shared" si="4"/>
         <v>310</v>
@@ -47909,7 +47905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A312">
         <f t="shared" si="4"/>
         <v>311</v>
@@ -47966,7 +47962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A313">
         <f t="shared" si="4"/>
         <v>312</v>
@@ -48023,7 +48019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A314">
         <f t="shared" si="4"/>
         <v>313</v>
@@ -48080,7 +48076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A315">
         <f t="shared" si="4"/>
         <v>314</v>
@@ -48137,7 +48133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A316">
         <f t="shared" si="4"/>
         <v>315</v>
@@ -48194,7 +48190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A317">
         <f t="shared" si="4"/>
         <v>316</v>
@@ -48251,7 +48247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A318">
         <f t="shared" si="4"/>
         <v>317</v>
@@ -48308,7 +48304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A319">
         <f t="shared" si="4"/>
         <v>318</v>
@@ -48365,7 +48361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A320">
         <f t="shared" si="4"/>
         <v>319</v>
@@ -48422,7 +48418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A321">
         <f t="shared" si="4"/>
         <v>320</v>
@@ -48479,7 +48475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A322">
         <f t="shared" si="4"/>
         <v>321</v>
@@ -48536,7 +48532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A323">
         <f t="shared" si="4"/>
         <v>322</v>
@@ -48593,7 +48589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A324">
         <f t="shared" ref="A324:A353" si="5">A323+1</f>
         <v>323</v>
@@ -48650,7 +48646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A325">
         <f t="shared" si="5"/>
         <v>324</v>
@@ -48707,7 +48703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A326">
         <f t="shared" si="5"/>
         <v>325</v>
@@ -48764,7 +48760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A327">
         <f t="shared" si="5"/>
         <v>326</v>
@@ -48821,7 +48817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A328">
         <f t="shared" si="5"/>
         <v>327</v>
@@ -48878,7 +48874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A329">
         <f t="shared" si="5"/>
         <v>328</v>
@@ -48935,7 +48931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A330">
         <f t="shared" si="5"/>
         <v>329</v>
@@ -48992,7 +48988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A331">
         <f t="shared" si="5"/>
         <v>330</v>
@@ -49049,7 +49045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A332">
         <f t="shared" si="5"/>
         <v>331</v>
@@ -49106,7 +49102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A333">
         <f t="shared" si="5"/>
         <v>332</v>
@@ -49163,7 +49159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A334">
         <f t="shared" si="5"/>
         <v>333</v>
@@ -49220,7 +49216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A335">
         <f t="shared" si="5"/>
         <v>334</v>
@@ -49277,7 +49273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A336">
         <f t="shared" si="5"/>
         <v>335</v>
@@ -49334,7 +49330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A337">
         <f t="shared" si="5"/>
         <v>336</v>
@@ -49391,7 +49387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A338">
         <f t="shared" si="5"/>
         <v>337</v>
@@ -49448,7 +49444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A339">
         <f t="shared" si="5"/>
         <v>338</v>
@@ -49505,7 +49501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A340">
         <f t="shared" si="5"/>
         <v>339</v>
@@ -49562,7 +49558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A341">
         <f t="shared" si="5"/>
         <v>340</v>
@@ -49619,7 +49615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A342">
         <f t="shared" si="5"/>
         <v>341</v>
@@ -49676,7 +49672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A343">
         <f t="shared" si="5"/>
         <v>342</v>
@@ -49733,7 +49729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A344">
         <f t="shared" si="5"/>
         <v>343</v>
@@ -49790,7 +49786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A345">
         <f t="shared" si="5"/>
         <v>344</v>
@@ -49847,7 +49843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A346">
         <f t="shared" si="5"/>
         <v>345</v>
@@ -49904,7 +49900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A347">
         <f t="shared" si="5"/>
         <v>346</v>
@@ -49961,7 +49957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A348">
         <f t="shared" si="5"/>
         <v>347</v>
@@ -50018,7 +50014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A349">
         <f t="shared" si="5"/>
         <v>348</v>
@@ -50075,7 +50071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A350">
         <f t="shared" si="5"/>
         <v>349</v>
@@ -50132,7 +50128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A351">
         <f t="shared" si="5"/>
         <v>350</v>
@@ -50189,7 +50185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A352">
         <f t="shared" si="5"/>
         <v>351</v>
@@ -50246,7 +50242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A353">
         <f t="shared" si="5"/>
         <v>352</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\develop\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02954F51-4FC1-4A5A-A4C3-958CC6A35493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8ED1BF-C970-4889-AEE3-4352C1306D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -2830,9 +2830,6 @@
   </si>
   <si>
     <t>技能最短施放間隔；普攻擊殺後換目標也沿用此間隔。</t>
-  </si>
-  <si>
-    <t>⌊a×當前等級 + b^(1 + 當前等級/c)⌋</t>
   </si>
   <si>
     <t>上限 5,000,000；降級全額退還。</t>
@@ -3640,6 +3637,51 @@
   </si>
   <si>
     <t>{1~3,64}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>a×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>當前等級</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + b^(1 + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>當前等級</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/c)</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4059,6 +4101,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R353"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="6" width="23.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -10729,7 +10774,7 @@
       </c>
       <c r="G91">
         <f>計算表!G91</f>
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="H91">
         <f>計算表!H91</f>
@@ -10803,7 +10848,7 @@
       </c>
       <c r="G92">
         <f>計算表!G92</f>
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="H92">
         <f>計算表!H92</f>
@@ -26261,7 +26306,7 @@
       </c>
       <c r="E301" t="str">
         <f>計算表!E301</f>
-        <v>⌊a×當前等級 + b^(1 + 當前等級/c)⌋</v>
+        <v>a×當前等級 + b^(1 + 當前等級/c)</v>
       </c>
       <c r="F301" t="str">
         <f>計算表!F301</f>
@@ -26269,7 +26314,7 @@
       </c>
       <c r="G301">
         <f>計算表!G301</f>
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H301">
         <f>計算表!H301</f>
@@ -30177,7 +30222,8 @@
   <cols>
     <col min="3" max="3" width="21.140625" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="6" width="21.140625" customWidth="1"/>
+    <col min="5" max="5" width="36.28515625" customWidth="1"/>
+    <col min="6" max="6" width="21.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -35329,7 +35375,7 @@
         <v>259</v>
       </c>
       <c r="G91">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="H91">
         <v>1</v>
@@ -35386,7 +35432,7 @@
         <v>259</v>
       </c>
       <c r="G92">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="H92">
         <v>1</v>
@@ -36055,13 +36101,13 @@
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C104" t="s">
         <v>295</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="E104" t="s">
         <v>297</v>
@@ -36070,7 +36116,7 @@
         <v>298</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H104">
         <v>0</v>
@@ -36112,13 +36158,13 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C105" t="s">
         <v>295</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="E105" t="s">
         <v>297</v>
@@ -36127,10 +36173,10 @@
         <v>298</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -36169,13 +36215,13 @@
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C106" t="s">
         <v>295</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="E106" t="s">
         <v>297</v>
@@ -36184,13 +36230,13 @@
         <v>298</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="J106">
         <v>0</v>
@@ -36226,13 +36272,13 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C107" t="s">
         <v>295</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="E107" t="s">
         <v>297</v>
@@ -36241,16 +36287,16 @@
         <v>298</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="H107" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="J107" s="2" t="s">
         <v>1077</v>
-      </c>
-      <c r="I107" s="2" t="s">
-        <v>1079</v>
-      </c>
-      <c r="J107" s="2" t="s">
-        <v>1078</v>
       </c>
       <c r="K107">
         <v>0</v>
@@ -36283,13 +36329,13 @@
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C108" t="s">
         <v>295</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="E108" t="s">
         <v>297</v>
@@ -36298,19 +36344,19 @@
         <v>298</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="L108">
         <v>0</v>
@@ -47292,14 +47338,14 @@
       <c r="D301" t="s">
         <v>766</v>
       </c>
-      <c r="E301" t="s">
+      <c r="E301" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F301" t="s">
         <v>932</v>
       </c>
-      <c r="F301" t="s">
-        <v>933</v>
-      </c>
       <c r="G301">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="H301">
         <v>20</v>
@@ -47347,13 +47393,13 @@
         <v>913</v>
       </c>
       <c r="D302" t="s">
+        <v>933</v>
+      </c>
+      <c r="E302" t="s">
         <v>934</v>
       </c>
-      <c r="E302" t="s">
+      <c r="F302" t="s">
         <v>935</v>
-      </c>
-      <c r="F302" t="s">
-        <v>936</v>
       </c>
       <c r="G302">
         <v>0</v>
@@ -47404,13 +47450,13 @@
         <v>913</v>
       </c>
       <c r="D303" t="s">
+        <v>936</v>
+      </c>
+      <c r="E303" t="s">
         <v>937</v>
       </c>
-      <c r="E303" t="s">
+      <c r="F303" t="s">
         <v>938</v>
-      </c>
-      <c r="F303" t="s">
-        <v>939</v>
       </c>
       <c r="G303">
         <v>30</v>
@@ -47458,16 +47504,16 @@
         <v>0</v>
       </c>
       <c r="C304" t="s">
+        <v>939</v>
+      </c>
+      <c r="D304" t="s">
         <v>940</v>
       </c>
-      <c r="D304" t="s">
+      <c r="E304" t="s">
         <v>941</v>
       </c>
-      <c r="E304" t="s">
+      <c r="F304" t="s">
         <v>942</v>
-      </c>
-      <c r="F304" t="s">
-        <v>943</v>
       </c>
       <c r="G304">
         <v>0.75</v>
@@ -47515,13 +47561,13 @@
         <v>0</v>
       </c>
       <c r="C305" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D305" t="s">
+        <v>943</v>
+      </c>
+      <c r="E305" t="s">
         <v>944</v>
-      </c>
-      <c r="E305" t="s">
-        <v>945</v>
       </c>
       <c r="F305">
         <v>0</v>
@@ -47572,16 +47618,16 @@
         <v>0</v>
       </c>
       <c r="C306" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D306" t="s">
+        <v>945</v>
+      </c>
+      <c r="E306" t="s">
         <v>946</v>
       </c>
-      <c r="E306" t="s">
+      <c r="F306" t="s">
         <v>947</v>
-      </c>
-      <c r="F306" t="s">
-        <v>948</v>
       </c>
       <c r="G306">
         <v>45</v>
@@ -47629,16 +47675,16 @@
         <v>0</v>
       </c>
       <c r="C307" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D307" t="s">
+        <v>948</v>
+      </c>
+      <c r="E307" t="s">
         <v>949</v>
       </c>
-      <c r="E307" t="s">
+      <c r="F307" t="s">
         <v>950</v>
-      </c>
-      <c r="F307" t="s">
-        <v>951</v>
       </c>
       <c r="G307">
         <v>0</v>
@@ -47686,16 +47732,16 @@
         <v>0</v>
       </c>
       <c r="C308" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D308" t="s">
+        <v>951</v>
+      </c>
+      <c r="E308" t="s">
         <v>952</v>
       </c>
-      <c r="E308" t="s">
+      <c r="F308" t="s">
         <v>953</v>
-      </c>
-      <c r="F308" t="s">
-        <v>954</v>
       </c>
       <c r="G308">
         <v>0.1</v>
@@ -47743,16 +47789,16 @@
         <v>0</v>
       </c>
       <c r="C309" t="s">
+        <v>954</v>
+      </c>
+      <c r="D309" t="s">
         <v>955</v>
       </c>
-      <c r="D309" t="s">
+      <c r="E309" t="s">
         <v>956</v>
       </c>
-      <c r="E309" t="s">
+      <c r="F309" t="s">
         <v>957</v>
-      </c>
-      <c r="F309" t="s">
-        <v>958</v>
       </c>
       <c r="G309">
         <v>24</v>
@@ -47800,16 +47846,16 @@
         <v>0</v>
       </c>
       <c r="C310" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="D310" t="s">
+        <v>958</v>
+      </c>
+      <c r="E310" t="s">
         <v>959</v>
       </c>
-      <c r="E310" t="s">
+      <c r="F310" t="s">
         <v>960</v>
-      </c>
-      <c r="F310" t="s">
-        <v>961</v>
       </c>
       <c r="G310">
         <v>10</v>
@@ -47857,16 +47903,16 @@
         <v>0</v>
       </c>
       <c r="C311" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="D311" t="s">
+        <v>961</v>
+      </c>
+      <c r="E311" t="s">
         <v>962</v>
       </c>
-      <c r="E311" t="s">
+      <c r="F311" t="s">
         <v>963</v>
-      </c>
-      <c r="F311" t="s">
-        <v>964</v>
       </c>
       <c r="G311">
         <v>20</v>
@@ -47914,16 +47960,16 @@
         <v>0</v>
       </c>
       <c r="C312" t="s">
+        <v>964</v>
+      </c>
+      <c r="D312" t="s">
         <v>965</v>
-      </c>
-      <c r="D312" t="s">
-        <v>966</v>
       </c>
       <c r="E312" t="s">
         <v>39</v>
       </c>
       <c r="F312" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G312">
         <v>1</v>
@@ -47971,16 +48017,16 @@
         <v>0</v>
       </c>
       <c r="C313" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D313" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="E313" t="s">
         <v>39</v>
       </c>
       <c r="F313" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G313">
         <v>1.35</v>
@@ -48028,16 +48074,16 @@
         <v>0</v>
       </c>
       <c r="C314" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D314" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E314" t="s">
         <v>39</v>
       </c>
       <c r="F314" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G314">
         <v>1.75</v>
@@ -48085,16 +48131,16 @@
         <v>0</v>
       </c>
       <c r="C315" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D315" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E315" t="s">
         <v>39</v>
       </c>
       <c r="F315" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G315">
         <v>2.2999999999999998</v>
@@ -48142,16 +48188,16 @@
         <v>0</v>
       </c>
       <c r="C316" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D316" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E316" t="s">
         <v>39</v>
       </c>
       <c r="F316" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G316">
         <v>3</v>
@@ -48199,16 +48245,16 @@
         <v>0</v>
       </c>
       <c r="C317" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D317" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="E317" t="s">
         <v>39</v>
       </c>
       <c r="F317" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G317">
         <v>4</v>
@@ -48256,16 +48302,16 @@
         <v>0</v>
       </c>
       <c r="C318" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D318" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E318" t="s">
         <v>39</v>
       </c>
       <c r="F318" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G318">
         <v>5.2</v>
@@ -48313,16 +48359,16 @@
         <v>0</v>
       </c>
       <c r="C319" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D319" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E319" t="s">
         <v>39</v>
       </c>
       <c r="F319" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G319">
         <v>6.8</v>
@@ -48370,16 +48416,16 @@
         <v>0</v>
       </c>
       <c r="C320" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D320" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E320" t="s">
         <v>39</v>
       </c>
       <c r="F320" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G320">
         <v>10.199999999999999</v>
@@ -48427,22 +48473,22 @@
         <v>0</v>
       </c>
       <c r="C321" t="s">
+        <v>975</v>
+      </c>
+      <c r="D321" t="s">
         <v>976</v>
       </c>
-      <c r="D321" t="s">
+      <c r="E321" t="s">
         <v>977</v>
       </c>
-      <c r="E321" t="s">
+      <c r="F321" t="s">
         <v>978</v>
-      </c>
-      <c r="F321" t="s">
-        <v>979</v>
       </c>
       <c r="G321">
         <v>25</v>
       </c>
       <c r="H321" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="I321">
         <v>0</v>
@@ -48484,22 +48530,22 @@
         <v>0</v>
       </c>
       <c r="C322" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D322" t="s">
+        <v>980</v>
+      </c>
+      <c r="E322" t="s">
+        <v>977</v>
+      </c>
+      <c r="F322" t="s">
         <v>981</v>
-      </c>
-      <c r="E322" t="s">
-        <v>978</v>
-      </c>
-      <c r="F322" t="s">
-        <v>982</v>
       </c>
       <c r="G322">
         <v>20</v>
       </c>
       <c r="H322" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="I322">
         <v>0</v>
@@ -48541,22 +48587,22 @@
         <v>0</v>
       </c>
       <c r="C323" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D323" t="s">
+        <v>982</v>
+      </c>
+      <c r="E323" t="s">
+        <v>977</v>
+      </c>
+      <c r="F323" t="s">
         <v>983</v>
-      </c>
-      <c r="E323" t="s">
-        <v>978</v>
-      </c>
-      <c r="F323" t="s">
-        <v>984</v>
       </c>
       <c r="G323">
         <v>25</v>
       </c>
       <c r="H323" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="I323">
         <v>0</v>
@@ -48598,22 +48644,22 @@
         <v>0</v>
       </c>
       <c r="C324" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D324" t="s">
+        <v>984</v>
+      </c>
+      <c r="E324" t="s">
+        <v>977</v>
+      </c>
+      <c r="F324" t="s">
         <v>985</v>
-      </c>
-      <c r="E324" t="s">
-        <v>978</v>
-      </c>
-      <c r="F324" t="s">
-        <v>986</v>
       </c>
       <c r="G324">
         <v>20</v>
       </c>
       <c r="H324" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="I324">
         <v>0</v>
@@ -48655,22 +48701,22 @@
         <v>0</v>
       </c>
       <c r="C325" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D325" t="s">
+        <v>986</v>
+      </c>
+      <c r="E325" t="s">
+        <v>977</v>
+      </c>
+      <c r="F325" t="s">
         <v>987</v>
-      </c>
-      <c r="E325" t="s">
-        <v>978</v>
-      </c>
-      <c r="F325" t="s">
-        <v>988</v>
       </c>
       <c r="G325">
         <v>0.4</v>
       </c>
       <c r="H325" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="I325">
         <v>0</v>
@@ -48712,22 +48758,22 @@
         <v>0</v>
       </c>
       <c r="C326" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D326" t="s">
+        <v>988</v>
+      </c>
+      <c r="E326" t="s">
+        <v>977</v>
+      </c>
+      <c r="F326" t="s">
         <v>989</v>
-      </c>
-      <c r="E326" t="s">
-        <v>978</v>
-      </c>
-      <c r="F326" t="s">
-        <v>990</v>
       </c>
       <c r="G326">
         <v>3</v>
       </c>
       <c r="H326" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="I326">
         <v>0</v>
@@ -48769,22 +48815,22 @@
         <v>0</v>
       </c>
       <c r="C327" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D327" t="s">
+        <v>990</v>
+      </c>
+      <c r="E327" t="s">
+        <v>977</v>
+      </c>
+      <c r="F327" t="s">
         <v>991</v>
-      </c>
-      <c r="E327" t="s">
-        <v>978</v>
-      </c>
-      <c r="F327" t="s">
-        <v>992</v>
       </c>
       <c r="G327">
         <v>1.5</v>
       </c>
       <c r="H327" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="I327">
         <v>0</v>
@@ -48826,22 +48872,22 @@
         <v>0</v>
       </c>
       <c r="C328" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D328" t="s">
+        <v>992</v>
+      </c>
+      <c r="E328" t="s">
+        <v>977</v>
+      </c>
+      <c r="F328" t="s">
         <v>993</v>
-      </c>
-      <c r="E328" t="s">
-        <v>978</v>
-      </c>
-      <c r="F328" t="s">
-        <v>994</v>
       </c>
       <c r="G328">
         <v>0.15</v>
       </c>
       <c r="H328" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="I328">
         <v>0</v>
@@ -48883,22 +48929,22 @@
         <v>0</v>
       </c>
       <c r="C329" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D329" t="s">
+        <v>994</v>
+      </c>
+      <c r="E329" t="s">
+        <v>977</v>
+      </c>
+      <c r="F329" t="s">
         <v>995</v>
-      </c>
-      <c r="E329" t="s">
-        <v>978</v>
-      </c>
-      <c r="F329" t="s">
-        <v>996</v>
       </c>
       <c r="G329">
         <v>0.5</v>
       </c>
       <c r="H329" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="I329">
         <v>0</v>
@@ -48940,22 +48986,22 @@
         <v>0</v>
       </c>
       <c r="C330" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D330" t="s">
+        <v>996</v>
+      </c>
+      <c r="E330" t="s">
+        <v>977</v>
+      </c>
+      <c r="F330" t="s">
         <v>997</v>
-      </c>
-      <c r="E330" t="s">
-        <v>978</v>
-      </c>
-      <c r="F330" t="s">
-        <v>998</v>
       </c>
       <c r="G330">
         <v>25</v>
       </c>
       <c r="H330" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="I330">
         <v>0</v>
@@ -48997,22 +49043,22 @@
         <v>0</v>
       </c>
       <c r="C331" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D331" t="s">
+        <v>998</v>
+      </c>
+      <c r="E331" t="s">
+        <v>977</v>
+      </c>
+      <c r="F331" t="s">
         <v>999</v>
-      </c>
-      <c r="E331" t="s">
-        <v>978</v>
-      </c>
-      <c r="F331" t="s">
-        <v>1000</v>
       </c>
       <c r="G331">
         <v>8</v>
       </c>
       <c r="H331" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="I331">
         <v>0</v>
@@ -49054,22 +49100,22 @@
         <v>0</v>
       </c>
       <c r="C332" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D332" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E332" t="s">
+        <v>977</v>
+      </c>
+      <c r="F332" t="s">
         <v>1002</v>
-      </c>
-      <c r="E332" t="s">
-        <v>978</v>
-      </c>
-      <c r="F332" t="s">
-        <v>1003</v>
       </c>
       <c r="G332">
         <v>15</v>
       </c>
       <c r="H332" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="I332">
         <v>0</v>
@@ -49111,16 +49157,16 @@
         <v>0</v>
       </c>
       <c r="C333" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D333" t="s">
         <v>1004</v>
       </c>
-      <c r="D333" t="s">
+      <c r="E333" t="s">
         <v>1005</v>
       </c>
-      <c r="E333" t="s">
+      <c r="F333" t="s">
         <v>1006</v>
-      </c>
-      <c r="F333" t="s">
-        <v>1007</v>
       </c>
       <c r="G333">
         <v>0.8</v>
@@ -49168,16 +49214,16 @@
         <v>0</v>
       </c>
       <c r="C334" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D334" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E334" t="s">
         <v>1008</v>
       </c>
-      <c r="E334" t="s">
+      <c r="F334" t="s">
         <v>1009</v>
-      </c>
-      <c r="F334" t="s">
-        <v>1010</v>
       </c>
       <c r="G334">
         <v>3</v>
@@ -49225,16 +49271,16 @@
         <v>0</v>
       </c>
       <c r="C335" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D335" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E335" t="s">
         <v>1011</v>
       </c>
-      <c r="E335" t="s">
+      <c r="F335" t="s">
         <v>1012</v>
-      </c>
-      <c r="F335" t="s">
-        <v>1013</v>
       </c>
       <c r="G335">
         <v>7</v>
@@ -49282,16 +49328,16 @@
         <v>0</v>
       </c>
       <c r="C336" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D336" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E336" t="s">
         <v>1014</v>
       </c>
-      <c r="E336" t="s">
+      <c r="F336" t="s">
         <v>1015</v>
-      </c>
-      <c r="F336" t="s">
-        <v>1016</v>
       </c>
       <c r="G336">
         <v>10</v>
@@ -49339,16 +49385,16 @@
         <v>0</v>
       </c>
       <c r="C337" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D337" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E337" t="s">
         <v>1017</v>
       </c>
-      <c r="E337" t="s">
+      <c r="F337" t="s">
         <v>1018</v>
-      </c>
-      <c r="F337" t="s">
-        <v>1019</v>
       </c>
       <c r="G337">
         <v>2</v>
@@ -49396,16 +49442,16 @@
         <v>0</v>
       </c>
       <c r="C338" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D338" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E338" t="s">
         <v>1020</v>
       </c>
-      <c r="E338" t="s">
+      <c r="F338" t="s">
         <v>1021</v>
-      </c>
-      <c r="F338" t="s">
-        <v>1022</v>
       </c>
       <c r="G338">
         <v>5</v>
@@ -49453,16 +49499,16 @@
         <v>0</v>
       </c>
       <c r="C339" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D339" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E339" t="s">
         <v>1023</v>
       </c>
-      <c r="E339" t="s">
+      <c r="F339" t="s">
         <v>1024</v>
-      </c>
-      <c r="F339" t="s">
-        <v>1025</v>
       </c>
       <c r="G339">
         <v>10</v>
@@ -49510,16 +49556,16 @@
         <v>0</v>
       </c>
       <c r="C340" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D340" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="E340" t="s">
         <v>39</v>
       </c>
       <c r="F340" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="G340">
         <v>15.3</v>
@@ -49567,16 +49613,16 @@
         <v>0</v>
       </c>
       <c r="C341" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="D341" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="E341" t="s">
         <v>39</v>
       </c>
       <c r="F341" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="G341">
         <v>22.95</v>
@@ -49627,13 +49673,13 @@
         <v>647</v>
       </c>
       <c r="D342" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E342" t="s">
         <v>1029</v>
       </c>
-      <c r="E342" t="s">
+      <c r="F342" t="s">
         <v>1030</v>
-      </c>
-      <c r="F342" t="s">
-        <v>1031</v>
       </c>
       <c r="G342">
         <v>20</v>
@@ -49684,13 +49730,13 @@
         <v>647</v>
       </c>
       <c r="D343" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E343" t="s">
         <v>1032</v>
       </c>
-      <c r="E343" t="s">
+      <c r="F343" t="s">
         <v>1033</v>
-      </c>
-      <c r="F343" t="s">
-        <v>1034</v>
       </c>
       <c r="G343">
         <v>500000000</v>
@@ -49741,13 +49787,13 @@
         <v>647</v>
       </c>
       <c r="D344" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E344" t="s">
         <v>1035</v>
       </c>
-      <c r="E344" t="s">
+      <c r="F344" t="s">
         <v>1036</v>
-      </c>
-      <c r="F344" t="s">
-        <v>1037</v>
       </c>
       <c r="G344">
         <v>13</v>
@@ -49798,13 +49844,13 @@
         <v>18</v>
       </c>
       <c r="D345" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E345" t="s">
         <v>1038</v>
       </c>
-      <c r="E345" t="s">
+      <c r="F345" t="s">
         <v>1039</v>
-      </c>
-      <c r="F345" t="s">
-        <v>1040</v>
       </c>
       <c r="G345">
         <v>30</v>
@@ -49855,13 +49901,13 @@
         <v>18</v>
       </c>
       <c r="D346" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E346" t="s">
         <v>1041</v>
       </c>
-      <c r="E346" t="s">
+      <c r="F346" t="s">
         <v>1042</v>
-      </c>
-      <c r="F346" t="s">
-        <v>1043</v>
       </c>
       <c r="G346">
         <v>1000</v>
@@ -49909,16 +49955,16 @@
         <v>0</v>
       </c>
       <c r="C347" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D347" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E347" t="s">
         <v>1044</v>
       </c>
-      <c r="E347" t="s">
+      <c r="F347" t="s">
         <v>1045</v>
-      </c>
-      <c r="F347" t="s">
-        <v>1046</v>
       </c>
       <c r="G347">
         <v>50000</v>
@@ -49966,16 +50012,16 @@
         <v>0</v>
       </c>
       <c r="C348" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D348" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E348" t="s">
         <v>1047</v>
       </c>
-      <c r="E348" t="s">
+      <c r="F348" t="s">
         <v>1048</v>
-      </c>
-      <c r="F348" t="s">
-        <v>1049</v>
       </c>
       <c r="G348">
         <v>10</v>
@@ -50023,16 +50069,16 @@
         <v>0</v>
       </c>
       <c r="C349" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D349" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E349" t="s">
         <v>1050</v>
       </c>
-      <c r="E349" t="s">
+      <c r="F349" t="s">
         <v>1051</v>
-      </c>
-      <c r="F349" t="s">
-        <v>1052</v>
       </c>
       <c r="G349">
         <v>75</v>
@@ -50080,16 +50126,16 @@
         <v>0</v>
       </c>
       <c r="C350" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D350" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E350" t="s">
         <v>1053</v>
       </c>
-      <c r="E350" t="s">
+      <c r="F350" t="s">
         <v>1054</v>
-      </c>
-      <c r="F350" t="s">
-        <v>1055</v>
       </c>
       <c r="G350">
         <v>25</v>
@@ -50137,16 +50183,16 @@
         <v>0</v>
       </c>
       <c r="C351" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D351" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E351" t="s">
+        <v>946</v>
+      </c>
+      <c r="F351" t="s">
         <v>1056</v>
-      </c>
-      <c r="E351" t="s">
-        <v>947</v>
-      </c>
-      <c r="F351" t="s">
-        <v>1057</v>
       </c>
       <c r="G351">
         <v>5</v>
@@ -50194,16 +50240,16 @@
         <v>0</v>
       </c>
       <c r="C352" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D352" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E352" t="s">
         <v>1058</v>
       </c>
-      <c r="E352" t="s">
+      <c r="F352" t="s">
         <v>1059</v>
-      </c>
-      <c r="F352" t="s">
-        <v>1060</v>
       </c>
       <c r="G352">
         <v>0.6</v>
@@ -50254,13 +50300,13 @@
         <v>640</v>
       </c>
       <c r="D353" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E353" t="s">
         <v>1061</v>
       </c>
-      <c r="E353" t="s">
+      <c r="F353" t="s">
         <v>1062</v>
-      </c>
-      <c r="F353" t="s">
-        <v>1063</v>
       </c>
       <c r="G353">
         <v>0.1</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8ED1BF-C970-4889-AEE3-4352C1306D62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF44151A-3F83-48AE-8AA0-BF0656E29F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -472,12 +472,6 @@
   </si>
   <si>
     <t>野外基礎生命恢復</t>
-  </si>
-  <si>
-    <t>最大生命×a%/秒</t>
-  </si>
-  <si>
-    <t>a=每秒回復比例（高塔內無此回復）。</t>
   </si>
   <si>
     <t>全局減傷</t>
@@ -3684,12 +3678,91 @@
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>(最大生命</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>a% + b )/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>秒</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>a=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t xml:space="preserve">生命加成比例 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t>b=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="細明體"/>
+        <family val="3"/>
+        <charset val="136"/>
+      </rPr>
+      <t>基礎值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -3728,6 +3801,11 @@
       <name val="細明體"/>
       <family val="2"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -7214,19 +7292,19 @@
       </c>
       <c r="E43" t="str">
         <f>計算表!E43</f>
-        <v>最大生命×a%/秒</v>
+        <v>(最大生命×a% + b )/秒</v>
       </c>
       <c r="F43" t="str">
         <f>計算表!F43</f>
-        <v>a=每秒回復比例（高塔內無此回復）。</v>
+        <v>a=生命加成比例 b=基礎值。</v>
       </c>
       <c r="G43">
         <f>計算表!G43</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H43">
         <f>計算表!H43</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I43">
         <f>計算表!I43</f>
@@ -10922,7 +11000,7 @@
       </c>
       <c r="G93">
         <f>計算表!G93</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H93">
         <f>計算表!H93</f>
@@ -31879,7 +31957,7 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30">
-        <f t="shared" si="0"/>
+        <f>A29+1</f>
         <v>29</v>
       </c>
       <c r="B30">
@@ -32618,7 +32696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -32632,17 +32710,17 @@
       <c r="D43" t="s">
         <v>145</v>
       </c>
-      <c r="E43" t="s">
-        <v>146</v>
-      </c>
-      <c r="F43" t="s">
-        <v>147</v>
+      <c r="E43" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>1083</v>
       </c>
       <c r="G43">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -32687,13 +32765,13 @@
         <v>103</v>
       </c>
       <c r="D44" t="s">
+        <v>146</v>
+      </c>
+      <c r="E44" t="s">
+        <v>147</v>
+      </c>
+      <c r="F44" t="s">
         <v>148</v>
-      </c>
-      <c r="E44" t="s">
-        <v>149</v>
-      </c>
-      <c r="F44" t="s">
-        <v>150</v>
       </c>
       <c r="G44">
         <v>100</v>
@@ -32741,16 +32819,16 @@
         <v>0</v>
       </c>
       <c r="C45" t="s">
+        <v>149</v>
+      </c>
+      <c r="D45" t="s">
+        <v>150</v>
+      </c>
+      <c r="E45" t="s">
         <v>151</v>
       </c>
-      <c r="D45" t="s">
+      <c r="F45" t="s">
         <v>152</v>
-      </c>
-      <c r="E45" t="s">
-        <v>153</v>
-      </c>
-      <c r="F45" t="s">
-        <v>154</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -32798,16 +32876,16 @@
         <v>0</v>
       </c>
       <c r="C46" t="s">
+        <v>149</v>
+      </c>
+      <c r="D46" t="s">
+        <v>153</v>
+      </c>
+      <c r="E46" t="s">
         <v>151</v>
       </c>
-      <c r="D46" t="s">
-        <v>155</v>
-      </c>
-      <c r="E46" t="s">
-        <v>153</v>
-      </c>
       <c r="F46" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -32855,16 +32933,16 @@
         <v>0</v>
       </c>
       <c r="C47" t="s">
+        <v>149</v>
+      </c>
+      <c r="D47" t="s">
+        <v>155</v>
+      </c>
+      <c r="E47" t="s">
         <v>151</v>
       </c>
-      <c r="D47" t="s">
-        <v>157</v>
-      </c>
-      <c r="E47" t="s">
-        <v>153</v>
-      </c>
       <c r="F47" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -32912,16 +32990,16 @@
         <v>0</v>
       </c>
       <c r="C48" t="s">
+        <v>149</v>
+      </c>
+      <c r="D48" t="s">
+        <v>157</v>
+      </c>
+      <c r="E48" t="s">
         <v>151</v>
       </c>
-      <c r="D48" t="s">
-        <v>159</v>
-      </c>
-      <c r="E48" t="s">
-        <v>153</v>
-      </c>
       <c r="F48" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G48">
         <v>60</v>
@@ -32969,16 +33047,16 @@
         <v>0</v>
       </c>
       <c r="C49" t="s">
+        <v>149</v>
+      </c>
+      <c r="D49" t="s">
+        <v>159</v>
+      </c>
+      <c r="E49" t="s">
         <v>151</v>
       </c>
-      <c r="D49" t="s">
-        <v>161</v>
-      </c>
-      <c r="E49" t="s">
-        <v>153</v>
-      </c>
       <c r="F49" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G49">
         <v>50</v>
@@ -33026,16 +33104,16 @@
         <v>0</v>
       </c>
       <c r="C50" t="s">
+        <v>149</v>
+      </c>
+      <c r="D50" t="s">
+        <v>161</v>
+      </c>
+      <c r="E50" t="s">
         <v>151</v>
       </c>
-      <c r="D50" t="s">
-        <v>163</v>
-      </c>
-      <c r="E50" t="s">
-        <v>153</v>
-      </c>
       <c r="F50" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -33083,16 +33161,16 @@
         <v>0</v>
       </c>
       <c r="C51" t="s">
+        <v>149</v>
+      </c>
+      <c r="D51" t="s">
+        <v>163</v>
+      </c>
+      <c r="E51" t="s">
         <v>151</v>
       </c>
-      <c r="D51" t="s">
-        <v>165</v>
-      </c>
-      <c r="E51" t="s">
-        <v>153</v>
-      </c>
       <c r="F51" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -33140,16 +33218,16 @@
         <v>0</v>
       </c>
       <c r="C52" t="s">
+        <v>149</v>
+      </c>
+      <c r="D52" t="s">
+        <v>165</v>
+      </c>
+      <c r="E52" t="s">
         <v>151</v>
       </c>
-      <c r="D52" t="s">
-        <v>167</v>
-      </c>
-      <c r="E52" t="s">
-        <v>153</v>
-      </c>
       <c r="F52" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G52">
         <v>50</v>
@@ -33197,16 +33275,16 @@
         <v>0</v>
       </c>
       <c r="C53" t="s">
+        <v>149</v>
+      </c>
+      <c r="D53" t="s">
+        <v>167</v>
+      </c>
+      <c r="E53" t="s">
         <v>151</v>
       </c>
-      <c r="D53" t="s">
-        <v>169</v>
-      </c>
-      <c r="E53" t="s">
-        <v>153</v>
-      </c>
       <c r="F53" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G53">
         <v>50</v>
@@ -33254,16 +33332,16 @@
         <v>0</v>
       </c>
       <c r="C54" t="s">
+        <v>149</v>
+      </c>
+      <c r="D54" t="s">
+        <v>169</v>
+      </c>
+      <c r="E54" t="s">
         <v>151</v>
       </c>
-      <c r="D54" t="s">
-        <v>171</v>
-      </c>
-      <c r="E54" t="s">
-        <v>153</v>
-      </c>
       <c r="F54" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -33311,16 +33389,16 @@
         <v>0</v>
       </c>
       <c r="C55" t="s">
+        <v>149</v>
+      </c>
+      <c r="D55" t="s">
+        <v>171</v>
+      </c>
+      <c r="E55" t="s">
         <v>151</v>
       </c>
-      <c r="D55" t="s">
-        <v>173</v>
-      </c>
-      <c r="E55" t="s">
-        <v>153</v>
-      </c>
       <c r="F55" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G55">
         <v>80</v>
@@ -33368,16 +33446,16 @@
         <v>0</v>
       </c>
       <c r="C56" t="s">
+        <v>149</v>
+      </c>
+      <c r="D56" t="s">
+        <v>173</v>
+      </c>
+      <c r="E56" t="s">
         <v>151</v>
       </c>
-      <c r="D56" t="s">
-        <v>175</v>
-      </c>
-      <c r="E56" t="s">
-        <v>153</v>
-      </c>
       <c r="F56" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G56">
         <v>80</v>
@@ -33425,16 +33503,16 @@
         <v>0</v>
       </c>
       <c r="C57" t="s">
+        <v>149</v>
+      </c>
+      <c r="D57" t="s">
+        <v>175</v>
+      </c>
+      <c r="E57" t="s">
         <v>151</v>
       </c>
-      <c r="D57" t="s">
-        <v>177</v>
-      </c>
-      <c r="E57" t="s">
-        <v>153</v>
-      </c>
       <c r="F57" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G57">
         <v>60</v>
@@ -33482,16 +33560,16 @@
         <v>0</v>
       </c>
       <c r="C58" t="s">
+        <v>149</v>
+      </c>
+      <c r="D58" t="s">
+        <v>177</v>
+      </c>
+      <c r="E58" t="s">
         <v>151</v>
       </c>
-      <c r="D58" t="s">
-        <v>179</v>
-      </c>
-      <c r="E58" t="s">
-        <v>153</v>
-      </c>
       <c r="F58" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G58">
         <v>50</v>
@@ -33539,16 +33617,16 @@
         <v>0</v>
       </c>
       <c r="C59" t="s">
+        <v>149</v>
+      </c>
+      <c r="D59" t="s">
+        <v>179</v>
+      </c>
+      <c r="E59" t="s">
         <v>151</v>
       </c>
-      <c r="D59" t="s">
-        <v>181</v>
-      </c>
-      <c r="E59" t="s">
-        <v>153</v>
-      </c>
       <c r="F59" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G59">
         <v>100</v>
@@ -33596,16 +33674,16 @@
         <v>0</v>
       </c>
       <c r="C60" t="s">
+        <v>149</v>
+      </c>
+      <c r="D60" t="s">
+        <v>181</v>
+      </c>
+      <c r="E60" t="s">
         <v>151</v>
       </c>
-      <c r="D60" t="s">
-        <v>183</v>
-      </c>
-      <c r="E60" t="s">
-        <v>153</v>
-      </c>
       <c r="F60" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G60">
         <v>60</v>
@@ -33653,16 +33731,16 @@
         <v>0</v>
       </c>
       <c r="C61" t="s">
+        <v>149</v>
+      </c>
+      <c r="D61" t="s">
+        <v>183</v>
+      </c>
+      <c r="E61" t="s">
         <v>151</v>
       </c>
-      <c r="D61" t="s">
-        <v>185</v>
-      </c>
-      <c r="E61" t="s">
-        <v>153</v>
-      </c>
       <c r="F61" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G61">
         <v>30</v>
@@ -33710,16 +33788,16 @@
         <v>0</v>
       </c>
       <c r="C62" t="s">
+        <v>149</v>
+      </c>
+      <c r="D62" t="s">
+        <v>185</v>
+      </c>
+      <c r="E62" t="s">
         <v>151</v>
       </c>
-      <c r="D62" t="s">
-        <v>187</v>
-      </c>
-      <c r="E62" t="s">
-        <v>153</v>
-      </c>
       <c r="F62" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G62">
         <v>100</v>
@@ -33767,16 +33845,16 @@
         <v>0</v>
       </c>
       <c r="C63" t="s">
+        <v>149</v>
+      </c>
+      <c r="D63" t="s">
+        <v>187</v>
+      </c>
+      <c r="E63" t="s">
         <v>151</v>
       </c>
-      <c r="D63" t="s">
-        <v>189</v>
-      </c>
-      <c r="E63" t="s">
-        <v>153</v>
-      </c>
       <c r="F63" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G63">
         <v>45</v>
@@ -33824,16 +33902,16 @@
         <v>0</v>
       </c>
       <c r="C64" t="s">
+        <v>149</v>
+      </c>
+      <c r="D64" t="s">
+        <v>189</v>
+      </c>
+      <c r="E64" t="s">
         <v>151</v>
       </c>
-      <c r="D64" t="s">
-        <v>191</v>
-      </c>
-      <c r="E64" t="s">
-        <v>153</v>
-      </c>
       <c r="F64" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G64">
         <v>30</v>
@@ -33881,16 +33959,16 @@
         <v>0</v>
       </c>
       <c r="C65" t="s">
+        <v>191</v>
+      </c>
+      <c r="D65" t="s">
+        <v>192</v>
+      </c>
+      <c r="E65" t="s">
         <v>193</v>
       </c>
-      <c r="D65" t="s">
+      <c r="F65" t="s">
         <v>194</v>
-      </c>
-      <c r="E65" t="s">
-        <v>195</v>
-      </c>
-      <c r="F65" t="s">
-        <v>196</v>
       </c>
       <c r="G65">
         <v>60</v>
@@ -33938,16 +34016,16 @@
         <v>0</v>
       </c>
       <c r="C66" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D66" t="s">
+        <v>195</v>
+      </c>
+      <c r="E66" t="s">
+        <v>196</v>
+      </c>
+      <c r="F66" t="s">
         <v>197</v>
-      </c>
-      <c r="E66" t="s">
-        <v>198</v>
-      </c>
-      <c r="F66" t="s">
-        <v>199</v>
       </c>
       <c r="G66">
         <v>100</v>
@@ -33995,16 +34073,16 @@
         <v>0</v>
       </c>
       <c r="C67" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D67" t="s">
+        <v>198</v>
+      </c>
+      <c r="E67" t="s">
+        <v>199</v>
+      </c>
+      <c r="F67" t="s">
         <v>200</v>
-      </c>
-      <c r="E67" t="s">
-        <v>201</v>
-      </c>
-      <c r="F67" t="s">
-        <v>202</v>
       </c>
       <c r="G67">
         <v>1.8</v>
@@ -34052,16 +34130,16 @@
         <v>0</v>
       </c>
       <c r="C68" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D68" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E68" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F68" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G68">
         <v>1.8</v>
@@ -34109,16 +34187,16 @@
         <v>0</v>
       </c>
       <c r="C69" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D69" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E69" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F69" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G69">
         <v>1.8</v>
@@ -34166,16 +34244,16 @@
         <v>0</v>
       </c>
       <c r="C70" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D70" t="s">
+        <v>204</v>
+      </c>
+      <c r="E70" t="s">
+        <v>205</v>
+      </c>
+      <c r="F70" t="s">
         <v>206</v>
-      </c>
-      <c r="E70" t="s">
-        <v>207</v>
-      </c>
-      <c r="F70" t="s">
-        <v>208</v>
       </c>
       <c r="G70">
         <v>0.9</v>
@@ -34223,16 +34301,16 @@
         <v>0</v>
       </c>
       <c r="C71" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D71" t="s">
+        <v>207</v>
+      </c>
+      <c r="E71" t="s">
+        <v>208</v>
+      </c>
+      <c r="F71" t="s">
         <v>209</v>
-      </c>
-      <c r="E71" t="s">
-        <v>210</v>
-      </c>
-      <c r="F71" t="s">
-        <v>211</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -34280,16 +34358,16 @@
         <v>0</v>
       </c>
       <c r="C72" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D72" t="s">
+        <v>210</v>
+      </c>
+      <c r="E72" t="s">
+        <v>211</v>
+      </c>
+      <c r="F72" t="s">
         <v>212</v>
-      </c>
-      <c r="E72" t="s">
-        <v>213</v>
-      </c>
-      <c r="F72" t="s">
-        <v>214</v>
       </c>
       <c r="G72">
         <v>0.7</v>
@@ -34337,16 +34415,16 @@
         <v>0</v>
       </c>
       <c r="C73" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D73" t="s">
+        <v>213</v>
+      </c>
+      <c r="E73" t="s">
+        <v>214</v>
+      </c>
+      <c r="F73" t="s">
         <v>215</v>
-      </c>
-      <c r="E73" t="s">
-        <v>216</v>
-      </c>
-      <c r="F73" t="s">
-        <v>217</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -34394,16 +34472,16 @@
         <v>0</v>
       </c>
       <c r="C74" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D74" t="s">
+        <v>216</v>
+      </c>
+      <c r="E74" t="s">
+        <v>217</v>
+      </c>
+      <c r="F74" t="s">
         <v>218</v>
-      </c>
-      <c r="E74" t="s">
-        <v>219</v>
-      </c>
-      <c r="F74" t="s">
-        <v>220</v>
       </c>
       <c r="G74">
         <v>12</v>
@@ -34451,16 +34529,16 @@
         <v>0</v>
       </c>
       <c r="C75" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D75" t="s">
+        <v>219</v>
+      </c>
+      <c r="E75" t="s">
+        <v>220</v>
+      </c>
+      <c r="F75" t="s">
         <v>221</v>
-      </c>
-      <c r="E75" t="s">
-        <v>222</v>
-      </c>
-      <c r="F75" t="s">
-        <v>223</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -34508,16 +34586,16 @@
         <v>0</v>
       </c>
       <c r="C76" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D76" t="s">
+        <v>222</v>
+      </c>
+      <c r="E76" t="s">
+        <v>223</v>
+      </c>
+      <c r="F76" t="s">
         <v>224</v>
-      </c>
-      <c r="E76" t="s">
-        <v>225</v>
-      </c>
-      <c r="F76" t="s">
-        <v>226</v>
       </c>
       <c r="G76">
         <v>10</v>
@@ -34565,16 +34643,16 @@
         <v>0</v>
       </c>
       <c r="C77" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D77" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E77" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F77" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G77">
         <v>10000</v>
@@ -34622,16 +34700,16 @@
         <v>0</v>
       </c>
       <c r="C78" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D78" t="s">
+        <v>227</v>
+      </c>
+      <c r="E78" t="s">
+        <v>228</v>
+      </c>
+      <c r="F78" t="s">
         <v>229</v>
-      </c>
-      <c r="E78" t="s">
-        <v>230</v>
-      </c>
-      <c r="F78" t="s">
-        <v>231</v>
       </c>
       <c r="G78">
         <v>50</v>
@@ -34679,16 +34757,16 @@
         <v>0</v>
       </c>
       <c r="C79" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D79" t="s">
+        <v>230</v>
+      </c>
+      <c r="E79" t="s">
+        <v>231</v>
+      </c>
+      <c r="F79" t="s">
         <v>232</v>
-      </c>
-      <c r="E79" t="s">
-        <v>233</v>
-      </c>
-      <c r="F79" t="s">
-        <v>234</v>
       </c>
       <c r="G79">
         <v>30</v>
@@ -34736,16 +34814,16 @@
         <v>0</v>
       </c>
       <c r="C80" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D80" t="s">
+        <v>233</v>
+      </c>
+      <c r="E80" t="s">
+        <v>234</v>
+      </c>
+      <c r="F80" t="s">
         <v>235</v>
-      </c>
-      <c r="E80" t="s">
-        <v>236</v>
-      </c>
-      <c r="F80" t="s">
-        <v>237</v>
       </c>
       <c r="G80">
         <v>100</v>
@@ -34793,16 +34871,16 @@
         <v>0</v>
       </c>
       <c r="C81" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D81" t="s">
+        <v>236</v>
+      </c>
+      <c r="E81" t="s">
+        <v>237</v>
+      </c>
+      <c r="F81" t="s">
         <v>238</v>
-      </c>
-      <c r="E81" t="s">
-        <v>239</v>
-      </c>
-      <c r="F81" t="s">
-        <v>240</v>
       </c>
       <c r="G81">
         <v>8</v>
@@ -34850,16 +34928,16 @@
         <v>0</v>
       </c>
       <c r="C82" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D82" t="s">
+        <v>239</v>
+      </c>
+      <c r="E82" t="s">
+        <v>240</v>
+      </c>
+      <c r="F82" t="s">
         <v>241</v>
-      </c>
-      <c r="E82" t="s">
-        <v>242</v>
-      </c>
-      <c r="F82" t="s">
-        <v>243</v>
       </c>
       <c r="G82">
         <v>0.01</v>
@@ -34907,16 +34985,16 @@
         <v>0</v>
       </c>
       <c r="C83" t="s">
+        <v>242</v>
+      </c>
+      <c r="D83" t="s">
+        <v>243</v>
+      </c>
+      <c r="E83" t="s">
         <v>244</v>
       </c>
-      <c r="D83" t="s">
+      <c r="F83" t="s">
         <v>245</v>
-      </c>
-      <c r="E83" t="s">
-        <v>246</v>
-      </c>
-      <c r="F83" t="s">
-        <v>247</v>
       </c>
       <c r="G83">
         <v>15</v>
@@ -34964,16 +35042,16 @@
         <v>0</v>
       </c>
       <c r="C84" t="s">
+        <v>242</v>
+      </c>
+      <c r="D84" t="s">
+        <v>246</v>
+      </c>
+      <c r="E84" t="s">
         <v>244</v>
       </c>
-      <c r="D84" t="s">
-        <v>248</v>
-      </c>
-      <c r="E84" t="s">
-        <v>246</v>
-      </c>
       <c r="F84" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G84">
         <v>10</v>
@@ -35021,16 +35099,16 @@
         <v>0</v>
       </c>
       <c r="C85" t="s">
+        <v>242</v>
+      </c>
+      <c r="D85" t="s">
+        <v>248</v>
+      </c>
+      <c r="E85" t="s">
         <v>244</v>
       </c>
-      <c r="D85" t="s">
-        <v>250</v>
-      </c>
-      <c r="E85" t="s">
-        <v>246</v>
-      </c>
       <c r="F85" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G85">
         <v>25</v>
@@ -35078,16 +35156,16 @@
         <v>0</v>
       </c>
       <c r="C86" t="s">
+        <v>242</v>
+      </c>
+      <c r="D86" t="s">
+        <v>250</v>
+      </c>
+      <c r="E86" t="s">
         <v>244</v>
       </c>
-      <c r="D86" t="s">
-        <v>252</v>
-      </c>
-      <c r="E86" t="s">
-        <v>246</v>
-      </c>
       <c r="F86" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G86">
         <v>20</v>
@@ -35135,16 +35213,16 @@
         <v>0</v>
       </c>
       <c r="C87" t="s">
+        <v>242</v>
+      </c>
+      <c r="D87" t="s">
+        <v>252</v>
+      </c>
+      <c r="E87" t="s">
         <v>244</v>
       </c>
-      <c r="D87" t="s">
-        <v>254</v>
-      </c>
-      <c r="E87" t="s">
-        <v>246</v>
-      </c>
       <c r="F87" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G87">
         <v>100</v>
@@ -35192,16 +35270,16 @@
         <v>0</v>
       </c>
       <c r="C88" t="s">
+        <v>254</v>
+      </c>
+      <c r="D88" t="s">
+        <v>255</v>
+      </c>
+      <c r="E88" t="s">
         <v>256</v>
       </c>
-      <c r="D88" t="s">
+      <c r="F88" t="s">
         <v>257</v>
-      </c>
-      <c r="E88" t="s">
-        <v>258</v>
-      </c>
-      <c r="F88" t="s">
-        <v>259</v>
       </c>
       <c r="G88">
         <v>30</v>
@@ -35249,16 +35327,16 @@
         <v>0</v>
       </c>
       <c r="C89" t="s">
+        <v>254</v>
+      </c>
+      <c r="D89" t="s">
+        <v>258</v>
+      </c>
+      <c r="E89" t="s">
         <v>256</v>
       </c>
-      <c r="D89" t="s">
-        <v>260</v>
-      </c>
-      <c r="E89" t="s">
-        <v>258</v>
-      </c>
       <c r="F89" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G89">
         <v>3</v>
@@ -35306,16 +35384,16 @@
         <v>0</v>
       </c>
       <c r="C90" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D90" t="s">
         <v>119</v>
       </c>
       <c r="E90" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F90" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G90">
         <v>2</v>
@@ -35363,16 +35441,16 @@
         <v>0</v>
       </c>
       <c r="C91" t="s">
+        <v>254</v>
+      </c>
+      <c r="D91" t="s">
+        <v>260</v>
+      </c>
+      <c r="E91" t="s">
         <v>256</v>
       </c>
-      <c r="D91" t="s">
-        <v>262</v>
-      </c>
-      <c r="E91" t="s">
-        <v>258</v>
-      </c>
       <c r="F91" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G91">
         <v>250</v>
@@ -35420,16 +35498,16 @@
         <v>0</v>
       </c>
       <c r="C92" t="s">
+        <v>254</v>
+      </c>
+      <c r="D92" t="s">
+        <v>261</v>
+      </c>
+      <c r="E92" t="s">
         <v>256</v>
       </c>
-      <c r="D92" t="s">
-        <v>263</v>
-      </c>
-      <c r="E92" t="s">
-        <v>258</v>
-      </c>
       <c r="F92" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G92">
         <v>60</v>
@@ -35477,19 +35555,19 @@
         <v>0</v>
       </c>
       <c r="C93" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D93" t="s">
         <v>134</v>
       </c>
       <c r="E93" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F93" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H93">
         <v>0</v>
@@ -35534,37 +35612,37 @@
         <v>0</v>
       </c>
       <c r="C94" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D94" t="s">
         <v>137</v>
       </c>
       <c r="E94" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F94" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G94">
         <v>100</v>
       </c>
       <c r="H94" t="s">
+        <v>266</v>
+      </c>
+      <c r="I94" t="s">
+        <v>267</v>
+      </c>
+      <c r="J94" t="s">
         <v>268</v>
       </c>
-      <c r="I94" t="s">
+      <c r="K94" t="s">
         <v>269</v>
       </c>
-      <c r="J94" t="s">
+      <c r="L94" t="s">
         <v>270</v>
       </c>
-      <c r="K94" t="s">
+      <c r="M94" t="s">
         <v>271</v>
-      </c>
-      <c r="L94" t="s">
-        <v>272</v>
-      </c>
-      <c r="M94" t="s">
-        <v>273</v>
       </c>
       <c r="N94">
         <v>0</v>
@@ -35591,37 +35669,37 @@
         <v>0</v>
       </c>
       <c r="C95" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D95" t="s">
         <v>140</v>
       </c>
       <c r="E95" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F95" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G95">
         <v>5</v>
       </c>
       <c r="H95" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="I95" t="s">
+        <v>273</v>
+      </c>
+      <c r="J95" t="s">
+        <v>274</v>
+      </c>
+      <c r="K95" t="s">
         <v>275</v>
       </c>
-      <c r="J95" t="s">
+      <c r="L95" t="s">
         <v>276</v>
       </c>
-      <c r="K95" t="s">
+      <c r="M95" t="s">
         <v>277</v>
-      </c>
-      <c r="L95" t="s">
-        <v>278</v>
-      </c>
-      <c r="M95" t="s">
-        <v>279</v>
       </c>
       <c r="N95">
         <v>0</v>
@@ -35648,16 +35726,16 @@
         <v>0</v>
       </c>
       <c r="C96" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D96" t="s">
+        <v>278</v>
+      </c>
+      <c r="E96" t="s">
+        <v>279</v>
+      </c>
+      <c r="F96" t="s">
         <v>280</v>
-      </c>
-      <c r="E96" t="s">
-        <v>281</v>
-      </c>
-      <c r="F96" t="s">
-        <v>282</v>
       </c>
       <c r="G96">
         <v>4</v>
@@ -35705,16 +35783,16 @@
         <v>0</v>
       </c>
       <c r="C97" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D97" t="s">
+        <v>281</v>
+      </c>
+      <c r="E97" t="s">
+        <v>282</v>
+      </c>
+      <c r="F97" t="s">
         <v>283</v>
-      </c>
-      <c r="E97" t="s">
-        <v>284</v>
-      </c>
-      <c r="F97" t="s">
-        <v>285</v>
       </c>
       <c r="G97">
         <v>1.3</v>
@@ -35762,16 +35840,16 @@
         <v>0</v>
       </c>
       <c r="C98" t="s">
+        <v>284</v>
+      </c>
+      <c r="D98" t="s">
+        <v>285</v>
+      </c>
+      <c r="E98" t="s">
         <v>286</v>
       </c>
-      <c r="D98" t="s">
+      <c r="F98" t="s">
         <v>287</v>
-      </c>
-      <c r="E98" t="s">
-        <v>288</v>
-      </c>
-      <c r="F98" t="s">
-        <v>289</v>
       </c>
       <c r="G98">
         <v>1</v>
@@ -35819,16 +35897,16 @@
         <v>0</v>
       </c>
       <c r="C99" t="s">
+        <v>284</v>
+      </c>
+      <c r="D99" t="s">
+        <v>288</v>
+      </c>
+      <c r="E99" t="s">
         <v>286</v>
       </c>
-      <c r="D99" t="s">
-        <v>290</v>
-      </c>
-      <c r="E99" t="s">
-        <v>288</v>
-      </c>
       <c r="F99" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G99">
         <v>2.2000000000000002</v>
@@ -35876,16 +35954,16 @@
         <v>0</v>
       </c>
       <c r="C100" t="s">
+        <v>284</v>
+      </c>
+      <c r="D100" t="s">
+        <v>289</v>
+      </c>
+      <c r="E100" t="s">
         <v>286</v>
       </c>
-      <c r="D100" t="s">
-        <v>291</v>
-      </c>
-      <c r="E100" t="s">
-        <v>288</v>
-      </c>
       <c r="F100" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G100">
         <v>4.5</v>
@@ -35933,16 +36011,16 @@
         <v>0</v>
       </c>
       <c r="C101" t="s">
+        <v>284</v>
+      </c>
+      <c r="D101" t="s">
+        <v>290</v>
+      </c>
+      <c r="E101" t="s">
         <v>286</v>
       </c>
-      <c r="D101" t="s">
-        <v>292</v>
-      </c>
-      <c r="E101" t="s">
-        <v>288</v>
-      </c>
       <c r="F101" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G101">
         <v>10</v>
@@ -35990,16 +36068,16 @@
         <v>0</v>
       </c>
       <c r="C102" t="s">
+        <v>284</v>
+      </c>
+      <c r="D102" t="s">
+        <v>291</v>
+      </c>
+      <c r="E102" t="s">
         <v>286</v>
       </c>
-      <c r="D102" t="s">
-        <v>293</v>
-      </c>
-      <c r="E102" t="s">
-        <v>288</v>
-      </c>
       <c r="F102" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G102">
         <v>25</v>
@@ -36047,16 +36125,16 @@
         <v>0</v>
       </c>
       <c r="C103" t="s">
+        <v>284</v>
+      </c>
+      <c r="D103" t="s">
+        <v>292</v>
+      </c>
+      <c r="E103" t="s">
         <v>286</v>
       </c>
-      <c r="D103" t="s">
-        <v>294</v>
-      </c>
-      <c r="E103" t="s">
-        <v>288</v>
-      </c>
       <c r="F103" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G103">
         <v>60</v>
@@ -36101,22 +36179,22 @@
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="C104" t="s">
+        <v>293</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E104" t="s">
         <v>295</v>
       </c>
-      <c r="D104" s="1" t="s">
-        <v>1063</v>
-      </c>
-      <c r="E104" t="s">
-        <v>297</v>
-      </c>
       <c r="F104" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="H104">
         <v>0</v>
@@ -36158,25 +36236,25 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="C105" t="s">
+        <v>293</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E105" t="s">
         <v>295</v>
       </c>
-      <c r="D105" s="1" t="s">
-        <v>1064</v>
-      </c>
-      <c r="E105" t="s">
-        <v>297</v>
-      </c>
       <c r="F105" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -36215,28 +36293,28 @@
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="C106" t="s">
+        <v>293</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E106" t="s">
         <v>295</v>
       </c>
-      <c r="D106" s="1" t="s">
-        <v>1065</v>
-      </c>
-      <c r="E106" t="s">
-        <v>297</v>
-      </c>
       <c r="F106" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="J106">
         <v>0</v>
@@ -36272,31 +36350,31 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="C107" t="s">
+        <v>293</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E107" t="s">
         <v>295</v>
       </c>
-      <c r="D107" s="1" t="s">
-        <v>1066</v>
-      </c>
-      <c r="E107" t="s">
-        <v>297</v>
-      </c>
       <c r="F107" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="H107" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="I107" s="2" t="s">
         <v>1076</v>
       </c>
-      <c r="I107" s="2" t="s">
-        <v>1078</v>
-      </c>
       <c r="J107" s="2" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="K107">
         <v>0</v>
@@ -36329,34 +36407,34 @@
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C108" t="s">
+        <v>293</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E108" t="s">
+        <v>295</v>
+      </c>
+      <c r="F108" t="s">
+        <v>296</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H108" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="C108" t="s">
-        <v>295</v>
-      </c>
-      <c r="D108" s="1" t="s">
+      <c r="I108" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="J108" s="2" t="s">
         <v>1067</v>
       </c>
-      <c r="E108" t="s">
-        <v>297</v>
-      </c>
-      <c r="F108" t="s">
-        <v>298</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>1070</v>
-      </c>
-      <c r="I108" s="2" t="s">
-        <v>1081</v>
-      </c>
-      <c r="J108" s="2" t="s">
-        <v>1069</v>
-      </c>
       <c r="K108" s="2" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="L108">
         <v>0</v>
@@ -36389,49 +36467,49 @@
         <v>0</v>
       </c>
       <c r="C109" t="s">
+        <v>293</v>
+      </c>
+      <c r="D109" t="s">
+        <v>294</v>
+      </c>
+      <c r="E109" t="s">
         <v>295</v>
       </c>
-      <c r="D109" t="s">
+      <c r="F109" t="s">
         <v>296</v>
       </c>
-      <c r="E109" t="s">
+      <c r="G109" t="s">
         <v>297</v>
       </c>
-      <c r="F109" t="s">
+      <c r="H109" t="s">
         <v>298</v>
       </c>
-      <c r="G109" t="s">
+      <c r="I109" t="s">
         <v>299</v>
       </c>
-      <c r="H109" t="s">
+      <c r="J109" t="s">
         <v>300</v>
       </c>
-      <c r="I109" t="s">
+      <c r="K109" t="s">
         <v>301</v>
       </c>
-      <c r="J109" t="s">
+      <c r="L109" t="s">
         <v>302</v>
       </c>
-      <c r="K109" t="s">
+      <c r="M109" t="s">
         <v>303</v>
       </c>
-      <c r="L109" t="s">
+      <c r="N109" t="s">
         <v>304</v>
       </c>
-      <c r="M109" t="s">
+      <c r="O109" t="s">
         <v>305</v>
       </c>
-      <c r="N109" t="s">
+      <c r="P109" t="s">
         <v>306</v>
       </c>
-      <c r="O109" t="s">
+      <c r="Q109" t="s">
         <v>307</v>
-      </c>
-      <c r="P109" t="s">
-        <v>308</v>
-      </c>
-      <c r="Q109" t="s">
-        <v>309</v>
       </c>
       <c r="R109">
         <v>0</v>
@@ -36446,25 +36524,25 @@
         <v>0</v>
       </c>
       <c r="C110" t="s">
+        <v>293</v>
+      </c>
+      <c r="D110" t="s">
+        <v>308</v>
+      </c>
+      <c r="E110" t="s">
         <v>295</v>
       </c>
-      <c r="D110" t="s">
+      <c r="F110" t="s">
+        <v>309</v>
+      </c>
+      <c r="G110" t="s">
         <v>310</v>
       </c>
-      <c r="E110" t="s">
-        <v>297</v>
-      </c>
-      <c r="F110" t="s">
+      <c r="H110" t="s">
         <v>311</v>
       </c>
-      <c r="G110" t="s">
+      <c r="I110" t="s">
         <v>312</v>
-      </c>
-      <c r="H110" t="s">
-        <v>313</v>
-      </c>
-      <c r="I110" t="s">
-        <v>314</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -36503,19 +36581,19 @@
         <v>0</v>
       </c>
       <c r="C111" t="s">
+        <v>293</v>
+      </c>
+      <c r="D111" t="s">
+        <v>313</v>
+      </c>
+      <c r="E111" t="s">
         <v>295</v>
       </c>
-      <c r="D111" t="s">
+      <c r="F111" t="s">
+        <v>314</v>
+      </c>
+      <c r="G111" t="s">
         <v>315</v>
-      </c>
-      <c r="E111" t="s">
-        <v>297</v>
-      </c>
-      <c r="F111" t="s">
-        <v>316</v>
-      </c>
-      <c r="G111" t="s">
-        <v>317</v>
       </c>
       <c r="H111">
         <v>0</v>
@@ -36560,16 +36638,16 @@
         <v>0</v>
       </c>
       <c r="C112" t="s">
+        <v>316</v>
+      </c>
+      <c r="D112" t="s">
+        <v>317</v>
+      </c>
+      <c r="E112" t="s">
         <v>318</v>
       </c>
-      <c r="D112" t="s">
+      <c r="F112" t="s">
         <v>319</v>
-      </c>
-      <c r="E112" t="s">
-        <v>320</v>
-      </c>
-      <c r="F112" t="s">
-        <v>321</v>
       </c>
       <c r="G112">
         <v>4</v>
@@ -36617,16 +36695,16 @@
         <v>0</v>
       </c>
       <c r="C113" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D113" t="s">
+        <v>320</v>
+      </c>
+      <c r="E113" t="s">
+        <v>321</v>
+      </c>
+      <c r="F113" t="s">
         <v>322</v>
-      </c>
-      <c r="E113" t="s">
-        <v>323</v>
-      </c>
-      <c r="F113" t="s">
-        <v>324</v>
       </c>
       <c r="G113">
         <v>2</v>
@@ -36674,16 +36752,16 @@
         <v>0</v>
       </c>
       <c r="C114" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D114" t="s">
+        <v>323</v>
+      </c>
+      <c r="E114" t="s">
+        <v>324</v>
+      </c>
+      <c r="F114" t="s">
         <v>325</v>
-      </c>
-      <c r="E114" t="s">
-        <v>326</v>
-      </c>
-      <c r="F114" t="s">
-        <v>327</v>
       </c>
       <c r="G114">
         <v>2</v>
@@ -36731,16 +36809,16 @@
         <v>0</v>
       </c>
       <c r="C115" t="s">
+        <v>326</v>
+      </c>
+      <c r="D115" t="s">
+        <v>327</v>
+      </c>
+      <c r="E115" t="s">
         <v>328</v>
       </c>
-      <c r="D115" t="s">
+      <c r="F115" t="s">
         <v>329</v>
-      </c>
-      <c r="E115" t="s">
-        <v>330</v>
-      </c>
-      <c r="F115" t="s">
-        <v>331</v>
       </c>
       <c r="G115">
         <v>50</v>
@@ -36788,16 +36866,16 @@
         <v>0</v>
       </c>
       <c r="C116" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D116" t="s">
+        <v>330</v>
+      </c>
+      <c r="E116" t="s">
+        <v>331</v>
+      </c>
+      <c r="F116" t="s">
         <v>332</v>
-      </c>
-      <c r="E116" t="s">
-        <v>333</v>
-      </c>
-      <c r="F116" t="s">
-        <v>334</v>
       </c>
       <c r="G116">
         <v>20</v>
@@ -36845,16 +36923,16 @@
         <v>0</v>
       </c>
       <c r="C117" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D117" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E117" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="F117" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G117">
         <v>3</v>
@@ -36902,16 +36980,16 @@
         <v>0</v>
       </c>
       <c r="C118" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D118" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E118" t="s">
         <v>39</v>
       </c>
       <c r="F118" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G118">
         <v>1</v>
@@ -36929,7 +37007,7 @@
         <v>1</v>
       </c>
       <c r="L118" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="M118">
         <v>0</v>
@@ -36959,16 +37037,16 @@
         <v>0</v>
       </c>
       <c r="C119" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D119" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E119" t="s">
         <v>39</v>
       </c>
       <c r="F119" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G119">
         <v>2.2000000000000002</v>
@@ -36986,7 +37064,7 @@
         <v>1.25</v>
       </c>
       <c r="L119" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="M119">
         <v>0</v>
@@ -37016,16 +37094,16 @@
         <v>0</v>
       </c>
       <c r="C120" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D120" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E120" t="s">
         <v>39</v>
       </c>
       <c r="F120" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G120">
         <v>4</v>
@@ -37043,7 +37121,7 @@
         <v>1.5</v>
       </c>
       <c r="L120" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="M120">
         <v>0</v>
@@ -37073,16 +37151,16 @@
         <v>0</v>
       </c>
       <c r="C121" t="s">
+        <v>339</v>
+      </c>
+      <c r="D121" t="s">
+        <v>340</v>
+      </c>
+      <c r="E121" t="s">
         <v>341</v>
       </c>
-      <c r="D121" t="s">
+      <c r="F121" t="s">
         <v>342</v>
-      </c>
-      <c r="E121" t="s">
-        <v>343</v>
-      </c>
-      <c r="F121" t="s">
-        <v>344</v>
       </c>
       <c r="G121">
         <v>4</v>
@@ -37130,16 +37208,16 @@
         <v>0</v>
       </c>
       <c r="C122" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D122" t="s">
+        <v>343</v>
+      </c>
+      <c r="E122" t="s">
+        <v>344</v>
+      </c>
+      <c r="F122" t="s">
         <v>345</v>
-      </c>
-      <c r="E122" t="s">
-        <v>346</v>
-      </c>
-      <c r="F122" t="s">
-        <v>347</v>
       </c>
       <c r="G122">
         <v>3</v>
@@ -37187,16 +37265,16 @@
         <v>0</v>
       </c>
       <c r="C123" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D123" t="s">
         <v>137</v>
       </c>
       <c r="E123" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F123" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G123">
         <v>200</v>
@@ -37244,25 +37322,25 @@
         <v>0</v>
       </c>
       <c r="C124" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D124" t="s">
+        <v>348</v>
+      </c>
+      <c r="E124" t="s">
+        <v>349</v>
+      </c>
+      <c r="F124" t="s">
         <v>350</v>
       </c>
-      <c r="E124" t="s">
+      <c r="G124" t="s">
         <v>351</v>
       </c>
-      <c r="F124" t="s">
+      <c r="H124" t="s">
         <v>352</v>
       </c>
-      <c r="G124" t="s">
+      <c r="I124" t="s">
         <v>353</v>
-      </c>
-      <c r="H124" t="s">
-        <v>354</v>
-      </c>
-      <c r="I124" t="s">
-        <v>355</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -37301,16 +37379,16 @@
         <v>0</v>
       </c>
       <c r="C125" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D125" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E125" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F125" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G125">
         <v>20</v>
@@ -37358,16 +37436,16 @@
         <v>0</v>
       </c>
       <c r="C126" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D126" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E126" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F126" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G126">
         <v>3</v>
@@ -37415,16 +37493,16 @@
         <v>0</v>
       </c>
       <c r="C127" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D127" t="s">
+        <v>358</v>
+      </c>
+      <c r="E127" t="s">
+        <v>359</v>
+      </c>
+      <c r="F127" t="s">
         <v>360</v>
-      </c>
-      <c r="E127" t="s">
-        <v>361</v>
-      </c>
-      <c r="F127" t="s">
-        <v>362</v>
       </c>
       <c r="G127">
         <v>10</v>
@@ -37472,16 +37550,16 @@
         <v>0</v>
       </c>
       <c r="C128" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D128" t="s">
+        <v>361</v>
+      </c>
+      <c r="E128" t="s">
+        <v>362</v>
+      </c>
+      <c r="F128" t="s">
         <v>363</v>
-      </c>
-      <c r="E128" t="s">
-        <v>364</v>
-      </c>
-      <c r="F128" t="s">
-        <v>365</v>
       </c>
       <c r="G128">
         <v>3</v>
@@ -37529,16 +37607,16 @@
         <v>0</v>
       </c>
       <c r="C129" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D129" t="s">
         <v>140</v>
       </c>
       <c r="E129" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F129" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G129">
         <v>20</v>
@@ -37586,16 +37664,16 @@
         <v>0</v>
       </c>
       <c r="C130" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D130" t="s">
+        <v>366</v>
+      </c>
+      <c r="E130" t="s">
+        <v>367</v>
+      </c>
+      <c r="F130" t="s">
         <v>368</v>
-      </c>
-      <c r="E130" t="s">
-        <v>369</v>
-      </c>
-      <c r="F130" t="s">
-        <v>370</v>
       </c>
       <c r="G130">
         <v>3</v>
@@ -37643,16 +37721,16 @@
         <v>0</v>
       </c>
       <c r="C131" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D131" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E131" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F131" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G131">
         <v>2</v>
@@ -37700,16 +37778,16 @@
         <v>0</v>
       </c>
       <c r="C132" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D132" t="s">
+        <v>371</v>
+      </c>
+      <c r="E132" t="s">
+        <v>372</v>
+      </c>
+      <c r="F132" t="s">
         <v>373</v>
-      </c>
-      <c r="E132" t="s">
-        <v>374</v>
-      </c>
-      <c r="F132" t="s">
-        <v>375</v>
       </c>
       <c r="G132">
         <v>60</v>
@@ -37757,16 +37835,16 @@
         <v>0</v>
       </c>
       <c r="C133" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D133" t="s">
+        <v>374</v>
+      </c>
+      <c r="E133" t="s">
+        <v>375</v>
+      </c>
+      <c r="F133" t="s">
         <v>376</v>
-      </c>
-      <c r="E133" t="s">
-        <v>377</v>
-      </c>
-      <c r="F133" t="s">
-        <v>378</v>
       </c>
       <c r="G133">
         <v>51</v>
@@ -37814,16 +37892,16 @@
         <v>0</v>
       </c>
       <c r="C134" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D134" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E134" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F134" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G134">
         <v>1</v>
@@ -37871,16 +37949,16 @@
         <v>0</v>
       </c>
       <c r="C135" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D135" t="s">
+        <v>379</v>
+      </c>
+      <c r="E135" t="s">
+        <v>380</v>
+      </c>
+      <c r="F135" t="s">
         <v>381</v>
-      </c>
-      <c r="E135" t="s">
-        <v>382</v>
-      </c>
-      <c r="F135" t="s">
-        <v>383</v>
       </c>
       <c r="G135">
         <v>5</v>
@@ -37928,16 +38006,16 @@
         <v>0</v>
       </c>
       <c r="C136" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D136" t="s">
+        <v>382</v>
+      </c>
+      <c r="E136" t="s">
+        <v>383</v>
+      </c>
+      <c r="F136" t="s">
         <v>384</v>
-      </c>
-      <c r="E136" t="s">
-        <v>385</v>
-      </c>
-      <c r="F136" t="s">
-        <v>386</v>
       </c>
       <c r="G136">
         <v>100</v>
@@ -37985,16 +38063,16 @@
         <v>0</v>
       </c>
       <c r="C137" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D137" t="s">
+        <v>385</v>
+      </c>
+      <c r="E137" t="s">
+        <v>386</v>
+      </c>
+      <c r="F137" t="s">
         <v>387</v>
-      </c>
-      <c r="E137" t="s">
-        <v>388</v>
-      </c>
-      <c r="F137" t="s">
-        <v>389</v>
       </c>
       <c r="G137">
         <v>30</v>
@@ -38042,25 +38120,25 @@
         <v>0</v>
       </c>
       <c r="C138" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D138" t="s">
+        <v>388</v>
+      </c>
+      <c r="E138" t="s">
+        <v>389</v>
+      </c>
+      <c r="F138" t="s">
+        <v>378</v>
+      </c>
+      <c r="G138" t="s">
         <v>390</v>
       </c>
-      <c r="E138" t="s">
+      <c r="H138" t="s">
         <v>391</v>
       </c>
-      <c r="F138" t="s">
-        <v>380</v>
-      </c>
-      <c r="G138" t="s">
+      <c r="I138" t="s">
         <v>392</v>
-      </c>
-      <c r="H138" t="s">
-        <v>393</v>
-      </c>
-      <c r="I138" t="s">
-        <v>394</v>
       </c>
       <c r="J138">
         <v>0</v>
@@ -38099,16 +38177,16 @@
         <v>0</v>
       </c>
       <c r="C139" t="s">
+        <v>393</v>
+      </c>
+      <c r="D139" t="s">
+        <v>394</v>
+      </c>
+      <c r="E139" t="s">
         <v>395</v>
       </c>
-      <c r="D139" t="s">
+      <c r="F139" t="s">
         <v>396</v>
-      </c>
-      <c r="E139" t="s">
-        <v>397</v>
-      </c>
-      <c r="F139" t="s">
-        <v>398</v>
       </c>
       <c r="G139">
         <v>0.5</v>
@@ -38156,16 +38234,16 @@
         <v>0</v>
       </c>
       <c r="C140" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D140" t="s">
+        <v>397</v>
+      </c>
+      <c r="E140" t="s">
+        <v>398</v>
+      </c>
+      <c r="F140" t="s">
         <v>399</v>
-      </c>
-      <c r="E140" t="s">
-        <v>400</v>
-      </c>
-      <c r="F140" t="s">
-        <v>401</v>
       </c>
       <c r="G140">
         <v>50</v>
@@ -38213,16 +38291,16 @@
         <v>0</v>
       </c>
       <c r="C141" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D141" t="s">
+        <v>400</v>
+      </c>
+      <c r="E141" t="s">
+        <v>401</v>
+      </c>
+      <c r="F141" t="s">
         <v>402</v>
-      </c>
-      <c r="E141" t="s">
-        <v>403</v>
-      </c>
-      <c r="F141" t="s">
-        <v>404</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -38270,16 +38348,16 @@
         <v>0</v>
       </c>
       <c r="C142" t="s">
+        <v>403</v>
+      </c>
+      <c r="D142" t="s">
+        <v>404</v>
+      </c>
+      <c r="E142" t="s">
         <v>405</v>
       </c>
-      <c r="D142" t="s">
+      <c r="F142" t="s">
         <v>406</v>
-      </c>
-      <c r="E142" t="s">
-        <v>407</v>
-      </c>
-      <c r="F142" t="s">
-        <v>408</v>
       </c>
       <c r="G142">
         <v>200</v>
@@ -38327,28 +38405,28 @@
         <v>0</v>
       </c>
       <c r="C143" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D143" t="s">
+        <v>407</v>
+      </c>
+      <c r="E143" t="s">
+        <v>408</v>
+      </c>
+      <c r="F143" t="s">
         <v>409</v>
-      </c>
-      <c r="E143" t="s">
-        <v>410</v>
-      </c>
-      <c r="F143" t="s">
-        <v>411</v>
       </c>
       <c r="G143">
         <v>55</v>
       </c>
       <c r="H143" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I143" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="J143" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="K143">
         <v>0</v>
@@ -38384,28 +38462,28 @@
         <v>0</v>
       </c>
       <c r="C144" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D144" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E144" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F144" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="G144">
         <v>25</v>
       </c>
       <c r="H144" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I144">
         <v>2</v>
       </c>
       <c r="J144" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="K144">
         <v>0</v>
@@ -38441,28 +38519,28 @@
         <v>0</v>
       </c>
       <c r="C145" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D145" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E145" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F145" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="G145">
         <v>12</v>
       </c>
       <c r="H145" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I145">
         <v>2.5</v>
       </c>
       <c r="J145" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="K145">
         <v>0</v>
@@ -38498,28 +38576,28 @@
         <v>0</v>
       </c>
       <c r="C146" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D146" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E146" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F146" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="G146">
         <v>5.5</v>
       </c>
       <c r="H146" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I146">
         <v>3</v>
       </c>
       <c r="J146" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="K146">
         <v>0</v>
@@ -38555,28 +38633,28 @@
         <v>0</v>
       </c>
       <c r="C147" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D147" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E147" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F147" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="G147">
         <v>1.8</v>
       </c>
       <c r="H147" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I147">
         <v>3.5</v>
       </c>
       <c r="J147" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="K147">
         <v>0</v>
@@ -38612,28 +38690,28 @@
         <v>0</v>
       </c>
       <c r="C148" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D148" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E148" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F148" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="G148">
         <v>0.35</v>
       </c>
       <c r="H148" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I148">
         <v>4</v>
       </c>
       <c r="J148" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="K148">
         <v>0</v>
@@ -38669,28 +38747,28 @@
         <v>0</v>
       </c>
       <c r="C149" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D149" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E149" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F149" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="G149">
         <v>0.08</v>
       </c>
       <c r="H149" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I149">
         <v>4.5</v>
       </c>
       <c r="J149" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="K149">
         <v>0</v>
@@ -38726,28 +38804,28 @@
         <v>0</v>
       </c>
       <c r="C150" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D150" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E150" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F150" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="G150">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="H150" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="I150">
         <v>5</v>
       </c>
       <c r="J150" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="K150">
         <v>0</v>
@@ -38783,37 +38861,37 @@
         <v>0</v>
       </c>
       <c r="C151" t="s">
+        <v>423</v>
+      </c>
+      <c r="D151" t="s">
+        <v>424</v>
+      </c>
+      <c r="E151" t="s">
         <v>425</v>
       </c>
-      <c r="D151" t="s">
+      <c r="F151" t="s">
         <v>426</v>
       </c>
-      <c r="E151" t="s">
+      <c r="G151" t="s">
         <v>427</v>
       </c>
-      <c r="F151" t="s">
+      <c r="H151" t="s">
         <v>428</v>
       </c>
-      <c r="G151" t="s">
+      <c r="I151" t="s">
         <v>429</v>
       </c>
-      <c r="H151" t="s">
+      <c r="J151" t="s">
         <v>430</v>
       </c>
-      <c r="I151" t="s">
+      <c r="K151" t="s">
         <v>431</v>
       </c>
-      <c r="J151" t="s">
+      <c r="L151" t="s">
         <v>432</v>
       </c>
-      <c r="K151" t="s">
+      <c r="M151" t="s">
         <v>433</v>
-      </c>
-      <c r="L151" t="s">
-        <v>434</v>
-      </c>
-      <c r="M151" t="s">
-        <v>435</v>
       </c>
       <c r="N151">
         <v>0</v>
@@ -38840,37 +38918,37 @@
         <v>0</v>
       </c>
       <c r="C152" t="s">
+        <v>423</v>
+      </c>
+      <c r="D152" t="s">
+        <v>434</v>
+      </c>
+      <c r="E152" t="s">
         <v>425</v>
       </c>
-      <c r="D152" t="s">
+      <c r="F152" t="s">
+        <v>426</v>
+      </c>
+      <c r="G152" t="s">
+        <v>435</v>
+      </c>
+      <c r="H152" t="s">
         <v>436</v>
       </c>
-      <c r="E152" t="s">
-        <v>427</v>
-      </c>
-      <c r="F152" t="s">
-        <v>428</v>
-      </c>
-      <c r="G152" t="s">
+      <c r="I152" t="s">
         <v>437</v>
       </c>
-      <c r="H152" t="s">
+      <c r="J152" t="s">
         <v>438</v>
       </c>
-      <c r="I152" t="s">
+      <c r="K152" t="s">
         <v>439</v>
       </c>
-      <c r="J152" t="s">
+      <c r="L152" t="s">
         <v>440</v>
       </c>
-      <c r="K152" t="s">
+      <c r="M152" t="s">
         <v>441</v>
-      </c>
-      <c r="L152" t="s">
-        <v>442</v>
-      </c>
-      <c r="M152" t="s">
-        <v>443</v>
       </c>
       <c r="N152">
         <v>0</v>
@@ -38897,37 +38975,37 @@
         <v>0</v>
       </c>
       <c r="C153" t="s">
+        <v>423</v>
+      </c>
+      <c r="D153" t="s">
+        <v>442</v>
+      </c>
+      <c r="E153" t="s">
         <v>425</v>
       </c>
-      <c r="D153" t="s">
+      <c r="F153" t="s">
+        <v>426</v>
+      </c>
+      <c r="G153" t="s">
+        <v>443</v>
+      </c>
+      <c r="H153" t="s">
         <v>444</v>
       </c>
-      <c r="E153" t="s">
-        <v>427</v>
-      </c>
-      <c r="F153" t="s">
-        <v>428</v>
-      </c>
-      <c r="G153" t="s">
+      <c r="I153" t="s">
         <v>445</v>
       </c>
-      <c r="H153" t="s">
+      <c r="J153" t="s">
         <v>446</v>
       </c>
-      <c r="I153" t="s">
+      <c r="K153" t="s">
         <v>447</v>
       </c>
-      <c r="J153" t="s">
+      <c r="L153" t="s">
         <v>448</v>
       </c>
-      <c r="K153" t="s">
+      <c r="M153" t="s">
         <v>449</v>
-      </c>
-      <c r="L153" t="s">
-        <v>450</v>
-      </c>
-      <c r="M153" t="s">
-        <v>451</v>
       </c>
       <c r="N153">
         <v>0</v>
@@ -38954,37 +39032,37 @@
         <v>0</v>
       </c>
       <c r="C154" t="s">
+        <v>423</v>
+      </c>
+      <c r="D154" t="s">
+        <v>450</v>
+      </c>
+      <c r="E154" t="s">
         <v>425</v>
       </c>
-      <c r="D154" t="s">
+      <c r="F154" t="s">
+        <v>426</v>
+      </c>
+      <c r="G154" t="s">
+        <v>451</v>
+      </c>
+      <c r="H154" t="s">
         <v>452</v>
       </c>
-      <c r="E154" t="s">
-        <v>427</v>
-      </c>
-      <c r="F154" t="s">
-        <v>428</v>
-      </c>
-      <c r="G154" t="s">
+      <c r="I154" t="s">
         <v>453</v>
       </c>
-      <c r="H154" t="s">
+      <c r="J154" t="s">
         <v>454</v>
       </c>
-      <c r="I154" t="s">
+      <c r="K154" t="s">
         <v>455</v>
       </c>
-      <c r="J154" t="s">
+      <c r="L154" t="s">
         <v>456</v>
       </c>
-      <c r="K154" t="s">
+      <c r="M154" t="s">
         <v>457</v>
-      </c>
-      <c r="L154" t="s">
-        <v>458</v>
-      </c>
-      <c r="M154" t="s">
-        <v>459</v>
       </c>
       <c r="N154">
         <v>0</v>
@@ -39011,37 +39089,37 @@
         <v>0</v>
       </c>
       <c r="C155" t="s">
+        <v>423</v>
+      </c>
+      <c r="D155" t="s">
+        <v>458</v>
+      </c>
+      <c r="E155" t="s">
         <v>425</v>
       </c>
-      <c r="D155" t="s">
+      <c r="F155" t="s">
+        <v>426</v>
+      </c>
+      <c r="G155" t="s">
+        <v>451</v>
+      </c>
+      <c r="H155" t="s">
+        <v>459</v>
+      </c>
+      <c r="I155" t="s">
         <v>460</v>
       </c>
-      <c r="E155" t="s">
-        <v>427</v>
-      </c>
-      <c r="F155" t="s">
-        <v>428</v>
-      </c>
-      <c r="G155" t="s">
-        <v>453</v>
-      </c>
-      <c r="H155" t="s">
+      <c r="J155" t="s">
         <v>461</v>
       </c>
-      <c r="I155" t="s">
+      <c r="K155" t="s">
         <v>462</v>
       </c>
-      <c r="J155" t="s">
+      <c r="L155" t="s">
         <v>463</v>
       </c>
-      <c r="K155" t="s">
+      <c r="M155" t="s">
         <v>464</v>
-      </c>
-      <c r="L155" t="s">
-        <v>465</v>
-      </c>
-      <c r="M155" t="s">
-        <v>466</v>
       </c>
       <c r="N155">
         <v>0</v>
@@ -39068,37 +39146,37 @@
         <v>0</v>
       </c>
       <c r="C156" t="s">
+        <v>423</v>
+      </c>
+      <c r="D156" t="s">
+        <v>465</v>
+      </c>
+      <c r="E156" t="s">
         <v>425</v>
       </c>
-      <c r="D156" t="s">
+      <c r="F156" t="s">
+        <v>426</v>
+      </c>
+      <c r="G156" t="s">
+        <v>451</v>
+      </c>
+      <c r="H156" t="s">
+        <v>466</v>
+      </c>
+      <c r="I156" t="s">
+        <v>268</v>
+      </c>
+      <c r="J156" t="s">
         <v>467</v>
       </c>
-      <c r="E156" t="s">
-        <v>427</v>
-      </c>
-      <c r="F156" t="s">
-        <v>428</v>
-      </c>
-      <c r="G156" t="s">
-        <v>453</v>
-      </c>
-      <c r="H156" t="s">
+      <c r="K156" t="s">
         <v>468</v>
       </c>
-      <c r="I156" t="s">
-        <v>270</v>
-      </c>
-      <c r="J156" t="s">
+      <c r="L156" t="s">
         <v>469</v>
       </c>
-      <c r="K156" t="s">
+      <c r="M156" t="s">
         <v>470</v>
-      </c>
-      <c r="L156" t="s">
-        <v>471</v>
-      </c>
-      <c r="M156" t="s">
-        <v>472</v>
       </c>
       <c r="N156">
         <v>0</v>
@@ -39125,37 +39203,37 @@
         <v>0</v>
       </c>
       <c r="C157" t="s">
+        <v>423</v>
+      </c>
+      <c r="D157" t="s">
+        <v>471</v>
+      </c>
+      <c r="E157" t="s">
         <v>425</v>
       </c>
-      <c r="D157" t="s">
+      <c r="F157" t="s">
+        <v>426</v>
+      </c>
+      <c r="G157" t="s">
+        <v>451</v>
+      </c>
+      <c r="H157" t="s">
+        <v>466</v>
+      </c>
+      <c r="I157" t="s">
+        <v>472</v>
+      </c>
+      <c r="J157" t="s">
         <v>473</v>
       </c>
-      <c r="E157" t="s">
-        <v>427</v>
-      </c>
-      <c r="F157" t="s">
-        <v>428</v>
-      </c>
-      <c r="G157" t="s">
-        <v>453</v>
-      </c>
-      <c r="H157" t="s">
-        <v>468</v>
-      </c>
-      <c r="I157" t="s">
+      <c r="K157" t="s">
         <v>474</v>
       </c>
-      <c r="J157" t="s">
+      <c r="L157" t="s">
         <v>475</v>
       </c>
-      <c r="K157" t="s">
+      <c r="M157" t="s">
         <v>476</v>
-      </c>
-      <c r="L157" t="s">
-        <v>477</v>
-      </c>
-      <c r="M157" t="s">
-        <v>478</v>
       </c>
       <c r="N157">
         <v>0</v>
@@ -39182,37 +39260,37 @@
         <v>0</v>
       </c>
       <c r="C158" t="s">
+        <v>423</v>
+      </c>
+      <c r="D158" t="s">
+        <v>477</v>
+      </c>
+      <c r="E158" t="s">
         <v>425</v>
       </c>
-      <c r="D158" t="s">
+      <c r="F158" t="s">
+        <v>426</v>
+      </c>
+      <c r="G158" t="s">
+        <v>451</v>
+      </c>
+      <c r="H158" t="s">
+        <v>466</v>
+      </c>
+      <c r="I158" t="s">
+        <v>472</v>
+      </c>
+      <c r="J158" t="s">
+        <v>478</v>
+      </c>
+      <c r="K158" t="s">
         <v>479</v>
       </c>
-      <c r="E158" t="s">
-        <v>427</v>
-      </c>
-      <c r="F158" t="s">
-        <v>428</v>
-      </c>
-      <c r="G158" t="s">
-        <v>453</v>
-      </c>
-      <c r="H158" t="s">
-        <v>468</v>
-      </c>
-      <c r="I158" t="s">
-        <v>474</v>
-      </c>
-      <c r="J158" t="s">
+      <c r="L158" t="s">
         <v>480</v>
       </c>
-      <c r="K158" t="s">
+      <c r="M158" t="s">
         <v>481</v>
-      </c>
-      <c r="L158" t="s">
-        <v>482</v>
-      </c>
-      <c r="M158" t="s">
-        <v>483</v>
       </c>
       <c r="N158">
         <v>0</v>
@@ -39239,16 +39317,16 @@
         <v>0</v>
       </c>
       <c r="C159" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D159" t="s">
+        <v>482</v>
+      </c>
+      <c r="E159" t="s">
+        <v>483</v>
+      </c>
+      <c r="F159" t="s">
         <v>484</v>
-      </c>
-      <c r="E159" t="s">
-        <v>485</v>
-      </c>
-      <c r="F159" t="s">
-        <v>486</v>
       </c>
       <c r="G159">
         <v>551</v>
@@ -39296,16 +39374,16 @@
         <v>0</v>
       </c>
       <c r="C160" t="s">
+        <v>485</v>
+      </c>
+      <c r="D160" t="s">
+        <v>486</v>
+      </c>
+      <c r="E160" t="s">
         <v>487</v>
       </c>
-      <c r="D160" t="s">
+      <c r="F160" t="s">
         <v>488</v>
-      </c>
-      <c r="E160" t="s">
-        <v>489</v>
-      </c>
-      <c r="F160" t="s">
-        <v>490</v>
       </c>
       <c r="G160">
         <v>2</v>
@@ -39353,16 +39431,16 @@
         <v>0</v>
       </c>
       <c r="C161" t="s">
+        <v>485</v>
+      </c>
+      <c r="D161" t="s">
+        <v>489</v>
+      </c>
+      <c r="E161" t="s">
         <v>487</v>
       </c>
-      <c r="D161" t="s">
-        <v>491</v>
-      </c>
-      <c r="E161" t="s">
-        <v>489</v>
-      </c>
       <c r="F161" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G161">
         <v>4</v>
@@ -39410,16 +39488,16 @@
         <v>0</v>
       </c>
       <c r="C162" t="s">
+        <v>485</v>
+      </c>
+      <c r="D162" t="s">
+        <v>490</v>
+      </c>
+      <c r="E162" t="s">
         <v>487</v>
       </c>
-      <c r="D162" t="s">
-        <v>492</v>
-      </c>
-      <c r="E162" t="s">
-        <v>489</v>
-      </c>
       <c r="F162" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G162">
         <v>6</v>
@@ -39467,16 +39545,16 @@
         <v>0</v>
       </c>
       <c r="C163" t="s">
+        <v>485</v>
+      </c>
+      <c r="D163" t="s">
+        <v>491</v>
+      </c>
+      <c r="E163" t="s">
         <v>487</v>
       </c>
-      <c r="D163" t="s">
-        <v>493</v>
-      </c>
-      <c r="E163" t="s">
-        <v>489</v>
-      </c>
       <c r="F163" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G163">
         <v>8</v>
@@ -39524,16 +39602,16 @@
         <v>0</v>
       </c>
       <c r="C164" t="s">
+        <v>485</v>
+      </c>
+      <c r="D164" t="s">
+        <v>492</v>
+      </c>
+      <c r="E164" t="s">
         <v>487</v>
       </c>
-      <c r="D164" t="s">
-        <v>494</v>
-      </c>
-      <c r="E164" t="s">
-        <v>489</v>
-      </c>
       <c r="F164" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G164">
         <v>10</v>
@@ -39581,16 +39659,16 @@
         <v>0</v>
       </c>
       <c r="C165" t="s">
+        <v>485</v>
+      </c>
+      <c r="D165" t="s">
+        <v>493</v>
+      </c>
+      <c r="E165" t="s">
         <v>487</v>
       </c>
-      <c r="D165" t="s">
-        <v>495</v>
-      </c>
-      <c r="E165" t="s">
-        <v>489</v>
-      </c>
       <c r="F165" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G165">
         <v>12</v>
@@ -39638,16 +39716,16 @@
         <v>0</v>
       </c>
       <c r="C166" t="s">
+        <v>485</v>
+      </c>
+      <c r="D166" t="s">
+        <v>494</v>
+      </c>
+      <c r="E166" t="s">
         <v>487</v>
       </c>
-      <c r="D166" t="s">
-        <v>496</v>
-      </c>
-      <c r="E166" t="s">
-        <v>489</v>
-      </c>
       <c r="F166" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G166">
         <v>14</v>
@@ -39695,16 +39773,16 @@
         <v>0</v>
       </c>
       <c r="C167" t="s">
+        <v>495</v>
+      </c>
+      <c r="D167" t="s">
+        <v>496</v>
+      </c>
+      <c r="E167" t="s">
         <v>497</v>
       </c>
-      <c r="D167" t="s">
+      <c r="F167" t="s">
         <v>498</v>
-      </c>
-      <c r="E167" t="s">
-        <v>499</v>
-      </c>
-      <c r="F167" t="s">
-        <v>500</v>
       </c>
       <c r="G167">
         <v>4</v>
@@ -39752,16 +39830,16 @@
         <v>0</v>
       </c>
       <c r="C168" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D168" t="s">
+        <v>499</v>
+      </c>
+      <c r="E168" t="s">
+        <v>500</v>
+      </c>
+      <c r="F168" t="s">
         <v>501</v>
-      </c>
-      <c r="E168" t="s">
-        <v>502</v>
-      </c>
-      <c r="F168" t="s">
-        <v>503</v>
       </c>
       <c r="G168">
         <v>5</v>
@@ -39809,16 +39887,16 @@
         <v>0</v>
       </c>
       <c r="C169" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D169" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E169" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F169" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G169">
         <v>10</v>
@@ -39866,16 +39944,16 @@
         <v>0</v>
       </c>
       <c r="C170" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D170" t="s">
+        <v>504</v>
+      </c>
+      <c r="E170" t="s">
+        <v>505</v>
+      </c>
+      <c r="F170" t="s">
         <v>506</v>
-      </c>
-      <c r="E170" t="s">
-        <v>507</v>
-      </c>
-      <c r="F170" t="s">
-        <v>508</v>
       </c>
       <c r="G170">
         <v>0.5</v>
@@ -39923,16 +40001,16 @@
         <v>0</v>
       </c>
       <c r="C171" t="s">
+        <v>507</v>
+      </c>
+      <c r="D171" t="s">
+        <v>508</v>
+      </c>
+      <c r="E171" t="s">
         <v>509</v>
       </c>
-      <c r="D171" t="s">
+      <c r="F171" t="s">
         <v>510</v>
-      </c>
-      <c r="E171" t="s">
-        <v>511</v>
-      </c>
-      <c r="F171" t="s">
-        <v>512</v>
       </c>
       <c r="G171">
         <v>100</v>
@@ -39980,16 +40058,16 @@
         <v>0</v>
       </c>
       <c r="C172" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D172" t="s">
+        <v>511</v>
+      </c>
+      <c r="E172" t="s">
+        <v>512</v>
+      </c>
+      <c r="F172" t="s">
         <v>513</v>
-      </c>
-      <c r="E172" t="s">
-        <v>514</v>
-      </c>
-      <c r="F172" t="s">
-        <v>515</v>
       </c>
       <c r="G172">
         <v>92</v>
@@ -40037,16 +40115,16 @@
         <v>0</v>
       </c>
       <c r="C173" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D173" t="s">
+        <v>514</v>
+      </c>
+      <c r="E173" t="s">
+        <v>515</v>
+      </c>
+      <c r="F173" t="s">
         <v>516</v>
-      </c>
-      <c r="E173" t="s">
-        <v>517</v>
-      </c>
-      <c r="F173" t="s">
-        <v>518</v>
       </c>
       <c r="G173">
         <v>78.099999999999994</v>
@@ -40094,16 +40172,16 @@
         <v>0</v>
       </c>
       <c r="C174" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D174" t="s">
+        <v>517</v>
+      </c>
+      <c r="E174" t="s">
+        <v>518</v>
+      </c>
+      <c r="F174" t="s">
         <v>519</v>
-      </c>
-      <c r="E174" t="s">
-        <v>520</v>
-      </c>
-      <c r="F174" t="s">
-        <v>521</v>
       </c>
       <c r="G174">
         <v>72.11</v>
@@ -40151,16 +40229,16 @@
         <v>0</v>
       </c>
       <c r="C175" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D175" t="s">
+        <v>520</v>
+      </c>
+      <c r="E175" t="s">
+        <v>521</v>
+      </c>
+      <c r="F175" t="s">
         <v>522</v>
-      </c>
-      <c r="E175" t="s">
-        <v>523</v>
-      </c>
-      <c r="F175" t="s">
-        <v>524</v>
       </c>
       <c r="G175">
         <v>74.349999999999994</v>
@@ -40208,16 +40286,16 @@
         <v>0</v>
       </c>
       <c r="C176" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D176" t="s">
+        <v>523</v>
+      </c>
+      <c r="E176" t="s">
+        <v>524</v>
+      </c>
+      <c r="F176" t="s">
         <v>525</v>
-      </c>
-      <c r="E176" t="s">
-        <v>526</v>
-      </c>
-      <c r="F176" t="s">
-        <v>527</v>
       </c>
       <c r="G176">
         <v>76.87</v>
@@ -40265,16 +40343,16 @@
         <v>0</v>
       </c>
       <c r="C177" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D177" t="s">
+        <v>526</v>
+      </c>
+      <c r="E177" t="s">
+        <v>527</v>
+      </c>
+      <c r="F177" t="s">
         <v>528</v>
-      </c>
-      <c r="E177" t="s">
-        <v>529</v>
-      </c>
-      <c r="F177" t="s">
-        <v>530</v>
       </c>
       <c r="G177">
         <v>69.92</v>
@@ -40322,16 +40400,16 @@
         <v>0</v>
       </c>
       <c r="C178" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D178" t="s">
+        <v>529</v>
+      </c>
+      <c r="E178" t="s">
+        <v>530</v>
+      </c>
+      <c r="F178" t="s">
         <v>531</v>
-      </c>
-      <c r="E178" t="s">
-        <v>532</v>
-      </c>
-      <c r="F178" t="s">
-        <v>533</v>
       </c>
       <c r="G178">
         <v>64.22</v>
@@ -40379,16 +40457,16 @@
         <v>0</v>
       </c>
       <c r="C179" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D179" t="s">
+        <v>532</v>
+      </c>
+      <c r="E179" t="s">
+        <v>533</v>
+      </c>
+      <c r="F179" t="s">
         <v>534</v>
-      </c>
-      <c r="E179" t="s">
-        <v>535</v>
-      </c>
-      <c r="F179" t="s">
-        <v>536</v>
       </c>
       <c r="G179">
         <v>59.92</v>
@@ -40436,16 +40514,16 @@
         <v>0</v>
       </c>
       <c r="C180" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D180" t="s">
+        <v>535</v>
+      </c>
+      <c r="E180" t="s">
+        <v>536</v>
+      </c>
+      <c r="F180" t="s">
         <v>537</v>
-      </c>
-      <c r="E180" t="s">
-        <v>538</v>
-      </c>
-      <c r="F180" t="s">
-        <v>539</v>
       </c>
       <c r="G180">
         <v>54.72</v>
@@ -40493,16 +40571,16 @@
         <v>0</v>
       </c>
       <c r="C181" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D181" t="s">
+        <v>538</v>
+      </c>
+      <c r="E181" t="s">
+        <v>539</v>
+      </c>
+      <c r="F181" t="s">
         <v>540</v>
-      </c>
-      <c r="E181" t="s">
-        <v>541</v>
-      </c>
-      <c r="F181" t="s">
-        <v>542</v>
       </c>
       <c r="G181">
         <v>1.35</v>
@@ -40550,16 +40628,16 @@
         <v>0</v>
       </c>
       <c r="C182" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D182" t="s">
+        <v>541</v>
+      </c>
+      <c r="E182" t="s">
+        <v>542</v>
+      </c>
+      <c r="F182" t="s">
         <v>543</v>
-      </c>
-      <c r="E182" t="s">
-        <v>544</v>
-      </c>
-      <c r="F182" t="s">
-        <v>545</v>
       </c>
       <c r="G182">
         <v>0.5</v>
@@ -40607,16 +40685,16 @@
         <v>0</v>
       </c>
       <c r="C183" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D183" t="s">
+        <v>544</v>
+      </c>
+      <c r="E183" t="s">
+        <v>545</v>
+      </c>
+      <c r="F183" t="s">
         <v>546</v>
-      </c>
-      <c r="E183" t="s">
-        <v>547</v>
-      </c>
-      <c r="F183" t="s">
-        <v>548</v>
       </c>
       <c r="G183">
         <v>4000</v>
@@ -40664,16 +40742,16 @@
         <v>0</v>
       </c>
       <c r="C184" t="s">
+        <v>547</v>
+      </c>
+      <c r="D184" t="s">
+        <v>548</v>
+      </c>
+      <c r="E184" t="s">
         <v>549</v>
       </c>
-      <c r="D184" t="s">
+      <c r="F184" t="s">
         <v>550</v>
-      </c>
-      <c r="E184" t="s">
-        <v>551</v>
-      </c>
-      <c r="F184" t="s">
-        <v>552</v>
       </c>
       <c r="G184">
         <v>4</v>
@@ -40721,16 +40799,16 @@
         <v>0</v>
       </c>
       <c r="C185" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D185" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E185" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="F185" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="G185">
         <v>200</v>
@@ -40778,16 +40856,16 @@
         <v>0</v>
       </c>
       <c r="C186" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D186" t="s">
+        <v>553</v>
+      </c>
+      <c r="E186" t="s">
+        <v>554</v>
+      </c>
+      <c r="F186" t="s">
         <v>555</v>
-      </c>
-      <c r="E186" t="s">
-        <v>556</v>
-      </c>
-      <c r="F186" t="s">
-        <v>557</v>
       </c>
       <c r="G186">
         <v>4</v>
@@ -40835,16 +40913,16 @@
         <v>0</v>
       </c>
       <c r="C187" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D187" t="s">
+        <v>556</v>
+      </c>
+      <c r="E187" t="s">
+        <v>557</v>
+      </c>
+      <c r="F187" t="s">
         <v>558</v>
-      </c>
-      <c r="E187" t="s">
-        <v>559</v>
-      </c>
-      <c r="F187" t="s">
-        <v>560</v>
       </c>
       <c r="G187">
         <v>3</v>
@@ -40892,16 +40970,16 @@
         <v>0</v>
       </c>
       <c r="C188" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D188" t="s">
+        <v>559</v>
+      </c>
+      <c r="E188" t="s">
+        <v>560</v>
+      </c>
+      <c r="F188" t="s">
         <v>561</v>
-      </c>
-      <c r="E188" t="s">
-        <v>562</v>
-      </c>
-      <c r="F188" t="s">
-        <v>563</v>
       </c>
       <c r="G188">
         <v>4</v>
@@ -40949,37 +41027,37 @@
         <v>0</v>
       </c>
       <c r="C189" t="s">
+        <v>562</v>
+      </c>
+      <c r="D189" t="s">
+        <v>424</v>
+      </c>
+      <c r="E189" t="s">
+        <v>563</v>
+      </c>
+      <c r="F189" t="s">
         <v>564</v>
       </c>
-      <c r="D189" t="s">
-        <v>426</v>
-      </c>
-      <c r="E189" t="s">
+      <c r="G189" t="s">
         <v>565</v>
       </c>
-      <c r="F189" t="s">
+      <c r="H189" t="s">
         <v>566</v>
       </c>
-      <c r="G189" t="s">
+      <c r="I189" t="s">
         <v>567</v>
       </c>
-      <c r="H189" t="s">
+      <c r="J189" t="s">
         <v>568</v>
       </c>
-      <c r="I189" t="s">
+      <c r="K189" t="s">
         <v>569</v>
       </c>
-      <c r="J189" t="s">
+      <c r="L189" t="s">
         <v>570</v>
       </c>
-      <c r="K189" t="s">
+      <c r="M189" t="s">
         <v>571</v>
-      </c>
-      <c r="L189" t="s">
-        <v>572</v>
-      </c>
-      <c r="M189" t="s">
-        <v>573</v>
       </c>
       <c r="N189">
         <v>0</v>
@@ -41006,37 +41084,37 @@
         <v>0</v>
       </c>
       <c r="C190" t="s">
+        <v>562</v>
+      </c>
+      <c r="D190" t="s">
+        <v>434</v>
+      </c>
+      <c r="E190" t="s">
+        <v>563</v>
+      </c>
+      <c r="F190" t="s">
         <v>564</v>
       </c>
-      <c r="D190" t="s">
-        <v>436</v>
-      </c>
-      <c r="E190" t="s">
+      <c r="G190" t="s">
         <v>565</v>
       </c>
-      <c r="F190" t="s">
+      <c r="H190" t="s">
         <v>566</v>
       </c>
-      <c r="G190" t="s">
+      <c r="I190" t="s">
         <v>567</v>
       </c>
-      <c r="H190" t="s">
+      <c r="J190" t="s">
         <v>568</v>
       </c>
-      <c r="I190" t="s">
+      <c r="K190" t="s">
         <v>569</v>
       </c>
-      <c r="J190" t="s">
+      <c r="L190" t="s">
         <v>570</v>
       </c>
-      <c r="K190" t="s">
+      <c r="M190" t="s">
         <v>571</v>
-      </c>
-      <c r="L190" t="s">
-        <v>572</v>
-      </c>
-      <c r="M190" t="s">
-        <v>573</v>
       </c>
       <c r="N190">
         <v>0</v>
@@ -41063,37 +41141,37 @@
         <v>0</v>
       </c>
       <c r="C191" t="s">
+        <v>562</v>
+      </c>
+      <c r="D191" t="s">
+        <v>442</v>
+      </c>
+      <c r="E191" t="s">
+        <v>563</v>
+      </c>
+      <c r="F191" t="s">
         <v>564</v>
       </c>
-      <c r="D191" t="s">
-        <v>444</v>
-      </c>
-      <c r="E191" t="s">
-        <v>565</v>
-      </c>
-      <c r="F191" t="s">
-        <v>566</v>
-      </c>
       <c r="G191" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H191" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="I191" t="s">
+        <v>567</v>
+      </c>
+      <c r="J191" t="s">
+        <v>568</v>
+      </c>
+      <c r="K191" t="s">
         <v>569</v>
       </c>
-      <c r="J191" t="s">
+      <c r="L191" t="s">
         <v>570</v>
       </c>
-      <c r="K191" t="s">
+      <c r="M191" t="s">
         <v>571</v>
-      </c>
-      <c r="L191" t="s">
-        <v>572</v>
-      </c>
-      <c r="M191" t="s">
-        <v>573</v>
       </c>
       <c r="N191">
         <v>0</v>
@@ -41120,37 +41198,37 @@
         <v>0</v>
       </c>
       <c r="C192" t="s">
+        <v>562</v>
+      </c>
+      <c r="D192" t="s">
+        <v>450</v>
+      </c>
+      <c r="E192" t="s">
+        <v>563</v>
+      </c>
+      <c r="F192" t="s">
         <v>564</v>
       </c>
-      <c r="D192" t="s">
-        <v>452</v>
-      </c>
-      <c r="E192" t="s">
-        <v>565</v>
-      </c>
-      <c r="F192" t="s">
-        <v>566</v>
-      </c>
       <c r="G192" t="s">
+        <v>574</v>
+      </c>
+      <c r="H192" t="s">
+        <v>573</v>
+      </c>
+      <c r="I192" t="s">
+        <v>575</v>
+      </c>
+      <c r="J192" t="s">
         <v>576</v>
       </c>
-      <c r="H192" t="s">
-        <v>575</v>
-      </c>
-      <c r="I192" t="s">
+      <c r="K192" t="s">
         <v>577</v>
       </c>
-      <c r="J192" t="s">
+      <c r="L192" t="s">
         <v>578</v>
       </c>
-      <c r="K192" t="s">
+      <c r="M192" t="s">
         <v>579</v>
-      </c>
-      <c r="L192" t="s">
-        <v>580</v>
-      </c>
-      <c r="M192" t="s">
-        <v>581</v>
       </c>
       <c r="N192">
         <v>0</v>
@@ -41177,37 +41255,37 @@
         <v>0</v>
       </c>
       <c r="C193" t="s">
+        <v>562</v>
+      </c>
+      <c r="D193" t="s">
+        <v>458</v>
+      </c>
+      <c r="E193" t="s">
+        <v>563</v>
+      </c>
+      <c r="F193" t="s">
         <v>564</v>
       </c>
-      <c r="D193" t="s">
-        <v>460</v>
-      </c>
-      <c r="E193" t="s">
-        <v>565</v>
-      </c>
-      <c r="F193" t="s">
-        <v>566</v>
-      </c>
       <c r="G193" t="s">
+        <v>580</v>
+      </c>
+      <c r="H193" t="s">
+        <v>581</v>
+      </c>
+      <c r="I193" t="s">
+        <v>575</v>
+      </c>
+      <c r="J193" t="s">
         <v>582</v>
       </c>
-      <c r="H193" t="s">
+      <c r="K193" t="s">
         <v>583</v>
       </c>
-      <c r="I193" t="s">
-        <v>577</v>
-      </c>
-      <c r="J193" t="s">
+      <c r="L193" t="s">
         <v>584</v>
       </c>
-      <c r="K193" t="s">
+      <c r="M193" t="s">
         <v>585</v>
-      </c>
-      <c r="L193" t="s">
-        <v>586</v>
-      </c>
-      <c r="M193" t="s">
-        <v>587</v>
       </c>
       <c r="N193">
         <v>0</v>
@@ -41234,37 +41312,37 @@
         <v>0</v>
       </c>
       <c r="C194" t="s">
+        <v>562</v>
+      </c>
+      <c r="D194" t="s">
+        <v>465</v>
+      </c>
+      <c r="E194" t="s">
+        <v>563</v>
+      </c>
+      <c r="F194" t="s">
         <v>564</v>
       </c>
-      <c r="D194" t="s">
-        <v>467</v>
-      </c>
-      <c r="E194" t="s">
-        <v>565</v>
-      </c>
-      <c r="F194" t="s">
-        <v>566</v>
-      </c>
       <c r="G194" t="s">
+        <v>586</v>
+      </c>
+      <c r="H194" t="s">
+        <v>587</v>
+      </c>
+      <c r="I194" t="s">
         <v>588</v>
       </c>
-      <c r="H194" t="s">
+      <c r="J194" t="s">
         <v>589</v>
       </c>
-      <c r="I194" t="s">
+      <c r="K194" t="s">
         <v>590</v>
       </c>
-      <c r="J194" t="s">
+      <c r="L194" t="s">
         <v>591</v>
       </c>
-      <c r="K194" t="s">
+      <c r="M194" t="s">
         <v>592</v>
-      </c>
-      <c r="L194" t="s">
-        <v>593</v>
-      </c>
-      <c r="M194" t="s">
-        <v>594</v>
       </c>
       <c r="N194">
         <v>0</v>
@@ -41291,37 +41369,37 @@
         <v>0</v>
       </c>
       <c r="C195" t="s">
+        <v>562</v>
+      </c>
+      <c r="D195" t="s">
+        <v>471</v>
+      </c>
+      <c r="E195" t="s">
+        <v>563</v>
+      </c>
+      <c r="F195" t="s">
         <v>564</v>
       </c>
-      <c r="D195" t="s">
-        <v>473</v>
-      </c>
-      <c r="E195" t="s">
+      <c r="G195" t="s">
         <v>565</v>
       </c>
-      <c r="F195" t="s">
-        <v>566</v>
-      </c>
-      <c r="G195" t="s">
-        <v>567</v>
-      </c>
       <c r="H195" t="s">
+        <v>593</v>
+      </c>
+      <c r="I195" t="s">
+        <v>594</v>
+      </c>
+      <c r="J195" t="s">
         <v>595</v>
       </c>
-      <c r="I195" t="s">
+      <c r="K195" t="s">
         <v>596</v>
       </c>
-      <c r="J195" t="s">
+      <c r="L195" t="s">
         <v>597</v>
       </c>
-      <c r="K195" t="s">
+      <c r="M195" t="s">
         <v>598</v>
-      </c>
-      <c r="L195" t="s">
-        <v>599</v>
-      </c>
-      <c r="M195" t="s">
-        <v>600</v>
       </c>
       <c r="N195">
         <v>0</v>
@@ -41348,37 +41426,37 @@
         <v>0</v>
       </c>
       <c r="C196" t="s">
+        <v>562</v>
+      </c>
+      <c r="D196" t="s">
+        <v>477</v>
+      </c>
+      <c r="E196" t="s">
+        <v>563</v>
+      </c>
+      <c r="F196" t="s">
         <v>564</v>
       </c>
-      <c r="D196" t="s">
-        <v>479</v>
-      </c>
-      <c r="E196" t="s">
+      <c r="G196" t="s">
         <v>565</v>
       </c>
-      <c r="F196" t="s">
+      <c r="H196" t="s">
         <v>566</v>
       </c>
-      <c r="G196" t="s">
-        <v>567</v>
-      </c>
-      <c r="H196" t="s">
-        <v>568</v>
-      </c>
       <c r="I196" t="s">
+        <v>599</v>
+      </c>
+      <c r="J196" t="s">
+        <v>600</v>
+      </c>
+      <c r="K196" t="s">
         <v>601</v>
       </c>
-      <c r="J196" t="s">
+      <c r="L196" t="s">
         <v>602</v>
       </c>
-      <c r="K196" t="s">
+      <c r="M196" t="s">
         <v>603</v>
-      </c>
-      <c r="L196" t="s">
-        <v>604</v>
-      </c>
-      <c r="M196" t="s">
-        <v>605</v>
       </c>
       <c r="N196">
         <v>0</v>
@@ -41405,16 +41483,16 @@
         <v>0</v>
       </c>
       <c r="C197" t="s">
+        <v>604</v>
+      </c>
+      <c r="D197" t="s">
+        <v>605</v>
+      </c>
+      <c r="E197" t="s">
         <v>606</v>
       </c>
-      <c r="D197" t="s">
+      <c r="F197" t="s">
         <v>607</v>
-      </c>
-      <c r="E197" t="s">
-        <v>608</v>
-      </c>
-      <c r="F197" t="s">
-        <v>609</v>
       </c>
       <c r="G197">
         <v>0</v>
@@ -41462,16 +41540,16 @@
         <v>0</v>
       </c>
       <c r="C198" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D198" t="s">
+        <v>608</v>
+      </c>
+      <c r="E198" t="s">
+        <v>609</v>
+      </c>
+      <c r="F198" t="s">
         <v>610</v>
-      </c>
-      <c r="E198" t="s">
-        <v>611</v>
-      </c>
-      <c r="F198" t="s">
-        <v>612</v>
       </c>
       <c r="G198">
         <v>1.35</v>
@@ -41519,16 +41597,16 @@
         <v>0</v>
       </c>
       <c r="C199" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D199" t="s">
+        <v>611</v>
+      </c>
+      <c r="E199" t="s">
+        <v>612</v>
+      </c>
+      <c r="F199" t="s">
         <v>613</v>
-      </c>
-      <c r="E199" t="s">
-        <v>614</v>
-      </c>
-      <c r="F199" t="s">
-        <v>615</v>
       </c>
       <c r="G199">
         <v>0.05</v>
@@ -41576,16 +41654,16 @@
         <v>0</v>
       </c>
       <c r="C200" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D200" t="s">
+        <v>614</v>
+      </c>
+      <c r="E200" t="s">
+        <v>615</v>
+      </c>
+      <c r="F200" t="s">
         <v>616</v>
-      </c>
-      <c r="E200" t="s">
-        <v>617</v>
-      </c>
-      <c r="F200" t="s">
-        <v>618</v>
       </c>
       <c r="G200">
         <v>2</v>
@@ -41633,16 +41711,16 @@
         <v>0</v>
       </c>
       <c r="C201" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D201" t="s">
+        <v>617</v>
+      </c>
+      <c r="E201" t="s">
+        <v>618</v>
+      </c>
+      <c r="F201" t="s">
         <v>619</v>
-      </c>
-      <c r="E201" t="s">
-        <v>620</v>
-      </c>
-      <c r="F201" t="s">
-        <v>621</v>
       </c>
       <c r="G201">
         <v>0</v>
@@ -41690,16 +41768,16 @@
         <v>0</v>
       </c>
       <c r="C202" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D202" t="s">
+        <v>620</v>
+      </c>
+      <c r="E202" t="s">
+        <v>621</v>
+      </c>
+      <c r="F202" t="s">
         <v>622</v>
-      </c>
-      <c r="E202" t="s">
-        <v>623</v>
-      </c>
-      <c r="F202" t="s">
-        <v>624</v>
       </c>
       <c r="G202">
         <v>5</v>
@@ -41747,16 +41825,16 @@
         <v>0</v>
       </c>
       <c r="C203" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D203" t="s">
+        <v>623</v>
+      </c>
+      <c r="E203" t="s">
+        <v>624</v>
+      </c>
+      <c r="F203" t="s">
         <v>625</v>
-      </c>
-      <c r="E203" t="s">
-        <v>626</v>
-      </c>
-      <c r="F203" t="s">
-        <v>627</v>
       </c>
       <c r="G203">
         <v>8</v>
@@ -41804,16 +41882,16 @@
         <v>0</v>
       </c>
       <c r="C204" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D204" t="s">
+        <v>626</v>
+      </c>
+      <c r="E204" t="s">
+        <v>627</v>
+      </c>
+      <c r="F204" t="s">
         <v>628</v>
-      </c>
-      <c r="E204" t="s">
-        <v>629</v>
-      </c>
-      <c r="F204" t="s">
-        <v>630</v>
       </c>
       <c r="G204">
         <v>1</v>
@@ -41861,16 +41939,16 @@
         <v>0</v>
       </c>
       <c r="C205" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D205" t="s">
+        <v>629</v>
+      </c>
+      <c r="E205" t="s">
+        <v>630</v>
+      </c>
+      <c r="F205" t="s">
         <v>631</v>
-      </c>
-      <c r="E205" t="s">
-        <v>632</v>
-      </c>
-      <c r="F205" t="s">
-        <v>633</v>
       </c>
       <c r="G205">
         <v>0.15</v>
@@ -41918,16 +41996,16 @@
         <v>0</v>
       </c>
       <c r="C206" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D206" t="s">
+        <v>632</v>
+      </c>
+      <c r="E206" t="s">
+        <v>633</v>
+      </c>
+      <c r="F206" t="s">
         <v>634</v>
-      </c>
-      <c r="E206" t="s">
-        <v>635</v>
-      </c>
-      <c r="F206" t="s">
-        <v>636</v>
       </c>
       <c r="G206">
         <v>2</v>
@@ -41975,16 +42053,16 @@
         <v>0</v>
       </c>
       <c r="C207" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D207" t="s">
+        <v>635</v>
+      </c>
+      <c r="E207" t="s">
+        <v>636</v>
+      </c>
+      <c r="F207" t="s">
         <v>637</v>
-      </c>
-      <c r="E207" t="s">
-        <v>638</v>
-      </c>
-      <c r="F207" t="s">
-        <v>639</v>
       </c>
       <c r="G207">
         <v>3</v>
@@ -42032,16 +42110,16 @@
         <v>0</v>
       </c>
       <c r="C208" t="s">
+        <v>638</v>
+      </c>
+      <c r="D208" t="s">
+        <v>639</v>
+      </c>
+      <c r="E208" t="s">
         <v>640</v>
       </c>
-      <c r="D208" t="s">
+      <c r="F208" t="s">
         <v>641</v>
-      </c>
-      <c r="E208" t="s">
-        <v>642</v>
-      </c>
-      <c r="F208" t="s">
-        <v>643</v>
       </c>
       <c r="G208">
         <v>5</v>
@@ -42089,16 +42167,16 @@
         <v>0</v>
       </c>
       <c r="C209" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D209" t="s">
+        <v>642</v>
+      </c>
+      <c r="E209" t="s">
+        <v>643</v>
+      </c>
+      <c r="F209" t="s">
         <v>644</v>
-      </c>
-      <c r="E209" t="s">
-        <v>645</v>
-      </c>
-      <c r="F209" t="s">
-        <v>646</v>
       </c>
       <c r="G209">
         <v>0</v>
@@ -42146,16 +42224,16 @@
         <v>0</v>
       </c>
       <c r="C210" t="s">
+        <v>645</v>
+      </c>
+      <c r="D210" t="s">
+        <v>646</v>
+      </c>
+      <c r="E210" t="s">
         <v>647</v>
       </c>
-      <c r="D210" t="s">
+      <c r="F210" t="s">
         <v>648</v>
-      </c>
-      <c r="E210" t="s">
-        <v>649</v>
-      </c>
-      <c r="F210" t="s">
-        <v>650</v>
       </c>
       <c r="G210">
         <v>5</v>
@@ -42203,16 +42281,16 @@
         <v>0</v>
       </c>
       <c r="C211" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D211" t="s">
+        <v>649</v>
+      </c>
+      <c r="E211" t="s">
+        <v>650</v>
+      </c>
+      <c r="F211" t="s">
         <v>651</v>
-      </c>
-      <c r="E211" t="s">
-        <v>652</v>
-      </c>
-      <c r="F211" t="s">
-        <v>653</v>
       </c>
       <c r="G211">
         <v>55</v>
@@ -42260,16 +42338,16 @@
         <v>0</v>
       </c>
       <c r="C212" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D212" t="s">
+        <v>652</v>
+      </c>
+      <c r="E212" t="s">
+        <v>653</v>
+      </c>
+      <c r="F212" t="s">
         <v>654</v>
-      </c>
-      <c r="E212" t="s">
-        <v>655</v>
-      </c>
-      <c r="F212" t="s">
-        <v>656</v>
       </c>
       <c r="G212">
         <v>5000000</v>
@@ -42317,13 +42395,13 @@
         <v>0</v>
       </c>
       <c r="C213" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D213" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E213" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="F213">
         <v>0</v>
@@ -42374,16 +42452,16 @@
         <v>0</v>
       </c>
       <c r="C214" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D214" t="s">
+        <v>656</v>
+      </c>
+      <c r="E214" t="s">
+        <v>657</v>
+      </c>
+      <c r="F214" t="s">
         <v>658</v>
-      </c>
-      <c r="E214" t="s">
-        <v>659</v>
-      </c>
-      <c r="F214" t="s">
-        <v>660</v>
       </c>
       <c r="G214">
         <v>3</v>
@@ -42431,16 +42509,16 @@
         <v>0</v>
       </c>
       <c r="C215" t="s">
+        <v>659</v>
+      </c>
+      <c r="D215" t="s">
+        <v>660</v>
+      </c>
+      <c r="E215" t="s">
         <v>661</v>
       </c>
-      <c r="D215" t="s">
+      <c r="F215" t="s">
         <v>662</v>
-      </c>
-      <c r="E215" t="s">
-        <v>663</v>
-      </c>
-      <c r="F215" t="s">
-        <v>664</v>
       </c>
       <c r="G215">
         <v>27</v>
@@ -42488,16 +42566,16 @@
         <v>0</v>
       </c>
       <c r="C216" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D216" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E216" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="F216" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="G216">
         <v>36</v>
@@ -42545,16 +42623,16 @@
         <v>0</v>
       </c>
       <c r="C217" t="s">
+        <v>645</v>
+      </c>
+      <c r="D217" t="s">
+        <v>665</v>
+      </c>
+      <c r="E217" t="s">
         <v>647</v>
       </c>
-      <c r="D217" t="s">
-        <v>667</v>
-      </c>
-      <c r="E217" t="s">
-        <v>649</v>
-      </c>
       <c r="F217" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="G217">
         <v>3</v>
@@ -42602,16 +42680,16 @@
         <v>0</v>
       </c>
       <c r="C218" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D218" t="s">
+        <v>667</v>
+      </c>
+      <c r="E218" t="s">
+        <v>668</v>
+      </c>
+      <c r="F218" t="s">
         <v>669</v>
-      </c>
-      <c r="E218" t="s">
-        <v>670</v>
-      </c>
-      <c r="F218" t="s">
-        <v>671</v>
       </c>
       <c r="G218">
         <v>50</v>
@@ -42659,16 +42737,16 @@
         <v>0</v>
       </c>
       <c r="C219" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D219" t="s">
+        <v>670</v>
+      </c>
+      <c r="E219" t="s">
+        <v>671</v>
+      </c>
+      <c r="F219" t="s">
         <v>672</v>
-      </c>
-      <c r="E219" t="s">
-        <v>673</v>
-      </c>
-      <c r="F219" t="s">
-        <v>674</v>
       </c>
       <c r="G219">
         <v>1000000</v>
@@ -42716,13 +42794,13 @@
         <v>0</v>
       </c>
       <c r="C220" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D220" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E220" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F220">
         <v>0</v>
@@ -42773,16 +42851,16 @@
         <v>0</v>
       </c>
       <c r="C221" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D221" t="s">
+        <v>675</v>
+      </c>
+      <c r="E221" t="s">
+        <v>676</v>
+      </c>
+      <c r="F221" t="s">
         <v>677</v>
-      </c>
-      <c r="E221" t="s">
-        <v>678</v>
-      </c>
-      <c r="F221" t="s">
-        <v>679</v>
       </c>
       <c r="G221">
         <v>3</v>
@@ -42830,16 +42908,16 @@
         <v>0</v>
       </c>
       <c r="C222" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D222" t="s">
+        <v>678</v>
+      </c>
+      <c r="E222" t="s">
+        <v>679</v>
+      </c>
+      <c r="F222" t="s">
         <v>680</v>
-      </c>
-      <c r="E222" t="s">
-        <v>681</v>
-      </c>
-      <c r="F222" t="s">
-        <v>682</v>
       </c>
       <c r="G222">
         <v>6</v>
@@ -42887,16 +42965,16 @@
         <v>0</v>
       </c>
       <c r="C223" t="s">
+        <v>681</v>
+      </c>
+      <c r="D223" t="s">
+        <v>682</v>
+      </c>
+      <c r="E223" t="s">
         <v>683</v>
       </c>
-      <c r="D223" t="s">
+      <c r="F223" t="s">
         <v>684</v>
-      </c>
-      <c r="E223" t="s">
-        <v>685</v>
-      </c>
-      <c r="F223" t="s">
-        <v>686</v>
       </c>
       <c r="G223">
         <v>30</v>
@@ -42944,13 +43022,13 @@
         <v>0</v>
       </c>
       <c r="C224" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D224" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E224" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="F224">
         <v>0</v>
@@ -43001,13 +43079,13 @@
         <v>0</v>
       </c>
       <c r="C225" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D225" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E225" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="F225">
         <v>0</v>
@@ -43058,16 +43136,16 @@
         <v>0</v>
       </c>
       <c r="C226" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D226" t="s">
+        <v>688</v>
+      </c>
+      <c r="E226" t="s">
+        <v>689</v>
+      </c>
+      <c r="F226" t="s">
         <v>690</v>
-      </c>
-      <c r="E226" t="s">
-        <v>691</v>
-      </c>
-      <c r="F226" t="s">
-        <v>692</v>
       </c>
       <c r="G226">
         <v>0</v>
@@ -43115,13 +43193,13 @@
         <v>0</v>
       </c>
       <c r="C227" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D227" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E227" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="F227">
         <v>0</v>
@@ -43172,16 +43250,16 @@
         <v>0</v>
       </c>
       <c r="C228" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D228" t="s">
+        <v>692</v>
+      </c>
+      <c r="E228" t="s">
+        <v>693</v>
+      </c>
+      <c r="F228" t="s">
         <v>694</v>
-      </c>
-      <c r="E228" t="s">
-        <v>695</v>
-      </c>
-      <c r="F228" t="s">
-        <v>696</v>
       </c>
       <c r="G228">
         <v>9</v>
@@ -43229,16 +43307,16 @@
         <v>0</v>
       </c>
       <c r="C229" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D229" t="s">
+        <v>695</v>
+      </c>
+      <c r="E229" t="s">
+        <v>696</v>
+      </c>
+      <c r="F229" t="s">
         <v>697</v>
-      </c>
-      <c r="E229" t="s">
-        <v>698</v>
-      </c>
-      <c r="F229" t="s">
-        <v>699</v>
       </c>
       <c r="G229">
         <v>1</v>
@@ -43286,16 +43364,16 @@
         <v>0</v>
       </c>
       <c r="C230" t="s">
+        <v>698</v>
+      </c>
+      <c r="D230" t="s">
+        <v>699</v>
+      </c>
+      <c r="E230" t="s">
         <v>700</v>
       </c>
-      <c r="D230" t="s">
+      <c r="F230" t="s">
         <v>701</v>
-      </c>
-      <c r="E230" t="s">
-        <v>702</v>
-      </c>
-      <c r="F230" t="s">
-        <v>703</v>
       </c>
       <c r="G230">
         <v>5</v>
@@ -43343,16 +43421,16 @@
         <v>0</v>
       </c>
       <c r="C231" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D231" t="s">
+        <v>702</v>
+      </c>
+      <c r="E231" t="s">
+        <v>703</v>
+      </c>
+      <c r="F231" t="s">
         <v>704</v>
-      </c>
-      <c r="E231" t="s">
-        <v>705</v>
-      </c>
-      <c r="F231" t="s">
-        <v>706</v>
       </c>
       <c r="G231">
         <v>0</v>
@@ -43400,16 +43478,16 @@
         <v>0</v>
       </c>
       <c r="C232" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D232" t="s">
+        <v>705</v>
+      </c>
+      <c r="E232" t="s">
+        <v>706</v>
+      </c>
+      <c r="F232" t="s">
         <v>707</v>
-      </c>
-      <c r="E232" t="s">
-        <v>708</v>
-      </c>
-      <c r="F232" t="s">
-        <v>709</v>
       </c>
       <c r="G232">
         <v>0</v>
@@ -43457,16 +43535,16 @@
         <v>0</v>
       </c>
       <c r="C233" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D233" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E233" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="F233" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G233">
         <v>0</v>
@@ -43514,16 +43592,16 @@
         <v>0</v>
       </c>
       <c r="C234" t="s">
+        <v>710</v>
+      </c>
+      <c r="D234" t="s">
+        <v>711</v>
+      </c>
+      <c r="E234" t="s">
         <v>712</v>
       </c>
-      <c r="D234" t="s">
+      <c r="F234" t="s">
         <v>713</v>
-      </c>
-      <c r="E234" t="s">
-        <v>714</v>
-      </c>
-      <c r="F234" t="s">
-        <v>715</v>
       </c>
       <c r="G234">
         <v>2</v>
@@ -43571,16 +43649,16 @@
         <v>0</v>
       </c>
       <c r="C235" t="s">
+        <v>714</v>
+      </c>
+      <c r="D235" t="s">
+        <v>715</v>
+      </c>
+      <c r="E235" t="s">
         <v>716</v>
       </c>
-      <c r="D235" t="s">
+      <c r="F235" t="s">
         <v>717</v>
-      </c>
-      <c r="E235" t="s">
-        <v>718</v>
-      </c>
-      <c r="F235" t="s">
-        <v>719</v>
       </c>
       <c r="G235">
         <v>10000</v>
@@ -43628,16 +43706,16 @@
         <v>0</v>
       </c>
       <c r="C236" t="s">
+        <v>718</v>
+      </c>
+      <c r="D236" t="s">
+        <v>719</v>
+      </c>
+      <c r="E236" t="s">
         <v>720</v>
       </c>
-      <c r="D236" t="s">
+      <c r="F236" t="s">
         <v>721</v>
-      </c>
-      <c r="E236" t="s">
-        <v>722</v>
-      </c>
-      <c r="F236" t="s">
-        <v>723</v>
       </c>
       <c r="G236">
         <v>20000</v>
@@ -43685,13 +43763,13 @@
         <v>0</v>
       </c>
       <c r="C237" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D237" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="E237" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="F237">
         <v>0</v>
@@ -43742,16 +43820,16 @@
         <v>0</v>
       </c>
       <c r="C238" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D238" t="s">
+        <v>724</v>
+      </c>
+      <c r="E238" t="s">
+        <v>725</v>
+      </c>
+      <c r="F238" t="s">
         <v>726</v>
-      </c>
-      <c r="E238" t="s">
-        <v>727</v>
-      </c>
-      <c r="F238" t="s">
-        <v>728</v>
       </c>
       <c r="G238">
         <v>100</v>
@@ -43799,16 +43877,16 @@
         <v>0</v>
       </c>
       <c r="C239" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D239" t="s">
+        <v>727</v>
+      </c>
+      <c r="E239" t="s">
+        <v>728</v>
+      </c>
+      <c r="F239" t="s">
         <v>729</v>
-      </c>
-      <c r="E239" t="s">
-        <v>730</v>
-      </c>
-      <c r="F239" t="s">
-        <v>731</v>
       </c>
       <c r="G239">
         <v>10000</v>
@@ -43856,13 +43934,13 @@
         <v>0</v>
       </c>
       <c r="C240" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D240" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="E240" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="F240">
         <v>0</v>
@@ -43913,16 +43991,16 @@
         <v>0</v>
       </c>
       <c r="C241" t="s">
+        <v>732</v>
+      </c>
+      <c r="D241" t="s">
+        <v>733</v>
+      </c>
+      <c r="E241" t="s">
         <v>734</v>
       </c>
-      <c r="D241" t="s">
+      <c r="F241" t="s">
         <v>735</v>
-      </c>
-      <c r="E241" t="s">
-        <v>736</v>
-      </c>
-      <c r="F241" t="s">
-        <v>737</v>
       </c>
       <c r="G241">
         <v>0.2</v>
@@ -43970,16 +44048,16 @@
         <v>0</v>
       </c>
       <c r="C242" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D242" t="s">
+        <v>736</v>
+      </c>
+      <c r="E242" t="s">
+        <v>737</v>
+      </c>
+      <c r="F242" t="s">
         <v>738</v>
-      </c>
-      <c r="E242" t="s">
-        <v>739</v>
-      </c>
-      <c r="F242" t="s">
-        <v>740</v>
       </c>
       <c r="G242">
         <v>2</v>
@@ -44027,16 +44105,16 @@
         <v>0</v>
       </c>
       <c r="C243" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D243" t="s">
+        <v>739</v>
+      </c>
+      <c r="E243" t="s">
+        <v>740</v>
+      </c>
+      <c r="F243" t="s">
         <v>741</v>
-      </c>
-      <c r="E243" t="s">
-        <v>742</v>
-      </c>
-      <c r="F243" t="s">
-        <v>743</v>
       </c>
       <c r="G243">
         <v>3</v>
@@ -44084,16 +44162,16 @@
         <v>0</v>
       </c>
       <c r="C244" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D244" t="s">
+        <v>742</v>
+      </c>
+      <c r="E244" t="s">
+        <v>743</v>
+      </c>
+      <c r="F244" t="s">
         <v>744</v>
-      </c>
-      <c r="E244" t="s">
-        <v>745</v>
-      </c>
-      <c r="F244" t="s">
-        <v>746</v>
       </c>
       <c r="G244">
         <v>3</v>
@@ -44141,16 +44219,16 @@
         <v>0</v>
       </c>
       <c r="C245" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D245" t="s">
+        <v>745</v>
+      </c>
+      <c r="E245" t="s">
+        <v>746</v>
+      </c>
+      <c r="F245" t="s">
         <v>747</v>
-      </c>
-      <c r="E245" t="s">
-        <v>748</v>
-      </c>
-      <c r="F245" t="s">
-        <v>749</v>
       </c>
       <c r="G245">
         <v>100</v>
@@ -44198,16 +44276,16 @@
         <v>0</v>
       </c>
       <c r="C246" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D246" t="s">
+        <v>748</v>
+      </c>
+      <c r="E246" t="s">
+        <v>749</v>
+      </c>
+      <c r="F246" t="s">
         <v>750</v>
-      </c>
-      <c r="E246" t="s">
-        <v>751</v>
-      </c>
-      <c r="F246" t="s">
-        <v>752</v>
       </c>
       <c r="G246">
         <v>9</v>
@@ -44255,16 +44333,16 @@
         <v>0</v>
       </c>
       <c r="C247" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D247" t="s">
+        <v>751</v>
+      </c>
+      <c r="E247" t="s">
+        <v>752</v>
+      </c>
+      <c r="F247" t="s">
         <v>753</v>
-      </c>
-      <c r="E247" t="s">
-        <v>754</v>
-      </c>
-      <c r="F247" t="s">
-        <v>755</v>
       </c>
       <c r="G247">
         <v>0.7</v>
@@ -44312,16 +44390,16 @@
         <v>0</v>
       </c>
       <c r="C248" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D248" t="s">
+        <v>754</v>
+      </c>
+      <c r="E248" t="s">
+        <v>755</v>
+      </c>
+      <c r="F248" t="s">
         <v>756</v>
-      </c>
-      <c r="E248" t="s">
-        <v>757</v>
-      </c>
-      <c r="F248" t="s">
-        <v>758</v>
       </c>
       <c r="G248">
         <v>0.7</v>
@@ -44369,16 +44447,16 @@
         <v>0</v>
       </c>
       <c r="C249" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D249" t="s">
+        <v>757</v>
+      </c>
+      <c r="E249" t="s">
+        <v>758</v>
+      </c>
+      <c r="F249" t="s">
         <v>759</v>
-      </c>
-      <c r="E249" t="s">
-        <v>760</v>
-      </c>
-      <c r="F249" t="s">
-        <v>761</v>
       </c>
       <c r="G249">
         <v>10</v>
@@ -44426,16 +44504,16 @@
         <v>0</v>
       </c>
       <c r="C250" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D250" t="s">
+        <v>760</v>
+      </c>
+      <c r="E250" t="s">
+        <v>761</v>
+      </c>
+      <c r="F250" t="s">
         <v>762</v>
-      </c>
-      <c r="E250" t="s">
-        <v>763</v>
-      </c>
-      <c r="F250" t="s">
-        <v>764</v>
       </c>
       <c r="G250">
         <v>0</v>
@@ -44483,16 +44561,16 @@
         <v>0</v>
       </c>
       <c r="C251" t="s">
+        <v>763</v>
+      </c>
+      <c r="D251" t="s">
+        <v>764</v>
+      </c>
+      <c r="E251" t="s">
         <v>765</v>
       </c>
-      <c r="D251" t="s">
+      <c r="F251" t="s">
         <v>766</v>
-      </c>
-      <c r="E251" t="s">
-        <v>767</v>
-      </c>
-      <c r="F251" t="s">
-        <v>768</v>
       </c>
       <c r="G251">
         <v>10000</v>
@@ -44540,16 +44618,16 @@
         <v>0</v>
       </c>
       <c r="C252" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D252" t="s">
+        <v>767</v>
+      </c>
+      <c r="E252" t="s">
+        <v>768</v>
+      </c>
+      <c r="F252" t="s">
         <v>769</v>
-      </c>
-      <c r="E252" t="s">
-        <v>770</v>
-      </c>
-      <c r="F252" t="s">
-        <v>771</v>
       </c>
       <c r="G252">
         <v>5000</v>
@@ -44597,13 +44675,13 @@
         <v>0</v>
       </c>
       <c r="C253" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D253" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E253" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="F253">
         <v>0</v>
@@ -44654,16 +44732,16 @@
         <v>0</v>
       </c>
       <c r="C254" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D254" t="s">
+        <v>772</v>
+      </c>
+      <c r="E254" t="s">
+        <v>773</v>
+      </c>
+      <c r="F254" t="s">
         <v>774</v>
-      </c>
-      <c r="E254" t="s">
-        <v>775</v>
-      </c>
-      <c r="F254" t="s">
-        <v>776</v>
       </c>
       <c r="G254">
         <v>10000</v>
@@ -44711,22 +44789,22 @@
         <v>0</v>
       </c>
       <c r="C255" t="s">
+        <v>775</v>
+      </c>
+      <c r="D255" t="s">
+        <v>776</v>
+      </c>
+      <c r="E255" t="s">
         <v>777</v>
       </c>
-      <c r="D255" t="s">
+      <c r="F255" t="s">
         <v>778</v>
       </c>
-      <c r="E255" t="s">
+      <c r="G255" t="s">
         <v>779</v>
       </c>
-      <c r="F255" t="s">
+      <c r="H255" t="s">
         <v>780</v>
-      </c>
-      <c r="G255" t="s">
-        <v>781</v>
-      </c>
-      <c r="H255" t="s">
-        <v>782</v>
       </c>
       <c r="I255">
         <v>0</v>
@@ -44768,25 +44846,25 @@
         <v>0</v>
       </c>
       <c r="C256" t="s">
+        <v>775</v>
+      </c>
+      <c r="D256" t="s">
+        <v>781</v>
+      </c>
+      <c r="E256" t="s">
         <v>777</v>
       </c>
-      <c r="D256" t="s">
+      <c r="F256" t="s">
+        <v>778</v>
+      </c>
+      <c r="G256" t="s">
+        <v>779</v>
+      </c>
+      <c r="H256" t="s">
+        <v>782</v>
+      </c>
+      <c r="I256" t="s">
         <v>783</v>
-      </c>
-      <c r="E256" t="s">
-        <v>779</v>
-      </c>
-      <c r="F256" t="s">
-        <v>780</v>
-      </c>
-      <c r="G256" t="s">
-        <v>781</v>
-      </c>
-      <c r="H256" t="s">
-        <v>784</v>
-      </c>
-      <c r="I256" t="s">
-        <v>785</v>
       </c>
       <c r="J256">
         <v>0</v>
@@ -44825,28 +44903,28 @@
         <v>0</v>
       </c>
       <c r="C257" t="s">
+        <v>775</v>
+      </c>
+      <c r="D257" t="s">
+        <v>784</v>
+      </c>
+      <c r="E257" t="s">
         <v>777</v>
       </c>
-      <c r="D257" t="s">
+      <c r="F257" t="s">
+        <v>778</v>
+      </c>
+      <c r="G257" t="s">
+        <v>779</v>
+      </c>
+      <c r="H257" t="s">
+        <v>785</v>
+      </c>
+      <c r="I257" t="s">
+        <v>783</v>
+      </c>
+      <c r="J257" t="s">
         <v>786</v>
-      </c>
-      <c r="E257" t="s">
-        <v>779</v>
-      </c>
-      <c r="F257" t="s">
-        <v>780</v>
-      </c>
-      <c r="G257" t="s">
-        <v>781</v>
-      </c>
-      <c r="H257" t="s">
-        <v>787</v>
-      </c>
-      <c r="I257" t="s">
-        <v>785</v>
-      </c>
-      <c r="J257" t="s">
-        <v>788</v>
       </c>
       <c r="K257">
         <v>0</v>
@@ -44882,28 +44960,28 @@
         <v>0</v>
       </c>
       <c r="C258" t="s">
+        <v>775</v>
+      </c>
+      <c r="D258" t="s">
+        <v>787</v>
+      </c>
+      <c r="E258" t="s">
         <v>777</v>
       </c>
-      <c r="D258" t="s">
+      <c r="F258" t="s">
+        <v>778</v>
+      </c>
+      <c r="G258" t="s">
+        <v>788</v>
+      </c>
+      <c r="H258" t="s">
+        <v>785</v>
+      </c>
+      <c r="I258" t="s">
         <v>789</v>
       </c>
-      <c r="E258" t="s">
-        <v>779</v>
-      </c>
-      <c r="F258" t="s">
-        <v>780</v>
-      </c>
-      <c r="G258" t="s">
-        <v>790</v>
-      </c>
-      <c r="H258" t="s">
-        <v>787</v>
-      </c>
-      <c r="I258" t="s">
-        <v>791</v>
-      </c>
       <c r="J258" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="K258">
         <v>0</v>
@@ -44939,28 +45017,28 @@
         <v>0</v>
       </c>
       <c r="C259" t="s">
+        <v>775</v>
+      </c>
+      <c r="D259" t="s">
+        <v>790</v>
+      </c>
+      <c r="E259" t="s">
         <v>777</v>
       </c>
-      <c r="D259" t="s">
+      <c r="F259" t="s">
+        <v>778</v>
+      </c>
+      <c r="G259" t="s">
+        <v>791</v>
+      </c>
+      <c r="H259" t="s">
+        <v>785</v>
+      </c>
+      <c r="I259" t="s">
+        <v>789</v>
+      </c>
+      <c r="J259" t="s">
         <v>792</v>
-      </c>
-      <c r="E259" t="s">
-        <v>779</v>
-      </c>
-      <c r="F259" t="s">
-        <v>780</v>
-      </c>
-      <c r="G259" t="s">
-        <v>793</v>
-      </c>
-      <c r="H259" t="s">
-        <v>787</v>
-      </c>
-      <c r="I259" t="s">
-        <v>791</v>
-      </c>
-      <c r="J259" t="s">
-        <v>794</v>
       </c>
       <c r="K259">
         <v>0</v>
@@ -44996,31 +45074,31 @@
         <v>0</v>
       </c>
       <c r="C260" t="s">
+        <v>775</v>
+      </c>
+      <c r="D260" t="s">
+        <v>793</v>
+      </c>
+      <c r="E260" t="s">
         <v>777</v>
       </c>
-      <c r="D260" t="s">
+      <c r="F260" t="s">
+        <v>778</v>
+      </c>
+      <c r="G260" t="s">
+        <v>794</v>
+      </c>
+      <c r="H260" t="s">
+        <v>785</v>
+      </c>
+      <c r="I260" t="s">
+        <v>789</v>
+      </c>
+      <c r="J260" t="s">
+        <v>792</v>
+      </c>
+      <c r="K260" t="s">
         <v>795</v>
-      </c>
-      <c r="E260" t="s">
-        <v>779</v>
-      </c>
-      <c r="F260" t="s">
-        <v>780</v>
-      </c>
-      <c r="G260" t="s">
-        <v>796</v>
-      </c>
-      <c r="H260" t="s">
-        <v>787</v>
-      </c>
-      <c r="I260" t="s">
-        <v>791</v>
-      </c>
-      <c r="J260" t="s">
-        <v>794</v>
-      </c>
-      <c r="K260" t="s">
-        <v>797</v>
       </c>
       <c r="L260">
         <v>0</v>
@@ -45053,31 +45131,31 @@
         <v>0</v>
       </c>
       <c r="C261" t="s">
+        <v>775</v>
+      </c>
+      <c r="D261" t="s">
+        <v>796</v>
+      </c>
+      <c r="E261" t="s">
         <v>777</v>
       </c>
-      <c r="D261" t="s">
+      <c r="F261" t="s">
+        <v>778</v>
+      </c>
+      <c r="G261" t="s">
+        <v>797</v>
+      </c>
+      <c r="H261" t="s">
         <v>798</v>
       </c>
-      <c r="E261" t="s">
-        <v>779</v>
-      </c>
-      <c r="F261" t="s">
-        <v>780</v>
-      </c>
-      <c r="G261" t="s">
+      <c r="I261" t="s">
+        <v>792</v>
+      </c>
+      <c r="J261" t="s">
         <v>799</v>
       </c>
-      <c r="H261" t="s">
+      <c r="K261" t="s">
         <v>800</v>
-      </c>
-      <c r="I261" t="s">
-        <v>794</v>
-      </c>
-      <c r="J261" t="s">
-        <v>801</v>
-      </c>
-      <c r="K261" t="s">
-        <v>802</v>
       </c>
       <c r="L261">
         <v>0</v>
@@ -45110,31 +45188,31 @@
         <v>0</v>
       </c>
       <c r="C262" t="s">
+        <v>775</v>
+      </c>
+      <c r="D262" t="s">
+        <v>801</v>
+      </c>
+      <c r="E262" t="s">
         <v>777</v>
       </c>
-      <c r="D262" t="s">
-        <v>803</v>
-      </c>
-      <c r="E262" t="s">
-        <v>779</v>
-      </c>
       <c r="F262" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="G262" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="H262" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="I262" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="J262" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="K262" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="L262">
         <v>0</v>
@@ -45167,31 +45245,31 @@
         <v>0</v>
       </c>
       <c r="C263" t="s">
+        <v>775</v>
+      </c>
+      <c r="D263" t="s">
+        <v>803</v>
+      </c>
+      <c r="E263" t="s">
         <v>777</v>
       </c>
-      <c r="D263" t="s">
+      <c r="F263" t="s">
+        <v>778</v>
+      </c>
+      <c r="G263" t="s">
+        <v>798</v>
+      </c>
+      <c r="H263" t="s">
+        <v>804</v>
+      </c>
+      <c r="I263" t="s">
+        <v>799</v>
+      </c>
+      <c r="J263" t="s">
         <v>805</v>
       </c>
-      <c r="E263" t="s">
-        <v>779</v>
-      </c>
-      <c r="F263" t="s">
-        <v>780</v>
-      </c>
-      <c r="G263" t="s">
-        <v>800</v>
-      </c>
-      <c r="H263" t="s">
+      <c r="K263" t="s">
         <v>806</v>
-      </c>
-      <c r="I263" t="s">
-        <v>801</v>
-      </c>
-      <c r="J263" t="s">
-        <v>807</v>
-      </c>
-      <c r="K263" t="s">
-        <v>808</v>
       </c>
       <c r="L263">
         <v>0</v>
@@ -45224,31 +45302,31 @@
         <v>0</v>
       </c>
       <c r="C264" t="s">
+        <v>775</v>
+      </c>
+      <c r="D264" t="s">
+        <v>807</v>
+      </c>
+      <c r="E264" t="s">
         <v>777</v>
       </c>
-      <c r="D264" t="s">
+      <c r="F264" t="s">
+        <v>778</v>
+      </c>
+      <c r="G264" t="s">
+        <v>804</v>
+      </c>
+      <c r="H264" t="s">
+        <v>808</v>
+      </c>
+      <c r="I264" t="s">
+        <v>805</v>
+      </c>
+      <c r="J264" t="s">
         <v>809</v>
       </c>
-      <c r="E264" t="s">
-        <v>779</v>
-      </c>
-      <c r="F264" t="s">
-        <v>780</v>
-      </c>
-      <c r="G264" t="s">
-        <v>806</v>
-      </c>
-      <c r="H264" t="s">
+      <c r="K264" t="s">
         <v>810</v>
-      </c>
-      <c r="I264" t="s">
-        <v>807</v>
-      </c>
-      <c r="J264" t="s">
-        <v>811</v>
-      </c>
-      <c r="K264" t="s">
-        <v>812</v>
       </c>
       <c r="L264">
         <v>0</v>
@@ -45281,31 +45359,31 @@
         <v>0</v>
       </c>
       <c r="C265" t="s">
+        <v>775</v>
+      </c>
+      <c r="D265" t="s">
+        <v>811</v>
+      </c>
+      <c r="E265" t="s">
         <v>777</v>
       </c>
-      <c r="D265" t="s">
+      <c r="F265" t="s">
+        <v>778</v>
+      </c>
+      <c r="G265" t="s">
+        <v>808</v>
+      </c>
+      <c r="H265" t="s">
+        <v>812</v>
+      </c>
+      <c r="I265" t="s">
+        <v>809</v>
+      </c>
+      <c r="J265" t="s">
         <v>813</v>
       </c>
-      <c r="E265" t="s">
-        <v>779</v>
-      </c>
-      <c r="F265" t="s">
-        <v>780</v>
-      </c>
-      <c r="G265" t="s">
-        <v>810</v>
-      </c>
-      <c r="H265" t="s">
+      <c r="K265" t="s">
         <v>814</v>
-      </c>
-      <c r="I265" t="s">
-        <v>811</v>
-      </c>
-      <c r="J265" t="s">
-        <v>815</v>
-      </c>
-      <c r="K265" t="s">
-        <v>816</v>
       </c>
       <c r="L265">
         <v>0</v>
@@ -45338,31 +45416,31 @@
         <v>0</v>
       </c>
       <c r="C266" t="s">
+        <v>775</v>
+      </c>
+      <c r="D266" t="s">
+        <v>815</v>
+      </c>
+      <c r="E266" t="s">
         <v>777</v>
       </c>
-      <c r="D266" t="s">
+      <c r="F266" t="s">
+        <v>778</v>
+      </c>
+      <c r="G266" t="s">
+        <v>812</v>
+      </c>
+      <c r="H266" t="s">
+        <v>816</v>
+      </c>
+      <c r="I266" t="s">
+        <v>813</v>
+      </c>
+      <c r="J266" t="s">
         <v>817</v>
       </c>
-      <c r="E266" t="s">
-        <v>779</v>
-      </c>
-      <c r="F266" t="s">
-        <v>780</v>
-      </c>
-      <c r="G266" t="s">
-        <v>814</v>
-      </c>
-      <c r="H266" t="s">
+      <c r="K266" t="s">
         <v>818</v>
-      </c>
-      <c r="I266" t="s">
-        <v>815</v>
-      </c>
-      <c r="J266" t="s">
-        <v>819</v>
-      </c>
-      <c r="K266" t="s">
-        <v>820</v>
       </c>
       <c r="L266">
         <v>0</v>
@@ -45395,31 +45473,31 @@
         <v>0</v>
       </c>
       <c r="C267" t="s">
+        <v>775</v>
+      </c>
+      <c r="D267" t="s">
+        <v>819</v>
+      </c>
+      <c r="E267" t="s">
         <v>777</v>
       </c>
-      <c r="D267" t="s">
+      <c r="F267" t="s">
+        <v>778</v>
+      </c>
+      <c r="G267" t="s">
+        <v>816</v>
+      </c>
+      <c r="H267" t="s">
+        <v>820</v>
+      </c>
+      <c r="I267" t="s">
+        <v>817</v>
+      </c>
+      <c r="J267" t="s">
         <v>821</v>
       </c>
-      <c r="E267" t="s">
-        <v>779</v>
-      </c>
-      <c r="F267" t="s">
-        <v>780</v>
-      </c>
-      <c r="G267" t="s">
-        <v>818</v>
-      </c>
-      <c r="H267" t="s">
+      <c r="K267" t="s">
         <v>822</v>
-      </c>
-      <c r="I267" t="s">
-        <v>819</v>
-      </c>
-      <c r="J267" t="s">
-        <v>823</v>
-      </c>
-      <c r="K267" t="s">
-        <v>824</v>
       </c>
       <c r="L267">
         <v>0</v>
@@ -45452,31 +45530,31 @@
         <v>0</v>
       </c>
       <c r="C268" t="s">
+        <v>775</v>
+      </c>
+      <c r="D268" t="s">
+        <v>823</v>
+      </c>
+      <c r="E268" t="s">
         <v>777</v>
       </c>
-      <c r="D268" t="s">
+      <c r="F268" t="s">
+        <v>778</v>
+      </c>
+      <c r="G268" t="s">
+        <v>820</v>
+      </c>
+      <c r="H268" t="s">
+        <v>824</v>
+      </c>
+      <c r="I268" t="s">
+        <v>821</v>
+      </c>
+      <c r="J268" t="s">
         <v>825</v>
       </c>
-      <c r="E268" t="s">
-        <v>779</v>
-      </c>
-      <c r="F268" t="s">
-        <v>780</v>
-      </c>
-      <c r="G268" t="s">
-        <v>822</v>
-      </c>
-      <c r="H268" t="s">
+      <c r="K268" t="s">
         <v>826</v>
-      </c>
-      <c r="I268" t="s">
-        <v>823</v>
-      </c>
-      <c r="J268" t="s">
-        <v>827</v>
-      </c>
-      <c r="K268" t="s">
-        <v>828</v>
       </c>
       <c r="L268">
         <v>0</v>
@@ -45509,31 +45587,31 @@
         <v>0</v>
       </c>
       <c r="C269" t="s">
+        <v>775</v>
+      </c>
+      <c r="D269" t="s">
+        <v>827</v>
+      </c>
+      <c r="E269" t="s">
         <v>777</v>
       </c>
-      <c r="D269" t="s">
+      <c r="F269" t="s">
+        <v>778</v>
+      </c>
+      <c r="G269" t="s">
+        <v>824</v>
+      </c>
+      <c r="H269" t="s">
+        <v>828</v>
+      </c>
+      <c r="I269" t="s">
+        <v>825</v>
+      </c>
+      <c r="J269" t="s">
         <v>829</v>
       </c>
-      <c r="E269" t="s">
-        <v>779</v>
-      </c>
-      <c r="F269" t="s">
-        <v>780</v>
-      </c>
-      <c r="G269" t="s">
-        <v>826</v>
-      </c>
-      <c r="H269" t="s">
+      <c r="K269" t="s">
         <v>830</v>
-      </c>
-      <c r="I269" t="s">
-        <v>827</v>
-      </c>
-      <c r="J269" t="s">
-        <v>831</v>
-      </c>
-      <c r="K269" t="s">
-        <v>832</v>
       </c>
       <c r="L269">
         <v>0</v>
@@ -45566,31 +45644,31 @@
         <v>0</v>
       </c>
       <c r="C270" t="s">
+        <v>775</v>
+      </c>
+      <c r="D270" t="s">
+        <v>831</v>
+      </c>
+      <c r="E270" t="s">
         <v>777</v>
       </c>
-      <c r="D270" t="s">
+      <c r="F270" t="s">
+        <v>778</v>
+      </c>
+      <c r="G270" t="s">
+        <v>828</v>
+      </c>
+      <c r="H270" t="s">
+        <v>832</v>
+      </c>
+      <c r="I270" t="s">
+        <v>829</v>
+      </c>
+      <c r="J270" t="s">
         <v>833</v>
       </c>
-      <c r="E270" t="s">
-        <v>779</v>
-      </c>
-      <c r="F270" t="s">
-        <v>780</v>
-      </c>
-      <c r="G270" t="s">
-        <v>830</v>
-      </c>
-      <c r="H270" t="s">
+      <c r="K270" t="s">
         <v>834</v>
-      </c>
-      <c r="I270" t="s">
-        <v>831</v>
-      </c>
-      <c r="J270" t="s">
-        <v>835</v>
-      </c>
-      <c r="K270" t="s">
-        <v>836</v>
       </c>
       <c r="L270">
         <v>0</v>
@@ -45623,31 +45701,31 @@
         <v>0</v>
       </c>
       <c r="C271" t="s">
+        <v>775</v>
+      </c>
+      <c r="D271" t="s">
+        <v>835</v>
+      </c>
+      <c r="E271" t="s">
         <v>777</v>
       </c>
-      <c r="D271" t="s">
+      <c r="F271" t="s">
+        <v>778</v>
+      </c>
+      <c r="G271" t="s">
+        <v>832</v>
+      </c>
+      <c r="H271" t="s">
+        <v>836</v>
+      </c>
+      <c r="I271" t="s">
+        <v>833</v>
+      </c>
+      <c r="J271" t="s">
         <v>837</v>
       </c>
-      <c r="E271" t="s">
-        <v>779</v>
-      </c>
-      <c r="F271" t="s">
-        <v>780</v>
-      </c>
-      <c r="G271" t="s">
-        <v>834</v>
-      </c>
-      <c r="H271" t="s">
+      <c r="K271" t="s">
         <v>838</v>
-      </c>
-      <c r="I271" t="s">
-        <v>835</v>
-      </c>
-      <c r="J271" t="s">
-        <v>839</v>
-      </c>
-      <c r="K271" t="s">
-        <v>840</v>
       </c>
       <c r="L271">
         <v>0</v>
@@ -45680,34 +45758,34 @@
         <v>0</v>
       </c>
       <c r="C272" t="s">
+        <v>775</v>
+      </c>
+      <c r="D272" t="s">
+        <v>839</v>
+      </c>
+      <c r="E272" t="s">
         <v>777</v>
       </c>
-      <c r="D272" t="s">
+      <c r="F272" t="s">
+        <v>778</v>
+      </c>
+      <c r="G272" t="s">
+        <v>822</v>
+      </c>
+      <c r="H272" t="s">
+        <v>840</v>
+      </c>
+      <c r="I272" t="s">
         <v>841</v>
       </c>
-      <c r="E272" t="s">
-        <v>779</v>
-      </c>
-      <c r="F272" t="s">
-        <v>780</v>
-      </c>
-      <c r="G272" t="s">
-        <v>824</v>
-      </c>
-      <c r="H272" t="s">
+      <c r="J272" t="s">
+        <v>837</v>
+      </c>
+      <c r="K272" t="s">
         <v>842</v>
       </c>
-      <c r="I272" t="s">
+      <c r="L272" t="s">
         <v>843</v>
-      </c>
-      <c r="J272" t="s">
-        <v>839</v>
-      </c>
-      <c r="K272" t="s">
-        <v>844</v>
-      </c>
-      <c r="L272" t="s">
-        <v>845</v>
       </c>
       <c r="M272">
         <v>0</v>
@@ -45737,34 +45815,34 @@
         <v>0</v>
       </c>
       <c r="C273" t="s">
+        <v>775</v>
+      </c>
+      <c r="D273" t="s">
+        <v>844</v>
+      </c>
+      <c r="E273" t="s">
         <v>777</v>
       </c>
-      <c r="D273" t="s">
-        <v>846</v>
-      </c>
-      <c r="E273" t="s">
-        <v>779</v>
-      </c>
       <c r="F273" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="G273" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="H273" t="s">
+        <v>840</v>
+      </c>
+      <c r="I273" t="s">
+        <v>841</v>
+      </c>
+      <c r="J273" t="s">
+        <v>837</v>
+      </c>
+      <c r="K273" t="s">
         <v>842</v>
       </c>
-      <c r="I273" t="s">
+      <c r="L273" t="s">
         <v>843</v>
-      </c>
-      <c r="J273" t="s">
-        <v>839</v>
-      </c>
-      <c r="K273" t="s">
-        <v>844</v>
-      </c>
-      <c r="L273" t="s">
-        <v>845</v>
       </c>
       <c r="M273">
         <v>0</v>
@@ -45794,34 +45872,34 @@
         <v>0</v>
       </c>
       <c r="C274" t="s">
+        <v>775</v>
+      </c>
+      <c r="D274" t="s">
+        <v>845</v>
+      </c>
+      <c r="E274" t="s">
         <v>777</v>
       </c>
-      <c r="D274" t="s">
-        <v>847</v>
-      </c>
-      <c r="E274" t="s">
-        <v>779</v>
-      </c>
       <c r="F274" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="G274" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="H274" t="s">
+        <v>840</v>
+      </c>
+      <c r="I274" t="s">
+        <v>841</v>
+      </c>
+      <c r="J274" t="s">
+        <v>837</v>
+      </c>
+      <c r="K274" t="s">
         <v>842</v>
       </c>
-      <c r="I274" t="s">
+      <c r="L274" t="s">
         <v>843</v>
-      </c>
-      <c r="J274" t="s">
-        <v>839</v>
-      </c>
-      <c r="K274" t="s">
-        <v>844</v>
-      </c>
-      <c r="L274" t="s">
-        <v>845</v>
       </c>
       <c r="M274">
         <v>0</v>
@@ -45851,28 +45929,28 @@
         <v>0</v>
       </c>
       <c r="C275" t="s">
+        <v>846</v>
+      </c>
+      <c r="D275" t="s">
+        <v>776</v>
+      </c>
+      <c r="E275" t="s">
+        <v>847</v>
+      </c>
+      <c r="F275" t="s">
         <v>848</v>
       </c>
-      <c r="D275" t="s">
-        <v>778</v>
-      </c>
-      <c r="E275" t="s">
+      <c r="G275" t="s">
         <v>849</v>
       </c>
-      <c r="F275" t="s">
+      <c r="H275" t="s">
         <v>850</v>
       </c>
-      <c r="G275" t="s">
+      <c r="I275" t="s">
         <v>851</v>
       </c>
-      <c r="H275" t="s">
+      <c r="J275" t="s">
         <v>852</v>
-      </c>
-      <c r="I275" t="s">
-        <v>853</v>
-      </c>
-      <c r="J275" t="s">
-        <v>854</v>
       </c>
       <c r="K275">
         <v>0</v>
@@ -45908,28 +45986,28 @@
         <v>0</v>
       </c>
       <c r="C276" t="s">
+        <v>846</v>
+      </c>
+      <c r="D276" t="s">
+        <v>781</v>
+      </c>
+      <c r="E276" t="s">
+        <v>847</v>
+      </c>
+      <c r="F276" t="s">
         <v>848</v>
       </c>
-      <c r="D276" t="s">
-        <v>783</v>
-      </c>
-      <c r="E276" t="s">
-        <v>849</v>
-      </c>
-      <c r="F276" t="s">
+      <c r="G276" t="s">
+        <v>853</v>
+      </c>
+      <c r="H276" t="s">
         <v>850</v>
       </c>
-      <c r="G276" t="s">
+      <c r="I276" t="s">
+        <v>854</v>
+      </c>
+      <c r="J276" t="s">
         <v>855</v>
-      </c>
-      <c r="H276" t="s">
-        <v>852</v>
-      </c>
-      <c r="I276" t="s">
-        <v>856</v>
-      </c>
-      <c r="J276" t="s">
-        <v>857</v>
       </c>
       <c r="K276">
         <v>0</v>
@@ -45965,28 +46043,28 @@
         <v>0</v>
       </c>
       <c r="C277" t="s">
+        <v>846</v>
+      </c>
+      <c r="D277" t="s">
+        <v>784</v>
+      </c>
+      <c r="E277" t="s">
+        <v>847</v>
+      </c>
+      <c r="F277" t="s">
         <v>848</v>
       </c>
-      <c r="D277" t="s">
-        <v>786</v>
-      </c>
-      <c r="E277" t="s">
-        <v>849</v>
-      </c>
-      <c r="F277" t="s">
+      <c r="G277" t="s">
+        <v>856</v>
+      </c>
+      <c r="H277" t="s">
         <v>850</v>
       </c>
-      <c r="G277" t="s">
+      <c r="I277" t="s">
+        <v>857</v>
+      </c>
+      <c r="J277" t="s">
         <v>858</v>
-      </c>
-      <c r="H277" t="s">
-        <v>852</v>
-      </c>
-      <c r="I277" t="s">
-        <v>859</v>
-      </c>
-      <c r="J277" t="s">
-        <v>860</v>
       </c>
       <c r="K277">
         <v>0</v>
@@ -46022,31 +46100,31 @@
         <v>0</v>
       </c>
       <c r="C278" t="s">
+        <v>846</v>
+      </c>
+      <c r="D278" t="s">
+        <v>787</v>
+      </c>
+      <c r="E278" t="s">
+        <v>847</v>
+      </c>
+      <c r="F278" t="s">
         <v>848</v>
       </c>
-      <c r="D278" t="s">
-        <v>789</v>
-      </c>
-      <c r="E278" t="s">
-        <v>849</v>
-      </c>
-      <c r="F278" t="s">
+      <c r="G278" t="s">
+        <v>859</v>
+      </c>
+      <c r="H278" t="s">
         <v>850</v>
       </c>
-      <c r="G278" t="s">
-        <v>861</v>
-      </c>
-      <c r="H278" t="s">
-        <v>852</v>
-      </c>
       <c r="I278" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="J278" t="s">
+        <v>858</v>
+      </c>
+      <c r="K278" t="s">
         <v>860</v>
-      </c>
-      <c r="K278" t="s">
-        <v>862</v>
       </c>
       <c r="L278">
         <v>0</v>
@@ -46079,31 +46157,31 @@
         <v>0</v>
       </c>
       <c r="C279" t="s">
+        <v>846</v>
+      </c>
+      <c r="D279" t="s">
+        <v>790</v>
+      </c>
+      <c r="E279" t="s">
+        <v>847</v>
+      </c>
+      <c r="F279" t="s">
         <v>848</v>
       </c>
-      <c r="D279" t="s">
-        <v>792</v>
-      </c>
-      <c r="E279" t="s">
-        <v>849</v>
-      </c>
-      <c r="F279" t="s">
+      <c r="G279" t="s">
+        <v>861</v>
+      </c>
+      <c r="H279" t="s">
         <v>850</v>
       </c>
-      <c r="G279" t="s">
+      <c r="I279" t="s">
+        <v>857</v>
+      </c>
+      <c r="J279" t="s">
+        <v>862</v>
+      </c>
+      <c r="K279" t="s">
         <v>863</v>
-      </c>
-      <c r="H279" t="s">
-        <v>852</v>
-      </c>
-      <c r="I279" t="s">
-        <v>859</v>
-      </c>
-      <c r="J279" t="s">
-        <v>864</v>
-      </c>
-      <c r="K279" t="s">
-        <v>865</v>
       </c>
       <c r="L279">
         <v>0</v>
@@ -46136,31 +46214,31 @@
         <v>0</v>
       </c>
       <c r="C280" t="s">
+        <v>846</v>
+      </c>
+      <c r="D280" t="s">
+        <v>793</v>
+      </c>
+      <c r="E280" t="s">
+        <v>847</v>
+      </c>
+      <c r="F280" t="s">
         <v>848</v>
       </c>
-      <c r="D280" t="s">
-        <v>795</v>
-      </c>
-      <c r="E280" t="s">
-        <v>849</v>
-      </c>
-      <c r="F280" t="s">
+      <c r="G280" t="s">
+        <v>864</v>
+      </c>
+      <c r="H280" t="s">
         <v>850</v>
       </c>
-      <c r="G280" t="s">
+      <c r="I280" t="s">
+        <v>857</v>
+      </c>
+      <c r="J280" t="s">
+        <v>865</v>
+      </c>
+      <c r="K280" t="s">
         <v>866</v>
-      </c>
-      <c r="H280" t="s">
-        <v>852</v>
-      </c>
-      <c r="I280" t="s">
-        <v>859</v>
-      </c>
-      <c r="J280" t="s">
-        <v>867</v>
-      </c>
-      <c r="K280" t="s">
-        <v>868</v>
       </c>
       <c r="L280">
         <v>0</v>
@@ -46193,31 +46271,31 @@
         <v>0</v>
       </c>
       <c r="C281" t="s">
+        <v>846</v>
+      </c>
+      <c r="D281" t="s">
+        <v>796</v>
+      </c>
+      <c r="E281" t="s">
+        <v>847</v>
+      </c>
+      <c r="F281" t="s">
         <v>848</v>
       </c>
-      <c r="D281" t="s">
-        <v>798</v>
-      </c>
-      <c r="E281" t="s">
-        <v>849</v>
-      </c>
-      <c r="F281" t="s">
+      <c r="G281" t="s">
+        <v>867</v>
+      </c>
+      <c r="H281" t="s">
         <v>850</v>
       </c>
-      <c r="G281" t="s">
+      <c r="I281" t="s">
+        <v>868</v>
+      </c>
+      <c r="J281" t="s">
         <v>869</v>
       </c>
-      <c r="H281" t="s">
-        <v>852</v>
-      </c>
-      <c r="I281" t="s">
+      <c r="K281" t="s">
         <v>870</v>
-      </c>
-      <c r="J281" t="s">
-        <v>871</v>
-      </c>
-      <c r="K281" t="s">
-        <v>872</v>
       </c>
       <c r="L281">
         <v>0</v>
@@ -46250,31 +46328,31 @@
         <v>0</v>
       </c>
       <c r="C282" t="s">
+        <v>846</v>
+      </c>
+      <c r="D282" t="s">
+        <v>801</v>
+      </c>
+      <c r="E282" t="s">
+        <v>847</v>
+      </c>
+      <c r="F282" t="s">
         <v>848</v>
       </c>
-      <c r="D282" t="s">
-        <v>803</v>
-      </c>
-      <c r="E282" t="s">
-        <v>849</v>
-      </c>
-      <c r="F282" t="s">
+      <c r="G282" t="s">
+        <v>871</v>
+      </c>
+      <c r="H282" t="s">
         <v>850</v>
       </c>
-      <c r="G282" t="s">
+      <c r="I282" t="s">
+        <v>872</v>
+      </c>
+      <c r="J282" t="s">
         <v>873</v>
       </c>
-      <c r="H282" t="s">
-        <v>852</v>
-      </c>
-      <c r="I282" t="s">
+      <c r="K282" t="s">
         <v>874</v>
-      </c>
-      <c r="J282" t="s">
-        <v>875</v>
-      </c>
-      <c r="K282" t="s">
-        <v>876</v>
       </c>
       <c r="L282">
         <v>0</v>
@@ -46307,31 +46385,31 @@
         <v>0</v>
       </c>
       <c r="C283" t="s">
+        <v>846</v>
+      </c>
+      <c r="D283" t="s">
+        <v>803</v>
+      </c>
+      <c r="E283" t="s">
+        <v>847</v>
+      </c>
+      <c r="F283" t="s">
         <v>848</v>
       </c>
-      <c r="D283" t="s">
-        <v>805</v>
-      </c>
-      <c r="E283" t="s">
-        <v>849</v>
-      </c>
-      <c r="F283" t="s">
+      <c r="G283" t="s">
+        <v>875</v>
+      </c>
+      <c r="H283" t="s">
         <v>850</v>
       </c>
-      <c r="G283" t="s">
+      <c r="I283" t="s">
+        <v>876</v>
+      </c>
+      <c r="J283" t="s">
         <v>877</v>
       </c>
-      <c r="H283" t="s">
-        <v>852</v>
-      </c>
-      <c r="I283" t="s">
+      <c r="K283" t="s">
         <v>878</v>
-      </c>
-      <c r="J283" t="s">
-        <v>879</v>
-      </c>
-      <c r="K283" t="s">
-        <v>880</v>
       </c>
       <c r="L283">
         <v>0</v>
@@ -46364,34 +46442,34 @@
         <v>0</v>
       </c>
       <c r="C284" t="s">
+        <v>846</v>
+      </c>
+      <c r="D284" t="s">
+        <v>807</v>
+      </c>
+      <c r="E284" t="s">
+        <v>847</v>
+      </c>
+      <c r="F284" t="s">
         <v>848</v>
       </c>
-      <c r="D284" t="s">
-        <v>809</v>
-      </c>
-      <c r="E284" t="s">
-        <v>849</v>
-      </c>
-      <c r="F284" t="s">
+      <c r="G284" t="s">
+        <v>879</v>
+      </c>
+      <c r="H284" t="s">
         <v>850</v>
       </c>
-      <c r="G284" t="s">
+      <c r="I284" t="s">
+        <v>876</v>
+      </c>
+      <c r="J284" t="s">
+        <v>877</v>
+      </c>
+      <c r="K284" t="s">
+        <v>880</v>
+      </c>
+      <c r="L284" t="s">
         <v>881</v>
-      </c>
-      <c r="H284" t="s">
-        <v>852</v>
-      </c>
-      <c r="I284" t="s">
-        <v>878</v>
-      </c>
-      <c r="J284" t="s">
-        <v>879</v>
-      </c>
-      <c r="K284" t="s">
-        <v>882</v>
-      </c>
-      <c r="L284" t="s">
-        <v>883</v>
       </c>
       <c r="M284">
         <v>0</v>
@@ -46421,34 +46499,34 @@
         <v>0</v>
       </c>
       <c r="C285" t="s">
+        <v>846</v>
+      </c>
+      <c r="D285" t="s">
+        <v>811</v>
+      </c>
+      <c r="E285" t="s">
+        <v>847</v>
+      </c>
+      <c r="F285" t="s">
         <v>848</v>
       </c>
-      <c r="D285" t="s">
-        <v>813</v>
-      </c>
-      <c r="E285" t="s">
-        <v>849</v>
-      </c>
-      <c r="F285" t="s">
+      <c r="G285" t="s">
+        <v>882</v>
+      </c>
+      <c r="H285" t="s">
         <v>850</v>
       </c>
-      <c r="G285" t="s">
+      <c r="I285" t="s">
+        <v>876</v>
+      </c>
+      <c r="J285" t="s">
+        <v>877</v>
+      </c>
+      <c r="K285" t="s">
+        <v>883</v>
+      </c>
+      <c r="L285" t="s">
         <v>884</v>
-      </c>
-      <c r="H285" t="s">
-        <v>852</v>
-      </c>
-      <c r="I285" t="s">
-        <v>878</v>
-      </c>
-      <c r="J285" t="s">
-        <v>879</v>
-      </c>
-      <c r="K285" t="s">
-        <v>885</v>
-      </c>
-      <c r="L285" t="s">
-        <v>886</v>
       </c>
       <c r="M285">
         <v>0</v>
@@ -46478,34 +46556,34 @@
         <v>0</v>
       </c>
       <c r="C286" t="s">
+        <v>846</v>
+      </c>
+      <c r="D286" t="s">
+        <v>815</v>
+      </c>
+      <c r="E286" t="s">
+        <v>847</v>
+      </c>
+      <c r="F286" t="s">
         <v>848</v>
       </c>
-      <c r="D286" t="s">
-        <v>817</v>
-      </c>
-      <c r="E286" t="s">
-        <v>849</v>
-      </c>
-      <c r="F286" t="s">
+      <c r="G286" t="s">
+        <v>885</v>
+      </c>
+      <c r="H286" t="s">
         <v>850</v>
       </c>
-      <c r="G286" t="s">
+      <c r="I286" t="s">
+        <v>886</v>
+      </c>
+      <c r="J286" t="s">
         <v>887</v>
       </c>
-      <c r="H286" t="s">
-        <v>852</v>
-      </c>
-      <c r="I286" t="s">
+      <c r="K286" t="s">
         <v>888</v>
       </c>
-      <c r="J286" t="s">
+      <c r="L286" t="s">
         <v>889</v>
-      </c>
-      <c r="K286" t="s">
-        <v>890</v>
-      </c>
-      <c r="L286" t="s">
-        <v>891</v>
       </c>
       <c r="M286">
         <v>0</v>
@@ -46535,34 +46613,34 @@
         <v>0</v>
       </c>
       <c r="C287" t="s">
+        <v>846</v>
+      </c>
+      <c r="D287" t="s">
+        <v>819</v>
+      </c>
+      <c r="E287" t="s">
+        <v>847</v>
+      </c>
+      <c r="F287" t="s">
         <v>848</v>
       </c>
-      <c r="D287" t="s">
-        <v>821</v>
-      </c>
-      <c r="E287" t="s">
-        <v>849</v>
-      </c>
-      <c r="F287" t="s">
+      <c r="G287" t="s">
+        <v>890</v>
+      </c>
+      <c r="H287" t="s">
         <v>850</v>
       </c>
-      <c r="G287" t="s">
-        <v>892</v>
-      </c>
-      <c r="H287" t="s">
-        <v>852</v>
-      </c>
       <c r="I287" t="s">
+        <v>886</v>
+      </c>
+      <c r="J287" t="s">
+        <v>887</v>
+      </c>
+      <c r="K287" t="s">
         <v>888</v>
       </c>
-      <c r="J287" t="s">
-        <v>889</v>
-      </c>
-      <c r="K287" t="s">
-        <v>890</v>
-      </c>
       <c r="L287" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M287">
         <v>0</v>
@@ -46592,34 +46670,34 @@
         <v>0</v>
       </c>
       <c r="C288" t="s">
+        <v>846</v>
+      </c>
+      <c r="D288" t="s">
+        <v>823</v>
+      </c>
+      <c r="E288" t="s">
+        <v>847</v>
+      </c>
+      <c r="F288" t="s">
         <v>848</v>
       </c>
-      <c r="D288" t="s">
-        <v>825</v>
-      </c>
-      <c r="E288" t="s">
-        <v>849</v>
-      </c>
-      <c r="F288" t="s">
+      <c r="G288" t="s">
+        <v>892</v>
+      </c>
+      <c r="H288" t="s">
         <v>850</v>
       </c>
-      <c r="G288" t="s">
-        <v>894</v>
-      </c>
-      <c r="H288" t="s">
-        <v>852</v>
-      </c>
       <c r="I288" t="s">
+        <v>886</v>
+      </c>
+      <c r="J288" t="s">
+        <v>887</v>
+      </c>
+      <c r="K288" t="s">
         <v>888</v>
       </c>
-      <c r="J288" t="s">
-        <v>889</v>
-      </c>
-      <c r="K288" t="s">
-        <v>890</v>
-      </c>
       <c r="L288" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="M288">
         <v>0</v>
@@ -46649,37 +46727,37 @@
         <v>0</v>
       </c>
       <c r="C289" t="s">
+        <v>846</v>
+      </c>
+      <c r="D289" t="s">
+        <v>827</v>
+      </c>
+      <c r="E289" t="s">
+        <v>847</v>
+      </c>
+      <c r="F289" t="s">
         <v>848</v>
       </c>
-      <c r="D289" t="s">
-        <v>829</v>
-      </c>
-      <c r="E289" t="s">
-        <v>849</v>
-      </c>
-      <c r="F289" t="s">
+      <c r="G289" t="s">
+        <v>894</v>
+      </c>
+      <c r="H289" t="s">
         <v>850</v>
       </c>
-      <c r="G289" t="s">
+      <c r="I289" t="s">
+        <v>886</v>
+      </c>
+      <c r="J289" t="s">
+        <v>895</v>
+      </c>
+      <c r="K289" t="s">
         <v>896</v>
       </c>
-      <c r="H289" t="s">
-        <v>852</v>
-      </c>
-      <c r="I289" t="s">
-        <v>888</v>
-      </c>
-      <c r="J289" t="s">
+      <c r="L289" t="s">
+        <v>889</v>
+      </c>
+      <c r="M289" t="s">
         <v>897</v>
-      </c>
-      <c r="K289" t="s">
-        <v>898</v>
-      </c>
-      <c r="L289" t="s">
-        <v>891</v>
-      </c>
-      <c r="M289" t="s">
-        <v>899</v>
       </c>
       <c r="N289">
         <v>0</v>
@@ -46706,37 +46784,37 @@
         <v>0</v>
       </c>
       <c r="C290" t="s">
+        <v>846</v>
+      </c>
+      <c r="D290" t="s">
+        <v>831</v>
+      </c>
+      <c r="E290" t="s">
+        <v>847</v>
+      </c>
+      <c r="F290" t="s">
         <v>848</v>
       </c>
-      <c r="D290" t="s">
-        <v>833</v>
-      </c>
-      <c r="E290" t="s">
-        <v>849</v>
-      </c>
-      <c r="F290" t="s">
+      <c r="G290" t="s">
+        <v>898</v>
+      </c>
+      <c r="H290" t="s">
         <v>850</v>
       </c>
-      <c r="G290" t="s">
-        <v>900</v>
-      </c>
-      <c r="H290" t="s">
-        <v>852</v>
-      </c>
       <c r="I290" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="J290" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="K290" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="L290" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M290" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="N290">
         <v>0</v>
@@ -46763,37 +46841,37 @@
         <v>0</v>
       </c>
       <c r="C291" t="s">
+        <v>846</v>
+      </c>
+      <c r="D291" t="s">
+        <v>835</v>
+      </c>
+      <c r="E291" t="s">
+        <v>847</v>
+      </c>
+      <c r="F291" t="s">
         <v>848</v>
       </c>
-      <c r="D291" t="s">
-        <v>837</v>
-      </c>
-      <c r="E291" t="s">
-        <v>849</v>
-      </c>
-      <c r="F291" t="s">
+      <c r="G291" t="s">
+        <v>900</v>
+      </c>
+      <c r="H291" t="s">
         <v>850</v>
       </c>
-      <c r="G291" t="s">
-        <v>902</v>
-      </c>
-      <c r="H291" t="s">
-        <v>852</v>
-      </c>
       <c r="I291" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="J291" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="K291" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="L291" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M291" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="N291">
         <v>0</v>
@@ -46820,40 +46898,40 @@
         <v>0</v>
       </c>
       <c r="C292" t="s">
+        <v>846</v>
+      </c>
+      <c r="D292" t="s">
+        <v>839</v>
+      </c>
+      <c r="E292" t="s">
+        <v>847</v>
+      </c>
+      <c r="F292" t="s">
         <v>848</v>
       </c>
-      <c r="D292" t="s">
-        <v>841</v>
-      </c>
-      <c r="E292" t="s">
-        <v>849</v>
-      </c>
-      <c r="F292" t="s">
+      <c r="G292" t="s">
+        <v>902</v>
+      </c>
+      <c r="H292" t="s">
         <v>850</v>
       </c>
-      <c r="G292" t="s">
-        <v>904</v>
-      </c>
-      <c r="H292" t="s">
-        <v>852</v>
-      </c>
       <c r="I292" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="J292" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="K292" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="L292" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="M292" t="s">
+        <v>901</v>
+      </c>
+      <c r="N292" t="s">
         <v>903</v>
-      </c>
-      <c r="N292" t="s">
-        <v>905</v>
       </c>
       <c r="O292">
         <v>0</v>
@@ -46877,43 +46955,43 @@
         <v>0</v>
       </c>
       <c r="C293" t="s">
+        <v>846</v>
+      </c>
+      <c r="D293" t="s">
+        <v>844</v>
+      </c>
+      <c r="E293" t="s">
+        <v>847</v>
+      </c>
+      <c r="F293" t="s">
         <v>848</v>
       </c>
-      <c r="D293" t="s">
-        <v>846</v>
-      </c>
-      <c r="E293" t="s">
-        <v>849</v>
-      </c>
-      <c r="F293" t="s">
+      <c r="G293" t="s">
+        <v>904</v>
+      </c>
+      <c r="H293" t="s">
         <v>850</v>
       </c>
-      <c r="G293" t="s">
+      <c r="I293" t="s">
+        <v>886</v>
+      </c>
+      <c r="J293" t="s">
+        <v>895</v>
+      </c>
+      <c r="K293" t="s">
+        <v>896</v>
+      </c>
+      <c r="L293" t="s">
+        <v>891</v>
+      </c>
+      <c r="M293" t="s">
+        <v>901</v>
+      </c>
+      <c r="N293" t="s">
+        <v>905</v>
+      </c>
+      <c r="O293" t="s">
         <v>906</v>
-      </c>
-      <c r="H293" t="s">
-        <v>852</v>
-      </c>
-      <c r="I293" t="s">
-        <v>888</v>
-      </c>
-      <c r="J293" t="s">
-        <v>897</v>
-      </c>
-      <c r="K293" t="s">
-        <v>898</v>
-      </c>
-      <c r="L293" t="s">
-        <v>893</v>
-      </c>
-      <c r="M293" t="s">
-        <v>903</v>
-      </c>
-      <c r="N293" t="s">
-        <v>907</v>
-      </c>
-      <c r="O293" t="s">
-        <v>908</v>
       </c>
       <c r="P293">
         <v>0</v>
@@ -46934,46 +47012,46 @@
         <v>0</v>
       </c>
       <c r="C294" t="s">
+        <v>846</v>
+      </c>
+      <c r="D294" t="s">
+        <v>845</v>
+      </c>
+      <c r="E294" t="s">
+        <v>847</v>
+      </c>
+      <c r="F294" t="s">
         <v>848</v>
       </c>
-      <c r="D294" t="s">
-        <v>847</v>
-      </c>
-      <c r="E294" t="s">
-        <v>849</v>
-      </c>
-      <c r="F294" t="s">
+      <c r="G294" t="s">
+        <v>907</v>
+      </c>
+      <c r="H294" t="s">
         <v>850</v>
       </c>
-      <c r="G294" t="s">
+      <c r="I294" t="s">
+        <v>886</v>
+      </c>
+      <c r="J294" t="s">
+        <v>895</v>
+      </c>
+      <c r="K294" t="s">
+        <v>896</v>
+      </c>
+      <c r="L294" t="s">
+        <v>891</v>
+      </c>
+      <c r="M294" t="s">
+        <v>901</v>
+      </c>
+      <c r="N294" t="s">
+        <v>908</v>
+      </c>
+      <c r="O294" t="s">
         <v>909</v>
       </c>
-      <c r="H294" t="s">
-        <v>852</v>
-      </c>
-      <c r="I294" t="s">
-        <v>888</v>
-      </c>
-      <c r="J294" t="s">
-        <v>897</v>
-      </c>
-      <c r="K294" t="s">
-        <v>898</v>
-      </c>
-      <c r="L294" t="s">
-        <v>893</v>
-      </c>
-      <c r="M294" t="s">
-        <v>903</v>
-      </c>
-      <c r="N294" t="s">
+      <c r="P294" t="s">
         <v>910</v>
-      </c>
-      <c r="O294" t="s">
-        <v>911</v>
-      </c>
-      <c r="P294" t="s">
-        <v>912</v>
       </c>
       <c r="Q294">
         <v>0</v>
@@ -46991,16 +47069,16 @@
         <v>0</v>
       </c>
       <c r="C295" t="s">
+        <v>911</v>
+      </c>
+      <c r="D295" t="s">
+        <v>912</v>
+      </c>
+      <c r="E295" t="s">
         <v>913</v>
       </c>
-      <c r="D295" t="s">
+      <c r="F295" t="s">
         <v>914</v>
-      </c>
-      <c r="E295" t="s">
-        <v>915</v>
-      </c>
-      <c r="F295" t="s">
-        <v>916</v>
       </c>
       <c r="G295">
         <v>0</v>
@@ -47048,16 +47126,16 @@
         <v>0</v>
       </c>
       <c r="C296" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D296" t="s">
+        <v>915</v>
+      </c>
+      <c r="E296" t="s">
+        <v>916</v>
+      </c>
+      <c r="F296" t="s">
         <v>917</v>
-      </c>
-      <c r="E296" t="s">
-        <v>918</v>
-      </c>
-      <c r="F296" t="s">
-        <v>919</v>
       </c>
       <c r="G296">
         <v>0.1</v>
@@ -47105,16 +47183,16 @@
         <v>0</v>
       </c>
       <c r="C297" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D297" t="s">
+        <v>918</v>
+      </c>
+      <c r="E297" t="s">
+        <v>919</v>
+      </c>
+      <c r="F297" t="s">
         <v>920</v>
-      </c>
-      <c r="E297" t="s">
-        <v>921</v>
-      </c>
-      <c r="F297" t="s">
-        <v>922</v>
       </c>
       <c r="G297">
         <v>0</v>
@@ -47162,16 +47240,16 @@
         <v>0</v>
       </c>
       <c r="C298" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D298" t="s">
+        <v>921</v>
+      </c>
+      <c r="E298" t="s">
+        <v>922</v>
+      </c>
+      <c r="F298" t="s">
         <v>923</v>
-      </c>
-      <c r="E298" t="s">
-        <v>924</v>
-      </c>
-      <c r="F298" t="s">
-        <v>925</v>
       </c>
       <c r="G298">
         <v>0</v>
@@ -47219,16 +47297,16 @@
         <v>0</v>
       </c>
       <c r="C299" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D299" t="s">
+        <v>924</v>
+      </c>
+      <c r="E299" t="s">
+        <v>925</v>
+      </c>
+      <c r="F299" t="s">
         <v>926</v>
-      </c>
-      <c r="E299" t="s">
-        <v>927</v>
-      </c>
-      <c r="F299" t="s">
-        <v>928</v>
       </c>
       <c r="G299">
         <v>0</v>
@@ -47276,16 +47354,16 @@
         <v>0</v>
       </c>
       <c r="C300" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D300" t="s">
+        <v>927</v>
+      </c>
+      <c r="E300" t="s">
+        <v>928</v>
+      </c>
+      <c r="F300" t="s">
         <v>929</v>
-      </c>
-      <c r="E300" t="s">
-        <v>930</v>
-      </c>
-      <c r="F300" t="s">
-        <v>931</v>
       </c>
       <c r="G300">
         <v>0.4</v>
@@ -47333,16 +47411,16 @@
         <v>0</v>
       </c>
       <c r="C301" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D301" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="F301" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="G301">
         <v>1000</v>
@@ -47390,16 +47468,16 @@
         <v>0</v>
       </c>
       <c r="C302" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D302" t="s">
+        <v>931</v>
+      </c>
+      <c r="E302" t="s">
+        <v>932</v>
+      </c>
+      <c r="F302" t="s">
         <v>933</v>
-      </c>
-      <c r="E302" t="s">
-        <v>934</v>
-      </c>
-      <c r="F302" t="s">
-        <v>935</v>
       </c>
       <c r="G302">
         <v>0</v>
@@ -47447,16 +47525,16 @@
         <v>0</v>
       </c>
       <c r="C303" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="D303" t="s">
+        <v>934</v>
+      </c>
+      <c r="E303" t="s">
+        <v>935</v>
+      </c>
+      <c r="F303" t="s">
         <v>936</v>
-      </c>
-      <c r="E303" t="s">
-        <v>937</v>
-      </c>
-      <c r="F303" t="s">
-        <v>938</v>
       </c>
       <c r="G303">
         <v>30</v>
@@ -47504,16 +47582,16 @@
         <v>0</v>
       </c>
       <c r="C304" t="s">
+        <v>937</v>
+      </c>
+      <c r="D304" t="s">
+        <v>938</v>
+      </c>
+      <c r="E304" t="s">
         <v>939</v>
       </c>
-      <c r="D304" t="s">
+      <c r="F304" t="s">
         <v>940</v>
-      </c>
-      <c r="E304" t="s">
-        <v>941</v>
-      </c>
-      <c r="F304" t="s">
-        <v>942</v>
       </c>
       <c r="G304">
         <v>0.75</v>
@@ -47561,13 +47639,13 @@
         <v>0</v>
       </c>
       <c r="C305" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D305" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="E305" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="F305">
         <v>0</v>
@@ -47618,16 +47696,16 @@
         <v>0</v>
       </c>
       <c r="C306" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D306" t="s">
+        <v>943</v>
+      </c>
+      <c r="E306" t="s">
+        <v>944</v>
+      </c>
+      <c r="F306" t="s">
         <v>945</v>
-      </c>
-      <c r="E306" t="s">
-        <v>946</v>
-      </c>
-      <c r="F306" t="s">
-        <v>947</v>
       </c>
       <c r="G306">
         <v>45</v>
@@ -47675,16 +47753,16 @@
         <v>0</v>
       </c>
       <c r="C307" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D307" t="s">
+        <v>946</v>
+      </c>
+      <c r="E307" t="s">
+        <v>947</v>
+      </c>
+      <c r="F307" t="s">
         <v>948</v>
-      </c>
-      <c r="E307" t="s">
-        <v>949</v>
-      </c>
-      <c r="F307" t="s">
-        <v>950</v>
       </c>
       <c r="G307">
         <v>0</v>
@@ -47732,16 +47810,16 @@
         <v>0</v>
       </c>
       <c r="C308" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D308" t="s">
+        <v>949</v>
+      </c>
+      <c r="E308" t="s">
+        <v>950</v>
+      </c>
+      <c r="F308" t="s">
         <v>951</v>
-      </c>
-      <c r="E308" t="s">
-        <v>952</v>
-      </c>
-      <c r="F308" t="s">
-        <v>953</v>
       </c>
       <c r="G308">
         <v>0.1</v>
@@ -47789,16 +47867,16 @@
         <v>0</v>
       </c>
       <c r="C309" t="s">
+        <v>952</v>
+      </c>
+      <c r="D309" t="s">
+        <v>953</v>
+      </c>
+      <c r="E309" t="s">
         <v>954</v>
       </c>
-      <c r="D309" t="s">
+      <c r="F309" t="s">
         <v>955</v>
-      </c>
-      <c r="E309" t="s">
-        <v>956</v>
-      </c>
-      <c r="F309" t="s">
-        <v>957</v>
       </c>
       <c r="G309">
         <v>24</v>
@@ -47846,16 +47924,16 @@
         <v>0</v>
       </c>
       <c r="C310" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D310" t="s">
+        <v>956</v>
+      </c>
+      <c r="E310" t="s">
+        <v>957</v>
+      </c>
+      <c r="F310" t="s">
         <v>958</v>
-      </c>
-      <c r="E310" t="s">
-        <v>959</v>
-      </c>
-      <c r="F310" t="s">
-        <v>960</v>
       </c>
       <c r="G310">
         <v>10</v>
@@ -47903,16 +47981,16 @@
         <v>0</v>
       </c>
       <c r="C311" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D311" t="s">
+        <v>959</v>
+      </c>
+      <c r="E311" t="s">
+        <v>960</v>
+      </c>
+      <c r="F311" t="s">
         <v>961</v>
-      </c>
-      <c r="E311" t="s">
-        <v>962</v>
-      </c>
-      <c r="F311" t="s">
-        <v>963</v>
       </c>
       <c r="G311">
         <v>20</v>
@@ -47960,16 +48038,16 @@
         <v>0</v>
       </c>
       <c r="C312" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="D312" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="E312" t="s">
         <v>39</v>
       </c>
       <c r="F312" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="G312">
         <v>1</v>
@@ -48017,16 +48095,16 @@
         <v>0</v>
       </c>
       <c r="C313" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="D313" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="E313" t="s">
         <v>39</v>
       </c>
       <c r="F313" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="G313">
         <v>1.35</v>
@@ -48074,16 +48152,16 @@
         <v>0</v>
       </c>
       <c r="C314" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="D314" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="E314" t="s">
         <v>39</v>
       </c>
       <c r="F314" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="G314">
         <v>1.75</v>
@@ -48131,16 +48209,16 @@
         <v>0</v>
       </c>
       <c r="C315" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="D315" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="E315" t="s">
         <v>39</v>
       </c>
       <c r="F315" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="G315">
         <v>2.2999999999999998</v>
@@ -48188,16 +48266,16 @@
         <v>0</v>
       </c>
       <c r="C316" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="D316" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="E316" t="s">
         <v>39</v>
       </c>
       <c r="F316" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="G316">
         <v>3</v>
@@ -48245,16 +48323,16 @@
         <v>0</v>
       </c>
       <c r="C317" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="D317" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="E317" t="s">
         <v>39</v>
       </c>
       <c r="F317" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="G317">
         <v>4</v>
@@ -48302,16 +48380,16 @@
         <v>0</v>
       </c>
       <c r="C318" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="D318" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="E318" t="s">
         <v>39</v>
       </c>
       <c r="F318" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="G318">
         <v>5.2</v>
@@ -48359,16 +48437,16 @@
         <v>0</v>
       </c>
       <c r="C319" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="D319" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="E319" t="s">
         <v>39</v>
       </c>
       <c r="F319" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="G319">
         <v>6.8</v>
@@ -48416,16 +48494,16 @@
         <v>0</v>
       </c>
       <c r="C320" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="D320" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="E320" t="s">
         <v>39</v>
       </c>
       <c r="F320" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="G320">
         <v>10.199999999999999</v>
@@ -48473,22 +48551,22 @@
         <v>0</v>
       </c>
       <c r="C321" t="s">
+        <v>973</v>
+      </c>
+      <c r="D321" t="s">
+        <v>974</v>
+      </c>
+      <c r="E321" t="s">
         <v>975</v>
       </c>
-      <c r="D321" t="s">
+      <c r="F321" t="s">
         <v>976</v>
-      </c>
-      <c r="E321" t="s">
-        <v>977</v>
-      </c>
-      <c r="F321" t="s">
-        <v>978</v>
       </c>
       <c r="G321">
         <v>25</v>
       </c>
       <c r="H321" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="I321">
         <v>0</v>
@@ -48530,22 +48608,22 @@
         <v>0</v>
       </c>
       <c r="C322" t="s">
+        <v>973</v>
+      </c>
+      <c r="D322" t="s">
+        <v>978</v>
+      </c>
+      <c r="E322" t="s">
         <v>975</v>
       </c>
-      <c r="D322" t="s">
-        <v>980</v>
-      </c>
-      <c r="E322" t="s">
-        <v>977</v>
-      </c>
       <c r="F322" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="G322">
         <v>20</v>
       </c>
       <c r="H322" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="I322">
         <v>0</v>
@@ -48587,22 +48665,22 @@
         <v>0</v>
       </c>
       <c r="C323" t="s">
+        <v>973</v>
+      </c>
+      <c r="D323" t="s">
+        <v>980</v>
+      </c>
+      <c r="E323" t="s">
         <v>975</v>
       </c>
-      <c r="D323" t="s">
-        <v>982</v>
-      </c>
-      <c r="E323" t="s">
-        <v>977</v>
-      </c>
       <c r="F323" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="G323">
         <v>25</v>
       </c>
       <c r="H323" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="I323">
         <v>0</v>
@@ -48644,22 +48722,22 @@
         <v>0</v>
       </c>
       <c r="C324" t="s">
+        <v>973</v>
+      </c>
+      <c r="D324" t="s">
+        <v>982</v>
+      </c>
+      <c r="E324" t="s">
         <v>975</v>
       </c>
-      <c r="D324" t="s">
-        <v>984</v>
-      </c>
-      <c r="E324" t="s">
-        <v>977</v>
-      </c>
       <c r="F324" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="G324">
         <v>20</v>
       </c>
       <c r="H324" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="I324">
         <v>0</v>
@@ -48701,22 +48779,22 @@
         <v>0</v>
       </c>
       <c r="C325" t="s">
+        <v>973</v>
+      </c>
+      <c r="D325" t="s">
+        <v>984</v>
+      </c>
+      <c r="E325" t="s">
         <v>975</v>
       </c>
-      <c r="D325" t="s">
-        <v>986</v>
-      </c>
-      <c r="E325" t="s">
-        <v>977</v>
-      </c>
       <c r="F325" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="G325">
         <v>0.4</v>
       </c>
       <c r="H325" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="I325">
         <v>0</v>
@@ -48758,22 +48836,22 @@
         <v>0</v>
       </c>
       <c r="C326" t="s">
+        <v>973</v>
+      </c>
+      <c r="D326" t="s">
+        <v>986</v>
+      </c>
+      <c r="E326" t="s">
         <v>975</v>
       </c>
-      <c r="D326" t="s">
-        <v>988</v>
-      </c>
-      <c r="E326" t="s">
-        <v>977</v>
-      </c>
       <c r="F326" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="G326">
         <v>3</v>
       </c>
       <c r="H326" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="I326">
         <v>0</v>
@@ -48815,22 +48893,22 @@
         <v>0</v>
       </c>
       <c r="C327" t="s">
+        <v>973</v>
+      </c>
+      <c r="D327" t="s">
+        <v>988</v>
+      </c>
+      <c r="E327" t="s">
         <v>975</v>
       </c>
-      <c r="D327" t="s">
-        <v>990</v>
-      </c>
-      <c r="E327" t="s">
-        <v>977</v>
-      </c>
       <c r="F327" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="G327">
         <v>1.5</v>
       </c>
       <c r="H327" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="I327">
         <v>0</v>
@@ -48872,22 +48950,22 @@
         <v>0</v>
       </c>
       <c r="C328" t="s">
+        <v>973</v>
+      </c>
+      <c r="D328" t="s">
+        <v>990</v>
+      </c>
+      <c r="E328" t="s">
         <v>975</v>
       </c>
-      <c r="D328" t="s">
-        <v>992</v>
-      </c>
-      <c r="E328" t="s">
-        <v>977</v>
-      </c>
       <c r="F328" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="G328">
         <v>0.15</v>
       </c>
       <c r="H328" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="I328">
         <v>0</v>
@@ -48929,22 +49007,22 @@
         <v>0</v>
       </c>
       <c r="C329" t="s">
+        <v>973</v>
+      </c>
+      <c r="D329" t="s">
+        <v>992</v>
+      </c>
+      <c r="E329" t="s">
         <v>975</v>
       </c>
-      <c r="D329" t="s">
-        <v>994</v>
-      </c>
-      <c r="E329" t="s">
-        <v>977</v>
-      </c>
       <c r="F329" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="G329">
         <v>0.5</v>
       </c>
       <c r="H329" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="I329">
         <v>0</v>
@@ -48986,22 +49064,22 @@
         <v>0</v>
       </c>
       <c r="C330" t="s">
+        <v>973</v>
+      </c>
+      <c r="D330" t="s">
+        <v>994</v>
+      </c>
+      <c r="E330" t="s">
         <v>975</v>
       </c>
-      <c r="D330" t="s">
-        <v>996</v>
-      </c>
-      <c r="E330" t="s">
-        <v>977</v>
-      </c>
       <c r="F330" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="G330">
         <v>25</v>
       </c>
       <c r="H330" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="I330">
         <v>0</v>
@@ -49043,22 +49121,22 @@
         <v>0</v>
       </c>
       <c r="C331" t="s">
+        <v>973</v>
+      </c>
+      <c r="D331" t="s">
+        <v>996</v>
+      </c>
+      <c r="E331" t="s">
         <v>975</v>
       </c>
-      <c r="D331" t="s">
-        <v>998</v>
-      </c>
-      <c r="E331" t="s">
-        <v>977</v>
-      </c>
       <c r="F331" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="G331">
         <v>8</v>
       </c>
       <c r="H331" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="I331">
         <v>0</v>
@@ -49100,22 +49178,22 @@
         <v>0</v>
       </c>
       <c r="C332" t="s">
+        <v>973</v>
+      </c>
+      <c r="D332" t="s">
+        <v>999</v>
+      </c>
+      <c r="E332" t="s">
         <v>975</v>
       </c>
-      <c r="D332" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E332" t="s">
-        <v>977</v>
-      </c>
       <c r="F332" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="G332">
         <v>15</v>
       </c>
       <c r="H332" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="I332">
         <v>0</v>
@@ -49157,16 +49235,16 @@
         <v>0</v>
       </c>
       <c r="C333" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D333" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E333" t="s">
         <v>1003</v>
       </c>
-      <c r="D333" t="s">
+      <c r="F333" t="s">
         <v>1004</v>
-      </c>
-      <c r="E333" t="s">
-        <v>1005</v>
-      </c>
-      <c r="F333" t="s">
-        <v>1006</v>
       </c>
       <c r="G333">
         <v>0.8</v>
@@ -49214,16 +49292,16 @@
         <v>0</v>
       </c>
       <c r="C334" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D334" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E334" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F334" t="s">
         <v>1007</v>
-      </c>
-      <c r="E334" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F334" t="s">
-        <v>1009</v>
       </c>
       <c r="G334">
         <v>3</v>
@@ -49271,16 +49349,16 @@
         <v>0</v>
       </c>
       <c r="C335" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D335" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E335" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F335" t="s">
         <v>1010</v>
-      </c>
-      <c r="E335" t="s">
-        <v>1011</v>
-      </c>
-      <c r="F335" t="s">
-        <v>1012</v>
       </c>
       <c r="G335">
         <v>7</v>
@@ -49328,16 +49406,16 @@
         <v>0</v>
       </c>
       <c r="C336" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D336" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E336" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F336" t="s">
         <v>1013</v>
-      </c>
-      <c r="E336" t="s">
-        <v>1014</v>
-      </c>
-      <c r="F336" t="s">
-        <v>1015</v>
       </c>
       <c r="G336">
         <v>10</v>
@@ -49385,16 +49463,16 @@
         <v>0</v>
       </c>
       <c r="C337" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D337" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E337" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F337" t="s">
         <v>1016</v>
-      </c>
-      <c r="E337" t="s">
-        <v>1017</v>
-      </c>
-      <c r="F337" t="s">
-        <v>1018</v>
       </c>
       <c r="G337">
         <v>2</v>
@@ -49442,16 +49520,16 @@
         <v>0</v>
       </c>
       <c r="C338" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D338" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E338" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F338" t="s">
         <v>1019</v>
-      </c>
-      <c r="E338" t="s">
-        <v>1020</v>
-      </c>
-      <c r="F338" t="s">
-        <v>1021</v>
       </c>
       <c r="G338">
         <v>5</v>
@@ -49499,16 +49577,16 @@
         <v>0</v>
       </c>
       <c r="C339" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D339" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E339" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F339" t="s">
         <v>1022</v>
-      </c>
-      <c r="E339" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F339" t="s">
-        <v>1024</v>
       </c>
       <c r="G339">
         <v>10</v>
@@ -49556,16 +49634,16 @@
         <v>0</v>
       </c>
       <c r="C340" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="D340" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="E340" t="s">
         <v>39</v>
       </c>
       <c r="F340" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="G340">
         <v>15.3</v>
@@ -49613,16 +49691,16 @@
         <v>0</v>
       </c>
       <c r="C341" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="D341" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="E341" t="s">
         <v>39</v>
       </c>
       <c r="F341" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="G341">
         <v>22.95</v>
@@ -49670,16 +49748,16 @@
         <v>0</v>
       </c>
       <c r="C342" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D342" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E342" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F342" t="s">
         <v>1028</v>
-      </c>
-      <c r="E342" t="s">
-        <v>1029</v>
-      </c>
-      <c r="F342" t="s">
-        <v>1030</v>
       </c>
       <c r="G342">
         <v>20</v>
@@ -49727,16 +49805,16 @@
         <v>0</v>
       </c>
       <c r="C343" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D343" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E343" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F343" t="s">
         <v>1031</v>
-      </c>
-      <c r="E343" t="s">
-        <v>1032</v>
-      </c>
-      <c r="F343" t="s">
-        <v>1033</v>
       </c>
       <c r="G343">
         <v>500000000</v>
@@ -49784,16 +49862,16 @@
         <v>0</v>
       </c>
       <c r="C344" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D344" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E344" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F344" t="s">
         <v>1034</v>
-      </c>
-      <c r="E344" t="s">
-        <v>1035</v>
-      </c>
-      <c r="F344" t="s">
-        <v>1036</v>
       </c>
       <c r="G344">
         <v>13</v>
@@ -49844,13 +49922,13 @@
         <v>18</v>
       </c>
       <c r="D345" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E345" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F345" t="s">
         <v>1037</v>
-      </c>
-      <c r="E345" t="s">
-        <v>1038</v>
-      </c>
-      <c r="F345" t="s">
-        <v>1039</v>
       </c>
       <c r="G345">
         <v>30</v>
@@ -49901,13 +49979,13 @@
         <v>18</v>
       </c>
       <c r="D346" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E346" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F346" t="s">
         <v>1040</v>
-      </c>
-      <c r="E346" t="s">
-        <v>1041</v>
-      </c>
-      <c r="F346" t="s">
-        <v>1042</v>
       </c>
       <c r="G346">
         <v>1000</v>
@@ -49955,16 +50033,16 @@
         <v>0</v>
       </c>
       <c r="C347" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D347" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E347" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F347" t="s">
         <v>1043</v>
-      </c>
-      <c r="E347" t="s">
-        <v>1044</v>
-      </c>
-      <c r="F347" t="s">
-        <v>1045</v>
       </c>
       <c r="G347">
         <v>50000</v>
@@ -50012,16 +50090,16 @@
         <v>0</v>
       </c>
       <c r="C348" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D348" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E348" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F348" t="s">
         <v>1046</v>
-      </c>
-      <c r="E348" t="s">
-        <v>1047</v>
-      </c>
-      <c r="F348" t="s">
-        <v>1048</v>
       </c>
       <c r="G348">
         <v>10</v>
@@ -50069,16 +50147,16 @@
         <v>0</v>
       </c>
       <c r="C349" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D349" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E349" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F349" t="s">
         <v>1049</v>
-      </c>
-      <c r="E349" t="s">
-        <v>1050</v>
-      </c>
-      <c r="F349" t="s">
-        <v>1051</v>
       </c>
       <c r="G349">
         <v>75</v>
@@ -50126,16 +50204,16 @@
         <v>0</v>
       </c>
       <c r="C350" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D350" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E350" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F350" t="s">
         <v>1052</v>
-      </c>
-      <c r="E350" t="s">
-        <v>1053</v>
-      </c>
-      <c r="F350" t="s">
-        <v>1054</v>
       </c>
       <c r="G350">
         <v>25</v>
@@ -50183,16 +50261,16 @@
         <v>0</v>
       </c>
       <c r="C351" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D351" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="E351" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="F351" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="G351">
         <v>5</v>
@@ -50240,16 +50318,16 @@
         <v>0</v>
       </c>
       <c r="C352" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D352" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E352" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F352" t="s">
         <v>1057</v>
-      </c>
-      <c r="E352" t="s">
-        <v>1058</v>
-      </c>
-      <c r="F352" t="s">
-        <v>1059</v>
       </c>
       <c r="G352">
         <v>0.6</v>
@@ -50297,16 +50375,16 @@
         <v>0</v>
       </c>
       <c r="C353" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D353" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E353" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F353" t="s">
         <v>1060</v>
-      </c>
-      <c r="E353" t="s">
-        <v>1061</v>
-      </c>
-      <c r="F353" t="s">
-        <v>1062</v>
       </c>
       <c r="G353">
         <v>0.1</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF44151A-3F83-48AE-8AA0-BF0656E29F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BAEFA8F-4B12-4CB7-AC4B-9E13AB6A853A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1889" uniqueCount="1084">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1889" uniqueCount="1085">
   <si>
     <t>編號</t>
   </si>
@@ -1317,12 +1317,6 @@
     <t>每品質獨立擲骰。實際機率 = 表值×(1+有效掉寶率%)，菁英再×1.5；場景倍率不作用於裝備。</t>
   </si>
   <si>
-    <t>{1~49=15}</t>
-  </si>
-  <si>
-    <t>{50~99=35}</t>
-  </si>
-  <si>
     <t>{100~149=40}</t>
   </si>
   <si>
@@ -1341,12 +1335,6 @@
     <t>精良裝備</t>
   </si>
   <si>
-    <t>{1~49=10}</t>
-  </si>
-  <si>
-    <t>{50~99=20}</t>
-  </si>
-  <si>
     <t>{100~149=30}</t>
   </si>
   <si>
@@ -1365,15 +1353,6 @@
     <t>稀有裝備</t>
   </si>
   <si>
-    <t>{1~49=5}</t>
-  </si>
-  <si>
-    <t>{50~99=8}</t>
-  </si>
-  <si>
-    <t>{100~149=15}</t>
-  </si>
-  <si>
     <t>{150~199=30}</t>
   </si>
   <si>
@@ -1392,9 +1371,6 @@
     <t>{1~49=0}</t>
   </si>
   <si>
-    <t>{50~99=4}</t>
-  </si>
-  <si>
     <t>{100~149=10}</t>
   </si>
   <si>
@@ -3142,9 +3118,6 @@
   </si>
   <si>
     <t>技能熟練度經驗需求</t>
-  </si>
-  <si>
-    <t>⌊a×L^b + c⌋</t>
   </si>
   <si>
     <t>技能熟練度升 1 級所需經驗（沿用玩家升級公式未轉生版；L=目前熟練度等級）。</t>
@@ -3754,6 +3727,65 @@
         <charset val="136"/>
       </rPr>
       <t>。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{100~149=20}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{1~19=25}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{20~99=35}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{20~99=20}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{1~19=15}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{1~19=10}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{1~19=0}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{20~99=5}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{20~99=15}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>a×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>熟練度等級</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>^b + c</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4492,7 +4524,7 @@
       </c>
       <c r="H5">
         <f>計算表!H5</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5">
         <f>計算表!I5</f>
@@ -6264,11 +6296,11 @@
       </c>
       <c r="G29">
         <f>計算表!G29</f>
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="H29">
         <f>計算表!H29</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I29">
         <f>計算表!I29</f>
@@ -15292,11 +15324,11 @@
       </c>
       <c r="G151" t="str">
         <f>計算表!G151</f>
-        <v>{1~49=15}</v>
+        <v>{1~19=25}</v>
       </c>
       <c r="H151" t="str">
         <f>計算表!H151</f>
-        <v>{50~99=35}</v>
+        <v>{20~99=35}</v>
       </c>
       <c r="I151" t="str">
         <f>計算表!I151</f>
@@ -15366,11 +15398,11 @@
       </c>
       <c r="G152" t="str">
         <f>計算表!G152</f>
-        <v>{1~49=10}</v>
+        <v>{1~19=15}</v>
       </c>
       <c r="H152" t="str">
         <f>計算表!H152</f>
-        <v>{50~99=20}</v>
+        <v>{20~99=20}</v>
       </c>
       <c r="I152" t="str">
         <f>計算表!I152</f>
@@ -15440,15 +15472,15 @@
       </c>
       <c r="G153" t="str">
         <f>計算表!G153</f>
-        <v>{1~49=5}</v>
+        <v>{1~19=10}</v>
       </c>
       <c r="H153" t="str">
         <f>計算表!H153</f>
-        <v>{50~99=8}</v>
+        <v>{20~99=15}</v>
       </c>
       <c r="I153" t="str">
         <f>計算表!I153</f>
-        <v>{100~149=15}</v>
+        <v>{100~149=20}</v>
       </c>
       <c r="J153" t="str">
         <f>計算表!J153</f>
@@ -15514,11 +15546,11 @@
       </c>
       <c r="G154" t="str">
         <f>計算表!G154</f>
-        <v>{1~49=0}</v>
+        <v>{1~19=0}</v>
       </c>
       <c r="H154" t="str">
         <f>計算表!H154</f>
-        <v>{50~99=4}</v>
+        <v>{20~99=5}</v>
       </c>
       <c r="I154" t="str">
         <f>計算表!I154</f>
@@ -29640,7 +29672,7 @@
       </c>
       <c r="E345" t="str">
         <f>計算表!E345</f>
-        <v>⌊a×L^b + c⌋</v>
+        <v>a×熟練度等級^b + c</v>
       </c>
       <c r="F345" t="str">
         <f>計算表!F345</f>
@@ -29656,7 +29688,7 @@
       </c>
       <c r="I345">
         <f>計算表!I345</f>
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J345">
         <f>計算表!J345</f>
@@ -29726,7 +29758,7 @@
       </c>
       <c r="H346">
         <f>計算表!H346</f>
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I346">
         <f>計算表!I346</f>
@@ -30301,7 +30333,8 @@
     <col min="3" max="3" width="21.140625" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="36.28515625" customWidth="1"/>
-    <col min="6" max="6" width="21.140625" customWidth="1"/>
+    <col min="6" max="6" width="35.5703125" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -30554,7 +30587,7 @@
         <v>50</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5">
         <v>20</v>
@@ -31919,10 +31952,10 @@
         <v>106</v>
       </c>
       <c r="G29">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="H29">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I29">
         <v>10</v>
@@ -32711,10 +32744,10 @@
         <v>145</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1082</v>
+        <v>1073</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>1083</v>
+        <v>1074</v>
       </c>
       <c r="G43">
         <v>2</v>
@@ -36179,13 +36212,13 @@
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>1066</v>
+        <v>1057</v>
       </c>
       <c r="C104" t="s">
         <v>293</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>1061</v>
+        <v>1052</v>
       </c>
       <c r="E104" t="s">
         <v>295</v>
@@ -36194,7 +36227,7 @@
         <v>296</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>1071</v>
+        <v>1062</v>
       </c>
       <c r="H104">
         <v>0</v>
@@ -36236,13 +36269,13 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>1066</v>
+        <v>1057</v>
       </c>
       <c r="C105" t="s">
         <v>293</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>1062</v>
+        <v>1053</v>
       </c>
       <c r="E105" t="s">
         <v>295</v>
@@ -36251,10 +36284,10 @@
         <v>296</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>1073</v>
+        <v>1064</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>1072</v>
+        <v>1063</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -36293,13 +36326,13 @@
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>1066</v>
+        <v>1057</v>
       </c>
       <c r="C106" t="s">
         <v>293</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>1063</v>
+        <v>1054</v>
       </c>
       <c r="E106" t="s">
         <v>295</v>
@@ -36308,13 +36341,13 @@
         <v>296</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>1070</v>
+        <v>1061</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>1074</v>
+        <v>1065</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>1069</v>
+        <v>1060</v>
       </c>
       <c r="J106">
         <v>0</v>
@@ -36350,13 +36383,13 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>1066</v>
+        <v>1057</v>
       </c>
       <c r="C107" t="s">
         <v>293</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>1064</v>
+        <v>1055</v>
       </c>
       <c r="E107" t="s">
         <v>295</v>
@@ -36365,16 +36398,16 @@
         <v>296</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>1077</v>
+        <v>1068</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>1074</v>
+        <v>1065</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>1076</v>
+        <v>1067</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>1075</v>
+        <v>1066</v>
       </c>
       <c r="K107">
         <v>0</v>
@@ -36407,13 +36440,13 @@
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>1066</v>
+        <v>1057</v>
       </c>
       <c r="C108" t="s">
         <v>293</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>1065</v>
+        <v>1056</v>
       </c>
       <c r="E108" t="s">
         <v>295</v>
@@ -36422,19 +36455,19 @@
         <v>296</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>1080</v>
+        <v>1071</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>1068</v>
+        <v>1059</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>1079</v>
+        <v>1070</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>1067</v>
+        <v>1058</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>1078</v>
+        <v>1069</v>
       </c>
       <c r="L108">
         <v>0</v>
@@ -38872,26 +38905,26 @@
       <c r="F151" t="s">
         <v>426</v>
       </c>
-      <c r="G151" t="s">
+      <c r="G151" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="I151" t="s">
         <v>427</v>
       </c>
-      <c r="H151" t="s">
+      <c r="J151" t="s">
         <v>428</v>
       </c>
-      <c r="I151" t="s">
+      <c r="K151" t="s">
         <v>429</v>
       </c>
-      <c r="J151" t="s">
+      <c r="L151" t="s">
         <v>430</v>
       </c>
-      <c r="K151" t="s">
+      <c r="M151" t="s">
         <v>431</v>
-      </c>
-      <c r="L151" t="s">
-        <v>432</v>
-      </c>
-      <c r="M151" t="s">
-        <v>433</v>
       </c>
       <c r="N151">
         <v>0</v>
@@ -38921,7 +38954,7 @@
         <v>423</v>
       </c>
       <c r="D152" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E152" t="s">
         <v>425</v>
@@ -38929,26 +38962,26 @@
       <c r="F152" t="s">
         <v>426</v>
       </c>
-      <c r="G152" t="s">
+      <c r="G152" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="I152" t="s">
+        <v>433</v>
+      </c>
+      <c r="J152" t="s">
+        <v>434</v>
+      </c>
+      <c r="K152" t="s">
         <v>435</v>
       </c>
-      <c r="H152" t="s">
+      <c r="L152" t="s">
         <v>436</v>
       </c>
-      <c r="I152" t="s">
+      <c r="M152" t="s">
         <v>437</v>
-      </c>
-      <c r="J152" t="s">
-        <v>438</v>
-      </c>
-      <c r="K152" t="s">
-        <v>439</v>
-      </c>
-      <c r="L152" t="s">
-        <v>440</v>
-      </c>
-      <c r="M152" t="s">
-        <v>441</v>
       </c>
       <c r="N152">
         <v>0</v>
@@ -38978,7 +39011,7 @@
         <v>423</v>
       </c>
       <c r="D153" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="E153" t="s">
         <v>425</v>
@@ -38986,26 +39019,26 @@
       <c r="F153" t="s">
         <v>426</v>
       </c>
-      <c r="G153" t="s">
-        <v>443</v>
-      </c>
-      <c r="H153" t="s">
-        <v>444</v>
-      </c>
-      <c r="I153" t="s">
-        <v>445</v>
+      <c r="G153" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>1075</v>
       </c>
       <c r="J153" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="K153" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="L153" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="M153" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="N153">
         <v>0</v>
@@ -39035,7 +39068,7 @@
         <v>423</v>
       </c>
       <c r="D154" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="E154" t="s">
         <v>425</v>
@@ -39043,26 +39076,26 @@
       <c r="F154" t="s">
         <v>426</v>
       </c>
-      <c r="G154" t="s">
-        <v>451</v>
-      </c>
-      <c r="H154" t="s">
-        <v>452</v>
+      <c r="G154" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>1082</v>
       </c>
       <c r="I154" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="J154" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="K154" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="L154" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="M154" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="N154">
         <v>0</v>
@@ -39092,7 +39125,7 @@
         <v>423</v>
       </c>
       <c r="D155" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="E155" t="s">
         <v>425</v>
@@ -39101,25 +39134,25 @@
         <v>426</v>
       </c>
       <c r="G155" t="s">
+        <v>444</v>
+      </c>
+      <c r="H155" t="s">
         <v>451</v>
       </c>
-      <c r="H155" t="s">
-        <v>459</v>
-      </c>
       <c r="I155" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="J155" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="K155" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="L155" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="M155" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="N155">
         <v>0</v>
@@ -39149,7 +39182,7 @@
         <v>423</v>
       </c>
       <c r="D156" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="E156" t="s">
         <v>425</v>
@@ -39158,25 +39191,25 @@
         <v>426</v>
       </c>
       <c r="G156" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="H156" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="I156" t="s">
         <v>268</v>
       </c>
       <c r="J156" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="K156" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="L156" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="M156" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="N156">
         <v>0</v>
@@ -39206,7 +39239,7 @@
         <v>423</v>
       </c>
       <c r="D157" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="E157" t="s">
         <v>425</v>
@@ -39215,25 +39248,25 @@
         <v>426</v>
       </c>
       <c r="G157" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="H157" t="s">
+        <v>458</v>
+      </c>
+      <c r="I157" t="s">
+        <v>464</v>
+      </c>
+      <c r="J157" t="s">
+        <v>465</v>
+      </c>
+      <c r="K157" t="s">
         <v>466</v>
       </c>
-      <c r="I157" t="s">
-        <v>472</v>
-      </c>
-      <c r="J157" t="s">
-        <v>473</v>
-      </c>
-      <c r="K157" t="s">
-        <v>474</v>
-      </c>
       <c r="L157" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="M157" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="N157">
         <v>0</v>
@@ -39263,7 +39296,7 @@
         <v>423</v>
       </c>
       <c r="D158" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="E158" t="s">
         <v>425</v>
@@ -39272,25 +39305,25 @@
         <v>426</v>
       </c>
       <c r="G158" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="H158" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="I158" t="s">
+        <v>464</v>
+      </c>
+      <c r="J158" t="s">
+        <v>470</v>
+      </c>
+      <c r="K158" t="s">
+        <v>471</v>
+      </c>
+      <c r="L158" t="s">
         <v>472</v>
       </c>
-      <c r="J158" t="s">
-        <v>478</v>
-      </c>
-      <c r="K158" t="s">
-        <v>479</v>
-      </c>
-      <c r="L158" t="s">
-        <v>480</v>
-      </c>
       <c r="M158" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="N158">
         <v>0</v>
@@ -39320,13 +39353,13 @@
         <v>423</v>
       </c>
       <c r="D159" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="E159" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="F159" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="G159">
         <v>551</v>
@@ -39374,16 +39407,16 @@
         <v>0</v>
       </c>
       <c r="C160" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="D160" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="E160" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="F160" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="G160">
         <v>2</v>
@@ -39431,16 +39464,16 @@
         <v>0</v>
       </c>
       <c r="C161" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="D161" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="E161" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="F161" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="G161">
         <v>4</v>
@@ -39488,16 +39521,16 @@
         <v>0</v>
       </c>
       <c r="C162" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="D162" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="E162" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="F162" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="G162">
         <v>6</v>
@@ -39545,16 +39578,16 @@
         <v>0</v>
       </c>
       <c r="C163" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="D163" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="E163" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="F163" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="G163">
         <v>8</v>
@@ -39602,16 +39635,16 @@
         <v>0</v>
       </c>
       <c r="C164" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="D164" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="E164" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="F164" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="G164">
         <v>10</v>
@@ -39659,16 +39692,16 @@
         <v>0</v>
       </c>
       <c r="C165" t="s">
+        <v>477</v>
+      </c>
+      <c r="D165" t="s">
         <v>485</v>
       </c>
-      <c r="D165" t="s">
-        <v>493</v>
-      </c>
       <c r="E165" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="F165" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="G165">
         <v>12</v>
@@ -39716,16 +39749,16 @@
         <v>0</v>
       </c>
       <c r="C166" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="D166" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="E166" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="F166" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="G166">
         <v>14</v>
@@ -39773,16 +39806,16 @@
         <v>0</v>
       </c>
       <c r="C167" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="D167" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="E167" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="F167" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="G167">
         <v>4</v>
@@ -39830,16 +39863,16 @@
         <v>0</v>
       </c>
       <c r="C168" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="D168" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="E168" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="F168" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="G168">
         <v>5</v>
@@ -39887,16 +39920,16 @@
         <v>0</v>
       </c>
       <c r="C169" t="s">
+        <v>487</v>
+      </c>
+      <c r="D169" t="s">
+        <v>494</v>
+      </c>
+      <c r="E169" t="s">
+        <v>492</v>
+      </c>
+      <c r="F169" t="s">
         <v>495</v>
-      </c>
-      <c r="D169" t="s">
-        <v>502</v>
-      </c>
-      <c r="E169" t="s">
-        <v>500</v>
-      </c>
-      <c r="F169" t="s">
-        <v>503</v>
       </c>
       <c r="G169">
         <v>10</v>
@@ -39944,16 +39977,16 @@
         <v>0</v>
       </c>
       <c r="C170" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="D170" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="E170" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="F170" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="G170">
         <v>0.5</v>
@@ -40001,16 +40034,16 @@
         <v>0</v>
       </c>
       <c r="C171" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="D171" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="E171" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="F171" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="G171">
         <v>100</v>
@@ -40058,16 +40091,16 @@
         <v>0</v>
       </c>
       <c r="C172" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="D172" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="E172" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="F172" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="G172">
         <v>92</v>
@@ -40115,16 +40148,16 @@
         <v>0</v>
       </c>
       <c r="C173" t="s">
+        <v>499</v>
+      </c>
+      <c r="D173" t="s">
+        <v>506</v>
+      </c>
+      <c r="E173" t="s">
         <v>507</v>
       </c>
-      <c r="D173" t="s">
-        <v>514</v>
-      </c>
-      <c r="E173" t="s">
-        <v>515</v>
-      </c>
       <c r="F173" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="G173">
         <v>78.099999999999994</v>
@@ -40172,16 +40205,16 @@
         <v>0</v>
       </c>
       <c r="C174" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="D174" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="E174" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="F174" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="G174">
         <v>72.11</v>
@@ -40229,16 +40262,16 @@
         <v>0</v>
       </c>
       <c r="C175" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="D175" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="E175" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="F175" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="G175">
         <v>74.349999999999994</v>
@@ -40286,16 +40319,16 @@
         <v>0</v>
       </c>
       <c r="C176" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="D176" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="E176" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="F176" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="G176">
         <v>76.87</v>
@@ -40343,16 +40376,16 @@
         <v>0</v>
       </c>
       <c r="C177" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="D177" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="E177" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="F177" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="G177">
         <v>69.92</v>
@@ -40400,16 +40433,16 @@
         <v>0</v>
       </c>
       <c r="C178" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="D178" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="E178" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="F178" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="G178">
         <v>64.22</v>
@@ -40457,16 +40490,16 @@
         <v>0</v>
       </c>
       <c r="C179" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="D179" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="E179" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="F179" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="G179">
         <v>59.92</v>
@@ -40514,16 +40547,16 @@
         <v>0</v>
       </c>
       <c r="C180" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="D180" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="E180" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="F180" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="G180">
         <v>54.72</v>
@@ -40571,16 +40604,16 @@
         <v>0</v>
       </c>
       <c r="C181" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="D181" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="E181" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="F181" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="G181">
         <v>1.35</v>
@@ -40628,16 +40661,16 @@
         <v>0</v>
       </c>
       <c r="C182" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="D182" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="E182" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="F182" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="G182">
         <v>0.5</v>
@@ -40685,16 +40718,16 @@
         <v>0</v>
       </c>
       <c r="C183" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="D183" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="E183" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="F183" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="G183">
         <v>4000</v>
@@ -40742,16 +40775,16 @@
         <v>0</v>
       </c>
       <c r="C184" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="D184" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="E184" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="F184" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="G184">
         <v>4</v>
@@ -40799,16 +40832,16 @@
         <v>0</v>
       </c>
       <c r="C185" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="D185" t="s">
         <v>260</v>
       </c>
       <c r="E185" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="F185" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="G185">
         <v>200</v>
@@ -40856,16 +40889,16 @@
         <v>0</v>
       </c>
       <c r="C186" t="s">
+        <v>539</v>
+      </c>
+      <c r="D186" t="s">
+        <v>545</v>
+      </c>
+      <c r="E186" t="s">
+        <v>546</v>
+      </c>
+      <c r="F186" t="s">
         <v>547</v>
-      </c>
-      <c r="D186" t="s">
-        <v>553</v>
-      </c>
-      <c r="E186" t="s">
-        <v>554</v>
-      </c>
-      <c r="F186" t="s">
-        <v>555</v>
       </c>
       <c r="G186">
         <v>4</v>
@@ -40913,16 +40946,16 @@
         <v>0</v>
       </c>
       <c r="C187" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="D187" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="E187" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="F187" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="G187">
         <v>3</v>
@@ -40970,16 +41003,16 @@
         <v>0</v>
       </c>
       <c r="C188" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="D188" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="E188" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="F188" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="G188">
         <v>4</v>
@@ -41027,37 +41060,37 @@
         <v>0</v>
       </c>
       <c r="C189" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="D189" t="s">
         <v>424</v>
       </c>
       <c r="E189" t="s">
+        <v>555</v>
+      </c>
+      <c r="F189" t="s">
+        <v>556</v>
+      </c>
+      <c r="G189" t="s">
+        <v>557</v>
+      </c>
+      <c r="H189" t="s">
+        <v>558</v>
+      </c>
+      <c r="I189" t="s">
+        <v>559</v>
+      </c>
+      <c r="J189" t="s">
+        <v>560</v>
+      </c>
+      <c r="K189" t="s">
+        <v>561</v>
+      </c>
+      <c r="L189" t="s">
+        <v>562</v>
+      </c>
+      <c r="M189" t="s">
         <v>563</v>
-      </c>
-      <c r="F189" t="s">
-        <v>564</v>
-      </c>
-      <c r="G189" t="s">
-        <v>565</v>
-      </c>
-      <c r="H189" t="s">
-        <v>566</v>
-      </c>
-      <c r="I189" t="s">
-        <v>567</v>
-      </c>
-      <c r="J189" t="s">
-        <v>568</v>
-      </c>
-      <c r="K189" t="s">
-        <v>569</v>
-      </c>
-      <c r="L189" t="s">
-        <v>570</v>
-      </c>
-      <c r="M189" t="s">
-        <v>571</v>
       </c>
       <c r="N189">
         <v>0</v>
@@ -41084,37 +41117,37 @@
         <v>0</v>
       </c>
       <c r="C190" t="s">
+        <v>554</v>
+      </c>
+      <c r="D190" t="s">
+        <v>432</v>
+      </c>
+      <c r="E190" t="s">
+        <v>555</v>
+      </c>
+      <c r="F190" t="s">
+        <v>556</v>
+      </c>
+      <c r="G190" t="s">
+        <v>557</v>
+      </c>
+      <c r="H190" t="s">
+        <v>558</v>
+      </c>
+      <c r="I190" t="s">
+        <v>559</v>
+      </c>
+      <c r="J190" t="s">
+        <v>560</v>
+      </c>
+      <c r="K190" t="s">
+        <v>561</v>
+      </c>
+      <c r="L190" t="s">
         <v>562</v>
       </c>
-      <c r="D190" t="s">
-        <v>434</v>
-      </c>
-      <c r="E190" t="s">
+      <c r="M190" t="s">
         <v>563</v>
-      </c>
-      <c r="F190" t="s">
-        <v>564</v>
-      </c>
-      <c r="G190" t="s">
-        <v>565</v>
-      </c>
-      <c r="H190" t="s">
-        <v>566</v>
-      </c>
-      <c r="I190" t="s">
-        <v>567</v>
-      </c>
-      <c r="J190" t="s">
-        <v>568</v>
-      </c>
-      <c r="K190" t="s">
-        <v>569</v>
-      </c>
-      <c r="L190" t="s">
-        <v>570</v>
-      </c>
-      <c r="M190" t="s">
-        <v>571</v>
       </c>
       <c r="N190">
         <v>0</v>
@@ -41141,37 +41174,37 @@
         <v>0</v>
       </c>
       <c r="C191" t="s">
+        <v>554</v>
+      </c>
+      <c r="D191" t="s">
+        <v>438</v>
+      </c>
+      <c r="E191" t="s">
+        <v>555</v>
+      </c>
+      <c r="F191" t="s">
+        <v>556</v>
+      </c>
+      <c r="G191" t="s">
+        <v>564</v>
+      </c>
+      <c r="H191" t="s">
+        <v>565</v>
+      </c>
+      <c r="I191" t="s">
+        <v>559</v>
+      </c>
+      <c r="J191" t="s">
+        <v>560</v>
+      </c>
+      <c r="K191" t="s">
+        <v>561</v>
+      </c>
+      <c r="L191" t="s">
         <v>562</v>
       </c>
-      <c r="D191" t="s">
-        <v>442</v>
-      </c>
-      <c r="E191" t="s">
+      <c r="M191" t="s">
         <v>563</v>
-      </c>
-      <c r="F191" t="s">
-        <v>564</v>
-      </c>
-      <c r="G191" t="s">
-        <v>572</v>
-      </c>
-      <c r="H191" t="s">
-        <v>573</v>
-      </c>
-      <c r="I191" t="s">
-        <v>567</v>
-      </c>
-      <c r="J191" t="s">
-        <v>568</v>
-      </c>
-      <c r="K191" t="s">
-        <v>569</v>
-      </c>
-      <c r="L191" t="s">
-        <v>570</v>
-      </c>
-      <c r="M191" t="s">
-        <v>571</v>
       </c>
       <c r="N191">
         <v>0</v>
@@ -41198,37 +41231,37 @@
         <v>0</v>
       </c>
       <c r="C192" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="D192" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="E192" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="F192" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="G192" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="H192" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="I192" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="J192" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="K192" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="L192" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="M192" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="N192">
         <v>0</v>
@@ -41255,37 +41288,37 @@
         <v>0</v>
       </c>
       <c r="C193" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="D193" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="E193" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="F193" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="G193" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="H193" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="I193" t="s">
+        <v>567</v>
+      </c>
+      <c r="J193" t="s">
+        <v>574</v>
+      </c>
+      <c r="K193" t="s">
         <v>575</v>
       </c>
-      <c r="J193" t="s">
-        <v>582</v>
-      </c>
-      <c r="K193" t="s">
-        <v>583</v>
-      </c>
       <c r="L193" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="M193" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="N193">
         <v>0</v>
@@ -41312,37 +41345,37 @@
         <v>0</v>
       </c>
       <c r="C194" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="D194" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="E194" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="F194" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="G194" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="H194" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="I194" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="J194" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="K194" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="L194" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="M194" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="N194">
         <v>0</v>
@@ -41369,37 +41402,37 @@
         <v>0</v>
       </c>
       <c r="C195" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="D195" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="E195" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="F195" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="G195" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="H195" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="I195" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="J195" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="K195" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="L195" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="M195" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="N195">
         <v>0</v>
@@ -41426,37 +41459,37 @@
         <v>0</v>
       </c>
       <c r="C196" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="D196" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="E196" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="F196" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="G196" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="H196" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="I196" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="J196" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="K196" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="L196" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="M196" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="N196">
         <v>0</v>
@@ -41483,16 +41516,16 @@
         <v>0</v>
       </c>
       <c r="C197" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="D197" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="E197" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="F197" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="G197">
         <v>0</v>
@@ -41540,16 +41573,16 @@
         <v>0</v>
       </c>
       <c r="C198" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="D198" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="E198" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="F198" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="G198">
         <v>1.35</v>
@@ -41597,16 +41630,16 @@
         <v>0</v>
       </c>
       <c r="C199" t="s">
+        <v>596</v>
+      </c>
+      <c r="D199" t="s">
+        <v>603</v>
+      </c>
+      <c r="E199" t="s">
         <v>604</v>
       </c>
-      <c r="D199" t="s">
-        <v>611</v>
-      </c>
-      <c r="E199" t="s">
-        <v>612</v>
-      </c>
       <c r="F199" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="G199">
         <v>0.05</v>
@@ -41654,16 +41687,16 @@
         <v>0</v>
       </c>
       <c r="C200" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="D200" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="E200" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="F200" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="G200">
         <v>2</v>
@@ -41711,16 +41744,16 @@
         <v>0</v>
       </c>
       <c r="C201" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="D201" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="E201" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="F201" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="G201">
         <v>0</v>
@@ -41768,16 +41801,16 @@
         <v>0</v>
       </c>
       <c r="C202" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="D202" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="E202" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="F202" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="G202">
         <v>5</v>
@@ -41825,16 +41858,16 @@
         <v>0</v>
       </c>
       <c r="C203" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="D203" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="E203" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="F203" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="G203">
         <v>8</v>
@@ -41882,16 +41915,16 @@
         <v>0</v>
       </c>
       <c r="C204" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="D204" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="E204" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="F204" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="G204">
         <v>1</v>
@@ -41939,16 +41972,16 @@
         <v>0</v>
       </c>
       <c r="C205" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="D205" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="E205" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="F205" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="G205">
         <v>0.15</v>
@@ -41996,16 +42029,16 @@
         <v>0</v>
       </c>
       <c r="C206" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="D206" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="E206" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="F206" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="G206">
         <v>2</v>
@@ -42053,16 +42086,16 @@
         <v>0</v>
       </c>
       <c r="C207" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="D207" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="E207" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="F207" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="G207">
         <v>3</v>
@@ -42110,16 +42143,16 @@
         <v>0</v>
       </c>
       <c r="C208" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="D208" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="E208" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="F208" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="G208">
         <v>5</v>
@@ -42167,16 +42200,16 @@
         <v>0</v>
       </c>
       <c r="C209" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="D209" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="E209" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="F209" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="G209">
         <v>0</v>
@@ -42224,16 +42257,16 @@
         <v>0</v>
       </c>
       <c r="C210" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="D210" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="E210" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="F210" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="G210">
         <v>5</v>
@@ -42281,16 +42314,16 @@
         <v>0</v>
       </c>
       <c r="C211" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="D211" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="E211" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="F211" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="G211">
         <v>55</v>
@@ -42338,16 +42371,16 @@
         <v>0</v>
       </c>
       <c r="C212" t="s">
+        <v>637</v>
+      </c>
+      <c r="D212" t="s">
+        <v>644</v>
+      </c>
+      <c r="E212" t="s">
         <v>645</v>
       </c>
-      <c r="D212" t="s">
-        <v>652</v>
-      </c>
-      <c r="E212" t="s">
-        <v>653</v>
-      </c>
       <c r="F212" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="G212">
         <v>5000000</v>
@@ -42395,13 +42428,13 @@
         <v>0</v>
       </c>
       <c r="C213" t="s">
+        <v>637</v>
+      </c>
+      <c r="D213" t="s">
+        <v>647</v>
+      </c>
+      <c r="E213" t="s">
         <v>645</v>
-      </c>
-      <c r="D213" t="s">
-        <v>655</v>
-      </c>
-      <c r="E213" t="s">
-        <v>653</v>
       </c>
       <c r="F213">
         <v>0</v>
@@ -42452,16 +42485,16 @@
         <v>0</v>
       </c>
       <c r="C214" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="D214" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
       <c r="E214" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="F214" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="G214">
         <v>3</v>
@@ -42509,16 +42542,16 @@
         <v>0</v>
       </c>
       <c r="C215" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="D215" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="E215" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="F215" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="G215">
         <v>27</v>
@@ -42566,16 +42599,16 @@
         <v>0</v>
       </c>
       <c r="C216" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="D216" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="E216" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="F216" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="G216">
         <v>36</v>
@@ -42623,16 +42656,16 @@
         <v>0</v>
       </c>
       <c r="C217" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="D217" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="E217" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="F217" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="G217">
         <v>3</v>
@@ -42680,16 +42713,16 @@
         <v>0</v>
       </c>
       <c r="C218" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="D218" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="E218" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="F218" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="G218">
         <v>50</v>
@@ -42737,16 +42770,16 @@
         <v>0</v>
       </c>
       <c r="C219" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="D219" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="E219" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="F219" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="G219">
         <v>1000000</v>
@@ -42794,13 +42827,13 @@
         <v>0</v>
       </c>
       <c r="C220" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="D220" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="E220" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
       <c r="F220">
         <v>0</v>
@@ -42851,16 +42884,16 @@
         <v>0</v>
       </c>
       <c r="C221" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="D221" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="E221" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="F221" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="G221">
         <v>3</v>
@@ -42908,16 +42941,16 @@
         <v>0</v>
       </c>
       <c r="C222" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="D222" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="E222" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="F222" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="G222">
         <v>6</v>
@@ -42965,16 +42998,16 @@
         <v>0</v>
       </c>
       <c r="C223" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="D223" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="E223" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="F223" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="G223">
         <v>30</v>
@@ -43022,13 +43055,13 @@
         <v>0</v>
       </c>
       <c r="C224" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="D224" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="E224" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="F224">
         <v>0</v>
@@ -43079,13 +43112,13 @@
         <v>0</v>
       </c>
       <c r="C225" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="D225" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="E225" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="F225">
         <v>0</v>
@@ -43136,16 +43169,16 @@
         <v>0</v>
       </c>
       <c r="C226" t="s">
+        <v>673</v>
+      </c>
+      <c r="D226" t="s">
+        <v>680</v>
+      </c>
+      <c r="E226" t="s">
         <v>681</v>
       </c>
-      <c r="D226" t="s">
-        <v>688</v>
-      </c>
-      <c r="E226" t="s">
-        <v>689</v>
-      </c>
       <c r="F226" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="G226">
         <v>0</v>
@@ -43193,13 +43226,13 @@
         <v>0</v>
       </c>
       <c r="C227" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="D227" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="E227" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="F227">
         <v>0</v>
@@ -43250,16 +43283,16 @@
         <v>0</v>
       </c>
       <c r="C228" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="D228" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="E228" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="F228" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="G228">
         <v>9</v>
@@ -43307,16 +43340,16 @@
         <v>0</v>
       </c>
       <c r="C229" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="D229" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="E229" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="F229" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="G229">
         <v>1</v>
@@ -43364,16 +43397,16 @@
         <v>0</v>
       </c>
       <c r="C230" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="D230" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="E230" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="F230" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="G230">
         <v>5</v>
@@ -43421,16 +43454,16 @@
         <v>0</v>
       </c>
       <c r="C231" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="D231" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="E231" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="F231" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="G231">
         <v>0</v>
@@ -43478,16 +43511,16 @@
         <v>0</v>
       </c>
       <c r="C232" t="s">
+        <v>690</v>
+      </c>
+      <c r="D232" t="s">
+        <v>697</v>
+      </c>
+      <c r="E232" t="s">
         <v>698</v>
       </c>
-      <c r="D232" t="s">
-        <v>705</v>
-      </c>
-      <c r="E232" t="s">
-        <v>706</v>
-      </c>
       <c r="F232" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="G232">
         <v>0</v>
@@ -43535,16 +43568,16 @@
         <v>0</v>
       </c>
       <c r="C233" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="D233" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="E233" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="F233" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="G233">
         <v>0</v>
@@ -43592,16 +43625,16 @@
         <v>0</v>
       </c>
       <c r="C234" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="D234" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="E234" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="F234" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="G234">
         <v>2</v>
@@ -43649,16 +43682,16 @@
         <v>0</v>
       </c>
       <c r="C235" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="D235" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="E235" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="F235" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="G235">
         <v>10000</v>
@@ -43706,16 +43739,16 @@
         <v>0</v>
       </c>
       <c r="C236" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="D236" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="E236" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="F236" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="G236">
         <v>20000</v>
@@ -43763,13 +43796,13 @@
         <v>0</v>
       </c>
       <c r="C237" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="D237" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="E237" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="F237">
         <v>0</v>
@@ -43820,16 +43853,16 @@
         <v>0</v>
       </c>
       <c r="C238" t="s">
+        <v>710</v>
+      </c>
+      <c r="D238" t="s">
+        <v>716</v>
+      </c>
+      <c r="E238" t="s">
+        <v>717</v>
+      </c>
+      <c r="F238" t="s">
         <v>718</v>
-      </c>
-      <c r="D238" t="s">
-        <v>724</v>
-      </c>
-      <c r="E238" t="s">
-        <v>725</v>
-      </c>
-      <c r="F238" t="s">
-        <v>726</v>
       </c>
       <c r="G238">
         <v>100</v>
@@ -43877,16 +43910,16 @@
         <v>0</v>
       </c>
       <c r="C239" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="D239" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="E239" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="F239" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="G239">
         <v>10000</v>
@@ -43934,13 +43967,13 @@
         <v>0</v>
       </c>
       <c r="C240" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="D240" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="E240" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="F240">
         <v>0</v>
@@ -43991,16 +44024,16 @@
         <v>0</v>
       </c>
       <c r="C241" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="D241" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="E241" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="F241" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="G241">
         <v>0.2</v>
@@ -44048,16 +44081,16 @@
         <v>0</v>
       </c>
       <c r="C242" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="D242" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
       <c r="E242" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="F242" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="G242">
         <v>2</v>
@@ -44105,16 +44138,16 @@
         <v>0</v>
       </c>
       <c r="C243" t="s">
+        <v>724</v>
+      </c>
+      <c r="D243" t="s">
+        <v>731</v>
+      </c>
+      <c r="E243" t="s">
         <v>732</v>
       </c>
-      <c r="D243" t="s">
-        <v>739</v>
-      </c>
-      <c r="E243" t="s">
-        <v>740</v>
-      </c>
       <c r="F243" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="G243">
         <v>3</v>
@@ -44162,16 +44195,16 @@
         <v>0</v>
       </c>
       <c r="C244" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="D244" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="E244" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="F244" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="G244">
         <v>3</v>
@@ -44219,16 +44252,16 @@
         <v>0</v>
       </c>
       <c r="C245" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="D245" t="s">
-        <v>745</v>
+        <v>737</v>
       </c>
       <c r="E245" t="s">
-        <v>746</v>
+        <v>738</v>
       </c>
       <c r="F245" t="s">
-        <v>747</v>
+        <v>739</v>
       </c>
       <c r="G245">
         <v>100</v>
@@ -44276,16 +44309,16 @@
         <v>0</v>
       </c>
       <c r="C246" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="D246" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="E246" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="F246" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="G246">
         <v>9</v>
@@ -44333,16 +44366,16 @@
         <v>0</v>
       </c>
       <c r="C247" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="D247" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="E247" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="F247" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
       <c r="G247">
         <v>0.7</v>
@@ -44390,16 +44423,16 @@
         <v>0</v>
       </c>
       <c r="C248" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="D248" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="E248" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="F248" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="G248">
         <v>0.7</v>
@@ -44447,16 +44480,16 @@
         <v>0</v>
       </c>
       <c r="C249" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="D249" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="E249" t="s">
-        <v>758</v>
+        <v>750</v>
       </c>
       <c r="F249" t="s">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="G249">
         <v>10</v>
@@ -44504,16 +44537,16 @@
         <v>0</v>
       </c>
       <c r="C250" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
       <c r="D250" t="s">
-        <v>760</v>
+        <v>752</v>
       </c>
       <c r="E250" t="s">
-        <v>761</v>
+        <v>753</v>
       </c>
       <c r="F250" t="s">
-        <v>762</v>
+        <v>754</v>
       </c>
       <c r="G250">
         <v>0</v>
@@ -44561,16 +44594,16 @@
         <v>0</v>
       </c>
       <c r="C251" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="D251" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="E251" t="s">
-        <v>765</v>
+        <v>757</v>
       </c>
       <c r="F251" t="s">
-        <v>766</v>
+        <v>758</v>
       </c>
       <c r="G251">
         <v>10000</v>
@@ -44618,16 +44651,16 @@
         <v>0</v>
       </c>
       <c r="C252" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="D252" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="E252" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
       <c r="F252" t="s">
-        <v>769</v>
+        <v>761</v>
       </c>
       <c r="G252">
         <v>5000</v>
@@ -44675,13 +44708,13 @@
         <v>0</v>
       </c>
       <c r="C253" t="s">
+        <v>755</v>
+      </c>
+      <c r="D253" t="s">
+        <v>762</v>
+      </c>
+      <c r="E253" t="s">
         <v>763</v>
-      </c>
-      <c r="D253" t="s">
-        <v>770</v>
-      </c>
-      <c r="E253" t="s">
-        <v>771</v>
       </c>
       <c r="F253">
         <v>0</v>
@@ -44732,16 +44765,16 @@
         <v>0</v>
       </c>
       <c r="C254" t="s">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="D254" t="s">
-        <v>772</v>
+        <v>764</v>
       </c>
       <c r="E254" t="s">
-        <v>773</v>
+        <v>765</v>
       </c>
       <c r="F254" t="s">
-        <v>774</v>
+        <v>766</v>
       </c>
       <c r="G254">
         <v>10000</v>
@@ -44789,22 +44822,22 @@
         <v>0</v>
       </c>
       <c r="C255" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="D255" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
       <c r="E255" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="F255" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="G255" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="H255" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="I255">
         <v>0</v>
@@ -44846,25 +44879,25 @@
         <v>0</v>
       </c>
       <c r="C256" t="s">
+        <v>767</v>
+      </c>
+      <c r="D256" t="s">
+        <v>773</v>
+      </c>
+      <c r="E256" t="s">
+        <v>769</v>
+      </c>
+      <c r="F256" t="s">
+        <v>770</v>
+      </c>
+      <c r="G256" t="s">
+        <v>771</v>
+      </c>
+      <c r="H256" t="s">
+        <v>774</v>
+      </c>
+      <c r="I256" t="s">
         <v>775</v>
-      </c>
-      <c r="D256" t="s">
-        <v>781</v>
-      </c>
-      <c r="E256" t="s">
-        <v>777</v>
-      </c>
-      <c r="F256" t="s">
-        <v>778</v>
-      </c>
-      <c r="G256" t="s">
-        <v>779</v>
-      </c>
-      <c r="H256" t="s">
-        <v>782</v>
-      </c>
-      <c r="I256" t="s">
-        <v>783</v>
       </c>
       <c r="J256">
         <v>0</v>
@@ -44903,28 +44936,28 @@
         <v>0</v>
       </c>
       <c r="C257" t="s">
+        <v>767</v>
+      </c>
+      <c r="D257" t="s">
+        <v>776</v>
+      </c>
+      <c r="E257" t="s">
+        <v>769</v>
+      </c>
+      <c r="F257" t="s">
+        <v>770</v>
+      </c>
+      <c r="G257" t="s">
+        <v>771</v>
+      </c>
+      <c r="H257" t="s">
+        <v>777</v>
+      </c>
+      <c r="I257" t="s">
         <v>775</v>
       </c>
-      <c r="D257" t="s">
-        <v>784</v>
-      </c>
-      <c r="E257" t="s">
-        <v>777</v>
-      </c>
-      <c r="F257" t="s">
+      <c r="J257" t="s">
         <v>778</v>
-      </c>
-      <c r="G257" t="s">
-        <v>779</v>
-      </c>
-      <c r="H257" t="s">
-        <v>785</v>
-      </c>
-      <c r="I257" t="s">
-        <v>783</v>
-      </c>
-      <c r="J257" t="s">
-        <v>786</v>
       </c>
       <c r="K257">
         <v>0</v>
@@ -44960,28 +44993,28 @@
         <v>0</v>
       </c>
       <c r="C258" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="D258" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="E258" t="s">
+        <v>769</v>
+      </c>
+      <c r="F258" t="s">
+        <v>770</v>
+      </c>
+      <c r="G258" t="s">
+        <v>780</v>
+      </c>
+      <c r="H258" t="s">
         <v>777</v>
       </c>
-      <c r="F258" t="s">
+      <c r="I258" t="s">
+        <v>781</v>
+      </c>
+      <c r="J258" t="s">
         <v>778</v>
-      </c>
-      <c r="G258" t="s">
-        <v>788</v>
-      </c>
-      <c r="H258" t="s">
-        <v>785</v>
-      </c>
-      <c r="I258" t="s">
-        <v>789</v>
-      </c>
-      <c r="J258" t="s">
-        <v>786</v>
       </c>
       <c r="K258">
         <v>0</v>
@@ -45017,28 +45050,28 @@
         <v>0</v>
       </c>
       <c r="C259" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="D259" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="E259" t="s">
+        <v>769</v>
+      </c>
+      <c r="F259" t="s">
+        <v>770</v>
+      </c>
+      <c r="G259" t="s">
+        <v>783</v>
+      </c>
+      <c r="H259" t="s">
         <v>777</v>
       </c>
-      <c r="F259" t="s">
-        <v>778</v>
-      </c>
-      <c r="G259" t="s">
-        <v>791</v>
-      </c>
-      <c r="H259" t="s">
-        <v>785</v>
-      </c>
       <c r="I259" t="s">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="J259" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="K259">
         <v>0</v>
@@ -45074,31 +45107,31 @@
         <v>0</v>
       </c>
       <c r="C260" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="D260" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="E260" t="s">
+        <v>769</v>
+      </c>
+      <c r="F260" t="s">
+        <v>770</v>
+      </c>
+      <c r="G260" t="s">
+        <v>786</v>
+      </c>
+      <c r="H260" t="s">
         <v>777</v>
       </c>
-      <c r="F260" t="s">
-        <v>778</v>
-      </c>
-      <c r="G260" t="s">
-        <v>794</v>
-      </c>
-      <c r="H260" t="s">
-        <v>785</v>
-      </c>
       <c r="I260" t="s">
-        <v>789</v>
+        <v>781</v>
       </c>
       <c r="J260" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="K260" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="L260">
         <v>0</v>
@@ -45131,31 +45164,31 @@
         <v>0</v>
       </c>
       <c r="C261" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="D261" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="E261" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="F261" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="G261" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="H261" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="I261" t="s">
+        <v>784</v>
+      </c>
+      <c r="J261" t="s">
+        <v>791</v>
+      </c>
+      <c r="K261" t="s">
         <v>792</v>
-      </c>
-      <c r="J261" t="s">
-        <v>799</v>
-      </c>
-      <c r="K261" t="s">
-        <v>800</v>
       </c>
       <c r="L261">
         <v>0</v>
@@ -45188,31 +45221,31 @@
         <v>0</v>
       </c>
       <c r="C262" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="D262" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="E262" t="s">
+        <v>769</v>
+      </c>
+      <c r="F262" t="s">
+        <v>770</v>
+      </c>
+      <c r="G262" t="s">
         <v>777</v>
       </c>
-      <c r="F262" t="s">
-        <v>778</v>
-      </c>
-      <c r="G262" t="s">
-        <v>785</v>
-      </c>
       <c r="H262" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="I262" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="J262" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="K262" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="L262">
         <v>0</v>
@@ -45245,31 +45278,31 @@
         <v>0</v>
       </c>
       <c r="C263" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="D263" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="E263" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="F263" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="G263" t="s">
+        <v>790</v>
+      </c>
+      <c r="H263" t="s">
+        <v>796</v>
+      </c>
+      <c r="I263" t="s">
+        <v>791</v>
+      </c>
+      <c r="J263" t="s">
+        <v>797</v>
+      </c>
+      <c r="K263" t="s">
         <v>798</v>
-      </c>
-      <c r="H263" t="s">
-        <v>804</v>
-      </c>
-      <c r="I263" t="s">
-        <v>799</v>
-      </c>
-      <c r="J263" t="s">
-        <v>805</v>
-      </c>
-      <c r="K263" t="s">
-        <v>806</v>
       </c>
       <c r="L263">
         <v>0</v>
@@ -45302,31 +45335,31 @@
         <v>0</v>
       </c>
       <c r="C264" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="D264" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="E264" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="F264" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="G264" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
       <c r="H264" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
       <c r="I264" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
       <c r="J264" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="K264" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
       <c r="L264">
         <v>0</v>
@@ -45359,31 +45392,31 @@
         <v>0</v>
       </c>
       <c r="C265" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="D265" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="E265" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="F265" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="G265" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
       <c r="H265" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
       <c r="I265" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="J265" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="K265" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
       <c r="L265">
         <v>0</v>
@@ -45416,31 +45449,31 @@
         <v>0</v>
       </c>
       <c r="C266" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="D266" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="E266" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="F266" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="G266" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
       <c r="H266" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="I266" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="J266" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="K266" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="L266">
         <v>0</v>
@@ -45473,31 +45506,31 @@
         <v>0</v>
       </c>
       <c r="C267" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="D267" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="E267" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="F267" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="G267" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="H267" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="I267" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="J267" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="K267" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="L267">
         <v>0</v>
@@ -45530,31 +45563,31 @@
         <v>0</v>
       </c>
       <c r="C268" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="D268" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="E268" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="F268" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="G268" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="H268" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="I268" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="J268" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="K268" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="L268">
         <v>0</v>
@@ -45587,31 +45620,31 @@
         <v>0</v>
       </c>
       <c r="C269" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="D269" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="E269" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="F269" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="G269" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="H269" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="I269" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="J269" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="K269" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="L269">
         <v>0</v>
@@ -45644,31 +45677,31 @@
         <v>0</v>
       </c>
       <c r="C270" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="D270" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="E270" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="F270" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="G270" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="H270" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="I270" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="J270" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="K270" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="L270">
         <v>0</v>
@@ -45701,31 +45734,31 @@
         <v>0</v>
       </c>
       <c r="C271" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="D271" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="E271" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="F271" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="G271" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="H271" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="I271" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="J271" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="K271" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="L271">
         <v>0</v>
@@ -45758,34 +45791,34 @@
         <v>0</v>
       </c>
       <c r="C272" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="D272" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="E272" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="F272" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="G272" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="H272" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="I272" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="J272" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="K272" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="L272" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="M272">
         <v>0</v>
@@ -45815,34 +45848,34 @@
         <v>0</v>
       </c>
       <c r="C273" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="D273" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="E273" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="F273" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="G273" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="H273" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="I273" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="J273" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="K273" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="L273" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="M273">
         <v>0</v>
@@ -45872,34 +45905,34 @@
         <v>0</v>
       </c>
       <c r="C274" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="D274" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
       <c r="E274" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="F274" t="s">
-        <v>778</v>
+        <v>770</v>
       </c>
       <c r="G274" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="H274" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="I274" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="J274" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="K274" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="L274" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="M274">
         <v>0</v>
@@ -45929,28 +45962,28 @@
         <v>0</v>
       </c>
       <c r="C275" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="D275" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
       <c r="E275" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="F275" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="G275" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="H275" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="I275" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="J275" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
       <c r="K275">
         <v>0</v>
@@ -45986,28 +46019,28 @@
         <v>0</v>
       </c>
       <c r="C276" t="s">
+        <v>838</v>
+      </c>
+      <c r="D276" t="s">
+        <v>773</v>
+      </c>
+      <c r="E276" t="s">
+        <v>839</v>
+      </c>
+      <c r="F276" t="s">
+        <v>840</v>
+      </c>
+      <c r="G276" t="s">
+        <v>845</v>
+      </c>
+      <c r="H276" t="s">
+        <v>842</v>
+      </c>
+      <c r="I276" t="s">
         <v>846</v>
       </c>
-      <c r="D276" t="s">
-        <v>781</v>
-      </c>
-      <c r="E276" t="s">
+      <c r="J276" t="s">
         <v>847</v>
-      </c>
-      <c r="F276" t="s">
-        <v>848</v>
-      </c>
-      <c r="G276" t="s">
-        <v>853</v>
-      </c>
-      <c r="H276" t="s">
-        <v>850</v>
-      </c>
-      <c r="I276" t="s">
-        <v>854</v>
-      </c>
-      <c r="J276" t="s">
-        <v>855</v>
       </c>
       <c r="K276">
         <v>0</v>
@@ -46043,28 +46076,28 @@
         <v>0</v>
       </c>
       <c r="C277" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="D277" t="s">
-        <v>784</v>
+        <v>776</v>
       </c>
       <c r="E277" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="F277" t="s">
+        <v>840</v>
+      </c>
+      <c r="G277" t="s">
         <v>848</v>
       </c>
-      <c r="G277" t="s">
-        <v>856</v>
-      </c>
       <c r="H277" t="s">
+        <v>842</v>
+      </c>
+      <c r="I277" t="s">
+        <v>849</v>
+      </c>
+      <c r="J277" t="s">
         <v>850</v>
-      </c>
-      <c r="I277" t="s">
-        <v>857</v>
-      </c>
-      <c r="J277" t="s">
-        <v>858</v>
       </c>
       <c r="K277">
         <v>0</v>
@@ -46100,31 +46133,31 @@
         <v>0</v>
       </c>
       <c r="C278" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="D278" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="E278" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="F278" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="G278" t="s">
-        <v>859</v>
+        <v>851</v>
       </c>
       <c r="H278" t="s">
+        <v>842</v>
+      </c>
+      <c r="I278" t="s">
+        <v>849</v>
+      </c>
+      <c r="J278" t="s">
         <v>850</v>
       </c>
-      <c r="I278" t="s">
-        <v>857</v>
-      </c>
-      <c r="J278" t="s">
-        <v>858</v>
-      </c>
       <c r="K278" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
       <c r="L278">
         <v>0</v>
@@ -46157,31 +46190,31 @@
         <v>0</v>
       </c>
       <c r="C279" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="D279" t="s">
-        <v>790</v>
+        <v>782</v>
       </c>
       <c r="E279" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="F279" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="G279" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
       <c r="H279" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="I279" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
       <c r="J279" t="s">
-        <v>862</v>
+        <v>854</v>
       </c>
       <c r="K279" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="L279">
         <v>0</v>
@@ -46214,31 +46247,31 @@
         <v>0</v>
       </c>
       <c r="C280" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="D280" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="E280" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="F280" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="G280" t="s">
-        <v>864</v>
+        <v>856</v>
       </c>
       <c r="H280" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="I280" t="s">
+        <v>849</v>
+      </c>
+      <c r="J280" t="s">
         <v>857</v>
       </c>
-      <c r="J280" t="s">
-        <v>865</v>
-      </c>
       <c r="K280" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="L280">
         <v>0</v>
@@ -46271,31 +46304,31 @@
         <v>0</v>
       </c>
       <c r="C281" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="D281" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
       <c r="E281" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="F281" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="G281" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="H281" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="I281" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="J281" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="K281" t="s">
-        <v>870</v>
+        <v>862</v>
       </c>
       <c r="L281">
         <v>0</v>
@@ -46328,31 +46361,31 @@
         <v>0</v>
       </c>
       <c r="C282" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="D282" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="E282" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="F282" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="G282" t="s">
-        <v>871</v>
+        <v>863</v>
       </c>
       <c r="H282" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="I282" t="s">
-        <v>872</v>
+        <v>864</v>
       </c>
       <c r="J282" t="s">
-        <v>873</v>
+        <v>865</v>
       </c>
       <c r="K282" t="s">
-        <v>874</v>
+        <v>866</v>
       </c>
       <c r="L282">
         <v>0</v>
@@ -46385,31 +46418,31 @@
         <v>0</v>
       </c>
       <c r="C283" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="D283" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="E283" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="F283" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="G283" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="H283" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="I283" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="J283" t="s">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="K283" t="s">
-        <v>878</v>
+        <v>870</v>
       </c>
       <c r="L283">
         <v>0</v>
@@ -46442,34 +46475,34 @@
         <v>0</v>
       </c>
       <c r="C284" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="D284" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="E284" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="F284" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="G284" t="s">
-        <v>879</v>
+        <v>871</v>
       </c>
       <c r="H284" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="I284" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="J284" t="s">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="K284" t="s">
-        <v>880</v>
+        <v>872</v>
       </c>
       <c r="L284" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
       <c r="M284">
         <v>0</v>
@@ -46499,34 +46532,34 @@
         <v>0</v>
       </c>
       <c r="C285" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="D285" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="E285" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="F285" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="G285" t="s">
-        <v>882</v>
+        <v>874</v>
       </c>
       <c r="H285" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="I285" t="s">
+        <v>868</v>
+      </c>
+      <c r="J285" t="s">
+        <v>869</v>
+      </c>
+      <c r="K285" t="s">
+        <v>875</v>
+      </c>
+      <c r="L285" t="s">
         <v>876</v>
-      </c>
-      <c r="J285" t="s">
-        <v>877</v>
-      </c>
-      <c r="K285" t="s">
-        <v>883</v>
-      </c>
-      <c r="L285" t="s">
-        <v>884</v>
       </c>
       <c r="M285">
         <v>0</v>
@@ -46556,34 +46589,34 @@
         <v>0</v>
       </c>
       <c r="C286" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="D286" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="E286" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="F286" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="G286" t="s">
-        <v>885</v>
+        <v>877</v>
       </c>
       <c r="H286" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="I286" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="J286" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="K286" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
       <c r="L286" t="s">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="M286">
         <v>0</v>
@@ -46613,34 +46646,34 @@
         <v>0</v>
       </c>
       <c r="C287" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="D287" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="E287" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="F287" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="G287" t="s">
-        <v>890</v>
+        <v>882</v>
       </c>
       <c r="H287" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="I287" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="J287" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="K287" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
       <c r="L287" t="s">
-        <v>891</v>
+        <v>883</v>
       </c>
       <c r="M287">
         <v>0</v>
@@ -46670,34 +46703,34 @@
         <v>0</v>
       </c>
       <c r="C288" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="D288" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="E288" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="F288" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="G288" t="s">
-        <v>892</v>
+        <v>884</v>
       </c>
       <c r="H288" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="I288" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="J288" t="s">
-        <v>887</v>
+        <v>879</v>
       </c>
       <c r="K288" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
       <c r="L288" t="s">
-        <v>893</v>
+        <v>885</v>
       </c>
       <c r="M288">
         <v>0</v>
@@ -46727,37 +46760,37 @@
         <v>0</v>
       </c>
       <c r="C289" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="D289" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="E289" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="F289" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="G289" t="s">
-        <v>894</v>
+        <v>886</v>
       </c>
       <c r="H289" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="I289" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="J289" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="K289" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="L289" t="s">
+        <v>881</v>
+      </c>
+      <c r="M289" t="s">
         <v>889</v>
-      </c>
-      <c r="M289" t="s">
-        <v>897</v>
       </c>
       <c r="N289">
         <v>0</v>
@@ -46784,37 +46817,37 @@
         <v>0</v>
       </c>
       <c r="C290" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="D290" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="E290" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="F290" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="G290" t="s">
-        <v>898</v>
+        <v>890</v>
       </c>
       <c r="H290" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="I290" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="J290" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="K290" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="L290" t="s">
+        <v>883</v>
+      </c>
+      <c r="M290" t="s">
         <v>891</v>
-      </c>
-      <c r="M290" t="s">
-        <v>899</v>
       </c>
       <c r="N290">
         <v>0</v>
@@ -46841,37 +46874,37 @@
         <v>0</v>
       </c>
       <c r="C291" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="D291" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="E291" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="F291" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="G291" t="s">
-        <v>900</v>
+        <v>892</v>
       </c>
       <c r="H291" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="I291" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="J291" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="K291" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="L291" t="s">
-        <v>891</v>
+        <v>883</v>
       </c>
       <c r="M291" t="s">
-        <v>901</v>
+        <v>893</v>
       </c>
       <c r="N291">
         <v>0</v>
@@ -46898,40 +46931,40 @@
         <v>0</v>
       </c>
       <c r="C292" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="D292" t="s">
+        <v>831</v>
+      </c>
+      <c r="E292" t="s">
         <v>839</v>
       </c>
-      <c r="E292" t="s">
-        <v>847</v>
-      </c>
       <c r="F292" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="G292" t="s">
-        <v>902</v>
+        <v>894</v>
       </c>
       <c r="H292" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="I292" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="J292" t="s">
+        <v>887</v>
+      </c>
+      <c r="K292" t="s">
+        <v>888</v>
+      </c>
+      <c r="L292" t="s">
+        <v>883</v>
+      </c>
+      <c r="M292" t="s">
+        <v>893</v>
+      </c>
+      <c r="N292" t="s">
         <v>895</v>
-      </c>
-      <c r="K292" t="s">
-        <v>896</v>
-      </c>
-      <c r="L292" t="s">
-        <v>891</v>
-      </c>
-      <c r="M292" t="s">
-        <v>901</v>
-      </c>
-      <c r="N292" t="s">
-        <v>903</v>
       </c>
       <c r="O292">
         <v>0</v>
@@ -46955,43 +46988,43 @@
         <v>0</v>
       </c>
       <c r="C293" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="D293" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="E293" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="F293" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="G293" t="s">
-        <v>904</v>
+        <v>896</v>
       </c>
       <c r="H293" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="I293" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="J293" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="K293" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="L293" t="s">
-        <v>891</v>
+        <v>883</v>
       </c>
       <c r="M293" t="s">
-        <v>901</v>
+        <v>893</v>
       </c>
       <c r="N293" t="s">
-        <v>905</v>
+        <v>897</v>
       </c>
       <c r="O293" t="s">
-        <v>906</v>
+        <v>898</v>
       </c>
       <c r="P293">
         <v>0</v>
@@ -47012,46 +47045,46 @@
         <v>0</v>
       </c>
       <c r="C294" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="D294" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
       <c r="E294" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="F294" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="G294" t="s">
-        <v>907</v>
+        <v>899</v>
       </c>
       <c r="H294" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="I294" t="s">
-        <v>886</v>
+        <v>878</v>
       </c>
       <c r="J294" t="s">
-        <v>895</v>
+        <v>887</v>
       </c>
       <c r="K294" t="s">
-        <v>896</v>
+        <v>888</v>
       </c>
       <c r="L294" t="s">
-        <v>891</v>
+        <v>883</v>
       </c>
       <c r="M294" t="s">
+        <v>893</v>
+      </c>
+      <c r="N294" t="s">
+        <v>900</v>
+      </c>
+      <c r="O294" t="s">
         <v>901</v>
       </c>
-      <c r="N294" t="s">
-        <v>908</v>
-      </c>
-      <c r="O294" t="s">
-        <v>909</v>
-      </c>
       <c r="P294" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
       <c r="Q294">
         <v>0</v>
@@ -47069,16 +47102,16 @@
         <v>0</v>
       </c>
       <c r="C295" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="D295" t="s">
-        <v>912</v>
+        <v>904</v>
       </c>
       <c r="E295" t="s">
-        <v>913</v>
+        <v>905</v>
       </c>
       <c r="F295" t="s">
-        <v>914</v>
+        <v>906</v>
       </c>
       <c r="G295">
         <v>0</v>
@@ -47126,16 +47159,16 @@
         <v>0</v>
       </c>
       <c r="C296" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="D296" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="E296" t="s">
-        <v>916</v>
+        <v>908</v>
       </c>
       <c r="F296" t="s">
-        <v>917</v>
+        <v>909</v>
       </c>
       <c r="G296">
         <v>0.1</v>
@@ -47183,16 +47216,16 @@
         <v>0</v>
       </c>
       <c r="C297" t="s">
+        <v>903</v>
+      </c>
+      <c r="D297" t="s">
+        <v>910</v>
+      </c>
+      <c r="E297" t="s">
         <v>911</v>
       </c>
-      <c r="D297" t="s">
-        <v>918</v>
-      </c>
-      <c r="E297" t="s">
-        <v>919</v>
-      </c>
       <c r="F297" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="G297">
         <v>0</v>
@@ -47240,16 +47273,16 @@
         <v>0</v>
       </c>
       <c r="C298" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="D298" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="E298" t="s">
-        <v>922</v>
+        <v>914</v>
       </c>
       <c r="F298" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="G298">
         <v>0</v>
@@ -47297,16 +47330,16 @@
         <v>0</v>
       </c>
       <c r="C299" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="D299" t="s">
-        <v>924</v>
+        <v>916</v>
       </c>
       <c r="E299" t="s">
-        <v>925</v>
+        <v>917</v>
       </c>
       <c r="F299" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="G299">
         <v>0</v>
@@ -47354,16 +47387,16 @@
         <v>0</v>
       </c>
       <c r="C300" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="D300" t="s">
-        <v>927</v>
+        <v>919</v>
       </c>
       <c r="E300" t="s">
-        <v>928</v>
+        <v>920</v>
       </c>
       <c r="F300" t="s">
-        <v>929</v>
+        <v>921</v>
       </c>
       <c r="G300">
         <v>0.4</v>
@@ -47411,16 +47444,16 @@
         <v>0</v>
       </c>
       <c r="C301" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="D301" t="s">
-        <v>764</v>
+        <v>756</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>1081</v>
+        <v>1072</v>
       </c>
       <c r="F301" t="s">
-        <v>930</v>
+        <v>922</v>
       </c>
       <c r="G301">
         <v>1000</v>
@@ -47468,16 +47501,16 @@
         <v>0</v>
       </c>
       <c r="C302" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="D302" t="s">
-        <v>931</v>
+        <v>923</v>
       </c>
       <c r="E302" t="s">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="F302" t="s">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="G302">
         <v>0</v>
@@ -47525,16 +47558,16 @@
         <v>0</v>
       </c>
       <c r="C303" t="s">
-        <v>911</v>
+        <v>903</v>
       </c>
       <c r="D303" t="s">
-        <v>934</v>
+        <v>926</v>
       </c>
       <c r="E303" t="s">
-        <v>935</v>
+        <v>927</v>
       </c>
       <c r="F303" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="G303">
         <v>30</v>
@@ -47582,16 +47615,16 @@
         <v>0</v>
       </c>
       <c r="C304" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="D304" t="s">
-        <v>938</v>
+        <v>930</v>
       </c>
       <c r="E304" t="s">
-        <v>939</v>
+        <v>931</v>
       </c>
       <c r="F304" t="s">
-        <v>940</v>
+        <v>932</v>
       </c>
       <c r="G304">
         <v>0.75</v>
@@ -47639,13 +47672,13 @@
         <v>0</v>
       </c>
       <c r="C305" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="D305" t="s">
-        <v>941</v>
+        <v>933</v>
       </c>
       <c r="E305" t="s">
-        <v>942</v>
+        <v>934</v>
       </c>
       <c r="F305">
         <v>0</v>
@@ -47696,16 +47729,16 @@
         <v>0</v>
       </c>
       <c r="C306" t="s">
+        <v>929</v>
+      </c>
+      <c r="D306" t="s">
+        <v>935</v>
+      </c>
+      <c r="E306" t="s">
+        <v>936</v>
+      </c>
+      <c r="F306" t="s">
         <v>937</v>
-      </c>
-      <c r="D306" t="s">
-        <v>943</v>
-      </c>
-      <c r="E306" t="s">
-        <v>944</v>
-      </c>
-      <c r="F306" t="s">
-        <v>945</v>
       </c>
       <c r="G306">
         <v>45</v>
@@ -47753,16 +47786,16 @@
         <v>0</v>
       </c>
       <c r="C307" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="D307" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
       <c r="E307" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="F307" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="G307">
         <v>0</v>
@@ -47810,16 +47843,16 @@
         <v>0</v>
       </c>
       <c r="C308" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="D308" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="E308" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="F308" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="G308">
         <v>0.1</v>
@@ -47867,16 +47900,16 @@
         <v>0</v>
       </c>
       <c r="C309" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="D309" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="E309" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="F309" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
       <c r="G309">
         <v>24</v>
@@ -47924,16 +47957,16 @@
         <v>0</v>
       </c>
       <c r="C310" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
       <c r="D310" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
       <c r="E310" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="F310" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="G310">
         <v>10</v>
@@ -47981,16 +48014,16 @@
         <v>0</v>
       </c>
       <c r="C311" t="s">
+        <v>944</v>
+      </c>
+      <c r="D311" t="s">
+        <v>951</v>
+      </c>
+      <c r="E311" t="s">
         <v>952</v>
       </c>
-      <c r="D311" t="s">
-        <v>959</v>
-      </c>
-      <c r="E311" t="s">
-        <v>960</v>
-      </c>
       <c r="F311" t="s">
-        <v>961</v>
+        <v>953</v>
       </c>
       <c r="G311">
         <v>20</v>
@@ -48038,16 +48071,16 @@
         <v>0</v>
       </c>
       <c r="C312" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="D312" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="E312" t="s">
         <v>39</v>
       </c>
       <c r="F312" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="G312">
         <v>1</v>
@@ -48095,16 +48128,16 @@
         <v>0</v>
       </c>
       <c r="C313" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="D313" t="s">
-        <v>965</v>
+        <v>957</v>
       </c>
       <c r="E313" t="s">
         <v>39</v>
       </c>
       <c r="F313" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="G313">
         <v>1.35</v>
@@ -48152,16 +48185,16 @@
         <v>0</v>
       </c>
       <c r="C314" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="D314" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="E314" t="s">
         <v>39</v>
       </c>
       <c r="F314" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="G314">
         <v>1.75</v>
@@ -48209,16 +48242,16 @@
         <v>0</v>
       </c>
       <c r="C315" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="D315" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="E315" t="s">
         <v>39</v>
       </c>
       <c r="F315" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="G315">
         <v>2.2999999999999998</v>
@@ -48266,16 +48299,16 @@
         <v>0</v>
       </c>
       <c r="C316" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="D316" t="s">
-        <v>968</v>
+        <v>960</v>
       </c>
       <c r="E316" t="s">
         <v>39</v>
       </c>
       <c r="F316" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="G316">
         <v>3</v>
@@ -48323,16 +48356,16 @@
         <v>0</v>
       </c>
       <c r="C317" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="D317" t="s">
-        <v>969</v>
+        <v>961</v>
       </c>
       <c r="E317" t="s">
         <v>39</v>
       </c>
       <c r="F317" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="G317">
         <v>4</v>
@@ -48380,16 +48413,16 @@
         <v>0</v>
       </c>
       <c r="C318" t="s">
+        <v>954</v>
+      </c>
+      <c r="D318" t="s">
         <v>962</v>
-      </c>
-      <c r="D318" t="s">
-        <v>970</v>
       </c>
       <c r="E318" t="s">
         <v>39</v>
       </c>
       <c r="F318" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="G318">
         <v>5.2</v>
@@ -48437,16 +48470,16 @@
         <v>0</v>
       </c>
       <c r="C319" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="D319" t="s">
-        <v>971</v>
+        <v>963</v>
       </c>
       <c r="E319" t="s">
         <v>39</v>
       </c>
       <c r="F319" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="G319">
         <v>6.8</v>
@@ -48494,16 +48527,16 @@
         <v>0</v>
       </c>
       <c r="C320" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="D320" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
       <c r="E320" t="s">
         <v>39</v>
       </c>
       <c r="F320" t="s">
-        <v>964</v>
+        <v>956</v>
       </c>
       <c r="G320">
         <v>10.199999999999999</v>
@@ -48551,22 +48584,22 @@
         <v>0</v>
       </c>
       <c r="C321" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="D321" t="s">
-        <v>974</v>
+        <v>966</v>
       </c>
       <c r="E321" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="F321" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
       <c r="G321">
         <v>25</v>
       </c>
       <c r="H321" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="I321">
         <v>0</v>
@@ -48608,22 +48641,22 @@
         <v>0</v>
       </c>
       <c r="C322" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="D322" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="E322" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="F322" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="G322">
         <v>20</v>
       </c>
       <c r="H322" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="I322">
         <v>0</v>
@@ -48665,22 +48698,22 @@
         <v>0</v>
       </c>
       <c r="C323" t="s">
+        <v>965</v>
+      </c>
+      <c r="D323" t="s">
+        <v>972</v>
+      </c>
+      <c r="E323" t="s">
+        <v>967</v>
+      </c>
+      <c r="F323" t="s">
         <v>973</v>
-      </c>
-      <c r="D323" t="s">
-        <v>980</v>
-      </c>
-      <c r="E323" t="s">
-        <v>975</v>
-      </c>
-      <c r="F323" t="s">
-        <v>981</v>
       </c>
       <c r="G323">
         <v>25</v>
       </c>
       <c r="H323" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="I323">
         <v>0</v>
@@ -48722,22 +48755,22 @@
         <v>0</v>
       </c>
       <c r="C324" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="D324" t="s">
-        <v>982</v>
+        <v>974</v>
       </c>
       <c r="E324" t="s">
+        <v>967</v>
+      </c>
+      <c r="F324" t="s">
         <v>975</v>
-      </c>
-      <c r="F324" t="s">
-        <v>983</v>
       </c>
       <c r="G324">
         <v>20</v>
       </c>
       <c r="H324" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="I324">
         <v>0</v>
@@ -48779,22 +48812,22 @@
         <v>0</v>
       </c>
       <c r="C325" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="D325" t="s">
-        <v>984</v>
+        <v>976</v>
       </c>
       <c r="E325" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="F325" t="s">
-        <v>985</v>
+        <v>977</v>
       </c>
       <c r="G325">
         <v>0.4</v>
       </c>
       <c r="H325" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="I325">
         <v>0</v>
@@ -48836,22 +48869,22 @@
         <v>0</v>
       </c>
       <c r="C326" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="D326" t="s">
-        <v>986</v>
+        <v>978</v>
       </c>
       <c r="E326" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="F326" t="s">
-        <v>987</v>
+        <v>979</v>
       </c>
       <c r="G326">
         <v>3</v>
       </c>
       <c r="H326" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="I326">
         <v>0</v>
@@ -48893,22 +48926,22 @@
         <v>0</v>
       </c>
       <c r="C327" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="D327" t="s">
-        <v>988</v>
+        <v>980</v>
       </c>
       <c r="E327" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="F327" t="s">
-        <v>989</v>
+        <v>981</v>
       </c>
       <c r="G327">
         <v>1.5</v>
       </c>
       <c r="H327" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="I327">
         <v>0</v>
@@ -48950,22 +48983,22 @@
         <v>0</v>
       </c>
       <c r="C328" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="D328" t="s">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="E328" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="F328" t="s">
-        <v>991</v>
+        <v>983</v>
       </c>
       <c r="G328">
         <v>0.15</v>
       </c>
       <c r="H328" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="I328">
         <v>0</v>
@@ -49007,22 +49040,22 @@
         <v>0</v>
       </c>
       <c r="C329" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="D329" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="E329" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="F329" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="G329">
         <v>0.5</v>
       </c>
       <c r="H329" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="I329">
         <v>0</v>
@@ -49064,22 +49097,22 @@
         <v>0</v>
       </c>
       <c r="C330" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="D330" t="s">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="E330" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="F330" t="s">
-        <v>995</v>
+        <v>987</v>
       </c>
       <c r="G330">
         <v>25</v>
       </c>
       <c r="H330" t="s">
-        <v>977</v>
+        <v>969</v>
       </c>
       <c r="I330">
         <v>0</v>
@@ -49121,22 +49154,22 @@
         <v>0</v>
       </c>
       <c r="C331" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="D331" t="s">
-        <v>996</v>
+        <v>988</v>
       </c>
       <c r="E331" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="F331" t="s">
-        <v>997</v>
+        <v>989</v>
       </c>
       <c r="G331">
         <v>8</v>
       </c>
       <c r="H331" t="s">
-        <v>998</v>
+        <v>990</v>
       </c>
       <c r="I331">
         <v>0</v>
@@ -49178,22 +49211,22 @@
         <v>0</v>
       </c>
       <c r="C332" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="D332" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
       <c r="E332" t="s">
-        <v>975</v>
+        <v>967</v>
       </c>
       <c r="F332" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
       <c r="G332">
         <v>15</v>
       </c>
       <c r="H332" t="s">
-        <v>998</v>
+        <v>990</v>
       </c>
       <c r="I332">
         <v>0</v>
@@ -49235,16 +49268,16 @@
         <v>0</v>
       </c>
       <c r="C333" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="D333" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="E333" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
       <c r="F333" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
       <c r="G333">
         <v>0.8</v>
@@ -49292,16 +49325,16 @@
         <v>0</v>
       </c>
       <c r="C334" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="D334" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
       <c r="E334" t="s">
-        <v>1006</v>
+        <v>998</v>
       </c>
       <c r="F334" t="s">
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="G334">
         <v>3</v>
@@ -49349,16 +49382,16 @@
         <v>0</v>
       </c>
       <c r="C335" t="s">
+        <v>993</v>
+      </c>
+      <c r="D335" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E335" t="s">
         <v>1001</v>
       </c>
-      <c r="D335" t="s">
-        <v>1008</v>
-      </c>
-      <c r="E335" t="s">
-        <v>1009</v>
-      </c>
       <c r="F335" t="s">
-        <v>1010</v>
+        <v>1002</v>
       </c>
       <c r="G335">
         <v>7</v>
@@ -49406,16 +49439,16 @@
         <v>0</v>
       </c>
       <c r="C336" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="D336" t="s">
-        <v>1011</v>
+        <v>1003</v>
       </c>
       <c r="E336" t="s">
-        <v>1012</v>
+        <v>1004</v>
       </c>
       <c r="F336" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="G336">
         <v>10</v>
@@ -49463,16 +49496,16 @@
         <v>0</v>
       </c>
       <c r="C337" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="D337" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="E337" t="s">
-        <v>1015</v>
+        <v>1007</v>
       </c>
       <c r="F337" t="s">
-        <v>1016</v>
+        <v>1008</v>
       </c>
       <c r="G337">
         <v>2</v>
@@ -49520,16 +49553,16 @@
         <v>0</v>
       </c>
       <c r="C338" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="D338" t="s">
-        <v>1017</v>
+        <v>1009</v>
       </c>
       <c r="E338" t="s">
-        <v>1018</v>
+        <v>1010</v>
       </c>
       <c r="F338" t="s">
-        <v>1019</v>
+        <v>1011</v>
       </c>
       <c r="G338">
         <v>5</v>
@@ -49577,16 +49610,16 @@
         <v>0</v>
       </c>
       <c r="C339" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="D339" t="s">
-        <v>1020</v>
+        <v>1012</v>
       </c>
       <c r="E339" t="s">
-        <v>1021</v>
+        <v>1013</v>
       </c>
       <c r="F339" t="s">
-        <v>1022</v>
+        <v>1014</v>
       </c>
       <c r="G339">
         <v>10</v>
@@ -49634,16 +49667,16 @@
         <v>0</v>
       </c>
       <c r="C340" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="D340" t="s">
-        <v>1023</v>
+        <v>1015</v>
       </c>
       <c r="E340" t="s">
         <v>39</v>
       </c>
       <c r="F340" t="s">
-        <v>1024</v>
+        <v>1016</v>
       </c>
       <c r="G340">
         <v>15.3</v>
@@ -49691,16 +49724,16 @@
         <v>0</v>
       </c>
       <c r="C341" t="s">
-        <v>962</v>
+        <v>954</v>
       </c>
       <c r="D341" t="s">
-        <v>1025</v>
+        <v>1017</v>
       </c>
       <c r="E341" t="s">
         <v>39</v>
       </c>
       <c r="F341" t="s">
-        <v>1024</v>
+        <v>1016</v>
       </c>
       <c r="G341">
         <v>22.95</v>
@@ -49748,16 +49781,16 @@
         <v>0</v>
       </c>
       <c r="C342" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="D342" t="s">
-        <v>1026</v>
+        <v>1018</v>
       </c>
       <c r="E342" t="s">
-        <v>1027</v>
+        <v>1019</v>
       </c>
       <c r="F342" t="s">
-        <v>1028</v>
+        <v>1020</v>
       </c>
       <c r="G342">
         <v>20</v>
@@ -49805,16 +49838,16 @@
         <v>0</v>
       </c>
       <c r="C343" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="D343" t="s">
-        <v>1029</v>
+        <v>1021</v>
       </c>
       <c r="E343" t="s">
-        <v>1030</v>
+        <v>1022</v>
       </c>
       <c r="F343" t="s">
-        <v>1031</v>
+        <v>1023</v>
       </c>
       <c r="G343">
         <v>500000000</v>
@@ -49862,16 +49895,16 @@
         <v>0</v>
       </c>
       <c r="C344" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="D344" t="s">
-        <v>1032</v>
+        <v>1024</v>
       </c>
       <c r="E344" t="s">
-        <v>1033</v>
+        <v>1025</v>
       </c>
       <c r="F344" t="s">
-        <v>1034</v>
+        <v>1026</v>
       </c>
       <c r="G344">
         <v>13</v>
@@ -49910,7 +49943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345">
         <f t="shared" si="5"/>
         <v>344</v>
@@ -49922,13 +49955,13 @@
         <v>18</v>
       </c>
       <c r="D345" t="s">
-        <v>1035</v>
-      </c>
-      <c r="E345" t="s">
-        <v>1036</v>
+        <v>1027</v>
+      </c>
+      <c r="E345" s="2" t="s">
+        <v>1084</v>
       </c>
       <c r="F345" t="s">
-        <v>1037</v>
+        <v>1028</v>
       </c>
       <c r="G345">
         <v>30</v>
@@ -49937,7 +49970,7 @@
         <v>3</v>
       </c>
       <c r="I345">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="J345">
         <v>0</v>
@@ -49979,19 +50012,19 @@
         <v>18</v>
       </c>
       <c r="D346" t="s">
-        <v>1038</v>
+        <v>1029</v>
       </c>
       <c r="E346" t="s">
-        <v>1039</v>
+        <v>1030</v>
       </c>
       <c r="F346" t="s">
-        <v>1040</v>
+        <v>1031</v>
       </c>
       <c r="G346">
         <v>1000</v>
       </c>
       <c r="H346">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I346">
         <v>0</v>
@@ -50033,16 +50066,16 @@
         <v>0</v>
       </c>
       <c r="C347" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="D347" t="s">
-        <v>1041</v>
+        <v>1032</v>
       </c>
       <c r="E347" t="s">
-        <v>1042</v>
+        <v>1033</v>
       </c>
       <c r="F347" t="s">
-        <v>1043</v>
+        <v>1034</v>
       </c>
       <c r="G347">
         <v>50000</v>
@@ -50090,16 +50123,16 @@
         <v>0</v>
       </c>
       <c r="C348" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="D348" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
       <c r="E348" t="s">
-        <v>1045</v>
+        <v>1036</v>
       </c>
       <c r="F348" t="s">
-        <v>1046</v>
+        <v>1037</v>
       </c>
       <c r="G348">
         <v>10</v>
@@ -50147,16 +50180,16 @@
         <v>0</v>
       </c>
       <c r="C349" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="D349" t="s">
-        <v>1047</v>
+        <v>1038</v>
       </c>
       <c r="E349" t="s">
-        <v>1048</v>
+        <v>1039</v>
       </c>
       <c r="F349" t="s">
-        <v>1049</v>
+        <v>1040</v>
       </c>
       <c r="G349">
         <v>75</v>
@@ -50204,16 +50237,16 @@
         <v>0</v>
       </c>
       <c r="C350" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="D350" t="s">
-        <v>1050</v>
+        <v>1041</v>
       </c>
       <c r="E350" t="s">
-        <v>1051</v>
+        <v>1042</v>
       </c>
       <c r="F350" t="s">
-        <v>1052</v>
+        <v>1043</v>
       </c>
       <c r="G350">
         <v>25</v>
@@ -50261,16 +50294,16 @@
         <v>0</v>
       </c>
       <c r="C351" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="D351" t="s">
-        <v>1053</v>
+        <v>1044</v>
       </c>
       <c r="E351" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="F351" t="s">
-        <v>1054</v>
+        <v>1045</v>
       </c>
       <c r="G351">
         <v>5</v>
@@ -50318,16 +50351,16 @@
         <v>0</v>
       </c>
       <c r="C352" t="s">
-        <v>937</v>
+        <v>929</v>
       </c>
       <c r="D352" t="s">
-        <v>1055</v>
+        <v>1046</v>
       </c>
       <c r="E352" t="s">
-        <v>1056</v>
+        <v>1047</v>
       </c>
       <c r="F352" t="s">
-        <v>1057</v>
+        <v>1048</v>
       </c>
       <c r="G352">
         <v>0.6</v>
@@ -50375,16 +50408,16 @@
         <v>0</v>
       </c>
       <c r="C353" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="D353" t="s">
-        <v>1058</v>
+        <v>1049</v>
       </c>
       <c r="E353" t="s">
-        <v>1059</v>
+        <v>1050</v>
       </c>
       <c r="F353" t="s">
-        <v>1060</v>
+        <v>1051</v>
       </c>
       <c r="G353">
         <v>0.1</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BAEFA8F-4B12-4CB7-AC4B-9E13AB6A853A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67F3DBE-654C-42D4-9290-47B44FA833F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11254,11 +11254,11 @@
       </c>
       <c r="G96">
         <f>計算表!G96</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H96">
         <f>計算表!H96</f>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I96">
         <f>計算表!I96</f>
@@ -11266,11 +11266,11 @@
       </c>
       <c r="J96">
         <f>計算表!J96</f>
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="K96">
         <f>計算表!K96</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L96">
         <f>計算表!L96</f>
@@ -35771,19 +35771,19 @@
         <v>280</v>
       </c>
       <c r="G96">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H96">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I96">
         <v>2</v>
       </c>
       <c r="J96">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="K96">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L96">
         <v>0</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67F3DBE-654C-42D4-9290-47B44FA833F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A03E33-EE0B-4708-9907-39DE80CC088B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6296,11 +6296,11 @@
       </c>
       <c r="G29">
         <f>計算表!G29</f>
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H29">
         <f>計算表!H29</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I29">
         <f>計算表!I29</f>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="G32">
         <f>計算表!G32</f>
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H32">
         <f>計算表!H32</f>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="G33">
         <f>計算表!G33</f>
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H33">
         <f>計算表!H33</f>
@@ -10144,15 +10144,15 @@
       </c>
       <c r="G81">
         <f>計算表!G81</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H81">
         <f>計算表!H81</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I81">
         <f>計算表!I81</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J81">
         <f>計算表!J81</f>
@@ -10662,11 +10662,11 @@
       </c>
       <c r="G88">
         <f>計算表!G88</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H88">
         <f>計算表!H88</f>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I88">
         <f>計算表!I88</f>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="H89">
         <f>計算表!H89</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I89">
         <f>計算表!I89</f>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="G96">
         <f>計算表!G96</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H96">
         <f>計算表!H96</f>
@@ -31952,10 +31952,10 @@
         <v>106</v>
       </c>
       <c r="G29">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="H29">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I29">
         <v>10</v>
@@ -32123,7 +32123,7 @@
         <v>115</v>
       </c>
       <c r="G32">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H32">
         <v>1.2</v>
@@ -32180,7 +32180,7 @@
         <v>118</v>
       </c>
       <c r="G33">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H33">
         <v>1.2</v>
@@ -34916,13 +34916,13 @@
         <v>238</v>
       </c>
       <c r="G81">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H81">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I81">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J81">
         <v>300</v>
@@ -35315,10 +35315,10 @@
         <v>257</v>
       </c>
       <c r="G88">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H88">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I88">
         <v>1.06</v>
@@ -35375,7 +35375,7 @@
         <v>3</v>
       </c>
       <c r="H89">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I89">
         <v>1.0549999999999999</v>
@@ -35771,7 +35771,7 @@
         <v>280</v>
       </c>
       <c r="G96">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H96">
         <v>2</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\claude\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A03E33-EE0B-4708-9907-39DE80CC088B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349465B2-46D8-49D0-A706-BE4EB9DA3184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1889" uniqueCount="1085">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="1086">
   <si>
     <t>編號</t>
   </si>
@@ -684,13 +684,7 @@
     <t>普通敵人每秒遞減 1%；菁英每秒遞減 3%；BOSS 不受控場遞減。</t>
   </si>
   <si>
-    <t>擊殺回復</t>
-  </si>
-  <si>
     <t>最大生命×a%</t>
-  </si>
-  <si>
-    <t>野外每擊殺一隻回復（吸魂被動再另加）。</t>
   </si>
   <si>
     <t>溢出治療轉護盾</t>
@@ -3551,62 +3545,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{6,5}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{4,20}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{5,2}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{1~3,90}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{1~3,100}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{4,5}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{1~3,95}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{4,8}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{6,1}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{5,3}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{1~3,88}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{7~9,1}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{5,10}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{1~3,64}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -3787,6 +3725,59 @@
       </rPr>
       <t>^b + c</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{1~2,90}</t>
+  </si>
+  <si>
+    <t>{1~2,88}</t>
+  </si>
+  <si>
+    <t>{4,2}</t>
+  </si>
+  <si>
+    <t>{1~3,85}</t>
+  </si>
+  <si>
+    <t>{4,10}</t>
+  </si>
+  <si>
+    <t>{5,4}</t>
+  </si>
+  <si>
+    <t>{6,1}</t>
+  </si>
+  <si>
+    <t>{1~3,80}</t>
+  </si>
+  <si>
+    <t>{4,12}</t>
+  </si>
+  <si>
+    <t>{5,6}</t>
+  </si>
+  <si>
+    <t>{6,2}</t>
+  </si>
+  <si>
+    <t>{1~3,64}</t>
+  </si>
+  <si>
+    <t>{4,20}</t>
+  </si>
+  <si>
+    <t>{6,5}</t>
+  </si>
+  <si>
+    <t>{7~9,1}</t>
+  </si>
+  <si>
+    <t>過關回復</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>野外整波敵人清空時回復一次（吸魂被動仍為擊殺時觸發）。高塔沒有此回復。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3862,7 +3853,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3873,6 +3864,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -9614,7 +9608,7 @@
       </c>
       <c r="D74" t="str">
         <f>計算表!D74</f>
-        <v>擊殺回復</v>
+        <v>過關回復</v>
       </c>
       <c r="E74" t="str">
         <f>計算表!E74</f>
@@ -9622,7 +9616,7 @@
       </c>
       <c r="F74" t="str">
         <f>計算表!F74</f>
-        <v>野外每擊殺一隻回復（吸魂被動再另加）。</v>
+        <v>野外整波敵人清空時回復一次（吸魂被動仍為擊殺時觸發）。高塔沒有此回復。</v>
       </c>
       <c r="G74">
         <f>計算表!G74</f>
@@ -11846,11 +11840,11 @@
       </c>
       <c r="G104" t="str">
         <f>計算表!G104</f>
-        <v>{1~3,100}</v>
-      </c>
-      <c r="H104">
+        <v>{1~2,90}</v>
+      </c>
+      <c r="H104" t="str">
         <f>計算表!H104</f>
-        <v>0</v>
+        <v>{3,10}</v>
       </c>
       <c r="I104">
         <f>計算表!I104</f>
@@ -11920,15 +11914,15 @@
       </c>
       <c r="G105" t="str">
         <f>計算表!G105</f>
-        <v>{1~3,95}</v>
+        <v>{1~2,88}</v>
       </c>
       <c r="H105" t="str">
         <f>計算表!H105</f>
-        <v>{4,5}</v>
-      </c>
-      <c r="I105">
+        <v>{3,10}</v>
+      </c>
+      <c r="I105" t="str">
         <f>計算表!I105</f>
-        <v>0</v>
+        <v>{4,2}</v>
       </c>
       <c r="J105">
         <f>計算表!J105</f>
@@ -11994,19 +11988,19 @@
       </c>
       <c r="G106" t="str">
         <f>計算表!G106</f>
-        <v>{1~3,90}</v>
+        <v>{1~3,85}</v>
       </c>
       <c r="H106" t="str">
         <f>計算表!H106</f>
-        <v>{4,8}</v>
+        <v>{4,10}</v>
       </c>
       <c r="I106" t="str">
         <f>計算表!I106</f>
-        <v>{5,2}</v>
-      </c>
-      <c r="J106">
+        <v>{5,4}</v>
+      </c>
+      <c r="J106" t="str">
         <f>計算表!J106</f>
-        <v>0</v>
+        <v>{6,1}</v>
       </c>
       <c r="K106">
         <f>計算表!K106</f>
@@ -12068,19 +12062,19 @@
       </c>
       <c r="G107" t="str">
         <f>計算表!G107</f>
-        <v>{1~3,88}</v>
+        <v>{1~3,80}</v>
       </c>
       <c r="H107" t="str">
         <f>計算表!H107</f>
-        <v>{4,8}</v>
+        <v>{4,12}</v>
       </c>
       <c r="I107" t="str">
         <f>計算表!I107</f>
-        <v>{5,3}</v>
+        <v>{5,6}</v>
       </c>
       <c r="J107" t="str">
         <f>計算表!J107</f>
-        <v>{6,1}</v>
+        <v>{6,2}</v>
       </c>
       <c r="K107">
         <f>計算表!K107</f>
@@ -32744,10 +32738,10 @@
         <v>145</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1073</v>
+        <v>1057</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>1074</v>
+        <v>1058</v>
       </c>
       <c r="G43">
         <v>2</v>
@@ -34507,14 +34501,14 @@
       <c r="C74" t="s">
         <v>191</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E74" t="s">
         <v>216</v>
       </c>
-      <c r="E74" t="s">
-        <v>217</v>
-      </c>
-      <c r="F74" t="s">
-        <v>218</v>
+      <c r="F74" s="4" t="s">
+        <v>1085</v>
       </c>
       <c r="G74">
         <v>12</v>
@@ -34565,13 +34559,13 @@
         <v>191</v>
       </c>
       <c r="D75" t="s">
+        <v>217</v>
+      </c>
+      <c r="E75" t="s">
+        <v>218</v>
+      </c>
+      <c r="F75" t="s">
         <v>219</v>
-      </c>
-      <c r="E75" t="s">
-        <v>220</v>
-      </c>
-      <c r="F75" t="s">
-        <v>221</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -34622,13 +34616,13 @@
         <v>191</v>
       </c>
       <c r="D76" t="s">
+        <v>220</v>
+      </c>
+      <c r="E76" t="s">
+        <v>221</v>
+      </c>
+      <c r="F76" t="s">
         <v>222</v>
-      </c>
-      <c r="E76" t="s">
-        <v>223</v>
-      </c>
-      <c r="F76" t="s">
-        <v>224</v>
       </c>
       <c r="G76">
         <v>10</v>
@@ -34679,13 +34673,13 @@
         <v>191</v>
       </c>
       <c r="D77" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E77" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F77" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G77">
         <v>10000</v>
@@ -34736,13 +34730,13 @@
         <v>191</v>
       </c>
       <c r="D78" t="s">
+        <v>225</v>
+      </c>
+      <c r="E78" t="s">
+        <v>226</v>
+      </c>
+      <c r="F78" t="s">
         <v>227</v>
-      </c>
-      <c r="E78" t="s">
-        <v>228</v>
-      </c>
-      <c r="F78" t="s">
-        <v>229</v>
       </c>
       <c r="G78">
         <v>50</v>
@@ -34793,13 +34787,13 @@
         <v>191</v>
       </c>
       <c r="D79" t="s">
+        <v>228</v>
+      </c>
+      <c r="E79" t="s">
+        <v>229</v>
+      </c>
+      <c r="F79" t="s">
         <v>230</v>
-      </c>
-      <c r="E79" t="s">
-        <v>231</v>
-      </c>
-      <c r="F79" t="s">
-        <v>232</v>
       </c>
       <c r="G79">
         <v>30</v>
@@ -34850,13 +34844,13 @@
         <v>191</v>
       </c>
       <c r="D80" t="s">
+        <v>231</v>
+      </c>
+      <c r="E80" t="s">
+        <v>232</v>
+      </c>
+      <c r="F80" t="s">
         <v>233</v>
-      </c>
-      <c r="E80" t="s">
-        <v>234</v>
-      </c>
-      <c r="F80" t="s">
-        <v>235</v>
       </c>
       <c r="G80">
         <v>100</v>
@@ -34907,13 +34901,13 @@
         <v>191</v>
       </c>
       <c r="D81" t="s">
+        <v>234</v>
+      </c>
+      <c r="E81" t="s">
+        <v>235</v>
+      </c>
+      <c r="F81" t="s">
         <v>236</v>
-      </c>
-      <c r="E81" t="s">
-        <v>237</v>
-      </c>
-      <c r="F81" t="s">
-        <v>238</v>
       </c>
       <c r="G81">
         <v>5</v>
@@ -34964,13 +34958,13 @@
         <v>191</v>
       </c>
       <c r="D82" t="s">
+        <v>237</v>
+      </c>
+      <c r="E82" t="s">
+        <v>238</v>
+      </c>
+      <c r="F82" t="s">
         <v>239</v>
-      </c>
-      <c r="E82" t="s">
-        <v>240</v>
-      </c>
-      <c r="F82" t="s">
-        <v>241</v>
       </c>
       <c r="G82">
         <v>0.01</v>
@@ -35018,16 +35012,16 @@
         <v>0</v>
       </c>
       <c r="C83" t="s">
+        <v>240</v>
+      </c>
+      <c r="D83" t="s">
+        <v>241</v>
+      </c>
+      <c r="E83" t="s">
         <v>242</v>
       </c>
-      <c r="D83" t="s">
+      <c r="F83" t="s">
         <v>243</v>
-      </c>
-      <c r="E83" t="s">
-        <v>244</v>
-      </c>
-      <c r="F83" t="s">
-        <v>245</v>
       </c>
       <c r="G83">
         <v>15</v>
@@ -35075,16 +35069,16 @@
         <v>0</v>
       </c>
       <c r="C84" t="s">
+        <v>240</v>
+      </c>
+      <c r="D84" t="s">
+        <v>244</v>
+      </c>
+      <c r="E84" t="s">
         <v>242</v>
       </c>
-      <c r="D84" t="s">
-        <v>246</v>
-      </c>
-      <c r="E84" t="s">
-        <v>244</v>
-      </c>
       <c r="F84" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G84">
         <v>10</v>
@@ -35132,16 +35126,16 @@
         <v>0</v>
       </c>
       <c r="C85" t="s">
+        <v>240</v>
+      </c>
+      <c r="D85" t="s">
+        <v>246</v>
+      </c>
+      <c r="E85" t="s">
         <v>242</v>
       </c>
-      <c r="D85" t="s">
-        <v>248</v>
-      </c>
-      <c r="E85" t="s">
-        <v>244</v>
-      </c>
       <c r="F85" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G85">
         <v>25</v>
@@ -35189,16 +35183,16 @@
         <v>0</v>
       </c>
       <c r="C86" t="s">
+        <v>240</v>
+      </c>
+      <c r="D86" t="s">
+        <v>248</v>
+      </c>
+      <c r="E86" t="s">
         <v>242</v>
       </c>
-      <c r="D86" t="s">
-        <v>250</v>
-      </c>
-      <c r="E86" t="s">
-        <v>244</v>
-      </c>
       <c r="F86" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G86">
         <v>20</v>
@@ -35246,16 +35240,16 @@
         <v>0</v>
       </c>
       <c r="C87" t="s">
+        <v>240</v>
+      </c>
+      <c r="D87" t="s">
+        <v>250</v>
+      </c>
+      <c r="E87" t="s">
         <v>242</v>
       </c>
-      <c r="D87" t="s">
-        <v>252</v>
-      </c>
-      <c r="E87" t="s">
-        <v>244</v>
-      </c>
       <c r="F87" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G87">
         <v>100</v>
@@ -35303,16 +35297,16 @@
         <v>0</v>
       </c>
       <c r="C88" t="s">
+        <v>252</v>
+      </c>
+      <c r="D88" t="s">
+        <v>253</v>
+      </c>
+      <c r="E88" t="s">
         <v>254</v>
       </c>
-      <c r="D88" t="s">
+      <c r="F88" t="s">
         <v>255</v>
-      </c>
-      <c r="E88" t="s">
-        <v>256</v>
-      </c>
-      <c r="F88" t="s">
-        <v>257</v>
       </c>
       <c r="G88">
         <v>20</v>
@@ -35360,16 +35354,16 @@
         <v>0</v>
       </c>
       <c r="C89" t="s">
+        <v>252</v>
+      </c>
+      <c r="D89" t="s">
+        <v>256</v>
+      </c>
+      <c r="E89" t="s">
         <v>254</v>
       </c>
-      <c r="D89" t="s">
-        <v>258</v>
-      </c>
-      <c r="E89" t="s">
-        <v>256</v>
-      </c>
       <c r="F89" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G89">
         <v>3</v>
@@ -35417,16 +35411,16 @@
         <v>0</v>
       </c>
       <c r="C90" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D90" t="s">
         <v>119</v>
       </c>
       <c r="E90" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F90" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G90">
         <v>2</v>
@@ -35474,16 +35468,16 @@
         <v>0</v>
       </c>
       <c r="C91" t="s">
+        <v>252</v>
+      </c>
+      <c r="D91" t="s">
+        <v>258</v>
+      </c>
+      <c r="E91" t="s">
         <v>254</v>
       </c>
-      <c r="D91" t="s">
-        <v>260</v>
-      </c>
-      <c r="E91" t="s">
-        <v>256</v>
-      </c>
       <c r="F91" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G91">
         <v>250</v>
@@ -35531,16 +35525,16 @@
         <v>0</v>
       </c>
       <c r="C92" t="s">
+        <v>252</v>
+      </c>
+      <c r="D92" t="s">
+        <v>259</v>
+      </c>
+      <c r="E92" t="s">
         <v>254</v>
       </c>
-      <c r="D92" t="s">
-        <v>261</v>
-      </c>
-      <c r="E92" t="s">
-        <v>256</v>
-      </c>
       <c r="F92" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G92">
         <v>60</v>
@@ -35588,16 +35582,16 @@
         <v>0</v>
       </c>
       <c r="C93" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D93" t="s">
         <v>134</v>
       </c>
       <c r="E93" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F93" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -35645,37 +35639,37 @@
         <v>0</v>
       </c>
       <c r="C94" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D94" t="s">
         <v>137</v>
       </c>
       <c r="E94" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F94" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G94">
         <v>100</v>
       </c>
       <c r="H94" t="s">
+        <v>264</v>
+      </c>
+      <c r="I94" t="s">
+        <v>265</v>
+      </c>
+      <c r="J94" t="s">
         <v>266</v>
       </c>
-      <c r="I94" t="s">
+      <c r="K94" t="s">
         <v>267</v>
       </c>
-      <c r="J94" t="s">
+      <c r="L94" t="s">
         <v>268</v>
       </c>
-      <c r="K94" t="s">
+      <c r="M94" t="s">
         <v>269</v>
-      </c>
-      <c r="L94" t="s">
-        <v>270</v>
-      </c>
-      <c r="M94" t="s">
-        <v>271</v>
       </c>
       <c r="N94">
         <v>0</v>
@@ -35702,37 +35696,37 @@
         <v>0</v>
       </c>
       <c r="C95" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D95" t="s">
         <v>140</v>
       </c>
       <c r="E95" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F95" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G95">
         <v>5</v>
       </c>
       <c r="H95" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I95" t="s">
+        <v>271</v>
+      </c>
+      <c r="J95" t="s">
+        <v>272</v>
+      </c>
+      <c r="K95" t="s">
         <v>273</v>
       </c>
-      <c r="J95" t="s">
+      <c r="L95" t="s">
         <v>274</v>
       </c>
-      <c r="K95" t="s">
+      <c r="M95" t="s">
         <v>275</v>
-      </c>
-      <c r="L95" t="s">
-        <v>276</v>
-      </c>
-      <c r="M95" t="s">
-        <v>277</v>
       </c>
       <c r="N95">
         <v>0</v>
@@ -35759,16 +35753,16 @@
         <v>0</v>
       </c>
       <c r="C96" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D96" t="s">
+        <v>276</v>
+      </c>
+      <c r="E96" t="s">
+        <v>277</v>
+      </c>
+      <c r="F96" t="s">
         <v>278</v>
-      </c>
-      <c r="E96" t="s">
-        <v>279</v>
-      </c>
-      <c r="F96" t="s">
-        <v>280</v>
       </c>
       <c r="G96">
         <v>4</v>
@@ -35816,16 +35810,16 @@
         <v>0</v>
       </c>
       <c r="C97" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D97" t="s">
+        <v>279</v>
+      </c>
+      <c r="E97" t="s">
+        <v>280</v>
+      </c>
+      <c r="F97" t="s">
         <v>281</v>
-      </c>
-      <c r="E97" t="s">
-        <v>282</v>
-      </c>
-      <c r="F97" t="s">
-        <v>283</v>
       </c>
       <c r="G97">
         <v>1.3</v>
@@ -35873,16 +35867,16 @@
         <v>0</v>
       </c>
       <c r="C98" t="s">
+        <v>282</v>
+      </c>
+      <c r="D98" t="s">
+        <v>283</v>
+      </c>
+      <c r="E98" t="s">
         <v>284</v>
       </c>
-      <c r="D98" t="s">
+      <c r="F98" t="s">
         <v>285</v>
-      </c>
-      <c r="E98" t="s">
-        <v>286</v>
-      </c>
-      <c r="F98" t="s">
-        <v>287</v>
       </c>
       <c r="G98">
         <v>1</v>
@@ -35930,16 +35924,16 @@
         <v>0</v>
       </c>
       <c r="C99" t="s">
+        <v>282</v>
+      </c>
+      <c r="D99" t="s">
+        <v>286</v>
+      </c>
+      <c r="E99" t="s">
         <v>284</v>
       </c>
-      <c r="D99" t="s">
-        <v>288</v>
-      </c>
-      <c r="E99" t="s">
-        <v>286</v>
-      </c>
       <c r="F99" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G99">
         <v>2.2000000000000002</v>
@@ -35987,16 +35981,16 @@
         <v>0</v>
       </c>
       <c r="C100" t="s">
+        <v>282</v>
+      </c>
+      <c r="D100" t="s">
+        <v>287</v>
+      </c>
+      <c r="E100" t="s">
         <v>284</v>
       </c>
-      <c r="D100" t="s">
-        <v>289</v>
-      </c>
-      <c r="E100" t="s">
-        <v>286</v>
-      </c>
       <c r="F100" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G100">
         <v>4.5</v>
@@ -36044,16 +36038,16 @@
         <v>0</v>
       </c>
       <c r="C101" t="s">
+        <v>282</v>
+      </c>
+      <c r="D101" t="s">
+        <v>288</v>
+      </c>
+      <c r="E101" t="s">
         <v>284</v>
       </c>
-      <c r="D101" t="s">
-        <v>290</v>
-      </c>
-      <c r="E101" t="s">
-        <v>286</v>
-      </c>
       <c r="F101" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G101">
         <v>10</v>
@@ -36101,16 +36095,16 @@
         <v>0</v>
       </c>
       <c r="C102" t="s">
+        <v>282</v>
+      </c>
+      <c r="D102" t="s">
+        <v>289</v>
+      </c>
+      <c r="E102" t="s">
         <v>284</v>
       </c>
-      <c r="D102" t="s">
-        <v>291</v>
-      </c>
-      <c r="E102" t="s">
-        <v>286</v>
-      </c>
       <c r="F102" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G102">
         <v>25</v>
@@ -36158,16 +36152,16 @@
         <v>0</v>
       </c>
       <c r="C103" t="s">
+        <v>282</v>
+      </c>
+      <c r="D103" t="s">
+        <v>290</v>
+      </c>
+      <c r="E103" t="s">
         <v>284</v>
       </c>
-      <c r="D103" t="s">
-        <v>292</v>
-      </c>
-      <c r="E103" t="s">
-        <v>286</v>
-      </c>
       <c r="F103" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G103">
         <v>60</v>
@@ -36212,25 +36206,25 @@
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C104" t="s">
+        <v>291</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E104" t="s">
         <v>293</v>
       </c>
-      <c r="D104" s="1" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E104" t="s">
-        <v>295</v>
-      </c>
       <c r="F104" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>1062</v>
-      </c>
-      <c r="H104">
-        <v>0</v>
+        <v>1069</v>
+      </c>
+      <c r="H104" t="s">
+        <v>310</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -36269,28 +36263,28 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C105" t="s">
+        <v>291</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E105" t="s">
         <v>293</v>
       </c>
-      <c r="D105" s="1" t="s">
-        <v>1053</v>
-      </c>
-      <c r="E105" t="s">
-        <v>295</v>
-      </c>
       <c r="F105" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="I105">
-        <v>0</v>
+        <v>310</v>
+      </c>
+      <c r="I105" t="s">
+        <v>1071</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -36326,31 +36320,31 @@
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C106" t="s">
+        <v>291</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E106" t="s">
         <v>293</v>
       </c>
-      <c r="D106" s="1" t="s">
-        <v>1054</v>
-      </c>
-      <c r="E106" t="s">
-        <v>295</v>
-      </c>
       <c r="F106" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>1061</v>
+        <v>1072</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>1065</v>
+        <v>1073</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>1060</v>
-      </c>
-      <c r="J106">
-        <v>0</v>
+        <v>1074</v>
+      </c>
+      <c r="J106" t="s">
+        <v>1075</v>
       </c>
       <c r="K106">
         <v>0</v>
@@ -36383,31 +36377,31 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C107" t="s">
+        <v>291</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E107" t="s">
         <v>293</v>
       </c>
-      <c r="D107" s="1" t="s">
-        <v>1055</v>
-      </c>
-      <c r="E107" t="s">
-        <v>295</v>
-      </c>
       <c r="F107" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>1068</v>
+        <v>1076</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>1065</v>
+        <v>1077</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>1066</v>
+        <v>1079</v>
       </c>
       <c r="K107">
         <v>0</v>
@@ -36440,34 +36434,34 @@
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="C108" t="s">
+        <v>291</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E108" t="s">
         <v>293</v>
       </c>
-      <c r="D108" s="1" t="s">
-        <v>1056</v>
-      </c>
-      <c r="E108" t="s">
-        <v>295</v>
-      </c>
       <c r="F108" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>1071</v>
+        <v>1080</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>1059</v>
+        <v>1081</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>1070</v>
+        <v>297</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>1058</v>
+        <v>1082</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>1069</v>
+        <v>1083</v>
       </c>
       <c r="L108">
         <v>0</v>
@@ -36500,49 +36494,49 @@
         <v>0</v>
       </c>
       <c r="C109" t="s">
+        <v>291</v>
+      </c>
+      <c r="D109" t="s">
+        <v>292</v>
+      </c>
+      <c r="E109" t="s">
         <v>293</v>
       </c>
-      <c r="D109" t="s">
+      <c r="F109" t="s">
         <v>294</v>
       </c>
-      <c r="E109" t="s">
+      <c r="G109" t="s">
         <v>295</v>
       </c>
-      <c r="F109" t="s">
+      <c r="H109" t="s">
         <v>296</v>
       </c>
-      <c r="G109" t="s">
+      <c r="I109" t="s">
         <v>297</v>
       </c>
-      <c r="H109" t="s">
+      <c r="J109" t="s">
         <v>298</v>
       </c>
-      <c r="I109" t="s">
+      <c r="K109" t="s">
         <v>299</v>
       </c>
-      <c r="J109" t="s">
+      <c r="L109" t="s">
         <v>300</v>
       </c>
-      <c r="K109" t="s">
+      <c r="M109" t="s">
         <v>301</v>
       </c>
-      <c r="L109" t="s">
+      <c r="N109" t="s">
         <v>302</v>
       </c>
-      <c r="M109" t="s">
+      <c r="O109" t="s">
         <v>303</v>
       </c>
-      <c r="N109" t="s">
+      <c r="P109" t="s">
         <v>304</v>
       </c>
-      <c r="O109" t="s">
+      <c r="Q109" t="s">
         <v>305</v>
-      </c>
-      <c r="P109" t="s">
-        <v>306</v>
-      </c>
-      <c r="Q109" t="s">
-        <v>307</v>
       </c>
       <c r="R109">
         <v>0</v>
@@ -36557,25 +36551,25 @@
         <v>0</v>
       </c>
       <c r="C110" t="s">
+        <v>291</v>
+      </c>
+      <c r="D110" t="s">
+        <v>306</v>
+      </c>
+      <c r="E110" t="s">
         <v>293</v>
       </c>
-      <c r="D110" t="s">
+      <c r="F110" t="s">
+        <v>307</v>
+      </c>
+      <c r="G110" t="s">
         <v>308</v>
       </c>
-      <c r="E110" t="s">
-        <v>295</v>
-      </c>
-      <c r="F110" t="s">
+      <c r="H110" t="s">
         <v>309</v>
       </c>
-      <c r="G110" t="s">
+      <c r="I110" t="s">
         <v>310</v>
-      </c>
-      <c r="H110" t="s">
-        <v>311</v>
-      </c>
-      <c r="I110" t="s">
-        <v>312</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -36614,19 +36608,19 @@
         <v>0</v>
       </c>
       <c r="C111" t="s">
+        <v>291</v>
+      </c>
+      <c r="D111" t="s">
+        <v>311</v>
+      </c>
+      <c r="E111" t="s">
         <v>293</v>
       </c>
-      <c r="D111" t="s">
+      <c r="F111" t="s">
+        <v>312</v>
+      </c>
+      <c r="G111" t="s">
         <v>313</v>
-      </c>
-      <c r="E111" t="s">
-        <v>295</v>
-      </c>
-      <c r="F111" t="s">
-        <v>314</v>
-      </c>
-      <c r="G111" t="s">
-        <v>315</v>
       </c>
       <c r="H111">
         <v>0</v>
@@ -36671,16 +36665,16 @@
         <v>0</v>
       </c>
       <c r="C112" t="s">
+        <v>314</v>
+      </c>
+      <c r="D112" t="s">
+        <v>315</v>
+      </c>
+      <c r="E112" t="s">
         <v>316</v>
       </c>
-      <c r="D112" t="s">
+      <c r="F112" t="s">
         <v>317</v>
-      </c>
-      <c r="E112" t="s">
-        <v>318</v>
-      </c>
-      <c r="F112" t="s">
-        <v>319</v>
       </c>
       <c r="G112">
         <v>4</v>
@@ -36728,16 +36722,16 @@
         <v>0</v>
       </c>
       <c r="C113" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D113" t="s">
+        <v>318</v>
+      </c>
+      <c r="E113" t="s">
+        <v>319</v>
+      </c>
+      <c r="F113" t="s">
         <v>320</v>
-      </c>
-      <c r="E113" t="s">
-        <v>321</v>
-      </c>
-      <c r="F113" t="s">
-        <v>322</v>
       </c>
       <c r="G113">
         <v>2</v>
@@ -36785,16 +36779,16 @@
         <v>0</v>
       </c>
       <c r="C114" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D114" t="s">
+        <v>321</v>
+      </c>
+      <c r="E114" t="s">
+        <v>322</v>
+      </c>
+      <c r="F114" t="s">
         <v>323</v>
-      </c>
-      <c r="E114" t="s">
-        <v>324</v>
-      </c>
-      <c r="F114" t="s">
-        <v>325</v>
       </c>
       <c r="G114">
         <v>2</v>
@@ -36842,16 +36836,16 @@
         <v>0</v>
       </c>
       <c r="C115" t="s">
+        <v>324</v>
+      </c>
+      <c r="D115" t="s">
+        <v>325</v>
+      </c>
+      <c r="E115" t="s">
         <v>326</v>
       </c>
-      <c r="D115" t="s">
+      <c r="F115" t="s">
         <v>327</v>
-      </c>
-      <c r="E115" t="s">
-        <v>328</v>
-      </c>
-      <c r="F115" t="s">
-        <v>329</v>
       </c>
       <c r="G115">
         <v>50</v>
@@ -36899,16 +36893,16 @@
         <v>0</v>
       </c>
       <c r="C116" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D116" t="s">
+        <v>328</v>
+      </c>
+      <c r="E116" t="s">
+        <v>329</v>
+      </c>
+      <c r="F116" t="s">
         <v>330</v>
-      </c>
-      <c r="E116" t="s">
-        <v>331</v>
-      </c>
-      <c r="F116" t="s">
-        <v>332</v>
       </c>
       <c r="G116">
         <v>20</v>
@@ -36956,16 +36950,16 @@
         <v>0</v>
       </c>
       <c r="C117" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D117" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E117" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F117" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="G117">
         <v>3</v>
@@ -37013,16 +37007,16 @@
         <v>0</v>
       </c>
       <c r="C118" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D118" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E118" t="s">
         <v>39</v>
       </c>
       <c r="F118" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G118">
         <v>1</v>
@@ -37040,7 +37034,7 @@
         <v>1</v>
       </c>
       <c r="L118" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="M118">
         <v>0</v>
@@ -37070,16 +37064,16 @@
         <v>0</v>
       </c>
       <c r="C119" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D119" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E119" t="s">
         <v>39</v>
       </c>
       <c r="F119" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G119">
         <v>2.2000000000000002</v>
@@ -37097,7 +37091,7 @@
         <v>1.25</v>
       </c>
       <c r="L119" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="M119">
         <v>0</v>
@@ -37127,16 +37121,16 @@
         <v>0</v>
       </c>
       <c r="C120" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D120" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E120" t="s">
         <v>39</v>
       </c>
       <c r="F120" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G120">
         <v>4</v>
@@ -37154,7 +37148,7 @@
         <v>1.5</v>
       </c>
       <c r="L120" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="M120">
         <v>0</v>
@@ -37184,16 +37178,16 @@
         <v>0</v>
       </c>
       <c r="C121" t="s">
+        <v>337</v>
+      </c>
+      <c r="D121" t="s">
+        <v>338</v>
+      </c>
+      <c r="E121" t="s">
         <v>339</v>
       </c>
-      <c r="D121" t="s">
+      <c r="F121" t="s">
         <v>340</v>
-      </c>
-      <c r="E121" t="s">
-        <v>341</v>
-      </c>
-      <c r="F121" t="s">
-        <v>342</v>
       </c>
       <c r="G121">
         <v>4</v>
@@ -37241,16 +37235,16 @@
         <v>0</v>
       </c>
       <c r="C122" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D122" t="s">
+        <v>341</v>
+      </c>
+      <c r="E122" t="s">
+        <v>342</v>
+      </c>
+      <c r="F122" t="s">
         <v>343</v>
-      </c>
-      <c r="E122" t="s">
-        <v>344</v>
-      </c>
-      <c r="F122" t="s">
-        <v>345</v>
       </c>
       <c r="G122">
         <v>3</v>
@@ -37298,16 +37292,16 @@
         <v>0</v>
       </c>
       <c r="C123" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D123" t="s">
         <v>137</v>
       </c>
       <c r="E123" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F123" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G123">
         <v>200</v>
@@ -37355,25 +37349,25 @@
         <v>0</v>
       </c>
       <c r="C124" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D124" t="s">
+        <v>346</v>
+      </c>
+      <c r="E124" t="s">
+        <v>347</v>
+      </c>
+      <c r="F124" t="s">
         <v>348</v>
       </c>
-      <c r="E124" t="s">
+      <c r="G124" t="s">
         <v>349</v>
       </c>
-      <c r="F124" t="s">
+      <c r="H124" t="s">
         <v>350</v>
       </c>
-      <c r="G124" t="s">
+      <c r="I124" t="s">
         <v>351</v>
-      </c>
-      <c r="H124" t="s">
-        <v>352</v>
-      </c>
-      <c r="I124" t="s">
-        <v>353</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -37412,16 +37406,16 @@
         <v>0</v>
       </c>
       <c r="C125" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D125" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E125" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F125" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G125">
         <v>20</v>
@@ -37469,16 +37463,16 @@
         <v>0</v>
       </c>
       <c r="C126" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D126" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E126" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F126" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G126">
         <v>3</v>
@@ -37526,16 +37520,16 @@
         <v>0</v>
       </c>
       <c r="C127" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D127" t="s">
+        <v>356</v>
+      </c>
+      <c r="E127" t="s">
+        <v>357</v>
+      </c>
+      <c r="F127" t="s">
         <v>358</v>
-      </c>
-      <c r="E127" t="s">
-        <v>359</v>
-      </c>
-      <c r="F127" t="s">
-        <v>360</v>
       </c>
       <c r="G127">
         <v>10</v>
@@ -37583,16 +37577,16 @@
         <v>0</v>
       </c>
       <c r="C128" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D128" t="s">
+        <v>359</v>
+      </c>
+      <c r="E128" t="s">
+        <v>360</v>
+      </c>
+      <c r="F128" t="s">
         <v>361</v>
-      </c>
-      <c r="E128" t="s">
-        <v>362</v>
-      </c>
-      <c r="F128" t="s">
-        <v>363</v>
       </c>
       <c r="G128">
         <v>3</v>
@@ -37640,16 +37634,16 @@
         <v>0</v>
       </c>
       <c r="C129" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D129" t="s">
         <v>140</v>
       </c>
       <c r="E129" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F129" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G129">
         <v>20</v>
@@ -37697,16 +37691,16 @@
         <v>0</v>
       </c>
       <c r="C130" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D130" t="s">
+        <v>364</v>
+      </c>
+      <c r="E130" t="s">
+        <v>365</v>
+      </c>
+      <c r="F130" t="s">
         <v>366</v>
-      </c>
-      <c r="E130" t="s">
-        <v>367</v>
-      </c>
-      <c r="F130" t="s">
-        <v>368</v>
       </c>
       <c r="G130">
         <v>3</v>
@@ -37754,16 +37748,16 @@
         <v>0</v>
       </c>
       <c r="C131" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D131" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E131" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F131" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G131">
         <v>2</v>
@@ -37811,16 +37805,16 @@
         <v>0</v>
       </c>
       <c r="C132" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D132" t="s">
+        <v>369</v>
+      </c>
+      <c r="E132" t="s">
+        <v>370</v>
+      </c>
+      <c r="F132" t="s">
         <v>371</v>
-      </c>
-      <c r="E132" t="s">
-        <v>372</v>
-      </c>
-      <c r="F132" t="s">
-        <v>373</v>
       </c>
       <c r="G132">
         <v>60</v>
@@ -37868,16 +37862,16 @@
         <v>0</v>
       </c>
       <c r="C133" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D133" t="s">
+        <v>372</v>
+      </c>
+      <c r="E133" t="s">
+        <v>373</v>
+      </c>
+      <c r="F133" t="s">
         <v>374</v>
-      </c>
-      <c r="E133" t="s">
-        <v>375</v>
-      </c>
-      <c r="F133" t="s">
-        <v>376</v>
       </c>
       <c r="G133">
         <v>51</v>
@@ -37925,16 +37919,16 @@
         <v>0</v>
       </c>
       <c r="C134" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D134" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E134" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F134" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G134">
         <v>1</v>
@@ -37982,16 +37976,16 @@
         <v>0</v>
       </c>
       <c r="C135" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D135" t="s">
+        <v>377</v>
+      </c>
+      <c r="E135" t="s">
+        <v>378</v>
+      </c>
+      <c r="F135" t="s">
         <v>379</v>
-      </c>
-      <c r="E135" t="s">
-        <v>380</v>
-      </c>
-      <c r="F135" t="s">
-        <v>381</v>
       </c>
       <c r="G135">
         <v>5</v>
@@ -38039,16 +38033,16 @@
         <v>0</v>
       </c>
       <c r="C136" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D136" t="s">
+        <v>380</v>
+      </c>
+      <c r="E136" t="s">
+        <v>381</v>
+      </c>
+      <c r="F136" t="s">
         <v>382</v>
-      </c>
-      <c r="E136" t="s">
-        <v>383</v>
-      </c>
-      <c r="F136" t="s">
-        <v>384</v>
       </c>
       <c r="G136">
         <v>100</v>
@@ -38096,16 +38090,16 @@
         <v>0</v>
       </c>
       <c r="C137" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D137" t="s">
+        <v>383</v>
+      </c>
+      <c r="E137" t="s">
+        <v>384</v>
+      </c>
+      <c r="F137" t="s">
         <v>385</v>
-      </c>
-      <c r="E137" t="s">
-        <v>386</v>
-      </c>
-      <c r="F137" t="s">
-        <v>387</v>
       </c>
       <c r="G137">
         <v>30</v>
@@ -38153,25 +38147,25 @@
         <v>0</v>
       </c>
       <c r="C138" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D138" t="s">
+        <v>386</v>
+      </c>
+      <c r="E138" t="s">
+        <v>387</v>
+      </c>
+      <c r="F138" t="s">
+        <v>376</v>
+      </c>
+      <c r="G138" t="s">
         <v>388</v>
       </c>
-      <c r="E138" t="s">
+      <c r="H138" t="s">
         <v>389</v>
       </c>
-      <c r="F138" t="s">
-        <v>378</v>
-      </c>
-      <c r="G138" t="s">
+      <c r="I138" t="s">
         <v>390</v>
-      </c>
-      <c r="H138" t="s">
-        <v>391</v>
-      </c>
-      <c r="I138" t="s">
-        <v>392</v>
       </c>
       <c r="J138">
         <v>0</v>
@@ -38210,16 +38204,16 @@
         <v>0</v>
       </c>
       <c r="C139" t="s">
+        <v>391</v>
+      </c>
+      <c r="D139" t="s">
+        <v>392</v>
+      </c>
+      <c r="E139" t="s">
         <v>393</v>
       </c>
-      <c r="D139" t="s">
+      <c r="F139" t="s">
         <v>394</v>
-      </c>
-      <c r="E139" t="s">
-        <v>395</v>
-      </c>
-      <c r="F139" t="s">
-        <v>396</v>
       </c>
       <c r="G139">
         <v>0.5</v>
@@ -38267,16 +38261,16 @@
         <v>0</v>
       </c>
       <c r="C140" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D140" t="s">
+        <v>395</v>
+      </c>
+      <c r="E140" t="s">
+        <v>396</v>
+      </c>
+      <c r="F140" t="s">
         <v>397</v>
-      </c>
-      <c r="E140" t="s">
-        <v>398</v>
-      </c>
-      <c r="F140" t="s">
-        <v>399</v>
       </c>
       <c r="G140">
         <v>50</v>
@@ -38324,16 +38318,16 @@
         <v>0</v>
       </c>
       <c r="C141" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D141" t="s">
+        <v>398</v>
+      </c>
+      <c r="E141" t="s">
+        <v>399</v>
+      </c>
+      <c r="F141" t="s">
         <v>400</v>
-      </c>
-      <c r="E141" t="s">
-        <v>401</v>
-      </c>
-      <c r="F141" t="s">
-        <v>402</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -38381,16 +38375,16 @@
         <v>0</v>
       </c>
       <c r="C142" t="s">
+        <v>401</v>
+      </c>
+      <c r="D142" t="s">
+        <v>402</v>
+      </c>
+      <c r="E142" t="s">
         <v>403</v>
       </c>
-      <c r="D142" t="s">
+      <c r="F142" t="s">
         <v>404</v>
-      </c>
-      <c r="E142" t="s">
-        <v>405</v>
-      </c>
-      <c r="F142" t="s">
-        <v>406</v>
       </c>
       <c r="G142">
         <v>200</v>
@@ -38438,28 +38432,28 @@
         <v>0</v>
       </c>
       <c r="C143" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D143" t="s">
+        <v>405</v>
+      </c>
+      <c r="E143" t="s">
+        <v>406</v>
+      </c>
+      <c r="F143" t="s">
         <v>407</v>
-      </c>
-      <c r="E143" t="s">
-        <v>408</v>
-      </c>
-      <c r="F143" t="s">
-        <v>409</v>
       </c>
       <c r="G143">
         <v>55</v>
       </c>
       <c r="H143" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I143" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="J143" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="K143">
         <v>0</v>
@@ -38495,28 +38489,28 @@
         <v>0</v>
       </c>
       <c r="C144" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D144" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E144" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F144" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G144">
         <v>25</v>
       </c>
       <c r="H144" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I144">
         <v>2</v>
       </c>
       <c r="J144" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="K144">
         <v>0</v>
@@ -38552,28 +38546,28 @@
         <v>0</v>
       </c>
       <c r="C145" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D145" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E145" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F145" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G145">
         <v>12</v>
       </c>
       <c r="H145" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I145">
         <v>2.5</v>
       </c>
       <c r="J145" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="K145">
         <v>0</v>
@@ -38609,28 +38603,28 @@
         <v>0</v>
       </c>
       <c r="C146" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D146" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E146" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F146" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G146">
         <v>5.5</v>
       </c>
       <c r="H146" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I146">
         <v>3</v>
       </c>
       <c r="J146" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="K146">
         <v>0</v>
@@ -38666,28 +38660,28 @@
         <v>0</v>
       </c>
       <c r="C147" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D147" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E147" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F147" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G147">
         <v>1.8</v>
       </c>
       <c r="H147" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I147">
         <v>3.5</v>
       </c>
       <c r="J147" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="K147">
         <v>0</v>
@@ -38723,28 +38717,28 @@
         <v>0</v>
       </c>
       <c r="C148" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D148" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E148" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F148" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G148">
         <v>0.35</v>
       </c>
       <c r="H148" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I148">
         <v>4</v>
       </c>
       <c r="J148" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="K148">
         <v>0</v>
@@ -38780,28 +38774,28 @@
         <v>0</v>
       </c>
       <c r="C149" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D149" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E149" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F149" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G149">
         <v>0.08</v>
       </c>
       <c r="H149" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I149">
         <v>4.5</v>
       </c>
       <c r="J149" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="K149">
         <v>0</v>
@@ -38837,28 +38831,28 @@
         <v>0</v>
       </c>
       <c r="C150" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D150" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E150" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F150" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G150">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="H150" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I150">
         <v>5</v>
       </c>
       <c r="J150" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="K150">
         <v>0</v>
@@ -38894,37 +38888,37 @@
         <v>0</v>
       </c>
       <c r="C151" t="s">
+        <v>421</v>
+      </c>
+      <c r="D151" t="s">
+        <v>422</v>
+      </c>
+      <c r="E151" t="s">
         <v>423</v>
       </c>
-      <c r="D151" t="s">
+      <c r="F151" t="s">
         <v>424</v>
       </c>
-      <c r="E151" t="s">
+      <c r="G151" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I151" t="s">
         <v>425</v>
       </c>
-      <c r="F151" t="s">
+      <c r="J151" t="s">
         <v>426</v>
       </c>
-      <c r="G151" s="2" t="s">
-        <v>1076</v>
-      </c>
-      <c r="H151" s="2" t="s">
-        <v>1077</v>
-      </c>
-      <c r="I151" t="s">
+      <c r="K151" t="s">
         <v>427</v>
       </c>
-      <c r="J151" t="s">
+      <c r="L151" t="s">
         <v>428</v>
       </c>
-      <c r="K151" t="s">
+      <c r="M151" t="s">
         <v>429</v>
-      </c>
-      <c r="L151" t="s">
-        <v>430</v>
-      </c>
-      <c r="M151" t="s">
-        <v>431</v>
       </c>
       <c r="N151">
         <v>0</v>
@@ -38951,37 +38945,37 @@
         <v>0</v>
       </c>
       <c r="C152" t="s">
+        <v>421</v>
+      </c>
+      <c r="D152" t="s">
+        <v>430</v>
+      </c>
+      <c r="E152" t="s">
         <v>423</v>
       </c>
-      <c r="D152" t="s">
+      <c r="F152" t="s">
+        <v>424</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="I152" t="s">
+        <v>431</v>
+      </c>
+      <c r="J152" t="s">
         <v>432</v>
       </c>
-      <c r="E152" t="s">
-        <v>425</v>
-      </c>
-      <c r="F152" t="s">
-        <v>426</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>1079</v>
-      </c>
-      <c r="H152" s="2" t="s">
-        <v>1078</v>
-      </c>
-      <c r="I152" t="s">
+      <c r="K152" t="s">
         <v>433</v>
       </c>
-      <c r="J152" t="s">
+      <c r="L152" t="s">
         <v>434</v>
       </c>
-      <c r="K152" t="s">
+      <c r="M152" t="s">
         <v>435</v>
-      </c>
-      <c r="L152" t="s">
-        <v>436</v>
-      </c>
-      <c r="M152" t="s">
-        <v>437</v>
       </c>
       <c r="N152">
         <v>0</v>
@@ -39008,37 +39002,37 @@
         <v>0</v>
       </c>
       <c r="C153" t="s">
+        <v>421</v>
+      </c>
+      <c r="D153" t="s">
+        <v>436</v>
+      </c>
+      <c r="E153" t="s">
         <v>423</v>
       </c>
-      <c r="D153" t="s">
+      <c r="F153" t="s">
+        <v>424</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="J153" t="s">
+        <v>437</v>
+      </c>
+      <c r="K153" t="s">
         <v>438</v>
       </c>
-      <c r="E153" t="s">
-        <v>425</v>
-      </c>
-      <c r="F153" t="s">
-        <v>426</v>
-      </c>
-      <c r="G153" s="2" t="s">
-        <v>1080</v>
-      </c>
-      <c r="H153" s="2" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I153" s="2" t="s">
-        <v>1075</v>
-      </c>
-      <c r="J153" t="s">
+      <c r="L153" t="s">
         <v>439</v>
       </c>
-      <c r="K153" t="s">
+      <c r="M153" t="s">
         <v>440</v>
-      </c>
-      <c r="L153" t="s">
-        <v>441</v>
-      </c>
-      <c r="M153" t="s">
-        <v>442</v>
       </c>
       <c r="N153">
         <v>0</v>
@@ -39065,37 +39059,37 @@
         <v>0</v>
       </c>
       <c r="C154" t="s">
+        <v>421</v>
+      </c>
+      <c r="D154" t="s">
+        <v>441</v>
+      </c>
+      <c r="E154" t="s">
         <v>423</v>
       </c>
-      <c r="D154" t="s">
+      <c r="F154" t="s">
+        <v>424</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>1065</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="I154" t="s">
         <v>443</v>
       </c>
-      <c r="E154" t="s">
-        <v>425</v>
-      </c>
-      <c r="F154" t="s">
-        <v>426</v>
-      </c>
-      <c r="G154" s="2" t="s">
-        <v>1081</v>
-      </c>
-      <c r="H154" s="2" t="s">
-        <v>1082</v>
-      </c>
-      <c r="I154" t="s">
+      <c r="J154" t="s">
+        <v>444</v>
+      </c>
+      <c r="K154" t="s">
         <v>445</v>
       </c>
-      <c r="J154" t="s">
+      <c r="L154" t="s">
         <v>446</v>
       </c>
-      <c r="K154" t="s">
+      <c r="M154" t="s">
         <v>447</v>
-      </c>
-      <c r="L154" t="s">
-        <v>448</v>
-      </c>
-      <c r="M154" t="s">
-        <v>449</v>
       </c>
       <c r="N154">
         <v>0</v>
@@ -39122,37 +39116,37 @@
         <v>0</v>
       </c>
       <c r="C155" t="s">
+        <v>421</v>
+      </c>
+      <c r="D155" t="s">
+        <v>448</v>
+      </c>
+      <c r="E155" t="s">
         <v>423</v>
       </c>
-      <c r="D155" t="s">
+      <c r="F155" t="s">
+        <v>424</v>
+      </c>
+      <c r="G155" t="s">
+        <v>442</v>
+      </c>
+      <c r="H155" t="s">
+        <v>449</v>
+      </c>
+      <c r="I155" t="s">
         <v>450</v>
       </c>
-      <c r="E155" t="s">
-        <v>425</v>
-      </c>
-      <c r="F155" t="s">
-        <v>426</v>
-      </c>
-      <c r="G155" t="s">
-        <v>444</v>
-      </c>
-      <c r="H155" t="s">
+      <c r="J155" t="s">
         <v>451</v>
       </c>
-      <c r="I155" t="s">
+      <c r="K155" t="s">
         <v>452</v>
       </c>
-      <c r="J155" t="s">
+      <c r="L155" t="s">
         <v>453</v>
       </c>
-      <c r="K155" t="s">
+      <c r="M155" t="s">
         <v>454</v>
-      </c>
-      <c r="L155" t="s">
-        <v>455</v>
-      </c>
-      <c r="M155" t="s">
-        <v>456</v>
       </c>
       <c r="N155">
         <v>0</v>
@@ -39179,37 +39173,37 @@
         <v>0</v>
       </c>
       <c r="C156" t="s">
+        <v>421</v>
+      </c>
+      <c r="D156" t="s">
+        <v>455</v>
+      </c>
+      <c r="E156" t="s">
         <v>423</v>
       </c>
-      <c r="D156" t="s">
+      <c r="F156" t="s">
+        <v>424</v>
+      </c>
+      <c r="G156" t="s">
+        <v>442</v>
+      </c>
+      <c r="H156" t="s">
+        <v>456</v>
+      </c>
+      <c r="I156" t="s">
+        <v>266</v>
+      </c>
+      <c r="J156" t="s">
         <v>457</v>
       </c>
-      <c r="E156" t="s">
-        <v>425</v>
-      </c>
-      <c r="F156" t="s">
-        <v>426</v>
-      </c>
-      <c r="G156" t="s">
-        <v>444</v>
-      </c>
-      <c r="H156" t="s">
+      <c r="K156" t="s">
         <v>458</v>
       </c>
-      <c r="I156" t="s">
-        <v>268</v>
-      </c>
-      <c r="J156" t="s">
+      <c r="L156" t="s">
         <v>459</v>
       </c>
-      <c r="K156" t="s">
+      <c r="M156" t="s">
         <v>460</v>
-      </c>
-      <c r="L156" t="s">
-        <v>461</v>
-      </c>
-      <c r="M156" t="s">
-        <v>462</v>
       </c>
       <c r="N156">
         <v>0</v>
@@ -39236,37 +39230,37 @@
         <v>0</v>
       </c>
       <c r="C157" t="s">
+        <v>421</v>
+      </c>
+      <c r="D157" t="s">
+        <v>461</v>
+      </c>
+      <c r="E157" t="s">
         <v>423</v>
       </c>
-      <c r="D157" t="s">
+      <c r="F157" t="s">
+        <v>424</v>
+      </c>
+      <c r="G157" t="s">
+        <v>442</v>
+      </c>
+      <c r="H157" t="s">
+        <v>456</v>
+      </c>
+      <c r="I157" t="s">
+        <v>462</v>
+      </c>
+      <c r="J157" t="s">
         <v>463</v>
       </c>
-      <c r="E157" t="s">
-        <v>425</v>
-      </c>
-      <c r="F157" t="s">
-        <v>426</v>
-      </c>
-      <c r="G157" t="s">
-        <v>444</v>
-      </c>
-      <c r="H157" t="s">
-        <v>458</v>
-      </c>
-      <c r="I157" t="s">
+      <c r="K157" t="s">
         <v>464</v>
       </c>
-      <c r="J157" t="s">
+      <c r="L157" t="s">
         <v>465</v>
       </c>
-      <c r="K157" t="s">
+      <c r="M157" t="s">
         <v>466</v>
-      </c>
-      <c r="L157" t="s">
-        <v>467</v>
-      </c>
-      <c r="M157" t="s">
-        <v>468</v>
       </c>
       <c r="N157">
         <v>0</v>
@@ -39293,37 +39287,37 @@
         <v>0</v>
       </c>
       <c r="C158" t="s">
+        <v>421</v>
+      </c>
+      <c r="D158" t="s">
+        <v>467</v>
+      </c>
+      <c r="E158" t="s">
         <v>423</v>
       </c>
-      <c r="D158" t="s">
+      <c r="F158" t="s">
+        <v>424</v>
+      </c>
+      <c r="G158" t="s">
+        <v>442</v>
+      </c>
+      <c r="H158" t="s">
+        <v>456</v>
+      </c>
+      <c r="I158" t="s">
+        <v>462</v>
+      </c>
+      <c r="J158" t="s">
+        <v>468</v>
+      </c>
+      <c r="K158" t="s">
         <v>469</v>
       </c>
-      <c r="E158" t="s">
-        <v>425</v>
-      </c>
-      <c r="F158" t="s">
-        <v>426</v>
-      </c>
-      <c r="G158" t="s">
-        <v>444</v>
-      </c>
-      <c r="H158" t="s">
-        <v>458</v>
-      </c>
-      <c r="I158" t="s">
-        <v>464</v>
-      </c>
-      <c r="J158" t="s">
+      <c r="L158" t="s">
         <v>470</v>
       </c>
-      <c r="K158" t="s">
+      <c r="M158" t="s">
         <v>471</v>
-      </c>
-      <c r="L158" t="s">
-        <v>472</v>
-      </c>
-      <c r="M158" t="s">
-        <v>473</v>
       </c>
       <c r="N158">
         <v>0</v>
@@ -39350,16 +39344,16 @@
         <v>0</v>
       </c>
       <c r="C159" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D159" t="s">
+        <v>472</v>
+      </c>
+      <c r="E159" t="s">
+        <v>473</v>
+      </c>
+      <c r="F159" t="s">
         <v>474</v>
-      </c>
-      <c r="E159" t="s">
-        <v>475</v>
-      </c>
-      <c r="F159" t="s">
-        <v>476</v>
       </c>
       <c r="G159">
         <v>551</v>
@@ -39407,16 +39401,16 @@
         <v>0</v>
       </c>
       <c r="C160" t="s">
+        <v>475</v>
+      </c>
+      <c r="D160" t="s">
+        <v>476</v>
+      </c>
+      <c r="E160" t="s">
         <v>477</v>
       </c>
-      <c r="D160" t="s">
+      <c r="F160" t="s">
         <v>478</v>
-      </c>
-      <c r="E160" t="s">
-        <v>479</v>
-      </c>
-      <c r="F160" t="s">
-        <v>480</v>
       </c>
       <c r="G160">
         <v>2</v>
@@ -39464,16 +39458,16 @@
         <v>0</v>
       </c>
       <c r="C161" t="s">
+        <v>475</v>
+      </c>
+      <c r="D161" t="s">
+        <v>479</v>
+      </c>
+      <c r="E161" t="s">
         <v>477</v>
       </c>
-      <c r="D161" t="s">
-        <v>481</v>
-      </c>
-      <c r="E161" t="s">
-        <v>479</v>
-      </c>
       <c r="F161" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G161">
         <v>4</v>
@@ -39521,16 +39515,16 @@
         <v>0</v>
       </c>
       <c r="C162" t="s">
+        <v>475</v>
+      </c>
+      <c r="D162" t="s">
+        <v>480</v>
+      </c>
+      <c r="E162" t="s">
         <v>477</v>
       </c>
-      <c r="D162" t="s">
-        <v>482</v>
-      </c>
-      <c r="E162" t="s">
-        <v>479</v>
-      </c>
       <c r="F162" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G162">
         <v>6</v>
@@ -39578,16 +39572,16 @@
         <v>0</v>
       </c>
       <c r="C163" t="s">
+        <v>475</v>
+      </c>
+      <c r="D163" t="s">
+        <v>481</v>
+      </c>
+      <c r="E163" t="s">
         <v>477</v>
       </c>
-      <c r="D163" t="s">
-        <v>483</v>
-      </c>
-      <c r="E163" t="s">
-        <v>479</v>
-      </c>
       <c r="F163" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G163">
         <v>8</v>
@@ -39635,16 +39629,16 @@
         <v>0</v>
       </c>
       <c r="C164" t="s">
+        <v>475</v>
+      </c>
+      <c r="D164" t="s">
+        <v>482</v>
+      </c>
+      <c r="E164" t="s">
         <v>477</v>
       </c>
-      <c r="D164" t="s">
-        <v>484</v>
-      </c>
-      <c r="E164" t="s">
-        <v>479</v>
-      </c>
       <c r="F164" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G164">
         <v>10</v>
@@ -39692,16 +39686,16 @@
         <v>0</v>
       </c>
       <c r="C165" t="s">
+        <v>475</v>
+      </c>
+      <c r="D165" t="s">
+        <v>483</v>
+      </c>
+      <c r="E165" t="s">
         <v>477</v>
       </c>
-      <c r="D165" t="s">
-        <v>485</v>
-      </c>
-      <c r="E165" t="s">
-        <v>479</v>
-      </c>
       <c r="F165" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G165">
         <v>12</v>
@@ -39749,16 +39743,16 @@
         <v>0</v>
       </c>
       <c r="C166" t="s">
+        <v>475</v>
+      </c>
+      <c r="D166" t="s">
+        <v>484</v>
+      </c>
+      <c r="E166" t="s">
         <v>477</v>
       </c>
-      <c r="D166" t="s">
-        <v>486</v>
-      </c>
-      <c r="E166" t="s">
-        <v>479</v>
-      </c>
       <c r="F166" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G166">
         <v>14</v>
@@ -39806,16 +39800,16 @@
         <v>0</v>
       </c>
       <c r="C167" t="s">
+        <v>485</v>
+      </c>
+      <c r="D167" t="s">
+        <v>486</v>
+      </c>
+      <c r="E167" t="s">
         <v>487</v>
       </c>
-      <c r="D167" t="s">
+      <c r="F167" t="s">
         <v>488</v>
-      </c>
-      <c r="E167" t="s">
-        <v>489</v>
-      </c>
-      <c r="F167" t="s">
-        <v>490</v>
       </c>
       <c r="G167">
         <v>4</v>
@@ -39863,16 +39857,16 @@
         <v>0</v>
       </c>
       <c r="C168" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D168" t="s">
+        <v>489</v>
+      </c>
+      <c r="E168" t="s">
+        <v>490</v>
+      </c>
+      <c r="F168" t="s">
         <v>491</v>
-      </c>
-      <c r="E168" t="s">
-        <v>492</v>
-      </c>
-      <c r="F168" t="s">
-        <v>493</v>
       </c>
       <c r="G168">
         <v>5</v>
@@ -39920,16 +39914,16 @@
         <v>0</v>
       </c>
       <c r="C169" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D169" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E169" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F169" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="G169">
         <v>10</v>
@@ -39977,16 +39971,16 @@
         <v>0</v>
       </c>
       <c r="C170" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D170" t="s">
+        <v>494</v>
+      </c>
+      <c r="E170" t="s">
+        <v>495</v>
+      </c>
+      <c r="F170" t="s">
         <v>496</v>
-      </c>
-      <c r="E170" t="s">
-        <v>497</v>
-      </c>
-      <c r="F170" t="s">
-        <v>498</v>
       </c>
       <c r="G170">
         <v>0.5</v>
@@ -40034,16 +40028,16 @@
         <v>0</v>
       </c>
       <c r="C171" t="s">
+        <v>497</v>
+      </c>
+      <c r="D171" t="s">
+        <v>498</v>
+      </c>
+      <c r="E171" t="s">
         <v>499</v>
       </c>
-      <c r="D171" t="s">
+      <c r="F171" t="s">
         <v>500</v>
-      </c>
-      <c r="E171" t="s">
-        <v>501</v>
-      </c>
-      <c r="F171" t="s">
-        <v>502</v>
       </c>
       <c r="G171">
         <v>100</v>
@@ -40091,16 +40085,16 @@
         <v>0</v>
       </c>
       <c r="C172" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D172" t="s">
+        <v>501</v>
+      </c>
+      <c r="E172" t="s">
+        <v>502</v>
+      </c>
+      <c r="F172" t="s">
         <v>503</v>
-      </c>
-      <c r="E172" t="s">
-        <v>504</v>
-      </c>
-      <c r="F172" t="s">
-        <v>505</v>
       </c>
       <c r="G172">
         <v>92</v>
@@ -40148,16 +40142,16 @@
         <v>0</v>
       </c>
       <c r="C173" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D173" t="s">
+        <v>504</v>
+      </c>
+      <c r="E173" t="s">
+        <v>505</v>
+      </c>
+      <c r="F173" t="s">
         <v>506</v>
-      </c>
-      <c r="E173" t="s">
-        <v>507</v>
-      </c>
-      <c r="F173" t="s">
-        <v>508</v>
       </c>
       <c r="G173">
         <v>78.099999999999994</v>
@@ -40205,16 +40199,16 @@
         <v>0</v>
       </c>
       <c r="C174" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D174" t="s">
+        <v>507</v>
+      </c>
+      <c r="E174" t="s">
+        <v>508</v>
+      </c>
+      <c r="F174" t="s">
         <v>509</v>
-      </c>
-      <c r="E174" t="s">
-        <v>510</v>
-      </c>
-      <c r="F174" t="s">
-        <v>511</v>
       </c>
       <c r="G174">
         <v>72.11</v>
@@ -40262,16 +40256,16 @@
         <v>0</v>
       </c>
       <c r="C175" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D175" t="s">
+        <v>510</v>
+      </c>
+      <c r="E175" t="s">
+        <v>511</v>
+      </c>
+      <c r="F175" t="s">
         <v>512</v>
-      </c>
-      <c r="E175" t="s">
-        <v>513</v>
-      </c>
-      <c r="F175" t="s">
-        <v>514</v>
       </c>
       <c r="G175">
         <v>74.349999999999994</v>
@@ -40319,16 +40313,16 @@
         <v>0</v>
       </c>
       <c r="C176" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D176" t="s">
+        <v>513</v>
+      </c>
+      <c r="E176" t="s">
+        <v>514</v>
+      </c>
+      <c r="F176" t="s">
         <v>515</v>
-      </c>
-      <c r="E176" t="s">
-        <v>516</v>
-      </c>
-      <c r="F176" t="s">
-        <v>517</v>
       </c>
       <c r="G176">
         <v>76.87</v>
@@ -40376,16 +40370,16 @@
         <v>0</v>
       </c>
       <c r="C177" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D177" t="s">
+        <v>516</v>
+      </c>
+      <c r="E177" t="s">
+        <v>517</v>
+      </c>
+      <c r="F177" t="s">
         <v>518</v>
-      </c>
-      <c r="E177" t="s">
-        <v>519</v>
-      </c>
-      <c r="F177" t="s">
-        <v>520</v>
       </c>
       <c r="G177">
         <v>69.92</v>
@@ -40433,16 +40427,16 @@
         <v>0</v>
       </c>
       <c r="C178" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D178" t="s">
+        <v>519</v>
+      </c>
+      <c r="E178" t="s">
+        <v>520</v>
+      </c>
+      <c r="F178" t="s">
         <v>521</v>
-      </c>
-      <c r="E178" t="s">
-        <v>522</v>
-      </c>
-      <c r="F178" t="s">
-        <v>523</v>
       </c>
       <c r="G178">
         <v>64.22</v>
@@ -40490,16 +40484,16 @@
         <v>0</v>
       </c>
       <c r="C179" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D179" t="s">
+        <v>522</v>
+      </c>
+      <c r="E179" t="s">
+        <v>523</v>
+      </c>
+      <c r="F179" t="s">
         <v>524</v>
-      </c>
-      <c r="E179" t="s">
-        <v>525</v>
-      </c>
-      <c r="F179" t="s">
-        <v>526</v>
       </c>
       <c r="G179">
         <v>59.92</v>
@@ -40547,16 +40541,16 @@
         <v>0</v>
       </c>
       <c r="C180" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D180" t="s">
+        <v>525</v>
+      </c>
+      <c r="E180" t="s">
+        <v>526</v>
+      </c>
+      <c r="F180" t="s">
         <v>527</v>
-      </c>
-      <c r="E180" t="s">
-        <v>528</v>
-      </c>
-      <c r="F180" t="s">
-        <v>529</v>
       </c>
       <c r="G180">
         <v>54.72</v>
@@ -40604,16 +40598,16 @@
         <v>0</v>
       </c>
       <c r="C181" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D181" t="s">
+        <v>528</v>
+      </c>
+      <c r="E181" t="s">
+        <v>529</v>
+      </c>
+      <c r="F181" t="s">
         <v>530</v>
-      </c>
-      <c r="E181" t="s">
-        <v>531</v>
-      </c>
-      <c r="F181" t="s">
-        <v>532</v>
       </c>
       <c r="G181">
         <v>1.35</v>
@@ -40661,16 +40655,16 @@
         <v>0</v>
       </c>
       <c r="C182" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D182" t="s">
+        <v>531</v>
+      </c>
+      <c r="E182" t="s">
+        <v>532</v>
+      </c>
+      <c r="F182" t="s">
         <v>533</v>
-      </c>
-      <c r="E182" t="s">
-        <v>534</v>
-      </c>
-      <c r="F182" t="s">
-        <v>535</v>
       </c>
       <c r="G182">
         <v>0.5</v>
@@ -40718,16 +40712,16 @@
         <v>0</v>
       </c>
       <c r="C183" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D183" t="s">
+        <v>534</v>
+      </c>
+      <c r="E183" t="s">
+        <v>535</v>
+      </c>
+      <c r="F183" t="s">
         <v>536</v>
-      </c>
-      <c r="E183" t="s">
-        <v>537</v>
-      </c>
-      <c r="F183" t="s">
-        <v>538</v>
       </c>
       <c r="G183">
         <v>4000</v>
@@ -40775,16 +40769,16 @@
         <v>0</v>
       </c>
       <c r="C184" t="s">
+        <v>537</v>
+      </c>
+      <c r="D184" t="s">
+        <v>538</v>
+      </c>
+      <c r="E184" t="s">
         <v>539</v>
       </c>
-      <c r="D184" t="s">
+      <c r="F184" t="s">
         <v>540</v>
-      </c>
-      <c r="E184" t="s">
-        <v>541</v>
-      </c>
-      <c r="F184" t="s">
-        <v>542</v>
       </c>
       <c r="G184">
         <v>4</v>
@@ -40832,16 +40826,16 @@
         <v>0</v>
       </c>
       <c r="C185" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D185" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E185" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="F185" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="G185">
         <v>200</v>
@@ -40889,16 +40883,16 @@
         <v>0</v>
       </c>
       <c r="C186" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D186" t="s">
+        <v>543</v>
+      </c>
+      <c r="E186" t="s">
+        <v>544</v>
+      </c>
+      <c r="F186" t="s">
         <v>545</v>
-      </c>
-      <c r="E186" t="s">
-        <v>546</v>
-      </c>
-      <c r="F186" t="s">
-        <v>547</v>
       </c>
       <c r="G186">
         <v>4</v>
@@ -40946,16 +40940,16 @@
         <v>0</v>
       </c>
       <c r="C187" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D187" t="s">
+        <v>546</v>
+      </c>
+      <c r="E187" t="s">
+        <v>547</v>
+      </c>
+      <c r="F187" t="s">
         <v>548</v>
-      </c>
-      <c r="E187" t="s">
-        <v>549</v>
-      </c>
-      <c r="F187" t="s">
-        <v>550</v>
       </c>
       <c r="G187">
         <v>3</v>
@@ -41003,16 +40997,16 @@
         <v>0</v>
       </c>
       <c r="C188" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D188" t="s">
+        <v>549</v>
+      </c>
+      <c r="E188" t="s">
+        <v>550</v>
+      </c>
+      <c r="F188" t="s">
         <v>551</v>
-      </c>
-      <c r="E188" t="s">
-        <v>552</v>
-      </c>
-      <c r="F188" t="s">
-        <v>553</v>
       </c>
       <c r="G188">
         <v>4</v>
@@ -41060,37 +41054,37 @@
         <v>0</v>
       </c>
       <c r="C189" t="s">
+        <v>552</v>
+      </c>
+      <c r="D189" t="s">
+        <v>422</v>
+      </c>
+      <c r="E189" t="s">
+        <v>553</v>
+      </c>
+      <c r="F189" t="s">
         <v>554</v>
       </c>
-      <c r="D189" t="s">
-        <v>424</v>
-      </c>
-      <c r="E189" t="s">
+      <c r="G189" t="s">
         <v>555</v>
       </c>
-      <c r="F189" t="s">
+      <c r="H189" t="s">
         <v>556</v>
       </c>
-      <c r="G189" t="s">
+      <c r="I189" t="s">
         <v>557</v>
       </c>
-      <c r="H189" t="s">
+      <c r="J189" t="s">
         <v>558</v>
       </c>
-      <c r="I189" t="s">
+      <c r="K189" t="s">
         <v>559</v>
       </c>
-      <c r="J189" t="s">
+      <c r="L189" t="s">
         <v>560</v>
       </c>
-      <c r="K189" t="s">
+      <c r="M189" t="s">
         <v>561</v>
-      </c>
-      <c r="L189" t="s">
-        <v>562</v>
-      </c>
-      <c r="M189" t="s">
-        <v>563</v>
       </c>
       <c r="N189">
         <v>0</v>
@@ -41117,37 +41111,37 @@
         <v>0</v>
       </c>
       <c r="C190" t="s">
+        <v>552</v>
+      </c>
+      <c r="D190" t="s">
+        <v>430</v>
+      </c>
+      <c r="E190" t="s">
+        <v>553</v>
+      </c>
+      <c r="F190" t="s">
         <v>554</v>
       </c>
-      <c r="D190" t="s">
-        <v>432</v>
-      </c>
-      <c r="E190" t="s">
+      <c r="G190" t="s">
         <v>555</v>
       </c>
-      <c r="F190" t="s">
+      <c r="H190" t="s">
         <v>556</v>
       </c>
-      <c r="G190" t="s">
+      <c r="I190" t="s">
         <v>557</v>
       </c>
-      <c r="H190" t="s">
+      <c r="J190" t="s">
         <v>558</v>
       </c>
-      <c r="I190" t="s">
+      <c r="K190" t="s">
         <v>559</v>
       </c>
-      <c r="J190" t="s">
+      <c r="L190" t="s">
         <v>560</v>
       </c>
-      <c r="K190" t="s">
+      <c r="M190" t="s">
         <v>561</v>
-      </c>
-      <c r="L190" t="s">
-        <v>562</v>
-      </c>
-      <c r="M190" t="s">
-        <v>563</v>
       </c>
       <c r="N190">
         <v>0</v>
@@ -41174,37 +41168,37 @@
         <v>0</v>
       </c>
       <c r="C191" t="s">
+        <v>552</v>
+      </c>
+      <c r="D191" t="s">
+        <v>436</v>
+      </c>
+      <c r="E191" t="s">
+        <v>553</v>
+      </c>
+      <c r="F191" t="s">
         <v>554</v>
       </c>
-      <c r="D191" t="s">
-        <v>438</v>
-      </c>
-      <c r="E191" t="s">
-        <v>555</v>
-      </c>
-      <c r="F191" t="s">
-        <v>556</v>
-      </c>
       <c r="G191" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H191" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="I191" t="s">
+        <v>557</v>
+      </c>
+      <c r="J191" t="s">
+        <v>558</v>
+      </c>
+      <c r="K191" t="s">
         <v>559</v>
       </c>
-      <c r="J191" t="s">
+      <c r="L191" t="s">
         <v>560</v>
       </c>
-      <c r="K191" t="s">
+      <c r="M191" t="s">
         <v>561</v>
-      </c>
-      <c r="L191" t="s">
-        <v>562</v>
-      </c>
-      <c r="M191" t="s">
-        <v>563</v>
       </c>
       <c r="N191">
         <v>0</v>
@@ -41231,37 +41225,37 @@
         <v>0</v>
       </c>
       <c r="C192" t="s">
+        <v>552</v>
+      </c>
+      <c r="D192" t="s">
+        <v>441</v>
+      </c>
+      <c r="E192" t="s">
+        <v>553</v>
+      </c>
+      <c r="F192" t="s">
         <v>554</v>
       </c>
-      <c r="D192" t="s">
-        <v>443</v>
-      </c>
-      <c r="E192" t="s">
-        <v>555</v>
-      </c>
-      <c r="F192" t="s">
-        <v>556</v>
-      </c>
       <c r="G192" t="s">
+        <v>564</v>
+      </c>
+      <c r="H192" t="s">
+        <v>563</v>
+      </c>
+      <c r="I192" t="s">
+        <v>565</v>
+      </c>
+      <c r="J192" t="s">
         <v>566</v>
       </c>
-      <c r="H192" t="s">
-        <v>565</v>
-      </c>
-      <c r="I192" t="s">
+      <c r="K192" t="s">
         <v>567</v>
       </c>
-      <c r="J192" t="s">
+      <c r="L192" t="s">
         <v>568</v>
       </c>
-      <c r="K192" t="s">
+      <c r="M192" t="s">
         <v>569</v>
-      </c>
-      <c r="L192" t="s">
-        <v>570</v>
-      </c>
-      <c r="M192" t="s">
-        <v>571</v>
       </c>
       <c r="N192">
         <v>0</v>
@@ -41288,37 +41282,37 @@
         <v>0</v>
       </c>
       <c r="C193" t="s">
+        <v>552</v>
+      </c>
+      <c r="D193" t="s">
+        <v>448</v>
+      </c>
+      <c r="E193" t="s">
+        <v>553</v>
+      </c>
+      <c r="F193" t="s">
         <v>554</v>
       </c>
-      <c r="D193" t="s">
-        <v>450</v>
-      </c>
-      <c r="E193" t="s">
-        <v>555</v>
-      </c>
-      <c r="F193" t="s">
-        <v>556</v>
-      </c>
       <c r="G193" t="s">
+        <v>570</v>
+      </c>
+      <c r="H193" t="s">
+        <v>571</v>
+      </c>
+      <c r="I193" t="s">
+        <v>565</v>
+      </c>
+      <c r="J193" t="s">
         <v>572</v>
       </c>
-      <c r="H193" t="s">
+      <c r="K193" t="s">
         <v>573</v>
       </c>
-      <c r="I193" t="s">
-        <v>567</v>
-      </c>
-      <c r="J193" t="s">
+      <c r="L193" t="s">
         <v>574</v>
       </c>
-      <c r="K193" t="s">
+      <c r="M193" t="s">
         <v>575</v>
-      </c>
-      <c r="L193" t="s">
-        <v>576</v>
-      </c>
-      <c r="M193" t="s">
-        <v>577</v>
       </c>
       <c r="N193">
         <v>0</v>
@@ -41345,37 +41339,37 @@
         <v>0</v>
       </c>
       <c r="C194" t="s">
+        <v>552</v>
+      </c>
+      <c r="D194" t="s">
+        <v>455</v>
+      </c>
+      <c r="E194" t="s">
+        <v>553</v>
+      </c>
+      <c r="F194" t="s">
         <v>554</v>
       </c>
-      <c r="D194" t="s">
-        <v>457</v>
-      </c>
-      <c r="E194" t="s">
-        <v>555</v>
-      </c>
-      <c r="F194" t="s">
-        <v>556</v>
-      </c>
       <c r="G194" t="s">
+        <v>576</v>
+      </c>
+      <c r="H194" t="s">
+        <v>577</v>
+      </c>
+      <c r="I194" t="s">
         <v>578</v>
       </c>
-      <c r="H194" t="s">
+      <c r="J194" t="s">
         <v>579</v>
       </c>
-      <c r="I194" t="s">
+      <c r="K194" t="s">
         <v>580</v>
       </c>
-      <c r="J194" t="s">
+      <c r="L194" t="s">
         <v>581</v>
       </c>
-      <c r="K194" t="s">
+      <c r="M194" t="s">
         <v>582</v>
-      </c>
-      <c r="L194" t="s">
-        <v>583</v>
-      </c>
-      <c r="M194" t="s">
-        <v>584</v>
       </c>
       <c r="N194">
         <v>0</v>
@@ -41402,37 +41396,37 @@
         <v>0</v>
       </c>
       <c r="C195" t="s">
+        <v>552</v>
+      </c>
+      <c r="D195" t="s">
+        <v>461</v>
+      </c>
+      <c r="E195" t="s">
+        <v>553</v>
+      </c>
+      <c r="F195" t="s">
         <v>554</v>
       </c>
-      <c r="D195" t="s">
-        <v>463</v>
-      </c>
-      <c r="E195" t="s">
+      <c r="G195" t="s">
         <v>555</v>
       </c>
-      <c r="F195" t="s">
-        <v>556</v>
-      </c>
-      <c r="G195" t="s">
-        <v>557</v>
-      </c>
       <c r="H195" t="s">
+        <v>583</v>
+      </c>
+      <c r="I195" t="s">
+        <v>584</v>
+      </c>
+      <c r="J195" t="s">
         <v>585</v>
       </c>
-      <c r="I195" t="s">
+      <c r="K195" t="s">
         <v>586</v>
       </c>
-      <c r="J195" t="s">
+      <c r="L195" t="s">
         <v>587</v>
       </c>
-      <c r="K195" t="s">
+      <c r="M195" t="s">
         <v>588</v>
-      </c>
-      <c r="L195" t="s">
-        <v>589</v>
-      </c>
-      <c r="M195" t="s">
-        <v>590</v>
       </c>
       <c r="N195">
         <v>0</v>
@@ -41459,37 +41453,37 @@
         <v>0</v>
       </c>
       <c r="C196" t="s">
+        <v>552</v>
+      </c>
+      <c r="D196" t="s">
+        <v>467</v>
+      </c>
+      <c r="E196" t="s">
+        <v>553</v>
+      </c>
+      <c r="F196" t="s">
         <v>554</v>
       </c>
-      <c r="D196" t="s">
-        <v>469</v>
-      </c>
-      <c r="E196" t="s">
+      <c r="G196" t="s">
         <v>555</v>
       </c>
-      <c r="F196" t="s">
+      <c r="H196" t="s">
         <v>556</v>
       </c>
-      <c r="G196" t="s">
-        <v>557</v>
-      </c>
-      <c r="H196" t="s">
-        <v>558</v>
-      </c>
       <c r="I196" t="s">
+        <v>589</v>
+      </c>
+      <c r="J196" t="s">
+        <v>590</v>
+      </c>
+      <c r="K196" t="s">
         <v>591</v>
       </c>
-      <c r="J196" t="s">
+      <c r="L196" t="s">
         <v>592</v>
       </c>
-      <c r="K196" t="s">
+      <c r="M196" t="s">
         <v>593</v>
-      </c>
-      <c r="L196" t="s">
-        <v>594</v>
-      </c>
-      <c r="M196" t="s">
-        <v>595</v>
       </c>
       <c r="N196">
         <v>0</v>
@@ -41516,16 +41510,16 @@
         <v>0</v>
       </c>
       <c r="C197" t="s">
+        <v>594</v>
+      </c>
+      <c r="D197" t="s">
+        <v>595</v>
+      </c>
+      <c r="E197" t="s">
         <v>596</v>
       </c>
-      <c r="D197" t="s">
+      <c r="F197" t="s">
         <v>597</v>
-      </c>
-      <c r="E197" t="s">
-        <v>598</v>
-      </c>
-      <c r="F197" t="s">
-        <v>599</v>
       </c>
       <c r="G197">
         <v>0</v>
@@ -41573,16 +41567,16 @@
         <v>0</v>
       </c>
       <c r="C198" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D198" t="s">
+        <v>598</v>
+      </c>
+      <c r="E198" t="s">
+        <v>599</v>
+      </c>
+      <c r="F198" t="s">
         <v>600</v>
-      </c>
-      <c r="E198" t="s">
-        <v>601</v>
-      </c>
-      <c r="F198" t="s">
-        <v>602</v>
       </c>
       <c r="G198">
         <v>1.35</v>
@@ -41630,16 +41624,16 @@
         <v>0</v>
       </c>
       <c r="C199" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D199" t="s">
+        <v>601</v>
+      </c>
+      <c r="E199" t="s">
+        <v>602</v>
+      </c>
+      <c r="F199" t="s">
         <v>603</v>
-      </c>
-      <c r="E199" t="s">
-        <v>604</v>
-      </c>
-      <c r="F199" t="s">
-        <v>605</v>
       </c>
       <c r="G199">
         <v>0.05</v>
@@ -41687,16 +41681,16 @@
         <v>0</v>
       </c>
       <c r="C200" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D200" t="s">
+        <v>604</v>
+      </c>
+      <c r="E200" t="s">
+        <v>605</v>
+      </c>
+      <c r="F200" t="s">
         <v>606</v>
-      </c>
-      <c r="E200" t="s">
-        <v>607</v>
-      </c>
-      <c r="F200" t="s">
-        <v>608</v>
       </c>
       <c r="G200">
         <v>2</v>
@@ -41744,16 +41738,16 @@
         <v>0</v>
       </c>
       <c r="C201" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D201" t="s">
+        <v>607</v>
+      </c>
+      <c r="E201" t="s">
+        <v>608</v>
+      </c>
+      <c r="F201" t="s">
         <v>609</v>
-      </c>
-      <c r="E201" t="s">
-        <v>610</v>
-      </c>
-      <c r="F201" t="s">
-        <v>611</v>
       </c>
       <c r="G201">
         <v>0</v>
@@ -41801,16 +41795,16 @@
         <v>0</v>
       </c>
       <c r="C202" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D202" t="s">
+        <v>610</v>
+      </c>
+      <c r="E202" t="s">
+        <v>611</v>
+      </c>
+      <c r="F202" t="s">
         <v>612</v>
-      </c>
-      <c r="E202" t="s">
-        <v>613</v>
-      </c>
-      <c r="F202" t="s">
-        <v>614</v>
       </c>
       <c r="G202">
         <v>5</v>
@@ -41858,16 +41852,16 @@
         <v>0</v>
       </c>
       <c r="C203" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D203" t="s">
+        <v>613</v>
+      </c>
+      <c r="E203" t="s">
+        <v>614</v>
+      </c>
+      <c r="F203" t="s">
         <v>615</v>
-      </c>
-      <c r="E203" t="s">
-        <v>616</v>
-      </c>
-      <c r="F203" t="s">
-        <v>617</v>
       </c>
       <c r="G203">
         <v>8</v>
@@ -41915,16 +41909,16 @@
         <v>0</v>
       </c>
       <c r="C204" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D204" t="s">
+        <v>616</v>
+      </c>
+      <c r="E204" t="s">
+        <v>617</v>
+      </c>
+      <c r="F204" t="s">
         <v>618</v>
-      </c>
-      <c r="E204" t="s">
-        <v>619</v>
-      </c>
-      <c r="F204" t="s">
-        <v>620</v>
       </c>
       <c r="G204">
         <v>1</v>
@@ -41972,16 +41966,16 @@
         <v>0</v>
       </c>
       <c r="C205" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D205" t="s">
+        <v>619</v>
+      </c>
+      <c r="E205" t="s">
+        <v>620</v>
+      </c>
+      <c r="F205" t="s">
         <v>621</v>
-      </c>
-      <c r="E205" t="s">
-        <v>622</v>
-      </c>
-      <c r="F205" t="s">
-        <v>623</v>
       </c>
       <c r="G205">
         <v>0.15</v>
@@ -42029,16 +42023,16 @@
         <v>0</v>
       </c>
       <c r="C206" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D206" t="s">
+        <v>622</v>
+      </c>
+      <c r="E206" t="s">
+        <v>623</v>
+      </c>
+      <c r="F206" t="s">
         <v>624</v>
-      </c>
-      <c r="E206" t="s">
-        <v>625</v>
-      </c>
-      <c r="F206" t="s">
-        <v>626</v>
       </c>
       <c r="G206">
         <v>2</v>
@@ -42086,16 +42080,16 @@
         <v>0</v>
       </c>
       <c r="C207" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D207" t="s">
+        <v>625</v>
+      </c>
+      <c r="E207" t="s">
+        <v>626</v>
+      </c>
+      <c r="F207" t="s">
         <v>627</v>
-      </c>
-      <c r="E207" t="s">
-        <v>628</v>
-      </c>
-      <c r="F207" t="s">
-        <v>629</v>
       </c>
       <c r="G207">
         <v>3</v>
@@ -42143,16 +42137,16 @@
         <v>0</v>
       </c>
       <c r="C208" t="s">
+        <v>628</v>
+      </c>
+      <c r="D208" t="s">
+        <v>629</v>
+      </c>
+      <c r="E208" t="s">
         <v>630</v>
       </c>
-      <c r="D208" t="s">
+      <c r="F208" t="s">
         <v>631</v>
-      </c>
-      <c r="E208" t="s">
-        <v>632</v>
-      </c>
-      <c r="F208" t="s">
-        <v>633</v>
       </c>
       <c r="G208">
         <v>5</v>
@@ -42200,16 +42194,16 @@
         <v>0</v>
       </c>
       <c r="C209" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D209" t="s">
+        <v>632</v>
+      </c>
+      <c r="E209" t="s">
+        <v>633</v>
+      </c>
+      <c r="F209" t="s">
         <v>634</v>
-      </c>
-      <c r="E209" t="s">
-        <v>635</v>
-      </c>
-      <c r="F209" t="s">
-        <v>636</v>
       </c>
       <c r="G209">
         <v>0</v>
@@ -42257,16 +42251,16 @@
         <v>0</v>
       </c>
       <c r="C210" t="s">
+        <v>635</v>
+      </c>
+      <c r="D210" t="s">
+        <v>636</v>
+      </c>
+      <c r="E210" t="s">
         <v>637</v>
       </c>
-      <c r="D210" t="s">
+      <c r="F210" t="s">
         <v>638</v>
-      </c>
-      <c r="E210" t="s">
-        <v>639</v>
-      </c>
-      <c r="F210" t="s">
-        <v>640</v>
       </c>
       <c r="G210">
         <v>5</v>
@@ -42314,16 +42308,16 @@
         <v>0</v>
       </c>
       <c r="C211" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D211" t="s">
+        <v>639</v>
+      </c>
+      <c r="E211" t="s">
+        <v>640</v>
+      </c>
+      <c r="F211" t="s">
         <v>641</v>
-      </c>
-      <c r="E211" t="s">
-        <v>642</v>
-      </c>
-      <c r="F211" t="s">
-        <v>643</v>
       </c>
       <c r="G211">
         <v>55</v>
@@ -42371,16 +42365,16 @@
         <v>0</v>
       </c>
       <c r="C212" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D212" t="s">
+        <v>642</v>
+      </c>
+      <c r="E212" t="s">
+        <v>643</v>
+      </c>
+      <c r="F212" t="s">
         <v>644</v>
-      </c>
-      <c r="E212" t="s">
-        <v>645</v>
-      </c>
-      <c r="F212" t="s">
-        <v>646</v>
       </c>
       <c r="G212">
         <v>5000000</v>
@@ -42428,13 +42422,13 @@
         <v>0</v>
       </c>
       <c r="C213" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D213" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E213" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="F213">
         <v>0</v>
@@ -42485,16 +42479,16 @@
         <v>0</v>
       </c>
       <c r="C214" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D214" t="s">
+        <v>646</v>
+      </c>
+      <c r="E214" t="s">
+        <v>647</v>
+      </c>
+      <c r="F214" t="s">
         <v>648</v>
-      </c>
-      <c r="E214" t="s">
-        <v>649</v>
-      </c>
-      <c r="F214" t="s">
-        <v>650</v>
       </c>
       <c r="G214">
         <v>3</v>
@@ -42542,16 +42536,16 @@
         <v>0</v>
       </c>
       <c r="C215" t="s">
+        <v>649</v>
+      </c>
+      <c r="D215" t="s">
+        <v>650</v>
+      </c>
+      <c r="E215" t="s">
         <v>651</v>
       </c>
-      <c r="D215" t="s">
+      <c r="F215" t="s">
         <v>652</v>
-      </c>
-      <c r="E215" t="s">
-        <v>653</v>
-      </c>
-      <c r="F215" t="s">
-        <v>654</v>
       </c>
       <c r="G215">
         <v>27</v>
@@ -42599,16 +42593,16 @@
         <v>0</v>
       </c>
       <c r="C216" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D216" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E216" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="F216" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G216">
         <v>36</v>
@@ -42656,16 +42650,16 @@
         <v>0</v>
       </c>
       <c r="C217" t="s">
+        <v>635</v>
+      </c>
+      <c r="D217" t="s">
+        <v>655</v>
+      </c>
+      <c r="E217" t="s">
         <v>637</v>
       </c>
-      <c r="D217" t="s">
-        <v>657</v>
-      </c>
-      <c r="E217" t="s">
-        <v>639</v>
-      </c>
       <c r="F217" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G217">
         <v>3</v>
@@ -42713,16 +42707,16 @@
         <v>0</v>
       </c>
       <c r="C218" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D218" t="s">
+        <v>657</v>
+      </c>
+      <c r="E218" t="s">
+        <v>658</v>
+      </c>
+      <c r="F218" t="s">
         <v>659</v>
-      </c>
-      <c r="E218" t="s">
-        <v>660</v>
-      </c>
-      <c r="F218" t="s">
-        <v>661</v>
       </c>
       <c r="G218">
         <v>50</v>
@@ -42770,16 +42764,16 @@
         <v>0</v>
       </c>
       <c r="C219" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D219" t="s">
+        <v>660</v>
+      </c>
+      <c r="E219" t="s">
+        <v>661</v>
+      </c>
+      <c r="F219" t="s">
         <v>662</v>
-      </c>
-      <c r="E219" t="s">
-        <v>663</v>
-      </c>
-      <c r="F219" t="s">
-        <v>664</v>
       </c>
       <c r="G219">
         <v>1000000</v>
@@ -42827,13 +42821,13 @@
         <v>0</v>
       </c>
       <c r="C220" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D220" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E220" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="F220">
         <v>0</v>
@@ -42884,16 +42878,16 @@
         <v>0</v>
       </c>
       <c r="C221" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D221" t="s">
+        <v>665</v>
+      </c>
+      <c r="E221" t="s">
+        <v>666</v>
+      </c>
+      <c r="F221" t="s">
         <v>667</v>
-      </c>
-      <c r="E221" t="s">
-        <v>668</v>
-      </c>
-      <c r="F221" t="s">
-        <v>669</v>
       </c>
       <c r="G221">
         <v>3</v>
@@ -42941,16 +42935,16 @@
         <v>0</v>
       </c>
       <c r="C222" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D222" t="s">
+        <v>668</v>
+      </c>
+      <c r="E222" t="s">
+        <v>669</v>
+      </c>
+      <c r="F222" t="s">
         <v>670</v>
-      </c>
-      <c r="E222" t="s">
-        <v>671</v>
-      </c>
-      <c r="F222" t="s">
-        <v>672</v>
       </c>
       <c r="G222">
         <v>6</v>
@@ -42998,16 +42992,16 @@
         <v>0</v>
       </c>
       <c r="C223" t="s">
+        <v>671</v>
+      </c>
+      <c r="D223" t="s">
+        <v>672</v>
+      </c>
+      <c r="E223" t="s">
         <v>673</v>
       </c>
-      <c r="D223" t="s">
+      <c r="F223" t="s">
         <v>674</v>
-      </c>
-      <c r="E223" t="s">
-        <v>675</v>
-      </c>
-      <c r="F223" t="s">
-        <v>676</v>
       </c>
       <c r="G223">
         <v>30</v>
@@ -43055,13 +43049,13 @@
         <v>0</v>
       </c>
       <c r="C224" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D224" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E224" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="F224">
         <v>0</v>
@@ -43112,13 +43106,13 @@
         <v>0</v>
       </c>
       <c r="C225" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D225" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E225" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="F225">
         <v>0</v>
@@ -43169,16 +43163,16 @@
         <v>0</v>
       </c>
       <c r="C226" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D226" t="s">
+        <v>678</v>
+      </c>
+      <c r="E226" t="s">
+        <v>679</v>
+      </c>
+      <c r="F226" t="s">
         <v>680</v>
-      </c>
-      <c r="E226" t="s">
-        <v>681</v>
-      </c>
-      <c r="F226" t="s">
-        <v>682</v>
       </c>
       <c r="G226">
         <v>0</v>
@@ -43226,13 +43220,13 @@
         <v>0</v>
       </c>
       <c r="C227" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D227" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E227" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="F227">
         <v>0</v>
@@ -43283,16 +43277,16 @@
         <v>0</v>
       </c>
       <c r="C228" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D228" t="s">
+        <v>682</v>
+      </c>
+      <c r="E228" t="s">
+        <v>683</v>
+      </c>
+      <c r="F228" t="s">
         <v>684</v>
-      </c>
-      <c r="E228" t="s">
-        <v>685</v>
-      </c>
-      <c r="F228" t="s">
-        <v>686</v>
       </c>
       <c r="G228">
         <v>9</v>
@@ -43340,16 +43334,16 @@
         <v>0</v>
       </c>
       <c r="C229" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D229" t="s">
+        <v>685</v>
+      </c>
+      <c r="E229" t="s">
+        <v>686</v>
+      </c>
+      <c r="F229" t="s">
         <v>687</v>
-      </c>
-      <c r="E229" t="s">
-        <v>688</v>
-      </c>
-      <c r="F229" t="s">
-        <v>689</v>
       </c>
       <c r="G229">
         <v>1</v>
@@ -43397,16 +43391,16 @@
         <v>0</v>
       </c>
       <c r="C230" t="s">
+        <v>688</v>
+      </c>
+      <c r="D230" t="s">
+        <v>689</v>
+      </c>
+      <c r="E230" t="s">
         <v>690</v>
       </c>
-      <c r="D230" t="s">
+      <c r="F230" t="s">
         <v>691</v>
-      </c>
-      <c r="E230" t="s">
-        <v>692</v>
-      </c>
-      <c r="F230" t="s">
-        <v>693</v>
       </c>
       <c r="G230">
         <v>5</v>
@@ -43454,16 +43448,16 @@
         <v>0</v>
       </c>
       <c r="C231" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D231" t="s">
+        <v>692</v>
+      </c>
+      <c r="E231" t="s">
+        <v>693</v>
+      </c>
+      <c r="F231" t="s">
         <v>694</v>
-      </c>
-      <c r="E231" t="s">
-        <v>695</v>
-      </c>
-      <c r="F231" t="s">
-        <v>696</v>
       </c>
       <c r="G231">
         <v>0</v>
@@ -43511,16 +43505,16 @@
         <v>0</v>
       </c>
       <c r="C232" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D232" t="s">
+        <v>695</v>
+      </c>
+      <c r="E232" t="s">
+        <v>696</v>
+      </c>
+      <c r="F232" t="s">
         <v>697</v>
-      </c>
-      <c r="E232" t="s">
-        <v>698</v>
-      </c>
-      <c r="F232" t="s">
-        <v>699</v>
       </c>
       <c r="G232">
         <v>0</v>
@@ -43568,16 +43562,16 @@
         <v>0</v>
       </c>
       <c r="C233" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D233" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E233" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F233" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="G233">
         <v>0</v>
@@ -43625,16 +43619,16 @@
         <v>0</v>
       </c>
       <c r="C234" t="s">
+        <v>700</v>
+      </c>
+      <c r="D234" t="s">
+        <v>701</v>
+      </c>
+      <c r="E234" t="s">
         <v>702</v>
       </c>
-      <c r="D234" t="s">
+      <c r="F234" t="s">
         <v>703</v>
-      </c>
-      <c r="E234" t="s">
-        <v>704</v>
-      </c>
-      <c r="F234" t="s">
-        <v>705</v>
       </c>
       <c r="G234">
         <v>2</v>
@@ -43682,16 +43676,16 @@
         <v>0</v>
       </c>
       <c r="C235" t="s">
+        <v>704</v>
+      </c>
+      <c r="D235" t="s">
+        <v>705</v>
+      </c>
+      <c r="E235" t="s">
         <v>706</v>
       </c>
-      <c r="D235" t="s">
+      <c r="F235" t="s">
         <v>707</v>
-      </c>
-      <c r="E235" t="s">
-        <v>708</v>
-      </c>
-      <c r="F235" t="s">
-        <v>709</v>
       </c>
       <c r="G235">
         <v>10000</v>
@@ -43739,16 +43733,16 @@
         <v>0</v>
       </c>
       <c r="C236" t="s">
+        <v>708</v>
+      </c>
+      <c r="D236" t="s">
+        <v>709</v>
+      </c>
+      <c r="E236" t="s">
         <v>710</v>
       </c>
-      <c r="D236" t="s">
+      <c r="F236" t="s">
         <v>711</v>
-      </c>
-      <c r="E236" t="s">
-        <v>712</v>
-      </c>
-      <c r="F236" t="s">
-        <v>713</v>
       </c>
       <c r="G236">
         <v>20000</v>
@@ -43796,13 +43790,13 @@
         <v>0</v>
       </c>
       <c r="C237" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D237" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="E237" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="F237">
         <v>0</v>
@@ -43853,16 +43847,16 @@
         <v>0</v>
       </c>
       <c r="C238" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D238" t="s">
+        <v>714</v>
+      </c>
+      <c r="E238" t="s">
+        <v>715</v>
+      </c>
+      <c r="F238" t="s">
         <v>716</v>
-      </c>
-      <c r="E238" t="s">
-        <v>717</v>
-      </c>
-      <c r="F238" t="s">
-        <v>718</v>
       </c>
       <c r="G238">
         <v>100</v>
@@ -43910,16 +43904,16 @@
         <v>0</v>
       </c>
       <c r="C239" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D239" t="s">
+        <v>717</v>
+      </c>
+      <c r="E239" t="s">
+        <v>718</v>
+      </c>
+      <c r="F239" t="s">
         <v>719</v>
-      </c>
-      <c r="E239" t="s">
-        <v>720</v>
-      </c>
-      <c r="F239" t="s">
-        <v>721</v>
       </c>
       <c r="G239">
         <v>10000</v>
@@ -43967,13 +43961,13 @@
         <v>0</v>
       </c>
       <c r="C240" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D240" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="E240" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="F240">
         <v>0</v>
@@ -44024,16 +44018,16 @@
         <v>0</v>
       </c>
       <c r="C241" t="s">
+        <v>722</v>
+      </c>
+      <c r="D241" t="s">
+        <v>723</v>
+      </c>
+      <c r="E241" t="s">
         <v>724</v>
       </c>
-      <c r="D241" t="s">
+      <c r="F241" t="s">
         <v>725</v>
-      </c>
-      <c r="E241" t="s">
-        <v>726</v>
-      </c>
-      <c r="F241" t="s">
-        <v>727</v>
       </c>
       <c r="G241">
         <v>0.2</v>
@@ -44081,16 +44075,16 @@
         <v>0</v>
       </c>
       <c r="C242" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D242" t="s">
+        <v>726</v>
+      </c>
+      <c r="E242" t="s">
+        <v>727</v>
+      </c>
+      <c r="F242" t="s">
         <v>728</v>
-      </c>
-      <c r="E242" t="s">
-        <v>729</v>
-      </c>
-      <c r="F242" t="s">
-        <v>730</v>
       </c>
       <c r="G242">
         <v>2</v>
@@ -44138,16 +44132,16 @@
         <v>0</v>
       </c>
       <c r="C243" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D243" t="s">
+        <v>729</v>
+      </c>
+      <c r="E243" t="s">
+        <v>730</v>
+      </c>
+      <c r="F243" t="s">
         <v>731</v>
-      </c>
-      <c r="E243" t="s">
-        <v>732</v>
-      </c>
-      <c r="F243" t="s">
-        <v>733</v>
       </c>
       <c r="G243">
         <v>3</v>
@@ -44195,16 +44189,16 @@
         <v>0</v>
       </c>
       <c r="C244" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D244" t="s">
+        <v>732</v>
+      </c>
+      <c r="E244" t="s">
+        <v>733</v>
+      </c>
+      <c r="F244" t="s">
         <v>734</v>
-      </c>
-      <c r="E244" t="s">
-        <v>735</v>
-      </c>
-      <c r="F244" t="s">
-        <v>736</v>
       </c>
       <c r="G244">
         <v>3</v>
@@ -44252,16 +44246,16 @@
         <v>0</v>
       </c>
       <c r="C245" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D245" t="s">
+        <v>735</v>
+      </c>
+      <c r="E245" t="s">
+        <v>736</v>
+      </c>
+      <c r="F245" t="s">
         <v>737</v>
-      </c>
-      <c r="E245" t="s">
-        <v>738</v>
-      </c>
-      <c r="F245" t="s">
-        <v>739</v>
       </c>
       <c r="G245">
         <v>100</v>
@@ -44309,16 +44303,16 @@
         <v>0</v>
       </c>
       <c r="C246" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D246" t="s">
+        <v>738</v>
+      </c>
+      <c r="E246" t="s">
+        <v>739</v>
+      </c>
+      <c r="F246" t="s">
         <v>740</v>
-      </c>
-      <c r="E246" t="s">
-        <v>741</v>
-      </c>
-      <c r="F246" t="s">
-        <v>742</v>
       </c>
       <c r="G246">
         <v>9</v>
@@ -44366,16 +44360,16 @@
         <v>0</v>
       </c>
       <c r="C247" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D247" t="s">
+        <v>741</v>
+      </c>
+      <c r="E247" t="s">
+        <v>742</v>
+      </c>
+      <c r="F247" t="s">
         <v>743</v>
-      </c>
-      <c r="E247" t="s">
-        <v>744</v>
-      </c>
-      <c r="F247" t="s">
-        <v>745</v>
       </c>
       <c r="G247">
         <v>0.7</v>
@@ -44423,16 +44417,16 @@
         <v>0</v>
       </c>
       <c r="C248" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D248" t="s">
+        <v>744</v>
+      </c>
+      <c r="E248" t="s">
+        <v>745</v>
+      </c>
+      <c r="F248" t="s">
         <v>746</v>
-      </c>
-      <c r="E248" t="s">
-        <v>747</v>
-      </c>
-      <c r="F248" t="s">
-        <v>748</v>
       </c>
       <c r="G248">
         <v>0.7</v>
@@ -44480,16 +44474,16 @@
         <v>0</v>
       </c>
       <c r="C249" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D249" t="s">
+        <v>747</v>
+      </c>
+      <c r="E249" t="s">
+        <v>748</v>
+      </c>
+      <c r="F249" t="s">
         <v>749</v>
-      </c>
-      <c r="E249" t="s">
-        <v>750</v>
-      </c>
-      <c r="F249" t="s">
-        <v>751</v>
       </c>
       <c r="G249">
         <v>10</v>
@@ -44537,16 +44531,16 @@
         <v>0</v>
       </c>
       <c r="C250" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D250" t="s">
+        <v>750</v>
+      </c>
+      <c r="E250" t="s">
+        <v>751</v>
+      </c>
+      <c r="F250" t="s">
         <v>752</v>
-      </c>
-      <c r="E250" t="s">
-        <v>753</v>
-      </c>
-      <c r="F250" t="s">
-        <v>754</v>
       </c>
       <c r="G250">
         <v>0</v>
@@ -44594,16 +44588,16 @@
         <v>0</v>
       </c>
       <c r="C251" t="s">
+        <v>753</v>
+      </c>
+      <c r="D251" t="s">
+        <v>754</v>
+      </c>
+      <c r="E251" t="s">
         <v>755</v>
       </c>
-      <c r="D251" t="s">
+      <c r="F251" t="s">
         <v>756</v>
-      </c>
-      <c r="E251" t="s">
-        <v>757</v>
-      </c>
-      <c r="F251" t="s">
-        <v>758</v>
       </c>
       <c r="G251">
         <v>10000</v>
@@ -44651,16 +44645,16 @@
         <v>0</v>
       </c>
       <c r="C252" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D252" t="s">
+        <v>757</v>
+      </c>
+      <c r="E252" t="s">
+        <v>758</v>
+      </c>
+      <c r="F252" t="s">
         <v>759</v>
-      </c>
-      <c r="E252" t="s">
-        <v>760</v>
-      </c>
-      <c r="F252" t="s">
-        <v>761</v>
       </c>
       <c r="G252">
         <v>5000</v>
@@ -44708,13 +44702,13 @@
         <v>0</v>
       </c>
       <c r="C253" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D253" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="E253" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="F253">
         <v>0</v>
@@ -44765,16 +44759,16 @@
         <v>0</v>
       </c>
       <c r="C254" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D254" t="s">
+        <v>762</v>
+      </c>
+      <c r="E254" t="s">
+        <v>763</v>
+      </c>
+      <c r="F254" t="s">
         <v>764</v>
-      </c>
-      <c r="E254" t="s">
-        <v>765</v>
-      </c>
-      <c r="F254" t="s">
-        <v>766</v>
       </c>
       <c r="G254">
         <v>10000</v>
@@ -44822,22 +44816,22 @@
         <v>0</v>
       </c>
       <c r="C255" t="s">
+        <v>765</v>
+      </c>
+      <c r="D255" t="s">
+        <v>766</v>
+      </c>
+      <c r="E255" t="s">
         <v>767</v>
       </c>
-      <c r="D255" t="s">
+      <c r="F255" t="s">
         <v>768</v>
       </c>
-      <c r="E255" t="s">
+      <c r="G255" t="s">
         <v>769</v>
       </c>
-      <c r="F255" t="s">
+      <c r="H255" t="s">
         <v>770</v>
-      </c>
-      <c r="G255" t="s">
-        <v>771</v>
-      </c>
-      <c r="H255" t="s">
-        <v>772</v>
       </c>
       <c r="I255">
         <v>0</v>
@@ -44879,25 +44873,25 @@
         <v>0</v>
       </c>
       <c r="C256" t="s">
+        <v>765</v>
+      </c>
+      <c r="D256" t="s">
+        <v>771</v>
+      </c>
+      <c r="E256" t="s">
         <v>767</v>
       </c>
-      <c r="D256" t="s">
+      <c r="F256" t="s">
+        <v>768</v>
+      </c>
+      <c r="G256" t="s">
+        <v>769</v>
+      </c>
+      <c r="H256" t="s">
+        <v>772</v>
+      </c>
+      <c r="I256" t="s">
         <v>773</v>
-      </c>
-      <c r="E256" t="s">
-        <v>769</v>
-      </c>
-      <c r="F256" t="s">
-        <v>770</v>
-      </c>
-      <c r="G256" t="s">
-        <v>771</v>
-      </c>
-      <c r="H256" t="s">
-        <v>774</v>
-      </c>
-      <c r="I256" t="s">
-        <v>775</v>
       </c>
       <c r="J256">
         <v>0</v>
@@ -44936,28 +44930,28 @@
         <v>0</v>
       </c>
       <c r="C257" t="s">
+        <v>765</v>
+      </c>
+      <c r="D257" t="s">
+        <v>774</v>
+      </c>
+      <c r="E257" t="s">
         <v>767</v>
       </c>
-      <c r="D257" t="s">
+      <c r="F257" t="s">
+        <v>768</v>
+      </c>
+      <c r="G257" t="s">
+        <v>769</v>
+      </c>
+      <c r="H257" t="s">
+        <v>775</v>
+      </c>
+      <c r="I257" t="s">
+        <v>773</v>
+      </c>
+      <c r="J257" t="s">
         <v>776</v>
-      </c>
-      <c r="E257" t="s">
-        <v>769</v>
-      </c>
-      <c r="F257" t="s">
-        <v>770</v>
-      </c>
-      <c r="G257" t="s">
-        <v>771</v>
-      </c>
-      <c r="H257" t="s">
-        <v>777</v>
-      </c>
-      <c r="I257" t="s">
-        <v>775</v>
-      </c>
-      <c r="J257" t="s">
-        <v>778</v>
       </c>
       <c r="K257">
         <v>0</v>
@@ -44993,28 +44987,28 @@
         <v>0</v>
       </c>
       <c r="C258" t="s">
+        <v>765</v>
+      </c>
+      <c r="D258" t="s">
+        <v>777</v>
+      </c>
+      <c r="E258" t="s">
         <v>767</v>
       </c>
-      <c r="D258" t="s">
+      <c r="F258" t="s">
+        <v>768</v>
+      </c>
+      <c r="G258" t="s">
+        <v>778</v>
+      </c>
+      <c r="H258" t="s">
+        <v>775</v>
+      </c>
+      <c r="I258" t="s">
         <v>779</v>
       </c>
-      <c r="E258" t="s">
-        <v>769</v>
-      </c>
-      <c r="F258" t="s">
-        <v>770</v>
-      </c>
-      <c r="G258" t="s">
-        <v>780</v>
-      </c>
-      <c r="H258" t="s">
-        <v>777</v>
-      </c>
-      <c r="I258" t="s">
-        <v>781</v>
-      </c>
       <c r="J258" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="K258">
         <v>0</v>
@@ -45050,28 +45044,28 @@
         <v>0</v>
       </c>
       <c r="C259" t="s">
+        <v>765</v>
+      </c>
+      <c r="D259" t="s">
+        <v>780</v>
+      </c>
+      <c r="E259" t="s">
         <v>767</v>
       </c>
-      <c r="D259" t="s">
+      <c r="F259" t="s">
+        <v>768</v>
+      </c>
+      <c r="G259" t="s">
+        <v>781</v>
+      </c>
+      <c r="H259" t="s">
+        <v>775</v>
+      </c>
+      <c r="I259" t="s">
+        <v>779</v>
+      </c>
+      <c r="J259" t="s">
         <v>782</v>
-      </c>
-      <c r="E259" t="s">
-        <v>769</v>
-      </c>
-      <c r="F259" t="s">
-        <v>770</v>
-      </c>
-      <c r="G259" t="s">
-        <v>783</v>
-      </c>
-      <c r="H259" t="s">
-        <v>777</v>
-      </c>
-      <c r="I259" t="s">
-        <v>781</v>
-      </c>
-      <c r="J259" t="s">
-        <v>784</v>
       </c>
       <c r="K259">
         <v>0</v>
@@ -45107,31 +45101,31 @@
         <v>0</v>
       </c>
       <c r="C260" t="s">
+        <v>765</v>
+      </c>
+      <c r="D260" t="s">
+        <v>783</v>
+      </c>
+      <c r="E260" t="s">
         <v>767</v>
       </c>
-      <c r="D260" t="s">
+      <c r="F260" t="s">
+        <v>768</v>
+      </c>
+      <c r="G260" t="s">
+        <v>784</v>
+      </c>
+      <c r="H260" t="s">
+        <v>775</v>
+      </c>
+      <c r="I260" t="s">
+        <v>779</v>
+      </c>
+      <c r="J260" t="s">
+        <v>782</v>
+      </c>
+      <c r="K260" t="s">
         <v>785</v>
-      </c>
-      <c r="E260" t="s">
-        <v>769</v>
-      </c>
-      <c r="F260" t="s">
-        <v>770</v>
-      </c>
-      <c r="G260" t="s">
-        <v>786</v>
-      </c>
-      <c r="H260" t="s">
-        <v>777</v>
-      </c>
-      <c r="I260" t="s">
-        <v>781</v>
-      </c>
-      <c r="J260" t="s">
-        <v>784</v>
-      </c>
-      <c r="K260" t="s">
-        <v>787</v>
       </c>
       <c r="L260">
         <v>0</v>
@@ -45164,31 +45158,31 @@
         <v>0</v>
       </c>
       <c r="C261" t="s">
+        <v>765</v>
+      </c>
+      <c r="D261" t="s">
+        <v>786</v>
+      </c>
+      <c r="E261" t="s">
         <v>767</v>
       </c>
-      <c r="D261" t="s">
+      <c r="F261" t="s">
+        <v>768</v>
+      </c>
+      <c r="G261" t="s">
+        <v>787</v>
+      </c>
+      <c r="H261" t="s">
         <v>788</v>
       </c>
-      <c r="E261" t="s">
-        <v>769</v>
-      </c>
-      <c r="F261" t="s">
-        <v>770</v>
-      </c>
-      <c r="G261" t="s">
+      <c r="I261" t="s">
+        <v>782</v>
+      </c>
+      <c r="J261" t="s">
         <v>789</v>
       </c>
-      <c r="H261" t="s">
+      <c r="K261" t="s">
         <v>790</v>
-      </c>
-      <c r="I261" t="s">
-        <v>784</v>
-      </c>
-      <c r="J261" t="s">
-        <v>791</v>
-      </c>
-      <c r="K261" t="s">
-        <v>792</v>
       </c>
       <c r="L261">
         <v>0</v>
@@ -45221,31 +45215,31 @@
         <v>0</v>
       </c>
       <c r="C262" t="s">
+        <v>765</v>
+      </c>
+      <c r="D262" t="s">
+        <v>791</v>
+      </c>
+      <c r="E262" t="s">
         <v>767</v>
       </c>
-      <c r="D262" t="s">
-        <v>793</v>
-      </c>
-      <c r="E262" t="s">
-        <v>769</v>
-      </c>
       <c r="F262" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="G262" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="H262" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="I262" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="J262" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="K262" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="L262">
         <v>0</v>
@@ -45278,31 +45272,31 @@
         <v>0</v>
       </c>
       <c r="C263" t="s">
+        <v>765</v>
+      </c>
+      <c r="D263" t="s">
+        <v>793</v>
+      </c>
+      <c r="E263" t="s">
         <v>767</v>
       </c>
-      <c r="D263" t="s">
+      <c r="F263" t="s">
+        <v>768</v>
+      </c>
+      <c r="G263" t="s">
+        <v>788</v>
+      </c>
+      <c r="H263" t="s">
+        <v>794</v>
+      </c>
+      <c r="I263" t="s">
+        <v>789</v>
+      </c>
+      <c r="J263" t="s">
         <v>795</v>
       </c>
-      <c r="E263" t="s">
-        <v>769</v>
-      </c>
-      <c r="F263" t="s">
-        <v>770</v>
-      </c>
-      <c r="G263" t="s">
-        <v>790</v>
-      </c>
-      <c r="H263" t="s">
+      <c r="K263" t="s">
         <v>796</v>
-      </c>
-      <c r="I263" t="s">
-        <v>791</v>
-      </c>
-      <c r="J263" t="s">
-        <v>797</v>
-      </c>
-      <c r="K263" t="s">
-        <v>798</v>
       </c>
       <c r="L263">
         <v>0</v>
@@ -45335,31 +45329,31 @@
         <v>0</v>
       </c>
       <c r="C264" t="s">
+        <v>765</v>
+      </c>
+      <c r="D264" t="s">
+        <v>797</v>
+      </c>
+      <c r="E264" t="s">
         <v>767</v>
       </c>
-      <c r="D264" t="s">
+      <c r="F264" t="s">
+        <v>768</v>
+      </c>
+      <c r="G264" t="s">
+        <v>794</v>
+      </c>
+      <c r="H264" t="s">
+        <v>798</v>
+      </c>
+      <c r="I264" t="s">
+        <v>795</v>
+      </c>
+      <c r="J264" t="s">
         <v>799</v>
       </c>
-      <c r="E264" t="s">
-        <v>769</v>
-      </c>
-      <c r="F264" t="s">
-        <v>770</v>
-      </c>
-      <c r="G264" t="s">
-        <v>796</v>
-      </c>
-      <c r="H264" t="s">
+      <c r="K264" t="s">
         <v>800</v>
-      </c>
-      <c r="I264" t="s">
-        <v>797</v>
-      </c>
-      <c r="J264" t="s">
-        <v>801</v>
-      </c>
-      <c r="K264" t="s">
-        <v>802</v>
       </c>
       <c r="L264">
         <v>0</v>
@@ -45392,31 +45386,31 @@
         <v>0</v>
       </c>
       <c r="C265" t="s">
+        <v>765</v>
+      </c>
+      <c r="D265" t="s">
+        <v>801</v>
+      </c>
+      <c r="E265" t="s">
         <v>767</v>
       </c>
-      <c r="D265" t="s">
+      <c r="F265" t="s">
+        <v>768</v>
+      </c>
+      <c r="G265" t="s">
+        <v>798</v>
+      </c>
+      <c r="H265" t="s">
+        <v>802</v>
+      </c>
+      <c r="I265" t="s">
+        <v>799</v>
+      </c>
+      <c r="J265" t="s">
         <v>803</v>
       </c>
-      <c r="E265" t="s">
-        <v>769</v>
-      </c>
-      <c r="F265" t="s">
-        <v>770</v>
-      </c>
-      <c r="G265" t="s">
-        <v>800</v>
-      </c>
-      <c r="H265" t="s">
+      <c r="K265" t="s">
         <v>804</v>
-      </c>
-      <c r="I265" t="s">
-        <v>801</v>
-      </c>
-      <c r="J265" t="s">
-        <v>805</v>
-      </c>
-      <c r="K265" t="s">
-        <v>806</v>
       </c>
       <c r="L265">
         <v>0</v>
@@ -45449,31 +45443,31 @@
         <v>0</v>
       </c>
       <c r="C266" t="s">
+        <v>765</v>
+      </c>
+      <c r="D266" t="s">
+        <v>805</v>
+      </c>
+      <c r="E266" t="s">
         <v>767</v>
       </c>
-      <c r="D266" t="s">
+      <c r="F266" t="s">
+        <v>768</v>
+      </c>
+      <c r="G266" t="s">
+        <v>802</v>
+      </c>
+      <c r="H266" t="s">
+        <v>806</v>
+      </c>
+      <c r="I266" t="s">
+        <v>803</v>
+      </c>
+      <c r="J266" t="s">
         <v>807</v>
       </c>
-      <c r="E266" t="s">
-        <v>769</v>
-      </c>
-      <c r="F266" t="s">
-        <v>770</v>
-      </c>
-      <c r="G266" t="s">
-        <v>804</v>
-      </c>
-      <c r="H266" t="s">
+      <c r="K266" t="s">
         <v>808</v>
-      </c>
-      <c r="I266" t="s">
-        <v>805</v>
-      </c>
-      <c r="J266" t="s">
-        <v>809</v>
-      </c>
-      <c r="K266" t="s">
-        <v>810</v>
       </c>
       <c r="L266">
         <v>0</v>
@@ -45506,31 +45500,31 @@
         <v>0</v>
       </c>
       <c r="C267" t="s">
+        <v>765</v>
+      </c>
+      <c r="D267" t="s">
+        <v>809</v>
+      </c>
+      <c r="E267" t="s">
         <v>767</v>
       </c>
-      <c r="D267" t="s">
+      <c r="F267" t="s">
+        <v>768</v>
+      </c>
+      <c r="G267" t="s">
+        <v>806</v>
+      </c>
+      <c r="H267" t="s">
+        <v>810</v>
+      </c>
+      <c r="I267" t="s">
+        <v>807</v>
+      </c>
+      <c r="J267" t="s">
         <v>811</v>
       </c>
-      <c r="E267" t="s">
-        <v>769</v>
-      </c>
-      <c r="F267" t="s">
-        <v>770</v>
-      </c>
-      <c r="G267" t="s">
-        <v>808</v>
-      </c>
-      <c r="H267" t="s">
+      <c r="K267" t="s">
         <v>812</v>
-      </c>
-      <c r="I267" t="s">
-        <v>809</v>
-      </c>
-      <c r="J267" t="s">
-        <v>813</v>
-      </c>
-      <c r="K267" t="s">
-        <v>814</v>
       </c>
       <c r="L267">
         <v>0</v>
@@ -45563,31 +45557,31 @@
         <v>0</v>
       </c>
       <c r="C268" t="s">
+        <v>765</v>
+      </c>
+      <c r="D268" t="s">
+        <v>813</v>
+      </c>
+      <c r="E268" t="s">
         <v>767</v>
       </c>
-      <c r="D268" t="s">
+      <c r="F268" t="s">
+        <v>768</v>
+      </c>
+      <c r="G268" t="s">
+        <v>810</v>
+      </c>
+      <c r="H268" t="s">
+        <v>814</v>
+      </c>
+      <c r="I268" t="s">
+        <v>811</v>
+      </c>
+      <c r="J268" t="s">
         <v>815</v>
       </c>
-      <c r="E268" t="s">
-        <v>769</v>
-      </c>
-      <c r="F268" t="s">
-        <v>770</v>
-      </c>
-      <c r="G268" t="s">
-        <v>812</v>
-      </c>
-      <c r="H268" t="s">
+      <c r="K268" t="s">
         <v>816</v>
-      </c>
-      <c r="I268" t="s">
-        <v>813</v>
-      </c>
-      <c r="J268" t="s">
-        <v>817</v>
-      </c>
-      <c r="K268" t="s">
-        <v>818</v>
       </c>
       <c r="L268">
         <v>0</v>
@@ -45620,31 +45614,31 @@
         <v>0</v>
       </c>
       <c r="C269" t="s">
+        <v>765</v>
+      </c>
+      <c r="D269" t="s">
+        <v>817</v>
+      </c>
+      <c r="E269" t="s">
         <v>767</v>
       </c>
-      <c r="D269" t="s">
+      <c r="F269" t="s">
+        <v>768</v>
+      </c>
+      <c r="G269" t="s">
+        <v>814</v>
+      </c>
+      <c r="H269" t="s">
+        <v>818</v>
+      </c>
+      <c r="I269" t="s">
+        <v>815</v>
+      </c>
+      <c r="J269" t="s">
         <v>819</v>
       </c>
-      <c r="E269" t="s">
-        <v>769</v>
-      </c>
-      <c r="F269" t="s">
-        <v>770</v>
-      </c>
-      <c r="G269" t="s">
-        <v>816</v>
-      </c>
-      <c r="H269" t="s">
+      <c r="K269" t="s">
         <v>820</v>
-      </c>
-      <c r="I269" t="s">
-        <v>817</v>
-      </c>
-      <c r="J269" t="s">
-        <v>821</v>
-      </c>
-      <c r="K269" t="s">
-        <v>822</v>
       </c>
       <c r="L269">
         <v>0</v>
@@ -45677,31 +45671,31 @@
         <v>0</v>
       </c>
       <c r="C270" t="s">
+        <v>765</v>
+      </c>
+      <c r="D270" t="s">
+        <v>821</v>
+      </c>
+      <c r="E270" t="s">
         <v>767</v>
       </c>
-      <c r="D270" t="s">
+      <c r="F270" t="s">
+        <v>768</v>
+      </c>
+      <c r="G270" t="s">
+        <v>818</v>
+      </c>
+      <c r="H270" t="s">
+        <v>822</v>
+      </c>
+      <c r="I270" t="s">
+        <v>819</v>
+      </c>
+      <c r="J270" t="s">
         <v>823</v>
       </c>
-      <c r="E270" t="s">
-        <v>769</v>
-      </c>
-      <c r="F270" t="s">
-        <v>770</v>
-      </c>
-      <c r="G270" t="s">
-        <v>820</v>
-      </c>
-      <c r="H270" t="s">
+      <c r="K270" t="s">
         <v>824</v>
-      </c>
-      <c r="I270" t="s">
-        <v>821</v>
-      </c>
-      <c r="J270" t="s">
-        <v>825</v>
-      </c>
-      <c r="K270" t="s">
-        <v>826</v>
       </c>
       <c r="L270">
         <v>0</v>
@@ -45734,31 +45728,31 @@
         <v>0</v>
       </c>
       <c r="C271" t="s">
+        <v>765</v>
+      </c>
+      <c r="D271" t="s">
+        <v>825</v>
+      </c>
+      <c r="E271" t="s">
         <v>767</v>
       </c>
-      <c r="D271" t="s">
+      <c r="F271" t="s">
+        <v>768</v>
+      </c>
+      <c r="G271" t="s">
+        <v>822</v>
+      </c>
+      <c r="H271" t="s">
+        <v>826</v>
+      </c>
+      <c r="I271" t="s">
+        <v>823</v>
+      </c>
+      <c r="J271" t="s">
         <v>827</v>
       </c>
-      <c r="E271" t="s">
-        <v>769</v>
-      </c>
-      <c r="F271" t="s">
-        <v>770</v>
-      </c>
-      <c r="G271" t="s">
-        <v>824</v>
-      </c>
-      <c r="H271" t="s">
+      <c r="K271" t="s">
         <v>828</v>
-      </c>
-      <c r="I271" t="s">
-        <v>825</v>
-      </c>
-      <c r="J271" t="s">
-        <v>829</v>
-      </c>
-      <c r="K271" t="s">
-        <v>830</v>
       </c>
       <c r="L271">
         <v>0</v>
@@ -45791,34 +45785,34 @@
         <v>0</v>
       </c>
       <c r="C272" t="s">
+        <v>765</v>
+      </c>
+      <c r="D272" t="s">
+        <v>829</v>
+      </c>
+      <c r="E272" t="s">
         <v>767</v>
       </c>
-      <c r="D272" t="s">
+      <c r="F272" t="s">
+        <v>768</v>
+      </c>
+      <c r="G272" t="s">
+        <v>812</v>
+      </c>
+      <c r="H272" t="s">
+        <v>830</v>
+      </c>
+      <c r="I272" t="s">
         <v>831</v>
       </c>
-      <c r="E272" t="s">
-        <v>769</v>
-      </c>
-      <c r="F272" t="s">
-        <v>770</v>
-      </c>
-      <c r="G272" t="s">
-        <v>814</v>
-      </c>
-      <c r="H272" t="s">
+      <c r="J272" t="s">
+        <v>827</v>
+      </c>
+      <c r="K272" t="s">
         <v>832</v>
       </c>
-      <c r="I272" t="s">
+      <c r="L272" t="s">
         <v>833</v>
-      </c>
-      <c r="J272" t="s">
-        <v>829</v>
-      </c>
-      <c r="K272" t="s">
-        <v>834</v>
-      </c>
-      <c r="L272" t="s">
-        <v>835</v>
       </c>
       <c r="M272">
         <v>0</v>
@@ -45848,34 +45842,34 @@
         <v>0</v>
       </c>
       <c r="C273" t="s">
+        <v>765</v>
+      </c>
+      <c r="D273" t="s">
+        <v>834</v>
+      </c>
+      <c r="E273" t="s">
         <v>767</v>
       </c>
-      <c r="D273" t="s">
-        <v>836</v>
-      </c>
-      <c r="E273" t="s">
-        <v>769</v>
-      </c>
       <c r="F273" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="G273" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="H273" t="s">
+        <v>830</v>
+      </c>
+      <c r="I273" t="s">
+        <v>831</v>
+      </c>
+      <c r="J273" t="s">
+        <v>827</v>
+      </c>
+      <c r="K273" t="s">
         <v>832</v>
       </c>
-      <c r="I273" t="s">
+      <c r="L273" t="s">
         <v>833</v>
-      </c>
-      <c r="J273" t="s">
-        <v>829</v>
-      </c>
-      <c r="K273" t="s">
-        <v>834</v>
-      </c>
-      <c r="L273" t="s">
-        <v>835</v>
       </c>
       <c r="M273">
         <v>0</v>
@@ -45905,34 +45899,34 @@
         <v>0</v>
       </c>
       <c r="C274" t="s">
+        <v>765</v>
+      </c>
+      <c r="D274" t="s">
+        <v>835</v>
+      </c>
+      <c r="E274" t="s">
         <v>767</v>
       </c>
-      <c r="D274" t="s">
-        <v>837</v>
-      </c>
-      <c r="E274" t="s">
-        <v>769</v>
-      </c>
       <c r="F274" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="G274" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="H274" t="s">
+        <v>830</v>
+      </c>
+      <c r="I274" t="s">
+        <v>831</v>
+      </c>
+      <c r="J274" t="s">
+        <v>827</v>
+      </c>
+      <c r="K274" t="s">
         <v>832</v>
       </c>
-      <c r="I274" t="s">
+      <c r="L274" t="s">
         <v>833</v>
-      </c>
-      <c r="J274" t="s">
-        <v>829</v>
-      </c>
-      <c r="K274" t="s">
-        <v>834</v>
-      </c>
-      <c r="L274" t="s">
-        <v>835</v>
       </c>
       <c r="M274">
         <v>0</v>
@@ -45962,28 +45956,28 @@
         <v>0</v>
       </c>
       <c r="C275" t="s">
+        <v>836</v>
+      </c>
+      <c r="D275" t="s">
+        <v>766</v>
+      </c>
+      <c r="E275" t="s">
+        <v>837</v>
+      </c>
+      <c r="F275" t="s">
         <v>838</v>
       </c>
-      <c r="D275" t="s">
-        <v>768</v>
-      </c>
-      <c r="E275" t="s">
+      <c r="G275" t="s">
         <v>839</v>
       </c>
-      <c r="F275" t="s">
+      <c r="H275" t="s">
         <v>840</v>
       </c>
-      <c r="G275" t="s">
+      <c r="I275" t="s">
         <v>841</v>
       </c>
-      <c r="H275" t="s">
+      <c r="J275" t="s">
         <v>842</v>
-      </c>
-      <c r="I275" t="s">
-        <v>843</v>
-      </c>
-      <c r="J275" t="s">
-        <v>844</v>
       </c>
       <c r="K275">
         <v>0</v>
@@ -46019,28 +46013,28 @@
         <v>0</v>
       </c>
       <c r="C276" t="s">
+        <v>836</v>
+      </c>
+      <c r="D276" t="s">
+        <v>771</v>
+      </c>
+      <c r="E276" t="s">
+        <v>837</v>
+      </c>
+      <c r="F276" t="s">
         <v>838</v>
       </c>
-      <c r="D276" t="s">
-        <v>773</v>
-      </c>
-      <c r="E276" t="s">
-        <v>839</v>
-      </c>
-      <c r="F276" t="s">
+      <c r="G276" t="s">
+        <v>843</v>
+      </c>
+      <c r="H276" t="s">
         <v>840</v>
       </c>
-      <c r="G276" t="s">
+      <c r="I276" t="s">
+        <v>844</v>
+      </c>
+      <c r="J276" t="s">
         <v>845</v>
-      </c>
-      <c r="H276" t="s">
-        <v>842</v>
-      </c>
-      <c r="I276" t="s">
-        <v>846</v>
-      </c>
-      <c r="J276" t="s">
-        <v>847</v>
       </c>
       <c r="K276">
         <v>0</v>
@@ -46076,28 +46070,28 @@
         <v>0</v>
       </c>
       <c r="C277" t="s">
+        <v>836</v>
+      </c>
+      <c r="D277" t="s">
+        <v>774</v>
+      </c>
+      <c r="E277" t="s">
+        <v>837</v>
+      </c>
+      <c r="F277" t="s">
         <v>838</v>
       </c>
-      <c r="D277" t="s">
-        <v>776</v>
-      </c>
-      <c r="E277" t="s">
-        <v>839</v>
-      </c>
-      <c r="F277" t="s">
+      <c r="G277" t="s">
+        <v>846</v>
+      </c>
+      <c r="H277" t="s">
         <v>840</v>
       </c>
-      <c r="G277" t="s">
+      <c r="I277" t="s">
+        <v>847</v>
+      </c>
+      <c r="J277" t="s">
         <v>848</v>
-      </c>
-      <c r="H277" t="s">
-        <v>842</v>
-      </c>
-      <c r="I277" t="s">
-        <v>849</v>
-      </c>
-      <c r="J277" t="s">
-        <v>850</v>
       </c>
       <c r="K277">
         <v>0</v>
@@ -46133,31 +46127,31 @@
         <v>0</v>
       </c>
       <c r="C278" t="s">
+        <v>836</v>
+      </c>
+      <c r="D278" t="s">
+        <v>777</v>
+      </c>
+      <c r="E278" t="s">
+        <v>837</v>
+      </c>
+      <c r="F278" t="s">
         <v>838</v>
       </c>
-      <c r="D278" t="s">
-        <v>779</v>
-      </c>
-      <c r="E278" t="s">
-        <v>839</v>
-      </c>
-      <c r="F278" t="s">
+      <c r="G278" t="s">
+        <v>849</v>
+      </c>
+      <c r="H278" t="s">
         <v>840</v>
       </c>
-      <c r="G278" t="s">
-        <v>851</v>
-      </c>
-      <c r="H278" t="s">
-        <v>842</v>
-      </c>
       <c r="I278" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="J278" t="s">
+        <v>848</v>
+      </c>
+      <c r="K278" t="s">
         <v>850</v>
-      </c>
-      <c r="K278" t="s">
-        <v>852</v>
       </c>
       <c r="L278">
         <v>0</v>
@@ -46190,31 +46184,31 @@
         <v>0</v>
       </c>
       <c r="C279" t="s">
+        <v>836</v>
+      </c>
+      <c r="D279" t="s">
+        <v>780</v>
+      </c>
+      <c r="E279" t="s">
+        <v>837</v>
+      </c>
+      <c r="F279" t="s">
         <v>838</v>
       </c>
-      <c r="D279" t="s">
-        <v>782</v>
-      </c>
-      <c r="E279" t="s">
-        <v>839</v>
-      </c>
-      <c r="F279" t="s">
+      <c r="G279" t="s">
+        <v>851</v>
+      </c>
+      <c r="H279" t="s">
         <v>840</v>
       </c>
-      <c r="G279" t="s">
+      <c r="I279" t="s">
+        <v>847</v>
+      </c>
+      <c r="J279" t="s">
+        <v>852</v>
+      </c>
+      <c r="K279" t="s">
         <v>853</v>
-      </c>
-      <c r="H279" t="s">
-        <v>842</v>
-      </c>
-      <c r="I279" t="s">
-        <v>849</v>
-      </c>
-      <c r="J279" t="s">
-        <v>854</v>
-      </c>
-      <c r="K279" t="s">
-        <v>855</v>
       </c>
       <c r="L279">
         <v>0</v>
@@ -46247,31 +46241,31 @@
         <v>0</v>
       </c>
       <c r="C280" t="s">
+        <v>836</v>
+      </c>
+      <c r="D280" t="s">
+        <v>783</v>
+      </c>
+      <c r="E280" t="s">
+        <v>837</v>
+      </c>
+      <c r="F280" t="s">
         <v>838</v>
       </c>
-      <c r="D280" t="s">
-        <v>785</v>
-      </c>
-      <c r="E280" t="s">
-        <v>839</v>
-      </c>
-      <c r="F280" t="s">
+      <c r="G280" t="s">
+        <v>854</v>
+      </c>
+      <c r="H280" t="s">
         <v>840</v>
       </c>
-      <c r="G280" t="s">
+      <c r="I280" t="s">
+        <v>847</v>
+      </c>
+      <c r="J280" t="s">
+        <v>855</v>
+      </c>
+      <c r="K280" t="s">
         <v>856</v>
-      </c>
-      <c r="H280" t="s">
-        <v>842</v>
-      </c>
-      <c r="I280" t="s">
-        <v>849</v>
-      </c>
-      <c r="J280" t="s">
-        <v>857</v>
-      </c>
-      <c r="K280" t="s">
-        <v>858</v>
       </c>
       <c r="L280">
         <v>0</v>
@@ -46304,31 +46298,31 @@
         <v>0</v>
       </c>
       <c r="C281" t="s">
+        <v>836</v>
+      </c>
+      <c r="D281" t="s">
+        <v>786</v>
+      </c>
+      <c r="E281" t="s">
+        <v>837</v>
+      </c>
+      <c r="F281" t="s">
         <v>838</v>
       </c>
-      <c r="D281" t="s">
-        <v>788</v>
-      </c>
-      <c r="E281" t="s">
-        <v>839</v>
-      </c>
-      <c r="F281" t="s">
+      <c r="G281" t="s">
+        <v>857</v>
+      </c>
+      <c r="H281" t="s">
         <v>840</v>
       </c>
-      <c r="G281" t="s">
+      <c r="I281" t="s">
+        <v>858</v>
+      </c>
+      <c r="J281" t="s">
         <v>859</v>
       </c>
-      <c r="H281" t="s">
-        <v>842</v>
-      </c>
-      <c r="I281" t="s">
+      <c r="K281" t="s">
         <v>860</v>
-      </c>
-      <c r="J281" t="s">
-        <v>861</v>
-      </c>
-      <c r="K281" t="s">
-        <v>862</v>
       </c>
       <c r="L281">
         <v>0</v>
@@ -46361,31 +46355,31 @@
         <v>0</v>
       </c>
       <c r="C282" t="s">
+        <v>836</v>
+      </c>
+      <c r="D282" t="s">
+        <v>791</v>
+      </c>
+      <c r="E282" t="s">
+        <v>837</v>
+      </c>
+      <c r="F282" t="s">
         <v>838</v>
       </c>
-      <c r="D282" t="s">
-        <v>793</v>
-      </c>
-      <c r="E282" t="s">
-        <v>839</v>
-      </c>
-      <c r="F282" t="s">
+      <c r="G282" t="s">
+        <v>861</v>
+      </c>
+      <c r="H282" t="s">
         <v>840</v>
       </c>
-      <c r="G282" t="s">
+      <c r="I282" t="s">
+        <v>862</v>
+      </c>
+      <c r="J282" t="s">
         <v>863</v>
       </c>
-      <c r="H282" t="s">
-        <v>842</v>
-      </c>
-      <c r="I282" t="s">
+      <c r="K282" t="s">
         <v>864</v>
-      </c>
-      <c r="J282" t="s">
-        <v>865</v>
-      </c>
-      <c r="K282" t="s">
-        <v>866</v>
       </c>
       <c r="L282">
         <v>0</v>
@@ -46418,31 +46412,31 @@
         <v>0</v>
       </c>
       <c r="C283" t="s">
+        <v>836</v>
+      </c>
+      <c r="D283" t="s">
+        <v>793</v>
+      </c>
+      <c r="E283" t="s">
+        <v>837</v>
+      </c>
+      <c r="F283" t="s">
         <v>838</v>
       </c>
-      <c r="D283" t="s">
-        <v>795</v>
-      </c>
-      <c r="E283" t="s">
-        <v>839</v>
-      </c>
-      <c r="F283" t="s">
+      <c r="G283" t="s">
+        <v>865</v>
+      </c>
+      <c r="H283" t="s">
         <v>840</v>
       </c>
-      <c r="G283" t="s">
+      <c r="I283" t="s">
+        <v>866</v>
+      </c>
+      <c r="J283" t="s">
         <v>867</v>
       </c>
-      <c r="H283" t="s">
-        <v>842</v>
-      </c>
-      <c r="I283" t="s">
+      <c r="K283" t="s">
         <v>868</v>
-      </c>
-      <c r="J283" t="s">
-        <v>869</v>
-      </c>
-      <c r="K283" t="s">
-        <v>870</v>
       </c>
       <c r="L283">
         <v>0</v>
@@ -46475,34 +46469,34 @@
         <v>0</v>
       </c>
       <c r="C284" t="s">
+        <v>836</v>
+      </c>
+      <c r="D284" t="s">
+        <v>797</v>
+      </c>
+      <c r="E284" t="s">
+        <v>837</v>
+      </c>
+      <c r="F284" t="s">
         <v>838</v>
       </c>
-      <c r="D284" t="s">
-        <v>799</v>
-      </c>
-      <c r="E284" t="s">
-        <v>839</v>
-      </c>
-      <c r="F284" t="s">
+      <c r="G284" t="s">
+        <v>869</v>
+      </c>
+      <c r="H284" t="s">
         <v>840</v>
       </c>
-      <c r="G284" t="s">
+      <c r="I284" t="s">
+        <v>866</v>
+      </c>
+      <c r="J284" t="s">
+        <v>867</v>
+      </c>
+      <c r="K284" t="s">
+        <v>870</v>
+      </c>
+      <c r="L284" t="s">
         <v>871</v>
-      </c>
-      <c r="H284" t="s">
-        <v>842</v>
-      </c>
-      <c r="I284" t="s">
-        <v>868</v>
-      </c>
-      <c r="J284" t="s">
-        <v>869</v>
-      </c>
-      <c r="K284" t="s">
-        <v>872</v>
-      </c>
-      <c r="L284" t="s">
-        <v>873</v>
       </c>
       <c r="M284">
         <v>0</v>
@@ -46532,34 +46526,34 @@
         <v>0</v>
       </c>
       <c r="C285" t="s">
+        <v>836</v>
+      </c>
+      <c r="D285" t="s">
+        <v>801</v>
+      </c>
+      <c r="E285" t="s">
+        <v>837</v>
+      </c>
+      <c r="F285" t="s">
         <v>838</v>
       </c>
-      <c r="D285" t="s">
-        <v>803</v>
-      </c>
-      <c r="E285" t="s">
-        <v>839</v>
-      </c>
-      <c r="F285" t="s">
+      <c r="G285" t="s">
+        <v>872</v>
+      </c>
+      <c r="H285" t="s">
         <v>840</v>
       </c>
-      <c r="G285" t="s">
+      <c r="I285" t="s">
+        <v>866</v>
+      </c>
+      <c r="J285" t="s">
+        <v>867</v>
+      </c>
+      <c r="K285" t="s">
+        <v>873</v>
+      </c>
+      <c r="L285" t="s">
         <v>874</v>
-      </c>
-      <c r="H285" t="s">
-        <v>842</v>
-      </c>
-      <c r="I285" t="s">
-        <v>868</v>
-      </c>
-      <c r="J285" t="s">
-        <v>869</v>
-      </c>
-      <c r="K285" t="s">
-        <v>875</v>
-      </c>
-      <c r="L285" t="s">
-        <v>876</v>
       </c>
       <c r="M285">
         <v>0</v>
@@ -46589,34 +46583,34 @@
         <v>0</v>
       </c>
       <c r="C286" t="s">
+        <v>836</v>
+      </c>
+      <c r="D286" t="s">
+        <v>805</v>
+      </c>
+      <c r="E286" t="s">
+        <v>837</v>
+      </c>
+      <c r="F286" t="s">
         <v>838</v>
       </c>
-      <c r="D286" t="s">
-        <v>807</v>
-      </c>
-      <c r="E286" t="s">
-        <v>839</v>
-      </c>
-      <c r="F286" t="s">
+      <c r="G286" t="s">
+        <v>875</v>
+      </c>
+      <c r="H286" t="s">
         <v>840</v>
       </c>
-      <c r="G286" t="s">
+      <c r="I286" t="s">
+        <v>876</v>
+      </c>
+      <c r="J286" t="s">
         <v>877</v>
       </c>
-      <c r="H286" t="s">
-        <v>842</v>
-      </c>
-      <c r="I286" t="s">
+      <c r="K286" t="s">
         <v>878</v>
       </c>
-      <c r="J286" t="s">
+      <c r="L286" t="s">
         <v>879</v>
-      </c>
-      <c r="K286" t="s">
-        <v>880</v>
-      </c>
-      <c r="L286" t="s">
-        <v>881</v>
       </c>
       <c r="M286">
         <v>0</v>
@@ -46646,34 +46640,34 @@
         <v>0</v>
       </c>
       <c r="C287" t="s">
+        <v>836</v>
+      </c>
+      <c r="D287" t="s">
+        <v>809</v>
+      </c>
+      <c r="E287" t="s">
+        <v>837</v>
+      </c>
+      <c r="F287" t="s">
         <v>838</v>
       </c>
-      <c r="D287" t="s">
-        <v>811</v>
-      </c>
-      <c r="E287" t="s">
-        <v>839</v>
-      </c>
-      <c r="F287" t="s">
+      <c r="G287" t="s">
+        <v>880</v>
+      </c>
+      <c r="H287" t="s">
         <v>840</v>
       </c>
-      <c r="G287" t="s">
-        <v>882</v>
-      </c>
-      <c r="H287" t="s">
-        <v>842</v>
-      </c>
       <c r="I287" t="s">
+        <v>876</v>
+      </c>
+      <c r="J287" t="s">
+        <v>877</v>
+      </c>
+      <c r="K287" t="s">
         <v>878</v>
       </c>
-      <c r="J287" t="s">
-        <v>879</v>
-      </c>
-      <c r="K287" t="s">
-        <v>880</v>
-      </c>
       <c r="L287" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="M287">
         <v>0</v>
@@ -46703,34 +46697,34 @@
         <v>0</v>
       </c>
       <c r="C288" t="s">
+        <v>836</v>
+      </c>
+      <c r="D288" t="s">
+        <v>813</v>
+      </c>
+      <c r="E288" t="s">
+        <v>837</v>
+      </c>
+      <c r="F288" t="s">
         <v>838</v>
       </c>
-      <c r="D288" t="s">
-        <v>815</v>
-      </c>
-      <c r="E288" t="s">
-        <v>839</v>
-      </c>
-      <c r="F288" t="s">
+      <c r="G288" t="s">
+        <v>882</v>
+      </c>
+      <c r="H288" t="s">
         <v>840</v>
       </c>
-      <c r="G288" t="s">
-        <v>884</v>
-      </c>
-      <c r="H288" t="s">
-        <v>842</v>
-      </c>
       <c r="I288" t="s">
+        <v>876</v>
+      </c>
+      <c r="J288" t="s">
+        <v>877</v>
+      </c>
+      <c r="K288" t="s">
         <v>878</v>
       </c>
-      <c r="J288" t="s">
-        <v>879</v>
-      </c>
-      <c r="K288" t="s">
-        <v>880</v>
-      </c>
       <c r="L288" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="M288">
         <v>0</v>
@@ -46760,37 +46754,37 @@
         <v>0</v>
       </c>
       <c r="C289" t="s">
+        <v>836</v>
+      </c>
+      <c r="D289" t="s">
+        <v>817</v>
+      </c>
+      <c r="E289" t="s">
+        <v>837</v>
+      </c>
+      <c r="F289" t="s">
         <v>838</v>
       </c>
-      <c r="D289" t="s">
-        <v>819</v>
-      </c>
-      <c r="E289" t="s">
-        <v>839</v>
-      </c>
-      <c r="F289" t="s">
+      <c r="G289" t="s">
+        <v>884</v>
+      </c>
+      <c r="H289" t="s">
         <v>840</v>
       </c>
-      <c r="G289" t="s">
+      <c r="I289" t="s">
+        <v>876</v>
+      </c>
+      <c r="J289" t="s">
+        <v>885</v>
+      </c>
+      <c r="K289" t="s">
         <v>886</v>
       </c>
-      <c r="H289" t="s">
-        <v>842</v>
-      </c>
-      <c r="I289" t="s">
-        <v>878</v>
-      </c>
-      <c r="J289" t="s">
+      <c r="L289" t="s">
+        <v>879</v>
+      </c>
+      <c r="M289" t="s">
         <v>887</v>
-      </c>
-      <c r="K289" t="s">
-        <v>888</v>
-      </c>
-      <c r="L289" t="s">
-        <v>881</v>
-      </c>
-      <c r="M289" t="s">
-        <v>889</v>
       </c>
       <c r="N289">
         <v>0</v>
@@ -46817,37 +46811,37 @@
         <v>0</v>
       </c>
       <c r="C290" t="s">
+        <v>836</v>
+      </c>
+      <c r="D290" t="s">
+        <v>821</v>
+      </c>
+      <c r="E290" t="s">
+        <v>837</v>
+      </c>
+      <c r="F290" t="s">
         <v>838</v>
       </c>
-      <c r="D290" t="s">
-        <v>823</v>
-      </c>
-      <c r="E290" t="s">
-        <v>839</v>
-      </c>
-      <c r="F290" t="s">
+      <c r="G290" t="s">
+        <v>888</v>
+      </c>
+      <c r="H290" t="s">
         <v>840</v>
       </c>
-      <c r="G290" t="s">
-        <v>890</v>
-      </c>
-      <c r="H290" t="s">
-        <v>842</v>
-      </c>
       <c r="I290" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="J290" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="K290" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="L290" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="M290" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="N290">
         <v>0</v>
@@ -46874,37 +46868,37 @@
         <v>0</v>
       </c>
       <c r="C291" t="s">
+        <v>836</v>
+      </c>
+      <c r="D291" t="s">
+        <v>825</v>
+      </c>
+      <c r="E291" t="s">
+        <v>837</v>
+      </c>
+      <c r="F291" t="s">
         <v>838</v>
       </c>
-      <c r="D291" t="s">
-        <v>827</v>
-      </c>
-      <c r="E291" t="s">
-        <v>839</v>
-      </c>
-      <c r="F291" t="s">
+      <c r="G291" t="s">
+        <v>890</v>
+      </c>
+      <c r="H291" t="s">
         <v>840</v>
       </c>
-      <c r="G291" t="s">
-        <v>892</v>
-      </c>
-      <c r="H291" t="s">
-        <v>842</v>
-      </c>
       <c r="I291" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="J291" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="K291" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="L291" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="M291" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="N291">
         <v>0</v>
@@ -46931,40 +46925,40 @@
         <v>0</v>
       </c>
       <c r="C292" t="s">
+        <v>836</v>
+      </c>
+      <c r="D292" t="s">
+        <v>829</v>
+      </c>
+      <c r="E292" t="s">
+        <v>837</v>
+      </c>
+      <c r="F292" t="s">
         <v>838</v>
       </c>
-      <c r="D292" t="s">
-        <v>831</v>
-      </c>
-      <c r="E292" t="s">
-        <v>839</v>
-      </c>
-      <c r="F292" t="s">
+      <c r="G292" t="s">
+        <v>892</v>
+      </c>
+      <c r="H292" t="s">
         <v>840</v>
       </c>
-      <c r="G292" t="s">
-        <v>894</v>
-      </c>
-      <c r="H292" t="s">
-        <v>842</v>
-      </c>
       <c r="I292" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="J292" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="K292" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="L292" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="M292" t="s">
+        <v>891</v>
+      </c>
+      <c r="N292" t="s">
         <v>893</v>
-      </c>
-      <c r="N292" t="s">
-        <v>895</v>
       </c>
       <c r="O292">
         <v>0</v>
@@ -46988,43 +46982,43 @@
         <v>0</v>
       </c>
       <c r="C293" t="s">
+        <v>836</v>
+      </c>
+      <c r="D293" t="s">
+        <v>834</v>
+      </c>
+      <c r="E293" t="s">
+        <v>837</v>
+      </c>
+      <c r="F293" t="s">
         <v>838</v>
       </c>
-      <c r="D293" t="s">
-        <v>836</v>
-      </c>
-      <c r="E293" t="s">
-        <v>839</v>
-      </c>
-      <c r="F293" t="s">
+      <c r="G293" t="s">
+        <v>894</v>
+      </c>
+      <c r="H293" t="s">
         <v>840</v>
       </c>
-      <c r="G293" t="s">
+      <c r="I293" t="s">
+        <v>876</v>
+      </c>
+      <c r="J293" t="s">
+        <v>885</v>
+      </c>
+      <c r="K293" t="s">
+        <v>886</v>
+      </c>
+      <c r="L293" t="s">
+        <v>881</v>
+      </c>
+      <c r="M293" t="s">
+        <v>891</v>
+      </c>
+      <c r="N293" t="s">
+        <v>895</v>
+      </c>
+      <c r="O293" t="s">
         <v>896</v>
-      </c>
-      <c r="H293" t="s">
-        <v>842</v>
-      </c>
-      <c r="I293" t="s">
-        <v>878</v>
-      </c>
-      <c r="J293" t="s">
-        <v>887</v>
-      </c>
-      <c r="K293" t="s">
-        <v>888</v>
-      </c>
-      <c r="L293" t="s">
-        <v>883</v>
-      </c>
-      <c r="M293" t="s">
-        <v>893</v>
-      </c>
-      <c r="N293" t="s">
-        <v>897</v>
-      </c>
-      <c r="O293" t="s">
-        <v>898</v>
       </c>
       <c r="P293">
         <v>0</v>
@@ -47045,46 +47039,46 @@
         <v>0</v>
       </c>
       <c r="C294" t="s">
+        <v>836</v>
+      </c>
+      <c r="D294" t="s">
+        <v>835</v>
+      </c>
+      <c r="E294" t="s">
+        <v>837</v>
+      </c>
+      <c r="F294" t="s">
         <v>838</v>
       </c>
-      <c r="D294" t="s">
-        <v>837</v>
-      </c>
-      <c r="E294" t="s">
-        <v>839</v>
-      </c>
-      <c r="F294" t="s">
+      <c r="G294" t="s">
+        <v>897</v>
+      </c>
+      <c r="H294" t="s">
         <v>840</v>
       </c>
-      <c r="G294" t="s">
+      <c r="I294" t="s">
+        <v>876</v>
+      </c>
+      <c r="J294" t="s">
+        <v>885</v>
+      </c>
+      <c r="K294" t="s">
+        <v>886</v>
+      </c>
+      <c r="L294" t="s">
+        <v>881</v>
+      </c>
+      <c r="M294" t="s">
+        <v>891</v>
+      </c>
+      <c r="N294" t="s">
+        <v>898</v>
+      </c>
+      <c r="O294" t="s">
         <v>899</v>
       </c>
-      <c r="H294" t="s">
-        <v>842</v>
-      </c>
-      <c r="I294" t="s">
-        <v>878</v>
-      </c>
-      <c r="J294" t="s">
-        <v>887</v>
-      </c>
-      <c r="K294" t="s">
-        <v>888</v>
-      </c>
-      <c r="L294" t="s">
-        <v>883</v>
-      </c>
-      <c r="M294" t="s">
-        <v>893</v>
-      </c>
-      <c r="N294" t="s">
+      <c r="P294" t="s">
         <v>900</v>
-      </c>
-      <c r="O294" t="s">
-        <v>901</v>
-      </c>
-      <c r="P294" t="s">
-        <v>902</v>
       </c>
       <c r="Q294">
         <v>0</v>
@@ -47102,16 +47096,16 @@
         <v>0</v>
       </c>
       <c r="C295" t="s">
+        <v>901</v>
+      </c>
+      <c r="D295" t="s">
+        <v>902</v>
+      </c>
+      <c r="E295" t="s">
         <v>903</v>
       </c>
-      <c r="D295" t="s">
+      <c r="F295" t="s">
         <v>904</v>
-      </c>
-      <c r="E295" t="s">
-        <v>905</v>
-      </c>
-      <c r="F295" t="s">
-        <v>906</v>
       </c>
       <c r="G295">
         <v>0</v>
@@ -47159,16 +47153,16 @@
         <v>0</v>
       </c>
       <c r="C296" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D296" t="s">
+        <v>905</v>
+      </c>
+      <c r="E296" t="s">
+        <v>906</v>
+      </c>
+      <c r="F296" t="s">
         <v>907</v>
-      </c>
-      <c r="E296" t="s">
-        <v>908</v>
-      </c>
-      <c r="F296" t="s">
-        <v>909</v>
       </c>
       <c r="G296">
         <v>0.1</v>
@@ -47216,16 +47210,16 @@
         <v>0</v>
       </c>
       <c r="C297" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D297" t="s">
+        <v>908</v>
+      </c>
+      <c r="E297" t="s">
+        <v>909</v>
+      </c>
+      <c r="F297" t="s">
         <v>910</v>
-      </c>
-      <c r="E297" t="s">
-        <v>911</v>
-      </c>
-      <c r="F297" t="s">
-        <v>912</v>
       </c>
       <c r="G297">
         <v>0</v>
@@ -47273,16 +47267,16 @@
         <v>0</v>
       </c>
       <c r="C298" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D298" t="s">
+        <v>911</v>
+      </c>
+      <c r="E298" t="s">
+        <v>912</v>
+      </c>
+      <c r="F298" t="s">
         <v>913</v>
-      </c>
-      <c r="E298" t="s">
-        <v>914</v>
-      </c>
-      <c r="F298" t="s">
-        <v>915</v>
       </c>
       <c r="G298">
         <v>0</v>
@@ -47330,16 +47324,16 @@
         <v>0</v>
       </c>
       <c r="C299" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D299" t="s">
+        <v>914</v>
+      </c>
+      <c r="E299" t="s">
+        <v>915</v>
+      </c>
+      <c r="F299" t="s">
         <v>916</v>
-      </c>
-      <c r="E299" t="s">
-        <v>917</v>
-      </c>
-      <c r="F299" t="s">
-        <v>918</v>
       </c>
       <c r="G299">
         <v>0</v>
@@ -47387,16 +47381,16 @@
         <v>0</v>
       </c>
       <c r="C300" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D300" t="s">
+        <v>917</v>
+      </c>
+      <c r="E300" t="s">
+        <v>918</v>
+      </c>
+      <c r="F300" t="s">
         <v>919</v>
-      </c>
-      <c r="E300" t="s">
-        <v>920</v>
-      </c>
-      <c r="F300" t="s">
-        <v>921</v>
       </c>
       <c r="G300">
         <v>0.4</v>
@@ -47444,16 +47438,16 @@
         <v>0</v>
       </c>
       <c r="C301" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D301" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>1072</v>
+        <v>1056</v>
       </c>
       <c r="F301" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="G301">
         <v>1000</v>
@@ -47501,16 +47495,16 @@
         <v>0</v>
       </c>
       <c r="C302" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D302" t="s">
+        <v>921</v>
+      </c>
+      <c r="E302" t="s">
+        <v>922</v>
+      </c>
+      <c r="F302" t="s">
         <v>923</v>
-      </c>
-      <c r="E302" t="s">
-        <v>924</v>
-      </c>
-      <c r="F302" t="s">
-        <v>925</v>
       </c>
       <c r="G302">
         <v>0</v>
@@ -47558,16 +47552,16 @@
         <v>0</v>
       </c>
       <c r="C303" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D303" t="s">
+        <v>924</v>
+      </c>
+      <c r="E303" t="s">
+        <v>925</v>
+      </c>
+      <c r="F303" t="s">
         <v>926</v>
-      </c>
-      <c r="E303" t="s">
-        <v>927</v>
-      </c>
-      <c r="F303" t="s">
-        <v>928</v>
       </c>
       <c r="G303">
         <v>30</v>
@@ -47615,16 +47609,16 @@
         <v>0</v>
       </c>
       <c r="C304" t="s">
+        <v>927</v>
+      </c>
+      <c r="D304" t="s">
+        <v>928</v>
+      </c>
+      <c r="E304" t="s">
         <v>929</v>
       </c>
-      <c r="D304" t="s">
+      <c r="F304" t="s">
         <v>930</v>
-      </c>
-      <c r="E304" t="s">
-        <v>931</v>
-      </c>
-      <c r="F304" t="s">
-        <v>932</v>
       </c>
       <c r="G304">
         <v>0.75</v>
@@ -47672,13 +47666,13 @@
         <v>0</v>
       </c>
       <c r="C305" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D305" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="E305" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="F305">
         <v>0</v>
@@ -47729,16 +47723,16 @@
         <v>0</v>
       </c>
       <c r="C306" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D306" t="s">
+        <v>933</v>
+      </c>
+      <c r="E306" t="s">
+        <v>934</v>
+      </c>
+      <c r="F306" t="s">
         <v>935</v>
-      </c>
-      <c r="E306" t="s">
-        <v>936</v>
-      </c>
-      <c r="F306" t="s">
-        <v>937</v>
       </c>
       <c r="G306">
         <v>45</v>
@@ -47786,16 +47780,16 @@
         <v>0</v>
       </c>
       <c r="C307" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D307" t="s">
+        <v>936</v>
+      </c>
+      <c r="E307" t="s">
+        <v>937</v>
+      </c>
+      <c r="F307" t="s">
         <v>938</v>
-      </c>
-      <c r="E307" t="s">
-        <v>939</v>
-      </c>
-      <c r="F307" t="s">
-        <v>940</v>
       </c>
       <c r="G307">
         <v>0</v>
@@ -47843,16 +47837,16 @@
         <v>0</v>
       </c>
       <c r="C308" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D308" t="s">
+        <v>939</v>
+      </c>
+      <c r="E308" t="s">
+        <v>940</v>
+      </c>
+      <c r="F308" t="s">
         <v>941</v>
-      </c>
-      <c r="E308" t="s">
-        <v>942</v>
-      </c>
-      <c r="F308" t="s">
-        <v>943</v>
       </c>
       <c r="G308">
         <v>0.1</v>
@@ -47900,16 +47894,16 @@
         <v>0</v>
       </c>
       <c r="C309" t="s">
+        <v>942</v>
+      </c>
+      <c r="D309" t="s">
+        <v>943</v>
+      </c>
+      <c r="E309" t="s">
         <v>944</v>
       </c>
-      <c r="D309" t="s">
+      <c r="F309" t="s">
         <v>945</v>
-      </c>
-      <c r="E309" t="s">
-        <v>946</v>
-      </c>
-      <c r="F309" t="s">
-        <v>947</v>
       </c>
       <c r="G309">
         <v>24</v>
@@ -47957,16 +47951,16 @@
         <v>0</v>
       </c>
       <c r="C310" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="D310" t="s">
+        <v>946</v>
+      </c>
+      <c r="E310" t="s">
+        <v>947</v>
+      </c>
+      <c r="F310" t="s">
         <v>948</v>
-      </c>
-      <c r="E310" t="s">
-        <v>949</v>
-      </c>
-      <c r="F310" t="s">
-        <v>950</v>
       </c>
       <c r="G310">
         <v>10</v>
@@ -48014,16 +48008,16 @@
         <v>0</v>
       </c>
       <c r="C311" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="D311" t="s">
+        <v>949</v>
+      </c>
+      <c r="E311" t="s">
+        <v>950</v>
+      </c>
+      <c r="F311" t="s">
         <v>951</v>
-      </c>
-      <c r="E311" t="s">
-        <v>952</v>
-      </c>
-      <c r="F311" t="s">
-        <v>953</v>
       </c>
       <c r="G311">
         <v>20</v>
@@ -48071,16 +48065,16 @@
         <v>0</v>
       </c>
       <c r="C312" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D312" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="E312" t="s">
         <v>39</v>
       </c>
       <c r="F312" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="G312">
         <v>1</v>
@@ -48128,16 +48122,16 @@
         <v>0</v>
       </c>
       <c r="C313" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D313" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="E313" t="s">
         <v>39</v>
       </c>
       <c r="F313" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="G313">
         <v>1.35</v>
@@ -48185,16 +48179,16 @@
         <v>0</v>
       </c>
       <c r="C314" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D314" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="E314" t="s">
         <v>39</v>
       </c>
       <c r="F314" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="G314">
         <v>1.75</v>
@@ -48242,16 +48236,16 @@
         <v>0</v>
       </c>
       <c r="C315" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D315" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="E315" t="s">
         <v>39</v>
       </c>
       <c r="F315" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="G315">
         <v>2.2999999999999998</v>
@@ -48299,16 +48293,16 @@
         <v>0</v>
       </c>
       <c r="C316" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D316" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="E316" t="s">
         <v>39</v>
       </c>
       <c r="F316" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="G316">
         <v>3</v>
@@ -48356,16 +48350,16 @@
         <v>0</v>
       </c>
       <c r="C317" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D317" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="E317" t="s">
         <v>39</v>
       </c>
       <c r="F317" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="G317">
         <v>4</v>
@@ -48413,16 +48407,16 @@
         <v>0</v>
       </c>
       <c r="C318" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D318" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="E318" t="s">
         <v>39</v>
       </c>
       <c r="F318" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="G318">
         <v>5.2</v>
@@ -48470,16 +48464,16 @@
         <v>0</v>
       </c>
       <c r="C319" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D319" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="E319" t="s">
         <v>39</v>
       </c>
       <c r="F319" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="G319">
         <v>6.8</v>
@@ -48527,16 +48521,16 @@
         <v>0</v>
       </c>
       <c r="C320" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D320" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="E320" t="s">
         <v>39</v>
       </c>
       <c r="F320" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="G320">
         <v>10.199999999999999</v>
@@ -48584,22 +48578,22 @@
         <v>0</v>
       </c>
       <c r="C321" t="s">
+        <v>963</v>
+      </c>
+      <c r="D321" t="s">
+        <v>964</v>
+      </c>
+      <c r="E321" t="s">
         <v>965</v>
       </c>
-      <c r="D321" t="s">
+      <c r="F321" t="s">
         <v>966</v>
-      </c>
-      <c r="E321" t="s">
-        <v>967</v>
-      </c>
-      <c r="F321" t="s">
-        <v>968</v>
       </c>
       <c r="G321">
         <v>25</v>
       </c>
       <c r="H321" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="I321">
         <v>0</v>
@@ -48641,22 +48635,22 @@
         <v>0</v>
       </c>
       <c r="C322" t="s">
+        <v>963</v>
+      </c>
+      <c r="D322" t="s">
+        <v>968</v>
+      </c>
+      <c r="E322" t="s">
         <v>965</v>
       </c>
-      <c r="D322" t="s">
-        <v>970</v>
-      </c>
-      <c r="E322" t="s">
-        <v>967</v>
-      </c>
       <c r="F322" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="G322">
         <v>20</v>
       </c>
       <c r="H322" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="I322">
         <v>0</v>
@@ -48698,22 +48692,22 @@
         <v>0</v>
       </c>
       <c r="C323" t="s">
+        <v>963</v>
+      </c>
+      <c r="D323" t="s">
+        <v>970</v>
+      </c>
+      <c r="E323" t="s">
         <v>965</v>
       </c>
-      <c r="D323" t="s">
-        <v>972</v>
-      </c>
-      <c r="E323" t="s">
-        <v>967</v>
-      </c>
       <c r="F323" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="G323">
         <v>25</v>
       </c>
       <c r="H323" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="I323">
         <v>0</v>
@@ -48755,22 +48749,22 @@
         <v>0</v>
       </c>
       <c r="C324" t="s">
+        <v>963</v>
+      </c>
+      <c r="D324" t="s">
+        <v>972</v>
+      </c>
+      <c r="E324" t="s">
         <v>965</v>
       </c>
-      <c r="D324" t="s">
-        <v>974</v>
-      </c>
-      <c r="E324" t="s">
-        <v>967</v>
-      </c>
       <c r="F324" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="G324">
         <v>20</v>
       </c>
       <c r="H324" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="I324">
         <v>0</v>
@@ -48812,22 +48806,22 @@
         <v>0</v>
       </c>
       <c r="C325" t="s">
+        <v>963</v>
+      </c>
+      <c r="D325" t="s">
+        <v>974</v>
+      </c>
+      <c r="E325" t="s">
         <v>965</v>
       </c>
-      <c r="D325" t="s">
-        <v>976</v>
-      </c>
-      <c r="E325" t="s">
-        <v>967</v>
-      </c>
       <c r="F325" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="G325">
         <v>0.4</v>
       </c>
       <c r="H325" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="I325">
         <v>0</v>
@@ -48869,22 +48863,22 @@
         <v>0</v>
       </c>
       <c r="C326" t="s">
+        <v>963</v>
+      </c>
+      <c r="D326" t="s">
+        <v>976</v>
+      </c>
+      <c r="E326" t="s">
         <v>965</v>
       </c>
-      <c r="D326" t="s">
-        <v>978</v>
-      </c>
-      <c r="E326" t="s">
-        <v>967</v>
-      </c>
       <c r="F326" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="G326">
         <v>3</v>
       </c>
       <c r="H326" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="I326">
         <v>0</v>
@@ -48926,22 +48920,22 @@
         <v>0</v>
       </c>
       <c r="C327" t="s">
+        <v>963</v>
+      </c>
+      <c r="D327" t="s">
+        <v>978</v>
+      </c>
+      <c r="E327" t="s">
         <v>965</v>
       </c>
-      <c r="D327" t="s">
-        <v>980</v>
-      </c>
-      <c r="E327" t="s">
-        <v>967</v>
-      </c>
       <c r="F327" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="G327">
         <v>1.5</v>
       </c>
       <c r="H327" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="I327">
         <v>0</v>
@@ -48983,22 +48977,22 @@
         <v>0</v>
       </c>
       <c r="C328" t="s">
+        <v>963</v>
+      </c>
+      <c r="D328" t="s">
+        <v>980</v>
+      </c>
+      <c r="E328" t="s">
         <v>965</v>
       </c>
-      <c r="D328" t="s">
-        <v>982</v>
-      </c>
-      <c r="E328" t="s">
-        <v>967</v>
-      </c>
       <c r="F328" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="G328">
         <v>0.15</v>
       </c>
       <c r="H328" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="I328">
         <v>0</v>
@@ -49040,22 +49034,22 @@
         <v>0</v>
       </c>
       <c r="C329" t="s">
+        <v>963</v>
+      </c>
+      <c r="D329" t="s">
+        <v>982</v>
+      </c>
+      <c r="E329" t="s">
         <v>965</v>
       </c>
-      <c r="D329" t="s">
-        <v>984</v>
-      </c>
-      <c r="E329" t="s">
-        <v>967</v>
-      </c>
       <c r="F329" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="G329">
         <v>0.5</v>
       </c>
       <c r="H329" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="I329">
         <v>0</v>
@@ -49097,22 +49091,22 @@
         <v>0</v>
       </c>
       <c r="C330" t="s">
+        <v>963</v>
+      </c>
+      <c r="D330" t="s">
+        <v>984</v>
+      </c>
+      <c r="E330" t="s">
         <v>965</v>
       </c>
-      <c r="D330" t="s">
-        <v>986</v>
-      </c>
-      <c r="E330" t="s">
-        <v>967</v>
-      </c>
       <c r="F330" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="G330">
         <v>25</v>
       </c>
       <c r="H330" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="I330">
         <v>0</v>
@@ -49154,22 +49148,22 @@
         <v>0</v>
       </c>
       <c r="C331" t="s">
+        <v>963</v>
+      </c>
+      <c r="D331" t="s">
+        <v>986</v>
+      </c>
+      <c r="E331" t="s">
         <v>965</v>
       </c>
-      <c r="D331" t="s">
-        <v>988</v>
-      </c>
-      <c r="E331" t="s">
-        <v>967</v>
-      </c>
       <c r="F331" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="G331">
         <v>8</v>
       </c>
       <c r="H331" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="I331">
         <v>0</v>
@@ -49211,22 +49205,22 @@
         <v>0</v>
       </c>
       <c r="C332" t="s">
+        <v>963</v>
+      </c>
+      <c r="D332" t="s">
+        <v>989</v>
+      </c>
+      <c r="E332" t="s">
         <v>965</v>
       </c>
-      <c r="D332" t="s">
-        <v>991</v>
-      </c>
-      <c r="E332" t="s">
-        <v>967</v>
-      </c>
       <c r="F332" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="G332">
         <v>15</v>
       </c>
       <c r="H332" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="I332">
         <v>0</v>
@@ -49268,16 +49262,16 @@
         <v>0</v>
       </c>
       <c r="C333" t="s">
+        <v>991</v>
+      </c>
+      <c r="D333" t="s">
+        <v>992</v>
+      </c>
+      <c r="E333" t="s">
         <v>993</v>
       </c>
-      <c r="D333" t="s">
+      <c r="F333" t="s">
         <v>994</v>
-      </c>
-      <c r="E333" t="s">
-        <v>995</v>
-      </c>
-      <c r="F333" t="s">
-        <v>996</v>
       </c>
       <c r="G333">
         <v>0.8</v>
@@ -49325,16 +49319,16 @@
         <v>0</v>
       </c>
       <c r="C334" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="D334" t="s">
+        <v>995</v>
+      </c>
+      <c r="E334" t="s">
+        <v>996</v>
+      </c>
+      <c r="F334" t="s">
         <v>997</v>
-      </c>
-      <c r="E334" t="s">
-        <v>998</v>
-      </c>
-      <c r="F334" t="s">
-        <v>999</v>
       </c>
       <c r="G334">
         <v>3</v>
@@ -49382,16 +49376,16 @@
         <v>0</v>
       </c>
       <c r="C335" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="D335" t="s">
+        <v>998</v>
+      </c>
+      <c r="E335" t="s">
+        <v>999</v>
+      </c>
+      <c r="F335" t="s">
         <v>1000</v>
-      </c>
-      <c r="E335" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F335" t="s">
-        <v>1002</v>
       </c>
       <c r="G335">
         <v>7</v>
@@ -49439,16 +49433,16 @@
         <v>0</v>
       </c>
       <c r="C336" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="D336" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E336" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F336" t="s">
         <v>1003</v>
-      </c>
-      <c r="E336" t="s">
-        <v>1004</v>
-      </c>
-      <c r="F336" t="s">
-        <v>1005</v>
       </c>
       <c r="G336">
         <v>10</v>
@@ -49496,16 +49490,16 @@
         <v>0</v>
       </c>
       <c r="C337" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="D337" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E337" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F337" t="s">
         <v>1006</v>
-      </c>
-      <c r="E337" t="s">
-        <v>1007</v>
-      </c>
-      <c r="F337" t="s">
-        <v>1008</v>
       </c>
       <c r="G337">
         <v>2</v>
@@ -49553,16 +49547,16 @@
         <v>0</v>
       </c>
       <c r="C338" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="D338" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E338" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F338" t="s">
         <v>1009</v>
-      </c>
-      <c r="E338" t="s">
-        <v>1010</v>
-      </c>
-      <c r="F338" t="s">
-        <v>1011</v>
       </c>
       <c r="G338">
         <v>5</v>
@@ -49610,16 +49604,16 @@
         <v>0</v>
       </c>
       <c r="C339" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="D339" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E339" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F339" t="s">
         <v>1012</v>
-      </c>
-      <c r="E339" t="s">
-        <v>1013</v>
-      </c>
-      <c r="F339" t="s">
-        <v>1014</v>
       </c>
       <c r="G339">
         <v>10</v>
@@ -49667,16 +49661,16 @@
         <v>0</v>
       </c>
       <c r="C340" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D340" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="E340" t="s">
         <v>39</v>
       </c>
       <c r="F340" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="G340">
         <v>15.3</v>
@@ -49724,16 +49718,16 @@
         <v>0</v>
       </c>
       <c r="C341" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D341" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="E341" t="s">
         <v>39</v>
       </c>
       <c r="F341" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="G341">
         <v>22.95</v>
@@ -49781,16 +49775,16 @@
         <v>0</v>
       </c>
       <c r="C342" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D342" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E342" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F342" t="s">
         <v>1018</v>
-      </c>
-      <c r="E342" t="s">
-        <v>1019</v>
-      </c>
-      <c r="F342" t="s">
-        <v>1020</v>
       </c>
       <c r="G342">
         <v>20</v>
@@ -49838,16 +49832,16 @@
         <v>0</v>
       </c>
       <c r="C343" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D343" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E343" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F343" t="s">
         <v>1021</v>
-      </c>
-      <c r="E343" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F343" t="s">
-        <v>1023</v>
       </c>
       <c r="G343">
         <v>500000000</v>
@@ -49895,16 +49889,16 @@
         <v>0</v>
       </c>
       <c r="C344" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D344" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E344" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F344" t="s">
         <v>1024</v>
-      </c>
-      <c r="E344" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F344" t="s">
-        <v>1026</v>
       </c>
       <c r="G344">
         <v>13</v>
@@ -49955,13 +49949,13 @@
         <v>18</v>
       </c>
       <c r="D345" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>1084</v>
+        <v>1068</v>
       </c>
       <c r="F345" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="G345">
         <v>30</v>
@@ -50012,13 +50006,13 @@
         <v>18</v>
       </c>
       <c r="D346" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E346" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F346" t="s">
         <v>1029</v>
-      </c>
-      <c r="E346" t="s">
-        <v>1030</v>
-      </c>
-      <c r="F346" t="s">
-        <v>1031</v>
       </c>
       <c r="G346">
         <v>1000</v>
@@ -50066,16 +50060,16 @@
         <v>0</v>
       </c>
       <c r="C347" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D347" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E347" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F347" t="s">
         <v>1032</v>
-      </c>
-      <c r="E347" t="s">
-        <v>1033</v>
-      </c>
-      <c r="F347" t="s">
-        <v>1034</v>
       </c>
       <c r="G347">
         <v>50000</v>
@@ -50123,16 +50117,16 @@
         <v>0</v>
       </c>
       <c r="C348" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D348" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E348" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F348" t="s">
         <v>1035</v>
-      </c>
-      <c r="E348" t="s">
-        <v>1036</v>
-      </c>
-      <c r="F348" t="s">
-        <v>1037</v>
       </c>
       <c r="G348">
         <v>10</v>
@@ -50180,16 +50174,16 @@
         <v>0</v>
       </c>
       <c r="C349" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D349" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E349" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F349" t="s">
         <v>1038</v>
-      </c>
-      <c r="E349" t="s">
-        <v>1039</v>
-      </c>
-      <c r="F349" t="s">
-        <v>1040</v>
       </c>
       <c r="G349">
         <v>75</v>
@@ -50237,16 +50231,16 @@
         <v>0</v>
       </c>
       <c r="C350" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D350" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E350" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F350" t="s">
         <v>1041</v>
-      </c>
-      <c r="E350" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F350" t="s">
-        <v>1043</v>
       </c>
       <c r="G350">
         <v>25</v>
@@ -50294,16 +50288,16 @@
         <v>0</v>
       </c>
       <c r="C351" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D351" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="E351" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="F351" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="G351">
         <v>5</v>
@@ -50351,16 +50345,16 @@
         <v>0</v>
       </c>
       <c r="C352" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="D352" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E352" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F352" t="s">
         <v>1046</v>
-      </c>
-      <c r="E352" t="s">
-        <v>1047</v>
-      </c>
-      <c r="F352" t="s">
-        <v>1048</v>
       </c>
       <c r="G352">
         <v>0.6</v>
@@ -50408,16 +50402,16 @@
         <v>0</v>
       </c>
       <c r="C353" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D353" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E353" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F353" t="s">
         <v>1049</v>
-      </c>
-      <c r="E353" t="s">
-        <v>1050</v>
-      </c>
-      <c r="F353" t="s">
-        <v>1051</v>
       </c>
       <c r="G353">
         <v>0.1</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\claude\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349465B2-46D8-49D0-A706-BE4EB9DA3184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DAABF8-E1EA-4E4E-8CA7-69DC9BCBAC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1363,12 +1363,6 @@
   </si>
   <si>
     <t>{1~49=0}</t>
-  </si>
-  <si>
-    <t>{100~149=10}</t>
-  </si>
-  <si>
-    <t>{150~199=10}</t>
   </si>
   <si>
     <t>{200~249=15}</t>
@@ -3693,14 +3687,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{1~19=0}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{20~99=5}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>{20~99=15}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3778,6 +3764,22 @@
   </si>
   <si>
     <t>野外整波敵人清空時回復一次（吸魂被動仍為擊殺時觸發）。高塔沒有此回復。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{20~99=10}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{150~199=15}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{100~149=10}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{1~19=7}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4440,7 +4442,7 @@
       </c>
       <c r="G4">
         <f>計算表!G4</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4">
         <f>計算表!H4</f>
@@ -6438,11 +6440,11 @@
       </c>
       <c r="G31">
         <f>計算表!G31</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H31">
         <f>計算表!H31</f>
-        <v>2E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="I31">
         <f>計算表!I31</f>
@@ -15540,11 +15542,11 @@
       </c>
       <c r="G154" t="str">
         <f>計算表!G154</f>
-        <v>{1~19=0}</v>
+        <v>{1~19=7}</v>
       </c>
       <c r="H154" t="str">
         <f>計算表!H154</f>
-        <v>{20~99=5}</v>
+        <v>{20~99=10}</v>
       </c>
       <c r="I154" t="str">
         <f>計算表!I154</f>
@@ -15552,7 +15554,7 @@
       </c>
       <c r="J154" t="str">
         <f>計算表!J154</f>
-        <v>{150~199=10}</v>
+        <v>{150~199=15}</v>
       </c>
       <c r="K154" t="str">
         <f>計算表!K154</f>
@@ -30328,7 +30330,7 @@
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="36.28515625" customWidth="1"/>
     <col min="6" max="6" width="35.5703125" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" customWidth="1"/>
+    <col min="7" max="13" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -30521,7 +30523,7 @@
         <v>27</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -32060,10 +32062,10 @@
         <v>112</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H31">
-        <v>2E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -32738,10 +32740,10 @@
         <v>145</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="G43">
         <v>2</v>
@@ -34502,13 +34504,13 @@
         <v>191</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="E74" t="s">
         <v>216</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="G74">
         <v>12</v>
@@ -36206,13 +36208,13 @@
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C104" t="s">
         <v>291</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="E104" t="s">
         <v>293</v>
@@ -36221,7 +36223,7 @@
         <v>294</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="H104" t="s">
         <v>310</v>
@@ -36263,13 +36265,13 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C105" t="s">
         <v>291</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="E105" t="s">
         <v>293</v>
@@ -36278,13 +36280,13 @@
         <v>294</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>310</v>
       </c>
       <c r="I105" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -36320,13 +36322,13 @@
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C106" t="s">
         <v>291</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="E106" t="s">
         <v>293</v>
@@ -36335,16 +36337,16 @@
         <v>294</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="J106" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="K106">
         <v>0</v>
@@ -36377,13 +36379,13 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C107" t="s">
         <v>291</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="E107" t="s">
         <v>293</v>
@@ -36392,16 +36394,16 @@
         <v>294</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="K107">
         <v>0</v>
@@ -36434,13 +36436,13 @@
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C108" t="s">
         <v>291</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E108" t="s">
         <v>293</v>
@@ -36449,19 +36451,19 @@
         <v>294</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>297</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="L108">
         <v>0</v>
@@ -38900,10 +38902,10 @@
         <v>424</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="I151" t="s">
         <v>425</v>
@@ -38957,10 +38959,10 @@
         <v>424</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="I152" t="s">
         <v>431</v>
@@ -39014,13 +39016,13 @@
         <v>424</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="I153" s="2" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="J153" t="s">
         <v>437</v>
@@ -39071,25 +39073,25 @@
         <v>424</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>1065</v>
+        <v>1085</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>1066</v>
-      </c>
-      <c r="I154" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="J154" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="K154" t="s">
         <v>443</v>
       </c>
-      <c r="J154" t="s">
+      <c r="L154" t="s">
         <v>444</v>
       </c>
-      <c r="K154" t="s">
+      <c r="M154" t="s">
         <v>445</v>
-      </c>
-      <c r="L154" t="s">
-        <v>446</v>
-      </c>
-      <c r="M154" t="s">
-        <v>447</v>
       </c>
       <c r="N154">
         <v>0</v>
@@ -39119,7 +39121,7 @@
         <v>421</v>
       </c>
       <c r="D155" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E155" t="s">
         <v>423</v>
@@ -39131,22 +39133,22 @@
         <v>442</v>
       </c>
       <c r="H155" t="s">
+        <v>447</v>
+      </c>
+      <c r="I155" t="s">
+        <v>448</v>
+      </c>
+      <c r="J155" t="s">
         <v>449</v>
       </c>
-      <c r="I155" t="s">
+      <c r="K155" t="s">
         <v>450</v>
       </c>
-      <c r="J155" t="s">
+      <c r="L155" t="s">
         <v>451</v>
       </c>
-      <c r="K155" t="s">
+      <c r="M155" t="s">
         <v>452</v>
-      </c>
-      <c r="L155" t="s">
-        <v>453</v>
-      </c>
-      <c r="M155" t="s">
-        <v>454</v>
       </c>
       <c r="N155">
         <v>0</v>
@@ -39176,7 +39178,7 @@
         <v>421</v>
       </c>
       <c r="D156" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E156" t="s">
         <v>423</v>
@@ -39188,22 +39190,22 @@
         <v>442</v>
       </c>
       <c r="H156" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="I156" t="s">
         <v>266</v>
       </c>
       <c r="J156" t="s">
+        <v>455</v>
+      </c>
+      <c r="K156" t="s">
+        <v>456</v>
+      </c>
+      <c r="L156" t="s">
         <v>457</v>
       </c>
-      <c r="K156" t="s">
+      <c r="M156" t="s">
         <v>458</v>
-      </c>
-      <c r="L156" t="s">
-        <v>459</v>
-      </c>
-      <c r="M156" t="s">
-        <v>460</v>
       </c>
       <c r="N156">
         <v>0</v>
@@ -39233,7 +39235,7 @@
         <v>421</v>
       </c>
       <c r="D157" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E157" t="s">
         <v>423</v>
@@ -39245,22 +39247,22 @@
         <v>442</v>
       </c>
       <c r="H157" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="I157" t="s">
+        <v>460</v>
+      </c>
+      <c r="J157" t="s">
+        <v>461</v>
+      </c>
+      <c r="K157" t="s">
         <v>462</v>
       </c>
-      <c r="J157" t="s">
+      <c r="L157" t="s">
         <v>463</v>
       </c>
-      <c r="K157" t="s">
+      <c r="M157" t="s">
         <v>464</v>
-      </c>
-      <c r="L157" t="s">
-        <v>465</v>
-      </c>
-      <c r="M157" t="s">
-        <v>466</v>
       </c>
       <c r="N157">
         <v>0</v>
@@ -39290,7 +39292,7 @@
         <v>421</v>
       </c>
       <c r="D158" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E158" t="s">
         <v>423</v>
@@ -39302,22 +39304,22 @@
         <v>442</v>
       </c>
       <c r="H158" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="I158" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="J158" t="s">
+        <v>466</v>
+      </c>
+      <c r="K158" t="s">
+        <v>467</v>
+      </c>
+      <c r="L158" t="s">
         <v>468</v>
       </c>
-      <c r="K158" t="s">
+      <c r="M158" t="s">
         <v>469</v>
-      </c>
-      <c r="L158" t="s">
-        <v>470</v>
-      </c>
-      <c r="M158" t="s">
-        <v>471</v>
       </c>
       <c r="N158">
         <v>0</v>
@@ -39347,13 +39349,13 @@
         <v>421</v>
       </c>
       <c r="D159" t="s">
+        <v>470</v>
+      </c>
+      <c r="E159" t="s">
+        <v>471</v>
+      </c>
+      <c r="F159" t="s">
         <v>472</v>
-      </c>
-      <c r="E159" t="s">
-        <v>473</v>
-      </c>
-      <c r="F159" t="s">
-        <v>474</v>
       </c>
       <c r="G159">
         <v>551</v>
@@ -39401,16 +39403,16 @@
         <v>0</v>
       </c>
       <c r="C160" t="s">
+        <v>473</v>
+      </c>
+      <c r="D160" t="s">
+        <v>474</v>
+      </c>
+      <c r="E160" t="s">
         <v>475</v>
       </c>
-      <c r="D160" t="s">
+      <c r="F160" t="s">
         <v>476</v>
-      </c>
-      <c r="E160" t="s">
-        <v>477</v>
-      </c>
-      <c r="F160" t="s">
-        <v>478</v>
       </c>
       <c r="G160">
         <v>2</v>
@@ -39458,16 +39460,16 @@
         <v>0</v>
       </c>
       <c r="C161" t="s">
+        <v>473</v>
+      </c>
+      <c r="D161" t="s">
+        <v>477</v>
+      </c>
+      <c r="E161" t="s">
         <v>475</v>
       </c>
-      <c r="D161" t="s">
-        <v>479</v>
-      </c>
-      <c r="E161" t="s">
-        <v>477</v>
-      </c>
       <c r="F161" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G161">
         <v>4</v>
@@ -39515,16 +39517,16 @@
         <v>0</v>
       </c>
       <c r="C162" t="s">
+        <v>473</v>
+      </c>
+      <c r="D162" t="s">
+        <v>478</v>
+      </c>
+      <c r="E162" t="s">
         <v>475</v>
       </c>
-      <c r="D162" t="s">
-        <v>480</v>
-      </c>
-      <c r="E162" t="s">
-        <v>477</v>
-      </c>
       <c r="F162" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G162">
         <v>6</v>
@@ -39572,16 +39574,16 @@
         <v>0</v>
       </c>
       <c r="C163" t="s">
+        <v>473</v>
+      </c>
+      <c r="D163" t="s">
+        <v>479</v>
+      </c>
+      <c r="E163" t="s">
         <v>475</v>
       </c>
-      <c r="D163" t="s">
-        <v>481</v>
-      </c>
-      <c r="E163" t="s">
-        <v>477</v>
-      </c>
       <c r="F163" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G163">
         <v>8</v>
@@ -39629,16 +39631,16 @@
         <v>0</v>
       </c>
       <c r="C164" t="s">
+        <v>473</v>
+      </c>
+      <c r="D164" t="s">
+        <v>480</v>
+      </c>
+      <c r="E164" t="s">
         <v>475</v>
       </c>
-      <c r="D164" t="s">
-        <v>482</v>
-      </c>
-      <c r="E164" t="s">
-        <v>477</v>
-      </c>
       <c r="F164" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G164">
         <v>10</v>
@@ -39686,16 +39688,16 @@
         <v>0</v>
       </c>
       <c r="C165" t="s">
+        <v>473</v>
+      </c>
+      <c r="D165" t="s">
+        <v>481</v>
+      </c>
+      <c r="E165" t="s">
         <v>475</v>
       </c>
-      <c r="D165" t="s">
-        <v>483</v>
-      </c>
-      <c r="E165" t="s">
-        <v>477</v>
-      </c>
       <c r="F165" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G165">
         <v>12</v>
@@ -39743,16 +39745,16 @@
         <v>0</v>
       </c>
       <c r="C166" t="s">
+        <v>473</v>
+      </c>
+      <c r="D166" t="s">
+        <v>482</v>
+      </c>
+      <c r="E166" t="s">
         <v>475</v>
       </c>
-      <c r="D166" t="s">
-        <v>484</v>
-      </c>
-      <c r="E166" t="s">
-        <v>477</v>
-      </c>
       <c r="F166" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G166">
         <v>14</v>
@@ -39800,16 +39802,16 @@
         <v>0</v>
       </c>
       <c r="C167" t="s">
+        <v>483</v>
+      </c>
+      <c r="D167" t="s">
+        <v>484</v>
+      </c>
+      <c r="E167" t="s">
         <v>485</v>
       </c>
-      <c r="D167" t="s">
+      <c r="F167" t="s">
         <v>486</v>
-      </c>
-      <c r="E167" t="s">
-        <v>487</v>
-      </c>
-      <c r="F167" t="s">
-        <v>488</v>
       </c>
       <c r="G167">
         <v>4</v>
@@ -39857,16 +39859,16 @@
         <v>0</v>
       </c>
       <c r="C168" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D168" t="s">
+        <v>487</v>
+      </c>
+      <c r="E168" t="s">
+        <v>488</v>
+      </c>
+      <c r="F168" t="s">
         <v>489</v>
-      </c>
-      <c r="E168" t="s">
-        <v>490</v>
-      </c>
-      <c r="F168" t="s">
-        <v>491</v>
       </c>
       <c r="G168">
         <v>5</v>
@@ -39914,16 +39916,16 @@
         <v>0</v>
       </c>
       <c r="C169" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D169" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E169" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F169" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G169">
         <v>10</v>
@@ -39971,16 +39973,16 @@
         <v>0</v>
       </c>
       <c r="C170" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D170" t="s">
+        <v>492</v>
+      </c>
+      <c r="E170" t="s">
+        <v>493</v>
+      </c>
+      <c r="F170" t="s">
         <v>494</v>
-      </c>
-      <c r="E170" t="s">
-        <v>495</v>
-      </c>
-      <c r="F170" t="s">
-        <v>496</v>
       </c>
       <c r="G170">
         <v>0.5</v>
@@ -40028,16 +40030,16 @@
         <v>0</v>
       </c>
       <c r="C171" t="s">
+        <v>495</v>
+      </c>
+      <c r="D171" t="s">
+        <v>496</v>
+      </c>
+      <c r="E171" t="s">
         <v>497</v>
       </c>
-      <c r="D171" t="s">
+      <c r="F171" t="s">
         <v>498</v>
-      </c>
-      <c r="E171" t="s">
-        <v>499</v>
-      </c>
-      <c r="F171" t="s">
-        <v>500</v>
       </c>
       <c r="G171">
         <v>100</v>
@@ -40085,16 +40087,16 @@
         <v>0</v>
       </c>
       <c r="C172" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D172" t="s">
+        <v>499</v>
+      </c>
+      <c r="E172" t="s">
+        <v>500</v>
+      </c>
+      <c r="F172" t="s">
         <v>501</v>
-      </c>
-      <c r="E172" t="s">
-        <v>502</v>
-      </c>
-      <c r="F172" t="s">
-        <v>503</v>
       </c>
       <c r="G172">
         <v>92</v>
@@ -40142,16 +40144,16 @@
         <v>0</v>
       </c>
       <c r="C173" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D173" t="s">
+        <v>502</v>
+      </c>
+      <c r="E173" t="s">
+        <v>503</v>
+      </c>
+      <c r="F173" t="s">
         <v>504</v>
-      </c>
-      <c r="E173" t="s">
-        <v>505</v>
-      </c>
-      <c r="F173" t="s">
-        <v>506</v>
       </c>
       <c r="G173">
         <v>78.099999999999994</v>
@@ -40199,16 +40201,16 @@
         <v>0</v>
       </c>
       <c r="C174" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D174" t="s">
+        <v>505</v>
+      </c>
+      <c r="E174" t="s">
+        <v>506</v>
+      </c>
+      <c r="F174" t="s">
         <v>507</v>
-      </c>
-      <c r="E174" t="s">
-        <v>508</v>
-      </c>
-      <c r="F174" t="s">
-        <v>509</v>
       </c>
       <c r="G174">
         <v>72.11</v>
@@ -40256,16 +40258,16 @@
         <v>0</v>
       </c>
       <c r="C175" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D175" t="s">
+        <v>508</v>
+      </c>
+      <c r="E175" t="s">
+        <v>509</v>
+      </c>
+      <c r="F175" t="s">
         <v>510</v>
-      </c>
-      <c r="E175" t="s">
-        <v>511</v>
-      </c>
-      <c r="F175" t="s">
-        <v>512</v>
       </c>
       <c r="G175">
         <v>74.349999999999994</v>
@@ -40313,16 +40315,16 @@
         <v>0</v>
       </c>
       <c r="C176" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D176" t="s">
+        <v>511</v>
+      </c>
+      <c r="E176" t="s">
+        <v>512</v>
+      </c>
+      <c r="F176" t="s">
         <v>513</v>
-      </c>
-      <c r="E176" t="s">
-        <v>514</v>
-      </c>
-      <c r="F176" t="s">
-        <v>515</v>
       </c>
       <c r="G176">
         <v>76.87</v>
@@ -40370,16 +40372,16 @@
         <v>0</v>
       </c>
       <c r="C177" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D177" t="s">
+        <v>514</v>
+      </c>
+      <c r="E177" t="s">
+        <v>515</v>
+      </c>
+      <c r="F177" t="s">
         <v>516</v>
-      </c>
-      <c r="E177" t="s">
-        <v>517</v>
-      </c>
-      <c r="F177" t="s">
-        <v>518</v>
       </c>
       <c r="G177">
         <v>69.92</v>
@@ -40427,16 +40429,16 @@
         <v>0</v>
       </c>
       <c r="C178" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D178" t="s">
+        <v>517</v>
+      </c>
+      <c r="E178" t="s">
+        <v>518</v>
+      </c>
+      <c r="F178" t="s">
         <v>519</v>
-      </c>
-      <c r="E178" t="s">
-        <v>520</v>
-      </c>
-      <c r="F178" t="s">
-        <v>521</v>
       </c>
       <c r="G178">
         <v>64.22</v>
@@ -40484,16 +40486,16 @@
         <v>0</v>
       </c>
       <c r="C179" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D179" t="s">
+        <v>520</v>
+      </c>
+      <c r="E179" t="s">
+        <v>521</v>
+      </c>
+      <c r="F179" t="s">
         <v>522</v>
-      </c>
-      <c r="E179" t="s">
-        <v>523</v>
-      </c>
-      <c r="F179" t="s">
-        <v>524</v>
       </c>
       <c r="G179">
         <v>59.92</v>
@@ -40541,16 +40543,16 @@
         <v>0</v>
       </c>
       <c r="C180" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D180" t="s">
+        <v>523</v>
+      </c>
+      <c r="E180" t="s">
+        <v>524</v>
+      </c>
+      <c r="F180" t="s">
         <v>525</v>
-      </c>
-      <c r="E180" t="s">
-        <v>526</v>
-      </c>
-      <c r="F180" t="s">
-        <v>527</v>
       </c>
       <c r="G180">
         <v>54.72</v>
@@ -40598,16 +40600,16 @@
         <v>0</v>
       </c>
       <c r="C181" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D181" t="s">
+        <v>526</v>
+      </c>
+      <c r="E181" t="s">
+        <v>527</v>
+      </c>
+      <c r="F181" t="s">
         <v>528</v>
-      </c>
-      <c r="E181" t="s">
-        <v>529</v>
-      </c>
-      <c r="F181" t="s">
-        <v>530</v>
       </c>
       <c r="G181">
         <v>1.35</v>
@@ -40655,16 +40657,16 @@
         <v>0</v>
       </c>
       <c r="C182" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D182" t="s">
+        <v>529</v>
+      </c>
+      <c r="E182" t="s">
+        <v>530</v>
+      </c>
+      <c r="F182" t="s">
         <v>531</v>
-      </c>
-      <c r="E182" t="s">
-        <v>532</v>
-      </c>
-      <c r="F182" t="s">
-        <v>533</v>
       </c>
       <c r="G182">
         <v>0.5</v>
@@ -40712,16 +40714,16 @@
         <v>0</v>
       </c>
       <c r="C183" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D183" t="s">
+        <v>532</v>
+      </c>
+      <c r="E183" t="s">
+        <v>533</v>
+      </c>
+      <c r="F183" t="s">
         <v>534</v>
-      </c>
-      <c r="E183" t="s">
-        <v>535</v>
-      </c>
-      <c r="F183" t="s">
-        <v>536</v>
       </c>
       <c r="G183">
         <v>4000</v>
@@ -40769,16 +40771,16 @@
         <v>0</v>
       </c>
       <c r="C184" t="s">
+        <v>535</v>
+      </c>
+      <c r="D184" t="s">
+        <v>536</v>
+      </c>
+      <c r="E184" t="s">
         <v>537</v>
       </c>
-      <c r="D184" t="s">
+      <c r="F184" t="s">
         <v>538</v>
-      </c>
-      <c r="E184" t="s">
-        <v>539</v>
-      </c>
-      <c r="F184" t="s">
-        <v>540</v>
       </c>
       <c r="G184">
         <v>4</v>
@@ -40826,16 +40828,16 @@
         <v>0</v>
       </c>
       <c r="C185" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D185" t="s">
         <v>258</v>
       </c>
       <c r="E185" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="F185" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="G185">
         <v>200</v>
@@ -40883,16 +40885,16 @@
         <v>0</v>
       </c>
       <c r="C186" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D186" t="s">
+        <v>541</v>
+      </c>
+      <c r="E186" t="s">
+        <v>542</v>
+      </c>
+      <c r="F186" t="s">
         <v>543</v>
-      </c>
-      <c r="E186" t="s">
-        <v>544</v>
-      </c>
-      <c r="F186" t="s">
-        <v>545</v>
       </c>
       <c r="G186">
         <v>4</v>
@@ -40940,16 +40942,16 @@
         <v>0</v>
       </c>
       <c r="C187" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D187" t="s">
+        <v>544</v>
+      </c>
+      <c r="E187" t="s">
+        <v>545</v>
+      </c>
+      <c r="F187" t="s">
         <v>546</v>
-      </c>
-      <c r="E187" t="s">
-        <v>547</v>
-      </c>
-      <c r="F187" t="s">
-        <v>548</v>
       </c>
       <c r="G187">
         <v>3</v>
@@ -40997,16 +40999,16 @@
         <v>0</v>
       </c>
       <c r="C188" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D188" t="s">
+        <v>547</v>
+      </c>
+      <c r="E188" t="s">
+        <v>548</v>
+      </c>
+      <c r="F188" t="s">
         <v>549</v>
-      </c>
-      <c r="E188" t="s">
-        <v>550</v>
-      </c>
-      <c r="F188" t="s">
-        <v>551</v>
       </c>
       <c r="G188">
         <v>4</v>
@@ -41054,37 +41056,37 @@
         <v>0</v>
       </c>
       <c r="C189" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D189" t="s">
         <v>422</v>
       </c>
       <c r="E189" t="s">
+        <v>551</v>
+      </c>
+      <c r="F189" t="s">
+        <v>552</v>
+      </c>
+      <c r="G189" t="s">
         <v>553</v>
       </c>
-      <c r="F189" t="s">
+      <c r="H189" t="s">
         <v>554</v>
       </c>
-      <c r="G189" t="s">
+      <c r="I189" t="s">
         <v>555</v>
       </c>
-      <c r="H189" t="s">
+      <c r="J189" t="s">
         <v>556</v>
       </c>
-      <c r="I189" t="s">
+      <c r="K189" t="s">
         <v>557</v>
       </c>
-      <c r="J189" t="s">
+      <c r="L189" t="s">
         <v>558</v>
       </c>
-      <c r="K189" t="s">
+      <c r="M189" t="s">
         <v>559</v>
-      </c>
-      <c r="L189" t="s">
-        <v>560</v>
-      </c>
-      <c r="M189" t="s">
-        <v>561</v>
       </c>
       <c r="N189">
         <v>0</v>
@@ -41111,37 +41113,37 @@
         <v>0</v>
       </c>
       <c r="C190" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D190" t="s">
         <v>430</v>
       </c>
       <c r="E190" t="s">
+        <v>551</v>
+      </c>
+      <c r="F190" t="s">
+        <v>552</v>
+      </c>
+      <c r="G190" t="s">
         <v>553</v>
       </c>
-      <c r="F190" t="s">
+      <c r="H190" t="s">
         <v>554</v>
       </c>
-      <c r="G190" t="s">
+      <c r="I190" t="s">
         <v>555</v>
       </c>
-      <c r="H190" t="s">
+      <c r="J190" t="s">
         <v>556</v>
       </c>
-      <c r="I190" t="s">
+      <c r="K190" t="s">
         <v>557</v>
       </c>
-      <c r="J190" t="s">
+      <c r="L190" t="s">
         <v>558</v>
       </c>
-      <c r="K190" t="s">
+      <c r="M190" t="s">
         <v>559</v>
-      </c>
-      <c r="L190" t="s">
-        <v>560</v>
-      </c>
-      <c r="M190" t="s">
-        <v>561</v>
       </c>
       <c r="N190">
         <v>0</v>
@@ -41168,37 +41170,37 @@
         <v>0</v>
       </c>
       <c r="C191" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D191" t="s">
         <v>436</v>
       </c>
       <c r="E191" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="F191" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="G191" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H191" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="I191" t="s">
+        <v>555</v>
+      </c>
+      <c r="J191" t="s">
+        <v>556</v>
+      </c>
+      <c r="K191" t="s">
         <v>557</v>
       </c>
-      <c r="J191" t="s">
+      <c r="L191" t="s">
         <v>558</v>
       </c>
-      <c r="K191" t="s">
+      <c r="M191" t="s">
         <v>559</v>
-      </c>
-      <c r="L191" t="s">
-        <v>560</v>
-      </c>
-      <c r="M191" t="s">
-        <v>561</v>
       </c>
       <c r="N191">
         <v>0</v>
@@ -41225,37 +41227,37 @@
         <v>0</v>
       </c>
       <c r="C192" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D192" t="s">
         <v>441</v>
       </c>
       <c r="E192" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="F192" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="G192" t="s">
+        <v>562</v>
+      </c>
+      <c r="H192" t="s">
+        <v>561</v>
+      </c>
+      <c r="I192" t="s">
+        <v>563</v>
+      </c>
+      <c r="J192" t="s">
         <v>564</v>
       </c>
-      <c r="H192" t="s">
-        <v>563</v>
-      </c>
-      <c r="I192" t="s">
+      <c r="K192" t="s">
         <v>565</v>
       </c>
-      <c r="J192" t="s">
+      <c r="L192" t="s">
         <v>566</v>
       </c>
-      <c r="K192" t="s">
+      <c r="M192" t="s">
         <v>567</v>
-      </c>
-      <c r="L192" t="s">
-        <v>568</v>
-      </c>
-      <c r="M192" t="s">
-        <v>569</v>
       </c>
       <c r="N192">
         <v>0</v>
@@ -41282,37 +41284,37 @@
         <v>0</v>
       </c>
       <c r="C193" t="s">
+        <v>550</v>
+      </c>
+      <c r="D193" t="s">
+        <v>446</v>
+      </c>
+      <c r="E193" t="s">
+        <v>551</v>
+      </c>
+      <c r="F193" t="s">
         <v>552</v>
       </c>
-      <c r="D193" t="s">
-        <v>448</v>
-      </c>
-      <c r="E193" t="s">
-        <v>553</v>
-      </c>
-      <c r="F193" t="s">
-        <v>554</v>
-      </c>
       <c r="G193" t="s">
+        <v>568</v>
+      </c>
+      <c r="H193" t="s">
+        <v>569</v>
+      </c>
+      <c r="I193" t="s">
+        <v>563</v>
+      </c>
+      <c r="J193" t="s">
         <v>570</v>
       </c>
-      <c r="H193" t="s">
+      <c r="K193" t="s">
         <v>571</v>
       </c>
-      <c r="I193" t="s">
-        <v>565</v>
-      </c>
-      <c r="J193" t="s">
+      <c r="L193" t="s">
         <v>572</v>
       </c>
-      <c r="K193" t="s">
+      <c r="M193" t="s">
         <v>573</v>
-      </c>
-      <c r="L193" t="s">
-        <v>574</v>
-      </c>
-      <c r="M193" t="s">
-        <v>575</v>
       </c>
       <c r="N193">
         <v>0</v>
@@ -41339,37 +41341,37 @@
         <v>0</v>
       </c>
       <c r="C194" t="s">
+        <v>550</v>
+      </c>
+      <c r="D194" t="s">
+        <v>453</v>
+      </c>
+      <c r="E194" t="s">
+        <v>551</v>
+      </c>
+      <c r="F194" t="s">
         <v>552</v>
       </c>
-      <c r="D194" t="s">
-        <v>455</v>
-      </c>
-      <c r="E194" t="s">
-        <v>553</v>
-      </c>
-      <c r="F194" t="s">
-        <v>554</v>
-      </c>
       <c r="G194" t="s">
+        <v>574</v>
+      </c>
+      <c r="H194" t="s">
+        <v>575</v>
+      </c>
+      <c r="I194" t="s">
         <v>576</v>
       </c>
-      <c r="H194" t="s">
+      <c r="J194" t="s">
         <v>577</v>
       </c>
-      <c r="I194" t="s">
+      <c r="K194" t="s">
         <v>578</v>
       </c>
-      <c r="J194" t="s">
+      <c r="L194" t="s">
         <v>579</v>
       </c>
-      <c r="K194" t="s">
+      <c r="M194" t="s">
         <v>580</v>
-      </c>
-      <c r="L194" t="s">
-        <v>581</v>
-      </c>
-      <c r="M194" t="s">
-        <v>582</v>
       </c>
       <c r="N194">
         <v>0</v>
@@ -41396,37 +41398,37 @@
         <v>0</v>
       </c>
       <c r="C195" t="s">
+        <v>550</v>
+      </c>
+      <c r="D195" t="s">
+        <v>459</v>
+      </c>
+      <c r="E195" t="s">
+        <v>551</v>
+      </c>
+      <c r="F195" t="s">
         <v>552</v>
       </c>
-      <c r="D195" t="s">
-        <v>461</v>
-      </c>
-      <c r="E195" t="s">
+      <c r="G195" t="s">
         <v>553</v>
       </c>
-      <c r="F195" t="s">
-        <v>554</v>
-      </c>
-      <c r="G195" t="s">
-        <v>555</v>
-      </c>
       <c r="H195" t="s">
+        <v>581</v>
+      </c>
+      <c r="I195" t="s">
+        <v>582</v>
+      </c>
+      <c r="J195" t="s">
         <v>583</v>
       </c>
-      <c r="I195" t="s">
+      <c r="K195" t="s">
         <v>584</v>
       </c>
-      <c r="J195" t="s">
+      <c r="L195" t="s">
         <v>585</v>
       </c>
-      <c r="K195" t="s">
+      <c r="M195" t="s">
         <v>586</v>
-      </c>
-      <c r="L195" t="s">
-        <v>587</v>
-      </c>
-      <c r="M195" t="s">
-        <v>588</v>
       </c>
       <c r="N195">
         <v>0</v>
@@ -41453,37 +41455,37 @@
         <v>0</v>
       </c>
       <c r="C196" t="s">
+        <v>550</v>
+      </c>
+      <c r="D196" t="s">
+        <v>465</v>
+      </c>
+      <c r="E196" t="s">
+        <v>551</v>
+      </c>
+      <c r="F196" t="s">
         <v>552</v>
       </c>
-      <c r="D196" t="s">
-        <v>467</v>
-      </c>
-      <c r="E196" t="s">
+      <c r="G196" t="s">
         <v>553</v>
       </c>
-      <c r="F196" t="s">
+      <c r="H196" t="s">
         <v>554</v>
       </c>
-      <c r="G196" t="s">
-        <v>555</v>
-      </c>
-      <c r="H196" t="s">
-        <v>556</v>
-      </c>
       <c r="I196" t="s">
+        <v>587</v>
+      </c>
+      <c r="J196" t="s">
+        <v>588</v>
+      </c>
+      <c r="K196" t="s">
         <v>589</v>
       </c>
-      <c r="J196" t="s">
+      <c r="L196" t="s">
         <v>590</v>
       </c>
-      <c r="K196" t="s">
+      <c r="M196" t="s">
         <v>591</v>
-      </c>
-      <c r="L196" t="s">
-        <v>592</v>
-      </c>
-      <c r="M196" t="s">
-        <v>593</v>
       </c>
       <c r="N196">
         <v>0</v>
@@ -41510,16 +41512,16 @@
         <v>0</v>
       </c>
       <c r="C197" t="s">
+        <v>592</v>
+      </c>
+      <c r="D197" t="s">
+        <v>593</v>
+      </c>
+      <c r="E197" t="s">
         <v>594</v>
       </c>
-      <c r="D197" t="s">
+      <c r="F197" t="s">
         <v>595</v>
-      </c>
-      <c r="E197" t="s">
-        <v>596</v>
-      </c>
-      <c r="F197" t="s">
-        <v>597</v>
       </c>
       <c r="G197">
         <v>0</v>
@@ -41567,16 +41569,16 @@
         <v>0</v>
       </c>
       <c r="C198" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D198" t="s">
+        <v>596</v>
+      </c>
+      <c r="E198" t="s">
+        <v>597</v>
+      </c>
+      <c r="F198" t="s">
         <v>598</v>
-      </c>
-      <c r="E198" t="s">
-        <v>599</v>
-      </c>
-      <c r="F198" t="s">
-        <v>600</v>
       </c>
       <c r="G198">
         <v>1.35</v>
@@ -41624,16 +41626,16 @@
         <v>0</v>
       </c>
       <c r="C199" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D199" t="s">
+        <v>599</v>
+      </c>
+      <c r="E199" t="s">
+        <v>600</v>
+      </c>
+      <c r="F199" t="s">
         <v>601</v>
-      </c>
-      <c r="E199" t="s">
-        <v>602</v>
-      </c>
-      <c r="F199" t="s">
-        <v>603</v>
       </c>
       <c r="G199">
         <v>0.05</v>
@@ -41681,16 +41683,16 @@
         <v>0</v>
       </c>
       <c r="C200" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D200" t="s">
+        <v>602</v>
+      </c>
+      <c r="E200" t="s">
+        <v>603</v>
+      </c>
+      <c r="F200" t="s">
         <v>604</v>
-      </c>
-      <c r="E200" t="s">
-        <v>605</v>
-      </c>
-      <c r="F200" t="s">
-        <v>606</v>
       </c>
       <c r="G200">
         <v>2</v>
@@ -41738,16 +41740,16 @@
         <v>0</v>
       </c>
       <c r="C201" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D201" t="s">
+        <v>605</v>
+      </c>
+      <c r="E201" t="s">
+        <v>606</v>
+      </c>
+      <c r="F201" t="s">
         <v>607</v>
-      </c>
-      <c r="E201" t="s">
-        <v>608</v>
-      </c>
-      <c r="F201" t="s">
-        <v>609</v>
       </c>
       <c r="G201">
         <v>0</v>
@@ -41795,16 +41797,16 @@
         <v>0</v>
       </c>
       <c r="C202" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D202" t="s">
+        <v>608</v>
+      </c>
+      <c r="E202" t="s">
+        <v>609</v>
+      </c>
+      <c r="F202" t="s">
         <v>610</v>
-      </c>
-      <c r="E202" t="s">
-        <v>611</v>
-      </c>
-      <c r="F202" t="s">
-        <v>612</v>
       </c>
       <c r="G202">
         <v>5</v>
@@ -41852,16 +41854,16 @@
         <v>0</v>
       </c>
       <c r="C203" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D203" t="s">
+        <v>611</v>
+      </c>
+      <c r="E203" t="s">
+        <v>612</v>
+      </c>
+      <c r="F203" t="s">
         <v>613</v>
-      </c>
-      <c r="E203" t="s">
-        <v>614</v>
-      </c>
-      <c r="F203" t="s">
-        <v>615</v>
       </c>
       <c r="G203">
         <v>8</v>
@@ -41909,16 +41911,16 @@
         <v>0</v>
       </c>
       <c r="C204" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D204" t="s">
+        <v>614</v>
+      </c>
+      <c r="E204" t="s">
+        <v>615</v>
+      </c>
+      <c r="F204" t="s">
         <v>616</v>
-      </c>
-      <c r="E204" t="s">
-        <v>617</v>
-      </c>
-      <c r="F204" t="s">
-        <v>618</v>
       </c>
       <c r="G204">
         <v>1</v>
@@ -41966,16 +41968,16 @@
         <v>0</v>
       </c>
       <c r="C205" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D205" t="s">
+        <v>617</v>
+      </c>
+      <c r="E205" t="s">
+        <v>618</v>
+      </c>
+      <c r="F205" t="s">
         <v>619</v>
-      </c>
-      <c r="E205" t="s">
-        <v>620</v>
-      </c>
-      <c r="F205" t="s">
-        <v>621</v>
       </c>
       <c r="G205">
         <v>0.15</v>
@@ -42023,16 +42025,16 @@
         <v>0</v>
       </c>
       <c r="C206" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D206" t="s">
+        <v>620</v>
+      </c>
+      <c r="E206" t="s">
+        <v>621</v>
+      </c>
+      <c r="F206" t="s">
         <v>622</v>
-      </c>
-      <c r="E206" t="s">
-        <v>623</v>
-      </c>
-      <c r="F206" t="s">
-        <v>624</v>
       </c>
       <c r="G206">
         <v>2</v>
@@ -42080,16 +42082,16 @@
         <v>0</v>
       </c>
       <c r="C207" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D207" t="s">
+        <v>623</v>
+      </c>
+      <c r="E207" t="s">
+        <v>624</v>
+      </c>
+      <c r="F207" t="s">
         <v>625</v>
-      </c>
-      <c r="E207" t="s">
-        <v>626</v>
-      </c>
-      <c r="F207" t="s">
-        <v>627</v>
       </c>
       <c r="G207">
         <v>3</v>
@@ -42137,16 +42139,16 @@
         <v>0</v>
       </c>
       <c r="C208" t="s">
+        <v>626</v>
+      </c>
+      <c r="D208" t="s">
+        <v>627</v>
+      </c>
+      <c r="E208" t="s">
         <v>628</v>
       </c>
-      <c r="D208" t="s">
+      <c r="F208" t="s">
         <v>629</v>
-      </c>
-      <c r="E208" t="s">
-        <v>630</v>
-      </c>
-      <c r="F208" t="s">
-        <v>631</v>
       </c>
       <c r="G208">
         <v>5</v>
@@ -42194,16 +42196,16 @@
         <v>0</v>
       </c>
       <c r="C209" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D209" t="s">
+        <v>630</v>
+      </c>
+      <c r="E209" t="s">
+        <v>631</v>
+      </c>
+      <c r="F209" t="s">
         <v>632</v>
-      </c>
-      <c r="E209" t="s">
-        <v>633</v>
-      </c>
-      <c r="F209" t="s">
-        <v>634</v>
       </c>
       <c r="G209">
         <v>0</v>
@@ -42251,16 +42253,16 @@
         <v>0</v>
       </c>
       <c r="C210" t="s">
+        <v>633</v>
+      </c>
+      <c r="D210" t="s">
+        <v>634</v>
+      </c>
+      <c r="E210" t="s">
         <v>635</v>
       </c>
-      <c r="D210" t="s">
+      <c r="F210" t="s">
         <v>636</v>
-      </c>
-      <c r="E210" t="s">
-        <v>637</v>
-      </c>
-      <c r="F210" t="s">
-        <v>638</v>
       </c>
       <c r="G210">
         <v>5</v>
@@ -42308,16 +42310,16 @@
         <v>0</v>
       </c>
       <c r="C211" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D211" t="s">
+        <v>637</v>
+      </c>
+      <c r="E211" t="s">
+        <v>638</v>
+      </c>
+      <c r="F211" t="s">
         <v>639</v>
-      </c>
-      <c r="E211" t="s">
-        <v>640</v>
-      </c>
-      <c r="F211" t="s">
-        <v>641</v>
       </c>
       <c r="G211">
         <v>55</v>
@@ -42365,16 +42367,16 @@
         <v>0</v>
       </c>
       <c r="C212" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D212" t="s">
+        <v>640</v>
+      </c>
+      <c r="E212" t="s">
+        <v>641</v>
+      </c>
+      <c r="F212" t="s">
         <v>642</v>
-      </c>
-      <c r="E212" t="s">
-        <v>643</v>
-      </c>
-      <c r="F212" t="s">
-        <v>644</v>
       </c>
       <c r="G212">
         <v>5000000</v>
@@ -42422,13 +42424,13 @@
         <v>0</v>
       </c>
       <c r="C213" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D213" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E213" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F213">
         <v>0</v>
@@ -42479,16 +42481,16 @@
         <v>0</v>
       </c>
       <c r="C214" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D214" t="s">
+        <v>644</v>
+      </c>
+      <c r="E214" t="s">
+        <v>645</v>
+      </c>
+      <c r="F214" t="s">
         <v>646</v>
-      </c>
-      <c r="E214" t="s">
-        <v>647</v>
-      </c>
-      <c r="F214" t="s">
-        <v>648</v>
       </c>
       <c r="G214">
         <v>3</v>
@@ -42536,16 +42538,16 @@
         <v>0</v>
       </c>
       <c r="C215" t="s">
+        <v>647</v>
+      </c>
+      <c r="D215" t="s">
+        <v>648</v>
+      </c>
+      <c r="E215" t="s">
         <v>649</v>
       </c>
-      <c r="D215" t="s">
+      <c r="F215" t="s">
         <v>650</v>
-      </c>
-      <c r="E215" t="s">
-        <v>651</v>
-      </c>
-      <c r="F215" t="s">
-        <v>652</v>
       </c>
       <c r="G215">
         <v>27</v>
@@ -42593,16 +42595,16 @@
         <v>0</v>
       </c>
       <c r="C216" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D216" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E216" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="F216" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G216">
         <v>36</v>
@@ -42650,16 +42652,16 @@
         <v>0</v>
       </c>
       <c r="C217" t="s">
+        <v>633</v>
+      </c>
+      <c r="D217" t="s">
+        <v>653</v>
+      </c>
+      <c r="E217" t="s">
         <v>635</v>
       </c>
-      <c r="D217" t="s">
-        <v>655</v>
-      </c>
-      <c r="E217" t="s">
-        <v>637</v>
-      </c>
       <c r="F217" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G217">
         <v>3</v>
@@ -42707,16 +42709,16 @@
         <v>0</v>
       </c>
       <c r="C218" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D218" t="s">
+        <v>655</v>
+      </c>
+      <c r="E218" t="s">
+        <v>656</v>
+      </c>
+      <c r="F218" t="s">
         <v>657</v>
-      </c>
-      <c r="E218" t="s">
-        <v>658</v>
-      </c>
-      <c r="F218" t="s">
-        <v>659</v>
       </c>
       <c r="G218">
         <v>50</v>
@@ -42764,16 +42766,16 @@
         <v>0</v>
       </c>
       <c r="C219" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D219" t="s">
+        <v>658</v>
+      </c>
+      <c r="E219" t="s">
+        <v>659</v>
+      </c>
+      <c r="F219" t="s">
         <v>660</v>
-      </c>
-      <c r="E219" t="s">
-        <v>661</v>
-      </c>
-      <c r="F219" t="s">
-        <v>662</v>
       </c>
       <c r="G219">
         <v>1000000</v>
@@ -42821,13 +42823,13 @@
         <v>0</v>
       </c>
       <c r="C220" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D220" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E220" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="F220">
         <v>0</v>
@@ -42878,16 +42880,16 @@
         <v>0</v>
       </c>
       <c r="C221" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D221" t="s">
+        <v>663</v>
+      </c>
+      <c r="E221" t="s">
+        <v>664</v>
+      </c>
+      <c r="F221" t="s">
         <v>665</v>
-      </c>
-      <c r="E221" t="s">
-        <v>666</v>
-      </c>
-      <c r="F221" t="s">
-        <v>667</v>
       </c>
       <c r="G221">
         <v>3</v>
@@ -42935,16 +42937,16 @@
         <v>0</v>
       </c>
       <c r="C222" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D222" t="s">
+        <v>666</v>
+      </c>
+      <c r="E222" t="s">
+        <v>667</v>
+      </c>
+      <c r="F222" t="s">
         <v>668</v>
-      </c>
-      <c r="E222" t="s">
-        <v>669</v>
-      </c>
-      <c r="F222" t="s">
-        <v>670</v>
       </c>
       <c r="G222">
         <v>6</v>
@@ -42992,16 +42994,16 @@
         <v>0</v>
       </c>
       <c r="C223" t="s">
+        <v>669</v>
+      </c>
+      <c r="D223" t="s">
+        <v>670</v>
+      </c>
+      <c r="E223" t="s">
         <v>671</v>
       </c>
-      <c r="D223" t="s">
+      <c r="F223" t="s">
         <v>672</v>
-      </c>
-      <c r="E223" t="s">
-        <v>673</v>
-      </c>
-      <c r="F223" t="s">
-        <v>674</v>
       </c>
       <c r="G223">
         <v>30</v>
@@ -43049,13 +43051,13 @@
         <v>0</v>
       </c>
       <c r="C224" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D224" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E224" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F224">
         <v>0</v>
@@ -43106,13 +43108,13 @@
         <v>0</v>
       </c>
       <c r="C225" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D225" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E225" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F225">
         <v>0</v>
@@ -43163,16 +43165,16 @@
         <v>0</v>
       </c>
       <c r="C226" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D226" t="s">
+        <v>676</v>
+      </c>
+      <c r="E226" t="s">
+        <v>677</v>
+      </c>
+      <c r="F226" t="s">
         <v>678</v>
-      </c>
-      <c r="E226" t="s">
-        <v>679</v>
-      </c>
-      <c r="F226" t="s">
-        <v>680</v>
       </c>
       <c r="G226">
         <v>0</v>
@@ -43220,13 +43222,13 @@
         <v>0</v>
       </c>
       <c r="C227" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D227" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E227" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="F227">
         <v>0</v>
@@ -43277,16 +43279,16 @@
         <v>0</v>
       </c>
       <c r="C228" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D228" t="s">
+        <v>680</v>
+      </c>
+      <c r="E228" t="s">
+        <v>681</v>
+      </c>
+      <c r="F228" t="s">
         <v>682</v>
-      </c>
-      <c r="E228" t="s">
-        <v>683</v>
-      </c>
-      <c r="F228" t="s">
-        <v>684</v>
       </c>
       <c r="G228">
         <v>9</v>
@@ -43334,16 +43336,16 @@
         <v>0</v>
       </c>
       <c r="C229" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D229" t="s">
+        <v>683</v>
+      </c>
+      <c r="E229" t="s">
+        <v>684</v>
+      </c>
+      <c r="F229" t="s">
         <v>685</v>
-      </c>
-      <c r="E229" t="s">
-        <v>686</v>
-      </c>
-      <c r="F229" t="s">
-        <v>687</v>
       </c>
       <c r="G229">
         <v>1</v>
@@ -43391,16 +43393,16 @@
         <v>0</v>
       </c>
       <c r="C230" t="s">
+        <v>686</v>
+      </c>
+      <c r="D230" t="s">
+        <v>687</v>
+      </c>
+      <c r="E230" t="s">
         <v>688</v>
       </c>
-      <c r="D230" t="s">
+      <c r="F230" t="s">
         <v>689</v>
-      </c>
-      <c r="E230" t="s">
-        <v>690</v>
-      </c>
-      <c r="F230" t="s">
-        <v>691</v>
       </c>
       <c r="G230">
         <v>5</v>
@@ -43448,16 +43450,16 @@
         <v>0</v>
       </c>
       <c r="C231" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D231" t="s">
+        <v>690</v>
+      </c>
+      <c r="E231" t="s">
+        <v>691</v>
+      </c>
+      <c r="F231" t="s">
         <v>692</v>
-      </c>
-      <c r="E231" t="s">
-        <v>693</v>
-      </c>
-      <c r="F231" t="s">
-        <v>694</v>
       </c>
       <c r="G231">
         <v>0</v>
@@ -43505,16 +43507,16 @@
         <v>0</v>
       </c>
       <c r="C232" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D232" t="s">
+        <v>693</v>
+      </c>
+      <c r="E232" t="s">
+        <v>694</v>
+      </c>
+      <c r="F232" t="s">
         <v>695</v>
-      </c>
-      <c r="E232" t="s">
-        <v>696</v>
-      </c>
-      <c r="F232" t="s">
-        <v>697</v>
       </c>
       <c r="G232">
         <v>0</v>
@@ -43562,16 +43564,16 @@
         <v>0</v>
       </c>
       <c r="C233" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D233" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="E233" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="F233" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="G233">
         <v>0</v>
@@ -43619,16 +43621,16 @@
         <v>0</v>
       </c>
       <c r="C234" t="s">
+        <v>698</v>
+      </c>
+      <c r="D234" t="s">
+        <v>699</v>
+      </c>
+      <c r="E234" t="s">
         <v>700</v>
       </c>
-      <c r="D234" t="s">
+      <c r="F234" t="s">
         <v>701</v>
-      </c>
-      <c r="E234" t="s">
-        <v>702</v>
-      </c>
-      <c r="F234" t="s">
-        <v>703</v>
       </c>
       <c r="G234">
         <v>2</v>
@@ -43676,16 +43678,16 @@
         <v>0</v>
       </c>
       <c r="C235" t="s">
+        <v>702</v>
+      </c>
+      <c r="D235" t="s">
+        <v>703</v>
+      </c>
+      <c r="E235" t="s">
         <v>704</v>
       </c>
-      <c r="D235" t="s">
+      <c r="F235" t="s">
         <v>705</v>
-      </c>
-      <c r="E235" t="s">
-        <v>706</v>
-      </c>
-      <c r="F235" t="s">
-        <v>707</v>
       </c>
       <c r="G235">
         <v>10000</v>
@@ -43733,16 +43735,16 @@
         <v>0</v>
       </c>
       <c r="C236" t="s">
+        <v>706</v>
+      </c>
+      <c r="D236" t="s">
+        <v>707</v>
+      </c>
+      <c r="E236" t="s">
         <v>708</v>
       </c>
-      <c r="D236" t="s">
+      <c r="F236" t="s">
         <v>709</v>
-      </c>
-      <c r="E236" t="s">
-        <v>710</v>
-      </c>
-      <c r="F236" t="s">
-        <v>711</v>
       </c>
       <c r="G236">
         <v>20000</v>
@@ -43790,13 +43792,13 @@
         <v>0</v>
       </c>
       <c r="C237" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D237" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="E237" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="F237">
         <v>0</v>
@@ -43847,16 +43849,16 @@
         <v>0</v>
       </c>
       <c r="C238" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D238" t="s">
+        <v>712</v>
+      </c>
+      <c r="E238" t="s">
+        <v>713</v>
+      </c>
+      <c r="F238" t="s">
         <v>714</v>
-      </c>
-      <c r="E238" t="s">
-        <v>715</v>
-      </c>
-      <c r="F238" t="s">
-        <v>716</v>
       </c>
       <c r="G238">
         <v>100</v>
@@ -43904,16 +43906,16 @@
         <v>0</v>
       </c>
       <c r="C239" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D239" t="s">
+        <v>715</v>
+      </c>
+      <c r="E239" t="s">
+        <v>716</v>
+      </c>
+      <c r="F239" t="s">
         <v>717</v>
-      </c>
-      <c r="E239" t="s">
-        <v>718</v>
-      </c>
-      <c r="F239" t="s">
-        <v>719</v>
       </c>
       <c r="G239">
         <v>10000</v>
@@ -43961,13 +43963,13 @@
         <v>0</v>
       </c>
       <c r="C240" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D240" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="E240" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="F240">
         <v>0</v>
@@ -44018,16 +44020,16 @@
         <v>0</v>
       </c>
       <c r="C241" t="s">
+        <v>720</v>
+      </c>
+      <c r="D241" t="s">
+        <v>721</v>
+      </c>
+      <c r="E241" t="s">
         <v>722</v>
       </c>
-      <c r="D241" t="s">
+      <c r="F241" t="s">
         <v>723</v>
-      </c>
-      <c r="E241" t="s">
-        <v>724</v>
-      </c>
-      <c r="F241" t="s">
-        <v>725</v>
       </c>
       <c r="G241">
         <v>0.2</v>
@@ -44075,16 +44077,16 @@
         <v>0</v>
       </c>
       <c r="C242" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D242" t="s">
+        <v>724</v>
+      </c>
+      <c r="E242" t="s">
+        <v>725</v>
+      </c>
+      <c r="F242" t="s">
         <v>726</v>
-      </c>
-      <c r="E242" t="s">
-        <v>727</v>
-      </c>
-      <c r="F242" t="s">
-        <v>728</v>
       </c>
       <c r="G242">
         <v>2</v>
@@ -44132,16 +44134,16 @@
         <v>0</v>
       </c>
       <c r="C243" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D243" t="s">
+        <v>727</v>
+      </c>
+      <c r="E243" t="s">
+        <v>728</v>
+      </c>
+      <c r="F243" t="s">
         <v>729</v>
-      </c>
-      <c r="E243" t="s">
-        <v>730</v>
-      </c>
-      <c r="F243" t="s">
-        <v>731</v>
       </c>
       <c r="G243">
         <v>3</v>
@@ -44189,16 +44191,16 @@
         <v>0</v>
       </c>
       <c r="C244" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D244" t="s">
+        <v>730</v>
+      </c>
+      <c r="E244" t="s">
+        <v>731</v>
+      </c>
+      <c r="F244" t="s">
         <v>732</v>
-      </c>
-      <c r="E244" t="s">
-        <v>733</v>
-      </c>
-      <c r="F244" t="s">
-        <v>734</v>
       </c>
       <c r="G244">
         <v>3</v>
@@ -44246,16 +44248,16 @@
         <v>0</v>
       </c>
       <c r="C245" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D245" t="s">
+        <v>733</v>
+      </c>
+      <c r="E245" t="s">
+        <v>734</v>
+      </c>
+      <c r="F245" t="s">
         <v>735</v>
-      </c>
-      <c r="E245" t="s">
-        <v>736</v>
-      </c>
-      <c r="F245" t="s">
-        <v>737</v>
       </c>
       <c r="G245">
         <v>100</v>
@@ -44303,16 +44305,16 @@
         <v>0</v>
       </c>
       <c r="C246" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D246" t="s">
+        <v>736</v>
+      </c>
+      <c r="E246" t="s">
+        <v>737</v>
+      </c>
+      <c r="F246" t="s">
         <v>738</v>
-      </c>
-      <c r="E246" t="s">
-        <v>739</v>
-      </c>
-      <c r="F246" t="s">
-        <v>740</v>
       </c>
       <c r="G246">
         <v>9</v>
@@ -44360,16 +44362,16 @@
         <v>0</v>
       </c>
       <c r="C247" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D247" t="s">
+        <v>739</v>
+      </c>
+      <c r="E247" t="s">
+        <v>740</v>
+      </c>
+      <c r="F247" t="s">
         <v>741</v>
-      </c>
-      <c r="E247" t="s">
-        <v>742</v>
-      </c>
-      <c r="F247" t="s">
-        <v>743</v>
       </c>
       <c r="G247">
         <v>0.7</v>
@@ -44417,16 +44419,16 @@
         <v>0</v>
       </c>
       <c r="C248" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D248" t="s">
+        <v>742</v>
+      </c>
+      <c r="E248" t="s">
+        <v>743</v>
+      </c>
+      <c r="F248" t="s">
         <v>744</v>
-      </c>
-      <c r="E248" t="s">
-        <v>745</v>
-      </c>
-      <c r="F248" t="s">
-        <v>746</v>
       </c>
       <c r="G248">
         <v>0.7</v>
@@ -44474,16 +44476,16 @@
         <v>0</v>
       </c>
       <c r="C249" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D249" t="s">
+        <v>745</v>
+      </c>
+      <c r="E249" t="s">
+        <v>746</v>
+      </c>
+      <c r="F249" t="s">
         <v>747</v>
-      </c>
-      <c r="E249" t="s">
-        <v>748</v>
-      </c>
-      <c r="F249" t="s">
-        <v>749</v>
       </c>
       <c r="G249">
         <v>10</v>
@@ -44531,16 +44533,16 @@
         <v>0</v>
       </c>
       <c r="C250" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D250" t="s">
+        <v>748</v>
+      </c>
+      <c r="E250" t="s">
+        <v>749</v>
+      </c>
+      <c r="F250" t="s">
         <v>750</v>
-      </c>
-      <c r="E250" t="s">
-        <v>751</v>
-      </c>
-      <c r="F250" t="s">
-        <v>752</v>
       </c>
       <c r="G250">
         <v>0</v>
@@ -44588,16 +44590,16 @@
         <v>0</v>
       </c>
       <c r="C251" t="s">
+        <v>751</v>
+      </c>
+      <c r="D251" t="s">
+        <v>752</v>
+      </c>
+      <c r="E251" t="s">
         <v>753</v>
       </c>
-      <c r="D251" t="s">
+      <c r="F251" t="s">
         <v>754</v>
-      </c>
-      <c r="E251" t="s">
-        <v>755</v>
-      </c>
-      <c r="F251" t="s">
-        <v>756</v>
       </c>
       <c r="G251">
         <v>10000</v>
@@ -44645,16 +44647,16 @@
         <v>0</v>
       </c>
       <c r="C252" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D252" t="s">
+        <v>755</v>
+      </c>
+      <c r="E252" t="s">
+        <v>756</v>
+      </c>
+      <c r="F252" t="s">
         <v>757</v>
-      </c>
-      <c r="E252" t="s">
-        <v>758</v>
-      </c>
-      <c r="F252" t="s">
-        <v>759</v>
       </c>
       <c r="G252">
         <v>5000</v>
@@ -44702,13 +44704,13 @@
         <v>0</v>
       </c>
       <c r="C253" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D253" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="E253" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="F253">
         <v>0</v>
@@ -44759,16 +44761,16 @@
         <v>0</v>
       </c>
       <c r="C254" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D254" t="s">
+        <v>760</v>
+      </c>
+      <c r="E254" t="s">
+        <v>761</v>
+      </c>
+      <c r="F254" t="s">
         <v>762</v>
-      </c>
-      <c r="E254" t="s">
-        <v>763</v>
-      </c>
-      <c r="F254" t="s">
-        <v>764</v>
       </c>
       <c r="G254">
         <v>10000</v>
@@ -44816,22 +44818,22 @@
         <v>0</v>
       </c>
       <c r="C255" t="s">
+        <v>763</v>
+      </c>
+      <c r="D255" t="s">
+        <v>764</v>
+      </c>
+      <c r="E255" t="s">
         <v>765</v>
       </c>
-      <c r="D255" t="s">
+      <c r="F255" t="s">
         <v>766</v>
       </c>
-      <c r="E255" t="s">
+      <c r="G255" t="s">
         <v>767</v>
       </c>
-      <c r="F255" t="s">
+      <c r="H255" t="s">
         <v>768</v>
-      </c>
-      <c r="G255" t="s">
-        <v>769</v>
-      </c>
-      <c r="H255" t="s">
-        <v>770</v>
       </c>
       <c r="I255">
         <v>0</v>
@@ -44873,25 +44875,25 @@
         <v>0</v>
       </c>
       <c r="C256" t="s">
+        <v>763</v>
+      </c>
+      <c r="D256" t="s">
+        <v>769</v>
+      </c>
+      <c r="E256" t="s">
         <v>765</v>
       </c>
-      <c r="D256" t="s">
+      <c r="F256" t="s">
+        <v>766</v>
+      </c>
+      <c r="G256" t="s">
+        <v>767</v>
+      </c>
+      <c r="H256" t="s">
+        <v>770</v>
+      </c>
+      <c r="I256" t="s">
         <v>771</v>
-      </c>
-      <c r="E256" t="s">
-        <v>767</v>
-      </c>
-      <c r="F256" t="s">
-        <v>768</v>
-      </c>
-      <c r="G256" t="s">
-        <v>769</v>
-      </c>
-      <c r="H256" t="s">
-        <v>772</v>
-      </c>
-      <c r="I256" t="s">
-        <v>773</v>
       </c>
       <c r="J256">
         <v>0</v>
@@ -44930,28 +44932,28 @@
         <v>0</v>
       </c>
       <c r="C257" t="s">
+        <v>763</v>
+      </c>
+      <c r="D257" t="s">
+        <v>772</v>
+      </c>
+      <c r="E257" t="s">
         <v>765</v>
       </c>
-      <c r="D257" t="s">
+      <c r="F257" t="s">
+        <v>766</v>
+      </c>
+      <c r="G257" t="s">
+        <v>767</v>
+      </c>
+      <c r="H257" t="s">
+        <v>773</v>
+      </c>
+      <c r="I257" t="s">
+        <v>771</v>
+      </c>
+      <c r="J257" t="s">
         <v>774</v>
-      </c>
-      <c r="E257" t="s">
-        <v>767</v>
-      </c>
-      <c r="F257" t="s">
-        <v>768</v>
-      </c>
-      <c r="G257" t="s">
-        <v>769</v>
-      </c>
-      <c r="H257" t="s">
-        <v>775</v>
-      </c>
-      <c r="I257" t="s">
-        <v>773</v>
-      </c>
-      <c r="J257" t="s">
-        <v>776</v>
       </c>
       <c r="K257">
         <v>0</v>
@@ -44987,28 +44989,28 @@
         <v>0</v>
       </c>
       <c r="C258" t="s">
+        <v>763</v>
+      </c>
+      <c r="D258" t="s">
+        <v>775</v>
+      </c>
+      <c r="E258" t="s">
         <v>765</v>
       </c>
-      <c r="D258" t="s">
+      <c r="F258" t="s">
+        <v>766</v>
+      </c>
+      <c r="G258" t="s">
+        <v>776</v>
+      </c>
+      <c r="H258" t="s">
+        <v>773</v>
+      </c>
+      <c r="I258" t="s">
         <v>777</v>
       </c>
-      <c r="E258" t="s">
-        <v>767</v>
-      </c>
-      <c r="F258" t="s">
-        <v>768</v>
-      </c>
-      <c r="G258" t="s">
-        <v>778</v>
-      </c>
-      <c r="H258" t="s">
-        <v>775</v>
-      </c>
-      <c r="I258" t="s">
-        <v>779</v>
-      </c>
       <c r="J258" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="K258">
         <v>0</v>
@@ -45044,28 +45046,28 @@
         <v>0</v>
       </c>
       <c r="C259" t="s">
+        <v>763</v>
+      </c>
+      <c r="D259" t="s">
+        <v>778</v>
+      </c>
+      <c r="E259" t="s">
         <v>765</v>
       </c>
-      <c r="D259" t="s">
+      <c r="F259" t="s">
+        <v>766</v>
+      </c>
+      <c r="G259" t="s">
+        <v>779</v>
+      </c>
+      <c r="H259" t="s">
+        <v>773</v>
+      </c>
+      <c r="I259" t="s">
+        <v>777</v>
+      </c>
+      <c r="J259" t="s">
         <v>780</v>
-      </c>
-      <c r="E259" t="s">
-        <v>767</v>
-      </c>
-      <c r="F259" t="s">
-        <v>768</v>
-      </c>
-      <c r="G259" t="s">
-        <v>781</v>
-      </c>
-      <c r="H259" t="s">
-        <v>775</v>
-      </c>
-      <c r="I259" t="s">
-        <v>779</v>
-      </c>
-      <c r="J259" t="s">
-        <v>782</v>
       </c>
       <c r="K259">
         <v>0</v>
@@ -45101,31 +45103,31 @@
         <v>0</v>
       </c>
       <c r="C260" t="s">
+        <v>763</v>
+      </c>
+      <c r="D260" t="s">
+        <v>781</v>
+      </c>
+      <c r="E260" t="s">
         <v>765</v>
       </c>
-      <c r="D260" t="s">
+      <c r="F260" t="s">
+        <v>766</v>
+      </c>
+      <c r="G260" t="s">
+        <v>782</v>
+      </c>
+      <c r="H260" t="s">
+        <v>773</v>
+      </c>
+      <c r="I260" t="s">
+        <v>777</v>
+      </c>
+      <c r="J260" t="s">
+        <v>780</v>
+      </c>
+      <c r="K260" t="s">
         <v>783</v>
-      </c>
-      <c r="E260" t="s">
-        <v>767</v>
-      </c>
-      <c r="F260" t="s">
-        <v>768</v>
-      </c>
-      <c r="G260" t="s">
-        <v>784</v>
-      </c>
-      <c r="H260" t="s">
-        <v>775</v>
-      </c>
-      <c r="I260" t="s">
-        <v>779</v>
-      </c>
-      <c r="J260" t="s">
-        <v>782</v>
-      </c>
-      <c r="K260" t="s">
-        <v>785</v>
       </c>
       <c r="L260">
         <v>0</v>
@@ -45158,31 +45160,31 @@
         <v>0</v>
       </c>
       <c r="C261" t="s">
+        <v>763</v>
+      </c>
+      <c r="D261" t="s">
+        <v>784</v>
+      </c>
+      <c r="E261" t="s">
         <v>765</v>
       </c>
-      <c r="D261" t="s">
+      <c r="F261" t="s">
+        <v>766</v>
+      </c>
+      <c r="G261" t="s">
+        <v>785</v>
+      </c>
+      <c r="H261" t="s">
         <v>786</v>
       </c>
-      <c r="E261" t="s">
-        <v>767</v>
-      </c>
-      <c r="F261" t="s">
-        <v>768</v>
-      </c>
-      <c r="G261" t="s">
+      <c r="I261" t="s">
+        <v>780</v>
+      </c>
+      <c r="J261" t="s">
         <v>787</v>
       </c>
-      <c r="H261" t="s">
+      <c r="K261" t="s">
         <v>788</v>
-      </c>
-      <c r="I261" t="s">
-        <v>782</v>
-      </c>
-      <c r="J261" t="s">
-        <v>789</v>
-      </c>
-      <c r="K261" t="s">
-        <v>790</v>
       </c>
       <c r="L261">
         <v>0</v>
@@ -45215,31 +45217,31 @@
         <v>0</v>
       </c>
       <c r="C262" t="s">
+        <v>763</v>
+      </c>
+      <c r="D262" t="s">
+        <v>789</v>
+      </c>
+      <c r="E262" t="s">
         <v>765</v>
       </c>
-      <c r="D262" t="s">
-        <v>791</v>
-      </c>
-      <c r="E262" t="s">
-        <v>767</v>
-      </c>
       <c r="F262" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="G262" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="H262" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="I262" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="J262" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="K262" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="L262">
         <v>0</v>
@@ -45272,31 +45274,31 @@
         <v>0</v>
       </c>
       <c r="C263" t="s">
+        <v>763</v>
+      </c>
+      <c r="D263" t="s">
+        <v>791</v>
+      </c>
+      <c r="E263" t="s">
         <v>765</v>
       </c>
-      <c r="D263" t="s">
+      <c r="F263" t="s">
+        <v>766</v>
+      </c>
+      <c r="G263" t="s">
+        <v>786</v>
+      </c>
+      <c r="H263" t="s">
+        <v>792</v>
+      </c>
+      <c r="I263" t="s">
+        <v>787</v>
+      </c>
+      <c r="J263" t="s">
         <v>793</v>
       </c>
-      <c r="E263" t="s">
-        <v>767</v>
-      </c>
-      <c r="F263" t="s">
-        <v>768</v>
-      </c>
-      <c r="G263" t="s">
-        <v>788</v>
-      </c>
-      <c r="H263" t="s">
+      <c r="K263" t="s">
         <v>794</v>
-      </c>
-      <c r="I263" t="s">
-        <v>789</v>
-      </c>
-      <c r="J263" t="s">
-        <v>795</v>
-      </c>
-      <c r="K263" t="s">
-        <v>796</v>
       </c>
       <c r="L263">
         <v>0</v>
@@ -45329,31 +45331,31 @@
         <v>0</v>
       </c>
       <c r="C264" t="s">
+        <v>763</v>
+      </c>
+      <c r="D264" t="s">
+        <v>795</v>
+      </c>
+      <c r="E264" t="s">
         <v>765</v>
       </c>
-      <c r="D264" t="s">
+      <c r="F264" t="s">
+        <v>766</v>
+      </c>
+      <c r="G264" t="s">
+        <v>792</v>
+      </c>
+      <c r="H264" t="s">
+        <v>796</v>
+      </c>
+      <c r="I264" t="s">
+        <v>793</v>
+      </c>
+      <c r="J264" t="s">
         <v>797</v>
       </c>
-      <c r="E264" t="s">
-        <v>767</v>
-      </c>
-      <c r="F264" t="s">
-        <v>768</v>
-      </c>
-      <c r="G264" t="s">
-        <v>794</v>
-      </c>
-      <c r="H264" t="s">
+      <c r="K264" t="s">
         <v>798</v>
-      </c>
-      <c r="I264" t="s">
-        <v>795</v>
-      </c>
-      <c r="J264" t="s">
-        <v>799</v>
-      </c>
-      <c r="K264" t="s">
-        <v>800</v>
       </c>
       <c r="L264">
         <v>0</v>
@@ -45386,31 +45388,31 @@
         <v>0</v>
       </c>
       <c r="C265" t="s">
+        <v>763</v>
+      </c>
+      <c r="D265" t="s">
+        <v>799</v>
+      </c>
+      <c r="E265" t="s">
         <v>765</v>
       </c>
-      <c r="D265" t="s">
+      <c r="F265" t="s">
+        <v>766</v>
+      </c>
+      <c r="G265" t="s">
+        <v>796</v>
+      </c>
+      <c r="H265" t="s">
+        <v>800</v>
+      </c>
+      <c r="I265" t="s">
+        <v>797</v>
+      </c>
+      <c r="J265" t="s">
         <v>801</v>
       </c>
-      <c r="E265" t="s">
-        <v>767</v>
-      </c>
-      <c r="F265" t="s">
-        <v>768</v>
-      </c>
-      <c r="G265" t="s">
-        <v>798</v>
-      </c>
-      <c r="H265" t="s">
+      <c r="K265" t="s">
         <v>802</v>
-      </c>
-      <c r="I265" t="s">
-        <v>799</v>
-      </c>
-      <c r="J265" t="s">
-        <v>803</v>
-      </c>
-      <c r="K265" t="s">
-        <v>804</v>
       </c>
       <c r="L265">
         <v>0</v>
@@ -45443,31 +45445,31 @@
         <v>0</v>
       </c>
       <c r="C266" t="s">
+        <v>763</v>
+      </c>
+      <c r="D266" t="s">
+        <v>803</v>
+      </c>
+      <c r="E266" t="s">
         <v>765</v>
       </c>
-      <c r="D266" t="s">
+      <c r="F266" t="s">
+        <v>766</v>
+      </c>
+      <c r="G266" t="s">
+        <v>800</v>
+      </c>
+      <c r="H266" t="s">
+        <v>804</v>
+      </c>
+      <c r="I266" t="s">
+        <v>801</v>
+      </c>
+      <c r="J266" t="s">
         <v>805</v>
       </c>
-      <c r="E266" t="s">
-        <v>767</v>
-      </c>
-      <c r="F266" t="s">
-        <v>768</v>
-      </c>
-      <c r="G266" t="s">
-        <v>802</v>
-      </c>
-      <c r="H266" t="s">
+      <c r="K266" t="s">
         <v>806</v>
-      </c>
-      <c r="I266" t="s">
-        <v>803</v>
-      </c>
-      <c r="J266" t="s">
-        <v>807</v>
-      </c>
-      <c r="K266" t="s">
-        <v>808</v>
       </c>
       <c r="L266">
         <v>0</v>
@@ -45500,31 +45502,31 @@
         <v>0</v>
       </c>
       <c r="C267" t="s">
+        <v>763</v>
+      </c>
+      <c r="D267" t="s">
+        <v>807</v>
+      </c>
+      <c r="E267" t="s">
         <v>765</v>
       </c>
-      <c r="D267" t="s">
+      <c r="F267" t="s">
+        <v>766</v>
+      </c>
+      <c r="G267" t="s">
+        <v>804</v>
+      </c>
+      <c r="H267" t="s">
+        <v>808</v>
+      </c>
+      <c r="I267" t="s">
+        <v>805</v>
+      </c>
+      <c r="J267" t="s">
         <v>809</v>
       </c>
-      <c r="E267" t="s">
-        <v>767</v>
-      </c>
-      <c r="F267" t="s">
-        <v>768</v>
-      </c>
-      <c r="G267" t="s">
-        <v>806</v>
-      </c>
-      <c r="H267" t="s">
+      <c r="K267" t="s">
         <v>810</v>
-      </c>
-      <c r="I267" t="s">
-        <v>807</v>
-      </c>
-      <c r="J267" t="s">
-        <v>811</v>
-      </c>
-      <c r="K267" t="s">
-        <v>812</v>
       </c>
       <c r="L267">
         <v>0</v>
@@ -45557,31 +45559,31 @@
         <v>0</v>
       </c>
       <c r="C268" t="s">
+        <v>763</v>
+      </c>
+      <c r="D268" t="s">
+        <v>811</v>
+      </c>
+      <c r="E268" t="s">
         <v>765</v>
       </c>
-      <c r="D268" t="s">
+      <c r="F268" t="s">
+        <v>766</v>
+      </c>
+      <c r="G268" t="s">
+        <v>808</v>
+      </c>
+      <c r="H268" t="s">
+        <v>812</v>
+      </c>
+      <c r="I268" t="s">
+        <v>809</v>
+      </c>
+      <c r="J268" t="s">
         <v>813</v>
       </c>
-      <c r="E268" t="s">
-        <v>767</v>
-      </c>
-      <c r="F268" t="s">
-        <v>768</v>
-      </c>
-      <c r="G268" t="s">
-        <v>810</v>
-      </c>
-      <c r="H268" t="s">
+      <c r="K268" t="s">
         <v>814</v>
-      </c>
-      <c r="I268" t="s">
-        <v>811</v>
-      </c>
-      <c r="J268" t="s">
-        <v>815</v>
-      </c>
-      <c r="K268" t="s">
-        <v>816</v>
       </c>
       <c r="L268">
         <v>0</v>
@@ -45614,31 +45616,31 @@
         <v>0</v>
       </c>
       <c r="C269" t="s">
+        <v>763</v>
+      </c>
+      <c r="D269" t="s">
+        <v>815</v>
+      </c>
+      <c r="E269" t="s">
         <v>765</v>
       </c>
-      <c r="D269" t="s">
+      <c r="F269" t="s">
+        <v>766</v>
+      </c>
+      <c r="G269" t="s">
+        <v>812</v>
+      </c>
+      <c r="H269" t="s">
+        <v>816</v>
+      </c>
+      <c r="I269" t="s">
+        <v>813</v>
+      </c>
+      <c r="J269" t="s">
         <v>817</v>
       </c>
-      <c r="E269" t="s">
-        <v>767</v>
-      </c>
-      <c r="F269" t="s">
-        <v>768</v>
-      </c>
-      <c r="G269" t="s">
-        <v>814</v>
-      </c>
-      <c r="H269" t="s">
+      <c r="K269" t="s">
         <v>818</v>
-      </c>
-      <c r="I269" t="s">
-        <v>815</v>
-      </c>
-      <c r="J269" t="s">
-        <v>819</v>
-      </c>
-      <c r="K269" t="s">
-        <v>820</v>
       </c>
       <c r="L269">
         <v>0</v>
@@ -45671,31 +45673,31 @@
         <v>0</v>
       </c>
       <c r="C270" t="s">
+        <v>763</v>
+      </c>
+      <c r="D270" t="s">
+        <v>819</v>
+      </c>
+      <c r="E270" t="s">
         <v>765</v>
       </c>
-      <c r="D270" t="s">
+      <c r="F270" t="s">
+        <v>766</v>
+      </c>
+      <c r="G270" t="s">
+        <v>816</v>
+      </c>
+      <c r="H270" t="s">
+        <v>820</v>
+      </c>
+      <c r="I270" t="s">
+        <v>817</v>
+      </c>
+      <c r="J270" t="s">
         <v>821</v>
       </c>
-      <c r="E270" t="s">
-        <v>767</v>
-      </c>
-      <c r="F270" t="s">
-        <v>768</v>
-      </c>
-      <c r="G270" t="s">
-        <v>818</v>
-      </c>
-      <c r="H270" t="s">
+      <c r="K270" t="s">
         <v>822</v>
-      </c>
-      <c r="I270" t="s">
-        <v>819</v>
-      </c>
-      <c r="J270" t="s">
-        <v>823</v>
-      </c>
-      <c r="K270" t="s">
-        <v>824</v>
       </c>
       <c r="L270">
         <v>0</v>
@@ -45728,31 +45730,31 @@
         <v>0</v>
       </c>
       <c r="C271" t="s">
+        <v>763</v>
+      </c>
+      <c r="D271" t="s">
+        <v>823</v>
+      </c>
+      <c r="E271" t="s">
         <v>765</v>
       </c>
-      <c r="D271" t="s">
+      <c r="F271" t="s">
+        <v>766</v>
+      </c>
+      <c r="G271" t="s">
+        <v>820</v>
+      </c>
+      <c r="H271" t="s">
+        <v>824</v>
+      </c>
+      <c r="I271" t="s">
+        <v>821</v>
+      </c>
+      <c r="J271" t="s">
         <v>825</v>
       </c>
-      <c r="E271" t="s">
-        <v>767</v>
-      </c>
-      <c r="F271" t="s">
-        <v>768</v>
-      </c>
-      <c r="G271" t="s">
-        <v>822</v>
-      </c>
-      <c r="H271" t="s">
+      <c r="K271" t="s">
         <v>826</v>
-      </c>
-      <c r="I271" t="s">
-        <v>823</v>
-      </c>
-      <c r="J271" t="s">
-        <v>827</v>
-      </c>
-      <c r="K271" t="s">
-        <v>828</v>
       </c>
       <c r="L271">
         <v>0</v>
@@ -45785,34 +45787,34 @@
         <v>0</v>
       </c>
       <c r="C272" t="s">
+        <v>763</v>
+      </c>
+      <c r="D272" t="s">
+        <v>827</v>
+      </c>
+      <c r="E272" t="s">
         <v>765</v>
       </c>
-      <c r="D272" t="s">
+      <c r="F272" t="s">
+        <v>766</v>
+      </c>
+      <c r="G272" t="s">
+        <v>810</v>
+      </c>
+      <c r="H272" t="s">
+        <v>828</v>
+      </c>
+      <c r="I272" t="s">
         <v>829</v>
       </c>
-      <c r="E272" t="s">
-        <v>767</v>
-      </c>
-      <c r="F272" t="s">
-        <v>768</v>
-      </c>
-      <c r="G272" t="s">
-        <v>812</v>
-      </c>
-      <c r="H272" t="s">
+      <c r="J272" t="s">
+        <v>825</v>
+      </c>
+      <c r="K272" t="s">
         <v>830</v>
       </c>
-      <c r="I272" t="s">
+      <c r="L272" t="s">
         <v>831</v>
-      </c>
-      <c r="J272" t="s">
-        <v>827</v>
-      </c>
-      <c r="K272" t="s">
-        <v>832</v>
-      </c>
-      <c r="L272" t="s">
-        <v>833</v>
       </c>
       <c r="M272">
         <v>0</v>
@@ -45842,34 +45844,34 @@
         <v>0</v>
       </c>
       <c r="C273" t="s">
+        <v>763</v>
+      </c>
+      <c r="D273" t="s">
+        <v>832</v>
+      </c>
+      <c r="E273" t="s">
         <v>765</v>
       </c>
-      <c r="D273" t="s">
-        <v>834</v>
-      </c>
-      <c r="E273" t="s">
-        <v>767</v>
-      </c>
       <c r="F273" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="G273" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="H273" t="s">
+        <v>828</v>
+      </c>
+      <c r="I273" t="s">
+        <v>829</v>
+      </c>
+      <c r="J273" t="s">
+        <v>825</v>
+      </c>
+      <c r="K273" t="s">
         <v>830</v>
       </c>
-      <c r="I273" t="s">
+      <c r="L273" t="s">
         <v>831</v>
-      </c>
-      <c r="J273" t="s">
-        <v>827</v>
-      </c>
-      <c r="K273" t="s">
-        <v>832</v>
-      </c>
-      <c r="L273" t="s">
-        <v>833</v>
       </c>
       <c r="M273">
         <v>0</v>
@@ -45899,34 +45901,34 @@
         <v>0</v>
       </c>
       <c r="C274" t="s">
+        <v>763</v>
+      </c>
+      <c r="D274" t="s">
+        <v>833</v>
+      </c>
+      <c r="E274" t="s">
         <v>765</v>
       </c>
-      <c r="D274" t="s">
-        <v>835</v>
-      </c>
-      <c r="E274" t="s">
-        <v>767</v>
-      </c>
       <c r="F274" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="G274" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="H274" t="s">
+        <v>828</v>
+      </c>
+      <c r="I274" t="s">
+        <v>829</v>
+      </c>
+      <c r="J274" t="s">
+        <v>825</v>
+      </c>
+      <c r="K274" t="s">
         <v>830</v>
       </c>
-      <c r="I274" t="s">
+      <c r="L274" t="s">
         <v>831</v>
-      </c>
-      <c r="J274" t="s">
-        <v>827</v>
-      </c>
-      <c r="K274" t="s">
-        <v>832</v>
-      </c>
-      <c r="L274" t="s">
-        <v>833</v>
       </c>
       <c r="M274">
         <v>0</v>
@@ -45956,28 +45958,28 @@
         <v>0</v>
       </c>
       <c r="C275" t="s">
+        <v>834</v>
+      </c>
+      <c r="D275" t="s">
+        <v>764</v>
+      </c>
+      <c r="E275" t="s">
+        <v>835</v>
+      </c>
+      <c r="F275" t="s">
         <v>836</v>
       </c>
-      <c r="D275" t="s">
-        <v>766</v>
-      </c>
-      <c r="E275" t="s">
+      <c r="G275" t="s">
         <v>837</v>
       </c>
-      <c r="F275" t="s">
+      <c r="H275" t="s">
         <v>838</v>
       </c>
-      <c r="G275" t="s">
+      <c r="I275" t="s">
         <v>839</v>
       </c>
-      <c r="H275" t="s">
+      <c r="J275" t="s">
         <v>840</v>
-      </c>
-      <c r="I275" t="s">
-        <v>841</v>
-      </c>
-      <c r="J275" t="s">
-        <v>842</v>
       </c>
       <c r="K275">
         <v>0</v>
@@ -46013,28 +46015,28 @@
         <v>0</v>
       </c>
       <c r="C276" t="s">
+        <v>834</v>
+      </c>
+      <c r="D276" t="s">
+        <v>769</v>
+      </c>
+      <c r="E276" t="s">
+        <v>835</v>
+      </c>
+      <c r="F276" t="s">
         <v>836</v>
       </c>
-      <c r="D276" t="s">
-        <v>771</v>
-      </c>
-      <c r="E276" t="s">
-        <v>837</v>
-      </c>
-      <c r="F276" t="s">
+      <c r="G276" t="s">
+        <v>841</v>
+      </c>
+      <c r="H276" t="s">
         <v>838</v>
       </c>
-      <c r="G276" t="s">
+      <c r="I276" t="s">
+        <v>842</v>
+      </c>
+      <c r="J276" t="s">
         <v>843</v>
-      </c>
-      <c r="H276" t="s">
-        <v>840</v>
-      </c>
-      <c r="I276" t="s">
-        <v>844</v>
-      </c>
-      <c r="J276" t="s">
-        <v>845</v>
       </c>
       <c r="K276">
         <v>0</v>
@@ -46070,28 +46072,28 @@
         <v>0</v>
       </c>
       <c r="C277" t="s">
+        <v>834</v>
+      </c>
+      <c r="D277" t="s">
+        <v>772</v>
+      </c>
+      <c r="E277" t="s">
+        <v>835</v>
+      </c>
+      <c r="F277" t="s">
         <v>836</v>
       </c>
-      <c r="D277" t="s">
-        <v>774</v>
-      </c>
-      <c r="E277" t="s">
-        <v>837</v>
-      </c>
-      <c r="F277" t="s">
+      <c r="G277" t="s">
+        <v>844</v>
+      </c>
+      <c r="H277" t="s">
         <v>838</v>
       </c>
-      <c r="G277" t="s">
+      <c r="I277" t="s">
+        <v>845</v>
+      </c>
+      <c r="J277" t="s">
         <v>846</v>
-      </c>
-      <c r="H277" t="s">
-        <v>840</v>
-      </c>
-      <c r="I277" t="s">
-        <v>847</v>
-      </c>
-      <c r="J277" t="s">
-        <v>848</v>
       </c>
       <c r="K277">
         <v>0</v>
@@ -46127,31 +46129,31 @@
         <v>0</v>
       </c>
       <c r="C278" t="s">
+        <v>834</v>
+      </c>
+      <c r="D278" t="s">
+        <v>775</v>
+      </c>
+      <c r="E278" t="s">
+        <v>835</v>
+      </c>
+      <c r="F278" t="s">
         <v>836</v>
       </c>
-      <c r="D278" t="s">
-        <v>777</v>
-      </c>
-      <c r="E278" t="s">
-        <v>837</v>
-      </c>
-      <c r="F278" t="s">
+      <c r="G278" t="s">
+        <v>847</v>
+      </c>
+      <c r="H278" t="s">
         <v>838</v>
       </c>
-      <c r="G278" t="s">
-        <v>849</v>
-      </c>
-      <c r="H278" t="s">
-        <v>840</v>
-      </c>
       <c r="I278" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="J278" t="s">
+        <v>846</v>
+      </c>
+      <c r="K278" t="s">
         <v>848</v>
-      </c>
-      <c r="K278" t="s">
-        <v>850</v>
       </c>
       <c r="L278">
         <v>0</v>
@@ -46184,31 +46186,31 @@
         <v>0</v>
       </c>
       <c r="C279" t="s">
+        <v>834</v>
+      </c>
+      <c r="D279" t="s">
+        <v>778</v>
+      </c>
+      <c r="E279" t="s">
+        <v>835</v>
+      </c>
+      <c r="F279" t="s">
         <v>836</v>
       </c>
-      <c r="D279" t="s">
-        <v>780</v>
-      </c>
-      <c r="E279" t="s">
-        <v>837</v>
-      </c>
-      <c r="F279" t="s">
+      <c r="G279" t="s">
+        <v>849</v>
+      </c>
+      <c r="H279" t="s">
         <v>838</v>
       </c>
-      <c r="G279" t="s">
+      <c r="I279" t="s">
+        <v>845</v>
+      </c>
+      <c r="J279" t="s">
+        <v>850</v>
+      </c>
+      <c r="K279" t="s">
         <v>851</v>
-      </c>
-      <c r="H279" t="s">
-        <v>840</v>
-      </c>
-      <c r="I279" t="s">
-        <v>847</v>
-      </c>
-      <c r="J279" t="s">
-        <v>852</v>
-      </c>
-      <c r="K279" t="s">
-        <v>853</v>
       </c>
       <c r="L279">
         <v>0</v>
@@ -46241,31 +46243,31 @@
         <v>0</v>
       </c>
       <c r="C280" t="s">
+        <v>834</v>
+      </c>
+      <c r="D280" t="s">
+        <v>781</v>
+      </c>
+      <c r="E280" t="s">
+        <v>835</v>
+      </c>
+      <c r="F280" t="s">
         <v>836</v>
       </c>
-      <c r="D280" t="s">
-        <v>783</v>
-      </c>
-      <c r="E280" t="s">
-        <v>837</v>
-      </c>
-      <c r="F280" t="s">
+      <c r="G280" t="s">
+        <v>852</v>
+      </c>
+      <c r="H280" t="s">
         <v>838</v>
       </c>
-      <c r="G280" t="s">
+      <c r="I280" t="s">
+        <v>845</v>
+      </c>
+      <c r="J280" t="s">
+        <v>853</v>
+      </c>
+      <c r="K280" t="s">
         <v>854</v>
-      </c>
-      <c r="H280" t="s">
-        <v>840</v>
-      </c>
-      <c r="I280" t="s">
-        <v>847</v>
-      </c>
-      <c r="J280" t="s">
-        <v>855</v>
-      </c>
-      <c r="K280" t="s">
-        <v>856</v>
       </c>
       <c r="L280">
         <v>0</v>
@@ -46298,31 +46300,31 @@
         <v>0</v>
       </c>
       <c r="C281" t="s">
+        <v>834</v>
+      </c>
+      <c r="D281" t="s">
+        <v>784</v>
+      </c>
+      <c r="E281" t="s">
+        <v>835</v>
+      </c>
+      <c r="F281" t="s">
         <v>836</v>
       </c>
-      <c r="D281" t="s">
-        <v>786</v>
-      </c>
-      <c r="E281" t="s">
-        <v>837</v>
-      </c>
-      <c r="F281" t="s">
+      <c r="G281" t="s">
+        <v>855</v>
+      </c>
+      <c r="H281" t="s">
         <v>838</v>
       </c>
-      <c r="G281" t="s">
+      <c r="I281" t="s">
+        <v>856</v>
+      </c>
+      <c r="J281" t="s">
         <v>857</v>
       </c>
-      <c r="H281" t="s">
-        <v>840</v>
-      </c>
-      <c r="I281" t="s">
+      <c r="K281" t="s">
         <v>858</v>
-      </c>
-      <c r="J281" t="s">
-        <v>859</v>
-      </c>
-      <c r="K281" t="s">
-        <v>860</v>
       </c>
       <c r="L281">
         <v>0</v>
@@ -46355,31 +46357,31 @@
         <v>0</v>
       </c>
       <c r="C282" t="s">
+        <v>834</v>
+      </c>
+      <c r="D282" t="s">
+        <v>789</v>
+      </c>
+      <c r="E282" t="s">
+        <v>835</v>
+      </c>
+      <c r="F282" t="s">
         <v>836</v>
       </c>
-      <c r="D282" t="s">
-        <v>791</v>
-      </c>
-      <c r="E282" t="s">
-        <v>837</v>
-      </c>
-      <c r="F282" t="s">
+      <c r="G282" t="s">
+        <v>859</v>
+      </c>
+      <c r="H282" t="s">
         <v>838</v>
       </c>
-      <c r="G282" t="s">
+      <c r="I282" t="s">
+        <v>860</v>
+      </c>
+      <c r="J282" t="s">
         <v>861</v>
       </c>
-      <c r="H282" t="s">
-        <v>840</v>
-      </c>
-      <c r="I282" t="s">
+      <c r="K282" t="s">
         <v>862</v>
-      </c>
-      <c r="J282" t="s">
-        <v>863</v>
-      </c>
-      <c r="K282" t="s">
-        <v>864</v>
       </c>
       <c r="L282">
         <v>0</v>
@@ -46412,31 +46414,31 @@
         <v>0</v>
       </c>
       <c r="C283" t="s">
+        <v>834</v>
+      </c>
+      <c r="D283" t="s">
+        <v>791</v>
+      </c>
+      <c r="E283" t="s">
+        <v>835</v>
+      </c>
+      <c r="F283" t="s">
         <v>836</v>
       </c>
-      <c r="D283" t="s">
-        <v>793</v>
-      </c>
-      <c r="E283" t="s">
-        <v>837</v>
-      </c>
-      <c r="F283" t="s">
+      <c r="G283" t="s">
+        <v>863</v>
+      </c>
+      <c r="H283" t="s">
         <v>838</v>
       </c>
-      <c r="G283" t="s">
+      <c r="I283" t="s">
+        <v>864</v>
+      </c>
+      <c r="J283" t="s">
         <v>865</v>
       </c>
-      <c r="H283" t="s">
-        <v>840</v>
-      </c>
-      <c r="I283" t="s">
+      <c r="K283" t="s">
         <v>866</v>
-      </c>
-      <c r="J283" t="s">
-        <v>867</v>
-      </c>
-      <c r="K283" t="s">
-        <v>868</v>
       </c>
       <c r="L283">
         <v>0</v>
@@ -46469,34 +46471,34 @@
         <v>0</v>
       </c>
       <c r="C284" t="s">
+        <v>834</v>
+      </c>
+      <c r="D284" t="s">
+        <v>795</v>
+      </c>
+      <c r="E284" t="s">
+        <v>835</v>
+      </c>
+      <c r="F284" t="s">
         <v>836</v>
       </c>
-      <c r="D284" t="s">
-        <v>797</v>
-      </c>
-      <c r="E284" t="s">
-        <v>837</v>
-      </c>
-      <c r="F284" t="s">
+      <c r="G284" t="s">
+        <v>867</v>
+      </c>
+      <c r="H284" t="s">
         <v>838</v>
       </c>
-      <c r="G284" t="s">
+      <c r="I284" t="s">
+        <v>864</v>
+      </c>
+      <c r="J284" t="s">
+        <v>865</v>
+      </c>
+      <c r="K284" t="s">
+        <v>868</v>
+      </c>
+      <c r="L284" t="s">
         <v>869</v>
-      </c>
-      <c r="H284" t="s">
-        <v>840</v>
-      </c>
-      <c r="I284" t="s">
-        <v>866</v>
-      </c>
-      <c r="J284" t="s">
-        <v>867</v>
-      </c>
-      <c r="K284" t="s">
-        <v>870</v>
-      </c>
-      <c r="L284" t="s">
-        <v>871</v>
       </c>
       <c r="M284">
         <v>0</v>
@@ -46526,34 +46528,34 @@
         <v>0</v>
       </c>
       <c r="C285" t="s">
+        <v>834</v>
+      </c>
+      <c r="D285" t="s">
+        <v>799</v>
+      </c>
+      <c r="E285" t="s">
+        <v>835</v>
+      </c>
+      <c r="F285" t="s">
         <v>836</v>
       </c>
-      <c r="D285" t="s">
-        <v>801</v>
-      </c>
-      <c r="E285" t="s">
-        <v>837</v>
-      </c>
-      <c r="F285" t="s">
+      <c r="G285" t="s">
+        <v>870</v>
+      </c>
+      <c r="H285" t="s">
         <v>838</v>
       </c>
-      <c r="G285" t="s">
+      <c r="I285" t="s">
+        <v>864</v>
+      </c>
+      <c r="J285" t="s">
+        <v>865</v>
+      </c>
+      <c r="K285" t="s">
+        <v>871</v>
+      </c>
+      <c r="L285" t="s">
         <v>872</v>
-      </c>
-      <c r="H285" t="s">
-        <v>840</v>
-      </c>
-      <c r="I285" t="s">
-        <v>866</v>
-      </c>
-      <c r="J285" t="s">
-        <v>867</v>
-      </c>
-      <c r="K285" t="s">
-        <v>873</v>
-      </c>
-      <c r="L285" t="s">
-        <v>874</v>
       </c>
       <c r="M285">
         <v>0</v>
@@ -46583,34 +46585,34 @@
         <v>0</v>
       </c>
       <c r="C286" t="s">
+        <v>834</v>
+      </c>
+      <c r="D286" t="s">
+        <v>803</v>
+      </c>
+      <c r="E286" t="s">
+        <v>835</v>
+      </c>
+      <c r="F286" t="s">
         <v>836</v>
       </c>
-      <c r="D286" t="s">
-        <v>805</v>
-      </c>
-      <c r="E286" t="s">
-        <v>837</v>
-      </c>
-      <c r="F286" t="s">
+      <c r="G286" t="s">
+        <v>873</v>
+      </c>
+      <c r="H286" t="s">
         <v>838</v>
       </c>
-      <c r="G286" t="s">
+      <c r="I286" t="s">
+        <v>874</v>
+      </c>
+      <c r="J286" t="s">
         <v>875</v>
       </c>
-      <c r="H286" t="s">
-        <v>840</v>
-      </c>
-      <c r="I286" t="s">
+      <c r="K286" t="s">
         <v>876</v>
       </c>
-      <c r="J286" t="s">
+      <c r="L286" t="s">
         <v>877</v>
-      </c>
-      <c r="K286" t="s">
-        <v>878</v>
-      </c>
-      <c r="L286" t="s">
-        <v>879</v>
       </c>
       <c r="M286">
         <v>0</v>
@@ -46640,34 +46642,34 @@
         <v>0</v>
       </c>
       <c r="C287" t="s">
+        <v>834</v>
+      </c>
+      <c r="D287" t="s">
+        <v>807</v>
+      </c>
+      <c r="E287" t="s">
+        <v>835</v>
+      </c>
+      <c r="F287" t="s">
         <v>836</v>
       </c>
-      <c r="D287" t="s">
-        <v>809</v>
-      </c>
-      <c r="E287" t="s">
-        <v>837</v>
-      </c>
-      <c r="F287" t="s">
+      <c r="G287" t="s">
+        <v>878</v>
+      </c>
+      <c r="H287" t="s">
         <v>838</v>
       </c>
-      <c r="G287" t="s">
-        <v>880</v>
-      </c>
-      <c r="H287" t="s">
-        <v>840</v>
-      </c>
       <c r="I287" t="s">
+        <v>874</v>
+      </c>
+      <c r="J287" t="s">
+        <v>875</v>
+      </c>
+      <c r="K287" t="s">
         <v>876</v>
       </c>
-      <c r="J287" t="s">
-        <v>877</v>
-      </c>
-      <c r="K287" t="s">
-        <v>878</v>
-      </c>
       <c r="L287" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="M287">
         <v>0</v>
@@ -46697,34 +46699,34 @@
         <v>0</v>
       </c>
       <c r="C288" t="s">
+        <v>834</v>
+      </c>
+      <c r="D288" t="s">
+        <v>811</v>
+      </c>
+      <c r="E288" t="s">
+        <v>835</v>
+      </c>
+      <c r="F288" t="s">
         <v>836</v>
       </c>
-      <c r="D288" t="s">
-        <v>813</v>
-      </c>
-      <c r="E288" t="s">
-        <v>837</v>
-      </c>
-      <c r="F288" t="s">
+      <c r="G288" t="s">
+        <v>880</v>
+      </c>
+      <c r="H288" t="s">
         <v>838</v>
       </c>
-      <c r="G288" t="s">
-        <v>882</v>
-      </c>
-      <c r="H288" t="s">
-        <v>840</v>
-      </c>
       <c r="I288" t="s">
+        <v>874</v>
+      </c>
+      <c r="J288" t="s">
+        <v>875</v>
+      </c>
+      <c r="K288" t="s">
         <v>876</v>
       </c>
-      <c r="J288" t="s">
-        <v>877</v>
-      </c>
-      <c r="K288" t="s">
-        <v>878</v>
-      </c>
       <c r="L288" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="M288">
         <v>0</v>
@@ -46754,37 +46756,37 @@
         <v>0</v>
       </c>
       <c r="C289" t="s">
+        <v>834</v>
+      </c>
+      <c r="D289" t="s">
+        <v>815</v>
+      </c>
+      <c r="E289" t="s">
+        <v>835</v>
+      </c>
+      <c r="F289" t="s">
         <v>836</v>
       </c>
-      <c r="D289" t="s">
-        <v>817</v>
-      </c>
-      <c r="E289" t="s">
-        <v>837</v>
-      </c>
-      <c r="F289" t="s">
+      <c r="G289" t="s">
+        <v>882</v>
+      </c>
+      <c r="H289" t="s">
         <v>838</v>
       </c>
-      <c r="G289" t="s">
+      <c r="I289" t="s">
+        <v>874</v>
+      </c>
+      <c r="J289" t="s">
+        <v>883</v>
+      </c>
+      <c r="K289" t="s">
         <v>884</v>
       </c>
-      <c r="H289" t="s">
-        <v>840</v>
-      </c>
-      <c r="I289" t="s">
-        <v>876</v>
-      </c>
-      <c r="J289" t="s">
+      <c r="L289" t="s">
+        <v>877</v>
+      </c>
+      <c r="M289" t="s">
         <v>885</v>
-      </c>
-      <c r="K289" t="s">
-        <v>886</v>
-      </c>
-      <c r="L289" t="s">
-        <v>879</v>
-      </c>
-      <c r="M289" t="s">
-        <v>887</v>
       </c>
       <c r="N289">
         <v>0</v>
@@ -46811,37 +46813,37 @@
         <v>0</v>
       </c>
       <c r="C290" t="s">
+        <v>834</v>
+      </c>
+      <c r="D290" t="s">
+        <v>819</v>
+      </c>
+      <c r="E290" t="s">
+        <v>835</v>
+      </c>
+      <c r="F290" t="s">
         <v>836</v>
       </c>
-      <c r="D290" t="s">
-        <v>821</v>
-      </c>
-      <c r="E290" t="s">
-        <v>837</v>
-      </c>
-      <c r="F290" t="s">
+      <c r="G290" t="s">
+        <v>886</v>
+      </c>
+      <c r="H290" t="s">
         <v>838</v>
       </c>
-      <c r="G290" t="s">
-        <v>888</v>
-      </c>
-      <c r="H290" t="s">
-        <v>840</v>
-      </c>
       <c r="I290" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="J290" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="K290" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="L290" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="M290" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="N290">
         <v>0</v>
@@ -46868,37 +46870,37 @@
         <v>0</v>
       </c>
       <c r="C291" t="s">
+        <v>834</v>
+      </c>
+      <c r="D291" t="s">
+        <v>823</v>
+      </c>
+      <c r="E291" t="s">
+        <v>835</v>
+      </c>
+      <c r="F291" t="s">
         <v>836</v>
       </c>
-      <c r="D291" t="s">
-        <v>825</v>
-      </c>
-      <c r="E291" t="s">
-        <v>837</v>
-      </c>
-      <c r="F291" t="s">
+      <c r="G291" t="s">
+        <v>888</v>
+      </c>
+      <c r="H291" t="s">
         <v>838</v>
       </c>
-      <c r="G291" t="s">
-        <v>890</v>
-      </c>
-      <c r="H291" t="s">
-        <v>840</v>
-      </c>
       <c r="I291" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="J291" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="K291" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="L291" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="M291" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="N291">
         <v>0</v>
@@ -46925,40 +46927,40 @@
         <v>0</v>
       </c>
       <c r="C292" t="s">
+        <v>834</v>
+      </c>
+      <c r="D292" t="s">
+        <v>827</v>
+      </c>
+      <c r="E292" t="s">
+        <v>835</v>
+      </c>
+      <c r="F292" t="s">
         <v>836</v>
       </c>
-      <c r="D292" t="s">
-        <v>829</v>
-      </c>
-      <c r="E292" t="s">
-        <v>837</v>
-      </c>
-      <c r="F292" t="s">
+      <c r="G292" t="s">
+        <v>890</v>
+      </c>
+      <c r="H292" t="s">
         <v>838</v>
       </c>
-      <c r="G292" t="s">
-        <v>892</v>
-      </c>
-      <c r="H292" t="s">
-        <v>840</v>
-      </c>
       <c r="I292" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="J292" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="K292" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="L292" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="M292" t="s">
+        <v>889</v>
+      </c>
+      <c r="N292" t="s">
         <v>891</v>
-      </c>
-      <c r="N292" t="s">
-        <v>893</v>
       </c>
       <c r="O292">
         <v>0</v>
@@ -46982,43 +46984,43 @@
         <v>0</v>
       </c>
       <c r="C293" t="s">
+        <v>834</v>
+      </c>
+      <c r="D293" t="s">
+        <v>832</v>
+      </c>
+      <c r="E293" t="s">
+        <v>835</v>
+      </c>
+      <c r="F293" t="s">
         <v>836</v>
       </c>
-      <c r="D293" t="s">
-        <v>834</v>
-      </c>
-      <c r="E293" t="s">
-        <v>837</v>
-      </c>
-      <c r="F293" t="s">
+      <c r="G293" t="s">
+        <v>892</v>
+      </c>
+      <c r="H293" t="s">
         <v>838</v>
       </c>
-      <c r="G293" t="s">
+      <c r="I293" t="s">
+        <v>874</v>
+      </c>
+      <c r="J293" t="s">
+        <v>883</v>
+      </c>
+      <c r="K293" t="s">
+        <v>884</v>
+      </c>
+      <c r="L293" t="s">
+        <v>879</v>
+      </c>
+      <c r="M293" t="s">
+        <v>889</v>
+      </c>
+      <c r="N293" t="s">
+        <v>893</v>
+      </c>
+      <c r="O293" t="s">
         <v>894</v>
-      </c>
-      <c r="H293" t="s">
-        <v>840</v>
-      </c>
-      <c r="I293" t="s">
-        <v>876</v>
-      </c>
-      <c r="J293" t="s">
-        <v>885</v>
-      </c>
-      <c r="K293" t="s">
-        <v>886</v>
-      </c>
-      <c r="L293" t="s">
-        <v>881</v>
-      </c>
-      <c r="M293" t="s">
-        <v>891</v>
-      </c>
-      <c r="N293" t="s">
-        <v>895</v>
-      </c>
-      <c r="O293" t="s">
-        <v>896</v>
       </c>
       <c r="P293">
         <v>0</v>
@@ -47039,46 +47041,46 @@
         <v>0</v>
       </c>
       <c r="C294" t="s">
+        <v>834</v>
+      </c>
+      <c r="D294" t="s">
+        <v>833</v>
+      </c>
+      <c r="E294" t="s">
+        <v>835</v>
+      </c>
+      <c r="F294" t="s">
         <v>836</v>
       </c>
-      <c r="D294" t="s">
-        <v>835</v>
-      </c>
-      <c r="E294" t="s">
-        <v>837</v>
-      </c>
-      <c r="F294" t="s">
+      <c r="G294" t="s">
+        <v>895</v>
+      </c>
+      <c r="H294" t="s">
         <v>838</v>
       </c>
-      <c r="G294" t="s">
+      <c r="I294" t="s">
+        <v>874</v>
+      </c>
+      <c r="J294" t="s">
+        <v>883</v>
+      </c>
+      <c r="K294" t="s">
+        <v>884</v>
+      </c>
+      <c r="L294" t="s">
+        <v>879</v>
+      </c>
+      <c r="M294" t="s">
+        <v>889</v>
+      </c>
+      <c r="N294" t="s">
+        <v>896</v>
+      </c>
+      <c r="O294" t="s">
         <v>897</v>
       </c>
-      <c r="H294" t="s">
-        <v>840</v>
-      </c>
-      <c r="I294" t="s">
-        <v>876</v>
-      </c>
-      <c r="J294" t="s">
-        <v>885</v>
-      </c>
-      <c r="K294" t="s">
-        <v>886</v>
-      </c>
-      <c r="L294" t="s">
-        <v>881</v>
-      </c>
-      <c r="M294" t="s">
-        <v>891</v>
-      </c>
-      <c r="N294" t="s">
+      <c r="P294" t="s">
         <v>898</v>
-      </c>
-      <c r="O294" t="s">
-        <v>899</v>
-      </c>
-      <c r="P294" t="s">
-        <v>900</v>
       </c>
       <c r="Q294">
         <v>0</v>
@@ -47096,16 +47098,16 @@
         <v>0</v>
       </c>
       <c r="C295" t="s">
+        <v>899</v>
+      </c>
+      <c r="D295" t="s">
+        <v>900</v>
+      </c>
+      <c r="E295" t="s">
         <v>901</v>
       </c>
-      <c r="D295" t="s">
+      <c r="F295" t="s">
         <v>902</v>
-      </c>
-      <c r="E295" t="s">
-        <v>903</v>
-      </c>
-      <c r="F295" t="s">
-        <v>904</v>
       </c>
       <c r="G295">
         <v>0</v>
@@ -47153,16 +47155,16 @@
         <v>0</v>
       </c>
       <c r="C296" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="D296" t="s">
+        <v>903</v>
+      </c>
+      <c r="E296" t="s">
+        <v>904</v>
+      </c>
+      <c r="F296" t="s">
         <v>905</v>
-      </c>
-      <c r="E296" t="s">
-        <v>906</v>
-      </c>
-      <c r="F296" t="s">
-        <v>907</v>
       </c>
       <c r="G296">
         <v>0.1</v>
@@ -47210,16 +47212,16 @@
         <v>0</v>
       </c>
       <c r="C297" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="D297" t="s">
+        <v>906</v>
+      </c>
+      <c r="E297" t="s">
+        <v>907</v>
+      </c>
+      <c r="F297" t="s">
         <v>908</v>
-      </c>
-      <c r="E297" t="s">
-        <v>909</v>
-      </c>
-      <c r="F297" t="s">
-        <v>910</v>
       </c>
       <c r="G297">
         <v>0</v>
@@ -47267,16 +47269,16 @@
         <v>0</v>
       </c>
       <c r="C298" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="D298" t="s">
+        <v>909</v>
+      </c>
+      <c r="E298" t="s">
+        <v>910</v>
+      </c>
+      <c r="F298" t="s">
         <v>911</v>
-      </c>
-      <c r="E298" t="s">
-        <v>912</v>
-      </c>
-      <c r="F298" t="s">
-        <v>913</v>
       </c>
       <c r="G298">
         <v>0</v>
@@ -47324,16 +47326,16 @@
         <v>0</v>
       </c>
       <c r="C299" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="D299" t="s">
+        <v>912</v>
+      </c>
+      <c r="E299" t="s">
+        <v>913</v>
+      </c>
+      <c r="F299" t="s">
         <v>914</v>
-      </c>
-      <c r="E299" t="s">
-        <v>915</v>
-      </c>
-      <c r="F299" t="s">
-        <v>916</v>
       </c>
       <c r="G299">
         <v>0</v>
@@ -47381,16 +47383,16 @@
         <v>0</v>
       </c>
       <c r="C300" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="D300" t="s">
+        <v>915</v>
+      </c>
+      <c r="E300" t="s">
+        <v>916</v>
+      </c>
+      <c r="F300" t="s">
         <v>917</v>
-      </c>
-      <c r="E300" t="s">
-        <v>918</v>
-      </c>
-      <c r="F300" t="s">
-        <v>919</v>
       </c>
       <c r="G300">
         <v>0.4</v>
@@ -47438,16 +47440,16 @@
         <v>0</v>
       </c>
       <c r="C301" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="D301" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="F301" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="G301">
         <v>1000</v>
@@ -47495,16 +47497,16 @@
         <v>0</v>
       </c>
       <c r="C302" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="D302" t="s">
+        <v>919</v>
+      </c>
+      <c r="E302" t="s">
+        <v>920</v>
+      </c>
+      <c r="F302" t="s">
         <v>921</v>
-      </c>
-      <c r="E302" t="s">
-        <v>922</v>
-      </c>
-      <c r="F302" t="s">
-        <v>923</v>
       </c>
       <c r="G302">
         <v>0</v>
@@ -47552,16 +47554,16 @@
         <v>0</v>
       </c>
       <c r="C303" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="D303" t="s">
+        <v>922</v>
+      </c>
+      <c r="E303" t="s">
+        <v>923</v>
+      </c>
+      <c r="F303" t="s">
         <v>924</v>
-      </c>
-      <c r="E303" t="s">
-        <v>925</v>
-      </c>
-      <c r="F303" t="s">
-        <v>926</v>
       </c>
       <c r="G303">
         <v>30</v>
@@ -47609,16 +47611,16 @@
         <v>0</v>
       </c>
       <c r="C304" t="s">
+        <v>925</v>
+      </c>
+      <c r="D304" t="s">
+        <v>926</v>
+      </c>
+      <c r="E304" t="s">
         <v>927</v>
       </c>
-      <c r="D304" t="s">
+      <c r="F304" t="s">
         <v>928</v>
-      </c>
-      <c r="E304" t="s">
-        <v>929</v>
-      </c>
-      <c r="F304" t="s">
-        <v>930</v>
       </c>
       <c r="G304">
         <v>0.75</v>
@@ -47666,13 +47668,13 @@
         <v>0</v>
       </c>
       <c r="C305" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="D305" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="E305" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="F305">
         <v>0</v>
@@ -47723,16 +47725,16 @@
         <v>0</v>
       </c>
       <c r="C306" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="D306" t="s">
+        <v>931</v>
+      </c>
+      <c r="E306" t="s">
+        <v>932</v>
+      </c>
+      <c r="F306" t="s">
         <v>933</v>
-      </c>
-      <c r="E306" t="s">
-        <v>934</v>
-      </c>
-      <c r="F306" t="s">
-        <v>935</v>
       </c>
       <c r="G306">
         <v>45</v>
@@ -47780,16 +47782,16 @@
         <v>0</v>
       </c>
       <c r="C307" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="D307" t="s">
+        <v>934</v>
+      </c>
+      <c r="E307" t="s">
+        <v>935</v>
+      </c>
+      <c r="F307" t="s">
         <v>936</v>
-      </c>
-      <c r="E307" t="s">
-        <v>937</v>
-      </c>
-      <c r="F307" t="s">
-        <v>938</v>
       </c>
       <c r="G307">
         <v>0</v>
@@ -47837,16 +47839,16 @@
         <v>0</v>
       </c>
       <c r="C308" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="D308" t="s">
+        <v>937</v>
+      </c>
+      <c r="E308" t="s">
+        <v>938</v>
+      </c>
+      <c r="F308" t="s">
         <v>939</v>
-      </c>
-      <c r="E308" t="s">
-        <v>940</v>
-      </c>
-      <c r="F308" t="s">
-        <v>941</v>
       </c>
       <c r="G308">
         <v>0.1</v>
@@ -47894,16 +47896,16 @@
         <v>0</v>
       </c>
       <c r="C309" t="s">
+        <v>940</v>
+      </c>
+      <c r="D309" t="s">
+        <v>941</v>
+      </c>
+      <c r="E309" t="s">
         <v>942</v>
       </c>
-      <c r="D309" t="s">
+      <c r="F309" t="s">
         <v>943</v>
-      </c>
-      <c r="E309" t="s">
-        <v>944</v>
-      </c>
-      <c r="F309" t="s">
-        <v>945</v>
       </c>
       <c r="G309">
         <v>24</v>
@@ -47951,16 +47953,16 @@
         <v>0</v>
       </c>
       <c r="C310" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="D310" t="s">
+        <v>944</v>
+      </c>
+      <c r="E310" t="s">
+        <v>945</v>
+      </c>
+      <c r="F310" t="s">
         <v>946</v>
-      </c>
-      <c r="E310" t="s">
-        <v>947</v>
-      </c>
-      <c r="F310" t="s">
-        <v>948</v>
       </c>
       <c r="G310">
         <v>10</v>
@@ -48008,16 +48010,16 @@
         <v>0</v>
       </c>
       <c r="C311" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="D311" t="s">
+        <v>947</v>
+      </c>
+      <c r="E311" t="s">
+        <v>948</v>
+      </c>
+      <c r="F311" t="s">
         <v>949</v>
-      </c>
-      <c r="E311" t="s">
-        <v>950</v>
-      </c>
-      <c r="F311" t="s">
-        <v>951</v>
       </c>
       <c r="G311">
         <v>20</v>
@@ -48065,16 +48067,16 @@
         <v>0</v>
       </c>
       <c r="C312" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="D312" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="E312" t="s">
         <v>39</v>
       </c>
       <c r="F312" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="G312">
         <v>1</v>
@@ -48122,16 +48124,16 @@
         <v>0</v>
       </c>
       <c r="C313" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="D313" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="E313" t="s">
         <v>39</v>
       </c>
       <c r="F313" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="G313">
         <v>1.35</v>
@@ -48179,16 +48181,16 @@
         <v>0</v>
       </c>
       <c r="C314" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="D314" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="E314" t="s">
         <v>39</v>
       </c>
       <c r="F314" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="G314">
         <v>1.75</v>
@@ -48236,16 +48238,16 @@
         <v>0</v>
       </c>
       <c r="C315" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="D315" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="E315" t="s">
         <v>39</v>
       </c>
       <c r="F315" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="G315">
         <v>2.2999999999999998</v>
@@ -48293,16 +48295,16 @@
         <v>0</v>
       </c>
       <c r="C316" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="D316" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="E316" t="s">
         <v>39</v>
       </c>
       <c r="F316" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="G316">
         <v>3</v>
@@ -48350,16 +48352,16 @@
         <v>0</v>
       </c>
       <c r="C317" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="D317" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="E317" t="s">
         <v>39</v>
       </c>
       <c r="F317" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="G317">
         <v>4</v>
@@ -48407,16 +48409,16 @@
         <v>0</v>
       </c>
       <c r="C318" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="D318" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="E318" t="s">
         <v>39</v>
       </c>
       <c r="F318" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="G318">
         <v>5.2</v>
@@ -48464,16 +48466,16 @@
         <v>0</v>
       </c>
       <c r="C319" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="D319" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="E319" t="s">
         <v>39</v>
       </c>
       <c r="F319" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="G319">
         <v>6.8</v>
@@ -48521,16 +48523,16 @@
         <v>0</v>
       </c>
       <c r="C320" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="D320" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="E320" t="s">
         <v>39</v>
       </c>
       <c r="F320" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="G320">
         <v>10.199999999999999</v>
@@ -48578,22 +48580,22 @@
         <v>0</v>
       </c>
       <c r="C321" t="s">
+        <v>961</v>
+      </c>
+      <c r="D321" t="s">
+        <v>962</v>
+      </c>
+      <c r="E321" t="s">
         <v>963</v>
       </c>
-      <c r="D321" t="s">
+      <c r="F321" t="s">
         <v>964</v>
-      </c>
-      <c r="E321" t="s">
-        <v>965</v>
-      </c>
-      <c r="F321" t="s">
-        <v>966</v>
       </c>
       <c r="G321">
         <v>25</v>
       </c>
       <c r="H321" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="I321">
         <v>0</v>
@@ -48635,22 +48637,22 @@
         <v>0</v>
       </c>
       <c r="C322" t="s">
+        <v>961</v>
+      </c>
+      <c r="D322" t="s">
+        <v>966</v>
+      </c>
+      <c r="E322" t="s">
         <v>963</v>
       </c>
-      <c r="D322" t="s">
-        <v>968</v>
-      </c>
-      <c r="E322" t="s">
-        <v>965</v>
-      </c>
       <c r="F322" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="G322">
         <v>20</v>
       </c>
       <c r="H322" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="I322">
         <v>0</v>
@@ -48692,22 +48694,22 @@
         <v>0</v>
       </c>
       <c r="C323" t="s">
+        <v>961</v>
+      </c>
+      <c r="D323" t="s">
+        <v>968</v>
+      </c>
+      <c r="E323" t="s">
         <v>963</v>
       </c>
-      <c r="D323" t="s">
-        <v>970</v>
-      </c>
-      <c r="E323" t="s">
-        <v>965</v>
-      </c>
       <c r="F323" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="G323">
         <v>25</v>
       </c>
       <c r="H323" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="I323">
         <v>0</v>
@@ -48749,22 +48751,22 @@
         <v>0</v>
       </c>
       <c r="C324" t="s">
+        <v>961</v>
+      </c>
+      <c r="D324" t="s">
+        <v>970</v>
+      </c>
+      <c r="E324" t="s">
         <v>963</v>
       </c>
-      <c r="D324" t="s">
-        <v>972</v>
-      </c>
-      <c r="E324" t="s">
-        <v>965</v>
-      </c>
       <c r="F324" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="G324">
         <v>20</v>
       </c>
       <c r="H324" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="I324">
         <v>0</v>
@@ -48806,22 +48808,22 @@
         <v>0</v>
       </c>
       <c r="C325" t="s">
+        <v>961</v>
+      </c>
+      <c r="D325" t="s">
+        <v>972</v>
+      </c>
+      <c r="E325" t="s">
         <v>963</v>
       </c>
-      <c r="D325" t="s">
-        <v>974</v>
-      </c>
-      <c r="E325" t="s">
-        <v>965</v>
-      </c>
       <c r="F325" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="G325">
         <v>0.4</v>
       </c>
       <c r="H325" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="I325">
         <v>0</v>
@@ -48863,22 +48865,22 @@
         <v>0</v>
       </c>
       <c r="C326" t="s">
+        <v>961</v>
+      </c>
+      <c r="D326" t="s">
+        <v>974</v>
+      </c>
+      <c r="E326" t="s">
         <v>963</v>
       </c>
-      <c r="D326" t="s">
-        <v>976</v>
-      </c>
-      <c r="E326" t="s">
-        <v>965</v>
-      </c>
       <c r="F326" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="G326">
         <v>3</v>
       </c>
       <c r="H326" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="I326">
         <v>0</v>
@@ -48920,22 +48922,22 @@
         <v>0</v>
       </c>
       <c r="C327" t="s">
+        <v>961</v>
+      </c>
+      <c r="D327" t="s">
+        <v>976</v>
+      </c>
+      <c r="E327" t="s">
         <v>963</v>
       </c>
-      <c r="D327" t="s">
-        <v>978</v>
-      </c>
-      <c r="E327" t="s">
-        <v>965</v>
-      </c>
       <c r="F327" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="G327">
         <v>1.5</v>
       </c>
       <c r="H327" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="I327">
         <v>0</v>
@@ -48977,22 +48979,22 @@
         <v>0</v>
       </c>
       <c r="C328" t="s">
+        <v>961</v>
+      </c>
+      <c r="D328" t="s">
+        <v>978</v>
+      </c>
+      <c r="E328" t="s">
         <v>963</v>
       </c>
-      <c r="D328" t="s">
-        <v>980</v>
-      </c>
-      <c r="E328" t="s">
-        <v>965</v>
-      </c>
       <c r="F328" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="G328">
         <v>0.15</v>
       </c>
       <c r="H328" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="I328">
         <v>0</v>
@@ -49034,22 +49036,22 @@
         <v>0</v>
       </c>
       <c r="C329" t="s">
+        <v>961</v>
+      </c>
+      <c r="D329" t="s">
+        <v>980</v>
+      </c>
+      <c r="E329" t="s">
         <v>963</v>
       </c>
-      <c r="D329" t="s">
-        <v>982</v>
-      </c>
-      <c r="E329" t="s">
-        <v>965</v>
-      </c>
       <c r="F329" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="G329">
         <v>0.5</v>
       </c>
       <c r="H329" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="I329">
         <v>0</v>
@@ -49091,22 +49093,22 @@
         <v>0</v>
       </c>
       <c r="C330" t="s">
+        <v>961</v>
+      </c>
+      <c r="D330" t="s">
+        <v>982</v>
+      </c>
+      <c r="E330" t="s">
         <v>963</v>
       </c>
-      <c r="D330" t="s">
-        <v>984</v>
-      </c>
-      <c r="E330" t="s">
-        <v>965</v>
-      </c>
       <c r="F330" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="G330">
         <v>25</v>
       </c>
       <c r="H330" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="I330">
         <v>0</v>
@@ -49148,22 +49150,22 @@
         <v>0</v>
       </c>
       <c r="C331" t="s">
+        <v>961</v>
+      </c>
+      <c r="D331" t="s">
+        <v>984</v>
+      </c>
+      <c r="E331" t="s">
         <v>963</v>
       </c>
-      <c r="D331" t="s">
-        <v>986</v>
-      </c>
-      <c r="E331" t="s">
-        <v>965</v>
-      </c>
       <c r="F331" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="G331">
         <v>8</v>
       </c>
       <c r="H331" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="I331">
         <v>0</v>
@@ -49205,22 +49207,22 @@
         <v>0</v>
       </c>
       <c r="C332" t="s">
+        <v>961</v>
+      </c>
+      <c r="D332" t="s">
+        <v>987</v>
+      </c>
+      <c r="E332" t="s">
         <v>963</v>
       </c>
-      <c r="D332" t="s">
-        <v>989</v>
-      </c>
-      <c r="E332" t="s">
-        <v>965</v>
-      </c>
       <c r="F332" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="G332">
         <v>15</v>
       </c>
       <c r="H332" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="I332">
         <v>0</v>
@@ -49262,16 +49264,16 @@
         <v>0</v>
       </c>
       <c r="C333" t="s">
+        <v>989</v>
+      </c>
+      <c r="D333" t="s">
+        <v>990</v>
+      </c>
+      <c r="E333" t="s">
         <v>991</v>
       </c>
-      <c r="D333" t="s">
+      <c r="F333" t="s">
         <v>992</v>
-      </c>
-      <c r="E333" t="s">
-        <v>993</v>
-      </c>
-      <c r="F333" t="s">
-        <v>994</v>
       </c>
       <c r="G333">
         <v>0.8</v>
@@ -49319,16 +49321,16 @@
         <v>0</v>
       </c>
       <c r="C334" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="D334" t="s">
+        <v>993</v>
+      </c>
+      <c r="E334" t="s">
+        <v>994</v>
+      </c>
+      <c r="F334" t="s">
         <v>995</v>
-      </c>
-      <c r="E334" t="s">
-        <v>996</v>
-      </c>
-      <c r="F334" t="s">
-        <v>997</v>
       </c>
       <c r="G334">
         <v>3</v>
@@ -49376,16 +49378,16 @@
         <v>0</v>
       </c>
       <c r="C335" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="D335" t="s">
+        <v>996</v>
+      </c>
+      <c r="E335" t="s">
+        <v>997</v>
+      </c>
+      <c r="F335" t="s">
         <v>998</v>
-      </c>
-      <c r="E335" t="s">
-        <v>999</v>
-      </c>
-      <c r="F335" t="s">
-        <v>1000</v>
       </c>
       <c r="G335">
         <v>7</v>
@@ -49433,16 +49435,16 @@
         <v>0</v>
       </c>
       <c r="C336" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="D336" t="s">
+        <v>999</v>
+      </c>
+      <c r="E336" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F336" t="s">
         <v>1001</v>
-      </c>
-      <c r="E336" t="s">
-        <v>1002</v>
-      </c>
-      <c r="F336" t="s">
-        <v>1003</v>
       </c>
       <c r="G336">
         <v>10</v>
@@ -49490,16 +49492,16 @@
         <v>0</v>
       </c>
       <c r="C337" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="D337" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E337" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F337" t="s">
         <v>1004</v>
-      </c>
-      <c r="E337" t="s">
-        <v>1005</v>
-      </c>
-      <c r="F337" t="s">
-        <v>1006</v>
       </c>
       <c r="G337">
         <v>2</v>
@@ -49547,16 +49549,16 @@
         <v>0</v>
       </c>
       <c r="C338" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="D338" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E338" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F338" t="s">
         <v>1007</v>
-      </c>
-      <c r="E338" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F338" t="s">
-        <v>1009</v>
       </c>
       <c r="G338">
         <v>5</v>
@@ -49604,16 +49606,16 @@
         <v>0</v>
       </c>
       <c r="C339" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="D339" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E339" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F339" t="s">
         <v>1010</v>
-      </c>
-      <c r="E339" t="s">
-        <v>1011</v>
-      </c>
-      <c r="F339" t="s">
-        <v>1012</v>
       </c>
       <c r="G339">
         <v>10</v>
@@ -49661,16 +49663,16 @@
         <v>0</v>
       </c>
       <c r="C340" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="D340" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="E340" t="s">
         <v>39</v>
       </c>
       <c r="F340" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G340">
         <v>15.3</v>
@@ -49718,16 +49720,16 @@
         <v>0</v>
       </c>
       <c r="C341" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="D341" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="E341" t="s">
         <v>39</v>
       </c>
       <c r="F341" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="G341">
         <v>22.95</v>
@@ -49775,16 +49777,16 @@
         <v>0</v>
       </c>
       <c r="C342" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D342" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E342" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F342" t="s">
         <v>1016</v>
-      </c>
-      <c r="E342" t="s">
-        <v>1017</v>
-      </c>
-      <c r="F342" t="s">
-        <v>1018</v>
       </c>
       <c r="G342">
         <v>20</v>
@@ -49832,16 +49834,16 @@
         <v>0</v>
       </c>
       <c r="C343" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D343" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E343" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F343" t="s">
         <v>1019</v>
-      </c>
-      <c r="E343" t="s">
-        <v>1020</v>
-      </c>
-      <c r="F343" t="s">
-        <v>1021</v>
       </c>
       <c r="G343">
         <v>500000000</v>
@@ -49889,16 +49891,16 @@
         <v>0</v>
       </c>
       <c r="C344" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D344" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E344" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F344" t="s">
         <v>1022</v>
-      </c>
-      <c r="E344" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F344" t="s">
-        <v>1024</v>
       </c>
       <c r="G344">
         <v>13</v>
@@ -49949,13 +49951,13 @@
         <v>18</v>
       </c>
       <c r="D345" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="F345" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="G345">
         <v>30</v>
@@ -50006,13 +50008,13 @@
         <v>18</v>
       </c>
       <c r="D346" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E346" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F346" t="s">
         <v>1027</v>
-      </c>
-      <c r="E346" t="s">
-        <v>1028</v>
-      </c>
-      <c r="F346" t="s">
-        <v>1029</v>
       </c>
       <c r="G346">
         <v>1000</v>
@@ -50060,16 +50062,16 @@
         <v>0</v>
       </c>
       <c r="C347" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="D347" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E347" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F347" t="s">
         <v>1030</v>
-      </c>
-      <c r="E347" t="s">
-        <v>1031</v>
-      </c>
-      <c r="F347" t="s">
-        <v>1032</v>
       </c>
       <c r="G347">
         <v>50000</v>
@@ -50117,16 +50119,16 @@
         <v>0</v>
       </c>
       <c r="C348" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="D348" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E348" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F348" t="s">
         <v>1033</v>
-      </c>
-      <c r="E348" t="s">
-        <v>1034</v>
-      </c>
-      <c r="F348" t="s">
-        <v>1035</v>
       </c>
       <c r="G348">
         <v>10</v>
@@ -50174,16 +50176,16 @@
         <v>0</v>
       </c>
       <c r="C349" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="D349" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E349" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F349" t="s">
         <v>1036</v>
-      </c>
-      <c r="E349" t="s">
-        <v>1037</v>
-      </c>
-      <c r="F349" t="s">
-        <v>1038</v>
       </c>
       <c r="G349">
         <v>75</v>
@@ -50231,16 +50233,16 @@
         <v>0</v>
       </c>
       <c r="C350" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="D350" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E350" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F350" t="s">
         <v>1039</v>
-      </c>
-      <c r="E350" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F350" t="s">
-        <v>1041</v>
       </c>
       <c r="G350">
         <v>25</v>
@@ -50288,16 +50290,16 @@
         <v>0</v>
       </c>
       <c r="C351" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="D351" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="E351" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="F351" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="G351">
         <v>5</v>
@@ -50345,16 +50347,16 @@
         <v>0</v>
       </c>
       <c r="C352" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="D352" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E352" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F352" t="s">
         <v>1044</v>
-      </c>
-      <c r="E352" t="s">
-        <v>1045</v>
-      </c>
-      <c r="F352" t="s">
-        <v>1046</v>
       </c>
       <c r="G352">
         <v>0.6</v>
@@ -50402,16 +50404,16 @@
         <v>0</v>
       </c>
       <c r="C353" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D353" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E353" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F353" t="s">
         <v>1047</v>
-      </c>
-      <c r="E353" t="s">
-        <v>1048</v>
-      </c>
-      <c r="F353" t="s">
-        <v>1049</v>
       </c>
       <c r="G353">
         <v>0.1</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DAABF8-E1EA-4E4E-8CA7-69DC9BCBAC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D45562C-4139-4C3A-8762-184536822EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3767,10 +3767,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{20~99=10}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>{150~199=15}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3779,7 +3775,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>{1~19=7}</t>
+    <t>{1~19=0}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{20~99=5}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -15542,11 +15542,11 @@
       </c>
       <c r="G154" t="str">
         <f>計算表!G154</f>
-        <v>{1~19=7}</v>
+        <v>{1~19=0}</v>
       </c>
       <c r="H154" t="str">
         <f>計算表!H154</f>
-        <v>{20~99=10}</v>
+        <v>{20~99=5}</v>
       </c>
       <c r="I154" t="str">
         <f>計算表!I154</f>
@@ -39073,16 +39073,16 @@
         <v>424</v>
       </c>
       <c r="G154" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H154" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="H154" s="2" t="s">
+      <c r="I154" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="J154" s="2" t="s">
         <v>1082</v>
-      </c>
-      <c r="I154" s="2" t="s">
-        <v>1084</v>
-      </c>
-      <c r="J154" s="2" t="s">
-        <v>1083</v>
       </c>
       <c r="K154" t="s">
         <v>443</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D45562C-4139-4C3A-8762-184536822EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF647FC-D46A-4574-9473-337A072D8B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10662,7 +10662,7 @@
       </c>
       <c r="H88">
         <f>計算表!H88</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I88">
         <f>計算表!I88</f>
@@ -10732,11 +10732,11 @@
       </c>
       <c r="G89">
         <f>計算表!G89</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H89">
         <f>計算表!H89</f>
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I89">
         <f>計算表!I89</f>
@@ -29754,7 +29754,7 @@
       </c>
       <c r="H346">
         <f>計算表!H346</f>
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="I346">
         <f>計算表!I346</f>
@@ -35314,7 +35314,7 @@
         <v>20</v>
       </c>
       <c r="H88">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I88">
         <v>1.06</v>
@@ -35368,10 +35368,10 @@
         <v>255</v>
       </c>
       <c r="G89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H89">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I89">
         <v>1.0549999999999999</v>
@@ -50020,7 +50020,7 @@
         <v>1000</v>
       </c>
       <c r="H346">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="I346">
         <v>0</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF647FC-D46A-4574-9473-337A072D8B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6180D24-7589-41EB-A7CB-83B2E29CFDD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="H29">
         <f>計算表!H29</f>
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I29">
         <f>計算表!I29</f>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="G30">
         <f>計算表!G30</f>
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="H30">
         <f>計算表!H30</f>
@@ -11398,23 +11398,23 @@
       </c>
       <c r="G98">
         <f>計算表!G98</f>
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="H98">
         <f>計算表!H98</f>
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="I98">
         <f>計算表!I98</f>
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J98">
         <f>計算表!J98</f>
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K98">
         <f>計算表!K98</f>
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L98">
         <f>計算表!L98</f>
@@ -11472,11 +11472,11 @@
       </c>
       <c r="G99">
         <f>計算表!G99</f>
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="H99">
         <f>計算表!H99</f>
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="I99">
         <f>計算表!I99</f>
@@ -31951,7 +31951,7 @@
         <v>500</v>
       </c>
       <c r="H29">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I29">
         <v>10</v>
@@ -32005,7 +32005,7 @@
         <v>109</v>
       </c>
       <c r="G30">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="H30">
         <v>2</v>
@@ -35881,19 +35881,19 @@
         <v>285</v>
       </c>
       <c r="G98">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="H98">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="I98">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J98">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K98">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L98">
         <v>0</v>
@@ -35938,10 +35938,10 @@
         <v>285</v>
       </c>
       <c r="G99">
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="H99">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="I99">
         <v>1.5</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6180D24-7589-41EB-A7CB-83B2E29CFDD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0926D46B-B453-4CCE-AB9C-F0350BF68FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="1086">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1893" uniqueCount="1088">
   <si>
     <t>編號</t>
   </si>
@@ -1375,9 +1375,6 @@
   </si>
   <si>
     <t>史詩裝備</t>
-  </si>
-  <si>
-    <t>{50~99=0.5}</t>
   </si>
   <si>
     <t>{100~149=2.5}</t>
@@ -3780,6 +3777,18 @@
   </si>
   <si>
     <t>{20~99=5}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{1~39=0}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{40~49=1.5}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{50~99=1}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -15616,35 +15625,35 @@
       </c>
       <c r="G155" t="str">
         <f>計算表!G155</f>
-        <v>{1~49=0}</v>
+        <v>{1~39=0}</v>
       </c>
       <c r="H155" t="str">
         <f>計算表!H155</f>
-        <v>{50~99=0.5}</v>
+        <v>{40~49=1.5}</v>
       </c>
       <c r="I155" t="str">
         <f>計算表!I155</f>
-        <v>{100~149=2.5}</v>
+        <v>{50~99=1}</v>
       </c>
       <c r="J155" t="str">
         <f>計算表!J155</f>
-        <v>{150~199=5}</v>
+        <v>{100~149=2.5}</v>
       </c>
       <c r="K155" t="str">
         <f>計算表!K155</f>
-        <v>{200~249=6}</v>
+        <v>{150~199=5}</v>
       </c>
       <c r="L155" t="str">
         <f>計算表!L155</f>
-        <v>{250~299=7}</v>
+        <v>{200~249=6}</v>
       </c>
       <c r="M155" t="str">
         <f>計算表!M155</f>
+        <v>{250~299=7}</v>
+      </c>
+      <c r="N155" t="str">
+        <f>計算表!N155</f>
         <v>{300+=8}</v>
-      </c>
-      <c r="N155">
-        <f>計算表!N155</f>
-        <v>0</v>
       </c>
       <c r="O155">
         <f>計算表!O155</f>
@@ -32740,10 +32749,10 @@
         <v>145</v>
       </c>
       <c r="E43" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>1055</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>1056</v>
       </c>
       <c r="G43">
         <v>2</v>
@@ -34504,13 +34513,13 @@
         <v>191</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="E74" t="s">
         <v>216</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="G74">
         <v>12</v>
@@ -36208,13 +36217,13 @@
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C104" t="s">
         <v>291</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="E104" t="s">
         <v>293</v>
@@ -36223,7 +36232,7 @@
         <v>294</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="H104" t="s">
         <v>310</v>
@@ -36265,13 +36274,13 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C105" t="s">
         <v>291</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E105" t="s">
         <v>293</v>
@@ -36280,13 +36289,13 @@
         <v>294</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>310</v>
       </c>
       <c r="I105" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -36322,13 +36331,13 @@
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C106" t="s">
         <v>291</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E106" t="s">
         <v>293</v>
@@ -36337,16 +36346,16 @@
         <v>294</v>
       </c>
       <c r="G106" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="H106" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="H106" s="2" t="s">
+      <c r="I106" s="2" t="s">
         <v>1069</v>
       </c>
-      <c r="I106" s="2" t="s">
+      <c r="J106" t="s">
         <v>1070</v>
-      </c>
-      <c r="J106" t="s">
-        <v>1071</v>
       </c>
       <c r="K106">
         <v>0</v>
@@ -36379,13 +36388,13 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C107" t="s">
         <v>291</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="E107" t="s">
         <v>293</v>
@@ -36394,16 +36403,16 @@
         <v>294</v>
       </c>
       <c r="G107" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="H107" s="2" t="s">
         <v>1072</v>
       </c>
-      <c r="H107" s="2" t="s">
+      <c r="I107" s="2" t="s">
         <v>1073</v>
       </c>
-      <c r="I107" s="2" t="s">
+      <c r="J107" s="2" t="s">
         <v>1074</v>
-      </c>
-      <c r="J107" s="2" t="s">
-        <v>1075</v>
       </c>
       <c r="K107">
         <v>0</v>
@@ -36436,13 +36445,13 @@
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C108" t="s">
         <v>291</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="E108" t="s">
         <v>293</v>
@@ -36451,19 +36460,19 @@
         <v>294</v>
       </c>
       <c r="G108" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H108" s="2" t="s">
         <v>1076</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>1077</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>297</v>
       </c>
       <c r="J108" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="K108" s="2" t="s">
         <v>1078</v>
-      </c>
-      <c r="K108" s="2" t="s">
-        <v>1079</v>
       </c>
       <c r="L108">
         <v>0</v>
@@ -38902,10 +38911,10 @@
         <v>424</v>
       </c>
       <c r="G151" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="H151" s="2" t="s">
         <v>1058</v>
-      </c>
-      <c r="H151" s="2" t="s">
-        <v>1059</v>
       </c>
       <c r="I151" t="s">
         <v>425</v>
@@ -38959,10 +38968,10 @@
         <v>424</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="I152" t="s">
         <v>431</v>
@@ -39016,13 +39025,13 @@
         <v>424</v>
       </c>
       <c r="G153" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H153" s="2" t="s">
         <v>1062</v>
       </c>
-      <c r="H153" s="2" t="s">
-        <v>1063</v>
-      </c>
       <c r="I153" s="2" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="J153" t="s">
         <v>437</v>
@@ -39073,16 +39082,16 @@
         <v>424</v>
       </c>
       <c r="G154" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="H154" s="2" t="s">
         <v>1084</v>
       </c>
-      <c r="H154" s="2" t="s">
-        <v>1085</v>
-      </c>
       <c r="I154" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="K154" t="s">
         <v>443</v>
@@ -39129,29 +39138,29 @@
       <c r="F155" t="s">
         <v>424</v>
       </c>
-      <c r="G155" t="s">
-        <v>442</v>
-      </c>
-      <c r="H155" t="s">
+      <c r="G155" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="J155" t="s">
         <v>447</v>
       </c>
-      <c r="I155" t="s">
+      <c r="K155" t="s">
         <v>448</v>
       </c>
-      <c r="J155" t="s">
+      <c r="L155" t="s">
         <v>449</v>
       </c>
-      <c r="K155" t="s">
+      <c r="M155" t="s">
         <v>450</v>
       </c>
-      <c r="L155" t="s">
+      <c r="N155" t="s">
         <v>451</v>
-      </c>
-      <c r="M155" t="s">
-        <v>452</v>
-      </c>
-      <c r="N155">
-        <v>0</v>
       </c>
       <c r="O155">
         <v>0</v>
@@ -39178,7 +39187,7 @@
         <v>421</v>
       </c>
       <c r="D156" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E156" t="s">
         <v>423</v>
@@ -39190,22 +39199,22 @@
         <v>442</v>
       </c>
       <c r="H156" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I156" t="s">
         <v>266</v>
       </c>
       <c r="J156" t="s">
+        <v>454</v>
+      </c>
+      <c r="K156" t="s">
         <v>455</v>
       </c>
-      <c r="K156" t="s">
+      <c r="L156" t="s">
         <v>456</v>
       </c>
-      <c r="L156" t="s">
+      <c r="M156" t="s">
         <v>457</v>
-      </c>
-      <c r="M156" t="s">
-        <v>458</v>
       </c>
       <c r="N156">
         <v>0</v>
@@ -39235,7 +39244,7 @@
         <v>421</v>
       </c>
       <c r="D157" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E157" t="s">
         <v>423</v>
@@ -39247,22 +39256,22 @@
         <v>442</v>
       </c>
       <c r="H157" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I157" t="s">
+        <v>459</v>
+      </c>
+      <c r="J157" t="s">
         <v>460</v>
       </c>
-      <c r="J157" t="s">
+      <c r="K157" t="s">
         <v>461</v>
       </c>
-      <c r="K157" t="s">
+      <c r="L157" t="s">
         <v>462</v>
       </c>
-      <c r="L157" t="s">
+      <c r="M157" t="s">
         <v>463</v>
-      </c>
-      <c r="M157" t="s">
-        <v>464</v>
       </c>
       <c r="N157">
         <v>0</v>
@@ -39292,7 +39301,7 @@
         <v>421</v>
       </c>
       <c r="D158" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E158" t="s">
         <v>423</v>
@@ -39304,22 +39313,22 @@
         <v>442</v>
       </c>
       <c r="H158" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I158" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J158" t="s">
+        <v>465</v>
+      </c>
+      <c r="K158" t="s">
         <v>466</v>
       </c>
-      <c r="K158" t="s">
+      <c r="L158" t="s">
         <v>467</v>
       </c>
-      <c r="L158" t="s">
+      <c r="M158" t="s">
         <v>468</v>
-      </c>
-      <c r="M158" t="s">
-        <v>469</v>
       </c>
       <c r="N158">
         <v>0</v>
@@ -39349,13 +39358,13 @@
         <v>421</v>
       </c>
       <c r="D159" t="s">
+        <v>469</v>
+      </c>
+      <c r="E159" t="s">
         <v>470</v>
       </c>
-      <c r="E159" t="s">
+      <c r="F159" t="s">
         <v>471</v>
-      </c>
-      <c r="F159" t="s">
-        <v>472</v>
       </c>
       <c r="G159">
         <v>551</v>
@@ -39403,16 +39412,16 @@
         <v>0</v>
       </c>
       <c r="C160" t="s">
+        <v>472</v>
+      </c>
+      <c r="D160" t="s">
         <v>473</v>
       </c>
-      <c r="D160" t="s">
+      <c r="E160" t="s">
         <v>474</v>
       </c>
-      <c r="E160" t="s">
+      <c r="F160" t="s">
         <v>475</v>
-      </c>
-      <c r="F160" t="s">
-        <v>476</v>
       </c>
       <c r="G160">
         <v>2</v>
@@ -39460,16 +39469,16 @@
         <v>0</v>
       </c>
       <c r="C161" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D161" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E161" t="s">
+        <v>474</v>
+      </c>
+      <c r="F161" t="s">
         <v>475</v>
-      </c>
-      <c r="F161" t="s">
-        <v>476</v>
       </c>
       <c r="G161">
         <v>4</v>
@@ -39517,16 +39526,16 @@
         <v>0</v>
       </c>
       <c r="C162" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D162" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E162" t="s">
+        <v>474</v>
+      </c>
+      <c r="F162" t="s">
         <v>475</v>
-      </c>
-      <c r="F162" t="s">
-        <v>476</v>
       </c>
       <c r="G162">
         <v>6</v>
@@ -39574,16 +39583,16 @@
         <v>0</v>
       </c>
       <c r="C163" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D163" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E163" t="s">
+        <v>474</v>
+      </c>
+      <c r="F163" t="s">
         <v>475</v>
-      </c>
-      <c r="F163" t="s">
-        <v>476</v>
       </c>
       <c r="G163">
         <v>8</v>
@@ -39631,16 +39640,16 @@
         <v>0</v>
       </c>
       <c r="C164" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D164" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E164" t="s">
+        <v>474</v>
+      </c>
+      <c r="F164" t="s">
         <v>475</v>
-      </c>
-      <c r="F164" t="s">
-        <v>476</v>
       </c>
       <c r="G164">
         <v>10</v>
@@ -39688,16 +39697,16 @@
         <v>0</v>
       </c>
       <c r="C165" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D165" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E165" t="s">
+        <v>474</v>
+      </c>
+      <c r="F165" t="s">
         <v>475</v>
-      </c>
-      <c r="F165" t="s">
-        <v>476</v>
       </c>
       <c r="G165">
         <v>12</v>
@@ -39745,16 +39754,16 @@
         <v>0</v>
       </c>
       <c r="C166" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D166" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E166" t="s">
+        <v>474</v>
+      </c>
+      <c r="F166" t="s">
         <v>475</v>
-      </c>
-      <c r="F166" t="s">
-        <v>476</v>
       </c>
       <c r="G166">
         <v>14</v>
@@ -39802,16 +39811,16 @@
         <v>0</v>
       </c>
       <c r="C167" t="s">
+        <v>482</v>
+      </c>
+      <c r="D167" t="s">
         <v>483</v>
       </c>
-      <c r="D167" t="s">
+      <c r="E167" t="s">
         <v>484</v>
       </c>
-      <c r="E167" t="s">
+      <c r="F167" t="s">
         <v>485</v>
-      </c>
-      <c r="F167" t="s">
-        <v>486</v>
       </c>
       <c r="G167">
         <v>4</v>
@@ -39859,16 +39868,16 @@
         <v>0</v>
       </c>
       <c r="C168" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D168" t="s">
+        <v>486</v>
+      </c>
+      <c r="E168" t="s">
         <v>487</v>
       </c>
-      <c r="E168" t="s">
+      <c r="F168" t="s">
         <v>488</v>
-      </c>
-      <c r="F168" t="s">
-        <v>489</v>
       </c>
       <c r="G168">
         <v>5</v>
@@ -39916,16 +39925,16 @@
         <v>0</v>
       </c>
       <c r="C169" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D169" t="s">
+        <v>489</v>
+      </c>
+      <c r="E169" t="s">
+        <v>487</v>
+      </c>
+      <c r="F169" t="s">
         <v>490</v>
-      </c>
-      <c r="E169" t="s">
-        <v>488</v>
-      </c>
-      <c r="F169" t="s">
-        <v>491</v>
       </c>
       <c r="G169">
         <v>10</v>
@@ -39973,16 +39982,16 @@
         <v>0</v>
       </c>
       <c r="C170" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D170" t="s">
+        <v>491</v>
+      </c>
+      <c r="E170" t="s">
         <v>492</v>
       </c>
-      <c r="E170" t="s">
+      <c r="F170" t="s">
         <v>493</v>
-      </c>
-      <c r="F170" t="s">
-        <v>494</v>
       </c>
       <c r="G170">
         <v>0.5</v>
@@ -40030,16 +40039,16 @@
         <v>0</v>
       </c>
       <c r="C171" t="s">
+        <v>494</v>
+      </c>
+      <c r="D171" t="s">
         <v>495</v>
       </c>
-      <c r="D171" t="s">
+      <c r="E171" t="s">
         <v>496</v>
       </c>
-      <c r="E171" t="s">
+      <c r="F171" t="s">
         <v>497</v>
-      </c>
-      <c r="F171" t="s">
-        <v>498</v>
       </c>
       <c r="G171">
         <v>100</v>
@@ -40087,16 +40096,16 @@
         <v>0</v>
       </c>
       <c r="C172" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D172" t="s">
+        <v>498</v>
+      </c>
+      <c r="E172" t="s">
         <v>499</v>
       </c>
-      <c r="E172" t="s">
+      <c r="F172" t="s">
         <v>500</v>
-      </c>
-      <c r="F172" t="s">
-        <v>501</v>
       </c>
       <c r="G172">
         <v>92</v>
@@ -40144,16 +40153,16 @@
         <v>0</v>
       </c>
       <c r="C173" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D173" t="s">
+        <v>501</v>
+      </c>
+      <c r="E173" t="s">
         <v>502</v>
       </c>
-      <c r="E173" t="s">
+      <c r="F173" t="s">
         <v>503</v>
-      </c>
-      <c r="F173" t="s">
-        <v>504</v>
       </c>
       <c r="G173">
         <v>78.099999999999994</v>
@@ -40201,16 +40210,16 @@
         <v>0</v>
       </c>
       <c r="C174" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D174" t="s">
+        <v>504</v>
+      </c>
+      <c r="E174" t="s">
         <v>505</v>
       </c>
-      <c r="E174" t="s">
+      <c r="F174" t="s">
         <v>506</v>
-      </c>
-      <c r="F174" t="s">
-        <v>507</v>
       </c>
       <c r="G174">
         <v>72.11</v>
@@ -40258,16 +40267,16 @@
         <v>0</v>
       </c>
       <c r="C175" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D175" t="s">
+        <v>507</v>
+      </c>
+      <c r="E175" t="s">
         <v>508</v>
       </c>
-      <c r="E175" t="s">
+      <c r="F175" t="s">
         <v>509</v>
-      </c>
-      <c r="F175" t="s">
-        <v>510</v>
       </c>
       <c r="G175">
         <v>74.349999999999994</v>
@@ -40315,16 +40324,16 @@
         <v>0</v>
       </c>
       <c r="C176" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D176" t="s">
+        <v>510</v>
+      </c>
+      <c r="E176" t="s">
         <v>511</v>
       </c>
-      <c r="E176" t="s">
+      <c r="F176" t="s">
         <v>512</v>
-      </c>
-      <c r="F176" t="s">
-        <v>513</v>
       </c>
       <c r="G176">
         <v>76.87</v>
@@ -40372,16 +40381,16 @@
         <v>0</v>
       </c>
       <c r="C177" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D177" t="s">
+        <v>513</v>
+      </c>
+      <c r="E177" t="s">
         <v>514</v>
       </c>
-      <c r="E177" t="s">
+      <c r="F177" t="s">
         <v>515</v>
-      </c>
-      <c r="F177" t="s">
-        <v>516</v>
       </c>
       <c r="G177">
         <v>69.92</v>
@@ -40429,16 +40438,16 @@
         <v>0</v>
       </c>
       <c r="C178" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D178" t="s">
+        <v>516</v>
+      </c>
+      <c r="E178" t="s">
         <v>517</v>
       </c>
-      <c r="E178" t="s">
+      <c r="F178" t="s">
         <v>518</v>
-      </c>
-      <c r="F178" t="s">
-        <v>519</v>
       </c>
       <c r="G178">
         <v>64.22</v>
@@ -40486,16 +40495,16 @@
         <v>0</v>
       </c>
       <c r="C179" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D179" t="s">
+        <v>519</v>
+      </c>
+      <c r="E179" t="s">
         <v>520</v>
       </c>
-      <c r="E179" t="s">
+      <c r="F179" t="s">
         <v>521</v>
-      </c>
-      <c r="F179" t="s">
-        <v>522</v>
       </c>
       <c r="G179">
         <v>59.92</v>
@@ -40543,16 +40552,16 @@
         <v>0</v>
       </c>
       <c r="C180" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D180" t="s">
+        <v>522</v>
+      </c>
+      <c r="E180" t="s">
         <v>523</v>
       </c>
-      <c r="E180" t="s">
+      <c r="F180" t="s">
         <v>524</v>
-      </c>
-      <c r="F180" t="s">
-        <v>525</v>
       </c>
       <c r="G180">
         <v>54.72</v>
@@ -40600,16 +40609,16 @@
         <v>0</v>
       </c>
       <c r="C181" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D181" t="s">
+        <v>525</v>
+      </c>
+      <c r="E181" t="s">
         <v>526</v>
       </c>
-      <c r="E181" t="s">
+      <c r="F181" t="s">
         <v>527</v>
-      </c>
-      <c r="F181" t="s">
-        <v>528</v>
       </c>
       <c r="G181">
         <v>1.35</v>
@@ -40657,16 +40666,16 @@
         <v>0</v>
       </c>
       <c r="C182" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D182" t="s">
+        <v>528</v>
+      </c>
+      <c r="E182" t="s">
         <v>529</v>
       </c>
-      <c r="E182" t="s">
+      <c r="F182" t="s">
         <v>530</v>
-      </c>
-      <c r="F182" t="s">
-        <v>531</v>
       </c>
       <c r="G182">
         <v>0.5</v>
@@ -40714,16 +40723,16 @@
         <v>0</v>
       </c>
       <c r="C183" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D183" t="s">
+        <v>531</v>
+      </c>
+      <c r="E183" t="s">
         <v>532</v>
       </c>
-      <c r="E183" t="s">
+      <c r="F183" t="s">
         <v>533</v>
-      </c>
-      <c r="F183" t="s">
-        <v>534</v>
       </c>
       <c r="G183">
         <v>4000</v>
@@ -40771,16 +40780,16 @@
         <v>0</v>
       </c>
       <c r="C184" t="s">
+        <v>534</v>
+      </c>
+      <c r="D184" t="s">
         <v>535</v>
       </c>
-      <c r="D184" t="s">
+      <c r="E184" t="s">
         <v>536</v>
       </c>
-      <c r="E184" t="s">
+      <c r="F184" t="s">
         <v>537</v>
-      </c>
-      <c r="F184" t="s">
-        <v>538</v>
       </c>
       <c r="G184">
         <v>4</v>
@@ -40828,16 +40837,16 @@
         <v>0</v>
       </c>
       <c r="C185" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D185" t="s">
         <v>258</v>
       </c>
       <c r="E185" t="s">
+        <v>538</v>
+      </c>
+      <c r="F185" t="s">
         <v>539</v>
-      </c>
-      <c r="F185" t="s">
-        <v>540</v>
       </c>
       <c r="G185">
         <v>200</v>
@@ -40885,16 +40894,16 @@
         <v>0</v>
       </c>
       <c r="C186" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D186" t="s">
+        <v>540</v>
+      </c>
+      <c r="E186" t="s">
         <v>541</v>
       </c>
-      <c r="E186" t="s">
+      <c r="F186" t="s">
         <v>542</v>
-      </c>
-      <c r="F186" t="s">
-        <v>543</v>
       </c>
       <c r="G186">
         <v>4</v>
@@ -40942,16 +40951,16 @@
         <v>0</v>
       </c>
       <c r="C187" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D187" t="s">
+        <v>543</v>
+      </c>
+      <c r="E187" t="s">
         <v>544</v>
       </c>
-      <c r="E187" t="s">
+      <c r="F187" t="s">
         <v>545</v>
-      </c>
-      <c r="F187" t="s">
-        <v>546</v>
       </c>
       <c r="G187">
         <v>3</v>
@@ -40999,16 +41008,16 @@
         <v>0</v>
       </c>
       <c r="C188" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D188" t="s">
+        <v>546</v>
+      </c>
+      <c r="E188" t="s">
         <v>547</v>
       </c>
-      <c r="E188" t="s">
+      <c r="F188" t="s">
         <v>548</v>
-      </c>
-      <c r="F188" t="s">
-        <v>549</v>
       </c>
       <c r="G188">
         <v>4</v>
@@ -41056,37 +41065,37 @@
         <v>0</v>
       </c>
       <c r="C189" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D189" t="s">
         <v>422</v>
       </c>
       <c r="E189" t="s">
+        <v>550</v>
+      </c>
+      <c r="F189" t="s">
         <v>551</v>
       </c>
-      <c r="F189" t="s">
+      <c r="G189" t="s">
         <v>552</v>
       </c>
-      <c r="G189" t="s">
+      <c r="H189" t="s">
         <v>553</v>
       </c>
-      <c r="H189" t="s">
+      <c r="I189" t="s">
         <v>554</v>
       </c>
-      <c r="I189" t="s">
+      <c r="J189" t="s">
         <v>555</v>
       </c>
-      <c r="J189" t="s">
+      <c r="K189" t="s">
         <v>556</v>
       </c>
-      <c r="K189" t="s">
+      <c r="L189" t="s">
         <v>557</v>
       </c>
-      <c r="L189" t="s">
+      <c r="M189" t="s">
         <v>558</v>
-      </c>
-      <c r="M189" t="s">
-        <v>559</v>
       </c>
       <c r="N189">
         <v>0</v>
@@ -41113,37 +41122,37 @@
         <v>0</v>
       </c>
       <c r="C190" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D190" t="s">
         <v>430</v>
       </c>
       <c r="E190" t="s">
+        <v>550</v>
+      </c>
+      <c r="F190" t="s">
         <v>551</v>
       </c>
-      <c r="F190" t="s">
+      <c r="G190" t="s">
         <v>552</v>
       </c>
-      <c r="G190" t="s">
+      <c r="H190" t="s">
         <v>553</v>
       </c>
-      <c r="H190" t="s">
+      <c r="I190" t="s">
         <v>554</v>
       </c>
-      <c r="I190" t="s">
+      <c r="J190" t="s">
         <v>555</v>
       </c>
-      <c r="J190" t="s">
+      <c r="K190" t="s">
         <v>556</v>
       </c>
-      <c r="K190" t="s">
+      <c r="L190" t="s">
         <v>557</v>
       </c>
-      <c r="L190" t="s">
+      <c r="M190" t="s">
         <v>558</v>
-      </c>
-      <c r="M190" t="s">
-        <v>559</v>
       </c>
       <c r="N190">
         <v>0</v>
@@ -41170,37 +41179,37 @@
         <v>0</v>
       </c>
       <c r="C191" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D191" t="s">
         <v>436</v>
       </c>
       <c r="E191" t="s">
+        <v>550</v>
+      </c>
+      <c r="F191" t="s">
         <v>551</v>
       </c>
-      <c r="F191" t="s">
-        <v>552</v>
-      </c>
       <c r="G191" t="s">
+        <v>559</v>
+      </c>
+      <c r="H191" t="s">
         <v>560</v>
       </c>
-      <c r="H191" t="s">
-        <v>561</v>
-      </c>
       <c r="I191" t="s">
+        <v>554</v>
+      </c>
+      <c r="J191" t="s">
         <v>555</v>
       </c>
-      <c r="J191" t="s">
+      <c r="K191" t="s">
         <v>556</v>
       </c>
-      <c r="K191" t="s">
+      <c r="L191" t="s">
         <v>557</v>
       </c>
-      <c r="L191" t="s">
+      <c r="M191" t="s">
         <v>558</v>
-      </c>
-      <c r="M191" t="s">
-        <v>559</v>
       </c>
       <c r="N191">
         <v>0</v>
@@ -41227,37 +41236,37 @@
         <v>0</v>
       </c>
       <c r="C192" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D192" t="s">
         <v>441</v>
       </c>
       <c r="E192" t="s">
+        <v>550</v>
+      </c>
+      <c r="F192" t="s">
         <v>551</v>
       </c>
-      <c r="F192" t="s">
-        <v>552</v>
-      </c>
       <c r="G192" t="s">
+        <v>561</v>
+      </c>
+      <c r="H192" t="s">
+        <v>560</v>
+      </c>
+      <c r="I192" t="s">
         <v>562</v>
       </c>
-      <c r="H192" t="s">
-        <v>561</v>
-      </c>
-      <c r="I192" t="s">
+      <c r="J192" t="s">
         <v>563</v>
       </c>
-      <c r="J192" t="s">
+      <c r="K192" t="s">
         <v>564</v>
       </c>
-      <c r="K192" t="s">
+      <c r="L192" t="s">
         <v>565</v>
       </c>
-      <c r="L192" t="s">
+      <c r="M192" t="s">
         <v>566</v>
-      </c>
-      <c r="M192" t="s">
-        <v>567</v>
       </c>
       <c r="N192">
         <v>0</v>
@@ -41284,37 +41293,37 @@
         <v>0</v>
       </c>
       <c r="C193" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D193" t="s">
         <v>446</v>
       </c>
       <c r="E193" t="s">
+        <v>550</v>
+      </c>
+      <c r="F193" t="s">
         <v>551</v>
       </c>
-      <c r="F193" t="s">
-        <v>552</v>
-      </c>
       <c r="G193" t="s">
+        <v>567</v>
+      </c>
+      <c r="H193" t="s">
         <v>568</v>
       </c>
-      <c r="H193" t="s">
+      <c r="I193" t="s">
+        <v>562</v>
+      </c>
+      <c r="J193" t="s">
         <v>569</v>
       </c>
-      <c r="I193" t="s">
-        <v>563</v>
-      </c>
-      <c r="J193" t="s">
+      <c r="K193" t="s">
         <v>570</v>
       </c>
-      <c r="K193" t="s">
+      <c r="L193" t="s">
         <v>571</v>
       </c>
-      <c r="L193" t="s">
+      <c r="M193" t="s">
         <v>572</v>
-      </c>
-      <c r="M193" t="s">
-        <v>573</v>
       </c>
       <c r="N193">
         <v>0</v>
@@ -41341,37 +41350,37 @@
         <v>0</v>
       </c>
       <c r="C194" t="s">
+        <v>549</v>
+      </c>
+      <c r="D194" t="s">
+        <v>452</v>
+      </c>
+      <c r="E194" t="s">
         <v>550</v>
       </c>
-      <c r="D194" t="s">
-        <v>453</v>
-      </c>
-      <c r="E194" t="s">
+      <c r="F194" t="s">
         <v>551</v>
       </c>
-      <c r="F194" t="s">
-        <v>552</v>
-      </c>
       <c r="G194" t="s">
+        <v>573</v>
+      </c>
+      <c r="H194" t="s">
         <v>574</v>
       </c>
-      <c r="H194" t="s">
+      <c r="I194" t="s">
         <v>575</v>
       </c>
-      <c r="I194" t="s">
+      <c r="J194" t="s">
         <v>576</v>
       </c>
-      <c r="J194" t="s">
+      <c r="K194" t="s">
         <v>577</v>
       </c>
-      <c r="K194" t="s">
+      <c r="L194" t="s">
         <v>578</v>
       </c>
-      <c r="L194" t="s">
+      <c r="M194" t="s">
         <v>579</v>
-      </c>
-      <c r="M194" t="s">
-        <v>580</v>
       </c>
       <c r="N194">
         <v>0</v>
@@ -41398,37 +41407,37 @@
         <v>0</v>
       </c>
       <c r="C195" t="s">
+        <v>549</v>
+      </c>
+      <c r="D195" t="s">
+        <v>458</v>
+      </c>
+      <c r="E195" t="s">
         <v>550</v>
       </c>
-      <c r="D195" t="s">
-        <v>459</v>
-      </c>
-      <c r="E195" t="s">
+      <c r="F195" t="s">
         <v>551</v>
       </c>
-      <c r="F195" t="s">
+      <c r="G195" t="s">
         <v>552</v>
       </c>
-      <c r="G195" t="s">
-        <v>553</v>
-      </c>
       <c r="H195" t="s">
+        <v>580</v>
+      </c>
+      <c r="I195" t="s">
         <v>581</v>
       </c>
-      <c r="I195" t="s">
+      <c r="J195" t="s">
         <v>582</v>
       </c>
-      <c r="J195" t="s">
+      <c r="K195" t="s">
         <v>583</v>
       </c>
-      <c r="K195" t="s">
+      <c r="L195" t="s">
         <v>584</v>
       </c>
-      <c r="L195" t="s">
+      <c r="M195" t="s">
         <v>585</v>
-      </c>
-      <c r="M195" t="s">
-        <v>586</v>
       </c>
       <c r="N195">
         <v>0</v>
@@ -41455,37 +41464,37 @@
         <v>0</v>
       </c>
       <c r="C196" t="s">
+        <v>549</v>
+      </c>
+      <c r="D196" t="s">
+        <v>464</v>
+      </c>
+      <c r="E196" t="s">
         <v>550</v>
       </c>
-      <c r="D196" t="s">
-        <v>465</v>
-      </c>
-      <c r="E196" t="s">
+      <c r="F196" t="s">
         <v>551</v>
       </c>
-      <c r="F196" t="s">
+      <c r="G196" t="s">
         <v>552</v>
       </c>
-      <c r="G196" t="s">
+      <c r="H196" t="s">
         <v>553</v>
       </c>
-      <c r="H196" t="s">
-        <v>554</v>
-      </c>
       <c r="I196" t="s">
+        <v>586</v>
+      </c>
+      <c r="J196" t="s">
         <v>587</v>
       </c>
-      <c r="J196" t="s">
+      <c r="K196" t="s">
         <v>588</v>
       </c>
-      <c r="K196" t="s">
+      <c r="L196" t="s">
         <v>589</v>
       </c>
-      <c r="L196" t="s">
+      <c r="M196" t="s">
         <v>590</v>
-      </c>
-      <c r="M196" t="s">
-        <v>591</v>
       </c>
       <c r="N196">
         <v>0</v>
@@ -41512,16 +41521,16 @@
         <v>0</v>
       </c>
       <c r="C197" t="s">
+        <v>591</v>
+      </c>
+      <c r="D197" t="s">
         <v>592</v>
       </c>
-      <c r="D197" t="s">
+      <c r="E197" t="s">
         <v>593</v>
       </c>
-      <c r="E197" t="s">
+      <c r="F197" t="s">
         <v>594</v>
-      </c>
-      <c r="F197" t="s">
-        <v>595</v>
       </c>
       <c r="G197">
         <v>0</v>
@@ -41569,16 +41578,16 @@
         <v>0</v>
       </c>
       <c r="C198" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D198" t="s">
+        <v>595</v>
+      </c>
+      <c r="E198" t="s">
         <v>596</v>
       </c>
-      <c r="E198" t="s">
+      <c r="F198" t="s">
         <v>597</v>
-      </c>
-      <c r="F198" t="s">
-        <v>598</v>
       </c>
       <c r="G198">
         <v>1.35</v>
@@ -41626,16 +41635,16 @@
         <v>0</v>
       </c>
       <c r="C199" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D199" t="s">
+        <v>598</v>
+      </c>
+      <c r="E199" t="s">
         <v>599</v>
       </c>
-      <c r="E199" t="s">
+      <c r="F199" t="s">
         <v>600</v>
-      </c>
-      <c r="F199" t="s">
-        <v>601</v>
       </c>
       <c r="G199">
         <v>0.05</v>
@@ -41683,16 +41692,16 @@
         <v>0</v>
       </c>
       <c r="C200" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D200" t="s">
+        <v>601</v>
+      </c>
+      <c r="E200" t="s">
         <v>602</v>
       </c>
-      <c r="E200" t="s">
+      <c r="F200" t="s">
         <v>603</v>
-      </c>
-      <c r="F200" t="s">
-        <v>604</v>
       </c>
       <c r="G200">
         <v>2</v>
@@ -41740,16 +41749,16 @@
         <v>0</v>
       </c>
       <c r="C201" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D201" t="s">
+        <v>604</v>
+      </c>
+      <c r="E201" t="s">
         <v>605</v>
       </c>
-      <c r="E201" t="s">
+      <c r="F201" t="s">
         <v>606</v>
-      </c>
-      <c r="F201" t="s">
-        <v>607</v>
       </c>
       <c r="G201">
         <v>0</v>
@@ -41797,16 +41806,16 @@
         <v>0</v>
       </c>
       <c r="C202" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D202" t="s">
+        <v>607</v>
+      </c>
+      <c r="E202" t="s">
         <v>608</v>
       </c>
-      <c r="E202" t="s">
+      <c r="F202" t="s">
         <v>609</v>
-      </c>
-      <c r="F202" t="s">
-        <v>610</v>
       </c>
       <c r="G202">
         <v>5</v>
@@ -41854,16 +41863,16 @@
         <v>0</v>
       </c>
       <c r="C203" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D203" t="s">
+        <v>610</v>
+      </c>
+      <c r="E203" t="s">
         <v>611</v>
       </c>
-      <c r="E203" t="s">
+      <c r="F203" t="s">
         <v>612</v>
-      </c>
-      <c r="F203" t="s">
-        <v>613</v>
       </c>
       <c r="G203">
         <v>8</v>
@@ -41911,16 +41920,16 @@
         <v>0</v>
       </c>
       <c r="C204" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D204" t="s">
+        <v>613</v>
+      </c>
+      <c r="E204" t="s">
         <v>614</v>
       </c>
-      <c r="E204" t="s">
+      <c r="F204" t="s">
         <v>615</v>
-      </c>
-      <c r="F204" t="s">
-        <v>616</v>
       </c>
       <c r="G204">
         <v>1</v>
@@ -41968,16 +41977,16 @@
         <v>0</v>
       </c>
       <c r="C205" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D205" t="s">
+        <v>616</v>
+      </c>
+      <c r="E205" t="s">
         <v>617</v>
       </c>
-      <c r="E205" t="s">
+      <c r="F205" t="s">
         <v>618</v>
-      </c>
-      <c r="F205" t="s">
-        <v>619</v>
       </c>
       <c r="G205">
         <v>0.15</v>
@@ -42025,16 +42034,16 @@
         <v>0</v>
       </c>
       <c r="C206" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D206" t="s">
+        <v>619</v>
+      </c>
+      <c r="E206" t="s">
         <v>620</v>
       </c>
-      <c r="E206" t="s">
+      <c r="F206" t="s">
         <v>621</v>
-      </c>
-      <c r="F206" t="s">
-        <v>622</v>
       </c>
       <c r="G206">
         <v>2</v>
@@ -42082,16 +42091,16 @@
         <v>0</v>
       </c>
       <c r="C207" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D207" t="s">
+        <v>622</v>
+      </c>
+      <c r="E207" t="s">
         <v>623</v>
       </c>
-      <c r="E207" t="s">
+      <c r="F207" t="s">
         <v>624</v>
-      </c>
-      <c r="F207" t="s">
-        <v>625</v>
       </c>
       <c r="G207">
         <v>3</v>
@@ -42139,16 +42148,16 @@
         <v>0</v>
       </c>
       <c r="C208" t="s">
+        <v>625</v>
+      </c>
+      <c r="D208" t="s">
         <v>626</v>
       </c>
-      <c r="D208" t="s">
+      <c r="E208" t="s">
         <v>627</v>
       </c>
-      <c r="E208" t="s">
+      <c r="F208" t="s">
         <v>628</v>
-      </c>
-      <c r="F208" t="s">
-        <v>629</v>
       </c>
       <c r="G208">
         <v>5</v>
@@ -42196,16 +42205,16 @@
         <v>0</v>
       </c>
       <c r="C209" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D209" t="s">
+        <v>629</v>
+      </c>
+      <c r="E209" t="s">
         <v>630</v>
       </c>
-      <c r="E209" t="s">
+      <c r="F209" t="s">
         <v>631</v>
-      </c>
-      <c r="F209" t="s">
-        <v>632</v>
       </c>
       <c r="G209">
         <v>0</v>
@@ -42253,16 +42262,16 @@
         <v>0</v>
       </c>
       <c r="C210" t="s">
+        <v>632</v>
+      </c>
+      <c r="D210" t="s">
         <v>633</v>
       </c>
-      <c r="D210" t="s">
+      <c r="E210" t="s">
         <v>634</v>
       </c>
-      <c r="E210" t="s">
+      <c r="F210" t="s">
         <v>635</v>
-      </c>
-      <c r="F210" t="s">
-        <v>636</v>
       </c>
       <c r="G210">
         <v>5</v>
@@ -42310,16 +42319,16 @@
         <v>0</v>
       </c>
       <c r="C211" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D211" t="s">
+        <v>636</v>
+      </c>
+      <c r="E211" t="s">
         <v>637</v>
       </c>
-      <c r="E211" t="s">
+      <c r="F211" t="s">
         <v>638</v>
-      </c>
-      <c r="F211" t="s">
-        <v>639</v>
       </c>
       <c r="G211">
         <v>55</v>
@@ -42367,16 +42376,16 @@
         <v>0</v>
       </c>
       <c r="C212" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D212" t="s">
+        <v>639</v>
+      </c>
+      <c r="E212" t="s">
         <v>640</v>
       </c>
-      <c r="E212" t="s">
+      <c r="F212" t="s">
         <v>641</v>
-      </c>
-      <c r="F212" t="s">
-        <v>642</v>
       </c>
       <c r="G212">
         <v>5000000</v>
@@ -42424,13 +42433,13 @@
         <v>0</v>
       </c>
       <c r="C213" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D213" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E213" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="F213">
         <v>0</v>
@@ -42481,16 +42490,16 @@
         <v>0</v>
       </c>
       <c r="C214" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D214" t="s">
+        <v>643</v>
+      </c>
+      <c r="E214" t="s">
         <v>644</v>
       </c>
-      <c r="E214" t="s">
+      <c r="F214" t="s">
         <v>645</v>
-      </c>
-      <c r="F214" t="s">
-        <v>646</v>
       </c>
       <c r="G214">
         <v>3</v>
@@ -42538,16 +42547,16 @@
         <v>0</v>
       </c>
       <c r="C215" t="s">
+        <v>646</v>
+      </c>
+      <c r="D215" t="s">
         <v>647</v>
       </c>
-      <c r="D215" t="s">
+      <c r="E215" t="s">
         <v>648</v>
       </c>
-      <c r="E215" t="s">
+      <c r="F215" t="s">
         <v>649</v>
-      </c>
-      <c r="F215" t="s">
-        <v>650</v>
       </c>
       <c r="G215">
         <v>27</v>
@@ -42595,16 +42604,16 @@
         <v>0</v>
       </c>
       <c r="C216" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D216" t="s">
+        <v>650</v>
+      </c>
+      <c r="E216" t="s">
         <v>651</v>
       </c>
-      <c r="E216" t="s">
-        <v>652</v>
-      </c>
       <c r="F216" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G216">
         <v>36</v>
@@ -42652,16 +42661,16 @@
         <v>0</v>
       </c>
       <c r="C217" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D217" t="s">
+        <v>652</v>
+      </c>
+      <c r="E217" t="s">
+        <v>634</v>
+      </c>
+      <c r="F217" t="s">
         <v>653</v>
-      </c>
-      <c r="E217" t="s">
-        <v>635</v>
-      </c>
-      <c r="F217" t="s">
-        <v>654</v>
       </c>
       <c r="G217">
         <v>3</v>
@@ -42709,16 +42718,16 @@
         <v>0</v>
       </c>
       <c r="C218" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D218" t="s">
+        <v>654</v>
+      </c>
+      <c r="E218" t="s">
         <v>655</v>
       </c>
-      <c r="E218" t="s">
+      <c r="F218" t="s">
         <v>656</v>
-      </c>
-      <c r="F218" t="s">
-        <v>657</v>
       </c>
       <c r="G218">
         <v>50</v>
@@ -42766,16 +42775,16 @@
         <v>0</v>
       </c>
       <c r="C219" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D219" t="s">
+        <v>657</v>
+      </c>
+      <c r="E219" t="s">
         <v>658</v>
       </c>
-      <c r="E219" t="s">
+      <c r="F219" t="s">
         <v>659</v>
-      </c>
-      <c r="F219" t="s">
-        <v>660</v>
       </c>
       <c r="G219">
         <v>1000000</v>
@@ -42823,13 +42832,13 @@
         <v>0</v>
       </c>
       <c r="C220" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D220" t="s">
+        <v>660</v>
+      </c>
+      <c r="E220" t="s">
         <v>661</v>
-      </c>
-      <c r="E220" t="s">
-        <v>662</v>
       </c>
       <c r="F220">
         <v>0</v>
@@ -42880,16 +42889,16 @@
         <v>0</v>
       </c>
       <c r="C221" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D221" t="s">
+        <v>662</v>
+      </c>
+      <c r="E221" t="s">
         <v>663</v>
       </c>
-      <c r="E221" t="s">
+      <c r="F221" t="s">
         <v>664</v>
-      </c>
-      <c r="F221" t="s">
-        <v>665</v>
       </c>
       <c r="G221">
         <v>3</v>
@@ -42937,16 +42946,16 @@
         <v>0</v>
       </c>
       <c r="C222" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D222" t="s">
+        <v>665</v>
+      </c>
+      <c r="E222" t="s">
         <v>666</v>
       </c>
-      <c r="E222" t="s">
+      <c r="F222" t="s">
         <v>667</v>
-      </c>
-      <c r="F222" t="s">
-        <v>668</v>
       </c>
       <c r="G222">
         <v>6</v>
@@ -42994,16 +43003,16 @@
         <v>0</v>
       </c>
       <c r="C223" t="s">
+        <v>668</v>
+      </c>
+      <c r="D223" t="s">
         <v>669</v>
       </c>
-      <c r="D223" t="s">
+      <c r="E223" t="s">
         <v>670</v>
       </c>
-      <c r="E223" t="s">
+      <c r="F223" t="s">
         <v>671</v>
-      </c>
-      <c r="F223" t="s">
-        <v>672</v>
       </c>
       <c r="G223">
         <v>30</v>
@@ -43051,13 +43060,13 @@
         <v>0</v>
       </c>
       <c r="C224" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D224" t="s">
+        <v>672</v>
+      </c>
+      <c r="E224" t="s">
         <v>673</v>
-      </c>
-      <c r="E224" t="s">
-        <v>674</v>
       </c>
       <c r="F224">
         <v>0</v>
@@ -43108,13 +43117,13 @@
         <v>0</v>
       </c>
       <c r="C225" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D225" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E225" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F225">
         <v>0</v>
@@ -43165,16 +43174,16 @@
         <v>0</v>
       </c>
       <c r="C226" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D226" t="s">
+        <v>675</v>
+      </c>
+      <c r="E226" t="s">
         <v>676</v>
       </c>
-      <c r="E226" t="s">
+      <c r="F226" t="s">
         <v>677</v>
-      </c>
-      <c r="F226" t="s">
-        <v>678</v>
       </c>
       <c r="G226">
         <v>0</v>
@@ -43222,13 +43231,13 @@
         <v>0</v>
       </c>
       <c r="C227" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D227" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E227" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="F227">
         <v>0</v>
@@ -43279,16 +43288,16 @@
         <v>0</v>
       </c>
       <c r="C228" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D228" t="s">
+        <v>679</v>
+      </c>
+      <c r="E228" t="s">
         <v>680</v>
       </c>
-      <c r="E228" t="s">
+      <c r="F228" t="s">
         <v>681</v>
-      </c>
-      <c r="F228" t="s">
-        <v>682</v>
       </c>
       <c r="G228">
         <v>9</v>
@@ -43336,16 +43345,16 @@
         <v>0</v>
       </c>
       <c r="C229" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D229" t="s">
+        <v>682</v>
+      </c>
+      <c r="E229" t="s">
         <v>683</v>
       </c>
-      <c r="E229" t="s">
+      <c r="F229" t="s">
         <v>684</v>
-      </c>
-      <c r="F229" t="s">
-        <v>685</v>
       </c>
       <c r="G229">
         <v>1</v>
@@ -43393,16 +43402,16 @@
         <v>0</v>
       </c>
       <c r="C230" t="s">
+        <v>685</v>
+      </c>
+      <c r="D230" t="s">
         <v>686</v>
       </c>
-      <c r="D230" t="s">
+      <c r="E230" t="s">
         <v>687</v>
       </c>
-      <c r="E230" t="s">
+      <c r="F230" t="s">
         <v>688</v>
-      </c>
-      <c r="F230" t="s">
-        <v>689</v>
       </c>
       <c r="G230">
         <v>5</v>
@@ -43450,16 +43459,16 @@
         <v>0</v>
       </c>
       <c r="C231" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D231" t="s">
+        <v>689</v>
+      </c>
+      <c r="E231" t="s">
         <v>690</v>
       </c>
-      <c r="E231" t="s">
+      <c r="F231" t="s">
         <v>691</v>
-      </c>
-      <c r="F231" t="s">
-        <v>692</v>
       </c>
       <c r="G231">
         <v>0</v>
@@ -43507,16 +43516,16 @@
         <v>0</v>
       </c>
       <c r="C232" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D232" t="s">
+        <v>692</v>
+      </c>
+      <c r="E232" t="s">
         <v>693</v>
       </c>
-      <c r="E232" t="s">
+      <c r="F232" t="s">
         <v>694</v>
-      </c>
-      <c r="F232" t="s">
-        <v>695</v>
       </c>
       <c r="G232">
         <v>0</v>
@@ -43564,16 +43573,16 @@
         <v>0</v>
       </c>
       <c r="C233" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D233" t="s">
+        <v>695</v>
+      </c>
+      <c r="E233" t="s">
         <v>696</v>
       </c>
-      <c r="E233" t="s">
-        <v>697</v>
-      </c>
       <c r="F233" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="G233">
         <v>0</v>
@@ -43621,16 +43630,16 @@
         <v>0</v>
       </c>
       <c r="C234" t="s">
+        <v>697</v>
+      </c>
+      <c r="D234" t="s">
         <v>698</v>
       </c>
-      <c r="D234" t="s">
+      <c r="E234" t="s">
         <v>699</v>
       </c>
-      <c r="E234" t="s">
+      <c r="F234" t="s">
         <v>700</v>
-      </c>
-      <c r="F234" t="s">
-        <v>701</v>
       </c>
       <c r="G234">
         <v>2</v>
@@ -43678,16 +43687,16 @@
         <v>0</v>
       </c>
       <c r="C235" t="s">
+        <v>701</v>
+      </c>
+      <c r="D235" t="s">
         <v>702</v>
       </c>
-      <c r="D235" t="s">
+      <c r="E235" t="s">
         <v>703</v>
       </c>
-      <c r="E235" t="s">
+      <c r="F235" t="s">
         <v>704</v>
-      </c>
-      <c r="F235" t="s">
-        <v>705</v>
       </c>
       <c r="G235">
         <v>10000</v>
@@ -43735,16 +43744,16 @@
         <v>0</v>
       </c>
       <c r="C236" t="s">
+        <v>705</v>
+      </c>
+      <c r="D236" t="s">
         <v>706</v>
       </c>
-      <c r="D236" t="s">
+      <c r="E236" t="s">
         <v>707</v>
       </c>
-      <c r="E236" t="s">
+      <c r="F236" t="s">
         <v>708</v>
-      </c>
-      <c r="F236" t="s">
-        <v>709</v>
       </c>
       <c r="G236">
         <v>20000</v>
@@ -43792,13 +43801,13 @@
         <v>0</v>
       </c>
       <c r="C237" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D237" t="s">
+        <v>709</v>
+      </c>
+      <c r="E237" t="s">
         <v>710</v>
-      </c>
-      <c r="E237" t="s">
-        <v>711</v>
       </c>
       <c r="F237">
         <v>0</v>
@@ -43849,16 +43858,16 @@
         <v>0</v>
       </c>
       <c r="C238" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D238" t="s">
+        <v>711</v>
+      </c>
+      <c r="E238" t="s">
         <v>712</v>
       </c>
-      <c r="E238" t="s">
+      <c r="F238" t="s">
         <v>713</v>
-      </c>
-      <c r="F238" t="s">
-        <v>714</v>
       </c>
       <c r="G238">
         <v>100</v>
@@ -43906,16 +43915,16 @@
         <v>0</v>
       </c>
       <c r="C239" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D239" t="s">
+        <v>714</v>
+      </c>
+      <c r="E239" t="s">
         <v>715</v>
       </c>
-      <c r="E239" t="s">
+      <c r="F239" t="s">
         <v>716</v>
-      </c>
-      <c r="F239" t="s">
-        <v>717</v>
       </c>
       <c r="G239">
         <v>10000</v>
@@ -43963,13 +43972,13 @@
         <v>0</v>
       </c>
       <c r="C240" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D240" t="s">
+        <v>717</v>
+      </c>
+      <c r="E240" t="s">
         <v>718</v>
-      </c>
-      <c r="E240" t="s">
-        <v>719</v>
       </c>
       <c r="F240">
         <v>0</v>
@@ -44020,16 +44029,16 @@
         <v>0</v>
       </c>
       <c r="C241" t="s">
+        <v>719</v>
+      </c>
+      <c r="D241" t="s">
         <v>720</v>
       </c>
-      <c r="D241" t="s">
+      <c r="E241" t="s">
         <v>721</v>
       </c>
-      <c r="E241" t="s">
+      <c r="F241" t="s">
         <v>722</v>
-      </c>
-      <c r="F241" t="s">
-        <v>723</v>
       </c>
       <c r="G241">
         <v>0.2</v>
@@ -44077,16 +44086,16 @@
         <v>0</v>
       </c>
       <c r="C242" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D242" t="s">
+        <v>723</v>
+      </c>
+      <c r="E242" t="s">
         <v>724</v>
       </c>
-      <c r="E242" t="s">
+      <c r="F242" t="s">
         <v>725</v>
-      </c>
-      <c r="F242" t="s">
-        <v>726</v>
       </c>
       <c r="G242">
         <v>2</v>
@@ -44134,16 +44143,16 @@
         <v>0</v>
       </c>
       <c r="C243" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D243" t="s">
+        <v>726</v>
+      </c>
+      <c r="E243" t="s">
         <v>727</v>
       </c>
-      <c r="E243" t="s">
+      <c r="F243" t="s">
         <v>728</v>
-      </c>
-      <c r="F243" t="s">
-        <v>729</v>
       </c>
       <c r="G243">
         <v>3</v>
@@ -44191,16 +44200,16 @@
         <v>0</v>
       </c>
       <c r="C244" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D244" t="s">
+        <v>729</v>
+      </c>
+      <c r="E244" t="s">
         <v>730</v>
       </c>
-      <c r="E244" t="s">
+      <c r="F244" t="s">
         <v>731</v>
-      </c>
-      <c r="F244" t="s">
-        <v>732</v>
       </c>
       <c r="G244">
         <v>3</v>
@@ -44248,16 +44257,16 @@
         <v>0</v>
       </c>
       <c r="C245" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D245" t="s">
+        <v>732</v>
+      </c>
+      <c r="E245" t="s">
         <v>733</v>
       </c>
-      <c r="E245" t="s">
+      <c r="F245" t="s">
         <v>734</v>
-      </c>
-      <c r="F245" t="s">
-        <v>735</v>
       </c>
       <c r="G245">
         <v>100</v>
@@ -44305,16 +44314,16 @@
         <v>0</v>
       </c>
       <c r="C246" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D246" t="s">
+        <v>735</v>
+      </c>
+      <c r="E246" t="s">
         <v>736</v>
       </c>
-      <c r="E246" t="s">
+      <c r="F246" t="s">
         <v>737</v>
-      </c>
-      <c r="F246" t="s">
-        <v>738</v>
       </c>
       <c r="G246">
         <v>9</v>
@@ -44362,16 +44371,16 @@
         <v>0</v>
       </c>
       <c r="C247" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D247" t="s">
+        <v>738</v>
+      </c>
+      <c r="E247" t="s">
         <v>739</v>
       </c>
-      <c r="E247" t="s">
+      <c r="F247" t="s">
         <v>740</v>
-      </c>
-      <c r="F247" t="s">
-        <v>741</v>
       </c>
       <c r="G247">
         <v>0.7</v>
@@ -44419,16 +44428,16 @@
         <v>0</v>
       </c>
       <c r="C248" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D248" t="s">
+        <v>741</v>
+      </c>
+      <c r="E248" t="s">
         <v>742</v>
       </c>
-      <c r="E248" t="s">
+      <c r="F248" t="s">
         <v>743</v>
-      </c>
-      <c r="F248" t="s">
-        <v>744</v>
       </c>
       <c r="G248">
         <v>0.7</v>
@@ -44476,16 +44485,16 @@
         <v>0</v>
       </c>
       <c r="C249" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D249" t="s">
+        <v>744</v>
+      </c>
+      <c r="E249" t="s">
         <v>745</v>
       </c>
-      <c r="E249" t="s">
+      <c r="F249" t="s">
         <v>746</v>
-      </c>
-      <c r="F249" t="s">
-        <v>747</v>
       </c>
       <c r="G249">
         <v>10</v>
@@ -44533,16 +44542,16 @@
         <v>0</v>
       </c>
       <c r="C250" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D250" t="s">
+        <v>747</v>
+      </c>
+      <c r="E250" t="s">
         <v>748</v>
       </c>
-      <c r="E250" t="s">
+      <c r="F250" t="s">
         <v>749</v>
-      </c>
-      <c r="F250" t="s">
-        <v>750</v>
       </c>
       <c r="G250">
         <v>0</v>
@@ -44590,16 +44599,16 @@
         <v>0</v>
       </c>
       <c r="C251" t="s">
+        <v>750</v>
+      </c>
+      <c r="D251" t="s">
         <v>751</v>
       </c>
-      <c r="D251" t="s">
+      <c r="E251" t="s">
         <v>752</v>
       </c>
-      <c r="E251" t="s">
+      <c r="F251" t="s">
         <v>753</v>
-      </c>
-      <c r="F251" t="s">
-        <v>754</v>
       </c>
       <c r="G251">
         <v>10000</v>
@@ -44647,16 +44656,16 @@
         <v>0</v>
       </c>
       <c r="C252" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D252" t="s">
+        <v>754</v>
+      </c>
+      <c r="E252" t="s">
         <v>755</v>
       </c>
-      <c r="E252" t="s">
+      <c r="F252" t="s">
         <v>756</v>
-      </c>
-      <c r="F252" t="s">
-        <v>757</v>
       </c>
       <c r="G252">
         <v>5000</v>
@@ -44704,13 +44713,13 @@
         <v>0</v>
       </c>
       <c r="C253" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D253" t="s">
+        <v>757</v>
+      </c>
+      <c r="E253" t="s">
         <v>758</v>
-      </c>
-      <c r="E253" t="s">
-        <v>759</v>
       </c>
       <c r="F253">
         <v>0</v>
@@ -44761,16 +44770,16 @@
         <v>0</v>
       </c>
       <c r="C254" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D254" t="s">
+        <v>759</v>
+      </c>
+      <c r="E254" t="s">
         <v>760</v>
       </c>
-      <c r="E254" t="s">
+      <c r="F254" t="s">
         <v>761</v>
-      </c>
-      <c r="F254" t="s">
-        <v>762</v>
       </c>
       <c r="G254">
         <v>10000</v>
@@ -44818,22 +44827,22 @@
         <v>0</v>
       </c>
       <c r="C255" t="s">
+        <v>762</v>
+      </c>
+      <c r="D255" t="s">
         <v>763</v>
       </c>
-      <c r="D255" t="s">
+      <c r="E255" t="s">
         <v>764</v>
       </c>
-      <c r="E255" t="s">
+      <c r="F255" t="s">
         <v>765</v>
       </c>
-      <c r="F255" t="s">
+      <c r="G255" t="s">
         <v>766</v>
       </c>
-      <c r="G255" t="s">
+      <c r="H255" t="s">
         <v>767</v>
-      </c>
-      <c r="H255" t="s">
-        <v>768</v>
       </c>
       <c r="I255">
         <v>0</v>
@@ -44875,25 +44884,25 @@
         <v>0</v>
       </c>
       <c r="C256" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D256" t="s">
+        <v>768</v>
+      </c>
+      <c r="E256" t="s">
+        <v>764</v>
+      </c>
+      <c r="F256" t="s">
+        <v>765</v>
+      </c>
+      <c r="G256" t="s">
+        <v>766</v>
+      </c>
+      <c r="H256" t="s">
         <v>769</v>
       </c>
-      <c r="E256" t="s">
-        <v>765</v>
-      </c>
-      <c r="F256" t="s">
-        <v>766</v>
-      </c>
-      <c r="G256" t="s">
-        <v>767</v>
-      </c>
-      <c r="H256" t="s">
+      <c r="I256" t="s">
         <v>770</v>
-      </c>
-      <c r="I256" t="s">
-        <v>771</v>
       </c>
       <c r="J256">
         <v>0</v>
@@ -44932,28 +44941,28 @@
         <v>0</v>
       </c>
       <c r="C257" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D257" t="s">
+        <v>771</v>
+      </c>
+      <c r="E257" t="s">
+        <v>764</v>
+      </c>
+      <c r="F257" t="s">
+        <v>765</v>
+      </c>
+      <c r="G257" t="s">
+        <v>766</v>
+      </c>
+      <c r="H257" t="s">
         <v>772</v>
       </c>
-      <c r="E257" t="s">
-        <v>765</v>
-      </c>
-      <c r="F257" t="s">
-        <v>766</v>
-      </c>
-      <c r="G257" t="s">
-        <v>767</v>
-      </c>
-      <c r="H257" t="s">
+      <c r="I257" t="s">
+        <v>770</v>
+      </c>
+      <c r="J257" t="s">
         <v>773</v>
-      </c>
-      <c r="I257" t="s">
-        <v>771</v>
-      </c>
-      <c r="J257" t="s">
-        <v>774</v>
       </c>
       <c r="K257">
         <v>0</v>
@@ -44989,28 +44998,28 @@
         <v>0</v>
       </c>
       <c r="C258" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D258" t="s">
+        <v>774</v>
+      </c>
+      <c r="E258" t="s">
+        <v>764</v>
+      </c>
+      <c r="F258" t="s">
+        <v>765</v>
+      </c>
+      <c r="G258" t="s">
         <v>775</v>
       </c>
-      <c r="E258" t="s">
-        <v>765</v>
-      </c>
-      <c r="F258" t="s">
-        <v>766</v>
-      </c>
-      <c r="G258" t="s">
+      <c r="H258" t="s">
+        <v>772</v>
+      </c>
+      <c r="I258" t="s">
         <v>776</v>
       </c>
-      <c r="H258" t="s">
+      <c r="J258" t="s">
         <v>773</v>
-      </c>
-      <c r="I258" t="s">
-        <v>777</v>
-      </c>
-      <c r="J258" t="s">
-        <v>774</v>
       </c>
       <c r="K258">
         <v>0</v>
@@ -45046,28 +45055,28 @@
         <v>0</v>
       </c>
       <c r="C259" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D259" t="s">
+        <v>777</v>
+      </c>
+      <c r="E259" t="s">
+        <v>764</v>
+      </c>
+      <c r="F259" t="s">
+        <v>765</v>
+      </c>
+      <c r="G259" t="s">
         <v>778</v>
       </c>
-      <c r="E259" t="s">
-        <v>765</v>
-      </c>
-      <c r="F259" t="s">
-        <v>766</v>
-      </c>
-      <c r="G259" t="s">
+      <c r="H259" t="s">
+        <v>772</v>
+      </c>
+      <c r="I259" t="s">
+        <v>776</v>
+      </c>
+      <c r="J259" t="s">
         <v>779</v>
-      </c>
-      <c r="H259" t="s">
-        <v>773</v>
-      </c>
-      <c r="I259" t="s">
-        <v>777</v>
-      </c>
-      <c r="J259" t="s">
-        <v>780</v>
       </c>
       <c r="K259">
         <v>0</v>
@@ -45103,31 +45112,31 @@
         <v>0</v>
       </c>
       <c r="C260" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D260" t="s">
+        <v>780</v>
+      </c>
+      <c r="E260" t="s">
+        <v>764</v>
+      </c>
+      <c r="F260" t="s">
+        <v>765</v>
+      </c>
+      <c r="G260" t="s">
         <v>781</v>
       </c>
-      <c r="E260" t="s">
-        <v>765</v>
-      </c>
-      <c r="F260" t="s">
-        <v>766</v>
-      </c>
-      <c r="G260" t="s">
+      <c r="H260" t="s">
+        <v>772</v>
+      </c>
+      <c r="I260" t="s">
+        <v>776</v>
+      </c>
+      <c r="J260" t="s">
+        <v>779</v>
+      </c>
+      <c r="K260" t="s">
         <v>782</v>
-      </c>
-      <c r="H260" t="s">
-        <v>773</v>
-      </c>
-      <c r="I260" t="s">
-        <v>777</v>
-      </c>
-      <c r="J260" t="s">
-        <v>780</v>
-      </c>
-      <c r="K260" t="s">
-        <v>783</v>
       </c>
       <c r="L260">
         <v>0</v>
@@ -45160,31 +45169,31 @@
         <v>0</v>
       </c>
       <c r="C261" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D261" t="s">
+        <v>783</v>
+      </c>
+      <c r="E261" t="s">
+        <v>764</v>
+      </c>
+      <c r="F261" t="s">
+        <v>765</v>
+      </c>
+      <c r="G261" t="s">
         <v>784</v>
       </c>
-      <c r="E261" t="s">
-        <v>765</v>
-      </c>
-      <c r="F261" t="s">
-        <v>766</v>
-      </c>
-      <c r="G261" t="s">
+      <c r="H261" t="s">
         <v>785</v>
       </c>
-      <c r="H261" t="s">
+      <c r="I261" t="s">
+        <v>779</v>
+      </c>
+      <c r="J261" t="s">
         <v>786</v>
       </c>
-      <c r="I261" t="s">
-        <v>780</v>
-      </c>
-      <c r="J261" t="s">
+      <c r="K261" t="s">
         <v>787</v>
-      </c>
-      <c r="K261" t="s">
-        <v>788</v>
       </c>
       <c r="L261">
         <v>0</v>
@@ -45217,31 +45226,31 @@
         <v>0</v>
       </c>
       <c r="C262" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D262" t="s">
+        <v>788</v>
+      </c>
+      <c r="E262" t="s">
+        <v>764</v>
+      </c>
+      <c r="F262" t="s">
+        <v>765</v>
+      </c>
+      <c r="G262" t="s">
+        <v>772</v>
+      </c>
+      <c r="H262" t="s">
+        <v>785</v>
+      </c>
+      <c r="I262" t="s">
+        <v>779</v>
+      </c>
+      <c r="J262" t="s">
+        <v>786</v>
+      </c>
+      <c r="K262" t="s">
         <v>789</v>
-      </c>
-      <c r="E262" t="s">
-        <v>765</v>
-      </c>
-      <c r="F262" t="s">
-        <v>766</v>
-      </c>
-      <c r="G262" t="s">
-        <v>773</v>
-      </c>
-      <c r="H262" t="s">
-        <v>786</v>
-      </c>
-      <c r="I262" t="s">
-        <v>780</v>
-      </c>
-      <c r="J262" t="s">
-        <v>787</v>
-      </c>
-      <c r="K262" t="s">
-        <v>790</v>
       </c>
       <c r="L262">
         <v>0</v>
@@ -45274,31 +45283,31 @@
         <v>0</v>
       </c>
       <c r="C263" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D263" t="s">
+        <v>790</v>
+      </c>
+      <c r="E263" t="s">
+        <v>764</v>
+      </c>
+      <c r="F263" t="s">
+        <v>765</v>
+      </c>
+      <c r="G263" t="s">
+        <v>785</v>
+      </c>
+      <c r="H263" t="s">
         <v>791</v>
       </c>
-      <c r="E263" t="s">
-        <v>765</v>
-      </c>
-      <c r="F263" t="s">
-        <v>766</v>
-      </c>
-      <c r="G263" t="s">
+      <c r="I263" t="s">
         <v>786</v>
       </c>
-      <c r="H263" t="s">
+      <c r="J263" t="s">
         <v>792</v>
       </c>
-      <c r="I263" t="s">
-        <v>787</v>
-      </c>
-      <c r="J263" t="s">
+      <c r="K263" t="s">
         <v>793</v>
-      </c>
-      <c r="K263" t="s">
-        <v>794</v>
       </c>
       <c r="L263">
         <v>0</v>
@@ -45331,31 +45340,31 @@
         <v>0</v>
       </c>
       <c r="C264" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D264" t="s">
+        <v>794</v>
+      </c>
+      <c r="E264" t="s">
+        <v>764</v>
+      </c>
+      <c r="F264" t="s">
+        <v>765</v>
+      </c>
+      <c r="G264" t="s">
+        <v>791</v>
+      </c>
+      <c r="H264" t="s">
         <v>795</v>
       </c>
-      <c r="E264" t="s">
-        <v>765</v>
-      </c>
-      <c r="F264" t="s">
-        <v>766</v>
-      </c>
-      <c r="G264" t="s">
+      <c r="I264" t="s">
         <v>792</v>
       </c>
-      <c r="H264" t="s">
+      <c r="J264" t="s">
         <v>796</v>
       </c>
-      <c r="I264" t="s">
-        <v>793</v>
-      </c>
-      <c r="J264" t="s">
+      <c r="K264" t="s">
         <v>797</v>
-      </c>
-      <c r="K264" t="s">
-        <v>798</v>
       </c>
       <c r="L264">
         <v>0</v>
@@ -45388,31 +45397,31 @@
         <v>0</v>
       </c>
       <c r="C265" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D265" t="s">
+        <v>798</v>
+      </c>
+      <c r="E265" t="s">
+        <v>764</v>
+      </c>
+      <c r="F265" t="s">
+        <v>765</v>
+      </c>
+      <c r="G265" t="s">
+        <v>795</v>
+      </c>
+      <c r="H265" t="s">
         <v>799</v>
       </c>
-      <c r="E265" t="s">
-        <v>765</v>
-      </c>
-      <c r="F265" t="s">
-        <v>766</v>
-      </c>
-      <c r="G265" t="s">
+      <c r="I265" t="s">
         <v>796</v>
       </c>
-      <c r="H265" t="s">
+      <c r="J265" t="s">
         <v>800</v>
       </c>
-      <c r="I265" t="s">
-        <v>797</v>
-      </c>
-      <c r="J265" t="s">
+      <c r="K265" t="s">
         <v>801</v>
-      </c>
-      <c r="K265" t="s">
-        <v>802</v>
       </c>
       <c r="L265">
         <v>0</v>
@@ -45445,31 +45454,31 @@
         <v>0</v>
       </c>
       <c r="C266" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D266" t="s">
+        <v>802</v>
+      </c>
+      <c r="E266" t="s">
+        <v>764</v>
+      </c>
+      <c r="F266" t="s">
+        <v>765</v>
+      </c>
+      <c r="G266" t="s">
+        <v>799</v>
+      </c>
+      <c r="H266" t="s">
         <v>803</v>
       </c>
-      <c r="E266" t="s">
-        <v>765</v>
-      </c>
-      <c r="F266" t="s">
-        <v>766</v>
-      </c>
-      <c r="G266" t="s">
+      <c r="I266" t="s">
         <v>800</v>
       </c>
-      <c r="H266" t="s">
+      <c r="J266" t="s">
         <v>804</v>
       </c>
-      <c r="I266" t="s">
-        <v>801</v>
-      </c>
-      <c r="J266" t="s">
+      <c r="K266" t="s">
         <v>805</v>
-      </c>
-      <c r="K266" t="s">
-        <v>806</v>
       </c>
       <c r="L266">
         <v>0</v>
@@ -45502,31 +45511,31 @@
         <v>0</v>
       </c>
       <c r="C267" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D267" t="s">
+        <v>806</v>
+      </c>
+      <c r="E267" t="s">
+        <v>764</v>
+      </c>
+      <c r="F267" t="s">
+        <v>765</v>
+      </c>
+      <c r="G267" t="s">
+        <v>803</v>
+      </c>
+      <c r="H267" t="s">
         <v>807</v>
       </c>
-      <c r="E267" t="s">
-        <v>765</v>
-      </c>
-      <c r="F267" t="s">
-        <v>766</v>
-      </c>
-      <c r="G267" t="s">
+      <c r="I267" t="s">
         <v>804</v>
       </c>
-      <c r="H267" t="s">
+      <c r="J267" t="s">
         <v>808</v>
       </c>
-      <c r="I267" t="s">
-        <v>805</v>
-      </c>
-      <c r="J267" t="s">
+      <c r="K267" t="s">
         <v>809</v>
-      </c>
-      <c r="K267" t="s">
-        <v>810</v>
       </c>
       <c r="L267">
         <v>0</v>
@@ -45559,31 +45568,31 @@
         <v>0</v>
       </c>
       <c r="C268" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D268" t="s">
+        <v>810</v>
+      </c>
+      <c r="E268" t="s">
+        <v>764</v>
+      </c>
+      <c r="F268" t="s">
+        <v>765</v>
+      </c>
+      <c r="G268" t="s">
+        <v>807</v>
+      </c>
+      <c r="H268" t="s">
         <v>811</v>
       </c>
-      <c r="E268" t="s">
-        <v>765</v>
-      </c>
-      <c r="F268" t="s">
-        <v>766</v>
-      </c>
-      <c r="G268" t="s">
+      <c r="I268" t="s">
         <v>808</v>
       </c>
-      <c r="H268" t="s">
+      <c r="J268" t="s">
         <v>812</v>
       </c>
-      <c r="I268" t="s">
-        <v>809</v>
-      </c>
-      <c r="J268" t="s">
+      <c r="K268" t="s">
         <v>813</v>
-      </c>
-      <c r="K268" t="s">
-        <v>814</v>
       </c>
       <c r="L268">
         <v>0</v>
@@ -45616,31 +45625,31 @@
         <v>0</v>
       </c>
       <c r="C269" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D269" t="s">
+        <v>814</v>
+      </c>
+      <c r="E269" t="s">
+        <v>764</v>
+      </c>
+      <c r="F269" t="s">
+        <v>765</v>
+      </c>
+      <c r="G269" t="s">
+        <v>811</v>
+      </c>
+      <c r="H269" t="s">
         <v>815</v>
       </c>
-      <c r="E269" t="s">
-        <v>765</v>
-      </c>
-      <c r="F269" t="s">
-        <v>766</v>
-      </c>
-      <c r="G269" t="s">
+      <c r="I269" t="s">
         <v>812</v>
       </c>
-      <c r="H269" t="s">
+      <c r="J269" t="s">
         <v>816</v>
       </c>
-      <c r="I269" t="s">
-        <v>813</v>
-      </c>
-      <c r="J269" t="s">
+      <c r="K269" t="s">
         <v>817</v>
-      </c>
-      <c r="K269" t="s">
-        <v>818</v>
       </c>
       <c r="L269">
         <v>0</v>
@@ -45673,31 +45682,31 @@
         <v>0</v>
       </c>
       <c r="C270" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D270" t="s">
+        <v>818</v>
+      </c>
+      <c r="E270" t="s">
+        <v>764</v>
+      </c>
+      <c r="F270" t="s">
+        <v>765</v>
+      </c>
+      <c r="G270" t="s">
+        <v>815</v>
+      </c>
+      <c r="H270" t="s">
         <v>819</v>
       </c>
-      <c r="E270" t="s">
-        <v>765</v>
-      </c>
-      <c r="F270" t="s">
-        <v>766</v>
-      </c>
-      <c r="G270" t="s">
+      <c r="I270" t="s">
         <v>816</v>
       </c>
-      <c r="H270" t="s">
+      <c r="J270" t="s">
         <v>820</v>
       </c>
-      <c r="I270" t="s">
-        <v>817</v>
-      </c>
-      <c r="J270" t="s">
+      <c r="K270" t="s">
         <v>821</v>
-      </c>
-      <c r="K270" t="s">
-        <v>822</v>
       </c>
       <c r="L270">
         <v>0</v>
@@ -45730,31 +45739,31 @@
         <v>0</v>
       </c>
       <c r="C271" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D271" t="s">
+        <v>822</v>
+      </c>
+      <c r="E271" t="s">
+        <v>764</v>
+      </c>
+      <c r="F271" t="s">
+        <v>765</v>
+      </c>
+      <c r="G271" t="s">
+        <v>819</v>
+      </c>
+      <c r="H271" t="s">
         <v>823</v>
       </c>
-      <c r="E271" t="s">
-        <v>765</v>
-      </c>
-      <c r="F271" t="s">
-        <v>766</v>
-      </c>
-      <c r="G271" t="s">
+      <c r="I271" t="s">
         <v>820</v>
       </c>
-      <c r="H271" t="s">
+      <c r="J271" t="s">
         <v>824</v>
       </c>
-      <c r="I271" t="s">
-        <v>821</v>
-      </c>
-      <c r="J271" t="s">
+      <c r="K271" t="s">
         <v>825</v>
-      </c>
-      <c r="K271" t="s">
-        <v>826</v>
       </c>
       <c r="L271">
         <v>0</v>
@@ -45787,34 +45796,34 @@
         <v>0</v>
       </c>
       <c r="C272" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D272" t="s">
+        <v>826</v>
+      </c>
+      <c r="E272" t="s">
+        <v>764</v>
+      </c>
+      <c r="F272" t="s">
+        <v>765</v>
+      </c>
+      <c r="G272" t="s">
+        <v>809</v>
+      </c>
+      <c r="H272" t="s">
         <v>827</v>
       </c>
-      <c r="E272" t="s">
-        <v>765</v>
-      </c>
-      <c r="F272" t="s">
-        <v>766</v>
-      </c>
-      <c r="G272" t="s">
-        <v>810</v>
-      </c>
-      <c r="H272" t="s">
+      <c r="I272" t="s">
         <v>828</v>
       </c>
-      <c r="I272" t="s">
+      <c r="J272" t="s">
+        <v>824</v>
+      </c>
+      <c r="K272" t="s">
         <v>829</v>
       </c>
-      <c r="J272" t="s">
-        <v>825</v>
-      </c>
-      <c r="K272" t="s">
+      <c r="L272" t="s">
         <v>830</v>
-      </c>
-      <c r="L272" t="s">
-        <v>831</v>
       </c>
       <c r="M272">
         <v>0</v>
@@ -45844,34 +45853,34 @@
         <v>0</v>
       </c>
       <c r="C273" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D273" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E273" t="s">
+        <v>764</v>
+      </c>
+      <c r="F273" t="s">
         <v>765</v>
       </c>
-      <c r="F273" t="s">
-        <v>766</v>
-      </c>
       <c r="G273" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H273" t="s">
+        <v>827</v>
+      </c>
+      <c r="I273" t="s">
         <v>828</v>
       </c>
-      <c r="I273" t="s">
+      <c r="J273" t="s">
+        <v>824</v>
+      </c>
+      <c r="K273" t="s">
         <v>829</v>
       </c>
-      <c r="J273" t="s">
-        <v>825</v>
-      </c>
-      <c r="K273" t="s">
+      <c r="L273" t="s">
         <v>830</v>
-      </c>
-      <c r="L273" t="s">
-        <v>831</v>
       </c>
       <c r="M273">
         <v>0</v>
@@ -45901,34 +45910,34 @@
         <v>0</v>
       </c>
       <c r="C274" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D274" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E274" t="s">
+        <v>764</v>
+      </c>
+      <c r="F274" t="s">
         <v>765</v>
       </c>
-      <c r="F274" t="s">
-        <v>766</v>
-      </c>
       <c r="G274" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H274" t="s">
+        <v>827</v>
+      </c>
+      <c r="I274" t="s">
         <v>828</v>
       </c>
-      <c r="I274" t="s">
+      <c r="J274" t="s">
+        <v>824</v>
+      </c>
+      <c r="K274" t="s">
         <v>829</v>
       </c>
-      <c r="J274" t="s">
-        <v>825</v>
-      </c>
-      <c r="K274" t="s">
+      <c r="L274" t="s">
         <v>830</v>
-      </c>
-      <c r="L274" t="s">
-        <v>831</v>
       </c>
       <c r="M274">
         <v>0</v>
@@ -45958,28 +45967,28 @@
         <v>0</v>
       </c>
       <c r="C275" t="s">
+        <v>833</v>
+      </c>
+      <c r="D275" t="s">
+        <v>763</v>
+      </c>
+      <c r="E275" t="s">
         <v>834</v>
       </c>
-      <c r="D275" t="s">
-        <v>764</v>
-      </c>
-      <c r="E275" t="s">
+      <c r="F275" t="s">
         <v>835</v>
       </c>
-      <c r="F275" t="s">
+      <c r="G275" t="s">
         <v>836</v>
       </c>
-      <c r="G275" t="s">
+      <c r="H275" t="s">
         <v>837</v>
       </c>
-      <c r="H275" t="s">
+      <c r="I275" t="s">
         <v>838</v>
       </c>
-      <c r="I275" t="s">
+      <c r="J275" t="s">
         <v>839</v>
-      </c>
-      <c r="J275" t="s">
-        <v>840</v>
       </c>
       <c r="K275">
         <v>0</v>
@@ -46015,28 +46024,28 @@
         <v>0</v>
       </c>
       <c r="C276" t="s">
+        <v>833</v>
+      </c>
+      <c r="D276" t="s">
+        <v>768</v>
+      </c>
+      <c r="E276" t="s">
         <v>834</v>
       </c>
-      <c r="D276" t="s">
-        <v>769</v>
-      </c>
-      <c r="E276" t="s">
+      <c r="F276" t="s">
         <v>835</v>
       </c>
-      <c r="F276" t="s">
-        <v>836</v>
-      </c>
       <c r="G276" t="s">
+        <v>840</v>
+      </c>
+      <c r="H276" t="s">
+        <v>837</v>
+      </c>
+      <c r="I276" t="s">
         <v>841</v>
       </c>
-      <c r="H276" t="s">
-        <v>838</v>
-      </c>
-      <c r="I276" t="s">
+      <c r="J276" t="s">
         <v>842</v>
-      </c>
-      <c r="J276" t="s">
-        <v>843</v>
       </c>
       <c r="K276">
         <v>0</v>
@@ -46072,28 +46081,28 @@
         <v>0</v>
       </c>
       <c r="C277" t="s">
+        <v>833</v>
+      </c>
+      <c r="D277" t="s">
+        <v>771</v>
+      </c>
+      <c r="E277" t="s">
         <v>834</v>
       </c>
-      <c r="D277" t="s">
-        <v>772</v>
-      </c>
-      <c r="E277" t="s">
+      <c r="F277" t="s">
         <v>835</v>
       </c>
-      <c r="F277" t="s">
-        <v>836</v>
-      </c>
       <c r="G277" t="s">
+        <v>843</v>
+      </c>
+      <c r="H277" t="s">
+        <v>837</v>
+      </c>
+      <c r="I277" t="s">
         <v>844</v>
       </c>
-      <c r="H277" t="s">
-        <v>838</v>
-      </c>
-      <c r="I277" t="s">
+      <c r="J277" t="s">
         <v>845</v>
-      </c>
-      <c r="J277" t="s">
-        <v>846</v>
       </c>
       <c r="K277">
         <v>0</v>
@@ -46129,31 +46138,31 @@
         <v>0</v>
       </c>
       <c r="C278" t="s">
+        <v>833</v>
+      </c>
+      <c r="D278" t="s">
+        <v>774</v>
+      </c>
+      <c r="E278" t="s">
         <v>834</v>
       </c>
-      <c r="D278" t="s">
-        <v>775</v>
-      </c>
-      <c r="E278" t="s">
+      <c r="F278" t="s">
         <v>835</v>
       </c>
-      <c r="F278" t="s">
-        <v>836</v>
-      </c>
       <c r="G278" t="s">
+        <v>846</v>
+      </c>
+      <c r="H278" t="s">
+        <v>837</v>
+      </c>
+      <c r="I278" t="s">
+        <v>844</v>
+      </c>
+      <c r="J278" t="s">
+        <v>845</v>
+      </c>
+      <c r="K278" t="s">
         <v>847</v>
-      </c>
-      <c r="H278" t="s">
-        <v>838</v>
-      </c>
-      <c r="I278" t="s">
-        <v>845</v>
-      </c>
-      <c r="J278" t="s">
-        <v>846</v>
-      </c>
-      <c r="K278" t="s">
-        <v>848</v>
       </c>
       <c r="L278">
         <v>0</v>
@@ -46186,31 +46195,31 @@
         <v>0</v>
       </c>
       <c r="C279" t="s">
+        <v>833</v>
+      </c>
+      <c r="D279" t="s">
+        <v>777</v>
+      </c>
+      <c r="E279" t="s">
         <v>834</v>
       </c>
-      <c r="D279" t="s">
-        <v>778</v>
-      </c>
-      <c r="E279" t="s">
+      <c r="F279" t="s">
         <v>835</v>
       </c>
-      <c r="F279" t="s">
-        <v>836</v>
-      </c>
       <c r="G279" t="s">
+        <v>848</v>
+      </c>
+      <c r="H279" t="s">
+        <v>837</v>
+      </c>
+      <c r="I279" t="s">
+        <v>844</v>
+      </c>
+      <c r="J279" t="s">
         <v>849</v>
       </c>
-      <c r="H279" t="s">
-        <v>838</v>
-      </c>
-      <c r="I279" t="s">
-        <v>845</v>
-      </c>
-      <c r="J279" t="s">
+      <c r="K279" t="s">
         <v>850</v>
-      </c>
-      <c r="K279" t="s">
-        <v>851</v>
       </c>
       <c r="L279">
         <v>0</v>
@@ -46243,31 +46252,31 @@
         <v>0</v>
       </c>
       <c r="C280" t="s">
+        <v>833</v>
+      </c>
+      <c r="D280" t="s">
+        <v>780</v>
+      </c>
+      <c r="E280" t="s">
         <v>834</v>
       </c>
-      <c r="D280" t="s">
-        <v>781</v>
-      </c>
-      <c r="E280" t="s">
+      <c r="F280" t="s">
         <v>835</v>
       </c>
-      <c r="F280" t="s">
-        <v>836</v>
-      </c>
       <c r="G280" t="s">
+        <v>851</v>
+      </c>
+      <c r="H280" t="s">
+        <v>837</v>
+      </c>
+      <c r="I280" t="s">
+        <v>844</v>
+      </c>
+      <c r="J280" t="s">
         <v>852</v>
       </c>
-      <c r="H280" t="s">
-        <v>838</v>
-      </c>
-      <c r="I280" t="s">
-        <v>845</v>
-      </c>
-      <c r="J280" t="s">
+      <c r="K280" t="s">
         <v>853</v>
-      </c>
-      <c r="K280" t="s">
-        <v>854</v>
       </c>
       <c r="L280">
         <v>0</v>
@@ -46300,31 +46309,31 @@
         <v>0</v>
       </c>
       <c r="C281" t="s">
+        <v>833</v>
+      </c>
+      <c r="D281" t="s">
+        <v>783</v>
+      </c>
+      <c r="E281" t="s">
         <v>834</v>
       </c>
-      <c r="D281" t="s">
-        <v>784</v>
-      </c>
-      <c r="E281" t="s">
+      <c r="F281" t="s">
         <v>835</v>
       </c>
-      <c r="F281" t="s">
-        <v>836</v>
-      </c>
       <c r="G281" t="s">
+        <v>854</v>
+      </c>
+      <c r="H281" t="s">
+        <v>837</v>
+      </c>
+      <c r="I281" t="s">
         <v>855</v>
       </c>
-      <c r="H281" t="s">
-        <v>838</v>
-      </c>
-      <c r="I281" t="s">
+      <c r="J281" t="s">
         <v>856</v>
       </c>
-      <c r="J281" t="s">
+      <c r="K281" t="s">
         <v>857</v>
-      </c>
-      <c r="K281" t="s">
-        <v>858</v>
       </c>
       <c r="L281">
         <v>0</v>
@@ -46357,31 +46366,31 @@
         <v>0</v>
       </c>
       <c r="C282" t="s">
+        <v>833</v>
+      </c>
+      <c r="D282" t="s">
+        <v>788</v>
+      </c>
+      <c r="E282" t="s">
         <v>834</v>
       </c>
-      <c r="D282" t="s">
-        <v>789</v>
-      </c>
-      <c r="E282" t="s">
+      <c r="F282" t="s">
         <v>835</v>
       </c>
-      <c r="F282" t="s">
-        <v>836</v>
-      </c>
       <c r="G282" t="s">
+        <v>858</v>
+      </c>
+      <c r="H282" t="s">
+        <v>837</v>
+      </c>
+      <c r="I282" t="s">
         <v>859</v>
       </c>
-      <c r="H282" t="s">
-        <v>838</v>
-      </c>
-      <c r="I282" t="s">
+      <c r="J282" t="s">
         <v>860</v>
       </c>
-      <c r="J282" t="s">
+      <c r="K282" t="s">
         <v>861</v>
-      </c>
-      <c r="K282" t="s">
-        <v>862</v>
       </c>
       <c r="L282">
         <v>0</v>
@@ -46414,31 +46423,31 @@
         <v>0</v>
       </c>
       <c r="C283" t="s">
+        <v>833</v>
+      </c>
+      <c r="D283" t="s">
+        <v>790</v>
+      </c>
+      <c r="E283" t="s">
         <v>834</v>
       </c>
-      <c r="D283" t="s">
-        <v>791</v>
-      </c>
-      <c r="E283" t="s">
+      <c r="F283" t="s">
         <v>835</v>
       </c>
-      <c r="F283" t="s">
-        <v>836</v>
-      </c>
       <c r="G283" t="s">
+        <v>862</v>
+      </c>
+      <c r="H283" t="s">
+        <v>837</v>
+      </c>
+      <c r="I283" t="s">
         <v>863</v>
       </c>
-      <c r="H283" t="s">
-        <v>838</v>
-      </c>
-      <c r="I283" t="s">
+      <c r="J283" t="s">
         <v>864</v>
       </c>
-      <c r="J283" t="s">
+      <c r="K283" t="s">
         <v>865</v>
-      </c>
-      <c r="K283" t="s">
-        <v>866</v>
       </c>
       <c r="L283">
         <v>0</v>
@@ -46471,34 +46480,34 @@
         <v>0</v>
       </c>
       <c r="C284" t="s">
+        <v>833</v>
+      </c>
+      <c r="D284" t="s">
+        <v>794</v>
+      </c>
+      <c r="E284" t="s">
         <v>834</v>
       </c>
-      <c r="D284" t="s">
-        <v>795</v>
-      </c>
-      <c r="E284" t="s">
+      <c r="F284" t="s">
         <v>835</v>
       </c>
-      <c r="F284" t="s">
-        <v>836</v>
-      </c>
       <c r="G284" t="s">
+        <v>866</v>
+      </c>
+      <c r="H284" t="s">
+        <v>837</v>
+      </c>
+      <c r="I284" t="s">
+        <v>863</v>
+      </c>
+      <c r="J284" t="s">
+        <v>864</v>
+      </c>
+      <c r="K284" t="s">
         <v>867</v>
       </c>
-      <c r="H284" t="s">
-        <v>838</v>
-      </c>
-      <c r="I284" t="s">
-        <v>864</v>
-      </c>
-      <c r="J284" t="s">
-        <v>865</v>
-      </c>
-      <c r="K284" t="s">
+      <c r="L284" t="s">
         <v>868</v>
-      </c>
-      <c r="L284" t="s">
-        <v>869</v>
       </c>
       <c r="M284">
         <v>0</v>
@@ -46528,34 +46537,34 @@
         <v>0</v>
       </c>
       <c r="C285" t="s">
+        <v>833</v>
+      </c>
+      <c r="D285" t="s">
+        <v>798</v>
+      </c>
+      <c r="E285" t="s">
         <v>834</v>
       </c>
-      <c r="D285" t="s">
-        <v>799</v>
-      </c>
-      <c r="E285" t="s">
+      <c r="F285" t="s">
         <v>835</v>
       </c>
-      <c r="F285" t="s">
-        <v>836</v>
-      </c>
       <c r="G285" t="s">
+        <v>869</v>
+      </c>
+      <c r="H285" t="s">
+        <v>837</v>
+      </c>
+      <c r="I285" t="s">
+        <v>863</v>
+      </c>
+      <c r="J285" t="s">
+        <v>864</v>
+      </c>
+      <c r="K285" t="s">
         <v>870</v>
       </c>
-      <c r="H285" t="s">
-        <v>838</v>
-      </c>
-      <c r="I285" t="s">
-        <v>864</v>
-      </c>
-      <c r="J285" t="s">
-        <v>865</v>
-      </c>
-      <c r="K285" t="s">
+      <c r="L285" t="s">
         <v>871</v>
-      </c>
-      <c r="L285" t="s">
-        <v>872</v>
       </c>
       <c r="M285">
         <v>0</v>
@@ -46585,34 +46594,34 @@
         <v>0</v>
       </c>
       <c r="C286" t="s">
+        <v>833</v>
+      </c>
+      <c r="D286" t="s">
+        <v>802</v>
+      </c>
+      <c r="E286" t="s">
         <v>834</v>
       </c>
-      <c r="D286" t="s">
-        <v>803</v>
-      </c>
-      <c r="E286" t="s">
+      <c r="F286" t="s">
         <v>835</v>
       </c>
-      <c r="F286" t="s">
-        <v>836</v>
-      </c>
       <c r="G286" t="s">
+        <v>872</v>
+      </c>
+      <c r="H286" t="s">
+        <v>837</v>
+      </c>
+      <c r="I286" t="s">
         <v>873</v>
       </c>
-      <c r="H286" t="s">
-        <v>838</v>
-      </c>
-      <c r="I286" t="s">
+      <c r="J286" t="s">
         <v>874</v>
       </c>
-      <c r="J286" t="s">
+      <c r="K286" t="s">
         <v>875</v>
       </c>
-      <c r="K286" t="s">
+      <c r="L286" t="s">
         <v>876</v>
-      </c>
-      <c r="L286" t="s">
-        <v>877</v>
       </c>
       <c r="M286">
         <v>0</v>
@@ -46642,34 +46651,34 @@
         <v>0</v>
       </c>
       <c r="C287" t="s">
+        <v>833</v>
+      </c>
+      <c r="D287" t="s">
+        <v>806</v>
+      </c>
+      <c r="E287" t="s">
         <v>834</v>
       </c>
-      <c r="D287" t="s">
-        <v>807</v>
-      </c>
-      <c r="E287" t="s">
+      <c r="F287" t="s">
         <v>835</v>
       </c>
-      <c r="F287" t="s">
-        <v>836</v>
-      </c>
       <c r="G287" t="s">
+        <v>877</v>
+      </c>
+      <c r="H287" t="s">
+        <v>837</v>
+      </c>
+      <c r="I287" t="s">
+        <v>873</v>
+      </c>
+      <c r="J287" t="s">
+        <v>874</v>
+      </c>
+      <c r="K287" t="s">
+        <v>875</v>
+      </c>
+      <c r="L287" t="s">
         <v>878</v>
-      </c>
-      <c r="H287" t="s">
-        <v>838</v>
-      </c>
-      <c r="I287" t="s">
-        <v>874</v>
-      </c>
-      <c r="J287" t="s">
-        <v>875</v>
-      </c>
-      <c r="K287" t="s">
-        <v>876</v>
-      </c>
-      <c r="L287" t="s">
-        <v>879</v>
       </c>
       <c r="M287">
         <v>0</v>
@@ -46699,34 +46708,34 @@
         <v>0</v>
       </c>
       <c r="C288" t="s">
+        <v>833</v>
+      </c>
+      <c r="D288" t="s">
+        <v>810</v>
+      </c>
+      <c r="E288" t="s">
         <v>834</v>
       </c>
-      <c r="D288" t="s">
-        <v>811</v>
-      </c>
-      <c r="E288" t="s">
+      <c r="F288" t="s">
         <v>835</v>
       </c>
-      <c r="F288" t="s">
-        <v>836</v>
-      </c>
       <c r="G288" t="s">
+        <v>879</v>
+      </c>
+      <c r="H288" t="s">
+        <v>837</v>
+      </c>
+      <c r="I288" t="s">
+        <v>873</v>
+      </c>
+      <c r="J288" t="s">
+        <v>874</v>
+      </c>
+      <c r="K288" t="s">
+        <v>875</v>
+      </c>
+      <c r="L288" t="s">
         <v>880</v>
-      </c>
-      <c r="H288" t="s">
-        <v>838</v>
-      </c>
-      <c r="I288" t="s">
-        <v>874</v>
-      </c>
-      <c r="J288" t="s">
-        <v>875</v>
-      </c>
-      <c r="K288" t="s">
-        <v>876</v>
-      </c>
-      <c r="L288" t="s">
-        <v>881</v>
       </c>
       <c r="M288">
         <v>0</v>
@@ -46756,37 +46765,37 @@
         <v>0</v>
       </c>
       <c r="C289" t="s">
+        <v>833</v>
+      </c>
+      <c r="D289" t="s">
+        <v>814</v>
+      </c>
+      <c r="E289" t="s">
         <v>834</v>
       </c>
-      <c r="D289" t="s">
-        <v>815</v>
-      </c>
-      <c r="E289" t="s">
+      <c r="F289" t="s">
         <v>835</v>
       </c>
-      <c r="F289" t="s">
-        <v>836</v>
-      </c>
       <c r="G289" t="s">
+        <v>881</v>
+      </c>
+      <c r="H289" t="s">
+        <v>837</v>
+      </c>
+      <c r="I289" t="s">
+        <v>873</v>
+      </c>
+      <c r="J289" t="s">
         <v>882</v>
       </c>
-      <c r="H289" t="s">
-        <v>838</v>
-      </c>
-      <c r="I289" t="s">
-        <v>874</v>
-      </c>
-      <c r="J289" t="s">
+      <c r="K289" t="s">
         <v>883</v>
       </c>
-      <c r="K289" t="s">
+      <c r="L289" t="s">
+        <v>876</v>
+      </c>
+      <c r="M289" t="s">
         <v>884</v>
-      </c>
-      <c r="L289" t="s">
-        <v>877</v>
-      </c>
-      <c r="M289" t="s">
-        <v>885</v>
       </c>
       <c r="N289">
         <v>0</v>
@@ -46813,37 +46822,37 @@
         <v>0</v>
       </c>
       <c r="C290" t="s">
+        <v>833</v>
+      </c>
+      <c r="D290" t="s">
+        <v>818</v>
+      </c>
+      <c r="E290" t="s">
         <v>834</v>
       </c>
-      <c r="D290" t="s">
-        <v>819</v>
-      </c>
-      <c r="E290" t="s">
+      <c r="F290" t="s">
         <v>835</v>
       </c>
-      <c r="F290" t="s">
-        <v>836</v>
-      </c>
       <c r="G290" t="s">
+        <v>885</v>
+      </c>
+      <c r="H290" t="s">
+        <v>837</v>
+      </c>
+      <c r="I290" t="s">
+        <v>873</v>
+      </c>
+      <c r="J290" t="s">
+        <v>882</v>
+      </c>
+      <c r="K290" t="s">
+        <v>883</v>
+      </c>
+      <c r="L290" t="s">
+        <v>878</v>
+      </c>
+      <c r="M290" t="s">
         <v>886</v>
-      </c>
-      <c r="H290" t="s">
-        <v>838</v>
-      </c>
-      <c r="I290" t="s">
-        <v>874</v>
-      </c>
-      <c r="J290" t="s">
-        <v>883</v>
-      </c>
-      <c r="K290" t="s">
-        <v>884</v>
-      </c>
-      <c r="L290" t="s">
-        <v>879</v>
-      </c>
-      <c r="M290" t="s">
-        <v>887</v>
       </c>
       <c r="N290">
         <v>0</v>
@@ -46870,37 +46879,37 @@
         <v>0</v>
       </c>
       <c r="C291" t="s">
+        <v>833</v>
+      </c>
+      <c r="D291" t="s">
+        <v>822</v>
+      </c>
+      <c r="E291" t="s">
         <v>834</v>
       </c>
-      <c r="D291" t="s">
-        <v>823</v>
-      </c>
-      <c r="E291" t="s">
+      <c r="F291" t="s">
         <v>835</v>
       </c>
-      <c r="F291" t="s">
-        <v>836</v>
-      </c>
       <c r="G291" t="s">
+        <v>887</v>
+      </c>
+      <c r="H291" t="s">
+        <v>837</v>
+      </c>
+      <c r="I291" t="s">
+        <v>873</v>
+      </c>
+      <c r="J291" t="s">
+        <v>882</v>
+      </c>
+      <c r="K291" t="s">
+        <v>883</v>
+      </c>
+      <c r="L291" t="s">
+        <v>878</v>
+      </c>
+      <c r="M291" t="s">
         <v>888</v>
-      </c>
-      <c r="H291" t="s">
-        <v>838</v>
-      </c>
-      <c r="I291" t="s">
-        <v>874</v>
-      </c>
-      <c r="J291" t="s">
-        <v>883</v>
-      </c>
-      <c r="K291" t="s">
-        <v>884</v>
-      </c>
-      <c r="L291" t="s">
-        <v>879</v>
-      </c>
-      <c r="M291" t="s">
-        <v>889</v>
       </c>
       <c r="N291">
         <v>0</v>
@@ -46927,40 +46936,40 @@
         <v>0</v>
       </c>
       <c r="C292" t="s">
+        <v>833</v>
+      </c>
+      <c r="D292" t="s">
+        <v>826</v>
+      </c>
+      <c r="E292" t="s">
         <v>834</v>
       </c>
-      <c r="D292" t="s">
-        <v>827</v>
-      </c>
-      <c r="E292" t="s">
+      <c r="F292" t="s">
         <v>835</v>
       </c>
-      <c r="F292" t="s">
-        <v>836</v>
-      </c>
       <c r="G292" t="s">
+        <v>889</v>
+      </c>
+      <c r="H292" t="s">
+        <v>837</v>
+      </c>
+      <c r="I292" t="s">
+        <v>873</v>
+      </c>
+      <c r="J292" t="s">
+        <v>882</v>
+      </c>
+      <c r="K292" t="s">
+        <v>883</v>
+      </c>
+      <c r="L292" t="s">
+        <v>878</v>
+      </c>
+      <c r="M292" t="s">
+        <v>888</v>
+      </c>
+      <c r="N292" t="s">
         <v>890</v>
-      </c>
-      <c r="H292" t="s">
-        <v>838</v>
-      </c>
-      <c r="I292" t="s">
-        <v>874</v>
-      </c>
-      <c r="J292" t="s">
-        <v>883</v>
-      </c>
-      <c r="K292" t="s">
-        <v>884</v>
-      </c>
-      <c r="L292" t="s">
-        <v>879</v>
-      </c>
-      <c r="M292" t="s">
-        <v>889</v>
-      </c>
-      <c r="N292" t="s">
-        <v>891</v>
       </c>
       <c r="O292">
         <v>0</v>
@@ -46984,43 +46993,43 @@
         <v>0</v>
       </c>
       <c r="C293" t="s">
+        <v>833</v>
+      </c>
+      <c r="D293" t="s">
+        <v>831</v>
+      </c>
+      <c r="E293" t="s">
         <v>834</v>
       </c>
-      <c r="D293" t="s">
-        <v>832</v>
-      </c>
-      <c r="E293" t="s">
+      <c r="F293" t="s">
         <v>835</v>
       </c>
-      <c r="F293" t="s">
-        <v>836</v>
-      </c>
       <c r="G293" t="s">
+        <v>891</v>
+      </c>
+      <c r="H293" t="s">
+        <v>837</v>
+      </c>
+      <c r="I293" t="s">
+        <v>873</v>
+      </c>
+      <c r="J293" t="s">
+        <v>882</v>
+      </c>
+      <c r="K293" t="s">
+        <v>883</v>
+      </c>
+      <c r="L293" t="s">
+        <v>878</v>
+      </c>
+      <c r="M293" t="s">
+        <v>888</v>
+      </c>
+      <c r="N293" t="s">
         <v>892</v>
       </c>
-      <c r="H293" t="s">
-        <v>838</v>
-      </c>
-      <c r="I293" t="s">
-        <v>874</v>
-      </c>
-      <c r="J293" t="s">
-        <v>883</v>
-      </c>
-      <c r="K293" t="s">
-        <v>884</v>
-      </c>
-      <c r="L293" t="s">
-        <v>879</v>
-      </c>
-      <c r="M293" t="s">
-        <v>889</v>
-      </c>
-      <c r="N293" t="s">
+      <c r="O293" t="s">
         <v>893</v>
-      </c>
-      <c r="O293" t="s">
-        <v>894</v>
       </c>
       <c r="P293">
         <v>0</v>
@@ -47041,46 +47050,46 @@
         <v>0</v>
       </c>
       <c r="C294" t="s">
+        <v>833</v>
+      </c>
+      <c r="D294" t="s">
+        <v>832</v>
+      </c>
+      <c r="E294" t="s">
         <v>834</v>
       </c>
-      <c r="D294" t="s">
-        <v>833</v>
-      </c>
-      <c r="E294" t="s">
+      <c r="F294" t="s">
         <v>835</v>
       </c>
-      <c r="F294" t="s">
-        <v>836</v>
-      </c>
       <c r="G294" t="s">
+        <v>894</v>
+      </c>
+      <c r="H294" t="s">
+        <v>837</v>
+      </c>
+      <c r="I294" t="s">
+        <v>873</v>
+      </c>
+      <c r="J294" t="s">
+        <v>882</v>
+      </c>
+      <c r="K294" t="s">
+        <v>883</v>
+      </c>
+      <c r="L294" t="s">
+        <v>878</v>
+      </c>
+      <c r="M294" t="s">
+        <v>888</v>
+      </c>
+      <c r="N294" t="s">
         <v>895</v>
       </c>
-      <c r="H294" t="s">
-        <v>838</v>
-      </c>
-      <c r="I294" t="s">
-        <v>874</v>
-      </c>
-      <c r="J294" t="s">
-        <v>883</v>
-      </c>
-      <c r="K294" t="s">
-        <v>884</v>
-      </c>
-      <c r="L294" t="s">
-        <v>879</v>
-      </c>
-      <c r="M294" t="s">
-        <v>889</v>
-      </c>
-      <c r="N294" t="s">
+      <c r="O294" t="s">
         <v>896</v>
       </c>
-      <c r="O294" t="s">
+      <c r="P294" t="s">
         <v>897</v>
-      </c>
-      <c r="P294" t="s">
-        <v>898</v>
       </c>
       <c r="Q294">
         <v>0</v>
@@ -47098,16 +47107,16 @@
         <v>0</v>
       </c>
       <c r="C295" t="s">
+        <v>898</v>
+      </c>
+      <c r="D295" t="s">
         <v>899</v>
       </c>
-      <c r="D295" t="s">
+      <c r="E295" t="s">
         <v>900</v>
       </c>
-      <c r="E295" t="s">
+      <c r="F295" t="s">
         <v>901</v>
-      </c>
-      <c r="F295" t="s">
-        <v>902</v>
       </c>
       <c r="G295">
         <v>0</v>
@@ -47155,16 +47164,16 @@
         <v>0</v>
       </c>
       <c r="C296" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D296" t="s">
+        <v>902</v>
+      </c>
+      <c r="E296" t="s">
         <v>903</v>
       </c>
-      <c r="E296" t="s">
+      <c r="F296" t="s">
         <v>904</v>
-      </c>
-      <c r="F296" t="s">
-        <v>905</v>
       </c>
       <c r="G296">
         <v>0.1</v>
@@ -47212,16 +47221,16 @@
         <v>0</v>
       </c>
       <c r="C297" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D297" t="s">
+        <v>905</v>
+      </c>
+      <c r="E297" t="s">
         <v>906</v>
       </c>
-      <c r="E297" t="s">
+      <c r="F297" t="s">
         <v>907</v>
-      </c>
-      <c r="F297" t="s">
-        <v>908</v>
       </c>
       <c r="G297">
         <v>0</v>
@@ -47269,16 +47278,16 @@
         <v>0</v>
       </c>
       <c r="C298" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D298" t="s">
+        <v>908</v>
+      </c>
+      <c r="E298" t="s">
         <v>909</v>
       </c>
-      <c r="E298" t="s">
+      <c r="F298" t="s">
         <v>910</v>
-      </c>
-      <c r="F298" t="s">
-        <v>911</v>
       </c>
       <c r="G298">
         <v>0</v>
@@ -47326,16 +47335,16 @@
         <v>0</v>
       </c>
       <c r="C299" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D299" t="s">
+        <v>911</v>
+      </c>
+      <c r="E299" t="s">
         <v>912</v>
       </c>
-      <c r="E299" t="s">
+      <c r="F299" t="s">
         <v>913</v>
-      </c>
-      <c r="F299" t="s">
-        <v>914</v>
       </c>
       <c r="G299">
         <v>0</v>
@@ -47383,16 +47392,16 @@
         <v>0</v>
       </c>
       <c r="C300" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D300" t="s">
+        <v>914</v>
+      </c>
+      <c r="E300" t="s">
         <v>915</v>
       </c>
-      <c r="E300" t="s">
+      <c r="F300" t="s">
         <v>916</v>
-      </c>
-      <c r="F300" t="s">
-        <v>917</v>
       </c>
       <c r="G300">
         <v>0.4</v>
@@ -47440,16 +47449,16 @@
         <v>0</v>
       </c>
       <c r="C301" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D301" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="F301" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G301">
         <v>1000</v>
@@ -47497,16 +47506,16 @@
         <v>0</v>
       </c>
       <c r="C302" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D302" t="s">
+        <v>918</v>
+      </c>
+      <c r="E302" t="s">
         <v>919</v>
       </c>
-      <c r="E302" t="s">
+      <c r="F302" t="s">
         <v>920</v>
-      </c>
-      <c r="F302" t="s">
-        <v>921</v>
       </c>
       <c r="G302">
         <v>0</v>
@@ -47554,16 +47563,16 @@
         <v>0</v>
       </c>
       <c r="C303" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D303" t="s">
+        <v>921</v>
+      </c>
+      <c r="E303" t="s">
         <v>922</v>
       </c>
-      <c r="E303" t="s">
+      <c r="F303" t="s">
         <v>923</v>
-      </c>
-      <c r="F303" t="s">
-        <v>924</v>
       </c>
       <c r="G303">
         <v>30</v>
@@ -47611,16 +47620,16 @@
         <v>0</v>
       </c>
       <c r="C304" t="s">
+        <v>924</v>
+      </c>
+      <c r="D304" t="s">
         <v>925</v>
       </c>
-      <c r="D304" t="s">
+      <c r="E304" t="s">
         <v>926</v>
       </c>
-      <c r="E304" t="s">
+      <c r="F304" t="s">
         <v>927</v>
-      </c>
-      <c r="F304" t="s">
-        <v>928</v>
       </c>
       <c r="G304">
         <v>0.75</v>
@@ -47668,13 +47677,13 @@
         <v>0</v>
       </c>
       <c r="C305" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D305" t="s">
+        <v>928</v>
+      </c>
+      <c r="E305" t="s">
         <v>929</v>
-      </c>
-      <c r="E305" t="s">
-        <v>930</v>
       </c>
       <c r="F305">
         <v>0</v>
@@ -47725,16 +47734,16 @@
         <v>0</v>
       </c>
       <c r="C306" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D306" t="s">
+        <v>930</v>
+      </c>
+      <c r="E306" t="s">
         <v>931</v>
       </c>
-      <c r="E306" t="s">
+      <c r="F306" t="s">
         <v>932</v>
-      </c>
-      <c r="F306" t="s">
-        <v>933</v>
       </c>
       <c r="G306">
         <v>45</v>
@@ -47782,16 +47791,16 @@
         <v>0</v>
       </c>
       <c r="C307" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D307" t="s">
+        <v>933</v>
+      </c>
+      <c r="E307" t="s">
         <v>934</v>
       </c>
-      <c r="E307" t="s">
+      <c r="F307" t="s">
         <v>935</v>
-      </c>
-      <c r="F307" t="s">
-        <v>936</v>
       </c>
       <c r="G307">
         <v>0</v>
@@ -47839,16 +47848,16 @@
         <v>0</v>
       </c>
       <c r="C308" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D308" t="s">
+        <v>936</v>
+      </c>
+      <c r="E308" t="s">
         <v>937</v>
       </c>
-      <c r="E308" t="s">
+      <c r="F308" t="s">
         <v>938</v>
-      </c>
-      <c r="F308" t="s">
-        <v>939</v>
       </c>
       <c r="G308">
         <v>0.1</v>
@@ -47896,16 +47905,16 @@
         <v>0</v>
       </c>
       <c r="C309" t="s">
+        <v>939</v>
+      </c>
+      <c r="D309" t="s">
         <v>940</v>
       </c>
-      <c r="D309" t="s">
+      <c r="E309" t="s">
         <v>941</v>
       </c>
-      <c r="E309" t="s">
+      <c r="F309" t="s">
         <v>942</v>
-      </c>
-      <c r="F309" t="s">
-        <v>943</v>
       </c>
       <c r="G309">
         <v>24</v>
@@ -47953,16 +47962,16 @@
         <v>0</v>
       </c>
       <c r="C310" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D310" t="s">
+        <v>943</v>
+      </c>
+      <c r="E310" t="s">
         <v>944</v>
       </c>
-      <c r="E310" t="s">
+      <c r="F310" t="s">
         <v>945</v>
-      </c>
-      <c r="F310" t="s">
-        <v>946</v>
       </c>
       <c r="G310">
         <v>10</v>
@@ -48010,16 +48019,16 @@
         <v>0</v>
       </c>
       <c r="C311" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D311" t="s">
+        <v>946</v>
+      </c>
+      <c r="E311" t="s">
         <v>947</v>
       </c>
-      <c r="E311" t="s">
+      <c r="F311" t="s">
         <v>948</v>
-      </c>
-      <c r="F311" t="s">
-        <v>949</v>
       </c>
       <c r="G311">
         <v>20</v>
@@ -48067,16 +48076,16 @@
         <v>0</v>
       </c>
       <c r="C312" t="s">
+        <v>949</v>
+      </c>
+      <c r="D312" t="s">
         <v>950</v>
-      </c>
-      <c r="D312" t="s">
-        <v>951</v>
       </c>
       <c r="E312" t="s">
         <v>39</v>
       </c>
       <c r="F312" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G312">
         <v>1</v>
@@ -48124,16 +48133,16 @@
         <v>0</v>
       </c>
       <c r="C313" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D313" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E313" t="s">
         <v>39</v>
       </c>
       <c r="F313" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G313">
         <v>1.35</v>
@@ -48181,16 +48190,16 @@
         <v>0</v>
       </c>
       <c r="C314" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D314" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E314" t="s">
         <v>39</v>
       </c>
       <c r="F314" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G314">
         <v>1.75</v>
@@ -48238,16 +48247,16 @@
         <v>0</v>
       </c>
       <c r="C315" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D315" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E315" t="s">
         <v>39</v>
       </c>
       <c r="F315" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G315">
         <v>2.2999999999999998</v>
@@ -48295,16 +48304,16 @@
         <v>0</v>
       </c>
       <c r="C316" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D316" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E316" t="s">
         <v>39</v>
       </c>
       <c r="F316" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G316">
         <v>3</v>
@@ -48352,16 +48361,16 @@
         <v>0</v>
       </c>
       <c r="C317" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D317" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E317" t="s">
         <v>39</v>
       </c>
       <c r="F317" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G317">
         <v>4</v>
@@ -48409,16 +48418,16 @@
         <v>0</v>
       </c>
       <c r="C318" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D318" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="E318" t="s">
         <v>39</v>
       </c>
       <c r="F318" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G318">
         <v>5.2</v>
@@ -48466,16 +48475,16 @@
         <v>0</v>
       </c>
       <c r="C319" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D319" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E319" t="s">
         <v>39</v>
       </c>
       <c r="F319" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G319">
         <v>6.8</v>
@@ -48523,16 +48532,16 @@
         <v>0</v>
       </c>
       <c r="C320" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D320" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E320" t="s">
         <v>39</v>
       </c>
       <c r="F320" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G320">
         <v>10.199999999999999</v>
@@ -48580,22 +48589,22 @@
         <v>0</v>
       </c>
       <c r="C321" t="s">
+        <v>960</v>
+      </c>
+      <c r="D321" t="s">
         <v>961</v>
       </c>
-      <c r="D321" t="s">
+      <c r="E321" t="s">
         <v>962</v>
       </c>
-      <c r="E321" t="s">
+      <c r="F321" t="s">
         <v>963</v>
-      </c>
-      <c r="F321" t="s">
-        <v>964</v>
       </c>
       <c r="G321">
         <v>25</v>
       </c>
       <c r="H321" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="I321">
         <v>0</v>
@@ -48637,22 +48646,22 @@
         <v>0</v>
       </c>
       <c r="C322" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D322" t="s">
+        <v>965</v>
+      </c>
+      <c r="E322" t="s">
+        <v>962</v>
+      </c>
+      <c r="F322" t="s">
         <v>966</v>
-      </c>
-      <c r="E322" t="s">
-        <v>963</v>
-      </c>
-      <c r="F322" t="s">
-        <v>967</v>
       </c>
       <c r="G322">
         <v>20</v>
       </c>
       <c r="H322" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="I322">
         <v>0</v>
@@ -48694,22 +48703,22 @@
         <v>0</v>
       </c>
       <c r="C323" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D323" t="s">
+        <v>967</v>
+      </c>
+      <c r="E323" t="s">
+        <v>962</v>
+      </c>
+      <c r="F323" t="s">
         <v>968</v>
-      </c>
-      <c r="E323" t="s">
-        <v>963</v>
-      </c>
-      <c r="F323" t="s">
-        <v>969</v>
       </c>
       <c r="G323">
         <v>25</v>
       </c>
       <c r="H323" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="I323">
         <v>0</v>
@@ -48751,22 +48760,22 @@
         <v>0</v>
       </c>
       <c r="C324" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D324" t="s">
+        <v>969</v>
+      </c>
+      <c r="E324" t="s">
+        <v>962</v>
+      </c>
+      <c r="F324" t="s">
         <v>970</v>
-      </c>
-      <c r="E324" t="s">
-        <v>963</v>
-      </c>
-      <c r="F324" t="s">
-        <v>971</v>
       </c>
       <c r="G324">
         <v>20</v>
       </c>
       <c r="H324" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="I324">
         <v>0</v>
@@ -48808,22 +48817,22 @@
         <v>0</v>
       </c>
       <c r="C325" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D325" t="s">
+        <v>971</v>
+      </c>
+      <c r="E325" t="s">
+        <v>962</v>
+      </c>
+      <c r="F325" t="s">
         <v>972</v>
-      </c>
-      <c r="E325" t="s">
-        <v>963</v>
-      </c>
-      <c r="F325" t="s">
-        <v>973</v>
       </c>
       <c r="G325">
         <v>0.4</v>
       </c>
       <c r="H325" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="I325">
         <v>0</v>
@@ -48865,22 +48874,22 @@
         <v>0</v>
       </c>
       <c r="C326" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D326" t="s">
+        <v>973</v>
+      </c>
+      <c r="E326" t="s">
+        <v>962</v>
+      </c>
+      <c r="F326" t="s">
         <v>974</v>
-      </c>
-      <c r="E326" t="s">
-        <v>963</v>
-      </c>
-      <c r="F326" t="s">
-        <v>975</v>
       </c>
       <c r="G326">
         <v>3</v>
       </c>
       <c r="H326" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="I326">
         <v>0</v>
@@ -48922,22 +48931,22 @@
         <v>0</v>
       </c>
       <c r="C327" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D327" t="s">
+        <v>975</v>
+      </c>
+      <c r="E327" t="s">
+        <v>962</v>
+      </c>
+      <c r="F327" t="s">
         <v>976</v>
-      </c>
-      <c r="E327" t="s">
-        <v>963</v>
-      </c>
-      <c r="F327" t="s">
-        <v>977</v>
       </c>
       <c r="G327">
         <v>1.5</v>
       </c>
       <c r="H327" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="I327">
         <v>0</v>
@@ -48979,22 +48988,22 @@
         <v>0</v>
       </c>
       <c r="C328" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D328" t="s">
+        <v>977</v>
+      </c>
+      <c r="E328" t="s">
+        <v>962</v>
+      </c>
+      <c r="F328" t="s">
         <v>978</v>
-      </c>
-      <c r="E328" t="s">
-        <v>963</v>
-      </c>
-      <c r="F328" t="s">
-        <v>979</v>
       </c>
       <c r="G328">
         <v>0.15</v>
       </c>
       <c r="H328" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="I328">
         <v>0</v>
@@ -49036,22 +49045,22 @@
         <v>0</v>
       </c>
       <c r="C329" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D329" t="s">
+        <v>979</v>
+      </c>
+      <c r="E329" t="s">
+        <v>962</v>
+      </c>
+      <c r="F329" t="s">
         <v>980</v>
-      </c>
-      <c r="E329" t="s">
-        <v>963</v>
-      </c>
-      <c r="F329" t="s">
-        <v>981</v>
       </c>
       <c r="G329">
         <v>0.5</v>
       </c>
       <c r="H329" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="I329">
         <v>0</v>
@@ -49093,22 +49102,22 @@
         <v>0</v>
       </c>
       <c r="C330" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D330" t="s">
+        <v>981</v>
+      </c>
+      <c r="E330" t="s">
+        <v>962</v>
+      </c>
+      <c r="F330" t="s">
         <v>982</v>
-      </c>
-      <c r="E330" t="s">
-        <v>963</v>
-      </c>
-      <c r="F330" t="s">
-        <v>983</v>
       </c>
       <c r="G330">
         <v>25</v>
       </c>
       <c r="H330" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="I330">
         <v>0</v>
@@ -49150,22 +49159,22 @@
         <v>0</v>
       </c>
       <c r="C331" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D331" t="s">
+        <v>983</v>
+      </c>
+      <c r="E331" t="s">
+        <v>962</v>
+      </c>
+      <c r="F331" t="s">
         <v>984</v>
-      </c>
-      <c r="E331" t="s">
-        <v>963</v>
-      </c>
-      <c r="F331" t="s">
-        <v>985</v>
       </c>
       <c r="G331">
         <v>8</v>
       </c>
       <c r="H331" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="I331">
         <v>0</v>
@@ -49207,22 +49216,22 @@
         <v>0</v>
       </c>
       <c r="C332" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D332" t="s">
+        <v>986</v>
+      </c>
+      <c r="E332" t="s">
+        <v>962</v>
+      </c>
+      <c r="F332" t="s">
         <v>987</v>
-      </c>
-      <c r="E332" t="s">
-        <v>963</v>
-      </c>
-      <c r="F332" t="s">
-        <v>988</v>
       </c>
       <c r="G332">
         <v>15</v>
       </c>
       <c r="H332" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="I332">
         <v>0</v>
@@ -49264,16 +49273,16 @@
         <v>0</v>
       </c>
       <c r="C333" t="s">
+        <v>988</v>
+      </c>
+      <c r="D333" t="s">
         <v>989</v>
       </c>
-      <c r="D333" t="s">
+      <c r="E333" t="s">
         <v>990</v>
       </c>
-      <c r="E333" t="s">
+      <c r="F333" t="s">
         <v>991</v>
-      </c>
-      <c r="F333" t="s">
-        <v>992</v>
       </c>
       <c r="G333">
         <v>0.8</v>
@@ -49321,16 +49330,16 @@
         <v>0</v>
       </c>
       <c r="C334" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D334" t="s">
+        <v>992</v>
+      </c>
+      <c r="E334" t="s">
         <v>993</v>
       </c>
-      <c r="E334" t="s">
+      <c r="F334" t="s">
         <v>994</v>
-      </c>
-      <c r="F334" t="s">
-        <v>995</v>
       </c>
       <c r="G334">
         <v>3</v>
@@ -49378,16 +49387,16 @@
         <v>0</v>
       </c>
       <c r="C335" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D335" t="s">
+        <v>995</v>
+      </c>
+      <c r="E335" t="s">
         <v>996</v>
       </c>
-      <c r="E335" t="s">
+      <c r="F335" t="s">
         <v>997</v>
-      </c>
-      <c r="F335" t="s">
-        <v>998</v>
       </c>
       <c r="G335">
         <v>7</v>
@@ -49435,16 +49444,16 @@
         <v>0</v>
       </c>
       <c r="C336" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D336" t="s">
+        <v>998</v>
+      </c>
+      <c r="E336" t="s">
         <v>999</v>
       </c>
-      <c r="E336" t="s">
+      <c r="F336" t="s">
         <v>1000</v>
-      </c>
-      <c r="F336" t="s">
-        <v>1001</v>
       </c>
       <c r="G336">
         <v>10</v>
@@ -49492,16 +49501,16 @@
         <v>0</v>
       </c>
       <c r="C337" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D337" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E337" t="s">
         <v>1002</v>
       </c>
-      <c r="E337" t="s">
+      <c r="F337" t="s">
         <v>1003</v>
-      </c>
-      <c r="F337" t="s">
-        <v>1004</v>
       </c>
       <c r="G337">
         <v>2</v>
@@ -49549,16 +49558,16 @@
         <v>0</v>
       </c>
       <c r="C338" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D338" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E338" t="s">
         <v>1005</v>
       </c>
-      <c r="E338" t="s">
+      <c r="F338" t="s">
         <v>1006</v>
-      </c>
-      <c r="F338" t="s">
-        <v>1007</v>
       </c>
       <c r="G338">
         <v>5</v>
@@ -49606,16 +49615,16 @@
         <v>0</v>
       </c>
       <c r="C339" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D339" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E339" t="s">
         <v>1008</v>
       </c>
-      <c r="E339" t="s">
+      <c r="F339" t="s">
         <v>1009</v>
-      </c>
-      <c r="F339" t="s">
-        <v>1010</v>
       </c>
       <c r="G339">
         <v>10</v>
@@ -49663,16 +49672,16 @@
         <v>0</v>
       </c>
       <c r="C340" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D340" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E340" t="s">
         <v>39</v>
       </c>
       <c r="F340" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="G340">
         <v>15.3</v>
@@ -49720,16 +49729,16 @@
         <v>0</v>
       </c>
       <c r="C341" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D341" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="E341" t="s">
         <v>39</v>
       </c>
       <c r="F341" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="G341">
         <v>22.95</v>
@@ -49777,16 +49786,16 @@
         <v>0</v>
       </c>
       <c r="C342" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D342" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E342" t="s">
         <v>1014</v>
       </c>
-      <c r="E342" t="s">
+      <c r="F342" t="s">
         <v>1015</v>
-      </c>
-      <c r="F342" t="s">
-        <v>1016</v>
       </c>
       <c r="G342">
         <v>20</v>
@@ -49834,16 +49843,16 @@
         <v>0</v>
       </c>
       <c r="C343" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D343" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E343" t="s">
         <v>1017</v>
       </c>
-      <c r="E343" t="s">
+      <c r="F343" t="s">
         <v>1018</v>
-      </c>
-      <c r="F343" t="s">
-        <v>1019</v>
       </c>
       <c r="G343">
         <v>500000000</v>
@@ -49891,16 +49900,16 @@
         <v>0</v>
       </c>
       <c r="C344" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D344" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E344" t="s">
         <v>1020</v>
       </c>
-      <c r="E344" t="s">
+      <c r="F344" t="s">
         <v>1021</v>
-      </c>
-      <c r="F344" t="s">
-        <v>1022</v>
       </c>
       <c r="G344">
         <v>13</v>
@@ -49951,13 +49960,13 @@
         <v>18</v>
       </c>
       <c r="D345" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E345" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F345" t="s">
         <v>1023</v>
-      </c>
-      <c r="E345" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="F345" t="s">
-        <v>1024</v>
       </c>
       <c r="G345">
         <v>30</v>
@@ -50008,13 +50017,13 @@
         <v>18</v>
       </c>
       <c r="D346" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E346" t="s">
         <v>1025</v>
       </c>
-      <c r="E346" t="s">
+      <c r="F346" t="s">
         <v>1026</v>
-      </c>
-      <c r="F346" t="s">
-        <v>1027</v>
       </c>
       <c r="G346">
         <v>1000</v>
@@ -50062,16 +50071,16 @@
         <v>0</v>
       </c>
       <c r="C347" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D347" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E347" t="s">
         <v>1028</v>
       </c>
-      <c r="E347" t="s">
+      <c r="F347" t="s">
         <v>1029</v>
-      </c>
-      <c r="F347" t="s">
-        <v>1030</v>
       </c>
       <c r="G347">
         <v>50000</v>
@@ -50119,16 +50128,16 @@
         <v>0</v>
       </c>
       <c r="C348" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D348" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E348" t="s">
         <v>1031</v>
       </c>
-      <c r="E348" t="s">
+      <c r="F348" t="s">
         <v>1032</v>
-      </c>
-      <c r="F348" t="s">
-        <v>1033</v>
       </c>
       <c r="G348">
         <v>10</v>
@@ -50176,16 +50185,16 @@
         <v>0</v>
       </c>
       <c r="C349" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D349" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E349" t="s">
         <v>1034</v>
       </c>
-      <c r="E349" t="s">
+      <c r="F349" t="s">
         <v>1035</v>
-      </c>
-      <c r="F349" t="s">
-        <v>1036</v>
       </c>
       <c r="G349">
         <v>75</v>
@@ -50233,16 +50242,16 @@
         <v>0</v>
       </c>
       <c r="C350" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D350" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E350" t="s">
         <v>1037</v>
       </c>
-      <c r="E350" t="s">
+      <c r="F350" t="s">
         <v>1038</v>
-      </c>
-      <c r="F350" t="s">
-        <v>1039</v>
       </c>
       <c r="G350">
         <v>25</v>
@@ -50290,16 +50299,16 @@
         <v>0</v>
       </c>
       <c r="C351" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D351" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E351" t="s">
+        <v>931</v>
+      </c>
+      <c r="F351" t="s">
         <v>1040</v>
-      </c>
-      <c r="E351" t="s">
-        <v>932</v>
-      </c>
-      <c r="F351" t="s">
-        <v>1041</v>
       </c>
       <c r="G351">
         <v>5</v>
@@ -50347,16 +50356,16 @@
         <v>0</v>
       </c>
       <c r="C352" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D352" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E352" t="s">
         <v>1042</v>
       </c>
-      <c r="E352" t="s">
+      <c r="F352" t="s">
         <v>1043</v>
-      </c>
-      <c r="F352" t="s">
-        <v>1044</v>
       </c>
       <c r="G352">
         <v>0.6</v>
@@ -50404,16 +50413,16 @@
         <v>0</v>
       </c>
       <c r="C353" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D353" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E353" t="s">
         <v>1045</v>
       </c>
-      <c r="E353" t="s">
+      <c r="F353" t="s">
         <v>1046</v>
-      </c>
-      <c r="F353" t="s">
-        <v>1047</v>
       </c>
       <c r="G353">
         <v>0.1</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0926D46B-B453-4CCE-AB9C-F0350BF68FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16826240-ACE5-4961-AB3E-0D8172F60361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10963,11 +10963,11 @@
       </c>
       <c r="G92">
         <f>計算表!G92</f>
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H92">
         <f>計算表!H92</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I92">
         <f>計算表!I92</f>
@@ -35548,10 +35548,10 @@
         <v>255</v>
       </c>
       <c r="G92">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I92">
         <v>1.06</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16826240-ACE5-4961-AB3E-0D8172F60361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D113D3EE-47BF-403C-8933-2145359BE75B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -622,9 +622,6 @@
   </si>
   <si>
     <t>敵種傷害抗性</t>
-  </si>
-  <si>
-    <t>抗性值總合/(抗性值總合+a+b×攻擊者等級)</t>
   </si>
   <si>
     <t>a=常數 b=每級係數。普通敵人/菁英/BOSS傷害抗性三屬性共用曲線；依攻擊者敵種選用對應抗性總合，於全局減傷之後、最低傷害之前的最末端套用；抗性值≤0 時不減傷。詞條放出量見「表-詞條池」。</t>
@@ -3789,6 +3786,60 @@
   </si>
   <si>
     <t>{50~99=1}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>抗性值總合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>/(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>抗性值總合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>+a+b×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>攻擊者等級</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -9039,11 +9090,11 @@
       </c>
       <c r="G66">
         <f>計算表!G66</f>
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="H66">
         <f>計算表!H66</f>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I66">
         <f>計算表!I66</f>
@@ -10745,11 +10796,11 @@
       </c>
       <c r="H89">
         <f>計算表!H89</f>
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="I89">
         <f>計算表!I89</f>
-        <v>1.0549999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="J89">
         <f>計算表!J89</f>
@@ -32749,10 +32800,10 @@
         <v>145</v>
       </c>
       <c r="E43" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>1054</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>1055</v>
       </c>
       <c r="G43">
         <v>2</v>
@@ -34059,17 +34110,17 @@
       <c r="D66" t="s">
         <v>195</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F66" t="s">
         <v>196</v>
       </c>
-      <c r="F66" t="s">
-        <v>197</v>
-      </c>
       <c r="G66">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="H66">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -34114,13 +34165,13 @@
         <v>191</v>
       </c>
       <c r="D67" t="s">
+        <v>197</v>
+      </c>
+      <c r="E67" t="s">
         <v>198</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>199</v>
-      </c>
-      <c r="F67" t="s">
-        <v>200</v>
       </c>
       <c r="G67">
         <v>1.8</v>
@@ -34171,13 +34222,13 @@
         <v>191</v>
       </c>
       <c r="D68" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E68" t="s">
+        <v>198</v>
+      </c>
+      <c r="F68" t="s">
         <v>199</v>
-      </c>
-      <c r="F68" t="s">
-        <v>200</v>
       </c>
       <c r="G68">
         <v>1.8</v>
@@ -34228,13 +34279,13 @@
         <v>191</v>
       </c>
       <c r="D69" t="s">
+        <v>201</v>
+      </c>
+      <c r="E69" t="s">
+        <v>198</v>
+      </c>
+      <c r="F69" t="s">
         <v>202</v>
-      </c>
-      <c r="E69" t="s">
-        <v>199</v>
-      </c>
-      <c r="F69" t="s">
-        <v>203</v>
       </c>
       <c r="G69">
         <v>1.8</v>
@@ -34285,13 +34336,13 @@
         <v>191</v>
       </c>
       <c r="D70" t="s">
+        <v>203</v>
+      </c>
+      <c r="E70" t="s">
         <v>204</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>205</v>
-      </c>
-      <c r="F70" t="s">
-        <v>206</v>
       </c>
       <c r="G70">
         <v>0.9</v>
@@ -34342,13 +34393,13 @@
         <v>191</v>
       </c>
       <c r="D71" t="s">
+        <v>206</v>
+      </c>
+      <c r="E71" t="s">
         <v>207</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>208</v>
-      </c>
-      <c r="F71" t="s">
-        <v>209</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -34399,13 +34450,13 @@
         <v>191</v>
       </c>
       <c r="D72" t="s">
+        <v>209</v>
+      </c>
+      <c r="E72" t="s">
         <v>210</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>211</v>
-      </c>
-      <c r="F72" t="s">
-        <v>212</v>
       </c>
       <c r="G72">
         <v>0.7</v>
@@ -34456,13 +34507,13 @@
         <v>191</v>
       </c>
       <c r="D73" t="s">
+        <v>212</v>
+      </c>
+      <c r="E73" t="s">
         <v>213</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>214</v>
-      </c>
-      <c r="F73" t="s">
-        <v>215</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -34513,13 +34564,13 @@
         <v>191</v>
       </c>
       <c r="D74" s="4" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E74" t="s">
+        <v>215</v>
+      </c>
+      <c r="F74" s="4" t="s">
         <v>1079</v>
-      </c>
-      <c r="E74" t="s">
-        <v>216</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>1080</v>
       </c>
       <c r="G74">
         <v>12</v>
@@ -34570,13 +34621,13 @@
         <v>191</v>
       </c>
       <c r="D75" t="s">
+        <v>216</v>
+      </c>
+      <c r="E75" t="s">
         <v>217</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>218</v>
-      </c>
-      <c r="F75" t="s">
-        <v>219</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -34627,13 +34678,13 @@
         <v>191</v>
       </c>
       <c r="D76" t="s">
+        <v>219</v>
+      </c>
+      <c r="E76" t="s">
         <v>220</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>221</v>
-      </c>
-      <c r="F76" t="s">
-        <v>222</v>
       </c>
       <c r="G76">
         <v>10</v>
@@ -34684,13 +34735,13 @@
         <v>191</v>
       </c>
       <c r="D77" t="s">
+        <v>222</v>
+      </c>
+      <c r="E77" t="s">
+        <v>215</v>
+      </c>
+      <c r="F77" t="s">
         <v>223</v>
-      </c>
-      <c r="E77" t="s">
-        <v>216</v>
-      </c>
-      <c r="F77" t="s">
-        <v>224</v>
       </c>
       <c r="G77">
         <v>10000</v>
@@ -34741,13 +34792,13 @@
         <v>191</v>
       </c>
       <c r="D78" t="s">
+        <v>224</v>
+      </c>
+      <c r="E78" t="s">
         <v>225</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>226</v>
-      </c>
-      <c r="F78" t="s">
-        <v>227</v>
       </c>
       <c r="G78">
         <v>50</v>
@@ -34798,13 +34849,13 @@
         <v>191</v>
       </c>
       <c r="D79" t="s">
+        <v>227</v>
+      </c>
+      <c r="E79" t="s">
         <v>228</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>229</v>
-      </c>
-      <c r="F79" t="s">
-        <v>230</v>
       </c>
       <c r="G79">
         <v>30</v>
@@ -34855,13 +34906,13 @@
         <v>191</v>
       </c>
       <c r="D80" t="s">
+        <v>230</v>
+      </c>
+      <c r="E80" t="s">
         <v>231</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>232</v>
-      </c>
-      <c r="F80" t="s">
-        <v>233</v>
       </c>
       <c r="G80">
         <v>100</v>
@@ -34912,13 +34963,13 @@
         <v>191</v>
       </c>
       <c r="D81" t="s">
+        <v>233</v>
+      </c>
+      <c r="E81" t="s">
         <v>234</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>235</v>
-      </c>
-      <c r="F81" t="s">
-        <v>236</v>
       </c>
       <c r="G81">
         <v>5</v>
@@ -34969,13 +35020,13 @@
         <v>191</v>
       </c>
       <c r="D82" t="s">
+        <v>236</v>
+      </c>
+      <c r="E82" t="s">
         <v>237</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>238</v>
-      </c>
-      <c r="F82" t="s">
-        <v>239</v>
       </c>
       <c r="G82">
         <v>0.01</v>
@@ -35023,16 +35074,16 @@
         <v>0</v>
       </c>
       <c r="C83" t="s">
+        <v>239</v>
+      </c>
+      <c r="D83" t="s">
         <v>240</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
         <v>241</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>242</v>
-      </c>
-      <c r="F83" t="s">
-        <v>243</v>
       </c>
       <c r="G83">
         <v>15</v>
@@ -35080,16 +35131,16 @@
         <v>0</v>
       </c>
       <c r="C84" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D84" t="s">
+        <v>243</v>
+      </c>
+      <c r="E84" t="s">
+        <v>241</v>
+      </c>
+      <c r="F84" t="s">
         <v>244</v>
-      </c>
-      <c r="E84" t="s">
-        <v>242</v>
-      </c>
-      <c r="F84" t="s">
-        <v>245</v>
       </c>
       <c r="G84">
         <v>10</v>
@@ -35137,16 +35188,16 @@
         <v>0</v>
       </c>
       <c r="C85" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D85" t="s">
+        <v>245</v>
+      </c>
+      <c r="E85" t="s">
+        <v>241</v>
+      </c>
+      <c r="F85" t="s">
         <v>246</v>
-      </c>
-      <c r="E85" t="s">
-        <v>242</v>
-      </c>
-      <c r="F85" t="s">
-        <v>247</v>
       </c>
       <c r="G85">
         <v>25</v>
@@ -35194,16 +35245,16 @@
         <v>0</v>
       </c>
       <c r="C86" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D86" t="s">
+        <v>247</v>
+      </c>
+      <c r="E86" t="s">
+        <v>241</v>
+      </c>
+      <c r="F86" t="s">
         <v>248</v>
-      </c>
-      <c r="E86" t="s">
-        <v>242</v>
-      </c>
-      <c r="F86" t="s">
-        <v>249</v>
       </c>
       <c r="G86">
         <v>20</v>
@@ -35251,16 +35302,16 @@
         <v>0</v>
       </c>
       <c r="C87" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D87" t="s">
+        <v>249</v>
+      </c>
+      <c r="E87" t="s">
+        <v>241</v>
+      </c>
+      <c r="F87" t="s">
         <v>250</v>
-      </c>
-      <c r="E87" t="s">
-        <v>242</v>
-      </c>
-      <c r="F87" t="s">
-        <v>251</v>
       </c>
       <c r="G87">
         <v>100</v>
@@ -35308,16 +35359,16 @@
         <v>0</v>
       </c>
       <c r="C88" t="s">
+        <v>251</v>
+      </c>
+      <c r="D88" t="s">
         <v>252</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E88" t="s">
         <v>253</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>254</v>
-      </c>
-      <c r="F88" t="s">
-        <v>255</v>
       </c>
       <c r="G88">
         <v>20</v>
@@ -35365,25 +35416,25 @@
         <v>0</v>
       </c>
       <c r="C89" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D89" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E89" t="s">
+        <v>253</v>
+      </c>
+      <c r="F89" t="s">
         <v>254</v>
-      </c>
-      <c r="F89" t="s">
-        <v>255</v>
       </c>
       <c r="G89">
         <v>2</v>
       </c>
       <c r="H89">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="I89">
-        <v>1.0549999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -35422,16 +35473,16 @@
         <v>0</v>
       </c>
       <c r="C90" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D90" t="s">
         <v>119</v>
       </c>
       <c r="E90" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F90" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G90">
         <v>2</v>
@@ -35479,16 +35530,16 @@
         <v>0</v>
       </c>
       <c r="C91" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D91" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E91" t="s">
+        <v>253</v>
+      </c>
+      <c r="F91" t="s">
         <v>254</v>
-      </c>
-      <c r="F91" t="s">
-        <v>255</v>
       </c>
       <c r="G91">
         <v>250</v>
@@ -35536,16 +35587,16 @@
         <v>0</v>
       </c>
       <c r="C92" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D92" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E92" t="s">
+        <v>253</v>
+      </c>
+      <c r="F92" t="s">
         <v>254</v>
-      </c>
-      <c r="F92" t="s">
-        <v>255</v>
       </c>
       <c r="G92">
         <v>120</v>
@@ -35593,16 +35644,16 @@
         <v>0</v>
       </c>
       <c r="C93" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D93" t="s">
         <v>134</v>
       </c>
       <c r="E93" t="s">
+        <v>259</v>
+      </c>
+      <c r="F93" t="s">
         <v>260</v>
-      </c>
-      <c r="F93" t="s">
-        <v>261</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -35650,37 +35701,37 @@
         <v>0</v>
       </c>
       <c r="C94" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D94" t="s">
         <v>137</v>
       </c>
       <c r="E94" t="s">
+        <v>261</v>
+      </c>
+      <c r="F94" t="s">
         <v>262</v>
-      </c>
-      <c r="F94" t="s">
-        <v>263</v>
       </c>
       <c r="G94">
         <v>100</v>
       </c>
       <c r="H94" t="s">
+        <v>263</v>
+      </c>
+      <c r="I94" t="s">
         <v>264</v>
       </c>
-      <c r="I94" t="s">
+      <c r="J94" t="s">
         <v>265</v>
       </c>
-      <c r="J94" t="s">
+      <c r="K94" t="s">
         <v>266</v>
       </c>
-      <c r="K94" t="s">
+      <c r="L94" t="s">
         <v>267</v>
       </c>
-      <c r="L94" t="s">
+      <c r="M94" t="s">
         <v>268</v>
-      </c>
-      <c r="M94" t="s">
-        <v>269</v>
       </c>
       <c r="N94">
         <v>0</v>
@@ -35707,37 +35758,37 @@
         <v>0</v>
       </c>
       <c r="C95" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D95" t="s">
         <v>140</v>
       </c>
       <c r="E95" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F95" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G95">
         <v>5</v>
       </c>
       <c r="H95" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I95" t="s">
+        <v>270</v>
+      </c>
+      <c r="J95" t="s">
         <v>271</v>
       </c>
-      <c r="J95" t="s">
+      <c r="K95" t="s">
         <v>272</v>
       </c>
-      <c r="K95" t="s">
+      <c r="L95" t="s">
         <v>273</v>
       </c>
-      <c r="L95" t="s">
+      <c r="M95" t="s">
         <v>274</v>
-      </c>
-      <c r="M95" t="s">
-        <v>275</v>
       </c>
       <c r="N95">
         <v>0</v>
@@ -35764,16 +35815,16 @@
         <v>0</v>
       </c>
       <c r="C96" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D96" t="s">
+        <v>275</v>
+      </c>
+      <c r="E96" t="s">
         <v>276</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
         <v>277</v>
-      </c>
-      <c r="F96" t="s">
-        <v>278</v>
       </c>
       <c r="G96">
         <v>4</v>
@@ -35821,16 +35872,16 @@
         <v>0</v>
       </c>
       <c r="C97" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D97" t="s">
+        <v>278</v>
+      </c>
+      <c r="E97" t="s">
         <v>279</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>280</v>
-      </c>
-      <c r="F97" t="s">
-        <v>281</v>
       </c>
       <c r="G97">
         <v>1.3</v>
@@ -35878,16 +35929,16 @@
         <v>0</v>
       </c>
       <c r="C98" t="s">
+        <v>281</v>
+      </c>
+      <c r="D98" t="s">
         <v>282</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
         <v>283</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>284</v>
-      </c>
-      <c r="F98" t="s">
-        <v>285</v>
       </c>
       <c r="G98">
         <v>0.75</v>
@@ -35935,16 +35986,16 @@
         <v>0</v>
       </c>
       <c r="C99" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D99" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E99" t="s">
+        <v>283</v>
+      </c>
+      <c r="F99" t="s">
         <v>284</v>
-      </c>
-      <c r="F99" t="s">
-        <v>285</v>
       </c>
       <c r="G99">
         <v>2</v>
@@ -35992,16 +36043,16 @@
         <v>0</v>
       </c>
       <c r="C100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D100" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E100" t="s">
+        <v>283</v>
+      </c>
+      <c r="F100" t="s">
         <v>284</v>
-      </c>
-      <c r="F100" t="s">
-        <v>285</v>
       </c>
       <c r="G100">
         <v>4.5</v>
@@ -36049,16 +36100,16 @@
         <v>0</v>
       </c>
       <c r="C101" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D101" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E101" t="s">
+        <v>283</v>
+      </c>
+      <c r="F101" t="s">
         <v>284</v>
-      </c>
-      <c r="F101" t="s">
-        <v>285</v>
       </c>
       <c r="G101">
         <v>10</v>
@@ -36106,16 +36157,16 @@
         <v>0</v>
       </c>
       <c r="C102" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D102" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E102" t="s">
+        <v>283</v>
+      </c>
+      <c r="F102" t="s">
         <v>284</v>
-      </c>
-      <c r="F102" t="s">
-        <v>285</v>
       </c>
       <c r="G102">
         <v>25</v>
@@ -36163,16 +36214,16 @@
         <v>0</v>
       </c>
       <c r="C103" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D103" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E103" t="s">
+        <v>283</v>
+      </c>
+      <c r="F103" t="s">
         <v>284</v>
-      </c>
-      <c r="F103" t="s">
-        <v>285</v>
       </c>
       <c r="G103">
         <v>60</v>
@@ -36217,25 +36268,25 @@
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C104" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="E104" t="s">
+        <v>292</v>
+      </c>
+      <c r="F104" t="s">
         <v>293</v>
       </c>
-      <c r="F104" t="s">
-        <v>294</v>
-      </c>
       <c r="G104" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H104" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I104">
         <v>0</v>
@@ -36274,28 +36325,28 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C105" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="E105" t="s">
+        <v>292</v>
+      </c>
+      <c r="F105" t="s">
         <v>293</v>
       </c>
-      <c r="F105" t="s">
-        <v>294</v>
-      </c>
       <c r="G105" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="I105" t="s">
         <v>1065</v>
-      </c>
-      <c r="H105" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="I105" t="s">
-        <v>1066</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -36331,31 +36382,31 @@
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C106" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E106" t="s">
+        <v>292</v>
+      </c>
+      <c r="F106" t="s">
         <v>293</v>
       </c>
-      <c r="F106" t="s">
-        <v>294</v>
-      </c>
       <c r="G106" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H106" s="2" t="s">
         <v>1067</v>
       </c>
-      <c r="H106" s="2" t="s">
+      <c r="I106" s="2" t="s">
         <v>1068</v>
       </c>
-      <c r="I106" s="2" t="s">
+      <c r="J106" t="s">
         <v>1069</v>
-      </c>
-      <c r="J106" t="s">
-        <v>1070</v>
       </c>
       <c r="K106">
         <v>0</v>
@@ -36388,31 +36439,31 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C107" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E107" t="s">
+        <v>292</v>
+      </c>
+      <c r="F107" t="s">
         <v>293</v>
       </c>
-      <c r="F107" t="s">
-        <v>294</v>
-      </c>
       <c r="G107" s="2" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H107" s="2" t="s">
         <v>1071</v>
       </c>
-      <c r="H107" s="2" t="s">
+      <c r="I107" s="2" t="s">
         <v>1072</v>
       </c>
-      <c r="I107" s="2" t="s">
+      <c r="J107" s="2" t="s">
         <v>1073</v>
-      </c>
-      <c r="J107" s="2" t="s">
-        <v>1074</v>
       </c>
       <c r="K107">
         <v>0</v>
@@ -36445,34 +36496,34 @@
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C108" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="E108" t="s">
+        <v>292</v>
+      </c>
+      <c r="F108" t="s">
         <v>293</v>
       </c>
-      <c r="F108" t="s">
-        <v>294</v>
-      </c>
       <c r="G108" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H108" s="2" t="s">
         <v>1075</v>
       </c>
-      <c r="H108" s="2" t="s">
+      <c r="I108" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="J108" s="2" t="s">
         <v>1076</v>
       </c>
-      <c r="I108" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="J108" s="2" t="s">
+      <c r="K108" s="2" t="s">
         <v>1077</v>
-      </c>
-      <c r="K108" s="2" t="s">
-        <v>1078</v>
       </c>
       <c r="L108">
         <v>0</v>
@@ -36505,49 +36556,49 @@
         <v>0</v>
       </c>
       <c r="C109" t="s">
+        <v>290</v>
+      </c>
+      <c r="D109" t="s">
         <v>291</v>
       </c>
-      <c r="D109" t="s">
+      <c r="E109" t="s">
         <v>292</v>
       </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>293</v>
       </c>
-      <c r="F109" t="s">
+      <c r="G109" t="s">
         <v>294</v>
       </c>
-      <c r="G109" t="s">
+      <c r="H109" t="s">
         <v>295</v>
       </c>
-      <c r="H109" t="s">
+      <c r="I109" t="s">
         <v>296</v>
       </c>
-      <c r="I109" t="s">
+      <c r="J109" t="s">
         <v>297</v>
       </c>
-      <c r="J109" t="s">
+      <c r="K109" t="s">
         <v>298</v>
       </c>
-      <c r="K109" t="s">
+      <c r="L109" t="s">
         <v>299</v>
       </c>
-      <c r="L109" t="s">
+      <c r="M109" t="s">
         <v>300</v>
       </c>
-      <c r="M109" t="s">
+      <c r="N109" t="s">
         <v>301</v>
       </c>
-      <c r="N109" t="s">
+      <c r="O109" t="s">
         <v>302</v>
       </c>
-      <c r="O109" t="s">
+      <c r="P109" t="s">
         <v>303</v>
       </c>
-      <c r="P109" t="s">
+      <c r="Q109" t="s">
         <v>304</v>
-      </c>
-      <c r="Q109" t="s">
-        <v>305</v>
       </c>
       <c r="R109">
         <v>0</v>
@@ -36562,25 +36613,25 @@
         <v>0</v>
       </c>
       <c r="C110" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D110" t="s">
+        <v>305</v>
+      </c>
+      <c r="E110" t="s">
+        <v>292</v>
+      </c>
+      <c r="F110" t="s">
         <v>306</v>
       </c>
-      <c r="E110" t="s">
-        <v>293</v>
-      </c>
-      <c r="F110" t="s">
+      <c r="G110" t="s">
         <v>307</v>
       </c>
-      <c r="G110" t="s">
+      <c r="H110" t="s">
         <v>308</v>
       </c>
-      <c r="H110" t="s">
+      <c r="I110" t="s">
         <v>309</v>
-      </c>
-      <c r="I110" t="s">
-        <v>310</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -36619,19 +36670,19 @@
         <v>0</v>
       </c>
       <c r="C111" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D111" t="s">
+        <v>310</v>
+      </c>
+      <c r="E111" t="s">
+        <v>292</v>
+      </c>
+      <c r="F111" t="s">
         <v>311</v>
       </c>
-      <c r="E111" t="s">
-        <v>293</v>
-      </c>
-      <c r="F111" t="s">
+      <c r="G111" t="s">
         <v>312</v>
-      </c>
-      <c r="G111" t="s">
-        <v>313</v>
       </c>
       <c r="H111">
         <v>0</v>
@@ -36676,16 +36727,16 @@
         <v>0</v>
       </c>
       <c r="C112" t="s">
+        <v>313</v>
+      </c>
+      <c r="D112" t="s">
         <v>314</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112" t="s">
         <v>315</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
         <v>316</v>
-      </c>
-      <c r="F112" t="s">
-        <v>317</v>
       </c>
       <c r="G112">
         <v>4</v>
@@ -36733,16 +36784,16 @@
         <v>0</v>
       </c>
       <c r="C113" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D113" t="s">
+        <v>317</v>
+      </c>
+      <c r="E113" t="s">
         <v>318</v>
       </c>
-      <c r="E113" t="s">
+      <c r="F113" t="s">
         <v>319</v>
-      </c>
-      <c r="F113" t="s">
-        <v>320</v>
       </c>
       <c r="G113">
         <v>2</v>
@@ -36790,16 +36841,16 @@
         <v>0</v>
       </c>
       <c r="C114" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D114" t="s">
+        <v>320</v>
+      </c>
+      <c r="E114" t="s">
         <v>321</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
         <v>322</v>
-      </c>
-      <c r="F114" t="s">
-        <v>323</v>
       </c>
       <c r="G114">
         <v>2</v>
@@ -36847,16 +36898,16 @@
         <v>0</v>
       </c>
       <c r="C115" t="s">
+        <v>323</v>
+      </c>
+      <c r="D115" t="s">
         <v>324</v>
       </c>
-      <c r="D115" t="s">
+      <c r="E115" t="s">
         <v>325</v>
       </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
         <v>326</v>
-      </c>
-      <c r="F115" t="s">
-        <v>327</v>
       </c>
       <c r="G115">
         <v>50</v>
@@ -36904,16 +36955,16 @@
         <v>0</v>
       </c>
       <c r="C116" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D116" t="s">
+        <v>327</v>
+      </c>
+      <c r="E116" t="s">
         <v>328</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
         <v>329</v>
-      </c>
-      <c r="F116" t="s">
-        <v>330</v>
       </c>
       <c r="G116">
         <v>20</v>
@@ -36961,16 +37012,16 @@
         <v>0</v>
       </c>
       <c r="C117" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D117" t="s">
+        <v>330</v>
+      </c>
+      <c r="E117" t="s">
+        <v>279</v>
+      </c>
+      <c r="F117" t="s">
         <v>331</v>
-      </c>
-      <c r="E117" t="s">
-        <v>280</v>
-      </c>
-      <c r="F117" t="s">
-        <v>332</v>
       </c>
       <c r="G117">
         <v>3</v>
@@ -37018,16 +37069,16 @@
         <v>0</v>
       </c>
       <c r="C118" t="s">
+        <v>281</v>
+      </c>
+      <c r="D118" t="s">
         <v>282</v>
-      </c>
-      <c r="D118" t="s">
-        <v>283</v>
       </c>
       <c r="E118" t="s">
         <v>39</v>
       </c>
       <c r="F118" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G118">
         <v>1</v>
@@ -37045,7 +37096,7 @@
         <v>1</v>
       </c>
       <c r="L118" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M118">
         <v>0</v>
@@ -37075,16 +37126,16 @@
         <v>0</v>
       </c>
       <c r="C119" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D119" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E119" t="s">
         <v>39</v>
       </c>
       <c r="F119" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G119">
         <v>2.2000000000000002</v>
@@ -37102,7 +37153,7 @@
         <v>1.25</v>
       </c>
       <c r="L119" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="M119">
         <v>0</v>
@@ -37132,16 +37183,16 @@
         <v>0</v>
       </c>
       <c r="C120" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D120" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E120" t="s">
         <v>39</v>
       </c>
       <c r="F120" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G120">
         <v>4</v>
@@ -37159,7 +37210,7 @@
         <v>1.5</v>
       </c>
       <c r="L120" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M120">
         <v>0</v>
@@ -37189,16 +37240,16 @@
         <v>0</v>
       </c>
       <c r="C121" t="s">
+        <v>336</v>
+      </c>
+      <c r="D121" t="s">
         <v>337</v>
       </c>
-      <c r="D121" t="s">
+      <c r="E121" t="s">
         <v>338</v>
       </c>
-      <c r="E121" t="s">
+      <c r="F121" t="s">
         <v>339</v>
-      </c>
-      <c r="F121" t="s">
-        <v>340</v>
       </c>
       <c r="G121">
         <v>4</v>
@@ -37246,16 +37297,16 @@
         <v>0</v>
       </c>
       <c r="C122" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D122" t="s">
+        <v>340</v>
+      </c>
+      <c r="E122" t="s">
         <v>341</v>
       </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
         <v>342</v>
-      </c>
-      <c r="F122" t="s">
-        <v>343</v>
       </c>
       <c r="G122">
         <v>3</v>
@@ -37303,16 +37354,16 @@
         <v>0</v>
       </c>
       <c r="C123" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D123" t="s">
         <v>137</v>
       </c>
       <c r="E123" t="s">
+        <v>343</v>
+      </c>
+      <c r="F123" t="s">
         <v>344</v>
-      </c>
-      <c r="F123" t="s">
-        <v>345</v>
       </c>
       <c r="G123">
         <v>200</v>
@@ -37360,25 +37411,25 @@
         <v>0</v>
       </c>
       <c r="C124" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D124" t="s">
+        <v>345</v>
+      </c>
+      <c r="E124" t="s">
         <v>346</v>
       </c>
-      <c r="E124" t="s">
+      <c r="F124" t="s">
         <v>347</v>
       </c>
-      <c r="F124" t="s">
+      <c r="G124" t="s">
         <v>348</v>
       </c>
-      <c r="G124" t="s">
+      <c r="H124" t="s">
         <v>349</v>
       </c>
-      <c r="H124" t="s">
+      <c r="I124" t="s">
         <v>350</v>
-      </c>
-      <c r="I124" t="s">
-        <v>351</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -37417,16 +37468,16 @@
         <v>0</v>
       </c>
       <c r="C125" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D125" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E125" t="s">
+        <v>351</v>
+      </c>
+      <c r="F125" t="s">
         <v>352</v>
-      </c>
-      <c r="F125" t="s">
-        <v>353</v>
       </c>
       <c r="G125">
         <v>20</v>
@@ -37474,16 +37525,16 @@
         <v>0</v>
       </c>
       <c r="C126" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D126" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E126" t="s">
+        <v>353</v>
+      </c>
+      <c r="F126" t="s">
         <v>354</v>
-      </c>
-      <c r="F126" t="s">
-        <v>355</v>
       </c>
       <c r="G126">
         <v>3</v>
@@ -37531,16 +37582,16 @@
         <v>0</v>
       </c>
       <c r="C127" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D127" t="s">
+        <v>355</v>
+      </c>
+      <c r="E127" t="s">
         <v>356</v>
       </c>
-      <c r="E127" t="s">
+      <c r="F127" t="s">
         <v>357</v>
-      </c>
-      <c r="F127" t="s">
-        <v>358</v>
       </c>
       <c r="G127">
         <v>10</v>
@@ -37588,16 +37639,16 @@
         <v>0</v>
       </c>
       <c r="C128" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D128" t="s">
+        <v>358</v>
+      </c>
+      <c r="E128" t="s">
         <v>359</v>
       </c>
-      <c r="E128" t="s">
+      <c r="F128" t="s">
         <v>360</v>
-      </c>
-      <c r="F128" t="s">
-        <v>361</v>
       </c>
       <c r="G128">
         <v>3</v>
@@ -37645,16 +37696,16 @@
         <v>0</v>
       </c>
       <c r="C129" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D129" t="s">
         <v>140</v>
       </c>
       <c r="E129" t="s">
+        <v>361</v>
+      </c>
+      <c r="F129" t="s">
         <v>362</v>
-      </c>
-      <c r="F129" t="s">
-        <v>363</v>
       </c>
       <c r="G129">
         <v>20</v>
@@ -37702,16 +37753,16 @@
         <v>0</v>
       </c>
       <c r="C130" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D130" t="s">
+        <v>363</v>
+      </c>
+      <c r="E130" t="s">
         <v>364</v>
       </c>
-      <c r="E130" t="s">
+      <c r="F130" t="s">
         <v>365</v>
-      </c>
-      <c r="F130" t="s">
-        <v>366</v>
       </c>
       <c r="G130">
         <v>3</v>
@@ -37759,16 +37810,16 @@
         <v>0</v>
       </c>
       <c r="C131" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D131" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E131" t="s">
+        <v>366</v>
+      </c>
+      <c r="F131" t="s">
         <v>367</v>
-      </c>
-      <c r="F131" t="s">
-        <v>368</v>
       </c>
       <c r="G131">
         <v>2</v>
@@ -37816,16 +37867,16 @@
         <v>0</v>
       </c>
       <c r="C132" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D132" t="s">
+        <v>368</v>
+      </c>
+      <c r="E132" t="s">
         <v>369</v>
       </c>
-      <c r="E132" t="s">
+      <c r="F132" t="s">
         <v>370</v>
-      </c>
-      <c r="F132" t="s">
-        <v>371</v>
       </c>
       <c r="G132">
         <v>60</v>
@@ -37873,16 +37924,16 @@
         <v>0</v>
       </c>
       <c r="C133" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D133" t="s">
+        <v>371</v>
+      </c>
+      <c r="E133" t="s">
         <v>372</v>
       </c>
-      <c r="E133" t="s">
+      <c r="F133" t="s">
         <v>373</v>
-      </c>
-      <c r="F133" t="s">
-        <v>374</v>
       </c>
       <c r="G133">
         <v>51</v>
@@ -37930,16 +37981,16 @@
         <v>0</v>
       </c>
       <c r="C134" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D134" t="s">
+        <v>374</v>
+      </c>
+      <c r="E134" t="s">
+        <v>372</v>
+      </c>
+      <c r="F134" t="s">
         <v>375</v>
-      </c>
-      <c r="E134" t="s">
-        <v>373</v>
-      </c>
-      <c r="F134" t="s">
-        <v>376</v>
       </c>
       <c r="G134">
         <v>1</v>
@@ -37987,16 +38038,16 @@
         <v>0</v>
       </c>
       <c r="C135" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D135" t="s">
+        <v>376</v>
+      </c>
+      <c r="E135" t="s">
         <v>377</v>
       </c>
-      <c r="E135" t="s">
+      <c r="F135" t="s">
         <v>378</v>
-      </c>
-      <c r="F135" t="s">
-        <v>379</v>
       </c>
       <c r="G135">
         <v>5</v>
@@ -38044,16 +38095,16 @@
         <v>0</v>
       </c>
       <c r="C136" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D136" t="s">
+        <v>379</v>
+      </c>
+      <c r="E136" t="s">
         <v>380</v>
       </c>
-      <c r="E136" t="s">
+      <c r="F136" t="s">
         <v>381</v>
-      </c>
-      <c r="F136" t="s">
-        <v>382</v>
       </c>
       <c r="G136">
         <v>100</v>
@@ -38101,16 +38152,16 @@
         <v>0</v>
       </c>
       <c r="C137" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D137" t="s">
+        <v>382</v>
+      </c>
+      <c r="E137" t="s">
         <v>383</v>
       </c>
-      <c r="E137" t="s">
+      <c r="F137" t="s">
         <v>384</v>
-      </c>
-      <c r="F137" t="s">
-        <v>385</v>
       </c>
       <c r="G137">
         <v>30</v>
@@ -38158,25 +38209,25 @@
         <v>0</v>
       </c>
       <c r="C138" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D138" t="s">
+        <v>385</v>
+      </c>
+      <c r="E138" t="s">
         <v>386</v>
       </c>
-      <c r="E138" t="s">
+      <c r="F138" t="s">
+        <v>375</v>
+      </c>
+      <c r="G138" t="s">
         <v>387</v>
       </c>
-      <c r="F138" t="s">
-        <v>376</v>
-      </c>
-      <c r="G138" t="s">
+      <c r="H138" t="s">
         <v>388</v>
       </c>
-      <c r="H138" t="s">
+      <c r="I138" t="s">
         <v>389</v>
-      </c>
-      <c r="I138" t="s">
-        <v>390</v>
       </c>
       <c r="J138">
         <v>0</v>
@@ -38215,16 +38266,16 @@
         <v>0</v>
       </c>
       <c r="C139" t="s">
+        <v>390</v>
+      </c>
+      <c r="D139" t="s">
         <v>391</v>
       </c>
-      <c r="D139" t="s">
+      <c r="E139" t="s">
         <v>392</v>
       </c>
-      <c r="E139" t="s">
+      <c r="F139" t="s">
         <v>393</v>
-      </c>
-      <c r="F139" t="s">
-        <v>394</v>
       </c>
       <c r="G139">
         <v>0.5</v>
@@ -38272,16 +38323,16 @@
         <v>0</v>
       </c>
       <c r="C140" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D140" t="s">
+        <v>394</v>
+      </c>
+      <c r="E140" t="s">
         <v>395</v>
       </c>
-      <c r="E140" t="s">
+      <c r="F140" t="s">
         <v>396</v>
-      </c>
-      <c r="F140" t="s">
-        <v>397</v>
       </c>
       <c r="G140">
         <v>50</v>
@@ -38329,16 +38380,16 @@
         <v>0</v>
       </c>
       <c r="C141" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D141" t="s">
+        <v>397</v>
+      </c>
+      <c r="E141" t="s">
         <v>398</v>
       </c>
-      <c r="E141" t="s">
+      <c r="F141" t="s">
         <v>399</v>
-      </c>
-      <c r="F141" t="s">
-        <v>400</v>
       </c>
       <c r="G141">
         <v>0</v>
@@ -38386,16 +38437,16 @@
         <v>0</v>
       </c>
       <c r="C142" t="s">
+        <v>400</v>
+      </c>
+      <c r="D142" t="s">
         <v>401</v>
       </c>
-      <c r="D142" t="s">
+      <c r="E142" t="s">
         <v>402</v>
       </c>
-      <c r="E142" t="s">
+      <c r="F142" t="s">
         <v>403</v>
-      </c>
-      <c r="F142" t="s">
-        <v>404</v>
       </c>
       <c r="G142">
         <v>200</v>
@@ -38443,28 +38494,28 @@
         <v>0</v>
       </c>
       <c r="C143" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D143" t="s">
+        <v>404</v>
+      </c>
+      <c r="E143" t="s">
         <v>405</v>
       </c>
-      <c r="E143" t="s">
+      <c r="F143" t="s">
         <v>406</v>
-      </c>
-      <c r="F143" t="s">
-        <v>407</v>
       </c>
       <c r="G143">
         <v>55</v>
       </c>
       <c r="H143" t="s">
+        <v>407</v>
+      </c>
+      <c r="I143" t="s">
         <v>408</v>
       </c>
-      <c r="I143" t="s">
-        <v>409</v>
-      </c>
       <c r="J143" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K143">
         <v>0</v>
@@ -38500,28 +38551,28 @@
         <v>0</v>
       </c>
       <c r="C144" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D144" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E144" t="s">
+        <v>405</v>
+      </c>
+      <c r="F144" t="s">
         <v>406</v>
-      </c>
-      <c r="F144" t="s">
-        <v>407</v>
       </c>
       <c r="G144">
         <v>25</v>
       </c>
       <c r="H144" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I144">
         <v>2</v>
       </c>
       <c r="J144" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K144">
         <v>0</v>
@@ -38557,28 +38608,28 @@
         <v>0</v>
       </c>
       <c r="C145" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D145" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E145" t="s">
+        <v>405</v>
+      </c>
+      <c r="F145" t="s">
         <v>406</v>
-      </c>
-      <c r="F145" t="s">
-        <v>407</v>
       </c>
       <c r="G145">
         <v>12</v>
       </c>
       <c r="H145" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I145">
         <v>2.5</v>
       </c>
       <c r="J145" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K145">
         <v>0</v>
@@ -38614,28 +38665,28 @@
         <v>0</v>
       </c>
       <c r="C146" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D146" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E146" t="s">
+        <v>405</v>
+      </c>
+      <c r="F146" t="s">
         <v>406</v>
-      </c>
-      <c r="F146" t="s">
-        <v>407</v>
       </c>
       <c r="G146">
         <v>5.5</v>
       </c>
       <c r="H146" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I146">
         <v>3</v>
       </c>
       <c r="J146" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K146">
         <v>0</v>
@@ -38671,28 +38722,28 @@
         <v>0</v>
       </c>
       <c r="C147" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D147" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E147" t="s">
+        <v>405</v>
+      </c>
+      <c r="F147" t="s">
         <v>406</v>
-      </c>
-      <c r="F147" t="s">
-        <v>407</v>
       </c>
       <c r="G147">
         <v>1.8</v>
       </c>
       <c r="H147" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I147">
         <v>3.5</v>
       </c>
       <c r="J147" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K147">
         <v>0</v>
@@ -38728,28 +38779,28 @@
         <v>0</v>
       </c>
       <c r="C148" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D148" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E148" t="s">
+        <v>405</v>
+      </c>
+      <c r="F148" t="s">
         <v>406</v>
-      </c>
-      <c r="F148" t="s">
-        <v>407</v>
       </c>
       <c r="G148">
         <v>0.35</v>
       </c>
       <c r="H148" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I148">
         <v>4</v>
       </c>
       <c r="J148" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="K148">
         <v>0</v>
@@ -38785,28 +38836,28 @@
         <v>0</v>
       </c>
       <c r="C149" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D149" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E149" t="s">
+        <v>405</v>
+      </c>
+      <c r="F149" t="s">
         <v>406</v>
-      </c>
-      <c r="F149" t="s">
-        <v>407</v>
       </c>
       <c r="G149">
         <v>0.08</v>
       </c>
       <c r="H149" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I149">
         <v>4.5</v>
       </c>
       <c r="J149" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="K149">
         <v>0</v>
@@ -38842,28 +38893,28 @@
         <v>0</v>
       </c>
       <c r="C150" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D150" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E150" t="s">
+        <v>405</v>
+      </c>
+      <c r="F150" t="s">
         <v>406</v>
-      </c>
-      <c r="F150" t="s">
-        <v>407</v>
       </c>
       <c r="G150">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="H150" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I150">
         <v>5</v>
       </c>
       <c r="J150" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="K150">
         <v>0</v>
@@ -38899,37 +38950,37 @@
         <v>0</v>
       </c>
       <c r="C151" t="s">
+        <v>420</v>
+      </c>
+      <c r="D151" t="s">
         <v>421</v>
       </c>
-      <c r="D151" t="s">
+      <c r="E151" t="s">
         <v>422</v>
       </c>
-      <c r="E151" t="s">
+      <c r="F151" t="s">
         <v>423</v>
       </c>
-      <c r="F151" t="s">
+      <c r="G151" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="I151" t="s">
         <v>424</v>
       </c>
-      <c r="G151" s="2" t="s">
-        <v>1057</v>
-      </c>
-      <c r="H151" s="2" t="s">
-        <v>1058</v>
-      </c>
-      <c r="I151" t="s">
+      <c r="J151" t="s">
         <v>425</v>
       </c>
-      <c r="J151" t="s">
+      <c r="K151" t="s">
         <v>426</v>
       </c>
-      <c r="K151" t="s">
+      <c r="L151" t="s">
         <v>427</v>
       </c>
-      <c r="L151" t="s">
+      <c r="M151" t="s">
         <v>428</v>
-      </c>
-      <c r="M151" t="s">
-        <v>429</v>
       </c>
       <c r="N151">
         <v>0</v>
@@ -38956,37 +39007,37 @@
         <v>0</v>
       </c>
       <c r="C152" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D152" t="s">
+        <v>429</v>
+      </c>
+      <c r="E152" t="s">
+        <v>422</v>
+      </c>
+      <c r="F152" t="s">
+        <v>423</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="I152" t="s">
         <v>430</v>
       </c>
-      <c r="E152" t="s">
-        <v>423</v>
-      </c>
-      <c r="F152" t="s">
-        <v>424</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>1060</v>
-      </c>
-      <c r="H152" s="2" t="s">
-        <v>1059</v>
-      </c>
-      <c r="I152" t="s">
+      <c r="J152" t="s">
         <v>431</v>
       </c>
-      <c r="J152" t="s">
+      <c r="K152" t="s">
         <v>432</v>
       </c>
-      <c r="K152" t="s">
+      <c r="L152" t="s">
         <v>433</v>
       </c>
-      <c r="L152" t="s">
+      <c r="M152" t="s">
         <v>434</v>
-      </c>
-      <c r="M152" t="s">
-        <v>435</v>
       </c>
       <c r="N152">
         <v>0</v>
@@ -39013,37 +39064,37 @@
         <v>0</v>
       </c>
       <c r="C153" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D153" t="s">
+        <v>435</v>
+      </c>
+      <c r="E153" t="s">
+        <v>422</v>
+      </c>
+      <c r="F153" t="s">
+        <v>423</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="J153" t="s">
         <v>436</v>
       </c>
-      <c r="E153" t="s">
-        <v>423</v>
-      </c>
-      <c r="F153" t="s">
-        <v>424</v>
-      </c>
-      <c r="G153" s="2" t="s">
-        <v>1061</v>
-      </c>
-      <c r="H153" s="2" t="s">
-        <v>1062</v>
-      </c>
-      <c r="I153" s="2" t="s">
-        <v>1056</v>
-      </c>
-      <c r="J153" t="s">
+      <c r="K153" t="s">
         <v>437</v>
       </c>
-      <c r="K153" t="s">
+      <c r="L153" t="s">
         <v>438</v>
       </c>
-      <c r="L153" t="s">
+      <c r="M153" t="s">
         <v>439</v>
-      </c>
-      <c r="M153" t="s">
-        <v>440</v>
       </c>
       <c r="N153">
         <v>0</v>
@@ -39070,37 +39121,37 @@
         <v>0</v>
       </c>
       <c r="C154" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D154" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E154" t="s">
+        <v>422</v>
+      </c>
+      <c r="F154" t="s">
         <v>423</v>
       </c>
-      <c r="F154" t="s">
-        <v>424</v>
-      </c>
       <c r="G154" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H154" s="2" t="s">
         <v>1083</v>
       </c>
-      <c r="H154" s="2" t="s">
-        <v>1084</v>
-      </c>
       <c r="I154" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="J154" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="K154" t="s">
+        <v>442</v>
+      </c>
+      <c r="L154" t="s">
         <v>443</v>
       </c>
-      <c r="L154" t="s">
+      <c r="M154" t="s">
         <v>444</v>
-      </c>
-      <c r="M154" t="s">
-        <v>445</v>
       </c>
       <c r="N154">
         <v>0</v>
@@ -39127,40 +39178,40 @@
         <v>0</v>
       </c>
       <c r="C155" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D155" t="s">
+        <v>445</v>
+      </c>
+      <c r="E155" t="s">
+        <v>422</v>
+      </c>
+      <c r="F155" t="s">
+        <v>423</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="J155" t="s">
         <v>446</v>
       </c>
-      <c r="E155" t="s">
-        <v>423</v>
-      </c>
-      <c r="F155" t="s">
-        <v>424</v>
-      </c>
-      <c r="G155" s="2" t="s">
-        <v>1085</v>
-      </c>
-      <c r="H155" s="2" t="s">
-        <v>1086</v>
-      </c>
-      <c r="I155" s="2" t="s">
-        <v>1087</v>
-      </c>
-      <c r="J155" t="s">
+      <c r="K155" t="s">
         <v>447</v>
       </c>
-      <c r="K155" t="s">
+      <c r="L155" t="s">
         <v>448</v>
       </c>
-      <c r="L155" t="s">
+      <c r="M155" t="s">
         <v>449</v>
       </c>
-      <c r="M155" t="s">
+      <c r="N155" t="s">
         <v>450</v>
-      </c>
-      <c r="N155" t="s">
-        <v>451</v>
       </c>
       <c r="O155">
         <v>0</v>
@@ -39184,37 +39235,37 @@
         <v>0</v>
       </c>
       <c r="C156" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D156" t="s">
+        <v>451</v>
+      </c>
+      <c r="E156" t="s">
+        <v>422</v>
+      </c>
+      <c r="F156" t="s">
+        <v>423</v>
+      </c>
+      <c r="G156" t="s">
+        <v>441</v>
+      </c>
+      <c r="H156" t="s">
         <v>452</v>
       </c>
-      <c r="E156" t="s">
-        <v>423</v>
-      </c>
-      <c r="F156" t="s">
-        <v>424</v>
-      </c>
-      <c r="G156" t="s">
-        <v>442</v>
-      </c>
-      <c r="H156" t="s">
+      <c r="I156" t="s">
+        <v>265</v>
+      </c>
+      <c r="J156" t="s">
         <v>453</v>
       </c>
-      <c r="I156" t="s">
-        <v>266</v>
-      </c>
-      <c r="J156" t="s">
+      <c r="K156" t="s">
         <v>454</v>
       </c>
-      <c r="K156" t="s">
+      <c r="L156" t="s">
         <v>455</v>
       </c>
-      <c r="L156" t="s">
+      <c r="M156" t="s">
         <v>456</v>
-      </c>
-      <c r="M156" t="s">
-        <v>457</v>
       </c>
       <c r="N156">
         <v>0</v>
@@ -39241,37 +39292,37 @@
         <v>0</v>
       </c>
       <c r="C157" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D157" t="s">
+        <v>457</v>
+      </c>
+      <c r="E157" t="s">
+        <v>422</v>
+      </c>
+      <c r="F157" t="s">
+        <v>423</v>
+      </c>
+      <c r="G157" t="s">
+        <v>441</v>
+      </c>
+      <c r="H157" t="s">
+        <v>452</v>
+      </c>
+      <c r="I157" t="s">
         <v>458</v>
       </c>
-      <c r="E157" t="s">
-        <v>423</v>
-      </c>
-      <c r="F157" t="s">
-        <v>424</v>
-      </c>
-      <c r="G157" t="s">
-        <v>442</v>
-      </c>
-      <c r="H157" t="s">
-        <v>453</v>
-      </c>
-      <c r="I157" t="s">
+      <c r="J157" t="s">
         <v>459</v>
       </c>
-      <c r="J157" t="s">
+      <c r="K157" t="s">
         <v>460</v>
       </c>
-      <c r="K157" t="s">
+      <c r="L157" t="s">
         <v>461</v>
       </c>
-      <c r="L157" t="s">
+      <c r="M157" t="s">
         <v>462</v>
-      </c>
-      <c r="M157" t="s">
-        <v>463</v>
       </c>
       <c r="N157">
         <v>0</v>
@@ -39298,37 +39349,37 @@
         <v>0</v>
       </c>
       <c r="C158" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D158" t="s">
+        <v>463</v>
+      </c>
+      <c r="E158" t="s">
+        <v>422</v>
+      </c>
+      <c r="F158" t="s">
+        <v>423</v>
+      </c>
+      <c r="G158" t="s">
+        <v>441</v>
+      </c>
+      <c r="H158" t="s">
+        <v>452</v>
+      </c>
+      <c r="I158" t="s">
+        <v>458</v>
+      </c>
+      <c r="J158" t="s">
         <v>464</v>
       </c>
-      <c r="E158" t="s">
-        <v>423</v>
-      </c>
-      <c r="F158" t="s">
-        <v>424</v>
-      </c>
-      <c r="G158" t="s">
-        <v>442</v>
-      </c>
-      <c r="H158" t="s">
-        <v>453</v>
-      </c>
-      <c r="I158" t="s">
-        <v>459</v>
-      </c>
-      <c r="J158" t="s">
+      <c r="K158" t="s">
         <v>465</v>
       </c>
-      <c r="K158" t="s">
+      <c r="L158" t="s">
         <v>466</v>
       </c>
-      <c r="L158" t="s">
+      <c r="M158" t="s">
         <v>467</v>
-      </c>
-      <c r="M158" t="s">
-        <v>468</v>
       </c>
       <c r="N158">
         <v>0</v>
@@ -39355,16 +39406,16 @@
         <v>0</v>
       </c>
       <c r="C159" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D159" t="s">
+        <v>468</v>
+      </c>
+      <c r="E159" t="s">
         <v>469</v>
       </c>
-      <c r="E159" t="s">
+      <c r="F159" t="s">
         <v>470</v>
-      </c>
-      <c r="F159" t="s">
-        <v>471</v>
       </c>
       <c r="G159">
         <v>551</v>
@@ -39412,16 +39463,16 @@
         <v>0</v>
       </c>
       <c r="C160" t="s">
+        <v>471</v>
+      </c>
+      <c r="D160" t="s">
         <v>472</v>
       </c>
-      <c r="D160" t="s">
+      <c r="E160" t="s">
         <v>473</v>
       </c>
-      <c r="E160" t="s">
+      <c r="F160" t="s">
         <v>474</v>
-      </c>
-      <c r="F160" t="s">
-        <v>475</v>
       </c>
       <c r="G160">
         <v>2</v>
@@ -39469,16 +39520,16 @@
         <v>0</v>
       </c>
       <c r="C161" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D161" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E161" t="s">
+        <v>473</v>
+      </c>
+      <c r="F161" t="s">
         <v>474</v>
-      </c>
-      <c r="F161" t="s">
-        <v>475</v>
       </c>
       <c r="G161">
         <v>4</v>
@@ -39526,16 +39577,16 @@
         <v>0</v>
       </c>
       <c r="C162" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D162" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E162" t="s">
+        <v>473</v>
+      </c>
+      <c r="F162" t="s">
         <v>474</v>
-      </c>
-      <c r="F162" t="s">
-        <v>475</v>
       </c>
       <c r="G162">
         <v>6</v>
@@ -39583,16 +39634,16 @@
         <v>0</v>
       </c>
       <c r="C163" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D163" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E163" t="s">
+        <v>473</v>
+      </c>
+      <c r="F163" t="s">
         <v>474</v>
-      </c>
-      <c r="F163" t="s">
-        <v>475</v>
       </c>
       <c r="G163">
         <v>8</v>
@@ -39640,16 +39691,16 @@
         <v>0</v>
       </c>
       <c r="C164" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D164" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E164" t="s">
+        <v>473</v>
+      </c>
+      <c r="F164" t="s">
         <v>474</v>
-      </c>
-      <c r="F164" t="s">
-        <v>475</v>
       </c>
       <c r="G164">
         <v>10</v>
@@ -39697,16 +39748,16 @@
         <v>0</v>
       </c>
       <c r="C165" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D165" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E165" t="s">
+        <v>473</v>
+      </c>
+      <c r="F165" t="s">
         <v>474</v>
-      </c>
-      <c r="F165" t="s">
-        <v>475</v>
       </c>
       <c r="G165">
         <v>12</v>
@@ -39754,16 +39805,16 @@
         <v>0</v>
       </c>
       <c r="C166" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D166" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E166" t="s">
+        <v>473</v>
+      </c>
+      <c r="F166" t="s">
         <v>474</v>
-      </c>
-      <c r="F166" t="s">
-        <v>475</v>
       </c>
       <c r="G166">
         <v>14</v>
@@ -39811,16 +39862,16 @@
         <v>0</v>
       </c>
       <c r="C167" t="s">
+        <v>481</v>
+      </c>
+      <c r="D167" t="s">
         <v>482</v>
       </c>
-      <c r="D167" t="s">
+      <c r="E167" t="s">
         <v>483</v>
       </c>
-      <c r="E167" t="s">
+      <c r="F167" t="s">
         <v>484</v>
-      </c>
-      <c r="F167" t="s">
-        <v>485</v>
       </c>
       <c r="G167">
         <v>4</v>
@@ -39868,16 +39919,16 @@
         <v>0</v>
       </c>
       <c r="C168" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D168" t="s">
+        <v>485</v>
+      </c>
+      <c r="E168" t="s">
         <v>486</v>
       </c>
-      <c r="E168" t="s">
+      <c r="F168" t="s">
         <v>487</v>
-      </c>
-      <c r="F168" t="s">
-        <v>488</v>
       </c>
       <c r="G168">
         <v>5</v>
@@ -39925,16 +39976,16 @@
         <v>0</v>
       </c>
       <c r="C169" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D169" t="s">
+        <v>488</v>
+      </c>
+      <c r="E169" t="s">
+        <v>486</v>
+      </c>
+      <c r="F169" t="s">
         <v>489</v>
-      </c>
-      <c r="E169" t="s">
-        <v>487</v>
-      </c>
-      <c r="F169" t="s">
-        <v>490</v>
       </c>
       <c r="G169">
         <v>10</v>
@@ -39982,16 +40033,16 @@
         <v>0</v>
       </c>
       <c r="C170" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D170" t="s">
+        <v>490</v>
+      </c>
+      <c r="E170" t="s">
         <v>491</v>
       </c>
-      <c r="E170" t="s">
+      <c r="F170" t="s">
         <v>492</v>
-      </c>
-      <c r="F170" t="s">
-        <v>493</v>
       </c>
       <c r="G170">
         <v>0.5</v>
@@ -40039,16 +40090,16 @@
         <v>0</v>
       </c>
       <c r="C171" t="s">
+        <v>493</v>
+      </c>
+      <c r="D171" t="s">
         <v>494</v>
       </c>
-      <c r="D171" t="s">
+      <c r="E171" t="s">
         <v>495</v>
       </c>
-      <c r="E171" t="s">
+      <c r="F171" t="s">
         <v>496</v>
-      </c>
-      <c r="F171" t="s">
-        <v>497</v>
       </c>
       <c r="G171">
         <v>100</v>
@@ -40096,16 +40147,16 @@
         <v>0</v>
       </c>
       <c r="C172" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D172" t="s">
+        <v>497</v>
+      </c>
+      <c r="E172" t="s">
         <v>498</v>
       </c>
-      <c r="E172" t="s">
+      <c r="F172" t="s">
         <v>499</v>
-      </c>
-      <c r="F172" t="s">
-        <v>500</v>
       </c>
       <c r="G172">
         <v>92</v>
@@ -40153,16 +40204,16 @@
         <v>0</v>
       </c>
       <c r="C173" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D173" t="s">
+        <v>500</v>
+      </c>
+      <c r="E173" t="s">
         <v>501</v>
       </c>
-      <c r="E173" t="s">
+      <c r="F173" t="s">
         <v>502</v>
-      </c>
-      <c r="F173" t="s">
-        <v>503</v>
       </c>
       <c r="G173">
         <v>78.099999999999994</v>
@@ -40210,16 +40261,16 @@
         <v>0</v>
       </c>
       <c r="C174" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D174" t="s">
+        <v>503</v>
+      </c>
+      <c r="E174" t="s">
         <v>504</v>
       </c>
-      <c r="E174" t="s">
+      <c r="F174" t="s">
         <v>505</v>
-      </c>
-      <c r="F174" t="s">
-        <v>506</v>
       </c>
       <c r="G174">
         <v>72.11</v>
@@ -40267,16 +40318,16 @@
         <v>0</v>
       </c>
       <c r="C175" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D175" t="s">
+        <v>506</v>
+      </c>
+      <c r="E175" t="s">
         <v>507</v>
       </c>
-      <c r="E175" t="s">
+      <c r="F175" t="s">
         <v>508</v>
-      </c>
-      <c r="F175" t="s">
-        <v>509</v>
       </c>
       <c r="G175">
         <v>74.349999999999994</v>
@@ -40324,16 +40375,16 @@
         <v>0</v>
       </c>
       <c r="C176" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D176" t="s">
+        <v>509</v>
+      </c>
+      <c r="E176" t="s">
         <v>510</v>
       </c>
-      <c r="E176" t="s">
+      <c r="F176" t="s">
         <v>511</v>
-      </c>
-      <c r="F176" t="s">
-        <v>512</v>
       </c>
       <c r="G176">
         <v>76.87</v>
@@ -40381,16 +40432,16 @@
         <v>0</v>
       </c>
       <c r="C177" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D177" t="s">
+        <v>512</v>
+      </c>
+      <c r="E177" t="s">
         <v>513</v>
       </c>
-      <c r="E177" t="s">
+      <c r="F177" t="s">
         <v>514</v>
-      </c>
-      <c r="F177" t="s">
-        <v>515</v>
       </c>
       <c r="G177">
         <v>69.92</v>
@@ -40438,16 +40489,16 @@
         <v>0</v>
       </c>
       <c r="C178" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D178" t="s">
+        <v>515</v>
+      </c>
+      <c r="E178" t="s">
         <v>516</v>
       </c>
-      <c r="E178" t="s">
+      <c r="F178" t="s">
         <v>517</v>
-      </c>
-      <c r="F178" t="s">
-        <v>518</v>
       </c>
       <c r="G178">
         <v>64.22</v>
@@ -40495,16 +40546,16 @@
         <v>0</v>
       </c>
       <c r="C179" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D179" t="s">
+        <v>518</v>
+      </c>
+      <c r="E179" t="s">
         <v>519</v>
       </c>
-      <c r="E179" t="s">
+      <c r="F179" t="s">
         <v>520</v>
-      </c>
-      <c r="F179" t="s">
-        <v>521</v>
       </c>
       <c r="G179">
         <v>59.92</v>
@@ -40552,16 +40603,16 @@
         <v>0</v>
       </c>
       <c r="C180" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D180" t="s">
+        <v>521</v>
+      </c>
+      <c r="E180" t="s">
         <v>522</v>
       </c>
-      <c r="E180" t="s">
+      <c r="F180" t="s">
         <v>523</v>
-      </c>
-      <c r="F180" t="s">
-        <v>524</v>
       </c>
       <c r="G180">
         <v>54.72</v>
@@ -40609,16 +40660,16 @@
         <v>0</v>
       </c>
       <c r="C181" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D181" t="s">
+        <v>524</v>
+      </c>
+      <c r="E181" t="s">
         <v>525</v>
       </c>
-      <c r="E181" t="s">
+      <c r="F181" t="s">
         <v>526</v>
-      </c>
-      <c r="F181" t="s">
-        <v>527</v>
       </c>
       <c r="G181">
         <v>1.35</v>
@@ -40666,16 +40717,16 @@
         <v>0</v>
       </c>
       <c r="C182" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D182" t="s">
+        <v>527</v>
+      </c>
+      <c r="E182" t="s">
         <v>528</v>
       </c>
-      <c r="E182" t="s">
+      <c r="F182" t="s">
         <v>529</v>
-      </c>
-      <c r="F182" t="s">
-        <v>530</v>
       </c>
       <c r="G182">
         <v>0.5</v>
@@ -40723,16 +40774,16 @@
         <v>0</v>
       </c>
       <c r="C183" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D183" t="s">
+        <v>530</v>
+      </c>
+      <c r="E183" t="s">
         <v>531</v>
       </c>
-      <c r="E183" t="s">
+      <c r="F183" t="s">
         <v>532</v>
-      </c>
-      <c r="F183" t="s">
-        <v>533</v>
       </c>
       <c r="G183">
         <v>4000</v>
@@ -40780,16 +40831,16 @@
         <v>0</v>
       </c>
       <c r="C184" t="s">
+        <v>533</v>
+      </c>
+      <c r="D184" t="s">
         <v>534</v>
       </c>
-      <c r="D184" t="s">
+      <c r="E184" t="s">
         <v>535</v>
       </c>
-      <c r="E184" t="s">
+      <c r="F184" t="s">
         <v>536</v>
-      </c>
-      <c r="F184" t="s">
-        <v>537</v>
       </c>
       <c r="G184">
         <v>4</v>
@@ -40837,16 +40888,16 @@
         <v>0</v>
       </c>
       <c r="C185" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D185" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E185" t="s">
+        <v>537</v>
+      </c>
+      <c r="F185" t="s">
         <v>538</v>
-      </c>
-      <c r="F185" t="s">
-        <v>539</v>
       </c>
       <c r="G185">
         <v>200</v>
@@ -40894,16 +40945,16 @@
         <v>0</v>
       </c>
       <c r="C186" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D186" t="s">
+        <v>539</v>
+      </c>
+      <c r="E186" t="s">
         <v>540</v>
       </c>
-      <c r="E186" t="s">
+      <c r="F186" t="s">
         <v>541</v>
-      </c>
-      <c r="F186" t="s">
-        <v>542</v>
       </c>
       <c r="G186">
         <v>4</v>
@@ -40951,16 +41002,16 @@
         <v>0</v>
       </c>
       <c r="C187" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D187" t="s">
+        <v>542</v>
+      </c>
+      <c r="E187" t="s">
         <v>543</v>
       </c>
-      <c r="E187" t="s">
+      <c r="F187" t="s">
         <v>544</v>
-      </c>
-      <c r="F187" t="s">
-        <v>545</v>
       </c>
       <c r="G187">
         <v>3</v>
@@ -41008,16 +41059,16 @@
         <v>0</v>
       </c>
       <c r="C188" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D188" t="s">
+        <v>545</v>
+      </c>
+      <c r="E188" t="s">
         <v>546</v>
       </c>
-      <c r="E188" t="s">
+      <c r="F188" t="s">
         <v>547</v>
-      </c>
-      <c r="F188" t="s">
-        <v>548</v>
       </c>
       <c r="G188">
         <v>4</v>
@@ -41065,37 +41116,37 @@
         <v>0</v>
       </c>
       <c r="C189" t="s">
+        <v>548</v>
+      </c>
+      <c r="D189" t="s">
+        <v>421</v>
+      </c>
+      <c r="E189" t="s">
         <v>549</v>
       </c>
-      <c r="D189" t="s">
-        <v>422</v>
-      </c>
-      <c r="E189" t="s">
+      <c r="F189" t="s">
         <v>550</v>
       </c>
-      <c r="F189" t="s">
+      <c r="G189" t="s">
         <v>551</v>
       </c>
-      <c r="G189" t="s">
+      <c r="H189" t="s">
         <v>552</v>
       </c>
-      <c r="H189" t="s">
+      <c r="I189" t="s">
         <v>553</v>
       </c>
-      <c r="I189" t="s">
+      <c r="J189" t="s">
         <v>554</v>
       </c>
-      <c r="J189" t="s">
+      <c r="K189" t="s">
         <v>555</v>
       </c>
-      <c r="K189" t="s">
+      <c r="L189" t="s">
         <v>556</v>
       </c>
-      <c r="L189" t="s">
+      <c r="M189" t="s">
         <v>557</v>
-      </c>
-      <c r="M189" t="s">
-        <v>558</v>
       </c>
       <c r="N189">
         <v>0</v>
@@ -41122,37 +41173,37 @@
         <v>0</v>
       </c>
       <c r="C190" t="s">
+        <v>548</v>
+      </c>
+      <c r="D190" t="s">
+        <v>429</v>
+      </c>
+      <c r="E190" t="s">
         <v>549</v>
       </c>
-      <c r="D190" t="s">
-        <v>430</v>
-      </c>
-      <c r="E190" t="s">
+      <c r="F190" t="s">
         <v>550</v>
       </c>
-      <c r="F190" t="s">
+      <c r="G190" t="s">
         <v>551</v>
       </c>
-      <c r="G190" t="s">
+      <c r="H190" t="s">
         <v>552</v>
       </c>
-      <c r="H190" t="s">
+      <c r="I190" t="s">
         <v>553</v>
       </c>
-      <c r="I190" t="s">
+      <c r="J190" t="s">
         <v>554</v>
       </c>
-      <c r="J190" t="s">
+      <c r="K190" t="s">
         <v>555</v>
       </c>
-      <c r="K190" t="s">
+      <c r="L190" t="s">
         <v>556</v>
       </c>
-      <c r="L190" t="s">
+      <c r="M190" t="s">
         <v>557</v>
-      </c>
-      <c r="M190" t="s">
-        <v>558</v>
       </c>
       <c r="N190">
         <v>0</v>
@@ -41179,37 +41230,37 @@
         <v>0</v>
       </c>
       <c r="C191" t="s">
+        <v>548</v>
+      </c>
+      <c r="D191" t="s">
+        <v>435</v>
+      </c>
+      <c r="E191" t="s">
         <v>549</v>
       </c>
-      <c r="D191" t="s">
-        <v>436</v>
-      </c>
-      <c r="E191" t="s">
+      <c r="F191" t="s">
         <v>550</v>
       </c>
-      <c r="F191" t="s">
-        <v>551</v>
-      </c>
       <c r="G191" t="s">
+        <v>558</v>
+      </c>
+      <c r="H191" t="s">
         <v>559</v>
       </c>
-      <c r="H191" t="s">
-        <v>560</v>
-      </c>
       <c r="I191" t="s">
+        <v>553</v>
+      </c>
+      <c r="J191" t="s">
         <v>554</v>
       </c>
-      <c r="J191" t="s">
+      <c r="K191" t="s">
         <v>555</v>
       </c>
-      <c r="K191" t="s">
+      <c r="L191" t="s">
         <v>556</v>
       </c>
-      <c r="L191" t="s">
+      <c r="M191" t="s">
         <v>557</v>
-      </c>
-      <c r="M191" t="s">
-        <v>558</v>
       </c>
       <c r="N191">
         <v>0</v>
@@ -41236,37 +41287,37 @@
         <v>0</v>
       </c>
       <c r="C192" t="s">
+        <v>548</v>
+      </c>
+      <c r="D192" t="s">
+        <v>440</v>
+      </c>
+      <c r="E192" t="s">
         <v>549</v>
       </c>
-      <c r="D192" t="s">
-        <v>441</v>
-      </c>
-      <c r="E192" t="s">
+      <c r="F192" t="s">
         <v>550</v>
       </c>
-      <c r="F192" t="s">
-        <v>551</v>
-      </c>
       <c r="G192" t="s">
+        <v>560</v>
+      </c>
+      <c r="H192" t="s">
+        <v>559</v>
+      </c>
+      <c r="I192" t="s">
         <v>561</v>
       </c>
-      <c r="H192" t="s">
-        <v>560</v>
-      </c>
-      <c r="I192" t="s">
+      <c r="J192" t="s">
         <v>562</v>
       </c>
-      <c r="J192" t="s">
+      <c r="K192" t="s">
         <v>563</v>
       </c>
-      <c r="K192" t="s">
+      <c r="L192" t="s">
         <v>564</v>
       </c>
-      <c r="L192" t="s">
+      <c r="M192" t="s">
         <v>565</v>
-      </c>
-      <c r="M192" t="s">
-        <v>566</v>
       </c>
       <c r="N192">
         <v>0</v>
@@ -41293,37 +41344,37 @@
         <v>0</v>
       </c>
       <c r="C193" t="s">
+        <v>548</v>
+      </c>
+      <c r="D193" t="s">
+        <v>445</v>
+      </c>
+      <c r="E193" t="s">
         <v>549</v>
       </c>
-      <c r="D193" t="s">
-        <v>446</v>
-      </c>
-      <c r="E193" t="s">
+      <c r="F193" t="s">
         <v>550</v>
       </c>
-      <c r="F193" t="s">
-        <v>551</v>
-      </c>
       <c r="G193" t="s">
+        <v>566</v>
+      </c>
+      <c r="H193" t="s">
         <v>567</v>
       </c>
-      <c r="H193" t="s">
+      <c r="I193" t="s">
+        <v>561</v>
+      </c>
+      <c r="J193" t="s">
         <v>568</v>
       </c>
-      <c r="I193" t="s">
-        <v>562</v>
-      </c>
-      <c r="J193" t="s">
+      <c r="K193" t="s">
         <v>569</v>
       </c>
-      <c r="K193" t="s">
+      <c r="L193" t="s">
         <v>570</v>
       </c>
-      <c r="L193" t="s">
+      <c r="M193" t="s">
         <v>571</v>
-      </c>
-      <c r="M193" t="s">
-        <v>572</v>
       </c>
       <c r="N193">
         <v>0</v>
@@ -41350,37 +41401,37 @@
         <v>0</v>
       </c>
       <c r="C194" t="s">
+        <v>548</v>
+      </c>
+      <c r="D194" t="s">
+        <v>451</v>
+      </c>
+      <c r="E194" t="s">
         <v>549</v>
       </c>
-      <c r="D194" t="s">
-        <v>452</v>
-      </c>
-      <c r="E194" t="s">
+      <c r="F194" t="s">
         <v>550</v>
       </c>
-      <c r="F194" t="s">
-        <v>551</v>
-      </c>
       <c r="G194" t="s">
+        <v>572</v>
+      </c>
+      <c r="H194" t="s">
         <v>573</v>
       </c>
-      <c r="H194" t="s">
+      <c r="I194" t="s">
         <v>574</v>
       </c>
-      <c r="I194" t="s">
+      <c r="J194" t="s">
         <v>575</v>
       </c>
-      <c r="J194" t="s">
+      <c r="K194" t="s">
         <v>576</v>
       </c>
-      <c r="K194" t="s">
+      <c r="L194" t="s">
         <v>577</v>
       </c>
-      <c r="L194" t="s">
+      <c r="M194" t="s">
         <v>578</v>
-      </c>
-      <c r="M194" t="s">
-        <v>579</v>
       </c>
       <c r="N194">
         <v>0</v>
@@ -41407,37 +41458,37 @@
         <v>0</v>
       </c>
       <c r="C195" t="s">
+        <v>548</v>
+      </c>
+      <c r="D195" t="s">
+        <v>457</v>
+      </c>
+      <c r="E195" t="s">
         <v>549</v>
       </c>
-      <c r="D195" t="s">
-        <v>458</v>
-      </c>
-      <c r="E195" t="s">
+      <c r="F195" t="s">
         <v>550</v>
       </c>
-      <c r="F195" t="s">
+      <c r="G195" t="s">
         <v>551</v>
       </c>
-      <c r="G195" t="s">
-        <v>552</v>
-      </c>
       <c r="H195" t="s">
+        <v>579</v>
+      </c>
+      <c r="I195" t="s">
         <v>580</v>
       </c>
-      <c r="I195" t="s">
+      <c r="J195" t="s">
         <v>581</v>
       </c>
-      <c r="J195" t="s">
+      <c r="K195" t="s">
         <v>582</v>
       </c>
-      <c r="K195" t="s">
+      <c r="L195" t="s">
         <v>583</v>
       </c>
-      <c r="L195" t="s">
+      <c r="M195" t="s">
         <v>584</v>
-      </c>
-      <c r="M195" t="s">
-        <v>585</v>
       </c>
       <c r="N195">
         <v>0</v>
@@ -41464,37 +41515,37 @@
         <v>0</v>
       </c>
       <c r="C196" t="s">
+        <v>548</v>
+      </c>
+      <c r="D196" t="s">
+        <v>463</v>
+      </c>
+      <c r="E196" t="s">
         <v>549</v>
       </c>
-      <c r="D196" t="s">
-        <v>464</v>
-      </c>
-      <c r="E196" t="s">
+      <c r="F196" t="s">
         <v>550</v>
       </c>
-      <c r="F196" t="s">
+      <c r="G196" t="s">
         <v>551</v>
       </c>
-      <c r="G196" t="s">
+      <c r="H196" t="s">
         <v>552</v>
       </c>
-      <c r="H196" t="s">
-        <v>553</v>
-      </c>
       <c r="I196" t="s">
+        <v>585</v>
+      </c>
+      <c r="J196" t="s">
         <v>586</v>
       </c>
-      <c r="J196" t="s">
+      <c r="K196" t="s">
         <v>587</v>
       </c>
-      <c r="K196" t="s">
+      <c r="L196" t="s">
         <v>588</v>
       </c>
-      <c r="L196" t="s">
+      <c r="M196" t="s">
         <v>589</v>
-      </c>
-      <c r="M196" t="s">
-        <v>590</v>
       </c>
       <c r="N196">
         <v>0</v>
@@ -41521,16 +41572,16 @@
         <v>0</v>
       </c>
       <c r="C197" t="s">
+        <v>590</v>
+      </c>
+      <c r="D197" t="s">
         <v>591</v>
       </c>
-      <c r="D197" t="s">
+      <c r="E197" t="s">
         <v>592</v>
       </c>
-      <c r="E197" t="s">
+      <c r="F197" t="s">
         <v>593</v>
-      </c>
-      <c r="F197" t="s">
-        <v>594</v>
       </c>
       <c r="G197">
         <v>0</v>
@@ -41578,16 +41629,16 @@
         <v>0</v>
       </c>
       <c r="C198" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D198" t="s">
+        <v>594</v>
+      </c>
+      <c r="E198" t="s">
         <v>595</v>
       </c>
-      <c r="E198" t="s">
+      <c r="F198" t="s">
         <v>596</v>
-      </c>
-      <c r="F198" t="s">
-        <v>597</v>
       </c>
       <c r="G198">
         <v>1.35</v>
@@ -41635,16 +41686,16 @@
         <v>0</v>
       </c>
       <c r="C199" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D199" t="s">
+        <v>597</v>
+      </c>
+      <c r="E199" t="s">
         <v>598</v>
       </c>
-      <c r="E199" t="s">
+      <c r="F199" t="s">
         <v>599</v>
-      </c>
-      <c r="F199" t="s">
-        <v>600</v>
       </c>
       <c r="G199">
         <v>0.05</v>
@@ -41692,16 +41743,16 @@
         <v>0</v>
       </c>
       <c r="C200" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D200" t="s">
+        <v>600</v>
+      </c>
+      <c r="E200" t="s">
         <v>601</v>
       </c>
-      <c r="E200" t="s">
+      <c r="F200" t="s">
         <v>602</v>
-      </c>
-      <c r="F200" t="s">
-        <v>603</v>
       </c>
       <c r="G200">
         <v>2</v>
@@ -41749,16 +41800,16 @@
         <v>0</v>
       </c>
       <c r="C201" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D201" t="s">
+        <v>603</v>
+      </c>
+      <c r="E201" t="s">
         <v>604</v>
       </c>
-      <c r="E201" t="s">
+      <c r="F201" t="s">
         <v>605</v>
-      </c>
-      <c r="F201" t="s">
-        <v>606</v>
       </c>
       <c r="G201">
         <v>0</v>
@@ -41806,16 +41857,16 @@
         <v>0</v>
       </c>
       <c r="C202" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D202" t="s">
+        <v>606</v>
+      </c>
+      <c r="E202" t="s">
         <v>607</v>
       </c>
-      <c r="E202" t="s">
+      <c r="F202" t="s">
         <v>608</v>
-      </c>
-      <c r="F202" t="s">
-        <v>609</v>
       </c>
       <c r="G202">
         <v>5</v>
@@ -41863,16 +41914,16 @@
         <v>0</v>
       </c>
       <c r="C203" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D203" t="s">
+        <v>609</v>
+      </c>
+      <c r="E203" t="s">
         <v>610</v>
       </c>
-      <c r="E203" t="s">
+      <c r="F203" t="s">
         <v>611</v>
-      </c>
-      <c r="F203" t="s">
-        <v>612</v>
       </c>
       <c r="G203">
         <v>8</v>
@@ -41920,16 +41971,16 @@
         <v>0</v>
       </c>
       <c r="C204" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D204" t="s">
+        <v>612</v>
+      </c>
+      <c r="E204" t="s">
         <v>613</v>
       </c>
-      <c r="E204" t="s">
+      <c r="F204" t="s">
         <v>614</v>
-      </c>
-      <c r="F204" t="s">
-        <v>615</v>
       </c>
       <c r="G204">
         <v>1</v>
@@ -41977,16 +42028,16 @@
         <v>0</v>
       </c>
       <c r="C205" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D205" t="s">
+        <v>615</v>
+      </c>
+      <c r="E205" t="s">
         <v>616</v>
       </c>
-      <c r="E205" t="s">
+      <c r="F205" t="s">
         <v>617</v>
-      </c>
-      <c r="F205" t="s">
-        <v>618</v>
       </c>
       <c r="G205">
         <v>0.15</v>
@@ -42034,16 +42085,16 @@
         <v>0</v>
       </c>
       <c r="C206" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D206" t="s">
+        <v>618</v>
+      </c>
+      <c r="E206" t="s">
         <v>619</v>
       </c>
-      <c r="E206" t="s">
+      <c r="F206" t="s">
         <v>620</v>
-      </c>
-      <c r="F206" t="s">
-        <v>621</v>
       </c>
       <c r="G206">
         <v>2</v>
@@ -42091,16 +42142,16 @@
         <v>0</v>
       </c>
       <c r="C207" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D207" t="s">
+        <v>621</v>
+      </c>
+      <c r="E207" t="s">
         <v>622</v>
       </c>
-      <c r="E207" t="s">
+      <c r="F207" t="s">
         <v>623</v>
-      </c>
-      <c r="F207" t="s">
-        <v>624</v>
       </c>
       <c r="G207">
         <v>3</v>
@@ -42148,16 +42199,16 @@
         <v>0</v>
       </c>
       <c r="C208" t="s">
+        <v>624</v>
+      </c>
+      <c r="D208" t="s">
         <v>625</v>
       </c>
-      <c r="D208" t="s">
+      <c r="E208" t="s">
         <v>626</v>
       </c>
-      <c r="E208" t="s">
+      <c r="F208" t="s">
         <v>627</v>
-      </c>
-      <c r="F208" t="s">
-        <v>628</v>
       </c>
       <c r="G208">
         <v>5</v>
@@ -42205,16 +42256,16 @@
         <v>0</v>
       </c>
       <c r="C209" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D209" t="s">
+        <v>628</v>
+      </c>
+      <c r="E209" t="s">
         <v>629</v>
       </c>
-      <c r="E209" t="s">
+      <c r="F209" t="s">
         <v>630</v>
-      </c>
-      <c r="F209" t="s">
-        <v>631</v>
       </c>
       <c r="G209">
         <v>0</v>
@@ -42262,16 +42313,16 @@
         <v>0</v>
       </c>
       <c r="C210" t="s">
+        <v>631</v>
+      </c>
+      <c r="D210" t="s">
         <v>632</v>
       </c>
-      <c r="D210" t="s">
+      <c r="E210" t="s">
         <v>633</v>
       </c>
-      <c r="E210" t="s">
+      <c r="F210" t="s">
         <v>634</v>
-      </c>
-      <c r="F210" t="s">
-        <v>635</v>
       </c>
       <c r="G210">
         <v>5</v>
@@ -42319,16 +42370,16 @@
         <v>0</v>
       </c>
       <c r="C211" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D211" t="s">
+        <v>635</v>
+      </c>
+      <c r="E211" t="s">
         <v>636</v>
       </c>
-      <c r="E211" t="s">
+      <c r="F211" t="s">
         <v>637</v>
-      </c>
-      <c r="F211" t="s">
-        <v>638</v>
       </c>
       <c r="G211">
         <v>55</v>
@@ -42376,16 +42427,16 @@
         <v>0</v>
       </c>
       <c r="C212" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D212" t="s">
+        <v>638</v>
+      </c>
+      <c r="E212" t="s">
         <v>639</v>
       </c>
-      <c r="E212" t="s">
+      <c r="F212" t="s">
         <v>640</v>
-      </c>
-      <c r="F212" t="s">
-        <v>641</v>
       </c>
       <c r="G212">
         <v>5000000</v>
@@ -42433,13 +42484,13 @@
         <v>0</v>
       </c>
       <c r="C213" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D213" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E213" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="F213">
         <v>0</v>
@@ -42490,16 +42541,16 @@
         <v>0</v>
       </c>
       <c r="C214" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D214" t="s">
+        <v>642</v>
+      </c>
+      <c r="E214" t="s">
         <v>643</v>
       </c>
-      <c r="E214" t="s">
+      <c r="F214" t="s">
         <v>644</v>
-      </c>
-      <c r="F214" t="s">
-        <v>645</v>
       </c>
       <c r="G214">
         <v>3</v>
@@ -42547,16 +42598,16 @@
         <v>0</v>
       </c>
       <c r="C215" t="s">
+        <v>645</v>
+      </c>
+      <c r="D215" t="s">
         <v>646</v>
       </c>
-      <c r="D215" t="s">
+      <c r="E215" t="s">
         <v>647</v>
       </c>
-      <c r="E215" t="s">
+      <c r="F215" t="s">
         <v>648</v>
-      </c>
-      <c r="F215" t="s">
-        <v>649</v>
       </c>
       <c r="G215">
         <v>27</v>
@@ -42604,16 +42655,16 @@
         <v>0</v>
       </c>
       <c r="C216" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D216" t="s">
+        <v>649</v>
+      </c>
+      <c r="E216" t="s">
         <v>650</v>
       </c>
-      <c r="E216" t="s">
-        <v>651</v>
-      </c>
       <c r="F216" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G216">
         <v>36</v>
@@ -42661,16 +42712,16 @@
         <v>0</v>
       </c>
       <c r="C217" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D217" t="s">
+        <v>651</v>
+      </c>
+      <c r="E217" t="s">
+        <v>633</v>
+      </c>
+      <c r="F217" t="s">
         <v>652</v>
-      </c>
-      <c r="E217" t="s">
-        <v>634</v>
-      </c>
-      <c r="F217" t="s">
-        <v>653</v>
       </c>
       <c r="G217">
         <v>3</v>
@@ -42718,16 +42769,16 @@
         <v>0</v>
       </c>
       <c r="C218" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D218" t="s">
+        <v>653</v>
+      </c>
+      <c r="E218" t="s">
         <v>654</v>
       </c>
-      <c r="E218" t="s">
+      <c r="F218" t="s">
         <v>655</v>
-      </c>
-      <c r="F218" t="s">
-        <v>656</v>
       </c>
       <c r="G218">
         <v>50</v>
@@ -42775,16 +42826,16 @@
         <v>0</v>
       </c>
       <c r="C219" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D219" t="s">
+        <v>656</v>
+      </c>
+      <c r="E219" t="s">
         <v>657</v>
       </c>
-      <c r="E219" t="s">
+      <c r="F219" t="s">
         <v>658</v>
-      </c>
-      <c r="F219" t="s">
-        <v>659</v>
       </c>
       <c r="G219">
         <v>1000000</v>
@@ -42832,13 +42883,13 @@
         <v>0</v>
       </c>
       <c r="C220" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D220" t="s">
+        <v>659</v>
+      </c>
+      <c r="E220" t="s">
         <v>660</v>
-      </c>
-      <c r="E220" t="s">
-        <v>661</v>
       </c>
       <c r="F220">
         <v>0</v>
@@ -42889,16 +42940,16 @@
         <v>0</v>
       </c>
       <c r="C221" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D221" t="s">
+        <v>661</v>
+      </c>
+      <c r="E221" t="s">
         <v>662</v>
       </c>
-      <c r="E221" t="s">
+      <c r="F221" t="s">
         <v>663</v>
-      </c>
-      <c r="F221" t="s">
-        <v>664</v>
       </c>
       <c r="G221">
         <v>3</v>
@@ -42946,16 +42997,16 @@
         <v>0</v>
       </c>
       <c r="C222" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D222" t="s">
+        <v>664</v>
+      </c>
+      <c r="E222" t="s">
         <v>665</v>
       </c>
-      <c r="E222" t="s">
+      <c r="F222" t="s">
         <v>666</v>
-      </c>
-      <c r="F222" t="s">
-        <v>667</v>
       </c>
       <c r="G222">
         <v>6</v>
@@ -43003,16 +43054,16 @@
         <v>0</v>
       </c>
       <c r="C223" t="s">
+        <v>667</v>
+      </c>
+      <c r="D223" t="s">
         <v>668</v>
       </c>
-      <c r="D223" t="s">
+      <c r="E223" t="s">
         <v>669</v>
       </c>
-      <c r="E223" t="s">
+      <c r="F223" t="s">
         <v>670</v>
-      </c>
-      <c r="F223" t="s">
-        <v>671</v>
       </c>
       <c r="G223">
         <v>30</v>
@@ -43060,13 +43111,13 @@
         <v>0</v>
       </c>
       <c r="C224" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D224" t="s">
+        <v>671</v>
+      </c>
+      <c r="E224" t="s">
         <v>672</v>
-      </c>
-      <c r="E224" t="s">
-        <v>673</v>
       </c>
       <c r="F224">
         <v>0</v>
@@ -43117,13 +43168,13 @@
         <v>0</v>
       </c>
       <c r="C225" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D225" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E225" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F225">
         <v>0</v>
@@ -43174,16 +43225,16 @@
         <v>0</v>
       </c>
       <c r="C226" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D226" t="s">
+        <v>674</v>
+      </c>
+      <c r="E226" t="s">
         <v>675</v>
       </c>
-      <c r="E226" t="s">
+      <c r="F226" t="s">
         <v>676</v>
-      </c>
-      <c r="F226" t="s">
-        <v>677</v>
       </c>
       <c r="G226">
         <v>0</v>
@@ -43231,13 +43282,13 @@
         <v>0</v>
       </c>
       <c r="C227" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D227" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E227" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F227">
         <v>0</v>
@@ -43288,16 +43339,16 @@
         <v>0</v>
       </c>
       <c r="C228" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D228" t="s">
+        <v>678</v>
+      </c>
+      <c r="E228" t="s">
         <v>679</v>
       </c>
-      <c r="E228" t="s">
+      <c r="F228" t="s">
         <v>680</v>
-      </c>
-      <c r="F228" t="s">
-        <v>681</v>
       </c>
       <c r="G228">
         <v>9</v>
@@ -43345,16 +43396,16 @@
         <v>0</v>
       </c>
       <c r="C229" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D229" t="s">
+        <v>681</v>
+      </c>
+      <c r="E229" t="s">
         <v>682</v>
       </c>
-      <c r="E229" t="s">
+      <c r="F229" t="s">
         <v>683</v>
-      </c>
-      <c r="F229" t="s">
-        <v>684</v>
       </c>
       <c r="G229">
         <v>1</v>
@@ -43402,16 +43453,16 @@
         <v>0</v>
       </c>
       <c r="C230" t="s">
+        <v>684</v>
+      </c>
+      <c r="D230" t="s">
         <v>685</v>
       </c>
-      <c r="D230" t="s">
+      <c r="E230" t="s">
         <v>686</v>
       </c>
-      <c r="E230" t="s">
+      <c r="F230" t="s">
         <v>687</v>
-      </c>
-      <c r="F230" t="s">
-        <v>688</v>
       </c>
       <c r="G230">
         <v>5</v>
@@ -43459,16 +43510,16 @@
         <v>0</v>
       </c>
       <c r="C231" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D231" t="s">
+        <v>688</v>
+      </c>
+      <c r="E231" t="s">
         <v>689</v>
       </c>
-      <c r="E231" t="s">
+      <c r="F231" t="s">
         <v>690</v>
-      </c>
-      <c r="F231" t="s">
-        <v>691</v>
       </c>
       <c r="G231">
         <v>0</v>
@@ -43516,16 +43567,16 @@
         <v>0</v>
       </c>
       <c r="C232" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D232" t="s">
+        <v>691</v>
+      </c>
+      <c r="E232" t="s">
         <v>692</v>
       </c>
-      <c r="E232" t="s">
+      <c r="F232" t="s">
         <v>693</v>
-      </c>
-      <c r="F232" t="s">
-        <v>694</v>
       </c>
       <c r="G232">
         <v>0</v>
@@ -43573,16 +43624,16 @@
         <v>0</v>
       </c>
       <c r="C233" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D233" t="s">
+        <v>694</v>
+      </c>
+      <c r="E233" t="s">
         <v>695</v>
       </c>
-      <c r="E233" t="s">
-        <v>696</v>
-      </c>
       <c r="F233" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="G233">
         <v>0</v>
@@ -43630,16 +43681,16 @@
         <v>0</v>
       </c>
       <c r="C234" t="s">
+        <v>696</v>
+      </c>
+      <c r="D234" t="s">
         <v>697</v>
       </c>
-      <c r="D234" t="s">
+      <c r="E234" t="s">
         <v>698</v>
       </c>
-      <c r="E234" t="s">
+      <c r="F234" t="s">
         <v>699</v>
-      </c>
-      <c r="F234" t="s">
-        <v>700</v>
       </c>
       <c r="G234">
         <v>2</v>
@@ -43687,16 +43738,16 @@
         <v>0</v>
       </c>
       <c r="C235" t="s">
+        <v>700</v>
+      </c>
+      <c r="D235" t="s">
         <v>701</v>
       </c>
-      <c r="D235" t="s">
+      <c r="E235" t="s">
         <v>702</v>
       </c>
-      <c r="E235" t="s">
+      <c r="F235" t="s">
         <v>703</v>
-      </c>
-      <c r="F235" t="s">
-        <v>704</v>
       </c>
       <c r="G235">
         <v>10000</v>
@@ -43744,16 +43795,16 @@
         <v>0</v>
       </c>
       <c r="C236" t="s">
+        <v>704</v>
+      </c>
+      <c r="D236" t="s">
         <v>705</v>
       </c>
-      <c r="D236" t="s">
+      <c r="E236" t="s">
         <v>706</v>
       </c>
-      <c r="E236" t="s">
+      <c r="F236" t="s">
         <v>707</v>
-      </c>
-      <c r="F236" t="s">
-        <v>708</v>
       </c>
       <c r="G236">
         <v>20000</v>
@@ -43801,13 +43852,13 @@
         <v>0</v>
       </c>
       <c r="C237" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D237" t="s">
+        <v>708</v>
+      </c>
+      <c r="E237" t="s">
         <v>709</v>
-      </c>
-      <c r="E237" t="s">
-        <v>710</v>
       </c>
       <c r="F237">
         <v>0</v>
@@ -43858,16 +43909,16 @@
         <v>0</v>
       </c>
       <c r="C238" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D238" t="s">
+        <v>710</v>
+      </c>
+      <c r="E238" t="s">
         <v>711</v>
       </c>
-      <c r="E238" t="s">
+      <c r="F238" t="s">
         <v>712</v>
-      </c>
-      <c r="F238" t="s">
-        <v>713</v>
       </c>
       <c r="G238">
         <v>100</v>
@@ -43915,16 +43966,16 @@
         <v>0</v>
       </c>
       <c r="C239" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D239" t="s">
+        <v>713</v>
+      </c>
+      <c r="E239" t="s">
         <v>714</v>
       </c>
-      <c r="E239" t="s">
+      <c r="F239" t="s">
         <v>715</v>
-      </c>
-      <c r="F239" t="s">
-        <v>716</v>
       </c>
       <c r="G239">
         <v>10000</v>
@@ -43972,13 +44023,13 @@
         <v>0</v>
       </c>
       <c r="C240" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D240" t="s">
+        <v>716</v>
+      </c>
+      <c r="E240" t="s">
         <v>717</v>
-      </c>
-      <c r="E240" t="s">
-        <v>718</v>
       </c>
       <c r="F240">
         <v>0</v>
@@ -44029,16 +44080,16 @@
         <v>0</v>
       </c>
       <c r="C241" t="s">
+        <v>718</v>
+      </c>
+      <c r="D241" t="s">
         <v>719</v>
       </c>
-      <c r="D241" t="s">
+      <c r="E241" t="s">
         <v>720</v>
       </c>
-      <c r="E241" t="s">
+      <c r="F241" t="s">
         <v>721</v>
-      </c>
-      <c r="F241" t="s">
-        <v>722</v>
       </c>
       <c r="G241">
         <v>0.2</v>
@@ -44086,16 +44137,16 @@
         <v>0</v>
       </c>
       <c r="C242" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D242" t="s">
+        <v>722</v>
+      </c>
+      <c r="E242" t="s">
         <v>723</v>
       </c>
-      <c r="E242" t="s">
+      <c r="F242" t="s">
         <v>724</v>
-      </c>
-      <c r="F242" t="s">
-        <v>725</v>
       </c>
       <c r="G242">
         <v>2</v>
@@ -44143,16 +44194,16 @@
         <v>0</v>
       </c>
       <c r="C243" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D243" t="s">
+        <v>725</v>
+      </c>
+      <c r="E243" t="s">
         <v>726</v>
       </c>
-      <c r="E243" t="s">
+      <c r="F243" t="s">
         <v>727</v>
-      </c>
-      <c r="F243" t="s">
-        <v>728</v>
       </c>
       <c r="G243">
         <v>3</v>
@@ -44200,16 +44251,16 @@
         <v>0</v>
       </c>
       <c r="C244" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D244" t="s">
+        <v>728</v>
+      </c>
+      <c r="E244" t="s">
         <v>729</v>
       </c>
-      <c r="E244" t="s">
+      <c r="F244" t="s">
         <v>730</v>
-      </c>
-      <c r="F244" t="s">
-        <v>731</v>
       </c>
       <c r="G244">
         <v>3</v>
@@ -44257,16 +44308,16 @@
         <v>0</v>
       </c>
       <c r="C245" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D245" t="s">
+        <v>731</v>
+      </c>
+      <c r="E245" t="s">
         <v>732</v>
       </c>
-      <c r="E245" t="s">
+      <c r="F245" t="s">
         <v>733</v>
-      </c>
-      <c r="F245" t="s">
-        <v>734</v>
       </c>
       <c r="G245">
         <v>100</v>
@@ -44314,16 +44365,16 @@
         <v>0</v>
       </c>
       <c r="C246" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D246" t="s">
+        <v>734</v>
+      </c>
+      <c r="E246" t="s">
         <v>735</v>
       </c>
-      <c r="E246" t="s">
+      <c r="F246" t="s">
         <v>736</v>
-      </c>
-      <c r="F246" t="s">
-        <v>737</v>
       </c>
       <c r="G246">
         <v>9</v>
@@ -44371,16 +44422,16 @@
         <v>0</v>
       </c>
       <c r="C247" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D247" t="s">
+        <v>737</v>
+      </c>
+      <c r="E247" t="s">
         <v>738</v>
       </c>
-      <c r="E247" t="s">
+      <c r="F247" t="s">
         <v>739</v>
-      </c>
-      <c r="F247" t="s">
-        <v>740</v>
       </c>
       <c r="G247">
         <v>0.7</v>
@@ -44428,16 +44479,16 @@
         <v>0</v>
       </c>
       <c r="C248" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D248" t="s">
+        <v>740</v>
+      </c>
+      <c r="E248" t="s">
         <v>741</v>
       </c>
-      <c r="E248" t="s">
+      <c r="F248" t="s">
         <v>742</v>
-      </c>
-      <c r="F248" t="s">
-        <v>743</v>
       </c>
       <c r="G248">
         <v>0.7</v>
@@ -44485,16 +44536,16 @@
         <v>0</v>
       </c>
       <c r="C249" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D249" t="s">
+        <v>743</v>
+      </c>
+      <c r="E249" t="s">
         <v>744</v>
       </c>
-      <c r="E249" t="s">
+      <c r="F249" t="s">
         <v>745</v>
-      </c>
-      <c r="F249" t="s">
-        <v>746</v>
       </c>
       <c r="G249">
         <v>10</v>
@@ -44542,16 +44593,16 @@
         <v>0</v>
       </c>
       <c r="C250" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D250" t="s">
+        <v>746</v>
+      </c>
+      <c r="E250" t="s">
         <v>747</v>
       </c>
-      <c r="E250" t="s">
+      <c r="F250" t="s">
         <v>748</v>
-      </c>
-      <c r="F250" t="s">
-        <v>749</v>
       </c>
       <c r="G250">
         <v>0</v>
@@ -44599,16 +44650,16 @@
         <v>0</v>
       </c>
       <c r="C251" t="s">
+        <v>749</v>
+      </c>
+      <c r="D251" t="s">
         <v>750</v>
       </c>
-      <c r="D251" t="s">
+      <c r="E251" t="s">
         <v>751</v>
       </c>
-      <c r="E251" t="s">
+      <c r="F251" t="s">
         <v>752</v>
-      </c>
-      <c r="F251" t="s">
-        <v>753</v>
       </c>
       <c r="G251">
         <v>10000</v>
@@ -44656,16 +44707,16 @@
         <v>0</v>
       </c>
       <c r="C252" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D252" t="s">
+        <v>753</v>
+      </c>
+      <c r="E252" t="s">
         <v>754</v>
       </c>
-      <c r="E252" t="s">
+      <c r="F252" t="s">
         <v>755</v>
-      </c>
-      <c r="F252" t="s">
-        <v>756</v>
       </c>
       <c r="G252">
         <v>5000</v>
@@ -44713,13 +44764,13 @@
         <v>0</v>
       </c>
       <c r="C253" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D253" t="s">
+        <v>756</v>
+      </c>
+      <c r="E253" t="s">
         <v>757</v>
-      </c>
-      <c r="E253" t="s">
-        <v>758</v>
       </c>
       <c r="F253">
         <v>0</v>
@@ -44770,16 +44821,16 @@
         <v>0</v>
       </c>
       <c r="C254" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D254" t="s">
+        <v>758</v>
+      </c>
+      <c r="E254" t="s">
         <v>759</v>
       </c>
-      <c r="E254" t="s">
+      <c r="F254" t="s">
         <v>760</v>
-      </c>
-      <c r="F254" t="s">
-        <v>761</v>
       </c>
       <c r="G254">
         <v>10000</v>
@@ -44827,22 +44878,22 @@
         <v>0</v>
       </c>
       <c r="C255" t="s">
+        <v>761</v>
+      </c>
+      <c r="D255" t="s">
         <v>762</v>
       </c>
-      <c r="D255" t="s">
+      <c r="E255" t="s">
         <v>763</v>
       </c>
-      <c r="E255" t="s">
+      <c r="F255" t="s">
         <v>764</v>
       </c>
-      <c r="F255" t="s">
+      <c r="G255" t="s">
         <v>765</v>
       </c>
-      <c r="G255" t="s">
+      <c r="H255" t="s">
         <v>766</v>
-      </c>
-      <c r="H255" t="s">
-        <v>767</v>
       </c>
       <c r="I255">
         <v>0</v>
@@ -44884,25 +44935,25 @@
         <v>0</v>
       </c>
       <c r="C256" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D256" t="s">
+        <v>767</v>
+      </c>
+      <c r="E256" t="s">
+        <v>763</v>
+      </c>
+      <c r="F256" t="s">
+        <v>764</v>
+      </c>
+      <c r="G256" t="s">
+        <v>765</v>
+      </c>
+      <c r="H256" t="s">
         <v>768</v>
       </c>
-      <c r="E256" t="s">
-        <v>764</v>
-      </c>
-      <c r="F256" t="s">
-        <v>765</v>
-      </c>
-      <c r="G256" t="s">
-        <v>766</v>
-      </c>
-      <c r="H256" t="s">
+      <c r="I256" t="s">
         <v>769</v>
-      </c>
-      <c r="I256" t="s">
-        <v>770</v>
       </c>
       <c r="J256">
         <v>0</v>
@@ -44941,28 +44992,28 @@
         <v>0</v>
       </c>
       <c r="C257" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D257" t="s">
+        <v>770</v>
+      </c>
+      <c r="E257" t="s">
+        <v>763</v>
+      </c>
+      <c r="F257" t="s">
+        <v>764</v>
+      </c>
+      <c r="G257" t="s">
+        <v>765</v>
+      </c>
+      <c r="H257" t="s">
         <v>771</v>
       </c>
-      <c r="E257" t="s">
-        <v>764</v>
-      </c>
-      <c r="F257" t="s">
-        <v>765</v>
-      </c>
-      <c r="G257" t="s">
-        <v>766</v>
-      </c>
-      <c r="H257" t="s">
+      <c r="I257" t="s">
+        <v>769</v>
+      </c>
+      <c r="J257" t="s">
         <v>772</v>
-      </c>
-      <c r="I257" t="s">
-        <v>770</v>
-      </c>
-      <c r="J257" t="s">
-        <v>773</v>
       </c>
       <c r="K257">
         <v>0</v>
@@ -44998,28 +45049,28 @@
         <v>0</v>
       </c>
       <c r="C258" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D258" t="s">
+        <v>773</v>
+      </c>
+      <c r="E258" t="s">
+        <v>763</v>
+      </c>
+      <c r="F258" t="s">
+        <v>764</v>
+      </c>
+      <c r="G258" t="s">
         <v>774</v>
       </c>
-      <c r="E258" t="s">
-        <v>764</v>
-      </c>
-      <c r="F258" t="s">
-        <v>765</v>
-      </c>
-      <c r="G258" t="s">
+      <c r="H258" t="s">
+        <v>771</v>
+      </c>
+      <c r="I258" t="s">
         <v>775</v>
       </c>
-      <c r="H258" t="s">
+      <c r="J258" t="s">
         <v>772</v>
-      </c>
-      <c r="I258" t="s">
-        <v>776</v>
-      </c>
-      <c r="J258" t="s">
-        <v>773</v>
       </c>
       <c r="K258">
         <v>0</v>
@@ -45055,28 +45106,28 @@
         <v>0</v>
       </c>
       <c r="C259" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D259" t="s">
+        <v>776</v>
+      </c>
+      <c r="E259" t="s">
+        <v>763</v>
+      </c>
+      <c r="F259" t="s">
+        <v>764</v>
+      </c>
+      <c r="G259" t="s">
         <v>777</v>
       </c>
-      <c r="E259" t="s">
-        <v>764</v>
-      </c>
-      <c r="F259" t="s">
-        <v>765</v>
-      </c>
-      <c r="G259" t="s">
+      <c r="H259" t="s">
+        <v>771</v>
+      </c>
+      <c r="I259" t="s">
+        <v>775</v>
+      </c>
+      <c r="J259" t="s">
         <v>778</v>
-      </c>
-      <c r="H259" t="s">
-        <v>772</v>
-      </c>
-      <c r="I259" t="s">
-        <v>776</v>
-      </c>
-      <c r="J259" t="s">
-        <v>779</v>
       </c>
       <c r="K259">
         <v>0</v>
@@ -45112,31 +45163,31 @@
         <v>0</v>
       </c>
       <c r="C260" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D260" t="s">
+        <v>779</v>
+      </c>
+      <c r="E260" t="s">
+        <v>763</v>
+      </c>
+      <c r="F260" t="s">
+        <v>764</v>
+      </c>
+      <c r="G260" t="s">
         <v>780</v>
       </c>
-      <c r="E260" t="s">
-        <v>764</v>
-      </c>
-      <c r="F260" t="s">
-        <v>765</v>
-      </c>
-      <c r="G260" t="s">
+      <c r="H260" t="s">
+        <v>771</v>
+      </c>
+      <c r="I260" t="s">
+        <v>775</v>
+      </c>
+      <c r="J260" t="s">
+        <v>778</v>
+      </c>
+      <c r="K260" t="s">
         <v>781</v>
-      </c>
-      <c r="H260" t="s">
-        <v>772</v>
-      </c>
-      <c r="I260" t="s">
-        <v>776</v>
-      </c>
-      <c r="J260" t="s">
-        <v>779</v>
-      </c>
-      <c r="K260" t="s">
-        <v>782</v>
       </c>
       <c r="L260">
         <v>0</v>
@@ -45169,31 +45220,31 @@
         <v>0</v>
       </c>
       <c r="C261" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D261" t="s">
+        <v>782</v>
+      </c>
+      <c r="E261" t="s">
+        <v>763</v>
+      </c>
+      <c r="F261" t="s">
+        <v>764</v>
+      </c>
+      <c r="G261" t="s">
         <v>783</v>
       </c>
-      <c r="E261" t="s">
-        <v>764</v>
-      </c>
-      <c r="F261" t="s">
-        <v>765</v>
-      </c>
-      <c r="G261" t="s">
+      <c r="H261" t="s">
         <v>784</v>
       </c>
-      <c r="H261" t="s">
+      <c r="I261" t="s">
+        <v>778</v>
+      </c>
+      <c r="J261" t="s">
         <v>785</v>
       </c>
-      <c r="I261" t="s">
-        <v>779</v>
-      </c>
-      <c r="J261" t="s">
+      <c r="K261" t="s">
         <v>786</v>
-      </c>
-      <c r="K261" t="s">
-        <v>787</v>
       </c>
       <c r="L261">
         <v>0</v>
@@ -45226,31 +45277,31 @@
         <v>0</v>
       </c>
       <c r="C262" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D262" t="s">
+        <v>787</v>
+      </c>
+      <c r="E262" t="s">
+        <v>763</v>
+      </c>
+      <c r="F262" t="s">
+        <v>764</v>
+      </c>
+      <c r="G262" t="s">
+        <v>771</v>
+      </c>
+      <c r="H262" t="s">
+        <v>784</v>
+      </c>
+      <c r="I262" t="s">
+        <v>778</v>
+      </c>
+      <c r="J262" t="s">
+        <v>785</v>
+      </c>
+      <c r="K262" t="s">
         <v>788</v>
-      </c>
-      <c r="E262" t="s">
-        <v>764</v>
-      </c>
-      <c r="F262" t="s">
-        <v>765</v>
-      </c>
-      <c r="G262" t="s">
-        <v>772</v>
-      </c>
-      <c r="H262" t="s">
-        <v>785</v>
-      </c>
-      <c r="I262" t="s">
-        <v>779</v>
-      </c>
-      <c r="J262" t="s">
-        <v>786</v>
-      </c>
-      <c r="K262" t="s">
-        <v>789</v>
       </c>
       <c r="L262">
         <v>0</v>
@@ -45283,31 +45334,31 @@
         <v>0</v>
       </c>
       <c r="C263" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D263" t="s">
+        <v>789</v>
+      </c>
+      <c r="E263" t="s">
+        <v>763</v>
+      </c>
+      <c r="F263" t="s">
+        <v>764</v>
+      </c>
+      <c r="G263" t="s">
+        <v>784</v>
+      </c>
+      <c r="H263" t="s">
         <v>790</v>
       </c>
-      <c r="E263" t="s">
-        <v>764</v>
-      </c>
-      <c r="F263" t="s">
-        <v>765</v>
-      </c>
-      <c r="G263" t="s">
+      <c r="I263" t="s">
         <v>785</v>
       </c>
-      <c r="H263" t="s">
+      <c r="J263" t="s">
         <v>791</v>
       </c>
-      <c r="I263" t="s">
-        <v>786</v>
-      </c>
-      <c r="J263" t="s">
+      <c r="K263" t="s">
         <v>792</v>
-      </c>
-      <c r="K263" t="s">
-        <v>793</v>
       </c>
       <c r="L263">
         <v>0</v>
@@ -45340,31 +45391,31 @@
         <v>0</v>
       </c>
       <c r="C264" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D264" t="s">
+        <v>793</v>
+      </c>
+      <c r="E264" t="s">
+        <v>763</v>
+      </c>
+      <c r="F264" t="s">
+        <v>764</v>
+      </c>
+      <c r="G264" t="s">
+        <v>790</v>
+      </c>
+      <c r="H264" t="s">
         <v>794</v>
       </c>
-      <c r="E264" t="s">
-        <v>764</v>
-      </c>
-      <c r="F264" t="s">
-        <v>765</v>
-      </c>
-      <c r="G264" t="s">
+      <c r="I264" t="s">
         <v>791</v>
       </c>
-      <c r="H264" t="s">
+      <c r="J264" t="s">
         <v>795</v>
       </c>
-      <c r="I264" t="s">
-        <v>792</v>
-      </c>
-      <c r="J264" t="s">
+      <c r="K264" t="s">
         <v>796</v>
-      </c>
-      <c r="K264" t="s">
-        <v>797</v>
       </c>
       <c r="L264">
         <v>0</v>
@@ -45397,31 +45448,31 @@
         <v>0</v>
       </c>
       <c r="C265" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D265" t="s">
+        <v>797</v>
+      </c>
+      <c r="E265" t="s">
+        <v>763</v>
+      </c>
+      <c r="F265" t="s">
+        <v>764</v>
+      </c>
+      <c r="G265" t="s">
+        <v>794</v>
+      </c>
+      <c r="H265" t="s">
         <v>798</v>
       </c>
-      <c r="E265" t="s">
-        <v>764</v>
-      </c>
-      <c r="F265" t="s">
-        <v>765</v>
-      </c>
-      <c r="G265" t="s">
+      <c r="I265" t="s">
         <v>795</v>
       </c>
-      <c r="H265" t="s">
+      <c r="J265" t="s">
         <v>799</v>
       </c>
-      <c r="I265" t="s">
-        <v>796</v>
-      </c>
-      <c r="J265" t="s">
+      <c r="K265" t="s">
         <v>800</v>
-      </c>
-      <c r="K265" t="s">
-        <v>801</v>
       </c>
       <c r="L265">
         <v>0</v>
@@ -45454,31 +45505,31 @@
         <v>0</v>
       </c>
       <c r="C266" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D266" t="s">
+        <v>801</v>
+      </c>
+      <c r="E266" t="s">
+        <v>763</v>
+      </c>
+      <c r="F266" t="s">
+        <v>764</v>
+      </c>
+      <c r="G266" t="s">
+        <v>798</v>
+      </c>
+      <c r="H266" t="s">
         <v>802</v>
       </c>
-      <c r="E266" t="s">
-        <v>764</v>
-      </c>
-      <c r="F266" t="s">
-        <v>765</v>
-      </c>
-      <c r="G266" t="s">
+      <c r="I266" t="s">
         <v>799</v>
       </c>
-      <c r="H266" t="s">
+      <c r="J266" t="s">
         <v>803</v>
       </c>
-      <c r="I266" t="s">
-        <v>800</v>
-      </c>
-      <c r="J266" t="s">
+      <c r="K266" t="s">
         <v>804</v>
-      </c>
-      <c r="K266" t="s">
-        <v>805</v>
       </c>
       <c r="L266">
         <v>0</v>
@@ -45511,31 +45562,31 @@
         <v>0</v>
       </c>
       <c r="C267" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D267" t="s">
+        <v>805</v>
+      </c>
+      <c r="E267" t="s">
+        <v>763</v>
+      </c>
+      <c r="F267" t="s">
+        <v>764</v>
+      </c>
+      <c r="G267" t="s">
+        <v>802</v>
+      </c>
+      <c r="H267" t="s">
         <v>806</v>
       </c>
-      <c r="E267" t="s">
-        <v>764</v>
-      </c>
-      <c r="F267" t="s">
-        <v>765</v>
-      </c>
-      <c r="G267" t="s">
+      <c r="I267" t="s">
         <v>803</v>
       </c>
-      <c r="H267" t="s">
+      <c r="J267" t="s">
         <v>807</v>
       </c>
-      <c r="I267" t="s">
-        <v>804</v>
-      </c>
-      <c r="J267" t="s">
+      <c r="K267" t="s">
         <v>808</v>
-      </c>
-      <c r="K267" t="s">
-        <v>809</v>
       </c>
       <c r="L267">
         <v>0</v>
@@ -45568,31 +45619,31 @@
         <v>0</v>
       </c>
       <c r="C268" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D268" t="s">
+        <v>809</v>
+      </c>
+      <c r="E268" t="s">
+        <v>763</v>
+      </c>
+      <c r="F268" t="s">
+        <v>764</v>
+      </c>
+      <c r="G268" t="s">
+        <v>806</v>
+      </c>
+      <c r="H268" t="s">
         <v>810</v>
       </c>
-      <c r="E268" t="s">
-        <v>764</v>
-      </c>
-      <c r="F268" t="s">
-        <v>765</v>
-      </c>
-      <c r="G268" t="s">
+      <c r="I268" t="s">
         <v>807</v>
       </c>
-      <c r="H268" t="s">
+      <c r="J268" t="s">
         <v>811</v>
       </c>
-      <c r="I268" t="s">
-        <v>808</v>
-      </c>
-      <c r="J268" t="s">
+      <c r="K268" t="s">
         <v>812</v>
-      </c>
-      <c r="K268" t="s">
-        <v>813</v>
       </c>
       <c r="L268">
         <v>0</v>
@@ -45625,31 +45676,31 @@
         <v>0</v>
       </c>
       <c r="C269" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D269" t="s">
+        <v>813</v>
+      </c>
+      <c r="E269" t="s">
+        <v>763</v>
+      </c>
+      <c r="F269" t="s">
+        <v>764</v>
+      </c>
+      <c r="G269" t="s">
+        <v>810</v>
+      </c>
+      <c r="H269" t="s">
         <v>814</v>
       </c>
-      <c r="E269" t="s">
-        <v>764</v>
-      </c>
-      <c r="F269" t="s">
-        <v>765</v>
-      </c>
-      <c r="G269" t="s">
+      <c r="I269" t="s">
         <v>811</v>
       </c>
-      <c r="H269" t="s">
+      <c r="J269" t="s">
         <v>815</v>
       </c>
-      <c r="I269" t="s">
-        <v>812</v>
-      </c>
-      <c r="J269" t="s">
+      <c r="K269" t="s">
         <v>816</v>
-      </c>
-      <c r="K269" t="s">
-        <v>817</v>
       </c>
       <c r="L269">
         <v>0</v>
@@ -45682,31 +45733,31 @@
         <v>0</v>
       </c>
       <c r="C270" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D270" t="s">
+        <v>817</v>
+      </c>
+      <c r="E270" t="s">
+        <v>763</v>
+      </c>
+      <c r="F270" t="s">
+        <v>764</v>
+      </c>
+      <c r="G270" t="s">
+        <v>814</v>
+      </c>
+      <c r="H270" t="s">
         <v>818</v>
       </c>
-      <c r="E270" t="s">
-        <v>764</v>
-      </c>
-      <c r="F270" t="s">
-        <v>765</v>
-      </c>
-      <c r="G270" t="s">
+      <c r="I270" t="s">
         <v>815</v>
       </c>
-      <c r="H270" t="s">
+      <c r="J270" t="s">
         <v>819</v>
       </c>
-      <c r="I270" t="s">
-        <v>816</v>
-      </c>
-      <c r="J270" t="s">
+      <c r="K270" t="s">
         <v>820</v>
-      </c>
-      <c r="K270" t="s">
-        <v>821</v>
       </c>
       <c r="L270">
         <v>0</v>
@@ -45739,31 +45790,31 @@
         <v>0</v>
       </c>
       <c r="C271" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D271" t="s">
+        <v>821</v>
+      </c>
+      <c r="E271" t="s">
+        <v>763</v>
+      </c>
+      <c r="F271" t="s">
+        <v>764</v>
+      </c>
+      <c r="G271" t="s">
+        <v>818</v>
+      </c>
+      <c r="H271" t="s">
         <v>822</v>
       </c>
-      <c r="E271" t="s">
-        <v>764</v>
-      </c>
-      <c r="F271" t="s">
-        <v>765</v>
-      </c>
-      <c r="G271" t="s">
+      <c r="I271" t="s">
         <v>819</v>
       </c>
-      <c r="H271" t="s">
+      <c r="J271" t="s">
         <v>823</v>
       </c>
-      <c r="I271" t="s">
-        <v>820</v>
-      </c>
-      <c r="J271" t="s">
+      <c r="K271" t="s">
         <v>824</v>
-      </c>
-      <c r="K271" t="s">
-        <v>825</v>
       </c>
       <c r="L271">
         <v>0</v>
@@ -45796,34 +45847,34 @@
         <v>0</v>
       </c>
       <c r="C272" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D272" t="s">
+        <v>825</v>
+      </c>
+      <c r="E272" t="s">
+        <v>763</v>
+      </c>
+      <c r="F272" t="s">
+        <v>764</v>
+      </c>
+      <c r="G272" t="s">
+        <v>808</v>
+      </c>
+      <c r="H272" t="s">
         <v>826</v>
       </c>
-      <c r="E272" t="s">
-        <v>764</v>
-      </c>
-      <c r="F272" t="s">
-        <v>765</v>
-      </c>
-      <c r="G272" t="s">
-        <v>809</v>
-      </c>
-      <c r="H272" t="s">
+      <c r="I272" t="s">
         <v>827</v>
       </c>
-      <c r="I272" t="s">
+      <c r="J272" t="s">
+        <v>823</v>
+      </c>
+      <c r="K272" t="s">
         <v>828</v>
       </c>
-      <c r="J272" t="s">
-        <v>824</v>
-      </c>
-      <c r="K272" t="s">
+      <c r="L272" t="s">
         <v>829</v>
-      </c>
-      <c r="L272" t="s">
-        <v>830</v>
       </c>
       <c r="M272">
         <v>0</v>
@@ -45853,34 +45904,34 @@
         <v>0</v>
       </c>
       <c r="C273" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D273" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E273" t="s">
+        <v>763</v>
+      </c>
+      <c r="F273" t="s">
         <v>764</v>
       </c>
-      <c r="F273" t="s">
-        <v>765</v>
-      </c>
       <c r="G273" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H273" t="s">
+        <v>826</v>
+      </c>
+      <c r="I273" t="s">
         <v>827</v>
       </c>
-      <c r="I273" t="s">
+      <c r="J273" t="s">
+        <v>823</v>
+      </c>
+      <c r="K273" t="s">
         <v>828</v>
       </c>
-      <c r="J273" t="s">
-        <v>824</v>
-      </c>
-      <c r="K273" t="s">
+      <c r="L273" t="s">
         <v>829</v>
-      </c>
-      <c r="L273" t="s">
-        <v>830</v>
       </c>
       <c r="M273">
         <v>0</v>
@@ -45910,34 +45961,34 @@
         <v>0</v>
       </c>
       <c r="C274" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D274" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E274" t="s">
+        <v>763</v>
+      </c>
+      <c r="F274" t="s">
         <v>764</v>
       </c>
-      <c r="F274" t="s">
-        <v>765</v>
-      </c>
       <c r="G274" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H274" t="s">
+        <v>826</v>
+      </c>
+      <c r="I274" t="s">
         <v>827</v>
       </c>
-      <c r="I274" t="s">
+      <c r="J274" t="s">
+        <v>823</v>
+      </c>
+      <c r="K274" t="s">
         <v>828</v>
       </c>
-      <c r="J274" t="s">
-        <v>824</v>
-      </c>
-      <c r="K274" t="s">
+      <c r="L274" t="s">
         <v>829</v>
-      </c>
-      <c r="L274" t="s">
-        <v>830</v>
       </c>
       <c r="M274">
         <v>0</v>
@@ -45967,28 +46018,28 @@
         <v>0</v>
       </c>
       <c r="C275" t="s">
+        <v>832</v>
+      </c>
+      <c r="D275" t="s">
+        <v>762</v>
+      </c>
+      <c r="E275" t="s">
         <v>833</v>
       </c>
-      <c r="D275" t="s">
-        <v>763</v>
-      </c>
-      <c r="E275" t="s">
+      <c r="F275" t="s">
         <v>834</v>
       </c>
-      <c r="F275" t="s">
+      <c r="G275" t="s">
         <v>835</v>
       </c>
-      <c r="G275" t="s">
+      <c r="H275" t="s">
         <v>836</v>
       </c>
-      <c r="H275" t="s">
+      <c r="I275" t="s">
         <v>837</v>
       </c>
-      <c r="I275" t="s">
+      <c r="J275" t="s">
         <v>838</v>
-      </c>
-      <c r="J275" t="s">
-        <v>839</v>
       </c>
       <c r="K275">
         <v>0</v>
@@ -46024,28 +46075,28 @@
         <v>0</v>
       </c>
       <c r="C276" t="s">
+        <v>832</v>
+      </c>
+      <c r="D276" t="s">
+        <v>767</v>
+      </c>
+      <c r="E276" t="s">
         <v>833</v>
       </c>
-      <c r="D276" t="s">
-        <v>768</v>
-      </c>
-      <c r="E276" t="s">
+      <c r="F276" t="s">
         <v>834</v>
       </c>
-      <c r="F276" t="s">
-        <v>835</v>
-      </c>
       <c r="G276" t="s">
+        <v>839</v>
+      </c>
+      <c r="H276" t="s">
+        <v>836</v>
+      </c>
+      <c r="I276" t="s">
         <v>840</v>
       </c>
-      <c r="H276" t="s">
-        <v>837</v>
-      </c>
-      <c r="I276" t="s">
+      <c r="J276" t="s">
         <v>841</v>
-      </c>
-      <c r="J276" t="s">
-        <v>842</v>
       </c>
       <c r="K276">
         <v>0</v>
@@ -46081,28 +46132,28 @@
         <v>0</v>
       </c>
       <c r="C277" t="s">
+        <v>832</v>
+      </c>
+      <c r="D277" t="s">
+        <v>770</v>
+      </c>
+      <c r="E277" t="s">
         <v>833</v>
       </c>
-      <c r="D277" t="s">
-        <v>771</v>
-      </c>
-      <c r="E277" t="s">
+      <c r="F277" t="s">
         <v>834</v>
       </c>
-      <c r="F277" t="s">
-        <v>835</v>
-      </c>
       <c r="G277" t="s">
+        <v>842</v>
+      </c>
+      <c r="H277" t="s">
+        <v>836</v>
+      </c>
+      <c r="I277" t="s">
         <v>843</v>
       </c>
-      <c r="H277" t="s">
-        <v>837</v>
-      </c>
-      <c r="I277" t="s">
+      <c r="J277" t="s">
         <v>844</v>
-      </c>
-      <c r="J277" t="s">
-        <v>845</v>
       </c>
       <c r="K277">
         <v>0</v>
@@ -46138,31 +46189,31 @@
         <v>0</v>
       </c>
       <c r="C278" t="s">
+        <v>832</v>
+      </c>
+      <c r="D278" t="s">
+        <v>773</v>
+      </c>
+      <c r="E278" t="s">
         <v>833</v>
       </c>
-      <c r="D278" t="s">
-        <v>774</v>
-      </c>
-      <c r="E278" t="s">
+      <c r="F278" t="s">
         <v>834</v>
       </c>
-      <c r="F278" t="s">
-        <v>835</v>
-      </c>
       <c r="G278" t="s">
+        <v>845</v>
+      </c>
+      <c r="H278" t="s">
+        <v>836</v>
+      </c>
+      <c r="I278" t="s">
+        <v>843</v>
+      </c>
+      <c r="J278" t="s">
+        <v>844</v>
+      </c>
+      <c r="K278" t="s">
         <v>846</v>
-      </c>
-      <c r="H278" t="s">
-        <v>837</v>
-      </c>
-      <c r="I278" t="s">
-        <v>844</v>
-      </c>
-      <c r="J278" t="s">
-        <v>845</v>
-      </c>
-      <c r="K278" t="s">
-        <v>847</v>
       </c>
       <c r="L278">
         <v>0</v>
@@ -46195,31 +46246,31 @@
         <v>0</v>
       </c>
       <c r="C279" t="s">
+        <v>832</v>
+      </c>
+      <c r="D279" t="s">
+        <v>776</v>
+      </c>
+      <c r="E279" t="s">
         <v>833</v>
       </c>
-      <c r="D279" t="s">
-        <v>777</v>
-      </c>
-      <c r="E279" t="s">
+      <c r="F279" t="s">
         <v>834</v>
       </c>
-      <c r="F279" t="s">
-        <v>835</v>
-      </c>
       <c r="G279" t="s">
+        <v>847</v>
+      </c>
+      <c r="H279" t="s">
+        <v>836</v>
+      </c>
+      <c r="I279" t="s">
+        <v>843</v>
+      </c>
+      <c r="J279" t="s">
         <v>848</v>
       </c>
-      <c r="H279" t="s">
-        <v>837</v>
-      </c>
-      <c r="I279" t="s">
-        <v>844</v>
-      </c>
-      <c r="J279" t="s">
+      <c r="K279" t="s">
         <v>849</v>
-      </c>
-      <c r="K279" t="s">
-        <v>850</v>
       </c>
       <c r="L279">
         <v>0</v>
@@ -46252,31 +46303,31 @@
         <v>0</v>
       </c>
       <c r="C280" t="s">
+        <v>832</v>
+      </c>
+      <c r="D280" t="s">
+        <v>779</v>
+      </c>
+      <c r="E280" t="s">
         <v>833</v>
       </c>
-      <c r="D280" t="s">
-        <v>780</v>
-      </c>
-      <c r="E280" t="s">
+      <c r="F280" t="s">
         <v>834</v>
       </c>
-      <c r="F280" t="s">
-        <v>835</v>
-      </c>
       <c r="G280" t="s">
+        <v>850</v>
+      </c>
+      <c r="H280" t="s">
+        <v>836</v>
+      </c>
+      <c r="I280" t="s">
+        <v>843</v>
+      </c>
+      <c r="J280" t="s">
         <v>851</v>
       </c>
-      <c r="H280" t="s">
-        <v>837</v>
-      </c>
-      <c r="I280" t="s">
-        <v>844</v>
-      </c>
-      <c r="J280" t="s">
+      <c r="K280" t="s">
         <v>852</v>
-      </c>
-      <c r="K280" t="s">
-        <v>853</v>
       </c>
       <c r="L280">
         <v>0</v>
@@ -46309,31 +46360,31 @@
         <v>0</v>
       </c>
       <c r="C281" t="s">
+        <v>832</v>
+      </c>
+      <c r="D281" t="s">
+        <v>782</v>
+      </c>
+      <c r="E281" t="s">
         <v>833</v>
       </c>
-      <c r="D281" t="s">
-        <v>783</v>
-      </c>
-      <c r="E281" t="s">
+      <c r="F281" t="s">
         <v>834</v>
       </c>
-      <c r="F281" t="s">
-        <v>835</v>
-      </c>
       <c r="G281" t="s">
+        <v>853</v>
+      </c>
+      <c r="H281" t="s">
+        <v>836</v>
+      </c>
+      <c r="I281" t="s">
         <v>854</v>
       </c>
-      <c r="H281" t="s">
-        <v>837</v>
-      </c>
-      <c r="I281" t="s">
+      <c r="J281" t="s">
         <v>855</v>
       </c>
-      <c r="J281" t="s">
+      <c r="K281" t="s">
         <v>856</v>
-      </c>
-      <c r="K281" t="s">
-        <v>857</v>
       </c>
       <c r="L281">
         <v>0</v>
@@ -46366,31 +46417,31 @@
         <v>0</v>
       </c>
       <c r="C282" t="s">
+        <v>832</v>
+      </c>
+      <c r="D282" t="s">
+        <v>787</v>
+      </c>
+      <c r="E282" t="s">
         <v>833</v>
       </c>
-      <c r="D282" t="s">
-        <v>788</v>
-      </c>
-      <c r="E282" t="s">
+      <c r="F282" t="s">
         <v>834</v>
       </c>
-      <c r="F282" t="s">
-        <v>835</v>
-      </c>
       <c r="G282" t="s">
+        <v>857</v>
+      </c>
+      <c r="H282" t="s">
+        <v>836</v>
+      </c>
+      <c r="I282" t="s">
         <v>858</v>
       </c>
-      <c r="H282" t="s">
-        <v>837</v>
-      </c>
-      <c r="I282" t="s">
+      <c r="J282" t="s">
         <v>859</v>
       </c>
-      <c r="J282" t="s">
+      <c r="K282" t="s">
         <v>860</v>
-      </c>
-      <c r="K282" t="s">
-        <v>861</v>
       </c>
       <c r="L282">
         <v>0</v>
@@ -46423,31 +46474,31 @@
         <v>0</v>
       </c>
       <c r="C283" t="s">
+        <v>832</v>
+      </c>
+      <c r="D283" t="s">
+        <v>789</v>
+      </c>
+      <c r="E283" t="s">
         <v>833</v>
       </c>
-      <c r="D283" t="s">
-        <v>790</v>
-      </c>
-      <c r="E283" t="s">
+      <c r="F283" t="s">
         <v>834</v>
       </c>
-      <c r="F283" t="s">
-        <v>835</v>
-      </c>
       <c r="G283" t="s">
+        <v>861</v>
+      </c>
+      <c r="H283" t="s">
+        <v>836</v>
+      </c>
+      <c r="I283" t="s">
         <v>862</v>
       </c>
-      <c r="H283" t="s">
-        <v>837</v>
-      </c>
-      <c r="I283" t="s">
+      <c r="J283" t="s">
         <v>863</v>
       </c>
-      <c r="J283" t="s">
+      <c r="K283" t="s">
         <v>864</v>
-      </c>
-      <c r="K283" t="s">
-        <v>865</v>
       </c>
       <c r="L283">
         <v>0</v>
@@ -46480,34 +46531,34 @@
         <v>0</v>
       </c>
       <c r="C284" t="s">
+        <v>832</v>
+      </c>
+      <c r="D284" t="s">
+        <v>793</v>
+      </c>
+      <c r="E284" t="s">
         <v>833</v>
       </c>
-      <c r="D284" t="s">
-        <v>794</v>
-      </c>
-      <c r="E284" t="s">
+      <c r="F284" t="s">
         <v>834</v>
       </c>
-      <c r="F284" t="s">
-        <v>835</v>
-      </c>
       <c r="G284" t="s">
+        <v>865</v>
+      </c>
+      <c r="H284" t="s">
+        <v>836</v>
+      </c>
+      <c r="I284" t="s">
+        <v>862</v>
+      </c>
+      <c r="J284" t="s">
+        <v>863</v>
+      </c>
+      <c r="K284" t="s">
         <v>866</v>
       </c>
-      <c r="H284" t="s">
-        <v>837</v>
-      </c>
-      <c r="I284" t="s">
-        <v>863</v>
-      </c>
-      <c r="J284" t="s">
-        <v>864</v>
-      </c>
-      <c r="K284" t="s">
+      <c r="L284" t="s">
         <v>867</v>
-      </c>
-      <c r="L284" t="s">
-        <v>868</v>
       </c>
       <c r="M284">
         <v>0</v>
@@ -46537,34 +46588,34 @@
         <v>0</v>
       </c>
       <c r="C285" t="s">
+        <v>832</v>
+      </c>
+      <c r="D285" t="s">
+        <v>797</v>
+      </c>
+      <c r="E285" t="s">
         <v>833</v>
       </c>
-      <c r="D285" t="s">
-        <v>798</v>
-      </c>
-      <c r="E285" t="s">
+      <c r="F285" t="s">
         <v>834</v>
       </c>
-      <c r="F285" t="s">
-        <v>835</v>
-      </c>
       <c r="G285" t="s">
+        <v>868</v>
+      </c>
+      <c r="H285" t="s">
+        <v>836</v>
+      </c>
+      <c r="I285" t="s">
+        <v>862</v>
+      </c>
+      <c r="J285" t="s">
+        <v>863</v>
+      </c>
+      <c r="K285" t="s">
         <v>869</v>
       </c>
-      <c r="H285" t="s">
-        <v>837</v>
-      </c>
-      <c r="I285" t="s">
-        <v>863</v>
-      </c>
-      <c r="J285" t="s">
-        <v>864</v>
-      </c>
-      <c r="K285" t="s">
+      <c r="L285" t="s">
         <v>870</v>
-      </c>
-      <c r="L285" t="s">
-        <v>871</v>
       </c>
       <c r="M285">
         <v>0</v>
@@ -46594,34 +46645,34 @@
         <v>0</v>
       </c>
       <c r="C286" t="s">
+        <v>832</v>
+      </c>
+      <c r="D286" t="s">
+        <v>801</v>
+      </c>
+      <c r="E286" t="s">
         <v>833</v>
       </c>
-      <c r="D286" t="s">
-        <v>802</v>
-      </c>
-      <c r="E286" t="s">
+      <c r="F286" t="s">
         <v>834</v>
       </c>
-      <c r="F286" t="s">
-        <v>835</v>
-      </c>
       <c r="G286" t="s">
+        <v>871</v>
+      </c>
+      <c r="H286" t="s">
+        <v>836</v>
+      </c>
+      <c r="I286" t="s">
         <v>872</v>
       </c>
-      <c r="H286" t="s">
-        <v>837</v>
-      </c>
-      <c r="I286" t="s">
+      <c r="J286" t="s">
         <v>873</v>
       </c>
-      <c r="J286" t="s">
+      <c r="K286" t="s">
         <v>874</v>
       </c>
-      <c r="K286" t="s">
+      <c r="L286" t="s">
         <v>875</v>
-      </c>
-      <c r="L286" t="s">
-        <v>876</v>
       </c>
       <c r="M286">
         <v>0</v>
@@ -46651,34 +46702,34 @@
         <v>0</v>
       </c>
       <c r="C287" t="s">
+        <v>832</v>
+      </c>
+      <c r="D287" t="s">
+        <v>805</v>
+      </c>
+      <c r="E287" t="s">
         <v>833</v>
       </c>
-      <c r="D287" t="s">
-        <v>806</v>
-      </c>
-      <c r="E287" t="s">
+      <c r="F287" t="s">
         <v>834</v>
       </c>
-      <c r="F287" t="s">
-        <v>835</v>
-      </c>
       <c r="G287" t="s">
+        <v>876</v>
+      </c>
+      <c r="H287" t="s">
+        <v>836</v>
+      </c>
+      <c r="I287" t="s">
+        <v>872</v>
+      </c>
+      <c r="J287" t="s">
+        <v>873</v>
+      </c>
+      <c r="K287" t="s">
+        <v>874</v>
+      </c>
+      <c r="L287" t="s">
         <v>877</v>
-      </c>
-      <c r="H287" t="s">
-        <v>837</v>
-      </c>
-      <c r="I287" t="s">
-        <v>873</v>
-      </c>
-      <c r="J287" t="s">
-        <v>874</v>
-      </c>
-      <c r="K287" t="s">
-        <v>875</v>
-      </c>
-      <c r="L287" t="s">
-        <v>878</v>
       </c>
       <c r="M287">
         <v>0</v>
@@ -46708,34 +46759,34 @@
         <v>0</v>
       </c>
       <c r="C288" t="s">
+        <v>832</v>
+      </c>
+      <c r="D288" t="s">
+        <v>809</v>
+      </c>
+      <c r="E288" t="s">
         <v>833</v>
       </c>
-      <c r="D288" t="s">
-        <v>810</v>
-      </c>
-      <c r="E288" t="s">
+      <c r="F288" t="s">
         <v>834</v>
       </c>
-      <c r="F288" t="s">
-        <v>835</v>
-      </c>
       <c r="G288" t="s">
+        <v>878</v>
+      </c>
+      <c r="H288" t="s">
+        <v>836</v>
+      </c>
+      <c r="I288" t="s">
+        <v>872</v>
+      </c>
+      <c r="J288" t="s">
+        <v>873</v>
+      </c>
+      <c r="K288" t="s">
+        <v>874</v>
+      </c>
+      <c r="L288" t="s">
         <v>879</v>
-      </c>
-      <c r="H288" t="s">
-        <v>837</v>
-      </c>
-      <c r="I288" t="s">
-        <v>873</v>
-      </c>
-      <c r="J288" t="s">
-        <v>874</v>
-      </c>
-      <c r="K288" t="s">
-        <v>875</v>
-      </c>
-      <c r="L288" t="s">
-        <v>880</v>
       </c>
       <c r="M288">
         <v>0</v>
@@ -46765,37 +46816,37 @@
         <v>0</v>
       </c>
       <c r="C289" t="s">
+        <v>832</v>
+      </c>
+      <c r="D289" t="s">
+        <v>813</v>
+      </c>
+      <c r="E289" t="s">
         <v>833</v>
       </c>
-      <c r="D289" t="s">
-        <v>814</v>
-      </c>
-      <c r="E289" t="s">
+      <c r="F289" t="s">
         <v>834</v>
       </c>
-      <c r="F289" t="s">
-        <v>835</v>
-      </c>
       <c r="G289" t="s">
+        <v>880</v>
+      </c>
+      <c r="H289" t="s">
+        <v>836</v>
+      </c>
+      <c r="I289" t="s">
+        <v>872</v>
+      </c>
+      <c r="J289" t="s">
         <v>881</v>
       </c>
-      <c r="H289" t="s">
-        <v>837</v>
-      </c>
-      <c r="I289" t="s">
-        <v>873</v>
-      </c>
-      <c r="J289" t="s">
+      <c r="K289" t="s">
         <v>882</v>
       </c>
-      <c r="K289" t="s">
+      <c r="L289" t="s">
+        <v>875</v>
+      </c>
+      <c r="M289" t="s">
         <v>883</v>
-      </c>
-      <c r="L289" t="s">
-        <v>876</v>
-      </c>
-      <c r="M289" t="s">
-        <v>884</v>
       </c>
       <c r="N289">
         <v>0</v>
@@ -46822,37 +46873,37 @@
         <v>0</v>
       </c>
       <c r="C290" t="s">
+        <v>832</v>
+      </c>
+      <c r="D290" t="s">
+        <v>817</v>
+      </c>
+      <c r="E290" t="s">
         <v>833</v>
       </c>
-      <c r="D290" t="s">
-        <v>818</v>
-      </c>
-      <c r="E290" t="s">
+      <c r="F290" t="s">
         <v>834</v>
       </c>
-      <c r="F290" t="s">
-        <v>835</v>
-      </c>
       <c r="G290" t="s">
+        <v>884</v>
+      </c>
+      <c r="H290" t="s">
+        <v>836</v>
+      </c>
+      <c r="I290" t="s">
+        <v>872</v>
+      </c>
+      <c r="J290" t="s">
+        <v>881</v>
+      </c>
+      <c r="K290" t="s">
+        <v>882</v>
+      </c>
+      <c r="L290" t="s">
+        <v>877</v>
+      </c>
+      <c r="M290" t="s">
         <v>885</v>
-      </c>
-      <c r="H290" t="s">
-        <v>837</v>
-      </c>
-      <c r="I290" t="s">
-        <v>873</v>
-      </c>
-      <c r="J290" t="s">
-        <v>882</v>
-      </c>
-      <c r="K290" t="s">
-        <v>883</v>
-      </c>
-      <c r="L290" t="s">
-        <v>878</v>
-      </c>
-      <c r="M290" t="s">
-        <v>886</v>
       </c>
       <c r="N290">
         <v>0</v>
@@ -46879,37 +46930,37 @@
         <v>0</v>
       </c>
       <c r="C291" t="s">
+        <v>832</v>
+      </c>
+      <c r="D291" t="s">
+        <v>821</v>
+      </c>
+      <c r="E291" t="s">
         <v>833</v>
       </c>
-      <c r="D291" t="s">
-        <v>822</v>
-      </c>
-      <c r="E291" t="s">
+      <c r="F291" t="s">
         <v>834</v>
       </c>
-      <c r="F291" t="s">
-        <v>835</v>
-      </c>
       <c r="G291" t="s">
+        <v>886</v>
+      </c>
+      <c r="H291" t="s">
+        <v>836</v>
+      </c>
+      <c r="I291" t="s">
+        <v>872</v>
+      </c>
+      <c r="J291" t="s">
+        <v>881</v>
+      </c>
+      <c r="K291" t="s">
+        <v>882</v>
+      </c>
+      <c r="L291" t="s">
+        <v>877</v>
+      </c>
+      <c r="M291" t="s">
         <v>887</v>
-      </c>
-      <c r="H291" t="s">
-        <v>837</v>
-      </c>
-      <c r="I291" t="s">
-        <v>873</v>
-      </c>
-      <c r="J291" t="s">
-        <v>882</v>
-      </c>
-      <c r="K291" t="s">
-        <v>883</v>
-      </c>
-      <c r="L291" t="s">
-        <v>878</v>
-      </c>
-      <c r="M291" t="s">
-        <v>888</v>
       </c>
       <c r="N291">
         <v>0</v>
@@ -46936,40 +46987,40 @@
         <v>0</v>
       </c>
       <c r="C292" t="s">
+        <v>832</v>
+      </c>
+      <c r="D292" t="s">
+        <v>825</v>
+      </c>
+      <c r="E292" t="s">
         <v>833</v>
       </c>
-      <c r="D292" t="s">
-        <v>826</v>
-      </c>
-      <c r="E292" t="s">
+      <c r="F292" t="s">
         <v>834</v>
       </c>
-      <c r="F292" t="s">
-        <v>835</v>
-      </c>
       <c r="G292" t="s">
+        <v>888</v>
+      </c>
+      <c r="H292" t="s">
+        <v>836</v>
+      </c>
+      <c r="I292" t="s">
+        <v>872</v>
+      </c>
+      <c r="J292" t="s">
+        <v>881</v>
+      </c>
+      <c r="K292" t="s">
+        <v>882</v>
+      </c>
+      <c r="L292" t="s">
+        <v>877</v>
+      </c>
+      <c r="M292" t="s">
+        <v>887</v>
+      </c>
+      <c r="N292" t="s">
         <v>889</v>
-      </c>
-      <c r="H292" t="s">
-        <v>837</v>
-      </c>
-      <c r="I292" t="s">
-        <v>873</v>
-      </c>
-      <c r="J292" t="s">
-        <v>882</v>
-      </c>
-      <c r="K292" t="s">
-        <v>883</v>
-      </c>
-      <c r="L292" t="s">
-        <v>878</v>
-      </c>
-      <c r="M292" t="s">
-        <v>888</v>
-      </c>
-      <c r="N292" t="s">
-        <v>890</v>
       </c>
       <c r="O292">
         <v>0</v>
@@ -46993,43 +47044,43 @@
         <v>0</v>
       </c>
       <c r="C293" t="s">
+        <v>832</v>
+      </c>
+      <c r="D293" t="s">
+        <v>830</v>
+      </c>
+      <c r="E293" t="s">
         <v>833</v>
       </c>
-      <c r="D293" t="s">
-        <v>831</v>
-      </c>
-      <c r="E293" t="s">
+      <c r="F293" t="s">
         <v>834</v>
       </c>
-      <c r="F293" t="s">
-        <v>835</v>
-      </c>
       <c r="G293" t="s">
+        <v>890</v>
+      </c>
+      <c r="H293" t="s">
+        <v>836</v>
+      </c>
+      <c r="I293" t="s">
+        <v>872</v>
+      </c>
+      <c r="J293" t="s">
+        <v>881</v>
+      </c>
+      <c r="K293" t="s">
+        <v>882</v>
+      </c>
+      <c r="L293" t="s">
+        <v>877</v>
+      </c>
+      <c r="M293" t="s">
+        <v>887</v>
+      </c>
+      <c r="N293" t="s">
         <v>891</v>
       </c>
-      <c r="H293" t="s">
-        <v>837</v>
-      </c>
-      <c r="I293" t="s">
-        <v>873</v>
-      </c>
-      <c r="J293" t="s">
-        <v>882</v>
-      </c>
-      <c r="K293" t="s">
-        <v>883</v>
-      </c>
-      <c r="L293" t="s">
-        <v>878</v>
-      </c>
-      <c r="M293" t="s">
-        <v>888</v>
-      </c>
-      <c r="N293" t="s">
+      <c r="O293" t="s">
         <v>892</v>
-      </c>
-      <c r="O293" t="s">
-        <v>893</v>
       </c>
       <c r="P293">
         <v>0</v>
@@ -47050,46 +47101,46 @@
         <v>0</v>
       </c>
       <c r="C294" t="s">
+        <v>832</v>
+      </c>
+      <c r="D294" t="s">
+        <v>831</v>
+      </c>
+      <c r="E294" t="s">
         <v>833</v>
       </c>
-      <c r="D294" t="s">
-        <v>832</v>
-      </c>
-      <c r="E294" t="s">
+      <c r="F294" t="s">
         <v>834</v>
       </c>
-      <c r="F294" t="s">
-        <v>835</v>
-      </c>
       <c r="G294" t="s">
+        <v>893</v>
+      </c>
+      <c r="H294" t="s">
+        <v>836</v>
+      </c>
+      <c r="I294" t="s">
+        <v>872</v>
+      </c>
+      <c r="J294" t="s">
+        <v>881</v>
+      </c>
+      <c r="K294" t="s">
+        <v>882</v>
+      </c>
+      <c r="L294" t="s">
+        <v>877</v>
+      </c>
+      <c r="M294" t="s">
+        <v>887</v>
+      </c>
+      <c r="N294" t="s">
         <v>894</v>
       </c>
-      <c r="H294" t="s">
-        <v>837</v>
-      </c>
-      <c r="I294" t="s">
-        <v>873</v>
-      </c>
-      <c r="J294" t="s">
-        <v>882</v>
-      </c>
-      <c r="K294" t="s">
-        <v>883</v>
-      </c>
-      <c r="L294" t="s">
-        <v>878</v>
-      </c>
-      <c r="M294" t="s">
-        <v>888</v>
-      </c>
-      <c r="N294" t="s">
+      <c r="O294" t="s">
         <v>895</v>
       </c>
-      <c r="O294" t="s">
+      <c r="P294" t="s">
         <v>896</v>
-      </c>
-      <c r="P294" t="s">
-        <v>897</v>
       </c>
       <c r="Q294">
         <v>0</v>
@@ -47107,16 +47158,16 @@
         <v>0</v>
       </c>
       <c r="C295" t="s">
+        <v>897</v>
+      </c>
+      <c r="D295" t="s">
         <v>898</v>
       </c>
-      <c r="D295" t="s">
+      <c r="E295" t="s">
         <v>899</v>
       </c>
-      <c r="E295" t="s">
+      <c r="F295" t="s">
         <v>900</v>
-      </c>
-      <c r="F295" t="s">
-        <v>901</v>
       </c>
       <c r="G295">
         <v>0</v>
@@ -47164,16 +47215,16 @@
         <v>0</v>
       </c>
       <c r="C296" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D296" t="s">
+        <v>901</v>
+      </c>
+      <c r="E296" t="s">
         <v>902</v>
       </c>
-      <c r="E296" t="s">
+      <c r="F296" t="s">
         <v>903</v>
-      </c>
-      <c r="F296" t="s">
-        <v>904</v>
       </c>
       <c r="G296">
         <v>0.1</v>
@@ -47221,16 +47272,16 @@
         <v>0</v>
       </c>
       <c r="C297" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D297" t="s">
+        <v>904</v>
+      </c>
+      <c r="E297" t="s">
         <v>905</v>
       </c>
-      <c r="E297" t="s">
+      <c r="F297" t="s">
         <v>906</v>
-      </c>
-      <c r="F297" t="s">
-        <v>907</v>
       </c>
       <c r="G297">
         <v>0</v>
@@ -47278,16 +47329,16 @@
         <v>0</v>
       </c>
       <c r="C298" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D298" t="s">
+        <v>907</v>
+      </c>
+      <c r="E298" t="s">
         <v>908</v>
       </c>
-      <c r="E298" t="s">
+      <c r="F298" t="s">
         <v>909</v>
-      </c>
-      <c r="F298" t="s">
-        <v>910</v>
       </c>
       <c r="G298">
         <v>0</v>
@@ -47335,16 +47386,16 @@
         <v>0</v>
       </c>
       <c r="C299" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D299" t="s">
+        <v>910</v>
+      </c>
+      <c r="E299" t="s">
         <v>911</v>
       </c>
-      <c r="E299" t="s">
+      <c r="F299" t="s">
         <v>912</v>
-      </c>
-      <c r="F299" t="s">
-        <v>913</v>
       </c>
       <c r="G299">
         <v>0</v>
@@ -47392,16 +47443,16 @@
         <v>0</v>
       </c>
       <c r="C300" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D300" t="s">
+        <v>913</v>
+      </c>
+      <c r="E300" t="s">
         <v>914</v>
       </c>
-      <c r="E300" t="s">
+      <c r="F300" t="s">
         <v>915</v>
-      </c>
-      <c r="F300" t="s">
-        <v>916</v>
       </c>
       <c r="G300">
         <v>0.4</v>
@@ -47449,16 +47500,16 @@
         <v>0</v>
       </c>
       <c r="C301" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D301" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F301" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="G301">
         <v>1000</v>
@@ -47506,16 +47557,16 @@
         <v>0</v>
       </c>
       <c r="C302" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D302" t="s">
+        <v>917</v>
+      </c>
+      <c r="E302" t="s">
         <v>918</v>
       </c>
-      <c r="E302" t="s">
+      <c r="F302" t="s">
         <v>919</v>
-      </c>
-      <c r="F302" t="s">
-        <v>920</v>
       </c>
       <c r="G302">
         <v>0</v>
@@ -47563,16 +47614,16 @@
         <v>0</v>
       </c>
       <c r="C303" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D303" t="s">
+        <v>920</v>
+      </c>
+      <c r="E303" t="s">
         <v>921</v>
       </c>
-      <c r="E303" t="s">
+      <c r="F303" t="s">
         <v>922</v>
-      </c>
-      <c r="F303" t="s">
-        <v>923</v>
       </c>
       <c r="G303">
         <v>30</v>
@@ -47620,16 +47671,16 @@
         <v>0</v>
       </c>
       <c r="C304" t="s">
+        <v>923</v>
+      </c>
+      <c r="D304" t="s">
         <v>924</v>
       </c>
-      <c r="D304" t="s">
+      <c r="E304" t="s">
         <v>925</v>
       </c>
-      <c r="E304" t="s">
+      <c r="F304" t="s">
         <v>926</v>
-      </c>
-      <c r="F304" t="s">
-        <v>927</v>
       </c>
       <c r="G304">
         <v>0.75</v>
@@ -47677,13 +47728,13 @@
         <v>0</v>
       </c>
       <c r="C305" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D305" t="s">
+        <v>927</v>
+      </c>
+      <c r="E305" t="s">
         <v>928</v>
-      </c>
-      <c r="E305" t="s">
-        <v>929</v>
       </c>
       <c r="F305">
         <v>0</v>
@@ -47734,16 +47785,16 @@
         <v>0</v>
       </c>
       <c r="C306" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D306" t="s">
+        <v>929</v>
+      </c>
+      <c r="E306" t="s">
         <v>930</v>
       </c>
-      <c r="E306" t="s">
+      <c r="F306" t="s">
         <v>931</v>
-      </c>
-      <c r="F306" t="s">
-        <v>932</v>
       </c>
       <c r="G306">
         <v>45</v>
@@ -47791,16 +47842,16 @@
         <v>0</v>
       </c>
       <c r="C307" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D307" t="s">
+        <v>932</v>
+      </c>
+      <c r="E307" t="s">
         <v>933</v>
       </c>
-      <c r="E307" t="s">
+      <c r="F307" t="s">
         <v>934</v>
-      </c>
-      <c r="F307" t="s">
-        <v>935</v>
       </c>
       <c r="G307">
         <v>0</v>
@@ -47848,16 +47899,16 @@
         <v>0</v>
       </c>
       <c r="C308" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D308" t="s">
+        <v>935</v>
+      </c>
+      <c r="E308" t="s">
         <v>936</v>
       </c>
-      <c r="E308" t="s">
+      <c r="F308" t="s">
         <v>937</v>
-      </c>
-      <c r="F308" t="s">
-        <v>938</v>
       </c>
       <c r="G308">
         <v>0.1</v>
@@ -47905,16 +47956,16 @@
         <v>0</v>
       </c>
       <c r="C309" t="s">
+        <v>938</v>
+      </c>
+      <c r="D309" t="s">
         <v>939</v>
       </c>
-      <c r="D309" t="s">
+      <c r="E309" t="s">
         <v>940</v>
       </c>
-      <c r="E309" t="s">
+      <c r="F309" t="s">
         <v>941</v>
-      </c>
-      <c r="F309" t="s">
-        <v>942</v>
       </c>
       <c r="G309">
         <v>24</v>
@@ -47962,16 +48013,16 @@
         <v>0</v>
       </c>
       <c r="C310" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="D310" t="s">
+        <v>942</v>
+      </c>
+      <c r="E310" t="s">
         <v>943</v>
       </c>
-      <c r="E310" t="s">
+      <c r="F310" t="s">
         <v>944</v>
-      </c>
-      <c r="F310" t="s">
-        <v>945</v>
       </c>
       <c r="G310">
         <v>10</v>
@@ -48019,16 +48070,16 @@
         <v>0</v>
       </c>
       <c r="C311" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="D311" t="s">
+        <v>945</v>
+      </c>
+      <c r="E311" t="s">
         <v>946</v>
       </c>
-      <c r="E311" t="s">
+      <c r="F311" t="s">
         <v>947</v>
-      </c>
-      <c r="F311" t="s">
-        <v>948</v>
       </c>
       <c r="G311">
         <v>20</v>
@@ -48076,16 +48127,16 @@
         <v>0</v>
       </c>
       <c r="C312" t="s">
+        <v>948</v>
+      </c>
+      <c r="D312" t="s">
         <v>949</v>
-      </c>
-      <c r="D312" t="s">
-        <v>950</v>
       </c>
       <c r="E312" t="s">
         <v>39</v>
       </c>
       <c r="F312" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G312">
         <v>1</v>
@@ -48133,16 +48184,16 @@
         <v>0</v>
       </c>
       <c r="C313" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D313" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E313" t="s">
         <v>39</v>
       </c>
       <c r="F313" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G313">
         <v>1.35</v>
@@ -48190,16 +48241,16 @@
         <v>0</v>
       </c>
       <c r="C314" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D314" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E314" t="s">
         <v>39</v>
       </c>
       <c r="F314" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G314">
         <v>1.75</v>
@@ -48247,16 +48298,16 @@
         <v>0</v>
       </c>
       <c r="C315" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D315" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E315" t="s">
         <v>39</v>
       </c>
       <c r="F315" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G315">
         <v>2.2999999999999998</v>
@@ -48304,16 +48355,16 @@
         <v>0</v>
       </c>
       <c r="C316" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D316" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E316" t="s">
         <v>39</v>
       </c>
       <c r="F316" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G316">
         <v>3</v>
@@ -48361,16 +48412,16 @@
         <v>0</v>
       </c>
       <c r="C317" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D317" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E317" t="s">
         <v>39</v>
       </c>
       <c r="F317" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G317">
         <v>4</v>
@@ -48418,16 +48469,16 @@
         <v>0</v>
       </c>
       <c r="C318" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D318" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E318" t="s">
         <v>39</v>
       </c>
       <c r="F318" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G318">
         <v>5.2</v>
@@ -48475,16 +48526,16 @@
         <v>0</v>
       </c>
       <c r="C319" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D319" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="E319" t="s">
         <v>39</v>
       </c>
       <c r="F319" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G319">
         <v>6.8</v>
@@ -48532,16 +48583,16 @@
         <v>0</v>
       </c>
       <c r="C320" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D320" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E320" t="s">
         <v>39</v>
       </c>
       <c r="F320" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G320">
         <v>10.199999999999999</v>
@@ -48589,22 +48640,22 @@
         <v>0</v>
       </c>
       <c r="C321" t="s">
+        <v>959</v>
+      </c>
+      <c r="D321" t="s">
         <v>960</v>
       </c>
-      <c r="D321" t="s">
+      <c r="E321" t="s">
         <v>961</v>
       </c>
-      <c r="E321" t="s">
+      <c r="F321" t="s">
         <v>962</v>
-      </c>
-      <c r="F321" t="s">
-        <v>963</v>
       </c>
       <c r="G321">
         <v>25</v>
       </c>
       <c r="H321" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="I321">
         <v>0</v>
@@ -48646,22 +48697,22 @@
         <v>0</v>
       </c>
       <c r="C322" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D322" t="s">
+        <v>964</v>
+      </c>
+      <c r="E322" t="s">
+        <v>961</v>
+      </c>
+      <c r="F322" t="s">
         <v>965</v>
-      </c>
-      <c r="E322" t="s">
-        <v>962</v>
-      </c>
-      <c r="F322" t="s">
-        <v>966</v>
       </c>
       <c r="G322">
         <v>20</v>
       </c>
       <c r="H322" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="I322">
         <v>0</v>
@@ -48703,22 +48754,22 @@
         <v>0</v>
       </c>
       <c r="C323" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D323" t="s">
+        <v>966</v>
+      </c>
+      <c r="E323" t="s">
+        <v>961</v>
+      </c>
+      <c r="F323" t="s">
         <v>967</v>
-      </c>
-      <c r="E323" t="s">
-        <v>962</v>
-      </c>
-      <c r="F323" t="s">
-        <v>968</v>
       </c>
       <c r="G323">
         <v>25</v>
       </c>
       <c r="H323" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="I323">
         <v>0</v>
@@ -48760,22 +48811,22 @@
         <v>0</v>
       </c>
       <c r="C324" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D324" t="s">
+        <v>968</v>
+      </c>
+      <c r="E324" t="s">
+        <v>961</v>
+      </c>
+      <c r="F324" t="s">
         <v>969</v>
-      </c>
-      <c r="E324" t="s">
-        <v>962</v>
-      </c>
-      <c r="F324" t="s">
-        <v>970</v>
       </c>
       <c r="G324">
         <v>20</v>
       </c>
       <c r="H324" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="I324">
         <v>0</v>
@@ -48817,22 +48868,22 @@
         <v>0</v>
       </c>
       <c r="C325" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D325" t="s">
+        <v>970</v>
+      </c>
+      <c r="E325" t="s">
+        <v>961</v>
+      </c>
+      <c r="F325" t="s">
         <v>971</v>
-      </c>
-      <c r="E325" t="s">
-        <v>962</v>
-      </c>
-      <c r="F325" t="s">
-        <v>972</v>
       </c>
       <c r="G325">
         <v>0.4</v>
       </c>
       <c r="H325" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="I325">
         <v>0</v>
@@ -48874,22 +48925,22 @@
         <v>0</v>
       </c>
       <c r="C326" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D326" t="s">
+        <v>972</v>
+      </c>
+      <c r="E326" t="s">
+        <v>961</v>
+      </c>
+      <c r="F326" t="s">
         <v>973</v>
-      </c>
-      <c r="E326" t="s">
-        <v>962</v>
-      </c>
-      <c r="F326" t="s">
-        <v>974</v>
       </c>
       <c r="G326">
         <v>3</v>
       </c>
       <c r="H326" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="I326">
         <v>0</v>
@@ -48931,22 +48982,22 @@
         <v>0</v>
       </c>
       <c r="C327" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D327" t="s">
+        <v>974</v>
+      </c>
+      <c r="E327" t="s">
+        <v>961</v>
+      </c>
+      <c r="F327" t="s">
         <v>975</v>
-      </c>
-      <c r="E327" t="s">
-        <v>962</v>
-      </c>
-      <c r="F327" t="s">
-        <v>976</v>
       </c>
       <c r="G327">
         <v>1.5</v>
       </c>
       <c r="H327" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="I327">
         <v>0</v>
@@ -48988,22 +49039,22 @@
         <v>0</v>
       </c>
       <c r="C328" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D328" t="s">
+        <v>976</v>
+      </c>
+      <c r="E328" t="s">
+        <v>961</v>
+      </c>
+      <c r="F328" t="s">
         <v>977</v>
-      </c>
-      <c r="E328" t="s">
-        <v>962</v>
-      </c>
-      <c r="F328" t="s">
-        <v>978</v>
       </c>
       <c r="G328">
         <v>0.15</v>
       </c>
       <c r="H328" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="I328">
         <v>0</v>
@@ -49045,22 +49096,22 @@
         <v>0</v>
       </c>
       <c r="C329" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D329" t="s">
+        <v>978</v>
+      </c>
+      <c r="E329" t="s">
+        <v>961</v>
+      </c>
+      <c r="F329" t="s">
         <v>979</v>
-      </c>
-      <c r="E329" t="s">
-        <v>962</v>
-      </c>
-      <c r="F329" t="s">
-        <v>980</v>
       </c>
       <c r="G329">
         <v>0.5</v>
       </c>
       <c r="H329" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="I329">
         <v>0</v>
@@ -49102,22 +49153,22 @@
         <v>0</v>
       </c>
       <c r="C330" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D330" t="s">
+        <v>980</v>
+      </c>
+      <c r="E330" t="s">
+        <v>961</v>
+      </c>
+      <c r="F330" t="s">
         <v>981</v>
-      </c>
-      <c r="E330" t="s">
-        <v>962</v>
-      </c>
-      <c r="F330" t="s">
-        <v>982</v>
       </c>
       <c r="G330">
         <v>25</v>
       </c>
       <c r="H330" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="I330">
         <v>0</v>
@@ -49159,22 +49210,22 @@
         <v>0</v>
       </c>
       <c r="C331" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D331" t="s">
+        <v>982</v>
+      </c>
+      <c r="E331" t="s">
+        <v>961</v>
+      </c>
+      <c r="F331" t="s">
         <v>983</v>
-      </c>
-      <c r="E331" t="s">
-        <v>962</v>
-      </c>
-      <c r="F331" t="s">
-        <v>984</v>
       </c>
       <c r="G331">
         <v>8</v>
       </c>
       <c r="H331" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="I331">
         <v>0</v>
@@ -49216,22 +49267,22 @@
         <v>0</v>
       </c>
       <c r="C332" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="D332" t="s">
+        <v>985</v>
+      </c>
+      <c r="E332" t="s">
+        <v>961</v>
+      </c>
+      <c r="F332" t="s">
         <v>986</v>
-      </c>
-      <c r="E332" t="s">
-        <v>962</v>
-      </c>
-      <c r="F332" t="s">
-        <v>987</v>
       </c>
       <c r="G332">
         <v>15</v>
       </c>
       <c r="H332" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="I332">
         <v>0</v>
@@ -49273,16 +49324,16 @@
         <v>0</v>
       </c>
       <c r="C333" t="s">
+        <v>987</v>
+      </c>
+      <c r="D333" t="s">
         <v>988</v>
       </c>
-      <c r="D333" t="s">
+      <c r="E333" t="s">
         <v>989</v>
       </c>
-      <c r="E333" t="s">
+      <c r="F333" t="s">
         <v>990</v>
-      </c>
-      <c r="F333" t="s">
-        <v>991</v>
       </c>
       <c r="G333">
         <v>0.8</v>
@@ -49330,16 +49381,16 @@
         <v>0</v>
       </c>
       <c r="C334" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="D334" t="s">
+        <v>991</v>
+      </c>
+      <c r="E334" t="s">
         <v>992</v>
       </c>
-      <c r="E334" t="s">
+      <c r="F334" t="s">
         <v>993</v>
-      </c>
-      <c r="F334" t="s">
-        <v>994</v>
       </c>
       <c r="G334">
         <v>3</v>
@@ -49387,16 +49438,16 @@
         <v>0</v>
       </c>
       <c r="C335" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="D335" t="s">
+        <v>994</v>
+      </c>
+      <c r="E335" t="s">
         <v>995</v>
       </c>
-      <c r="E335" t="s">
+      <c r="F335" t="s">
         <v>996</v>
-      </c>
-      <c r="F335" t="s">
-        <v>997</v>
       </c>
       <c r="G335">
         <v>7</v>
@@ -49444,16 +49495,16 @@
         <v>0</v>
       </c>
       <c r="C336" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="D336" t="s">
+        <v>997</v>
+      </c>
+      <c r="E336" t="s">
         <v>998</v>
       </c>
-      <c r="E336" t="s">
+      <c r="F336" t="s">
         <v>999</v>
-      </c>
-      <c r="F336" t="s">
-        <v>1000</v>
       </c>
       <c r="G336">
         <v>10</v>
@@ -49501,16 +49552,16 @@
         <v>0</v>
       </c>
       <c r="C337" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="D337" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E337" t="s">
         <v>1001</v>
       </c>
-      <c r="E337" t="s">
+      <c r="F337" t="s">
         <v>1002</v>
-      </c>
-      <c r="F337" t="s">
-        <v>1003</v>
       </c>
       <c r="G337">
         <v>2</v>
@@ -49558,16 +49609,16 @@
         <v>0</v>
       </c>
       <c r="C338" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="D338" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E338" t="s">
         <v>1004</v>
       </c>
-      <c r="E338" t="s">
+      <c r="F338" t="s">
         <v>1005</v>
-      </c>
-      <c r="F338" t="s">
-        <v>1006</v>
       </c>
       <c r="G338">
         <v>5</v>
@@ -49615,16 +49666,16 @@
         <v>0</v>
       </c>
       <c r="C339" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="D339" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E339" t="s">
         <v>1007</v>
       </c>
-      <c r="E339" t="s">
+      <c r="F339" t="s">
         <v>1008</v>
-      </c>
-      <c r="F339" t="s">
-        <v>1009</v>
       </c>
       <c r="G339">
         <v>10</v>
@@ -49672,16 +49723,16 @@
         <v>0</v>
       </c>
       <c r="C340" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D340" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="E340" t="s">
         <v>39</v>
       </c>
       <c r="F340" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="G340">
         <v>15.3</v>
@@ -49729,16 +49780,16 @@
         <v>0</v>
       </c>
       <c r="C341" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D341" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="E341" t="s">
         <v>39</v>
       </c>
       <c r="F341" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="G341">
         <v>22.95</v>
@@ -49786,16 +49837,16 @@
         <v>0</v>
       </c>
       <c r="C342" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D342" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E342" t="s">
         <v>1013</v>
       </c>
-      <c r="E342" t="s">
+      <c r="F342" t="s">
         <v>1014</v>
-      </c>
-      <c r="F342" t="s">
-        <v>1015</v>
       </c>
       <c r="G342">
         <v>20</v>
@@ -49843,16 +49894,16 @@
         <v>0</v>
       </c>
       <c r="C343" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D343" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E343" t="s">
         <v>1016</v>
       </c>
-      <c r="E343" t="s">
+      <c r="F343" t="s">
         <v>1017</v>
-      </c>
-      <c r="F343" t="s">
-        <v>1018</v>
       </c>
       <c r="G343">
         <v>500000000</v>
@@ -49900,16 +49951,16 @@
         <v>0</v>
       </c>
       <c r="C344" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D344" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E344" t="s">
         <v>1019</v>
       </c>
-      <c r="E344" t="s">
+      <c r="F344" t="s">
         <v>1020</v>
-      </c>
-      <c r="F344" t="s">
-        <v>1021</v>
       </c>
       <c r="G344">
         <v>13</v>
@@ -49960,13 +50011,13 @@
         <v>18</v>
       </c>
       <c r="D345" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E345" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F345" t="s">
         <v>1022</v>
-      </c>
-      <c r="E345" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="F345" t="s">
-        <v>1023</v>
       </c>
       <c r="G345">
         <v>30</v>
@@ -50017,13 +50068,13 @@
         <v>18</v>
       </c>
       <c r="D346" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E346" t="s">
         <v>1024</v>
       </c>
-      <c r="E346" t="s">
+      <c r="F346" t="s">
         <v>1025</v>
-      </c>
-      <c r="F346" t="s">
-        <v>1026</v>
       </c>
       <c r="G346">
         <v>1000</v>
@@ -50071,16 +50122,16 @@
         <v>0</v>
       </c>
       <c r="C347" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D347" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E347" t="s">
         <v>1027</v>
       </c>
-      <c r="E347" t="s">
+      <c r="F347" t="s">
         <v>1028</v>
-      </c>
-      <c r="F347" t="s">
-        <v>1029</v>
       </c>
       <c r="G347">
         <v>50000</v>
@@ -50128,16 +50179,16 @@
         <v>0</v>
       </c>
       <c r="C348" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D348" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E348" t="s">
         <v>1030</v>
       </c>
-      <c r="E348" t="s">
+      <c r="F348" t="s">
         <v>1031</v>
-      </c>
-      <c r="F348" t="s">
-        <v>1032</v>
       </c>
       <c r="G348">
         <v>10</v>
@@ -50185,16 +50236,16 @@
         <v>0</v>
       </c>
       <c r="C349" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D349" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E349" t="s">
         <v>1033</v>
       </c>
-      <c r="E349" t="s">
+      <c r="F349" t="s">
         <v>1034</v>
-      </c>
-      <c r="F349" t="s">
-        <v>1035</v>
       </c>
       <c r="G349">
         <v>75</v>
@@ -50242,16 +50293,16 @@
         <v>0</v>
       </c>
       <c r="C350" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D350" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E350" t="s">
         <v>1036</v>
       </c>
-      <c r="E350" t="s">
+      <c r="F350" t="s">
         <v>1037</v>
-      </c>
-      <c r="F350" t="s">
-        <v>1038</v>
       </c>
       <c r="G350">
         <v>25</v>
@@ -50299,16 +50350,16 @@
         <v>0</v>
       </c>
       <c r="C351" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D351" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E351" t="s">
+        <v>930</v>
+      </c>
+      <c r="F351" t="s">
         <v>1039</v>
-      </c>
-      <c r="E351" t="s">
-        <v>931</v>
-      </c>
-      <c r="F351" t="s">
-        <v>1040</v>
       </c>
       <c r="G351">
         <v>5</v>
@@ -50356,16 +50407,16 @@
         <v>0</v>
       </c>
       <c r="C352" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D352" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E352" t="s">
         <v>1041</v>
       </c>
-      <c r="E352" t="s">
+      <c r="F352" t="s">
         <v>1042</v>
-      </c>
-      <c r="F352" t="s">
-        <v>1043</v>
       </c>
       <c r="G352">
         <v>0.6</v>
@@ -50413,16 +50464,16 @@
         <v>0</v>
       </c>
       <c r="C353" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D353" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E353" t="s">
         <v>1044</v>
       </c>
-      <c r="E353" t="s">
+      <c r="F353" t="s">
         <v>1045</v>
-      </c>
-      <c r="F353" t="s">
-        <v>1046</v>
       </c>
       <c r="G353">
         <v>0.1</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D113D3EE-47BF-403C-8933-2145359BE75B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96945834-3732-4045-AA6E-9A7E1CEAA2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11458,23 +11458,23 @@
       </c>
       <c r="G98">
         <f>計算表!G98</f>
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="H98">
         <f>計算表!H98</f>
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="I98">
         <f>計算表!I98</f>
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="J98">
         <f>計算表!J98</f>
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="K98">
         <f>計算表!K98</f>
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L98">
         <f>計算表!L98</f>
@@ -35941,19 +35941,19 @@
         <v>284</v>
       </c>
       <c r="G98">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="H98">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="I98">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="J98">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="K98">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L98">
         <v>0</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96945834-3732-4045-AA6E-9A7E1CEAA2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9361F57-4AAA-4334-89F6-B6F5C226E5C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="G2">
         <f>計算表!G2</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H2">
         <f>計算表!H2</f>
@@ -30469,7 +30469,7 @@
         <v>21</v>
       </c>
       <c r="G2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H2">
         <v>3</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\Idle-RPG\antigravity\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9361F57-4AAA-4334-89F6-B6F5C226E5C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4C3275B-B450-459D-8DC6-81D4A66FCC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -4266,12 +4266,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R353"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="6" width="23.85546875" customWidth="1"/>
+    <col min="3" max="6" width="23.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4327,7 +4327,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2">
         <f>計算表!A2</f>
         <v>1</v>
@@ -4401,7 +4401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>計算表!A3</f>
         <v>2</v>
@@ -4475,7 +4475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>計算表!A4</f>
         <v>3</v>
@@ -4549,7 +4549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>計算表!A5</f>
         <v>4</v>
@@ -4623,7 +4623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>計算表!A6</f>
         <v>5</v>
@@ -4697,7 +4697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>計算表!A7</f>
         <v>6</v>
@@ -4771,7 +4771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>計算表!A8</f>
         <v>7</v>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>計算表!A9</f>
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>計算表!A10</f>
         <v>9</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>計算表!A11</f>
         <v>10</v>
@@ -5067,7 +5067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>計算表!A12</f>
         <v>11</v>
@@ -5141,7 +5141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>計算表!A13</f>
         <v>12</v>
@@ -5215,7 +5215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>計算表!A14</f>
         <v>13</v>
@@ -5289,7 +5289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>計算表!A15</f>
         <v>14</v>
@@ -5363,7 +5363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>計算表!A16</f>
         <v>15</v>
@@ -5437,7 +5437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>計算表!A17</f>
         <v>16</v>
@@ -5511,7 +5511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>計算表!A18</f>
         <v>17</v>
@@ -5585,7 +5585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>計算表!A19</f>
         <v>18</v>
@@ -5659,7 +5659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>計算表!A20</f>
         <v>19</v>
@@ -5733,7 +5733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>計算表!A21</f>
         <v>20</v>
@@ -5807,7 +5807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>計算表!A22</f>
         <v>21</v>
@@ -5881,7 +5881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>計算表!A23</f>
         <v>22</v>
@@ -5955,7 +5955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>計算表!A24</f>
         <v>23</v>
@@ -6029,7 +6029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>計算表!A25</f>
         <v>24</v>
@@ -6103,7 +6103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>計算表!A26</f>
         <v>25</v>
@@ -6177,7 +6177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>計算表!A27</f>
         <v>26</v>
@@ -6251,7 +6251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>計算表!A28</f>
         <v>27</v>
@@ -6325,7 +6325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>計算表!A29</f>
         <v>28</v>
@@ -6399,7 +6399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>計算表!A30</f>
         <v>29</v>
@@ -6473,7 +6473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>計算表!A31</f>
         <v>30</v>
@@ -6547,7 +6547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>計算表!A32</f>
         <v>31</v>
@@ -6621,7 +6621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>計算表!A33</f>
         <v>32</v>
@@ -6695,7 +6695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>計算表!A34</f>
         <v>33</v>
@@ -6769,7 +6769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35">
         <f>計算表!A35</f>
         <v>34</v>
@@ -6843,7 +6843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36">
         <f>計算表!A36</f>
         <v>35</v>
@@ -6917,7 +6917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37">
         <f>計算表!A37</f>
         <v>36</v>
@@ -6991,7 +6991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38">
         <f>計算表!A38</f>
         <v>37</v>
@@ -7065,7 +7065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39">
         <f>計算表!A39</f>
         <v>38</v>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40">
         <f>計算表!A40</f>
         <v>39</v>
@@ -7213,7 +7213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41">
         <f>計算表!A41</f>
         <v>40</v>
@@ -7287,7 +7287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42">
         <f>計算表!A42</f>
         <v>41</v>
@@ -7361,7 +7361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43">
         <f>計算表!A43</f>
         <v>42</v>
@@ -7435,7 +7435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44">
         <f>計算表!A44</f>
         <v>43</v>
@@ -7509,7 +7509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45">
         <f>計算表!A45</f>
         <v>44</v>
@@ -7583,7 +7583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46">
         <f>計算表!A46</f>
         <v>45</v>
@@ -7657,7 +7657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47">
         <f>計算表!A47</f>
         <v>46</v>
@@ -7731,7 +7731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48">
         <f>計算表!A48</f>
         <v>47</v>
@@ -7805,7 +7805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49">
         <f>計算表!A49</f>
         <v>48</v>
@@ -7879,7 +7879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50">
         <f>計算表!A50</f>
         <v>49</v>
@@ -7953,7 +7953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51">
         <f>計算表!A51</f>
         <v>50</v>
@@ -8027,7 +8027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52">
         <f>計算表!A52</f>
         <v>51</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53">
         <f>計算表!A53</f>
         <v>52</v>
@@ -8175,7 +8175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54">
         <f>計算表!A54</f>
         <v>53</v>
@@ -8249,7 +8249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55">
         <f>計算表!A55</f>
         <v>54</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56">
         <f>計算表!A56</f>
         <v>55</v>
@@ -8397,7 +8397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57">
         <f>計算表!A57</f>
         <v>56</v>
@@ -8471,7 +8471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58">
         <f>計算表!A58</f>
         <v>57</v>
@@ -8545,7 +8545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59">
         <f>計算表!A59</f>
         <v>58</v>
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60">
         <f>計算表!A60</f>
         <v>59</v>
@@ -8693,7 +8693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61">
         <f>計算表!A61</f>
         <v>60</v>
@@ -8767,7 +8767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62">
         <f>計算表!A62</f>
         <v>61</v>
@@ -8841,7 +8841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63">
         <f>計算表!A63</f>
         <v>62</v>
@@ -8915,7 +8915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64">
         <f>計算表!A64</f>
         <v>63</v>
@@ -8989,7 +8989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65">
         <f>計算表!A65</f>
         <v>64</v>
@@ -9016,11 +9016,11 @@
       </c>
       <c r="G65">
         <f>計算表!G65</f>
-        <v>60</v>
+        <v>10000</v>
       </c>
       <c r="H65">
         <f>計算表!H65</f>
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="I65">
         <f>計算表!I65</f>
@@ -9063,7 +9063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66">
         <f>計算表!A66</f>
         <v>65</v>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="G66">
         <f>計算表!G66</f>
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="H66">
         <f>計算表!H66</f>
@@ -9137,7 +9137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67">
         <f>計算表!A67</f>
         <v>66</v>
@@ -9164,11 +9164,11 @@
       </c>
       <c r="G67">
         <f>計算表!G67</f>
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="H67">
         <f>計算表!H67</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I67">
         <f>計算表!I67</f>
@@ -9211,7 +9211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68">
         <f>計算表!A68</f>
         <v>67</v>
@@ -9238,11 +9238,11 @@
       </c>
       <c r="G68">
         <f>計算表!G68</f>
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="H68">
         <f>計算表!H68</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I68">
         <f>計算表!I68</f>
@@ -9285,7 +9285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69">
         <f>計算表!A69</f>
         <v>68</v>
@@ -9312,11 +9312,11 @@
       </c>
       <c r="G69">
         <f>計算表!G69</f>
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="H69">
         <f>計算表!H69</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I69">
         <f>計算表!I69</f>
@@ -9359,7 +9359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70">
         <f>計算表!A70</f>
         <v>69</v>
@@ -9433,7 +9433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A71">
         <f>計算表!A71</f>
         <v>70</v>
@@ -9507,7 +9507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72">
         <f>計算表!A72</f>
         <v>71</v>
@@ -9581,7 +9581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A73">
         <f>計算表!A73</f>
         <v>72</v>
@@ -9655,7 +9655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74">
         <f>計算表!A74</f>
         <v>73</v>
@@ -9729,7 +9729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75">
         <f>計算表!A75</f>
         <v>74</v>
@@ -9803,7 +9803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76">
         <f>計算表!A76</f>
         <v>75</v>
@@ -9877,7 +9877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77">
         <f>計算表!A77</f>
         <v>76</v>
@@ -9951,7 +9951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78">
         <f>計算表!A78</f>
         <v>77</v>
@@ -10025,7 +10025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79">
         <f>計算表!A79</f>
         <v>78</v>
@@ -10099,7 +10099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80">
         <f>計算表!A80</f>
         <v>79</v>
@@ -10173,7 +10173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81">
         <f>計算表!A81</f>
         <v>80</v>
@@ -10247,7 +10247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82">
         <f>計算表!A82</f>
         <v>81</v>
@@ -10321,7 +10321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83">
         <f>計算表!A83</f>
         <v>82</v>
@@ -10395,7 +10395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84">
         <f>計算表!A84</f>
         <v>83</v>
@@ -10469,7 +10469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85">
         <f>計算表!A85</f>
         <v>84</v>
@@ -10543,7 +10543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86">
         <f>計算表!A86</f>
         <v>85</v>
@@ -10617,7 +10617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87">
         <f>計算表!A87</f>
         <v>86</v>
@@ -10691,7 +10691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88">
         <f>計算表!A88</f>
         <v>87</v>
@@ -10765,7 +10765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89">
         <f>計算表!A89</f>
         <v>88</v>
@@ -10839,7 +10839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90">
         <f>計算表!A90</f>
         <v>89</v>
@@ -10913,7 +10913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91">
         <f>計算表!A91</f>
         <v>90</v>
@@ -10987,7 +10987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92">
         <f>計算表!A92</f>
         <v>91</v>
@@ -11061,7 +11061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93">
         <f>計算表!A93</f>
         <v>92</v>
@@ -11135,7 +11135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94">
         <f>計算表!A94</f>
         <v>93</v>
@@ -11209,7 +11209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95">
         <f>計算表!A95</f>
         <v>94</v>
@@ -11283,7 +11283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96">
         <f>計算表!A96</f>
         <v>95</v>
@@ -11357,7 +11357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97">
         <f>計算表!A97</f>
         <v>96</v>
@@ -11431,7 +11431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98">
         <f>計算表!A98</f>
         <v>97</v>
@@ -11505,7 +11505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A99">
         <f>計算表!A99</f>
         <v>98</v>
@@ -11579,7 +11579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100">
         <f>計算表!A100</f>
         <v>99</v>
@@ -11653,7 +11653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101">
         <f>計算表!A101</f>
         <v>100</v>
@@ -11727,7 +11727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102">
         <f>計算表!A102</f>
         <v>101</v>
@@ -11801,7 +11801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103">
         <f>計算表!A103</f>
         <v>102</v>
@@ -11875,7 +11875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A104">
         <f>計算表!A104</f>
         <v>103</v>
@@ -11949,7 +11949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A105">
         <f>計算表!A105</f>
         <v>104</v>
@@ -12023,7 +12023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A106">
         <f>計算表!A106</f>
         <v>105</v>
@@ -12097,7 +12097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A107">
         <f>計算表!A107</f>
         <v>106</v>
@@ -12171,7 +12171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A108">
         <f>計算表!A108</f>
         <v>107</v>
@@ -12245,7 +12245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A109">
         <f>計算表!A109</f>
         <v>108</v>
@@ -12319,7 +12319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A110">
         <f>計算表!A110</f>
         <v>109</v>
@@ -12393,7 +12393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A111">
         <f>計算表!A111</f>
         <v>110</v>
@@ -12467,7 +12467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A112">
         <f>計算表!A112</f>
         <v>111</v>
@@ -12541,7 +12541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A113">
         <f>計算表!A113</f>
         <v>112</v>
@@ -12615,7 +12615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A114">
         <f>計算表!A114</f>
         <v>113</v>
@@ -12689,7 +12689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A115">
         <f>計算表!A115</f>
         <v>114</v>
@@ -12763,7 +12763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A116">
         <f>計算表!A116</f>
         <v>115</v>
@@ -12837,7 +12837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A117">
         <f>計算表!A117</f>
         <v>116</v>
@@ -12911,7 +12911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A118">
         <f>計算表!A118</f>
         <v>117</v>
@@ -12985,7 +12985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A119">
         <f>計算表!A119</f>
         <v>118</v>
@@ -13059,7 +13059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A120">
         <f>計算表!A120</f>
         <v>119</v>
@@ -13133,7 +13133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A121">
         <f>計算表!A121</f>
         <v>120</v>
@@ -13207,7 +13207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A122">
         <f>計算表!A122</f>
         <v>121</v>
@@ -13281,7 +13281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A123">
         <f>計算表!A123</f>
         <v>122</v>
@@ -13355,7 +13355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A124">
         <f>計算表!A124</f>
         <v>123</v>
@@ -13429,7 +13429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A125">
         <f>計算表!A125</f>
         <v>124</v>
@@ -13503,7 +13503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A126">
         <f>計算表!A126</f>
         <v>125</v>
@@ -13577,7 +13577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A127">
         <f>計算表!A127</f>
         <v>126</v>
@@ -13651,7 +13651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A128">
         <f>計算表!A128</f>
         <v>127</v>
@@ -13725,7 +13725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A129">
         <f>計算表!A129</f>
         <v>128</v>
@@ -13799,7 +13799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A130">
         <f>計算表!A130</f>
         <v>129</v>
@@ -13873,7 +13873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A131">
         <f>計算表!A131</f>
         <v>130</v>
@@ -13947,7 +13947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A132">
         <f>計算表!A132</f>
         <v>131</v>
@@ -14021,7 +14021,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A133">
         <f>計算表!A133</f>
         <v>132</v>
@@ -14095,7 +14095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A134">
         <f>計算表!A134</f>
         <v>133</v>
@@ -14169,7 +14169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A135">
         <f>計算表!A135</f>
         <v>134</v>
@@ -14243,7 +14243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A136">
         <f>計算表!A136</f>
         <v>135</v>
@@ -14317,7 +14317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A137">
         <f>計算表!A137</f>
         <v>136</v>
@@ -14391,7 +14391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A138">
         <f>計算表!A138</f>
         <v>137</v>
@@ -14465,7 +14465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A139">
         <f>計算表!A139</f>
         <v>138</v>
@@ -14539,7 +14539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A140">
         <f>計算表!A140</f>
         <v>139</v>
@@ -14613,7 +14613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A141">
         <f>計算表!A141</f>
         <v>140</v>
@@ -14687,7 +14687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A142">
         <f>計算表!A142</f>
         <v>141</v>
@@ -14761,7 +14761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A143">
         <f>計算表!A143</f>
         <v>142</v>
@@ -14835,7 +14835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A144">
         <f>計算表!A144</f>
         <v>143</v>
@@ -14909,7 +14909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A145">
         <f>計算表!A145</f>
         <v>144</v>
@@ -14983,7 +14983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A146">
         <f>計算表!A146</f>
         <v>145</v>
@@ -15057,7 +15057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A147">
         <f>計算表!A147</f>
         <v>146</v>
@@ -15131,7 +15131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A148">
         <f>計算表!A148</f>
         <v>147</v>
@@ -15205,7 +15205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A149">
         <f>計算表!A149</f>
         <v>148</v>
@@ -15279,7 +15279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A150">
         <f>計算表!A150</f>
         <v>149</v>
@@ -15353,7 +15353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A151">
         <f>計算表!A151</f>
         <v>150</v>
@@ -15427,7 +15427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A152">
         <f>計算表!A152</f>
         <v>151</v>
@@ -15501,7 +15501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A153">
         <f>計算表!A153</f>
         <v>152</v>
@@ -15575,7 +15575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A154">
         <f>計算表!A154</f>
         <v>153</v>
@@ -15649,7 +15649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A155">
         <f>計算表!A155</f>
         <v>154</v>
@@ -15723,7 +15723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A156">
         <f>計算表!A156</f>
         <v>155</v>
@@ -15797,7 +15797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A157">
         <f>計算表!A157</f>
         <v>156</v>
@@ -15871,7 +15871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A158">
         <f>計算表!A158</f>
         <v>157</v>
@@ -15945,7 +15945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A159">
         <f>計算表!A159</f>
         <v>158</v>
@@ -16019,7 +16019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A160">
         <f>計算表!A160</f>
         <v>159</v>
@@ -16093,7 +16093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A161">
         <f>計算表!A161</f>
         <v>160</v>
@@ -16167,7 +16167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A162">
         <f>計算表!A162</f>
         <v>161</v>
@@ -16241,7 +16241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A163">
         <f>計算表!A163</f>
         <v>162</v>
@@ -16315,7 +16315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A164">
         <f>計算表!A164</f>
         <v>163</v>
@@ -16389,7 +16389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A165">
         <f>計算表!A165</f>
         <v>164</v>
@@ -16463,7 +16463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A166">
         <f>計算表!A166</f>
         <v>165</v>
@@ -16537,7 +16537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A167">
         <f>計算表!A167</f>
         <v>166</v>
@@ -16611,7 +16611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A168">
         <f>計算表!A168</f>
         <v>167</v>
@@ -16685,7 +16685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A169">
         <f>計算表!A169</f>
         <v>168</v>
@@ -16759,7 +16759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A170">
         <f>計算表!A170</f>
         <v>169</v>
@@ -16833,7 +16833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A171">
         <f>計算表!A171</f>
         <v>170</v>
@@ -16907,7 +16907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A172">
         <f>計算表!A172</f>
         <v>171</v>
@@ -16981,7 +16981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A173">
         <f>計算表!A173</f>
         <v>172</v>
@@ -17055,7 +17055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A174">
         <f>計算表!A174</f>
         <v>173</v>
@@ -17129,7 +17129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A175">
         <f>計算表!A175</f>
         <v>174</v>
@@ -17203,7 +17203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A176">
         <f>計算表!A176</f>
         <v>175</v>
@@ -17277,7 +17277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A177">
         <f>計算表!A177</f>
         <v>176</v>
@@ -17351,7 +17351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A178">
         <f>計算表!A178</f>
         <v>177</v>
@@ -17425,7 +17425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A179">
         <f>計算表!A179</f>
         <v>178</v>
@@ -17499,7 +17499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A180">
         <f>計算表!A180</f>
         <v>179</v>
@@ -17573,7 +17573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A181">
         <f>計算表!A181</f>
         <v>180</v>
@@ -17647,7 +17647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A182">
         <f>計算表!A182</f>
         <v>181</v>
@@ -17721,7 +17721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A183">
         <f>計算表!A183</f>
         <v>182</v>
@@ -17795,7 +17795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A184">
         <f>計算表!A184</f>
         <v>183</v>
@@ -17869,7 +17869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A185">
         <f>計算表!A185</f>
         <v>184</v>
@@ -17943,7 +17943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A186">
         <f>計算表!A186</f>
         <v>185</v>
@@ -18017,7 +18017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A187">
         <f>計算表!A187</f>
         <v>186</v>
@@ -18091,7 +18091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A188">
         <f>計算表!A188</f>
         <v>187</v>
@@ -18165,7 +18165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A189">
         <f>計算表!A189</f>
         <v>188</v>
@@ -18239,7 +18239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A190">
         <f>計算表!A190</f>
         <v>189</v>
@@ -18313,7 +18313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A191">
         <f>計算表!A191</f>
         <v>190</v>
@@ -18387,7 +18387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A192">
         <f>計算表!A192</f>
         <v>191</v>
@@ -18461,7 +18461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A193">
         <f>計算表!A193</f>
         <v>192</v>
@@ -18535,7 +18535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A194">
         <f>計算表!A194</f>
         <v>193</v>
@@ -18609,7 +18609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A195">
         <f>計算表!A195</f>
         <v>194</v>
@@ -18683,7 +18683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A196">
         <f>計算表!A196</f>
         <v>195</v>
@@ -18757,7 +18757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A197">
         <f>計算表!A197</f>
         <v>196</v>
@@ -18831,7 +18831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A198">
         <f>計算表!A198</f>
         <v>197</v>
@@ -18905,7 +18905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A199">
         <f>計算表!A199</f>
         <v>198</v>
@@ -18979,7 +18979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A200">
         <f>計算表!A200</f>
         <v>199</v>
@@ -19053,7 +19053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A201">
         <f>計算表!A201</f>
         <v>200</v>
@@ -19127,7 +19127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A202">
         <f>計算表!A202</f>
         <v>201</v>
@@ -19201,7 +19201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A203">
         <f>計算表!A203</f>
         <v>202</v>
@@ -19275,7 +19275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A204">
         <f>計算表!A204</f>
         <v>203</v>
@@ -19349,7 +19349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A205">
         <f>計算表!A205</f>
         <v>204</v>
@@ -19423,7 +19423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A206">
         <f>計算表!A206</f>
         <v>205</v>
@@ -19497,7 +19497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A207">
         <f>計算表!A207</f>
         <v>206</v>
@@ -19571,7 +19571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A208">
         <f>計算表!A208</f>
         <v>207</v>
@@ -19645,7 +19645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A209">
         <f>計算表!A209</f>
         <v>208</v>
@@ -19719,7 +19719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A210">
         <f>計算表!A210</f>
         <v>209</v>
@@ -19793,7 +19793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A211">
         <f>計算表!A211</f>
         <v>210</v>
@@ -19867,7 +19867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A212">
         <f>計算表!A212</f>
         <v>211</v>
@@ -19941,7 +19941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A213">
         <f>計算表!A213</f>
         <v>212</v>
@@ -20015,7 +20015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A214">
         <f>計算表!A214</f>
         <v>213</v>
@@ -20089,7 +20089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A215">
         <f>計算表!A215</f>
         <v>214</v>
@@ -20163,7 +20163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A216">
         <f>計算表!A216</f>
         <v>215</v>
@@ -20237,7 +20237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A217">
         <f>計算表!A217</f>
         <v>216</v>
@@ -20311,7 +20311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A218">
         <f>計算表!A218</f>
         <v>217</v>
@@ -20385,7 +20385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A219">
         <f>計算表!A219</f>
         <v>218</v>
@@ -20459,7 +20459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A220">
         <f>計算表!A220</f>
         <v>219</v>
@@ -20533,7 +20533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A221">
         <f>計算表!A221</f>
         <v>220</v>
@@ -20607,7 +20607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A222">
         <f>計算表!A222</f>
         <v>221</v>
@@ -20681,7 +20681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A223">
         <f>計算表!A223</f>
         <v>222</v>
@@ -20755,7 +20755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A224">
         <f>計算表!A224</f>
         <v>223</v>
@@ -20829,7 +20829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A225">
         <f>計算表!A225</f>
         <v>224</v>
@@ -20903,7 +20903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A226">
         <f>計算表!A226</f>
         <v>225</v>
@@ -20977,7 +20977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A227">
         <f>計算表!A227</f>
         <v>226</v>
@@ -21051,7 +21051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A228">
         <f>計算表!A228</f>
         <v>227</v>
@@ -21125,7 +21125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A229">
         <f>計算表!A229</f>
         <v>228</v>
@@ -21199,7 +21199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A230">
         <f>計算表!A230</f>
         <v>229</v>
@@ -21273,7 +21273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A231">
         <f>計算表!A231</f>
         <v>230</v>
@@ -21347,7 +21347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A232">
         <f>計算表!A232</f>
         <v>231</v>
@@ -21421,7 +21421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A233">
         <f>計算表!A233</f>
         <v>232</v>
@@ -21495,7 +21495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A234">
         <f>計算表!A234</f>
         <v>233</v>
@@ -21569,7 +21569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A235">
         <f>計算表!A235</f>
         <v>234</v>
@@ -21643,7 +21643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A236">
         <f>計算表!A236</f>
         <v>235</v>
@@ -21717,7 +21717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A237">
         <f>計算表!A237</f>
         <v>236</v>
@@ -21791,7 +21791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A238">
         <f>計算表!A238</f>
         <v>237</v>
@@ -21865,7 +21865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A239">
         <f>計算表!A239</f>
         <v>238</v>
@@ -21939,7 +21939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A240">
         <f>計算表!A240</f>
         <v>239</v>
@@ -22013,7 +22013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A241">
         <f>計算表!A241</f>
         <v>240</v>
@@ -22087,7 +22087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A242">
         <f>計算表!A242</f>
         <v>241</v>
@@ -22161,7 +22161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A243">
         <f>計算表!A243</f>
         <v>242</v>
@@ -22235,7 +22235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A244">
         <f>計算表!A244</f>
         <v>243</v>
@@ -22309,7 +22309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A245">
         <f>計算表!A245</f>
         <v>244</v>
@@ -22383,7 +22383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A246">
         <f>計算表!A246</f>
         <v>245</v>
@@ -22457,7 +22457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A247">
         <f>計算表!A247</f>
         <v>246</v>
@@ -22531,7 +22531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A248">
         <f>計算表!A248</f>
         <v>247</v>
@@ -22605,7 +22605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A249">
         <f>計算表!A249</f>
         <v>248</v>
@@ -22679,7 +22679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A250">
         <f>計算表!A250</f>
         <v>249</v>
@@ -22753,7 +22753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A251">
         <f>計算表!A251</f>
         <v>250</v>
@@ -22827,7 +22827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A252">
         <f>計算表!A252</f>
         <v>251</v>
@@ -22901,7 +22901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A253">
         <f>計算表!A253</f>
         <v>252</v>
@@ -22975,7 +22975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A254">
         <f>計算表!A254</f>
         <v>253</v>
@@ -23049,7 +23049,7 @@
         <v>0</v>
       </c>
     </